--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -1,64 +1,68 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\hall\resources\sample\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E47C1B-BA24-4765-AC11-CFC6213D4203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="794" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Warehouse" sheetId="42" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>最小准入金币</t>
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>-1 表示无上限</t>
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -67,7 +71,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -205,8 +208,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -217,14 +226,12 @@
     <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -232,64 +239,195 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Noto Sans CJK SC Regular"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -298,12 +436,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7993408001953185"/>
+        <fgColor theme="5" tint="0.799340800195319"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -326,30 +650,272 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="12">
+  <cellStyleXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -357,7 +923,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -375,35 +941,82 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="12">
+  <cellStyles count="60">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="常规 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="常规 2 2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
-    <cellStyle name="常规 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
-    <cellStyle name="常规 3 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
-    <cellStyle name="常规 4" xfId="6" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
-    <cellStyle name="常规 5" xfId="7" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
-    <cellStyle name="常规 6" xfId="8" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
-    <cellStyle name="常规 6 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
-    <cellStyle name="常规 6 2 2" xfId="10" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
-    <cellStyle name="常规 7" xfId="11" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
+    <cellStyle name="常规 2 2" xfId="50"/>
+    <cellStyle name="常规 2 2 2" xfId="51"/>
+    <cellStyle name="常规 3" xfId="52"/>
+    <cellStyle name="常规 3 2" xfId="53"/>
+    <cellStyle name="常规 4" xfId="54"/>
+    <cellStyle name="常规 5" xfId="55"/>
+    <cellStyle name="常规 6" xfId="56"/>
+    <cellStyle name="常规 6 2" xfId="57"/>
+    <cellStyle name="常规 6 2 2" xfId="58"/>
+    <cellStyle name="常规 7" xfId="59"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -661,13 +1274,13 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M40"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="9.375" style="1"/>
@@ -682,7 +1295,7 @@
     <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="16.5">
+    <row r="1" ht="16.5" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -717,7 +1330,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="16.5">
+    <row r="2" ht="16.5" spans="1:11">
       <c r="A2" s="4" t="s">
         <v>9</v>
       </c>
@@ -746,7 +1359,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="16.5">
+    <row r="3" ht="16.5" spans="1:11">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
@@ -772,7 +1385,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="16.5">
+    <row r="5" ht="16.5" spans="1:11">
       <c r="A5" s="1">
         <f>B5*10+E5</f>
         <v>1001001</v>
@@ -801,14 +1414,14 @@
       <c r="I5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="J5" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K5">
         <v>1000</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="16.5">
+    <row r="6" ht="16.5" spans="1:11">
       <c r="A6" s="1">
         <f t="shared" ref="A6:A40" si="0">B6*10+E6</f>
         <v>1001002</v>
@@ -838,14 +1451,14 @@
       <c r="I6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="J6" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K6">
         <v>100000</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="16.5">
+    <row r="7" ht="16.5" spans="1:11">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>1001003</v>
@@ -875,14 +1488,14 @@
       <c r="I7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="J7" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K7">
         <v>10000000</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="16.5">
+    <row r="8" ht="16.5" spans="1:11">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>2001001</v>
@@ -911,14 +1524,14 @@
       <c r="I8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="J8" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K8">
         <v>500</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="16.5">
+    <row r="9" ht="16.5" spans="1:11">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>2001002</v>
@@ -948,14 +1561,14 @@
       <c r="I9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J9" s="9" t="s">
+      <c r="J9" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K9">
         <v>20000</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="16.5">
+    <row r="10" ht="16.5" spans="1:11">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>2001003</v>
@@ -985,14 +1598,14 @@
       <c r="I10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J10" s="9" t="s">
+      <c r="J10" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K10">
         <v>2000000</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="16.5">
+    <row r="11" ht="16.5" spans="1:11">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>2001011</v>
@@ -1021,14 +1634,14 @@
       <c r="I11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="9" t="s">
+      <c r="J11" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K11">
         <v>500</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="16.5">
+    <row r="12" ht="16.5" spans="1:11">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>2001012</v>
@@ -1058,14 +1671,14 @@
       <c r="I12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J12" s="9" t="s">
+      <c r="J12" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K12">
         <v>20000</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="16.5">
+    <row r="13" ht="16.5" spans="1:11">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>2001013</v>
@@ -1095,14 +1708,14 @@
       <c r="I13" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J13" s="9" t="s">
+      <c r="J13" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K13">
         <v>2000000</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="16.5">
+    <row r="14" ht="16.5" spans="1:11">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>2003001</v>
@@ -1131,14 +1744,14 @@
       <c r="I14" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J14" s="9" t="s">
+      <c r="J14" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K14">
         <v>500</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="16.5">
+    <row r="15" ht="16.5" spans="1:11">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>2003002</v>
@@ -1168,14 +1781,14 @@
       <c r="I15" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J15" s="9" t="s">
+      <c r="J15" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K15">
         <v>20000</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="16.5">
+    <row r="16" ht="16.5" spans="1:11">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>2003003</v>
@@ -1205,14 +1818,14 @@
       <c r="I16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J16" s="9" t="s">
+      <c r="J16" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K16">
         <v>2000000</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="16.5">
+    <row r="17" ht="16.5" spans="1:11">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>2004001</v>
@@ -1241,14 +1854,14 @@
       <c r="I17" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J17" s="9" t="s">
+      <c r="J17" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K17">
         <v>500</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="16.5">
+    <row r="18" ht="16.5" spans="1:11">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>2004002</v>
@@ -1278,14 +1891,14 @@
       <c r="I18" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J18" s="9" t="s">
+      <c r="J18" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K18">
         <v>20000</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="16.5">
+    <row r="19" ht="16.5" spans="1:11">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>2004003</v>
@@ -1315,14 +1928,14 @@
       <c r="I19" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J19" s="9" t="s">
+      <c r="J19" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K19">
         <v>2000000</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="16.5">
+    <row r="20" ht="16.5" spans="1:11">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>2005001</v>
@@ -1340,25 +1953,25 @@
         <v>1</v>
       </c>
       <c r="F20" s="1">
-        <v>100</v>
+        <v>-1</v>
       </c>
       <c r="G20" s="1">
-        <v>5000000</v>
+        <v>-1</v>
       </c>
       <c r="H20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J20" s="9" t="s">
+      <c r="J20" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K20">
         <v>500</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="16.5">
+    <row r="21" ht="16.5" spans="1:11">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>2005002</v>
@@ -1376,25 +1989,25 @@
         <v>2</v>
       </c>
       <c r="F21" s="1">
-        <v>10000</v>
+        <v>-1</v>
       </c>
       <c r="G21" s="1">
-        <v>500000000</v>
+        <v>-1</v>
       </c>
       <c r="H21" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J21" s="9" t="s">
+      <c r="J21" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K21">
         <v>20000</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="16.5">
+    <row r="22" ht="16.5" spans="1:11">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>2005003</v>
@@ -1412,25 +2025,25 @@
         <v>3</v>
       </c>
       <c r="F22" s="1">
-        <v>1000000</v>
+        <v>-1</v>
       </c>
       <c r="G22" s="1">
         <v>-1</v>
       </c>
       <c r="H22" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J22" s="9" t="s">
+      <c r="J22" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K22">
         <v>2000000</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="16.5">
+    <row r="23" ht="16.5" spans="1:11">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>2006001</v>
@@ -1459,14 +2072,14 @@
       <c r="I23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J23" s="9" t="s">
+      <c r="J23" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K23">
         <v>500</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="16.5">
+    <row r="24" ht="16.5" spans="1:11">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>2006002</v>
@@ -1496,14 +2109,14 @@
       <c r="I24" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J24" s="9" t="s">
+      <c r="J24" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K24">
         <v>20000</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="16.5">
+    <row r="25" ht="16.5" spans="1:11">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>2006003</v>
@@ -1533,14 +2146,14 @@
       <c r="I25" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J25" s="9" t="s">
+      <c r="J25" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K25">
         <v>2000000</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="16.5">
+    <row r="26" ht="16.5" spans="1:11">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>2007001</v>
@@ -1569,14 +2182,14 @@
       <c r="I26" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J26" s="9" t="s">
+      <c r="J26" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K26">
         <v>500</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="16.5">
+    <row r="27" ht="16.5" spans="1:11">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>2007002</v>
@@ -1606,14 +2219,14 @@
       <c r="I27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J27" s="9" t="s">
+      <c r="J27" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K27">
         <v>20000</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="16.5">
+    <row r="28" ht="16.5" spans="1:11">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
         <v>2007003</v>
@@ -1643,14 +2256,14 @@
       <c r="I28" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J28" s="9" t="s">
+      <c r="J28" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K28">
         <v>2000000</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="16.5">
+    <row r="29" ht="16.5" spans="1:11">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
         <v>2008001</v>
@@ -1679,14 +2292,14 @@
       <c r="I29" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J29" s="9" t="s">
+      <c r="J29" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K29">
         <v>500</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="16.5">
+    <row r="30" ht="16.5" spans="1:11">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
         <v>2008002</v>
@@ -1715,14 +2328,14 @@
       <c r="I30" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J30" s="9" t="s">
+      <c r="J30" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K30">
         <v>20000</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="16.5">
+    <row r="31" ht="16.5" spans="1:11">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
         <v>2008003</v>
@@ -1751,14 +2364,14 @@
       <c r="I31" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J31" s="9" t="s">
+      <c r="J31" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K31">
         <v>2000000</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="16.5">
+    <row r="32" ht="16.5" spans="1:11">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
         <v>2009001</v>
@@ -1787,14 +2400,14 @@
       <c r="I32" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J32" s="9" t="s">
+      <c r="J32" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K32">
         <v>500</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="16.5">
+    <row r="33" ht="16.5" spans="1:11">
       <c r="A33" s="1">
         <f t="shared" si="0"/>
         <v>2009002</v>
@@ -1824,14 +2437,14 @@
       <c r="I33" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J33" s="9" t="s">
+      <c r="J33" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K33">
         <v>20000</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="16.5">
+    <row r="34" ht="16.5" spans="1:11">
       <c r="A34" s="1">
         <f t="shared" si="0"/>
         <v>2009003</v>
@@ -1861,14 +2474,14 @@
       <c r="I34" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J34" s="9" t="s">
+      <c r="J34" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K34">
         <v>2000000</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="16.5">
+    <row r="35" ht="16.5" spans="1:11">
       <c r="A35" s="1">
         <f t="shared" si="0"/>
         <v>2010001</v>
@@ -1897,14 +2510,14 @@
       <c r="I35" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J35" s="9" t="s">
+      <c r="J35" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K35">
         <v>500</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="16.5">
+    <row r="36" ht="16.5" spans="1:11">
       <c r="A36" s="1">
         <f t="shared" si="0"/>
         <v>2010002</v>
@@ -1933,14 +2546,14 @@
       <c r="I36" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J36" s="9" t="s">
+      <c r="J36" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K36">
         <v>20000</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="16.5">
+    <row r="37" ht="16.5" spans="1:11">
       <c r="A37" s="1">
         <f t="shared" si="0"/>
         <v>2010003</v>
@@ -1969,14 +2582,14 @@
       <c r="I37" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J37" s="9" t="s">
+      <c r="J37" s="10" t="s">
         <v>23</v>
       </c>
       <c r="K37">
         <v>2000000</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="16.5">
+    <row r="38" ht="16.5" spans="1:11">
       <c r="A38" s="1">
         <f t="shared" si="0"/>
         <v>3001001</v>
@@ -1999,17 +2612,17 @@
       <c r="G38" s="1">
         <v>-1</v>
       </c>
-      <c r="I38" s="10" t="s">
+      <c r="I38" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="J38" s="10" t="s">
+      <c r="J38" s="11" t="s">
         <v>38</v>
       </c>
       <c r="K38">
         <v>500</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="16.5">
+    <row r="39" ht="16.5" spans="1:11">
       <c r="A39" s="1">
         <f t="shared" si="0"/>
         <v>3001002</v>
@@ -2032,17 +2645,17 @@
       <c r="G39" s="1">
         <v>-1</v>
       </c>
-      <c r="I39" s="10" t="s">
+      <c r="I39" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="J39" s="10" t="s">
+      <c r="J39" s="11" t="s">
         <v>38</v>
       </c>
       <c r="K39">
         <v>20000</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="16.5">
+    <row r="40" ht="16.5" spans="1:11">
       <c r="A40" s="1">
         <f t="shared" si="0"/>
         <v>3001003</v>
@@ -2065,10 +2678,10 @@
       <c r="G40" s="1">
         <v>-1</v>
       </c>
-      <c r="I40" s="10" t="s">
+      <c r="I40" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="J40" s="10" t="s">
+      <c r="J40" s="11" t="s">
         <v>38</v>
       </c>
       <c r="K40">
@@ -2076,8 +2689,8 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="794"/>
+    <workbookView windowWidth="18885" windowHeight="7635" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Warehouse" sheetId="42" r:id="rId1"/>
@@ -32,6 +32,29 @@
     <author>Administrator</author>
   </authors>
   <commentList>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1-9 倍场ID
+10 需要付费开启得房间游戏</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="F1" authorId="0">
       <text>
         <r>
@@ -86,7 +109,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="44">
   <si>
     <t>sid</t>
   </si>
@@ -130,6 +153,9 @@
     <t>gameID</t>
   </si>
   <si>
+    <t>roomType</t>
+  </si>
+  <si>
     <t>enterLimit</t>
   </si>
   <si>
@@ -181,6 +207,9 @@
     <t>百家乐</t>
   </si>
   <si>
+    <t>4:3600</t>
+  </si>
+  <si>
     <t>三个骰子</t>
   </si>
   <si>
@@ -203,6 +232,15 @@
   </si>
   <si>
     <t>0:0</t>
+  </si>
+  <si>
+    <t>德州扑克</t>
+  </si>
+  <si>
+    <t>房间场</t>
+  </si>
+  <si>
+    <t>100:999</t>
   </si>
 </sst>
 </file>
@@ -215,7 +253,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -403,21 +441,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Noto Sans CJK SC Regular"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -426,8 +452,13 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -437,6 +468,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799340800195319"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -772,7 +809,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -796,16 +833,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -814,140 +851,146 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1280,18 +1323,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="9.375" style="1"/>
     <col min="3" max="6" width="9" style="1"/>
     <col min="7" max="7" width="11.25" style="1" customWidth="1"/>
     <col min="8" max="8" width="10.625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="29.75" style="1" customWidth="1"/>
+    <col min="9" max="9" width="29.7" style="1" customWidth="1"/>
     <col min="10" max="10" width="37.125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.25" customWidth="1"/>
+    <col min="11" max="11" width="17.2166666666667" customWidth="1"/>
     <col min="12" max="12" width="19.5" customWidth="1"/>
-    <col min="13" max="13" width="9" customWidth="1"/>
+    <col min="13" max="13" width="8.96666666666667" customWidth="1"/>
     <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1339,7 +1382,9 @@
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
+      <c r="E2" s="6" t="s">
+        <v>9</v>
+      </c>
       <c r="F2" s="6" t="s">
         <v>9</v>
       </c>
@@ -1366,23 +1411,26 @@
       <c r="B3" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="E3" s="6" t="s">
+        <v>14</v>
+      </c>
       <c r="F3" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:11">
@@ -1394,10 +1442,10 @@
         <v>100100</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -1412,10 +1460,10 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" s="10" t="s">
         <v>23</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>24</v>
       </c>
       <c r="K5">
         <v>1000</v>
@@ -1423,7 +1471,7 @@
     </row>
     <row r="6" ht="16.5" spans="1:11">
       <c r="A6" s="1">
-        <f t="shared" ref="A6:A40" si="0">B6*10+E6</f>
+        <f t="shared" ref="A6:A51" si="0">B6*10+E6</f>
         <v>1001002</v>
       </c>
       <c r="B6" s="7">
@@ -1434,7 +1482,7 @@
         <v>金矿大亨</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -1446,13 +1494,13 @@
         <v>-1</v>
       </c>
       <c r="H6" s="1">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" s="10" t="s">
         <v>23</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>24</v>
       </c>
       <c r="K6">
         <v>100000</v>
@@ -1471,7 +1519,7 @@
         <v>金矿大亨</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
@@ -1483,13 +1531,13 @@
         <v>-1</v>
       </c>
       <c r="H7" s="1">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J7" s="10" t="s">
         <v>23</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>24</v>
       </c>
       <c r="K7">
         <v>10000000</v>
@@ -1504,10 +1552,10 @@
         <v>200100</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -1519,16 +1567,16 @@
         <v>5000000</v>
       </c>
       <c r="H8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" s="10" t="s">
         <v>23</v>
       </c>
+      <c r="J8" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="K8">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:11">
@@ -1544,7 +1592,7 @@
         <v>红黑大战</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -1556,16 +1604,16 @@
         <v>500000000</v>
       </c>
       <c r="H9" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" s="10" t="s">
         <v>23</v>
       </c>
+      <c r="J9" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="K9">
-        <v>20000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:11">
@@ -1581,7 +1629,7 @@
         <v>红黑大战</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E10" s="1">
         <v>3</v>
@@ -1593,16 +1641,16 @@
         <v>-1</v>
       </c>
       <c r="H10" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J10" s="10" t="s">
         <v>23</v>
       </c>
+      <c r="J10" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="K10">
-        <v>2000000</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:11">
@@ -1614,10 +1662,10 @@
         <v>200101</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -1629,19 +1677,19 @@
         <v>5000000</v>
       </c>
       <c r="H11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" s="10" t="s">
         <v>23</v>
       </c>
+      <c r="J11" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="K11">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="12" ht="16.5" spans="1:11">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>2001012</v>
@@ -1654,7 +1702,7 @@
         <v>龙虎斗</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
@@ -1666,19 +1714,21 @@
         <v>500000000</v>
       </c>
       <c r="H12" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J12" s="10" t="s">
         <v>23</v>
       </c>
+      <c r="J12" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="K12">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:11">
+        <v>100000</v>
+      </c>
+      <c r="L12"/>
+      <c r="M12"/>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>2001013</v>
@@ -1691,7 +1741,7 @@
         <v>龙虎斗</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E13" s="1">
         <v>3</v>
@@ -1703,17 +1753,19 @@
         <v>-1</v>
       </c>
       <c r="H13" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J13" s="10" t="s">
         <v>23</v>
       </c>
+      <c r="J13" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="K13">
-        <v>2000000</v>
-      </c>
+        <v>10000000</v>
+      </c>
+      <c r="L13"/>
+      <c r="M13"/>
     </row>
     <row r="14" ht="16.5" spans="1:11">
       <c r="A14" s="1">
@@ -1724,10 +1776,10 @@
         <v>200300</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -1739,19 +1791,19 @@
         <v>5000000</v>
       </c>
       <c r="H14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J14" s="10" t="s">
         <v>23</v>
       </c>
+      <c r="J14" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="K14">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="15" ht="16.5" spans="1:11">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>2003002</v>
@@ -1764,7 +1816,7 @@
         <v>飞禽走兽</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E15" s="1">
         <v>2</v>
@@ -1776,19 +1828,21 @@
         <v>500000000</v>
       </c>
       <c r="H15" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J15" s="10" t="s">
         <v>23</v>
       </c>
+      <c r="J15" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="K15">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="16" ht="16.5" spans="1:11">
+        <v>100000</v>
+      </c>
+      <c r="L15"/>
+      <c r="M15"/>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>2003003</v>
@@ -1801,7 +1855,7 @@
         <v>飞禽走兽</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E16" s="1">
         <v>3</v>
@@ -1813,17 +1867,19 @@
         <v>-1</v>
       </c>
       <c r="H16" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J16" s="10" t="s">
         <v>23</v>
       </c>
+      <c r="J16" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="K16">
-        <v>2000000</v>
-      </c>
+        <v>10000000</v>
+      </c>
+      <c r="L16"/>
+      <c r="M16"/>
     </row>
     <row r="17" ht="16.5" spans="1:11">
       <c r="A17" s="1">
@@ -1834,10 +1890,10 @@
         <v>200400</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -1849,19 +1905,19 @@
         <v>5000000</v>
       </c>
       <c r="H17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J17" s="10" t="s">
         <v>23</v>
       </c>
+      <c r="J17" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="K17">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="18" ht="16.5" spans="1:11">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>2004002</v>
@@ -1874,7 +1930,7 @@
         <v>豪车俱乐部</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E18" s="1">
         <v>2</v>
@@ -1886,19 +1942,21 @@
         <v>500000000</v>
       </c>
       <c r="H18" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J18" s="10" t="s">
         <v>23</v>
       </c>
+      <c r="J18" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="K18">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="19" ht="16.5" spans="1:11">
+        <v>100000</v>
+      </c>
+      <c r="L18"/>
+      <c r="M18"/>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>2004003</v>
@@ -1911,7 +1969,7 @@
         <v>豪车俱乐部</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E19" s="1">
         <v>3</v>
@@ -1923,17 +1981,19 @@
         <v>-1</v>
       </c>
       <c r="H19" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J19" s="10" t="s">
         <v>23</v>
       </c>
+      <c r="J19" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="K19">
-        <v>2000000</v>
-      </c>
+        <v>10000000</v>
+      </c>
+      <c r="L19"/>
+      <c r="M19"/>
     </row>
     <row r="20" ht="16.5" spans="1:11">
       <c r="A20" s="1">
@@ -1944,31 +2004,31 @@
         <v>200500</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
       </c>
       <c r="F20" s="1">
-        <v>-1</v>
+        <v>100</v>
       </c>
       <c r="G20" s="1">
-        <v>-1</v>
+        <v>5000000</v>
       </c>
       <c r="H20" s="1">
         <v>0</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J20" s="10" t="s">
         <v>23</v>
       </c>
+      <c r="J20" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="K20">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:11">
@@ -1980,31 +2040,31 @@
         <v>200500</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E21" s="1">
         <v>2</v>
       </c>
       <c r="F21" s="1">
-        <v>-1</v>
+        <v>10000</v>
       </c>
       <c r="G21" s="1">
-        <v>-1</v>
+        <v>500000000</v>
       </c>
       <c r="H21" s="1">
         <v>0</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J21" s="10" t="s">
         <v>23</v>
       </c>
+      <c r="J21" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="K21">
-        <v>20000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:11">
@@ -2016,16 +2076,16 @@
         <v>200500</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E22" s="1">
         <v>3</v>
       </c>
       <c r="F22" s="1">
-        <v>-1</v>
+        <v>1000000</v>
       </c>
       <c r="G22" s="1">
         <v>-1</v>
@@ -2034,13 +2094,13 @@
         <v>0</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J22" s="10" t="s">
         <v>23</v>
       </c>
+      <c r="J22" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="K22">
-        <v>2000000</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:11">
@@ -2052,10 +2112,10 @@
         <v>200600</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -2067,19 +2127,19 @@
         <v>5000000</v>
       </c>
       <c r="H23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J23" s="10" t="s">
         <v>23</v>
       </c>
+      <c r="J23" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="K23">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="24" ht="16.5" spans="1:11">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>2006002</v>
@@ -2092,7 +2152,7 @@
         <v>三个骰子</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E24" s="1">
         <v>2</v>
@@ -2104,19 +2164,21 @@
         <v>500000000</v>
       </c>
       <c r="H24" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J24" s="10" t="s">
         <v>23</v>
       </c>
+      <c r="J24" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="K24">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="25" ht="16.5" spans="1:11">
+        <v>100000</v>
+      </c>
+      <c r="L24"/>
+      <c r="M24"/>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>2006003</v>
@@ -2129,7 +2191,7 @@
         <v>三个骰子</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E25" s="1">
         <v>3</v>
@@ -2141,17 +2203,19 @@
         <v>-1</v>
       </c>
       <c r="H25" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J25" s="10" t="s">
         <v>23</v>
       </c>
+      <c r="J25" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="K25">
-        <v>2000000</v>
-      </c>
+        <v>10000000</v>
+      </c>
+      <c r="L25"/>
+      <c r="M25"/>
     </row>
     <row r="26" ht="16.5" spans="1:11">
       <c r="A26" s="1">
@@ -2162,10 +2226,10 @@
         <v>200700</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -2177,19 +2241,19 @@
         <v>5000000</v>
       </c>
       <c r="H26" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J26" s="10" t="s">
         <v>23</v>
       </c>
+      <c r="J26" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="K26">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="27" ht="16.5" spans="1:11">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>2007002</v>
@@ -2202,7 +2266,7 @@
         <v>色碟</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E27" s="1">
         <v>2</v>
@@ -2214,19 +2278,21 @@
         <v>500000000</v>
       </c>
       <c r="H27" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J27" s="10" t="s">
         <v>23</v>
       </c>
+      <c r="J27" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="K27">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="28" ht="16.5" spans="1:11">
+        <v>100000</v>
+      </c>
+      <c r="L27"/>
+      <c r="M27"/>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
         <v>2007003</v>
@@ -2239,7 +2305,7 @@
         <v>色碟</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E28" s="1">
         <v>3</v>
@@ -2251,19 +2317,21 @@
         <v>-1</v>
       </c>
       <c r="H28" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J28" s="10" t="s">
         <v>23</v>
       </c>
+      <c r="J28" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="K28">
-        <v>2000000</v>
-      </c>
-    </row>
-    <row r="29" ht="16.5" spans="1:11">
+        <v>10000000</v>
+      </c>
+      <c r="L28"/>
+      <c r="M28"/>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
         <v>2008001</v>
@@ -2272,10 +2340,10 @@
         <v>200800</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -2287,19 +2355,21 @@
         <v>5000000</v>
       </c>
       <c r="H29" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J29" s="10" t="s">
         <v>23</v>
       </c>
+      <c r="J29" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="K29">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="30" ht="16.5" spans="1:11">
+        <v>1000</v>
+      </c>
+      <c r="L29"/>
+      <c r="M29"/>
+    </row>
+    <row r="30" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
         <v>2008002</v>
@@ -2308,10 +2378,10 @@
         <v>200800</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
@@ -2323,19 +2393,21 @@
         <v>500000000</v>
       </c>
       <c r="H30" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J30" s="10" t="s">
         <v>23</v>
       </c>
+      <c r="J30" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="K30">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="31" ht="16.5" spans="1:11">
+        <v>100000</v>
+      </c>
+      <c r="L30"/>
+      <c r="M30"/>
+    </row>
+    <row r="31" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
         <v>2008003</v>
@@ -2344,10 +2416,10 @@
         <v>200800</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E31" s="1">
         <v>3</v>
@@ -2359,17 +2431,19 @@
         <v>-1</v>
       </c>
       <c r="H31" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J31" s="10" t="s">
         <v>23</v>
       </c>
+      <c r="J31" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="K31">
-        <v>2000000</v>
-      </c>
+        <v>10000000</v>
+      </c>
+      <c r="L31"/>
+      <c r="M31"/>
     </row>
     <row r="32" ht="16.5" spans="1:11">
       <c r="A32" s="1">
@@ -2380,10 +2454,10 @@
         <v>200900</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -2395,16 +2469,16 @@
         <v>5000000</v>
       </c>
       <c r="H32" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J32" s="10" t="s">
         <v>23</v>
       </c>
+      <c r="J32" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="K32">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="1:11">
@@ -2420,7 +2494,7 @@
         <v>鱼虾蟹</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E33" s="1">
         <v>2</v>
@@ -2432,16 +2506,16 @@
         <v>500000000</v>
       </c>
       <c r="H33" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J33" s="10" t="s">
         <v>23</v>
       </c>
+      <c r="J33" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="K33">
-        <v>20000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="1:11">
@@ -2457,7 +2531,7 @@
         <v>鱼虾蟹</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E34" s="1">
         <v>3</v>
@@ -2469,16 +2543,16 @@
         <v>-1</v>
       </c>
       <c r="H34" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J34" s="10" t="s">
         <v>23</v>
       </c>
+      <c r="J34" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="K34">
-        <v>2000000</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="1:11">
@@ -2490,10 +2564,10 @@
         <v>201000</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
@@ -2505,16 +2579,16 @@
         <v>5000000</v>
       </c>
       <c r="H35" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J35" s="10" t="s">
         <v>23</v>
       </c>
+      <c r="J35" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="K35">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:11">
@@ -2526,10 +2600,10 @@
         <v>201000</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E36" s="1">
         <v>2</v>
@@ -2541,16 +2615,16 @@
         <v>500000000</v>
       </c>
       <c r="H36" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J36" s="10" t="s">
         <v>23</v>
       </c>
+      <c r="J36" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="K36">
-        <v>20000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="1:11">
@@ -2562,10 +2636,10 @@
         <v>201000</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E37" s="1">
         <v>3</v>
@@ -2577,16 +2651,16 @@
         <v>-1</v>
       </c>
       <c r="H37" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J37" s="10" t="s">
         <v>23</v>
       </c>
+      <c r="J37" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="K37">
-        <v>2000000</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="38" ht="16.5" spans="1:11">
@@ -2598,10 +2672,10 @@
         <v>300100</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
@@ -2612,17 +2686,20 @@
       <c r="G38" s="1">
         <v>-1</v>
       </c>
-      <c r="I38" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="J38" s="11" t="s">
-        <v>38</v>
+      <c r="H38" s="1">
+        <v>0</v>
+      </c>
+      <c r="I38" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="J38" s="13" t="s">
+        <v>40</v>
       </c>
       <c r="K38">
         <v>500</v>
       </c>
     </row>
-    <row r="39" ht="16.5" spans="1:11">
+    <row r="39" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A39" s="1">
         <f t="shared" si="0"/>
         <v>3001002</v>
@@ -2631,10 +2708,10 @@
         <v>300100</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
@@ -2645,17 +2722,22 @@
       <c r="G39" s="1">
         <v>-1</v>
       </c>
-      <c r="I39" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="J39" s="11" t="s">
-        <v>38</v>
+      <c r="H39" s="1">
+        <v>0</v>
+      </c>
+      <c r="I39" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="J39" s="13" t="s">
+        <v>40</v>
       </c>
       <c r="K39">
         <v>20000</v>
       </c>
-    </row>
-    <row r="40" ht="16.5" spans="1:11">
+      <c r="L39"/>
+      <c r="M39"/>
+    </row>
+    <row r="40" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A40" s="1">
         <f t="shared" si="0"/>
         <v>3001003</v>
@@ -2664,10 +2746,10 @@
         <v>300100</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E40" s="1">
         <v>3</v>
@@ -2678,14 +2760,529 @@
       <c r="G40" s="1">
         <v>-1</v>
       </c>
-      <c r="I40" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="J40" s="11" t="s">
-        <v>38</v>
+      <c r="H40" s="1">
+        <v>0</v>
+      </c>
+      <c r="I40" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="J40" s="13" t="s">
+        <v>40</v>
       </c>
       <c r="K40">
         <v>2000000</v>
+      </c>
+      <c r="L40"/>
+      <c r="M40"/>
+    </row>
+    <row r="41" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A41" s="1">
+        <f t="shared" si="0"/>
+        <v>3002001</v>
+      </c>
+      <c r="B41" s="7">
+        <v>300200</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E41" s="1">
+        <v>1</v>
+      </c>
+      <c r="F41" s="1">
+        <v>100</v>
+      </c>
+      <c r="G41" s="1">
+        <v>-1</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0</v>
+      </c>
+      <c r="I41" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="J41" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="K41"/>
+      <c r="L41"/>
+      <c r="M41"/>
+    </row>
+    <row r="42" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A42" s="1">
+        <f t="shared" si="0"/>
+        <v>3002002</v>
+      </c>
+      <c r="B42" s="7">
+        <v>300200</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E42" s="1">
+        <v>2</v>
+      </c>
+      <c r="F42" s="1">
+        <v>10000</v>
+      </c>
+      <c r="G42" s="1">
+        <v>-1</v>
+      </c>
+      <c r="H42" s="1">
+        <v>0</v>
+      </c>
+      <c r="I42" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="J42" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="K42"/>
+      <c r="L42"/>
+      <c r="M42"/>
+    </row>
+    <row r="43" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A43" s="1">
+        <f t="shared" si="0"/>
+        <v>3002003</v>
+      </c>
+      <c r="B43" s="7">
+        <v>300200</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E43" s="1">
+        <v>3</v>
+      </c>
+      <c r="F43" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="G43" s="1">
+        <v>-1</v>
+      </c>
+      <c r="H43" s="1">
+        <v>0</v>
+      </c>
+      <c r="I43" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="J43" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="K43"/>
+      <c r="L43"/>
+      <c r="M43"/>
+    </row>
+    <row r="44" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A44" s="1">
+        <f>B44*10+E44</f>
+        <v>1001010</v>
+      </c>
+      <c r="B44" s="9">
+        <v>100100</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E44" s="10">
+        <v>10</v>
+      </c>
+      <c r="F44" s="10">
+        <v>100</v>
+      </c>
+      <c r="G44" s="10">
+        <v>-1</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0</v>
+      </c>
+      <c r="I44" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="J44" s="10">
+        <v>1</v>
+      </c>
+      <c r="K44">
+        <v>100</v>
+      </c>
+      <c r="L44"/>
+      <c r="M44"/>
+    </row>
+    <row r="45" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A45" s="1">
+        <f>B45*10+E45</f>
+        <v>2001010</v>
+      </c>
+      <c r="B45" s="9">
+        <v>200100</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E45" s="10">
+        <v>10</v>
+      </c>
+      <c r="F45" s="10">
+        <v>10000</v>
+      </c>
+      <c r="G45" s="10">
+        <v>-1</v>
+      </c>
+      <c r="H45" s="1">
+        <v>0</v>
+      </c>
+      <c r="I45" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="J45" s="10">
+        <v>1</v>
+      </c>
+      <c r="K45">
+        <v>100</v>
+      </c>
+      <c r="L45"/>
+      <c r="M45"/>
+    </row>
+    <row r="46" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A46" s="1">
+        <f>B46*10+E46</f>
+        <v>2001020</v>
+      </c>
+      <c r="B46" s="9">
+        <v>200101</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E46" s="10">
+        <v>10</v>
+      </c>
+      <c r="F46" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="G46" s="10">
+        <v>-1</v>
+      </c>
+      <c r="H46" s="1">
+        <v>0</v>
+      </c>
+      <c r="I46" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="J46" s="10">
+        <v>1</v>
+      </c>
+      <c r="K46">
+        <v>100</v>
+      </c>
+      <c r="L46"/>
+      <c r="M46"/>
+    </row>
+    <row r="47" ht="16.5" spans="1:11">
+      <c r="A47" s="1">
+        <f>B47*10+E47</f>
+        <v>2003010</v>
+      </c>
+      <c r="B47" s="9">
+        <v>200300</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E47" s="10">
+        <v>10</v>
+      </c>
+      <c r="F47" s="10">
+        <v>100</v>
+      </c>
+      <c r="G47" s="10">
+        <v>-1</v>
+      </c>
+      <c r="H47" s="1">
+        <v>0</v>
+      </c>
+      <c r="I47" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="J47" s="10">
+        <v>1</v>
+      </c>
+      <c r="K47">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" ht="16.5" spans="1:11">
+      <c r="A48" s="1">
+        <f>B48*10+E48</f>
+        <v>2004010</v>
+      </c>
+      <c r="B48" s="9">
+        <v>200400</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E48" s="10">
+        <v>10</v>
+      </c>
+      <c r="F48" s="10">
+        <v>10000</v>
+      </c>
+      <c r="G48" s="10">
+        <v>-1</v>
+      </c>
+      <c r="H48" s="1">
+        <v>0</v>
+      </c>
+      <c r="I48" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="J48" s="10">
+        <v>1</v>
+      </c>
+      <c r="K48">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" ht="16.5" spans="1:11">
+      <c r="A49" s="1">
+        <f>B49*10+E49</f>
+        <v>2005010</v>
+      </c>
+      <c r="B49" s="9">
+        <v>200500</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E49" s="10">
+        <v>10</v>
+      </c>
+      <c r="F49" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="G49" s="10">
+        <v>-1</v>
+      </c>
+      <c r="H49" s="1">
+        <v>0</v>
+      </c>
+      <c r="I49" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="J49" s="10">
+        <v>1</v>
+      </c>
+      <c r="K49">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" ht="16.5" spans="1:11">
+      <c r="A50" s="1">
+        <f>B50*10+E50</f>
+        <v>2006010</v>
+      </c>
+      <c r="B50" s="9">
+        <v>200600</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E50" s="10">
+        <v>10</v>
+      </c>
+      <c r="F50" s="10">
+        <v>100</v>
+      </c>
+      <c r="G50" s="10">
+        <v>-1</v>
+      </c>
+      <c r="H50" s="1">
+        <v>0</v>
+      </c>
+      <c r="I50" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="J50" s="10">
+        <v>1</v>
+      </c>
+      <c r="K50">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" ht="16.5" spans="1:11">
+      <c r="A51" s="1">
+        <f>B51*10+E51</f>
+        <v>2007010</v>
+      </c>
+      <c r="B51" s="9">
+        <v>200700</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E51" s="10">
+        <v>10</v>
+      </c>
+      <c r="F51" s="10">
+        <v>10000</v>
+      </c>
+      <c r="G51" s="10">
+        <v>-1</v>
+      </c>
+      <c r="H51" s="1">
+        <v>0</v>
+      </c>
+      <c r="I51" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="J51" s="10">
+        <v>1</v>
+      </c>
+      <c r="K51">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" ht="16.5" spans="1:11">
+      <c r="A52" s="1">
+        <f>B52*10+E52</f>
+        <v>2008010</v>
+      </c>
+      <c r="B52" s="9">
+        <v>200800</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E52" s="10">
+        <v>10</v>
+      </c>
+      <c r="F52" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="G52" s="10">
+        <v>-1</v>
+      </c>
+      <c r="H52" s="1">
+        <v>0</v>
+      </c>
+      <c r="I52" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="J52" s="10">
+        <v>1</v>
+      </c>
+      <c r="K52">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" ht="16.5" spans="1:11">
+      <c r="A53" s="1">
+        <f>B53*10+E53</f>
+        <v>2009010</v>
+      </c>
+      <c r="B53" s="9">
+        <v>200900</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E53" s="10">
+        <v>10</v>
+      </c>
+      <c r="F53" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="G53" s="10">
+        <v>-1</v>
+      </c>
+      <c r="H53" s="1">
+        <v>0</v>
+      </c>
+      <c r="I53" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="J53" s="10">
+        <v>1</v>
+      </c>
+      <c r="K53">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" ht="16.5" spans="1:11">
+      <c r="A54" s="1">
+        <f>B54*10+E54</f>
+        <v>2010010</v>
+      </c>
+      <c r="B54" s="9">
+        <v>201000</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E54" s="10">
+        <v>10</v>
+      </c>
+      <c r="F54" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="G54" s="10">
+        <v>-1</v>
+      </c>
+      <c r="H54" s="1">
+        <v>0</v>
+      </c>
+      <c r="I54" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="J54" s="10">
+        <v>1</v>
+      </c>
+      <c r="K54">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -1,44 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\hall\resources\sample\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC001C20-83D1-46F2-A38A-03F84C009AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="18885" windowHeight="7635" tabRatio="794"/>
+    <workbookView xWindow="32625" yWindow="2910" windowWidth="21600" windowHeight="11385" tabRatio="794" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Warehouse" sheetId="42" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -47,6 +41,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -55,37 +50,40 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>最小准入金币</t>
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>-1 表示无上限</t>
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -94,6 +92,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -104,12 +103,37 @@
         </r>
       </text>
     </comment>
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+单局游戏获得金额大于此值时，添加至跑马灯列表播放
+当值小于等于0时，不播</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="50">
   <si>
     <t>sid</t>
   </si>
@@ -138,6 +162,9 @@
     <t>倍场显示默认押注</t>
   </si>
   <si>
+    <t>跑马触发金额</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -147,6 +174,9 @@
     <t>list&lt;int&gt;{:}</t>
   </si>
   <si>
+    <t>long</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -171,9 +201,6 @@
     <t>RoomDeletion_Solution</t>
   </si>
   <si>
-    <t>BetShow</t>
-  </si>
-  <si>
     <t>金矿大亨</t>
   </si>
   <si>
@@ -237,23 +264,34 @@
     <t>德州扑克</t>
   </si>
   <si>
+    <t>房间场-初级</t>
+  </si>
+  <si>
+    <t>100:999</t>
+  </si>
+  <si>
+    <t>房间场-中级</t>
+  </si>
+  <si>
+    <t>房间场-高级</t>
+  </si>
+  <si>
     <t>房间场</t>
   </si>
   <si>
-    <t>100:999</t>
+    <t>betShow</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>marqueeTrigger</t>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="29">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -292,173 +330,60 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Noto Sans CJK SC Regular"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Noto Sans CJK SC Regular"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -467,204 +392,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799340800195319"/>
+        <fgColor theme="5" tint="0.7993408001953185"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -687,295 +426,53 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="60">
+  <cellStyleXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -984,82 +481,39 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="60">
+  <cellStyles count="12">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 2" xfId="49"/>
-    <cellStyle name="常规 2 2" xfId="50"/>
-    <cellStyle name="常规 2 2 2" xfId="51"/>
-    <cellStyle name="常规 3" xfId="52"/>
-    <cellStyle name="常规 3 2" xfId="53"/>
-    <cellStyle name="常规 4" xfId="54"/>
-    <cellStyle name="常规 5" xfId="55"/>
-    <cellStyle name="常规 6" xfId="56"/>
-    <cellStyle name="常规 6 2" xfId="57"/>
-    <cellStyle name="常规 6 2 2" xfId="58"/>
-    <cellStyle name="常规 7" xfId="59"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="常规 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="常规 2 2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="常规 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
+    <cellStyle name="常规 3 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
+    <cellStyle name="常规 4" xfId="6" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
+    <cellStyle name="常规 5" xfId="7" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
+    <cellStyle name="常规 6" xfId="8" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
+    <cellStyle name="常规 6 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
+    <cellStyle name="常规 6 2 2" xfId="10" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
+    <cellStyle name="常规 7" xfId="11" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1317,28 +771,30 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:M54"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M56"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="9.375" style="1"/>
-    <col min="3" max="6" width="9" style="1"/>
+    <col min="3" max="3" width="9" style="1"/>
+    <col min="4" max="4" width="12" style="1" customWidth="1"/>
+    <col min="5" max="6" width="9" style="1"/>
     <col min="7" max="7" width="11.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="29.7" style="1" customWidth="1"/>
-    <col min="10" max="10" width="37.125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.2166666666667" customWidth="1"/>
+    <col min="8" max="8" width="9.25" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9.75" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.625" customWidth="1"/>
     <col min="12" max="12" width="19.5" customWidth="1"/>
-    <col min="13" max="13" width="8.96666666666667" customWidth="1"/>
+    <col min="13" max="13" width="9" customWidth="1"/>
     <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:11">
+    <row r="1" spans="1:12" ht="16.5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1372,68 +828,77 @@
       <c r="K1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:11">
+      <c r="L1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="16.5">
       <c r="A2" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:11">
+      <c r="L2" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="16.5">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" ht="16.5" spans="1:11">
+        <v>21</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="L3" s="14" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="16.5">
       <c r="A5" s="1">
         <f>B5*10+E5</f>
         <v>1001001</v>
@@ -1442,10 +907,10 @@
         <v>100100</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -1460,18 +925,22 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>24</v>
+        <v>24</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="K5">
         <v>1000</v>
       </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:11">
+      <c r="L5">
+        <f>K5*500</f>
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="16.5">
       <c r="A6" s="1">
-        <f t="shared" ref="A6:A51" si="0">B6*10+E6</f>
+        <f t="shared" ref="A6:A43" si="0">B6*10+E6</f>
         <v>1001002</v>
       </c>
       <c r="B6" s="7">
@@ -1482,7 +951,7 @@
         <v>金矿大亨</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -1497,16 +966,20 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>24</v>
+        <v>24</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="K6">
         <v>100000</v>
       </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:11">
+      <c r="L6">
+        <f t="shared" ref="L6:L37" si="2">K6*500</f>
+        <v>50000000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="16.5">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>1001003</v>
@@ -1519,7 +992,7 @@
         <v>金矿大亨</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
@@ -1534,16 +1007,20 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>24</v>
+        <v>24</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="K7">
         <v>10000000</v>
       </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:11">
+      <c r="L7">
+        <f t="shared" si="2"/>
+        <v>5000000000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="16.5">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>2001001</v>
@@ -1552,10 +1029,10 @@
         <v>200100</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -1570,16 +1047,20 @@
         <v>0</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J8" s="12" t="s">
-        <v>24</v>
+        <v>24</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="K8">
         <v>1000</v>
       </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:11">
+      <c r="L8">
+        <f t="shared" si="2"/>
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="16.5">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>2001002</v>
@@ -1592,7 +1073,7 @@
         <v>红黑大战</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -1607,16 +1088,20 @@
         <v>0</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J9" s="12" t="s">
-        <v>24</v>
+        <v>24</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="K9">
         <v>100000</v>
       </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:11">
+      <c r="L9">
+        <f t="shared" si="2"/>
+        <v>50000000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="16.5">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>2001003</v>
@@ -1629,7 +1114,7 @@
         <v>红黑大战</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E10" s="1">
         <v>3</v>
@@ -1644,16 +1129,20 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>24</v>
+        <v>24</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="K10">
         <v>10000000</v>
       </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:11">
+      <c r="L10">
+        <f t="shared" si="2"/>
+        <v>5000000000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="16.5">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>2001011</v>
@@ -1662,10 +1151,10 @@
         <v>200101</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -1680,16 +1169,20 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J11" s="12" t="s">
-        <v>24</v>
+        <v>24</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="K11">
         <v>1000</v>
       </c>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="L11">
+        <f t="shared" si="2"/>
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="16.5">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>2001012</v>
@@ -1698,11 +1191,11 @@
         <v>200101</v>
       </c>
       <c r="C12" s="7" t="str">
-        <f t="shared" ref="C12:C16" si="2">C11</f>
+        <f t="shared" ref="C12:C16" si="3">C11</f>
         <v>龙虎斗</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
@@ -1717,18 +1210,20 @@
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J12" s="12" t="s">
-        <v>24</v>
+        <v>24</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="K12">
         <v>100000</v>
       </c>
-      <c r="L12"/>
-      <c r="M12"/>
-    </row>
-    <row r="13" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="L12">
+        <f t="shared" si="2"/>
+        <v>50000000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="16.5">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>2001013</v>
@@ -1737,11 +1232,11 @@
         <v>200101</v>
       </c>
       <c r="C13" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>龙虎斗</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E13" s="1">
         <v>3</v>
@@ -1756,18 +1251,20 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>24</v>
+        <v>24</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="K13">
         <v>10000000</v>
       </c>
-      <c r="L13"/>
-      <c r="M13"/>
-    </row>
-    <row r="14" ht="16.5" spans="1:11">
+      <c r="L13">
+        <f t="shared" si="2"/>
+        <v>5000000000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="16.5">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>2003001</v>
@@ -1776,10 +1273,10 @@
         <v>200300</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -1794,16 +1291,20 @@
         <v>0</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J14" s="12" t="s">
-        <v>24</v>
+        <v>24</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="K14">
         <v>1000</v>
       </c>
-    </row>
-    <row r="15" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="L14">
+        <f t="shared" si="2"/>
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="16.5">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>2003002</v>
@@ -1812,11 +1313,11 @@
         <v>200300</v>
       </c>
       <c r="C15" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>飞禽走兽</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E15" s="1">
         <v>2</v>
@@ -1831,18 +1332,20 @@
         <v>0</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J15" s="12" t="s">
-        <v>24</v>
+        <v>24</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="K15">
         <v>100000</v>
       </c>
-      <c r="L15"/>
-      <c r="M15"/>
-    </row>
-    <row r="16" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="L15">
+        <f t="shared" si="2"/>
+        <v>50000000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="16.5">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>2003003</v>
@@ -1851,11 +1354,11 @@
         <v>200300</v>
       </c>
       <c r="C16" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>飞禽走兽</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E16" s="1">
         <v>3</v>
@@ -1870,18 +1373,20 @@
         <v>0</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J16" s="12" t="s">
-        <v>24</v>
+        <v>24</v>
+      </c>
+      <c r="J16" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="K16">
         <v>10000000</v>
       </c>
-      <c r="L16"/>
-      <c r="M16"/>
-    </row>
-    <row r="17" ht="16.5" spans="1:11">
+      <c r="L16">
+        <f t="shared" si="2"/>
+        <v>5000000000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="16.5">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>2004001</v>
@@ -1890,10 +1395,10 @@
         <v>200400</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -1908,16 +1413,20 @@
         <v>0</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J17" s="12" t="s">
-        <v>24</v>
+        <v>24</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="K17">
         <v>1000</v>
       </c>
-    </row>
-    <row r="18" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="L17">
+        <f t="shared" si="2"/>
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="16.5">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>2004002</v>
@@ -1930,7 +1439,7 @@
         <v>豪车俱乐部</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E18" s="1">
         <v>2</v>
@@ -1945,18 +1454,20 @@
         <v>0</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J18" s="12" t="s">
-        <v>24</v>
+        <v>24</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="K18">
         <v>100000</v>
       </c>
-      <c r="L18"/>
-      <c r="M18"/>
-    </row>
-    <row r="19" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="L18">
+        <f t="shared" si="2"/>
+        <v>50000000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="16.5">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>2004003</v>
@@ -1969,7 +1480,7 @@
         <v>豪车俱乐部</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E19" s="1">
         <v>3</v>
@@ -1984,18 +1495,20 @@
         <v>0</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J19" s="12" t="s">
-        <v>24</v>
+        <v>24</v>
+      </c>
+      <c r="J19" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="K19">
         <v>10000000</v>
       </c>
-      <c r="L19"/>
-      <c r="M19"/>
-    </row>
-    <row r="20" ht="16.5" spans="1:11">
+      <c r="L19">
+        <f t="shared" si="2"/>
+        <v>5000000000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="16.5">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>2005001</v>
@@ -2004,10 +1517,10 @@
         <v>200500</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
@@ -2022,16 +1535,20 @@
         <v>0</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J20" s="12" t="s">
-        <v>32</v>
+        <v>24</v>
+      </c>
+      <c r="J20" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="K20">
         <v>1000</v>
       </c>
-    </row>
-    <row r="21" ht="16.5" spans="1:11">
+      <c r="L20">
+        <f t="shared" si="2"/>
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="16.5">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>2005002</v>
@@ -2040,10 +1557,10 @@
         <v>200500</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E21" s="1">
         <v>2</v>
@@ -2058,16 +1575,20 @@
         <v>0</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J21" s="12" t="s">
-        <v>32</v>
+        <v>24</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="K21">
         <v>100000</v>
       </c>
-    </row>
-    <row r="22" ht="16.5" spans="1:11">
+      <c r="L21">
+        <f t="shared" si="2"/>
+        <v>50000000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="16.5">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>2005003</v>
@@ -2076,10 +1597,10 @@
         <v>200500</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E22" s="1">
         <v>3</v>
@@ -2094,16 +1615,20 @@
         <v>0</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J22" s="12" t="s">
-        <v>32</v>
+        <v>24</v>
+      </c>
+      <c r="J22" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="K22">
         <v>10000000</v>
       </c>
-    </row>
-    <row r="23" ht="16.5" spans="1:11">
+      <c r="L22">
+        <f t="shared" si="2"/>
+        <v>5000000000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="16.5">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>2006001</v>
@@ -2112,10 +1637,10 @@
         <v>200600</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -2130,16 +1655,20 @@
         <v>0</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J23" s="12" t="s">
-        <v>24</v>
+        <v>24</v>
+      </c>
+      <c r="J23" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="K23">
         <v>1000</v>
       </c>
-    </row>
-    <row r="24" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="L23">
+        <f t="shared" si="2"/>
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="16.5">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>2006002</v>
@@ -2148,11 +1677,11 @@
         <v>200600</v>
       </c>
       <c r="C24" s="7" t="str">
-        <f t="shared" ref="C24:C28" si="3">C23</f>
+        <f t="shared" ref="C24:C28" si="4">C23</f>
         <v>三个骰子</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E24" s="1">
         <v>2</v>
@@ -2167,18 +1696,20 @@
         <v>0</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J24" s="12" t="s">
-        <v>24</v>
+        <v>24</v>
+      </c>
+      <c r="J24" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="K24">
         <v>100000</v>
       </c>
-      <c r="L24"/>
-      <c r="M24"/>
-    </row>
-    <row r="25" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="L24">
+        <f t="shared" si="2"/>
+        <v>50000000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="16.5">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>2006003</v>
@@ -2187,11 +1718,11 @@
         <v>200600</v>
       </c>
       <c r="C25" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>三个骰子</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E25" s="1">
         <v>3</v>
@@ -2206,18 +1737,20 @@
         <v>0</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J25" s="12" t="s">
-        <v>24</v>
+        <v>24</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="K25">
         <v>10000000</v>
       </c>
-      <c r="L25"/>
-      <c r="M25"/>
-    </row>
-    <row r="26" ht="16.5" spans="1:11">
+      <c r="L25">
+        <f t="shared" si="2"/>
+        <v>5000000000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="16.5">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>2007001</v>
@@ -2226,10 +1759,10 @@
         <v>200700</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -2244,16 +1777,20 @@
         <v>0</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J26" s="12" t="s">
-        <v>24</v>
+        <v>24</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="K26">
         <v>1000</v>
       </c>
-    </row>
-    <row r="27" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="L26">
+        <f t="shared" si="2"/>
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="16.5">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>2007002</v>
@@ -2262,11 +1799,11 @@
         <v>200700</v>
       </c>
       <c r="C27" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>色碟</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E27" s="1">
         <v>2</v>
@@ -2281,18 +1818,20 @@
         <v>0</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J27" s="12" t="s">
-        <v>24</v>
+        <v>24</v>
+      </c>
+      <c r="J27" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="K27">
         <v>100000</v>
       </c>
-      <c r="L27"/>
-      <c r="M27"/>
-    </row>
-    <row r="28" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="L27">
+        <f t="shared" si="2"/>
+        <v>50000000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="16.5">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
         <v>2007003</v>
@@ -2301,11 +1840,11 @@
         <v>200700</v>
       </c>
       <c r="C28" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>色碟</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E28" s="1">
         <v>3</v>
@@ -2320,18 +1859,20 @@
         <v>0</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J28" s="12" t="s">
-        <v>24</v>
+        <v>24</v>
+      </c>
+      <c r="J28" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="K28">
         <v>10000000</v>
       </c>
-      <c r="L28"/>
-      <c r="M28"/>
-    </row>
-    <row r="29" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="L28">
+        <f t="shared" si="2"/>
+        <v>5000000000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="16.5">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
         <v>2008001</v>
@@ -2340,10 +1881,10 @@
         <v>200800</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -2358,18 +1899,20 @@
         <v>0</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J29" s="12" t="s">
-        <v>24</v>
+        <v>24</v>
+      </c>
+      <c r="J29" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="K29">
         <v>1000</v>
       </c>
-      <c r="L29"/>
-      <c r="M29"/>
-    </row>
-    <row r="30" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="L29">
+        <f t="shared" si="2"/>
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="16.5">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
         <v>2008002</v>
@@ -2378,10 +1921,10 @@
         <v>200800</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
@@ -2396,18 +1939,20 @@
         <v>0</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J30" s="12" t="s">
-        <v>24</v>
+        <v>24</v>
+      </c>
+      <c r="J30" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="K30">
         <v>100000</v>
       </c>
-      <c r="L30"/>
-      <c r="M30"/>
-    </row>
-    <row r="31" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="L30">
+        <f t="shared" si="2"/>
+        <v>50000000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="16.5">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
         <v>2008003</v>
@@ -2416,10 +1961,10 @@
         <v>200800</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E31" s="1">
         <v>3</v>
@@ -2434,18 +1979,20 @@
         <v>0</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J31" s="12" t="s">
-        <v>24</v>
+        <v>24</v>
+      </c>
+      <c r="J31" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="K31">
         <v>10000000</v>
       </c>
-      <c r="L31"/>
-      <c r="M31"/>
-    </row>
-    <row r="32" ht="16.5" spans="1:11">
+      <c r="L31">
+        <f t="shared" si="2"/>
+        <v>5000000000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="16.5">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
         <v>2009001</v>
@@ -2454,10 +2001,10 @@
         <v>200900</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -2472,16 +2019,20 @@
         <v>0</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J32" s="12" t="s">
-        <v>24</v>
+        <v>24</v>
+      </c>
+      <c r="J32" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="K32">
         <v>1000</v>
       </c>
-    </row>
-    <row r="33" ht="16.5" spans="1:11">
+      <c r="L32">
+        <f t="shared" si="2"/>
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="16.5">
       <c r="A33" s="1">
         <f t="shared" si="0"/>
         <v>2009002</v>
@@ -2494,7 +2045,7 @@
         <v>鱼虾蟹</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E33" s="1">
         <v>2</v>
@@ -2509,16 +2060,20 @@
         <v>0</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J33" s="12" t="s">
-        <v>24</v>
+        <v>24</v>
+      </c>
+      <c r="J33" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="K33">
         <v>100000</v>
       </c>
-    </row>
-    <row r="34" ht="16.5" spans="1:11">
+      <c r="L33">
+        <f t="shared" si="2"/>
+        <v>50000000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="16.5">
       <c r="A34" s="1">
         <f t="shared" si="0"/>
         <v>2009003</v>
@@ -2531,7 +2086,7 @@
         <v>鱼虾蟹</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E34" s="1">
         <v>3</v>
@@ -2546,16 +2101,20 @@
         <v>0</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J34" s="12" t="s">
-        <v>24</v>
+        <v>24</v>
+      </c>
+      <c r="J34" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="K34">
         <v>10000000</v>
       </c>
-    </row>
-    <row r="35" ht="16.5" spans="1:11">
+      <c r="L34">
+        <f t="shared" si="2"/>
+        <v>5000000000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="16.5">
       <c r="A35" s="1">
         <f t="shared" si="0"/>
         <v>2010001</v>
@@ -2564,10 +2123,10 @@
         <v>201000</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
@@ -2582,16 +2141,20 @@
         <v>0</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J35" s="12" t="s">
-        <v>24</v>
+        <v>24</v>
+      </c>
+      <c r="J35" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="K35">
         <v>1000</v>
       </c>
-    </row>
-    <row r="36" ht="16.5" spans="1:11">
+      <c r="L35">
+        <f t="shared" si="2"/>
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="16.5">
       <c r="A36" s="1">
         <f t="shared" si="0"/>
         <v>2010002</v>
@@ -2600,10 +2163,10 @@
         <v>201000</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E36" s="1">
         <v>2</v>
@@ -2618,16 +2181,20 @@
         <v>0</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J36" s="12" t="s">
-        <v>24</v>
+        <v>24</v>
+      </c>
+      <c r="J36" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="K36">
         <v>100000</v>
       </c>
-    </row>
-    <row r="37" ht="16.5" spans="1:11">
+      <c r="L36">
+        <f t="shared" si="2"/>
+        <v>50000000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="16.5">
       <c r="A37" s="1">
         <f t="shared" si="0"/>
         <v>2010003</v>
@@ -2636,10 +2203,10 @@
         <v>201000</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E37" s="1">
         <v>3</v>
@@ -2654,16 +2221,20 @@
         <v>0</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J37" s="12" t="s">
-        <v>24</v>
+        <v>24</v>
+      </c>
+      <c r="J37" s="11" t="s">
+        <v>25</v>
       </c>
       <c r="K37">
         <v>10000000</v>
       </c>
-    </row>
-    <row r="38" ht="16.5" spans="1:11">
+      <c r="L37">
+        <f t="shared" si="2"/>
+        <v>5000000000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="16.5">
       <c r="A38" s="1">
         <f t="shared" si="0"/>
         <v>3001001</v>
@@ -2672,10 +2243,10 @@
         <v>300100</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
@@ -2689,17 +2260,21 @@
       <c r="H38" s="1">
         <v>0</v>
       </c>
-      <c r="I38" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="J38" s="13" t="s">
+      <c r="I38" s="12" t="s">
         <v>40</v>
+      </c>
+      <c r="J38" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="K38">
         <v>500</v>
       </c>
-    </row>
-    <row r="39" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="L38">
+        <f t="shared" ref="L38:L43" si="5">K38*500</f>
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="16.5">
       <c r="A39" s="1">
         <f t="shared" si="0"/>
         <v>3001002</v>
@@ -2708,10 +2283,10 @@
         <v>300100</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
@@ -2725,19 +2300,21 @@
       <c r="H39" s="1">
         <v>0</v>
       </c>
-      <c r="I39" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="J39" s="13" t="s">
+      <c r="I39" s="12" t="s">
         <v>40</v>
+      </c>
+      <c r="J39" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="K39">
         <v>20000</v>
       </c>
-      <c r="L39"/>
-      <c r="M39"/>
-    </row>
-    <row r="40" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="L39">
+        <f t="shared" si="5"/>
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="16.5">
       <c r="A40" s="1">
         <f t="shared" si="0"/>
         <v>3001003</v>
@@ -2746,10 +2323,10 @@
         <v>300100</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E40" s="1">
         <v>3</v>
@@ -2763,19 +2340,21 @@
       <c r="H40" s="1">
         <v>0</v>
       </c>
-      <c r="I40" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="J40" s="13" t="s">
+      <c r="I40" s="12" t="s">
         <v>40</v>
+      </c>
+      <c r="J40" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="K40">
         <v>2000000</v>
       </c>
-      <c r="L40"/>
-      <c r="M40"/>
-    </row>
-    <row r="41" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="L40">
+        <f t="shared" si="5"/>
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="16.5">
       <c r="A41" s="1">
         <f t="shared" si="0"/>
         <v>3002001</v>
@@ -2784,10 +2363,10 @@
         <v>300200</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E41" s="1">
         <v>1</v>
@@ -2801,17 +2380,21 @@
       <c r="H41" s="1">
         <v>0</v>
       </c>
-      <c r="I41" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="J41" s="13" t="s">
+      <c r="I41" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="K41"/>
-      <c r="L41"/>
-      <c r="M41"/>
-    </row>
-    <row r="42" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="J41" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="K41">
+        <v>500</v>
+      </c>
+      <c r="L41">
+        <f t="shared" si="5"/>
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="16.5">
       <c r="A42" s="1">
         <f t="shared" si="0"/>
         <v>3002002</v>
@@ -2820,10 +2403,10 @@
         <v>300200</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E42" s="1">
         <v>2</v>
@@ -2837,17 +2420,21 @@
       <c r="H42" s="1">
         <v>0</v>
       </c>
-      <c r="I42" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="J42" s="13" t="s">
+      <c r="I42" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="K42"/>
-      <c r="L42"/>
-      <c r="M42"/>
-    </row>
-    <row r="43" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="J42" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="K42">
+        <v>20000</v>
+      </c>
+      <c r="L42">
+        <f t="shared" si="5"/>
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="16.5">
       <c r="A43" s="1">
         <f t="shared" si="0"/>
         <v>3002003</v>
@@ -2856,10 +2443,10 @@
         <v>300200</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E43" s="1">
         <v>3</v>
@@ -2873,29 +2460,33 @@
       <c r="H43" s="1">
         <v>0</v>
       </c>
-      <c r="I43" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="J43" s="13" t="s">
+      <c r="I43" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="K43"/>
-      <c r="L43"/>
-      <c r="M43"/>
-    </row>
-    <row r="44" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="J43" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="K43">
+        <v>2000000</v>
+      </c>
+      <c r="L43">
+        <f t="shared" si="5"/>
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="16.5">
       <c r="A44" s="1">
-        <f>B44*10+E44</f>
-        <v>1001010</v>
+        <f>B44*100+E44</f>
+        <v>10010010</v>
       </c>
       <c r="B44" s="9">
         <v>100100</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E44" s="10">
         <v>10</v>
@@ -2910,112 +2501,115 @@
         <v>0</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J44" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44">
         <v>100</v>
       </c>
-      <c r="L44"/>
-      <c r="M44"/>
-    </row>
-    <row r="45" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="L44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="16.5">
       <c r="A45" s="1">
-        <f>B45*10+E45</f>
-        <v>2001010</v>
+        <f>B45*100+E45</f>
+        <v>10010011</v>
       </c>
       <c r="B45" s="9">
+        <v>100100</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E45" s="10">
+        <v>11</v>
+      </c>
+      <c r="F45" s="10">
+        <v>100</v>
+      </c>
+      <c r="G45" s="10">
+        <v>-1</v>
+      </c>
+      <c r="H45" s="1">
+        <v>0</v>
+      </c>
+      <c r="I45" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="J45" s="10">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>100</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="16.5">
+      <c r="A46" s="1">
+        <f>B46*100+E46</f>
+        <v>10010012</v>
+      </c>
+      <c r="B46" s="9">
+        <v>100100</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E46" s="10">
+        <v>12</v>
+      </c>
+      <c r="F46" s="10">
+        <v>100</v>
+      </c>
+      <c r="G46" s="10">
+        <v>-1</v>
+      </c>
+      <c r="H46" s="1">
+        <v>0</v>
+      </c>
+      <c r="I46" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="J46" s="10">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>100</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="16.5">
+      <c r="A47" s="1">
+        <f t="shared" ref="A47:A56" si="6">B47*100+E47</f>
+        <v>20010010</v>
+      </c>
+      <c r="B47" s="9">
         <v>200100</v>
       </c>
-      <c r="C45" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D45" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="E45" s="10">
-        <v>10</v>
-      </c>
-      <c r="F45" s="10">
-        <v>10000</v>
-      </c>
-      <c r="G45" s="10">
-        <v>-1</v>
-      </c>
-      <c r="H45" s="1">
-        <v>0</v>
-      </c>
-      <c r="I45" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="J45" s="10">
-        <v>1</v>
-      </c>
-      <c r="K45">
-        <v>100</v>
-      </c>
-      <c r="L45"/>
-      <c r="M45"/>
-    </row>
-    <row r="46" s="1" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A46" s="1">
-        <f>B46*10+E46</f>
-        <v>2001020</v>
-      </c>
-      <c r="B46" s="9">
-        <v>200101</v>
-      </c>
-      <c r="C46" s="9" t="s">
+      <c r="C47" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D46" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="E46" s="10">
-        <v>10</v>
-      </c>
-      <c r="F46" s="10">
-        <v>1000000</v>
-      </c>
-      <c r="G46" s="10">
-        <v>-1</v>
-      </c>
-      <c r="H46" s="1">
-        <v>0</v>
-      </c>
-      <c r="I46" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="J46" s="10">
-        <v>1</v>
-      </c>
-      <c r="K46">
-        <v>100</v>
-      </c>
-      <c r="L46"/>
-      <c r="M46"/>
-    </row>
-    <row r="47" ht="16.5" spans="1:11">
-      <c r="A47" s="1">
-        <f>B47*10+E47</f>
-        <v>2003010</v>
-      </c>
-      <c r="B47" s="9">
-        <v>200300</v>
-      </c>
-      <c r="C47" s="9" t="s">
-        <v>29</v>
-      </c>
       <c r="D47" s="10" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E47" s="10">
         <v>10</v>
       </c>
       <c r="F47" s="10">
-        <v>100</v>
+        <v>10000</v>
       </c>
       <c r="G47" s="10">
         <v>-1</v>
@@ -3024,34 +2618,37 @@
         <v>0</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J47" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47">
         <v>100</v>
       </c>
-    </row>
-    <row r="48" ht="16.5" spans="1:11">
+      <c r="L47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="16.5">
       <c r="A48" s="1">
-        <f>B48*10+E48</f>
-        <v>2004010</v>
+        <f t="shared" si="6"/>
+        <v>20010110</v>
       </c>
       <c r="B48" s="9">
-        <v>200400</v>
+        <v>200101</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E48" s="10">
         <v>10</v>
       </c>
       <c r="F48" s="10">
-        <v>10000</v>
+        <v>1000000</v>
       </c>
       <c r="G48" s="10">
         <v>-1</v>
@@ -3060,34 +2657,37 @@
         <v>0</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J48" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48">
         <v>100</v>
       </c>
-    </row>
-    <row r="49" ht="16.5" spans="1:11">
+      <c r="L48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="16.5">
       <c r="A49" s="1">
-        <f>B49*10+E49</f>
-        <v>2005010</v>
+        <f t="shared" si="6"/>
+        <v>20030010</v>
       </c>
       <c r="B49" s="9">
-        <v>200500</v>
+        <v>200300</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E49" s="10">
         <v>10</v>
       </c>
       <c r="F49" s="10">
-        <v>1000000</v>
+        <v>100</v>
       </c>
       <c r="G49" s="10">
         <v>-1</v>
@@ -3096,34 +2696,37 @@
         <v>0</v>
       </c>
       <c r="I49" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J49" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49">
         <v>100</v>
       </c>
-    </row>
-    <row r="50" ht="16.5" spans="1:11">
+      <c r="L49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="16.5">
       <c r="A50" s="1">
-        <f>B50*10+E50</f>
-        <v>2006010</v>
+        <f t="shared" si="6"/>
+        <v>20040010</v>
       </c>
       <c r="B50" s="9">
-        <v>200600</v>
+        <v>200400</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E50" s="10">
         <v>10</v>
       </c>
       <c r="F50" s="10">
-        <v>100</v>
+        <v>10000</v>
       </c>
       <c r="G50" s="10">
         <v>-1</v>
@@ -3132,34 +2735,37 @@
         <v>0</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J50" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K50">
         <v>100</v>
       </c>
-    </row>
-    <row r="51" ht="16.5" spans="1:11">
+      <c r="L50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="16.5">
       <c r="A51" s="1">
-        <f>B51*10+E51</f>
-        <v>2007010</v>
+        <f t="shared" si="6"/>
+        <v>20050010</v>
       </c>
       <c r="B51" s="9">
-        <v>200700</v>
+        <v>200500</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E51" s="10">
         <v>10</v>
       </c>
       <c r="F51" s="10">
-        <v>10000</v>
+        <v>1000000</v>
       </c>
       <c r="G51" s="10">
         <v>-1</v>
@@ -3168,34 +2774,37 @@
         <v>0</v>
       </c>
       <c r="I51" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J51" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51">
         <v>100</v>
       </c>
-    </row>
-    <row r="52" ht="16.5" spans="1:11">
+      <c r="L51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="16.5">
       <c r="A52" s="1">
-        <f>B52*10+E52</f>
-        <v>2008010</v>
+        <f t="shared" si="6"/>
+        <v>20060010</v>
       </c>
       <c r="B52" s="9">
-        <v>200800</v>
+        <v>200600</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E52" s="10">
         <v>10</v>
       </c>
       <c r="F52" s="10">
-        <v>1000000</v>
+        <v>100</v>
       </c>
       <c r="G52" s="10">
         <v>-1</v>
@@ -3204,34 +2813,37 @@
         <v>0</v>
       </c>
       <c r="I52" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J52" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52">
         <v>100</v>
       </c>
-    </row>
-    <row r="53" ht="16.5" spans="1:11">
+      <c r="L52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="16.5">
       <c r="A53" s="1">
-        <f>B53*10+E53</f>
-        <v>2009010</v>
+        <f t="shared" si="6"/>
+        <v>20070010</v>
       </c>
       <c r="B53" s="9">
-        <v>200900</v>
+        <v>200700</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E53" s="10">
         <v>10</v>
       </c>
       <c r="F53" s="10">
-        <v>1000000</v>
+        <v>10000</v>
       </c>
       <c r="G53" s="10">
         <v>-1</v>
@@ -3240,28 +2852,31 @@
         <v>0</v>
       </c>
       <c r="I53" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J53" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K53">
         <v>100</v>
       </c>
-    </row>
-    <row r="54" ht="16.5" spans="1:11">
+      <c r="L53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="16.5">
       <c r="A54" s="1">
-        <f>B54*10+E54</f>
-        <v>2010010</v>
+        <f t="shared" si="6"/>
+        <v>20080010</v>
       </c>
       <c r="B54" s="9">
-        <v>201000</v>
+        <v>200800</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E54" s="10">
         <v>10</v>
@@ -3276,18 +2891,99 @@
         <v>0</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J54" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K54">
         <v>100</v>
       </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="16.5">
+      <c r="A55" s="1">
+        <f t="shared" si="6"/>
+        <v>20090010</v>
+      </c>
+      <c r="B55" s="9">
+        <v>200900</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E55" s="10">
+        <v>10</v>
+      </c>
+      <c r="F55" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="G55" s="10">
+        <v>-1</v>
+      </c>
+      <c r="H55" s="1">
+        <v>0</v>
+      </c>
+      <c r="I55" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="J55" s="10">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>100</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="16.5">
+      <c r="A56" s="1">
+        <f t="shared" si="6"/>
+        <v>20100010</v>
+      </c>
+      <c r="B56" s="9">
+        <v>201000</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E56" s="10">
+        <v>10</v>
+      </c>
+      <c r="F56" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="G56" s="10">
+        <v>-1</v>
+      </c>
+      <c r="H56" s="1">
+        <v>0</v>
+      </c>
+      <c r="I56" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="J56" s="10">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>100</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -1,38 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\hall\resources\sample\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC001C20-83D1-46F2-A38A-03F84C009AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32625" yWindow="2910" windowWidth="21600" windowHeight="11385" tabRatio="794" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Warehouse" sheetId="42" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -41,7 +47,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -50,40 +55,37 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>最小准入金币</t>
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>-1 表示无上限</t>
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -92,7 +94,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -103,14 +104,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="L1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -119,7 +119,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -133,7 +132,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="49">
   <si>
     <t>sid</t>
   </si>
@@ -198,7 +197,13 @@
     <t>participants_max</t>
   </si>
   <si>
-    <t>RoomDeletion_Solution</t>
+    <t>roomDeletion_Solution</t>
+  </si>
+  <si>
+    <t>betShow</t>
+  </si>
+  <si>
+    <t>marqueeTrigger</t>
   </si>
   <si>
     <t>金矿大亨</t>
@@ -274,24 +279,19 @@
   </si>
   <si>
     <t>房间场-高级</t>
-  </si>
-  <si>
-    <t>房间场</t>
-  </si>
-  <si>
-    <t>betShow</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>marqueeTrigger</t>
-    <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -330,60 +330,173 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Noto Sans CJK SC Regular"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -392,18 +505,204 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7993408001953185"/>
+        <fgColor theme="5" tint="0.799340800195319"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -426,53 +725,295 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="12">
+  <cellStyleXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -481,39 +1022,82 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="12">
+  <cellStyles count="60">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="常规 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="常规 2 2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
-    <cellStyle name="常规 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
-    <cellStyle name="常规 3 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
-    <cellStyle name="常规 4" xfId="6" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
-    <cellStyle name="常规 5" xfId="7" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
-    <cellStyle name="常规 6" xfId="8" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
-    <cellStyle name="常规 6 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
-    <cellStyle name="常规 6 2 2" xfId="10" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
-    <cellStyle name="常规 7" xfId="11" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
+    <cellStyle name="常规 2 2" xfId="50"/>
+    <cellStyle name="常规 2 2 2" xfId="51"/>
+    <cellStyle name="常规 3" xfId="52"/>
+    <cellStyle name="常规 3 2" xfId="53"/>
+    <cellStyle name="常规 4" xfId="54"/>
+    <cellStyle name="常规 5" xfId="55"/>
+    <cellStyle name="常规 6" xfId="56"/>
+    <cellStyle name="常规 6 2" xfId="57"/>
+    <cellStyle name="常规 6 2 2" xfId="58"/>
+    <cellStyle name="常规 7" xfId="59"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -771,13 +1355,13 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M56"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="9.375" style="1"/>
@@ -785,16 +1369,16 @@
     <col min="4" max="4" width="12" style="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="1"/>
     <col min="7" max="7" width="11.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.25" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9.75" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.625" customWidth="1"/>
+    <col min="8" max="8" width="9.25833333333333" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9.7" style="1" customWidth="1"/>
+    <col min="10" max="10" width="13.9666666666667" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.675" customWidth="1"/>
     <col min="12" max="12" width="19.5" customWidth="1"/>
-    <col min="13" max="13" width="9" customWidth="1"/>
+    <col min="13" max="13" width="8.96666666666667" customWidth="1"/>
     <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="16.5">
+    <row r="1" ht="16.5" spans="1:12">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -832,7 +1416,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="16.5">
+    <row r="2" ht="16.5" spans="1:12">
       <c r="A2" s="4" t="s">
         <v>10</v>
       </c>
@@ -866,7 +1450,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="16.5">
+    <row r="3" ht="16.5" spans="1:12">
       <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
@@ -891,14 +1475,14 @@
       <c r="J3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="L3" s="14" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="16.5">
+      <c r="K3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" ht="16.5" spans="1:12">
       <c r="A5" s="1">
         <f>B5*10+E5</f>
         <v>1001001</v>
@@ -907,10 +1491,10 @@
         <v>100100</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -925,10 +1509,10 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="K5">
         <v>1000</v>
@@ -938,9 +1522,9 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="16.5">
+    <row r="6" ht="16.5" spans="1:12">
       <c r="A6" s="1">
-        <f t="shared" ref="A6:A43" si="0">B6*10+E6</f>
+        <f t="shared" ref="A6:A54" si="0">B6*10+E6</f>
         <v>1001002</v>
       </c>
       <c r="B6" s="7">
@@ -951,7 +1535,7 @@
         <v>金矿大亨</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -966,10 +1550,10 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="K6">
         <v>100000</v>
@@ -979,7 +1563,7 @@
         <v>50000000</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="16.5">
+    <row r="7" ht="16.5" spans="1:12">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>1001003</v>
@@ -992,7 +1576,7 @@
         <v>金矿大亨</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
@@ -1007,10 +1591,10 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J7" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="K7">
         <v>10000000</v>
@@ -1020,7 +1604,7 @@
         <v>5000000000</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="16.5">
+    <row r="8" ht="16.5" spans="1:12">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>2001001</v>
@@ -1029,10 +1613,10 @@
         <v>200100</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -1047,10 +1631,10 @@
         <v>0</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="K8">
         <v>1000</v>
@@ -1060,7 +1644,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="16.5">
+    <row r="9" ht="16.5" spans="1:12">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>2001002</v>
@@ -1073,7 +1657,7 @@
         <v>红黑大战</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -1088,10 +1672,10 @@
         <v>0</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="K9">
         <v>100000</v>
@@ -1101,7 +1685,7 @@
         <v>50000000</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="16.5">
+    <row r="10" ht="16.5" spans="1:12">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>2001003</v>
@@ -1114,7 +1698,7 @@
         <v>红黑大战</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E10" s="1">
         <v>3</v>
@@ -1129,10 +1713,10 @@
         <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="K10">
         <v>10000000</v>
@@ -1142,7 +1726,7 @@
         <v>5000000000</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="16.5">
+    <row r="11" ht="16.5" spans="1:12">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>2001011</v>
@@ -1151,10 +1735,10 @@
         <v>200101</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -1169,10 +1753,10 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="K11">
         <v>1000</v>
@@ -1182,7 +1766,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="16.5">
+    <row r="12" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>2001012</v>
@@ -1195,7 +1779,7 @@
         <v>龙虎斗</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
@@ -1210,10 +1794,10 @@
         <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J12" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="K12">
         <v>100000</v>
@@ -1222,8 +1806,9 @@
         <f t="shared" si="2"/>
         <v>50000000</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" ht="16.5">
+      <c r="M12"/>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>2001013</v>
@@ -1236,7 +1821,7 @@
         <v>龙虎斗</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E13" s="1">
         <v>3</v>
@@ -1251,10 +1836,10 @@
         <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J13" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="K13">
         <v>10000000</v>
@@ -1263,8 +1848,9 @@
         <f t="shared" si="2"/>
         <v>5000000000</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" ht="16.5">
+      <c r="M13"/>
+    </row>
+    <row r="14" ht="16.5" spans="1:12">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>2003001</v>
@@ -1273,10 +1859,10 @@
         <v>200300</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -1291,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J14" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="K14">
         <v>1000</v>
@@ -1304,7 +1890,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="16.5">
+    <row r="15" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>2003002</v>
@@ -1317,7 +1903,7 @@
         <v>飞禽走兽</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E15" s="1">
         <v>2</v>
@@ -1332,10 +1918,10 @@
         <v>0</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J15" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="K15">
         <v>100000</v>
@@ -1344,8 +1930,9 @@
         <f t="shared" si="2"/>
         <v>50000000</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" ht="16.5">
+      <c r="M15"/>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>2003003</v>
@@ -1358,7 +1945,7 @@
         <v>飞禽走兽</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E16" s="1">
         <v>3</v>
@@ -1373,10 +1960,10 @@
         <v>0</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J16" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="K16">
         <v>10000000</v>
@@ -1385,8 +1972,9 @@
         <f t="shared" si="2"/>
         <v>5000000000</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" ht="16.5">
+      <c r="M16"/>
+    </row>
+    <row r="17" ht="16.5" spans="1:12">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>2004001</v>
@@ -1395,10 +1983,10 @@
         <v>200400</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -1413,10 +2001,10 @@
         <v>0</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J17" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J17" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="K17">
         <v>1000</v>
@@ -1426,7 +2014,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="16.5">
+    <row r="18" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>2004002</v>
@@ -1439,7 +2027,7 @@
         <v>豪车俱乐部</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E18" s="1">
         <v>2</v>
@@ -1454,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J18" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="K18">
         <v>100000</v>
@@ -1466,8 +2054,9 @@
         <f t="shared" si="2"/>
         <v>50000000</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" ht="16.5">
+      <c r="M18"/>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>2004003</v>
@@ -1480,7 +2069,7 @@
         <v>豪车俱乐部</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E19" s="1">
         <v>3</v>
@@ -1495,10 +2084,10 @@
         <v>0</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J19" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="K19">
         <v>10000000</v>
@@ -1507,8 +2096,9 @@
         <f t="shared" si="2"/>
         <v>5000000000</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" ht="16.5">
+      <c r="M19"/>
+    </row>
+    <row r="20" ht="16.5" spans="1:12">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>2005001</v>
@@ -1517,10 +2107,10 @@
         <v>200500</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
@@ -1535,10 +2125,10 @@
         <v>0</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J20" s="11" t="s">
-        <v>33</v>
+        <v>26</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>35</v>
       </c>
       <c r="K20">
         <v>1000</v>
@@ -1548,7 +2138,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="16.5">
+    <row r="21" ht="16.5" spans="1:12">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>2005002</v>
@@ -1557,10 +2147,10 @@
         <v>200500</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E21" s="1">
         <v>2</v>
@@ -1575,10 +2165,10 @@
         <v>0</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J21" s="11" t="s">
-        <v>33</v>
+        <v>26</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>35</v>
       </c>
       <c r="K21">
         <v>100000</v>
@@ -1588,7 +2178,7 @@
         <v>50000000</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="16.5">
+    <row r="22" ht="16.5" spans="1:12">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>2005003</v>
@@ -1597,10 +2187,10 @@
         <v>200500</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E22" s="1">
         <v>3</v>
@@ -1615,10 +2205,10 @@
         <v>0</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J22" s="11" t="s">
-        <v>33</v>
+        <v>26</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>35</v>
       </c>
       <c r="K22">
         <v>10000000</v>
@@ -1628,7 +2218,7 @@
         <v>5000000000</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="16.5">
+    <row r="23" ht="16.5" spans="1:12">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>2006001</v>
@@ -1637,10 +2227,10 @@
         <v>200600</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -1655,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J23" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J23" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="K23">
         <v>1000</v>
@@ -1668,7 +2258,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="16.5">
+    <row r="24" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>2006002</v>
@@ -1681,7 +2271,7 @@
         <v>三个骰子</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E24" s="1">
         <v>2</v>
@@ -1696,10 +2286,10 @@
         <v>0</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J24" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J24" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="K24">
         <v>100000</v>
@@ -1708,8 +2298,9 @@
         <f t="shared" si="2"/>
         <v>50000000</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" ht="16.5">
+      <c r="M24"/>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>2006003</v>
@@ -1722,7 +2313,7 @@
         <v>三个骰子</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E25" s="1">
         <v>3</v>
@@ -1737,10 +2328,10 @@
         <v>0</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J25" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J25" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="K25">
         <v>10000000</v>
@@ -1749,8 +2340,9 @@
         <f t="shared" si="2"/>
         <v>5000000000</v>
       </c>
-    </row>
-    <row r="26" spans="1:12" ht="16.5">
+      <c r="M25"/>
+    </row>
+    <row r="26" ht="16.5" spans="1:12">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>2007001</v>
@@ -1759,10 +2351,10 @@
         <v>200700</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -1777,10 +2369,10 @@
         <v>0</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J26" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J26" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="K26">
         <v>1000</v>
@@ -1790,7 +2382,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="16.5">
+    <row r="27" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>2007002</v>
@@ -1803,7 +2395,7 @@
         <v>色碟</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E27" s="1">
         <v>2</v>
@@ -1818,10 +2410,10 @@
         <v>0</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J27" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J27" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="K27">
         <v>100000</v>
@@ -1830,8 +2422,9 @@
         <f t="shared" si="2"/>
         <v>50000000</v>
       </c>
-    </row>
-    <row r="28" spans="1:12" ht="16.5">
+      <c r="M27"/>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
         <v>2007003</v>
@@ -1844,7 +2437,7 @@
         <v>色碟</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E28" s="1">
         <v>3</v>
@@ -1859,10 +2452,10 @@
         <v>0</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J28" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J28" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="K28">
         <v>10000000</v>
@@ -1871,8 +2464,9 @@
         <f t="shared" si="2"/>
         <v>5000000000</v>
       </c>
-    </row>
-    <row r="29" spans="1:12" ht="16.5">
+      <c r="M28"/>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
         <v>2008001</v>
@@ -1881,10 +2475,10 @@
         <v>200800</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -1899,10 +2493,10 @@
         <v>0</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J29" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J29" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="K29">
         <v>1000</v>
@@ -1911,8 +2505,9 @@
         <f t="shared" si="2"/>
         <v>500000</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" ht="16.5">
+      <c r="M29"/>
+    </row>
+    <row r="30" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
         <v>2008002</v>
@@ -1921,10 +2516,10 @@
         <v>200800</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
@@ -1939,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J30" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J30" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="K30">
         <v>100000</v>
@@ -1951,8 +2546,9 @@
         <f t="shared" si="2"/>
         <v>50000000</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" ht="16.5">
+      <c r="M30"/>
+    </row>
+    <row r="31" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
         <v>2008003</v>
@@ -1961,10 +2557,10 @@
         <v>200800</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E31" s="1">
         <v>3</v>
@@ -1979,10 +2575,10 @@
         <v>0</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J31" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J31" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="K31">
         <v>10000000</v>
@@ -1991,8 +2587,9 @@
         <f t="shared" si="2"/>
         <v>5000000000</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" ht="16.5">
+      <c r="M31"/>
+    </row>
+    <row r="32" ht="16.5" spans="1:12">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
         <v>2009001</v>
@@ -2001,10 +2598,10 @@
         <v>200900</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -2019,10 +2616,10 @@
         <v>0</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J32" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J32" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="K32">
         <v>1000</v>
@@ -2032,7 +2629,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="16.5">
+    <row r="33" ht="16.5" spans="1:12">
       <c r="A33" s="1">
         <f t="shared" si="0"/>
         <v>2009002</v>
@@ -2045,7 +2642,7 @@
         <v>鱼虾蟹</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E33" s="1">
         <v>2</v>
@@ -2060,10 +2657,10 @@
         <v>0</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J33" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J33" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="K33">
         <v>100000</v>
@@ -2073,7 +2670,7 @@
         <v>50000000</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="16.5">
+    <row r="34" ht="16.5" spans="1:12">
       <c r="A34" s="1">
         <f t="shared" si="0"/>
         <v>2009003</v>
@@ -2086,7 +2683,7 @@
         <v>鱼虾蟹</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E34" s="1">
         <v>3</v>
@@ -2101,10 +2698,10 @@
         <v>0</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J34" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J34" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="K34">
         <v>10000000</v>
@@ -2114,7 +2711,7 @@
         <v>5000000000</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="16.5">
+    <row r="35" ht="16.5" spans="1:12">
       <c r="A35" s="1">
         <f t="shared" si="0"/>
         <v>2010001</v>
@@ -2123,10 +2720,10 @@
         <v>201000</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
@@ -2141,10 +2738,10 @@
         <v>0</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J35" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J35" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="K35">
         <v>1000</v>
@@ -2154,7 +2751,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="16.5">
+    <row r="36" ht="16.5" spans="1:12">
       <c r="A36" s="1">
         <f t="shared" si="0"/>
         <v>2010002</v>
@@ -2163,10 +2760,10 @@
         <v>201000</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E36" s="1">
         <v>2</v>
@@ -2181,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J36" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J36" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="K36">
         <v>100000</v>
@@ -2194,7 +2791,7 @@
         <v>50000000</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="16.5">
+    <row r="37" ht="16.5" spans="1:12">
       <c r="A37" s="1">
         <f t="shared" si="0"/>
         <v>2010003</v>
@@ -2203,10 +2800,10 @@
         <v>201000</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E37" s="1">
         <v>3</v>
@@ -2221,10 +2818,10 @@
         <v>0</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J37" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J37" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="K37">
         <v>10000000</v>
@@ -2234,7 +2831,7 @@
         <v>5000000000</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="16.5">
+    <row r="38" ht="16.5" spans="1:12">
       <c r="A38" s="1">
         <f t="shared" si="0"/>
         <v>3001001</v>
@@ -2243,10 +2840,10 @@
         <v>300100</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
@@ -2260,11 +2857,11 @@
       <c r="H38" s="1">
         <v>0</v>
       </c>
-      <c r="I38" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="J38" s="12" t="s">
-        <v>41</v>
+      <c r="I38" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="J38" s="13" t="s">
+        <v>43</v>
       </c>
       <c r="K38">
         <v>500</v>
@@ -2274,7 +2871,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="16.5">
+    <row r="39" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A39" s="1">
         <f t="shared" si="0"/>
         <v>3001002</v>
@@ -2283,10 +2880,10 @@
         <v>300100</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
@@ -2300,11 +2897,11 @@
       <c r="H39" s="1">
         <v>0</v>
       </c>
-      <c r="I39" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="J39" s="12" t="s">
-        <v>41</v>
+      <c r="I39" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="J39" s="13" t="s">
+        <v>43</v>
       </c>
       <c r="K39">
         <v>20000</v>
@@ -2313,8 +2910,9 @@
         <f t="shared" si="5"/>
         <v>10000000</v>
       </c>
-    </row>
-    <row r="40" spans="1:12" ht="16.5">
+      <c r="M39"/>
+    </row>
+    <row r="40" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A40" s="1">
         <f t="shared" si="0"/>
         <v>3001003</v>
@@ -2323,10 +2921,10 @@
         <v>300100</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E40" s="1">
         <v>3</v>
@@ -2340,11 +2938,11 @@
       <c r="H40" s="1">
         <v>0</v>
       </c>
-      <c r="I40" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="J40" s="12" t="s">
-        <v>41</v>
+      <c r="I40" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="J40" s="13" t="s">
+        <v>43</v>
       </c>
       <c r="K40">
         <v>2000000</v>
@@ -2353,8 +2951,9 @@
         <f t="shared" si="5"/>
         <v>1000000000</v>
       </c>
-    </row>
-    <row r="41" spans="1:12" ht="16.5">
+      <c r="M40"/>
+    </row>
+    <row r="41" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A41" s="1">
         <f t="shared" si="0"/>
         <v>3002001</v>
@@ -2363,10 +2962,10 @@
         <v>300200</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E41" s="1">
         <v>1</v>
@@ -2380,11 +2979,11 @@
       <c r="H41" s="1">
         <v>0</v>
       </c>
-      <c r="I41" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="J41" s="12" t="s">
-        <v>41</v>
+      <c r="I41" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="J41" s="13" t="s">
+        <v>43</v>
       </c>
       <c r="K41">
         <v>500</v>
@@ -2393,8 +2992,9 @@
         <f t="shared" si="5"/>
         <v>250000</v>
       </c>
-    </row>
-    <row r="42" spans="1:12" ht="16.5">
+      <c r="M41"/>
+    </row>
+    <row r="42" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A42" s="1">
         <f t="shared" si="0"/>
         <v>3002002</v>
@@ -2403,10 +3003,10 @@
         <v>300200</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E42" s="1">
         <v>2</v>
@@ -2420,11 +3020,11 @@
       <c r="H42" s="1">
         <v>0</v>
       </c>
-      <c r="I42" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="J42" s="12" t="s">
-        <v>41</v>
+      <c r="I42" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="J42" s="13" t="s">
+        <v>43</v>
       </c>
       <c r="K42">
         <v>20000</v>
@@ -2433,8 +3033,9 @@
         <f t="shared" si="5"/>
         <v>10000000</v>
       </c>
-    </row>
-    <row r="43" spans="1:12" ht="16.5">
+      <c r="M42"/>
+    </row>
+    <row r="43" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A43" s="1">
         <f t="shared" si="0"/>
         <v>3002003</v>
@@ -2443,10 +3044,10 @@
         <v>300200</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E43" s="1">
         <v>3</v>
@@ -2460,11 +3061,11 @@
       <c r="H43" s="1">
         <v>0</v>
       </c>
-      <c r="I43" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="J43" s="12" t="s">
-        <v>41</v>
+      <c r="I43" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="J43" s="13" t="s">
+        <v>43</v>
       </c>
       <c r="K43">
         <v>2000000</v>
@@ -2473,26 +3074,27 @@
         <f t="shared" si="5"/>
         <v>1000000000</v>
       </c>
-    </row>
-    <row r="44" spans="1:12" ht="16.5">
+      <c r="M43"/>
+    </row>
+    <row r="44" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A44" s="1">
-        <f>B44*100+E44</f>
-        <v>10010010</v>
+        <f t="shared" ref="A44:A50" si="6">B44*100+E44</f>
+        <v>20010010</v>
       </c>
       <c r="B44" s="9">
-        <v>100100</v>
+        <v>200100</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E44" s="10">
         <v>10</v>
       </c>
       <c r="F44" s="10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G44" s="10">
         <v>-1</v>
@@ -2501,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J44" s="10">
         <v>0</v>
@@ -2512,26 +3114,27 @@
       <c r="L44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:12" ht="16.5">
+      <c r="M44"/>
+    </row>
+    <row r="45" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A45" s="1">
-        <f>B45*100+E45</f>
-        <v>10010011</v>
+        <f t="shared" si="6"/>
+        <v>20010011</v>
       </c>
       <c r="B45" s="9">
-        <v>100100</v>
+        <v>200100</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E45" s="10">
         <v>11</v>
       </c>
       <c r="F45" s="10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G45" s="10">
         <v>-1</v>
@@ -2540,7 +3143,7 @@
         <v>0</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J45" s="10">
         <v>0</v>
@@ -2551,26 +3154,27 @@
       <c r="L45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:12" ht="16.5">
+      <c r="M45"/>
+    </row>
+    <row r="46" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A46" s="1">
-        <f>B46*100+E46</f>
-        <v>10010012</v>
+        <f t="shared" si="6"/>
+        <v>20010012</v>
       </c>
       <c r="B46" s="9">
-        <v>100100</v>
+        <v>200100</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E46" s="10">
         <v>12</v>
       </c>
       <c r="F46" s="10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G46" s="10">
         <v>-1</v>
@@ -2579,7 +3183,7 @@
         <v>0</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J46" s="10">
         <v>0</v>
@@ -2590,26 +3194,27 @@
       <c r="L46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:12" ht="16.5">
+      <c r="M46"/>
+    </row>
+    <row r="47" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A47" s="1">
-        <f t="shared" ref="A47:A56" si="6">B47*100+E47</f>
-        <v>20010010</v>
+        <f t="shared" si="6"/>
+        <v>20010110</v>
       </c>
       <c r="B47" s="9">
-        <v>200100</v>
+        <v>200101</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E47" s="10">
         <v>10</v>
       </c>
       <c r="F47" s="10">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="G47" s="10">
         <v>-1</v>
@@ -2618,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J47" s="10">
         <v>0</v>
@@ -2629,26 +3234,27 @@
       <c r="L47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:12" ht="16.5">
+      <c r="M47"/>
+    </row>
+    <row r="48" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A48" s="1">
         <f t="shared" si="6"/>
-        <v>20010110</v>
+        <v>20010111</v>
       </c>
       <c r="B48" s="9">
         <v>200101</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D48" s="10" t="s">
         <v>47</v>
       </c>
       <c r="E48" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F48" s="10">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G48" s="10">
         <v>-1</v>
@@ -2657,7 +3263,7 @@
         <v>0</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J48" s="10">
         <v>0</v>
@@ -2668,26 +3274,27 @@
       <c r="L48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:12" ht="16.5">
+      <c r="M48"/>
+    </row>
+    <row r="49" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A49" s="1">
         <f t="shared" si="6"/>
-        <v>20030010</v>
+        <v>20010112</v>
       </c>
       <c r="B49" s="9">
-        <v>200300</v>
+        <v>200101</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E49" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F49" s="10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G49" s="10">
         <v>-1</v>
@@ -2696,7 +3303,7 @@
         <v>0</v>
       </c>
       <c r="I49" s="10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J49" s="10">
         <v>0</v>
@@ -2707,26 +3314,27 @@
       <c r="L49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:12" ht="16.5">
+      <c r="M49"/>
+    </row>
+    <row r="50" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A50" s="1">
         <f t="shared" si="6"/>
-        <v>20040010</v>
+        <v>20030010</v>
       </c>
       <c r="B50" s="9">
-        <v>200400</v>
+        <v>200300</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E50" s="10">
         <v>10</v>
       </c>
       <c r="F50" s="10">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="G50" s="10">
         <v>-1</v>
@@ -2735,7 +3343,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J50" s="10">
         <v>0</v>
@@ -2746,14 +3354,15 @@
       <c r="L50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:12" ht="16.5">
+      <c r="M50"/>
+    </row>
+    <row r="51" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A51" s="1">
-        <f t="shared" si="6"/>
-        <v>20050010</v>
+        <f t="shared" ref="A51:A59" si="7">B51*100+E51</f>
+        <v>20030011</v>
       </c>
       <c r="B51" s="9">
-        <v>200500</v>
+        <v>200300</v>
       </c>
       <c r="C51" s="9" t="s">
         <v>32</v>
@@ -2762,10 +3371,10 @@
         <v>47</v>
       </c>
       <c r="E51" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F51" s="10">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G51" s="10">
         <v>-1</v>
@@ -2774,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="I51" s="10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J51" s="10">
         <v>0</v>
@@ -2785,26 +3394,27 @@
       <c r="L51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:12" ht="16.5">
+      <c r="M51"/>
+    </row>
+    <row r="52" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A52" s="1">
-        <f t="shared" si="6"/>
-        <v>20060010</v>
+        <f t="shared" si="7"/>
+        <v>20030012</v>
       </c>
       <c r="B52" s="9">
-        <v>200600</v>
+        <v>200300</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E52" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F52" s="10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G52" s="10">
         <v>-1</v>
@@ -2813,7 +3423,7 @@
         <v>0</v>
       </c>
       <c r="I52" s="10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J52" s="10">
         <v>0</v>
@@ -2824,26 +3434,27 @@
       <c r="L52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:12" ht="16.5">
+      <c r="M52"/>
+    </row>
+    <row r="53" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A53" s="1">
-        <f t="shared" si="6"/>
-        <v>20070010</v>
+        <f t="shared" si="7"/>
+        <v>20040010</v>
       </c>
       <c r="B53" s="9">
-        <v>200700</v>
+        <v>200400</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E53" s="10">
         <v>10</v>
       </c>
       <c r="F53" s="10">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="G53" s="10">
         <v>-1</v>
@@ -2852,7 +3463,7 @@
         <v>0</v>
       </c>
       <c r="I53" s="10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J53" s="10">
         <v>0</v>
@@ -2863,26 +3474,27 @@
       <c r="L53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:12" ht="16.5">
+      <c r="M53"/>
+    </row>
+    <row r="54" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A54" s="1">
-        <f t="shared" si="6"/>
-        <v>20080010</v>
+        <f t="shared" si="7"/>
+        <v>20040011</v>
       </c>
       <c r="B54" s="9">
-        <v>200800</v>
+        <v>200400</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D54" s="10" t="s">
         <v>47</v>
       </c>
       <c r="E54" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F54" s="10">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G54" s="10">
         <v>-1</v>
@@ -2891,7 +3503,7 @@
         <v>0</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J54" s="10">
         <v>0</v>
@@ -2902,26 +3514,27 @@
       <c r="L54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:12" ht="16.5">
+      <c r="M54"/>
+    </row>
+    <row r="55" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A55" s="1">
-        <f t="shared" si="6"/>
-        <v>20090010</v>
+        <f t="shared" si="7"/>
+        <v>20040012</v>
       </c>
       <c r="B55" s="9">
-        <v>200900</v>
+        <v>200400</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E55" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F55" s="10">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G55" s="10">
         <v>-1</v>
@@ -2930,7 +3543,7 @@
         <v>0</v>
       </c>
       <c r="I55" s="10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J55" s="10">
         <v>0</v>
@@ -2941,26 +3554,27 @@
       <c r="L55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:12" ht="16.5">
+      <c r="M55"/>
+    </row>
+    <row r="56" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A56" s="1">
-        <f t="shared" si="6"/>
-        <v>20100010</v>
+        <f t="shared" si="7"/>
+        <v>20050010</v>
       </c>
       <c r="B56" s="9">
-        <v>201000</v>
+        <v>200500</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E56" s="10">
         <v>10</v>
       </c>
       <c r="F56" s="10">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G56" s="10">
         <v>-1</v>
@@ -2969,7 +3583,7 @@
         <v>0</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J56" s="10">
         <v>0</v>
@@ -2980,10 +3594,559 @@
       <c r="L56">
         <v>0</v>
       </c>
+      <c r="M56"/>
+    </row>
+    <row r="57" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A57" s="1">
+        <f t="shared" si="7"/>
+        <v>20050011</v>
+      </c>
+      <c r="B57" s="9">
+        <v>200500</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E57" s="10">
+        <v>11</v>
+      </c>
+      <c r="F57" s="10">
+        <v>0</v>
+      </c>
+      <c r="G57" s="10">
+        <v>-1</v>
+      </c>
+      <c r="H57" s="1">
+        <v>0</v>
+      </c>
+      <c r="I57" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J57" s="10">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>100</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57"/>
+    </row>
+    <row r="58" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A58" s="1">
+        <f t="shared" si="7"/>
+        <v>20050012</v>
+      </c>
+      <c r="B58" s="9">
+        <v>200500</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E58" s="10">
+        <v>12</v>
+      </c>
+      <c r="F58" s="10">
+        <v>0</v>
+      </c>
+      <c r="G58" s="10">
+        <v>-1</v>
+      </c>
+      <c r="H58" s="1">
+        <v>0</v>
+      </c>
+      <c r="I58" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J58" s="10">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>100</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58"/>
+    </row>
+    <row r="59" ht="16.5" spans="1:12">
+      <c r="A59" s="1">
+        <f t="shared" si="7"/>
+        <v>20060010</v>
+      </c>
+      <c r="B59" s="9">
+        <v>200600</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D59" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E59" s="10">
+        <v>10</v>
+      </c>
+      <c r="F59" s="10">
+        <v>0</v>
+      </c>
+      <c r="G59" s="10">
+        <v>-1</v>
+      </c>
+      <c r="H59" s="1">
+        <v>0</v>
+      </c>
+      <c r="I59" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J59" s="10">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>100</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" ht="16.5" spans="1:12">
+      <c r="A60" s="1">
+        <f t="shared" ref="A60:A70" si="8">B60*100+E60</f>
+        <v>20060011</v>
+      </c>
+      <c r="B60" s="9">
+        <v>200600</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D60" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E60" s="10">
+        <v>11</v>
+      </c>
+      <c r="F60" s="10">
+        <v>0</v>
+      </c>
+      <c r="G60" s="10">
+        <v>-1</v>
+      </c>
+      <c r="H60" s="1">
+        <v>0</v>
+      </c>
+      <c r="I60" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J60" s="10">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>100</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" ht="16.5" spans="1:12">
+      <c r="A61" s="1">
+        <f t="shared" si="8"/>
+        <v>20060012</v>
+      </c>
+      <c r="B61" s="9">
+        <v>200600</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D61" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E61" s="10">
+        <v>12</v>
+      </c>
+      <c r="F61" s="10">
+        <v>0</v>
+      </c>
+      <c r="G61" s="10">
+        <v>-1</v>
+      </c>
+      <c r="H61" s="1">
+        <v>0</v>
+      </c>
+      <c r="I61" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J61" s="10">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>100</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" ht="16.5" spans="1:12">
+      <c r="A62" s="1">
+        <f t="shared" si="8"/>
+        <v>20070010</v>
+      </c>
+      <c r="B62" s="9">
+        <v>200700</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D62" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E62" s="10">
+        <v>10</v>
+      </c>
+      <c r="F62" s="10">
+        <v>0</v>
+      </c>
+      <c r="G62" s="10">
+        <v>-1</v>
+      </c>
+      <c r="H62" s="1">
+        <v>0</v>
+      </c>
+      <c r="I62" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J62" s="10">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>100</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" ht="16.5" spans="1:12">
+      <c r="A63" s="1">
+        <f t="shared" si="8"/>
+        <v>20070011</v>
+      </c>
+      <c r="B63" s="9">
+        <v>200700</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D63" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E63" s="10">
+        <v>11</v>
+      </c>
+      <c r="F63" s="10">
+        <v>0</v>
+      </c>
+      <c r="G63" s="10">
+        <v>-1</v>
+      </c>
+      <c r="H63" s="1">
+        <v>0</v>
+      </c>
+      <c r="I63" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J63" s="10">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>100</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" ht="16.5" spans="1:12">
+      <c r="A64" s="1">
+        <f t="shared" si="8"/>
+        <v>20070012</v>
+      </c>
+      <c r="B64" s="9">
+        <v>200700</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D64" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E64" s="10">
+        <v>12</v>
+      </c>
+      <c r="F64" s="10">
+        <v>0</v>
+      </c>
+      <c r="G64" s="10">
+        <v>-1</v>
+      </c>
+      <c r="H64" s="1">
+        <v>0</v>
+      </c>
+      <c r="I64" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J64" s="10">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>100</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" ht="16.5" spans="1:12">
+      <c r="A65" s="1">
+        <f t="shared" si="8"/>
+        <v>20080010</v>
+      </c>
+      <c r="B65" s="9">
+        <v>200800</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D65" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E65" s="10">
+        <v>10</v>
+      </c>
+      <c r="F65" s="10">
+        <v>0</v>
+      </c>
+      <c r="G65" s="10">
+        <v>-1</v>
+      </c>
+      <c r="H65" s="1">
+        <v>0</v>
+      </c>
+      <c r="I65" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J65" s="10">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>100</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" ht="16.5" spans="1:12">
+      <c r="A66" s="1">
+        <f t="shared" si="8"/>
+        <v>20080011</v>
+      </c>
+      <c r="B66" s="9">
+        <v>200800</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D66" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E66" s="10">
+        <v>11</v>
+      </c>
+      <c r="F66" s="10">
+        <v>0</v>
+      </c>
+      <c r="G66" s="10">
+        <v>-1</v>
+      </c>
+      <c r="H66" s="1">
+        <v>0</v>
+      </c>
+      <c r="I66" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J66" s="10">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>100</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" ht="16.5" spans="1:12">
+      <c r="A67" s="1">
+        <f t="shared" si="8"/>
+        <v>20080012</v>
+      </c>
+      <c r="B67" s="9">
+        <v>200800</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D67" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E67" s="10">
+        <v>12</v>
+      </c>
+      <c r="F67" s="10">
+        <v>0</v>
+      </c>
+      <c r="G67" s="10">
+        <v>-1</v>
+      </c>
+      <c r="H67" s="1">
+        <v>0</v>
+      </c>
+      <c r="I67" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J67" s="10">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>100</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" ht="16.5" spans="1:12">
+      <c r="A68" s="1">
+        <f t="shared" si="8"/>
+        <v>20090010</v>
+      </c>
+      <c r="B68" s="9">
+        <v>200900</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D68" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E68" s="10">
+        <v>10</v>
+      </c>
+      <c r="F68" s="10">
+        <v>0</v>
+      </c>
+      <c r="G68" s="10">
+        <v>-1</v>
+      </c>
+      <c r="H68" s="1">
+        <v>0</v>
+      </c>
+      <c r="I68" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J68" s="10">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>100</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" ht="16.5" spans="1:12">
+      <c r="A69" s="1">
+        <f t="shared" si="8"/>
+        <v>20090011</v>
+      </c>
+      <c r="B69" s="9">
+        <v>200900</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D69" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E69" s="10">
+        <v>11</v>
+      </c>
+      <c r="F69" s="10">
+        <v>0</v>
+      </c>
+      <c r="G69" s="10">
+        <v>-1</v>
+      </c>
+      <c r="H69" s="1">
+        <v>0</v>
+      </c>
+      <c r="I69" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J69" s="10">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>100</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" ht="16.5" spans="1:12">
+      <c r="A70" s="1">
+        <f t="shared" si="8"/>
+        <v>20090012</v>
+      </c>
+      <c r="B70" s="9">
+        <v>200900</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D70" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E70" s="10">
+        <v>12</v>
+      </c>
+      <c r="F70" s="10">
+        <v>0</v>
+      </c>
+      <c r="G70" s="10">
+        <v>-1</v>
+      </c>
+      <c r="H70" s="1">
+        <v>0</v>
+      </c>
+      <c r="I70" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J70" s="10">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>100</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -32,7 +32,31 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0">
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1： Slot 电子拉霸
+2： 百人押注
+3： 激情对战</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -55,7 +79,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -67,7 +91,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -79,7 +103,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0">
+    <comment ref="L1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -109,7 +133,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="50">
   <si>
     <t>sid</t>
   </si>
@@ -117,6 +141,9 @@
     <t>游戏ID</t>
   </si>
   <si>
+    <t>游戏分类</t>
+  </si>
+  <si>
     <t>说明</t>
   </si>
   <si>
@@ -154,6 +181,9 @@
   </si>
   <si>
     <t>gameID</t>
+  </si>
+  <si>
+    <t>gameType</t>
   </si>
   <si>
     <t>nameid</t>
@@ -1338,24 +1368,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M70"/>
+  <dimension ref="A1:N70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="2" width="9.375" style="1"/>
-    <col min="3" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="11.625" style="1"/>
-    <col min="5" max="5" width="12" style="1" customWidth="1"/>
-    <col min="6" max="7" width="9" style="1"/>
-    <col min="8" max="8" width="11.25" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9.25833333333333" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.7" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.9666666666667" style="1" customWidth="1"/>
-    <col min="12" max="12" width="13.675" customWidth="1"/>
-    <col min="13" max="13" width="8.96666666666667" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="1"/>
+    <col min="1" max="3" width="9.375" style="1"/>
+    <col min="4" max="4" width="9" style="1"/>
+    <col min="5" max="5" width="11.625" style="1"/>
+    <col min="6" max="6" width="12" style="1" customWidth="1"/>
+    <col min="7" max="8" width="9" style="1"/>
+    <col min="9" max="9" width="11.25" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.25833333333333" style="1" customWidth="1"/>
+    <col min="11" max="11" width="9.7" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13.9666666666667" style="1" customWidth="1"/>
+    <col min="13" max="13" width="13.675" customWidth="1"/>
+    <col min="14" max="14" width="8.96666666666667" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:12">
+    <row r="1" ht="16.5" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1369,13 +1399,13 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>5</v>
@@ -1383,162 +1413,177 @@
       <c r="I1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:12">
+      <c r="M1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="1:13">
       <c r="A2" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="7" t="s">
-        <v>10</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="5"/>
+      <c r="E2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="5"/>
       <c r="G2" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="J2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="7" t="s">
         <v>11</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:12">
+      <c r="L2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" spans="1:13">
       <c r="A3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="C3" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="E3" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="G3" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="J3" s="7" t="s">
+        <v>21</v>
+      </c>
       <c r="K3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" s="7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" ht="16.5" spans="1:12">
+      <c r="L3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" ht="16.5" spans="1:13">
       <c r="A5" s="1">
-        <f>B5*10+F5</f>
+        <f>B5*10+G5</f>
         <v>1001001</v>
       </c>
       <c r="B5" s="8">
         <v>100100</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="9">
+      <c r="C5" s="8">
+        <v>1</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="9">
         <v>100100026</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="1">
+      <c r="F5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="1">
         <v>1</v>
       </c>
-      <c r="G5" s="1">
-        <v>0</v>
-      </c>
       <c r="H5" s="1">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="1">
-        <v>0</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K5" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5">
+        <v>-1</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5">
         <v>1000</v>
       </c>
     </row>
-    <row r="6" ht="16.5" spans="1:12">
+    <row r="6" ht="16.5" spans="1:13">
       <c r="A6" s="1">
-        <f t="shared" ref="A6:A54" si="0">B6*10+F6</f>
+        <f t="shared" ref="A6:A54" si="0">B6*10+G6</f>
         <v>1001002</v>
       </c>
       <c r="B6" s="8">
         <v>100100</v>
       </c>
-      <c r="C6" s="8" t="str">
-        <f t="shared" ref="C6:C10" si="1">C5</f>
+      <c r="C6" s="8">
+        <v>1</v>
+      </c>
+      <c r="D6" s="8" t="str">
+        <f t="shared" ref="D6:D10" si="1">D5</f>
         <v>金礦大亨</v>
       </c>
-      <c r="D6" s="9">
+      <c r="E6" s="9">
         <v>100100026</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="1">
+        <v>2</v>
+      </c>
+      <c r="H6" s="1">
+        <v>50</v>
+      </c>
+      <c r="I6" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="1">
-        <v>2</v>
-      </c>
-      <c r="G6" s="1">
-        <v>50</v>
-      </c>
-      <c r="H6" s="1">
-        <v>-1</v>
-      </c>
-      <c r="I6" s="1">
-        <v>0</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K6" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L6">
+      <c r="L6" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M6">
         <v>100000</v>
       </c>
     </row>
-    <row r="7" ht="16.5" spans="1:12">
+    <row r="7" ht="16.5" spans="1:13">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>1001003</v>
@@ -1546,39 +1591,42 @@
       <c r="B7" s="8">
         <v>100100</v>
       </c>
-      <c r="C7" s="8" t="str">
+      <c r="C7" s="8">
+        <v>1</v>
+      </c>
+      <c r="D7" s="8" t="str">
         <f t="shared" si="1"/>
         <v>金礦大亨</v>
       </c>
-      <c r="D7" s="9">
+      <c r="E7" s="9">
         <v>100100026</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="1">
+        <v>3</v>
+      </c>
+      <c r="H7" s="1">
+        <v>100</v>
+      </c>
+      <c r="I7" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="1">
-        <v>3</v>
-      </c>
-      <c r="G7" s="1">
-        <v>100</v>
-      </c>
-      <c r="H7" s="1">
-        <v>-1</v>
-      </c>
-      <c r="I7" s="1">
-        <v>0</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K7" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L7">
+      <c r="M7">
         <v>10000000</v>
       </c>
     </row>
-    <row r="8" ht="16.5" spans="1:12">
+    <row r="8" ht="16.5" spans="1:13">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>2001001</v>
@@ -1586,38 +1634,41 @@
       <c r="B8" s="8">
         <v>200100</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="9">
+      <c r="C8" s="8">
+        <v>2</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="9">
         <v>200100038</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="1">
+      <c r="F8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="1">
         <v>1</v>
       </c>
-      <c r="G8" s="1">
+      <c r="H8" s="1">
         <v>100</v>
       </c>
-      <c r="H8" s="1">
+      <c r="I8" s="1">
         <v>5000000</v>
       </c>
-      <c r="I8" s="1">
-        <v>0</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K8" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L8">
+      <c r="J8" s="1">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M8">
         <v>1000</v>
       </c>
     </row>
-    <row r="9" ht="16.5" spans="1:12">
+    <row r="9" ht="16.5" spans="1:13">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>2001002</v>
@@ -1625,39 +1676,42 @@
       <c r="B9" s="8">
         <v>200100</v>
       </c>
-      <c r="C9" s="8" t="str">
+      <c r="C9" s="8">
+        <v>2</v>
+      </c>
+      <c r="D9" s="8" t="str">
         <f t="shared" si="1"/>
         <v>紅黑大戰</v>
       </c>
-      <c r="D9" s="9">
+      <c r="E9" s="9">
         <v>200100038</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="1">
+        <v>2</v>
+      </c>
+      <c r="H9" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I9" s="1">
+        <v>500000000</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="1">
-        <v>2</v>
-      </c>
-      <c r="G9" s="1">
-        <v>10000</v>
-      </c>
-      <c r="H9" s="1">
-        <v>500000000</v>
-      </c>
-      <c r="I9" s="1">
-        <v>0</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K9" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L9">
+      <c r="L9" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M9">
         <v>100000</v>
       </c>
     </row>
-    <row r="10" ht="16.5" spans="1:12">
+    <row r="10" ht="16.5" spans="1:13">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>2001003</v>
@@ -1665,39 +1719,42 @@
       <c r="B10" s="8">
         <v>200100</v>
       </c>
-      <c r="C10" s="8" t="str">
+      <c r="C10" s="8">
+        <v>2</v>
+      </c>
+      <c r="D10" s="8" t="str">
         <f t="shared" si="1"/>
         <v>紅黑大戰</v>
       </c>
-      <c r="D10" s="9">
+      <c r="E10" s="9">
         <v>200100038</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" s="1">
+        <v>3</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="I10" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L10" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="1">
-        <v>3</v>
-      </c>
-      <c r="G10" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="H10" s="1">
-        <v>-1</v>
-      </c>
-      <c r="I10" s="1">
-        <v>0</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K10" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L10">
+      <c r="M10">
         <v>10000000</v>
       </c>
     </row>
-    <row r="11" ht="16.5" spans="1:12">
+    <row r="11" ht="16.5" spans="1:13">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>2001011</v>
@@ -1705,38 +1762,41 @@
       <c r="B11" s="8">
         <v>200101</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="9">
+      <c r="C11" s="8">
+        <v>2</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="9">
         <v>200101001</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="1">
+      <c r="F11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="1">
         <v>1</v>
       </c>
-      <c r="G11" s="1">
+      <c r="H11" s="1">
         <v>100</v>
       </c>
-      <c r="H11" s="1">
+      <c r="I11" s="1">
         <v>5000000</v>
       </c>
-      <c r="I11" s="1">
-        <v>0</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K11" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L11">
+      <c r="J11" s="1">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L11" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M11">
         <v>1000</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="16.5" spans="1:13">
+    <row r="12" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>2001012</v>
@@ -1744,40 +1804,43 @@
       <c r="B12" s="8">
         <v>200101</v>
       </c>
-      <c r="C12" s="8" t="str">
-        <f t="shared" ref="C12:C16" si="2">C11</f>
+      <c r="C12" s="8">
+        <v>2</v>
+      </c>
+      <c r="D12" s="8" t="str">
+        <f t="shared" ref="D12:D16" si="2">D11</f>
         <v>龍虎鬥</v>
       </c>
-      <c r="D12" s="9">
+      <c r="E12" s="9">
         <v>200101001</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="F12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="1">
+        <v>2</v>
+      </c>
+      <c r="H12" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I12" s="1">
+        <v>500000000</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F12" s="1">
-        <v>2</v>
-      </c>
-      <c r="G12" s="1">
-        <v>10000</v>
-      </c>
-      <c r="H12" s="1">
-        <v>500000000</v>
-      </c>
-      <c r="I12" s="1">
-        <v>0</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K12" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L12">
+      <c r="L12" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M12">
         <v>100000</v>
       </c>
-      <c r="M12"/>
-    </row>
-    <row r="13" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="N12"/>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>2001013</v>
@@ -1785,40 +1848,43 @@
       <c r="B13" s="8">
         <v>200101</v>
       </c>
-      <c r="C13" s="8" t="str">
+      <c r="C13" s="8">
+        <v>2</v>
+      </c>
+      <c r="D13" s="8" t="str">
         <f t="shared" si="2"/>
         <v>龍虎鬥</v>
       </c>
-      <c r="D13" s="9">
+      <c r="E13" s="9">
         <v>200101001</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" s="1">
+        <v>3</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="I13" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J13" s="1">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L13" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="F13" s="1">
-        <v>3</v>
-      </c>
-      <c r="G13" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="H13" s="1">
-        <v>-1</v>
-      </c>
-      <c r="I13" s="1">
-        <v>0</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K13" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L13">
+      <c r="M13">
         <v>10000000</v>
       </c>
-      <c r="M13"/>
-    </row>
-    <row r="14" ht="16.5" spans="1:12">
+      <c r="N13"/>
+    </row>
+    <row r="14" ht="16.5" spans="1:13">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>2003001</v>
@@ -1826,38 +1892,41 @@
       <c r="B14" s="8">
         <v>200300</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" s="9">
+      <c r="C14" s="8">
+        <v>2</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" s="9">
         <v>200300001</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" s="1">
+      <c r="F14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="1">
         <v>1</v>
       </c>
-      <c r="G14" s="1">
+      <c r="H14" s="1">
         <v>100</v>
       </c>
-      <c r="H14" s="1">
+      <c r="I14" s="1">
         <v>5000000</v>
       </c>
-      <c r="I14" s="1">
-        <v>0</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L14">
+      <c r="J14" s="1">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L14" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M14">
         <v>1000</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="16.5" spans="1:13">
+    <row r="15" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>2003002</v>
@@ -1865,40 +1934,43 @@
       <c r="B15" s="8">
         <v>200300</v>
       </c>
-      <c r="C15" s="8" t="str">
+      <c r="C15" s="8">
+        <v>2</v>
+      </c>
+      <c r="D15" s="8" t="str">
         <f t="shared" si="2"/>
         <v>飛禽走獸</v>
       </c>
-      <c r="D15" s="9">
+      <c r="E15" s="9">
         <v>200300001</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="F15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G15" s="1">
+        <v>2</v>
+      </c>
+      <c r="H15" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I15" s="1">
+        <v>500000000</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F15" s="1">
-        <v>2</v>
-      </c>
-      <c r="G15" s="1">
-        <v>10000</v>
-      </c>
-      <c r="H15" s="1">
-        <v>500000000</v>
-      </c>
-      <c r="I15" s="1">
-        <v>0</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K15" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L15">
+      <c r="L15" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M15">
         <v>100000</v>
       </c>
-      <c r="M15"/>
-    </row>
-    <row r="16" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="N15"/>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>2003003</v>
@@ -1906,40 +1978,43 @@
       <c r="B16" s="8">
         <v>200300</v>
       </c>
-      <c r="C16" s="8" t="str">
+      <c r="C16" s="8">
+        <v>2</v>
+      </c>
+      <c r="D16" s="8" t="str">
         <f t="shared" si="2"/>
         <v>飛禽走獸</v>
       </c>
-      <c r="D16" s="9">
+      <c r="E16" s="9">
         <v>200300001</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="F16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" s="1">
+        <v>3</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="I16" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J16" s="1">
+        <v>0</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L16" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="1">
-        <v>3</v>
-      </c>
-      <c r="G16" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="H16" s="1">
-        <v>-1</v>
-      </c>
-      <c r="I16" s="1">
-        <v>0</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K16" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L16">
+      <c r="M16">
         <v>10000000</v>
       </c>
-      <c r="M16"/>
-    </row>
-    <row r="17" ht="16.5" spans="1:12">
+      <c r="N16"/>
+    </row>
+    <row r="17" ht="16.5" spans="1:13">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>2004001</v>
@@ -1947,38 +2022,41 @@
       <c r="B17" s="8">
         <v>200400</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" s="9">
+      <c r="C17" s="8">
+        <v>2</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" s="9">
         <v>200400009</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F17" s="1">
+      <c r="F17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="1">
         <v>1</v>
       </c>
-      <c r="G17" s="1">
+      <c r="H17" s="1">
         <v>100</v>
       </c>
-      <c r="H17" s="1">
+      <c r="I17" s="1">
         <v>5000000</v>
       </c>
-      <c r="I17" s="1">
-        <v>0</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K17" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L17">
+      <c r="J17" s="1">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L17" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M17">
         <v>1000</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="16.5" spans="1:13">
+    <row r="18" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>2004002</v>
@@ -1986,39 +2064,42 @@
       <c r="B18" s="8">
         <v>200400</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" s="9">
+      <c r="C18" s="8">
+        <v>2</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="9">
         <v>200400009</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="F18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G18" s="1">
+        <v>2</v>
+      </c>
+      <c r="H18" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I18" s="1">
+        <v>500000000</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F18" s="1">
-        <v>2</v>
-      </c>
-      <c r="G18" s="1">
-        <v>10000</v>
-      </c>
-      <c r="H18" s="1">
-        <v>500000000</v>
-      </c>
-      <c r="I18" s="1">
-        <v>0</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K18" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L18">
+      <c r="L18" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M18">
         <v>100000</v>
       </c>
-      <c r="M18"/>
-    </row>
-    <row r="19" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="N18"/>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>2004003</v>
@@ -2026,39 +2107,42 @@
       <c r="B19" s="8">
         <v>200400</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" s="9">
+      <c r="C19" s="8">
+        <v>2</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="9">
         <v>200400009</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="F19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G19" s="1">
+        <v>3</v>
+      </c>
+      <c r="H19" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="I19" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J19" s="1">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L19" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="F19" s="1">
-        <v>3</v>
-      </c>
-      <c r="G19" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="H19" s="1">
-        <v>-1</v>
-      </c>
-      <c r="I19" s="1">
-        <v>0</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K19" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L19">
+      <c r="M19">
         <v>10000000</v>
       </c>
-      <c r="M19"/>
-    </row>
-    <row r="20" ht="16.5" spans="1:12">
+      <c r="N19"/>
+    </row>
+    <row r="20" ht="16.5" spans="1:13">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>2005001</v>
@@ -2066,38 +2150,41 @@
       <c r="B20" s="8">
         <v>200500</v>
       </c>
-      <c r="C20" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D20" s="9">
+      <c r="C20" s="8">
+        <v>2</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="9">
         <v>200500025</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F20" s="1">
+      <c r="F20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="1">
         <v>1</v>
       </c>
-      <c r="G20" s="1">
+      <c r="H20" s="1">
         <v>100</v>
       </c>
-      <c r="H20" s="1">
+      <c r="I20" s="1">
         <v>5000000</v>
       </c>
-      <c r="I20" s="1">
-        <v>0</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K20" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="L20">
+      <c r="J20" s="1">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L20" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="M20">
         <v>1000</v>
       </c>
     </row>
-    <row r="21" ht="16.5" spans="1:12">
+    <row r="21" ht="16.5" spans="1:13">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>2005002</v>
@@ -2105,38 +2192,41 @@
       <c r="B21" s="8">
         <v>200500</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D21" s="9">
+      <c r="C21" s="8">
+        <v>2</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="9">
         <v>200500025</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="F21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G21" s="1">
+        <v>2</v>
+      </c>
+      <c r="H21" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I21" s="1">
+        <v>500000000</v>
+      </c>
+      <c r="J21" s="1">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F21" s="1">
-        <v>2</v>
-      </c>
-      <c r="G21" s="1">
-        <v>10000</v>
-      </c>
-      <c r="H21" s="1">
-        <v>500000000</v>
-      </c>
-      <c r="I21" s="1">
-        <v>0</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K21" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="L21">
+      <c r="L21" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="M21">
         <v>100000</v>
       </c>
     </row>
-    <row r="22" ht="16.5" spans="1:12">
+    <row r="22" ht="16.5" spans="1:13">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>2005003</v>
@@ -2144,38 +2234,41 @@
       <c r="B22" s="8">
         <v>200500</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D22" s="9">
+      <c r="C22" s="8">
+        <v>2</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" s="9">
         <v>200500025</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F22" s="1">
+      <c r="F22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G22" s="1">
         <v>3</v>
       </c>
-      <c r="G22" s="1">
+      <c r="H22" s="1">
         <v>1000000</v>
       </c>
-      <c r="H22" s="1">
-        <v>-1</v>
-      </c>
       <c r="I22" s="1">
-        <v>0</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K22" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="L22">
+        <v>-1</v>
+      </c>
+      <c r="J22" s="1">
+        <v>0</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L22" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="M22">
         <v>10000000</v>
       </c>
     </row>
-    <row r="23" ht="16.5" spans="1:12">
+    <row r="23" ht="16.5" spans="1:13">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>2006001</v>
@@ -2183,38 +2276,41 @@
       <c r="B23" s="8">
         <v>200600</v>
       </c>
-      <c r="C23" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D23" s="9">
+      <c r="C23" s="8">
+        <v>2</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E23" s="9">
         <v>200600001</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F23" s="1">
+      <c r="F23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="1">
         <v>1</v>
       </c>
-      <c r="G23" s="1">
+      <c r="H23" s="1">
         <v>100</v>
       </c>
-      <c r="H23" s="1">
+      <c r="I23" s="1">
         <v>5000000</v>
       </c>
-      <c r="I23" s="1">
-        <v>0</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K23" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L23">
+      <c r="J23" s="1">
+        <v>0</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L23" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M23">
         <v>1000</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="16.5" spans="1:13">
+    <row r="24" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>2006002</v>
@@ -2222,39 +2318,42 @@
       <c r="B24" s="8">
         <v>200600</v>
       </c>
-      <c r="C24" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D24" s="9">
+      <c r="C24" s="8">
+        <v>2</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" s="9">
         <v>200600001</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="F24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G24" s="1">
+        <v>2</v>
+      </c>
+      <c r="H24" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I24" s="1">
+        <v>500000000</v>
+      </c>
+      <c r="J24" s="1">
+        <v>0</v>
+      </c>
+      <c r="K24" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="1">
-        <v>2</v>
-      </c>
-      <c r="G24" s="1">
-        <v>10000</v>
-      </c>
-      <c r="H24" s="1">
-        <v>500000000</v>
-      </c>
-      <c r="I24" s="1">
-        <v>0</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K24" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L24">
+      <c r="L24" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M24">
         <v>100000</v>
       </c>
-      <c r="M24"/>
-    </row>
-    <row r="25" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="N24"/>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>2006003</v>
@@ -2262,39 +2361,42 @@
       <c r="B25" s="8">
         <v>200600</v>
       </c>
-      <c r="C25" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D25" s="9">
+      <c r="C25" s="8">
+        <v>2</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E25" s="9">
         <v>200600001</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="F25" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G25" s="1">
+        <v>3</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="I25" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J25" s="1">
+        <v>0</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L25" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="F25" s="1">
-        <v>3</v>
-      </c>
-      <c r="G25" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="H25" s="1">
-        <v>-1</v>
-      </c>
-      <c r="I25" s="1">
-        <v>0</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K25" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L25">
+      <c r="M25">
         <v>10000000</v>
       </c>
-      <c r="M25"/>
-    </row>
-    <row r="26" ht="16.5" spans="1:12">
+      <c r="N25"/>
+    </row>
+    <row r="26" ht="16.5" spans="1:13">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>2007001</v>
@@ -2302,38 +2404,41 @@
       <c r="B26" s="8">
         <v>200700</v>
       </c>
-      <c r="C26" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D26" s="9">
+      <c r="C26" s="8">
+        <v>2</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E26" s="9">
         <v>200700001</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F26" s="1">
+      <c r="F26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="1">
         <v>1</v>
       </c>
-      <c r="G26" s="1">
+      <c r="H26" s="1">
         <v>100</v>
       </c>
-      <c r="H26" s="1">
+      <c r="I26" s="1">
         <v>5000000</v>
       </c>
-      <c r="I26" s="1">
-        <v>0</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K26" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L26">
+      <c r="J26" s="1">
+        <v>0</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L26" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M26">
         <v>1000</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" ht="16.5" spans="1:13">
+    <row r="27" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>2007002</v>
@@ -2341,40 +2446,43 @@
       <c r="B27" s="8">
         <v>200700</v>
       </c>
-      <c r="C27" s="8" t="str">
-        <f t="shared" ref="C24:C28" si="3">C26</f>
+      <c r="C27" s="8">
+        <v>2</v>
+      </c>
+      <c r="D27" s="8" t="str">
+        <f t="shared" ref="D24:D28" si="3">D26</f>
         <v>色碟</v>
       </c>
-      <c r="D27" s="9">
+      <c r="E27" s="9">
         <v>200700001</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="F27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G27" s="1">
+        <v>2</v>
+      </c>
+      <c r="H27" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I27" s="1">
+        <v>500000000</v>
+      </c>
+      <c r="J27" s="1">
+        <v>0</v>
+      </c>
+      <c r="K27" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F27" s="1">
-        <v>2</v>
-      </c>
-      <c r="G27" s="1">
-        <v>10000</v>
-      </c>
-      <c r="H27" s="1">
-        <v>500000000</v>
-      </c>
-      <c r="I27" s="1">
-        <v>0</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K27" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L27">
+      <c r="L27" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M27">
         <v>100000</v>
       </c>
-      <c r="M27"/>
-    </row>
-    <row r="28" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="N27"/>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
         <v>2007003</v>
@@ -2382,40 +2490,43 @@
       <c r="B28" s="8">
         <v>200700</v>
       </c>
-      <c r="C28" s="8" t="str">
+      <c r="C28" s="8">
+        <v>2</v>
+      </c>
+      <c r="D28" s="8" t="str">
         <f t="shared" si="3"/>
         <v>色碟</v>
       </c>
-      <c r="D28" s="9">
+      <c r="E28" s="9">
         <v>200700001</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="F28" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G28" s="1">
+        <v>3</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="I28" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J28" s="1">
+        <v>0</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L28" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="F28" s="1">
-        <v>3</v>
-      </c>
-      <c r="G28" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="H28" s="1">
-        <v>-1</v>
-      </c>
-      <c r="I28" s="1">
-        <v>0</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K28" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L28">
+      <c r="M28">
         <v>10000000</v>
       </c>
-      <c r="M28"/>
-    </row>
-    <row r="29" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="N28"/>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
         <v>2008001</v>
@@ -2423,39 +2534,42 @@
       <c r="B29" s="8">
         <v>200800</v>
       </c>
-      <c r="C29" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D29" s="9">
+      <c r="C29" s="8">
+        <v>2</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E29" s="9">
         <v>200800001</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F29" s="1">
+      <c r="F29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="1">
         <v>1</v>
       </c>
-      <c r="G29" s="1">
+      <c r="H29" s="1">
         <v>100</v>
       </c>
-      <c r="H29" s="1">
+      <c r="I29" s="1">
         <v>5000000</v>
       </c>
-      <c r="I29" s="1">
-        <v>0</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K29" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L29">
+      <c r="J29" s="1">
+        <v>0</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L29" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M29">
         <v>1000</v>
       </c>
-      <c r="M29"/>
-    </row>
-    <row r="30" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="N29"/>
+    </row>
+    <row r="30" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
         <v>2008002</v>
@@ -2463,39 +2577,42 @@
       <c r="B30" s="8">
         <v>200800</v>
       </c>
-      <c r="C30" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D30" s="9">
+      <c r="C30" s="8">
+        <v>2</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E30" s="9">
         <v>200800001</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="F30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G30" s="1">
+        <v>2</v>
+      </c>
+      <c r="H30" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I30" s="1">
+        <v>500000000</v>
+      </c>
+      <c r="J30" s="1">
+        <v>0</v>
+      </c>
+      <c r="K30" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F30" s="1">
-        <v>2</v>
-      </c>
-      <c r="G30" s="1">
-        <v>10000</v>
-      </c>
-      <c r="H30" s="1">
-        <v>500000000</v>
-      </c>
-      <c r="I30" s="1">
-        <v>0</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K30" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L30">
+      <c r="L30" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M30">
         <v>100000</v>
       </c>
-      <c r="M30"/>
-    </row>
-    <row r="31" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="N30"/>
+    </row>
+    <row r="31" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
         <v>2008003</v>
@@ -2503,39 +2620,42 @@
       <c r="B31" s="8">
         <v>200800</v>
       </c>
-      <c r="C31" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D31" s="9">
+      <c r="C31" s="8">
+        <v>2</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E31" s="9">
         <v>200800001</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="F31" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G31" s="1">
+        <v>3</v>
+      </c>
+      <c r="H31" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="I31" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J31" s="1">
+        <v>0</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L31" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="F31" s="1">
-        <v>3</v>
-      </c>
-      <c r="G31" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="H31" s="1">
-        <v>-1</v>
-      </c>
-      <c r="I31" s="1">
-        <v>0</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L31">
+      <c r="M31">
         <v>10000000</v>
       </c>
-      <c r="M31"/>
-    </row>
-    <row r="32" ht="16.5" spans="1:12">
+      <c r="N31"/>
+    </row>
+    <row r="32" ht="16.5" spans="1:13">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
         <v>2009001</v>
@@ -2543,38 +2663,41 @@
       <c r="B32" s="10">
         <v>200900</v>
       </c>
-      <c r="C32" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D32" s="9">
+      <c r="C32" s="8">
+        <v>2</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E32" s="9">
         <v>200900001</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F32" s="1">
+      <c r="F32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" s="1">
         <v>1</v>
       </c>
-      <c r="G32" s="1">
+      <c r="H32" s="1">
         <v>100</v>
       </c>
-      <c r="H32" s="1">
+      <c r="I32" s="1">
         <v>5000000</v>
       </c>
-      <c r="I32" s="1">
-        <v>0</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K32" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L32">
+      <c r="J32" s="1">
+        <v>0</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L32" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M32">
         <v>1000</v>
       </c>
     </row>
-    <row r="33" ht="16.5" spans="1:12">
+    <row r="33" ht="16.5" spans="1:13">
       <c r="A33" s="1">
         <f t="shared" si="0"/>
         <v>2009002</v>
@@ -2582,39 +2705,42 @@
       <c r="B33" s="8">
         <v>200900</v>
       </c>
-      <c r="C33" s="8" t="str">
-        <f>C32</f>
+      <c r="C33" s="8">
+        <v>2</v>
+      </c>
+      <c r="D33" s="8" t="str">
+        <f>D32</f>
         <v>魚蝦蟹</v>
       </c>
-      <c r="D33" s="9">
+      <c r="E33" s="9">
         <v>200900001</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="F33" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G33" s="1">
+        <v>2</v>
+      </c>
+      <c r="H33" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I33" s="1">
+        <v>500000000</v>
+      </c>
+      <c r="J33" s="1">
+        <v>0</v>
+      </c>
+      <c r="K33" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F33" s="1">
-        <v>2</v>
-      </c>
-      <c r="G33" s="1">
-        <v>10000</v>
-      </c>
-      <c r="H33" s="1">
-        <v>500000000</v>
-      </c>
-      <c r="I33" s="1">
-        <v>0</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K33" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L33">
+      <c r="L33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M33">
         <v>100000</v>
       </c>
     </row>
-    <row r="34" ht="16.5" spans="1:12">
+    <row r="34" ht="16.5" spans="1:13">
       <c r="A34" s="1">
         <f t="shared" si="0"/>
         <v>2009003</v>
@@ -2622,39 +2748,42 @@
       <c r="B34" s="8">
         <v>200900</v>
       </c>
-      <c r="C34" s="8" t="str">
-        <f>C33</f>
+      <c r="C34" s="8">
+        <v>2</v>
+      </c>
+      <c r="D34" s="8" t="str">
+        <f>D33</f>
         <v>魚蝦蟹</v>
       </c>
-      <c r="D34" s="9">
+      <c r="E34" s="9">
         <v>200900001</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="F34" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G34" s="1">
+        <v>3</v>
+      </c>
+      <c r="H34" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="I34" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J34" s="1">
+        <v>0</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L34" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="F34" s="1">
-        <v>3</v>
-      </c>
-      <c r="G34" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="H34" s="1">
-        <v>-1</v>
-      </c>
-      <c r="I34" s="1">
-        <v>0</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K34" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L34">
+      <c r="M34">
         <v>10000000</v>
       </c>
     </row>
-    <row r="35" ht="16.5" spans="1:12">
+    <row r="35" ht="16.5" spans="1:13">
       <c r="A35" s="1">
         <f t="shared" si="0"/>
         <v>2010001</v>
@@ -2662,38 +2791,41 @@
       <c r="B35" s="8">
         <v>201000</v>
       </c>
-      <c r="C35" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D35" s="9">
+      <c r="C35" s="8">
+        <v>2</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E35" s="9">
         <v>101000006</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F35" s="1">
+      <c r="F35" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="1">
         <v>1</v>
       </c>
-      <c r="G35" s="1">
+      <c r="H35" s="1">
         <v>100</v>
       </c>
-      <c r="H35" s="1">
+      <c r="I35" s="1">
         <v>5000000</v>
       </c>
-      <c r="I35" s="1">
-        <v>0</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K35" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L35">
+      <c r="J35" s="1">
+        <v>0</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L35" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M35">
         <v>1000</v>
       </c>
     </row>
-    <row r="36" ht="16.5" spans="1:12">
+    <row r="36" ht="16.5" spans="1:13">
       <c r="A36" s="1">
         <f t="shared" si="0"/>
         <v>2010002</v>
@@ -2701,38 +2833,41 @@
       <c r="B36" s="8">
         <v>201000</v>
       </c>
-      <c r="C36" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D36" s="9">
+      <c r="C36" s="8">
+        <v>2</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E36" s="9">
         <v>101000006</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="F36" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G36" s="1">
+        <v>2</v>
+      </c>
+      <c r="H36" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I36" s="1">
+        <v>500000000</v>
+      </c>
+      <c r="J36" s="1">
+        <v>0</v>
+      </c>
+      <c r="K36" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F36" s="1">
-        <v>2</v>
-      </c>
-      <c r="G36" s="1">
-        <v>10000</v>
-      </c>
-      <c r="H36" s="1">
-        <v>500000000</v>
-      </c>
-      <c r="I36" s="1">
-        <v>0</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K36" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L36">
+      <c r="L36" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M36">
         <v>100000</v>
       </c>
     </row>
-    <row r="37" ht="16.5" spans="1:12">
+    <row r="37" ht="16.5" spans="1:13">
       <c r="A37" s="1">
         <f t="shared" si="0"/>
         <v>2010003</v>
@@ -2740,38 +2875,41 @@
       <c r="B37" s="8">
         <v>201000</v>
       </c>
-      <c r="C37" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D37" s="9">
+      <c r="C37" s="8">
+        <v>2</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E37" s="9">
         <v>101000006</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="F37" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G37" s="1">
+        <v>3</v>
+      </c>
+      <c r="H37" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="I37" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J37" s="1">
+        <v>0</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L37" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="F37" s="1">
-        <v>3</v>
-      </c>
-      <c r="G37" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="H37" s="1">
-        <v>-1</v>
-      </c>
-      <c r="I37" s="1">
-        <v>0</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K37" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L37">
+      <c r="M37">
         <v>10000000</v>
       </c>
     </row>
-    <row r="38" ht="16.5" spans="1:12">
+    <row r="38" ht="16.5" spans="1:13">
       <c r="A38" s="1">
         <f t="shared" si="0"/>
         <v>3001001</v>
@@ -2779,38 +2917,41 @@
       <c r="B38" s="8">
         <v>300100</v>
       </c>
-      <c r="C38" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D38" s="9">
+      <c r="C38" s="8">
+        <v>3</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E38" s="9">
         <v>300100001</v>
       </c>
-      <c r="E38" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F38" s="1">
+      <c r="F38" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G38" s="1">
         <v>1</v>
       </c>
-      <c r="G38" s="1">
+      <c r="H38" s="1">
         <v>100</v>
       </c>
-      <c r="H38" s="1">
-        <v>-1</v>
-      </c>
       <c r="I38" s="1">
-        <v>0</v>
-      </c>
-      <c r="J38" s="14" t="s">
-        <v>41</v>
+        <v>-1</v>
+      </c>
+      <c r="J38" s="1">
+        <v>0</v>
       </c>
       <c r="K38" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="L38">
+        <v>43</v>
+      </c>
+      <c r="L38" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="M38">
         <v>500</v>
       </c>
     </row>
-    <row r="39" s="1" customFormat="1" ht="16.5" spans="1:13">
+    <row r="39" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A39" s="1">
         <f t="shared" si="0"/>
         <v>3001002</v>
@@ -2818,39 +2959,42 @@
       <c r="B39" s="8">
         <v>300100</v>
       </c>
-      <c r="C39" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D39" s="9">
+      <c r="C39" s="8">
+        <v>3</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E39" s="9">
         <v>300100001</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F39" s="1">
-        <v>2</v>
+      <c r="F39" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="G39" s="1">
+        <v>2</v>
+      </c>
+      <c r="H39" s="1">
         <v>10000</v>
       </c>
-      <c r="H39" s="1">
-        <v>-1</v>
-      </c>
       <c r="I39" s="1">
-        <v>0</v>
-      </c>
-      <c r="J39" s="14" t="s">
-        <v>41</v>
+        <v>-1</v>
+      </c>
+      <c r="J39" s="1">
+        <v>0</v>
       </c>
       <c r="K39" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="L39">
+        <v>43</v>
+      </c>
+      <c r="L39" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="M39">
         <v>20000</v>
       </c>
-      <c r="M39"/>
-    </row>
-    <row r="40" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="N39"/>
+    </row>
+    <row r="40" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A40" s="1">
         <f t="shared" si="0"/>
         <v>3001003</v>
@@ -2858,39 +3002,42 @@
       <c r="B40" s="8">
         <v>300100</v>
       </c>
-      <c r="C40" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D40" s="9">
+      <c r="C40" s="8">
+        <v>3</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E40" s="9">
         <v>300100001</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F40" s="1">
+      <c r="F40" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G40" s="1">
         <v>3</v>
       </c>
-      <c r="G40" s="1">
+      <c r="H40" s="1">
         <v>1000000</v>
       </c>
-      <c r="H40" s="1">
-        <v>-1</v>
-      </c>
       <c r="I40" s="1">
-        <v>0</v>
-      </c>
-      <c r="J40" s="14" t="s">
-        <v>41</v>
+        <v>-1</v>
+      </c>
+      <c r="J40" s="1">
+        <v>0</v>
       </c>
       <c r="K40" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="L40">
+        <v>43</v>
+      </c>
+      <c r="L40" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="M40">
         <v>2000000</v>
       </c>
-      <c r="M40"/>
-    </row>
-    <row r="41" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="N40"/>
+    </row>
+    <row r="41" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A41" s="1">
         <f t="shared" si="0"/>
         <v>3002001</v>
@@ -2898,39 +3045,42 @@
       <c r="B41" s="8">
         <v>300200</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="C41" s="8">
+        <v>3</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E41" s="9">
+        <v>300200006</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" s="1">
+        <v>1</v>
+      </c>
+      <c r="H41" s="1">
+        <v>100</v>
+      </c>
+      <c r="I41" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J41" s="1">
+        <v>0</v>
+      </c>
+      <c r="K41" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="D41" s="9">
-        <v>300200006</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F41" s="1">
-        <v>1</v>
-      </c>
-      <c r="G41" s="1">
-        <v>100</v>
-      </c>
-      <c r="H41" s="1">
-        <v>-1</v>
-      </c>
-      <c r="I41" s="1">
-        <v>0</v>
-      </c>
-      <c r="J41" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="K41" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="L41">
+      <c r="L41" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="M41">
         <v>500</v>
       </c>
-      <c r="M41"/>
-    </row>
-    <row r="42" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="N41"/>
+    </row>
+    <row r="42" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A42" s="1">
         <f t="shared" si="0"/>
         <v>3002002</v>
@@ -2938,39 +3088,42 @@
       <c r="B42" s="8">
         <v>300200</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C42" s="8">
+        <v>3</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E42" s="9">
+        <v>300200006</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G42" s="1">
+        <v>2</v>
+      </c>
+      <c r="H42" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I42" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J42" s="1">
+        <v>0</v>
+      </c>
+      <c r="K42" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="D42" s="9">
-        <v>300200006</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F42" s="1">
-        <v>2</v>
-      </c>
-      <c r="G42" s="1">
-        <v>10000</v>
-      </c>
-      <c r="H42" s="1">
-        <v>-1</v>
-      </c>
-      <c r="I42" s="1">
-        <v>0</v>
-      </c>
-      <c r="J42" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="K42" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="L42">
+      <c r="L42" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="M42">
         <v>20000</v>
       </c>
-      <c r="M42"/>
-    </row>
-    <row r="43" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="N42"/>
+    </row>
+    <row r="43" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A43" s="1">
         <f t="shared" si="0"/>
         <v>3002003</v>
@@ -2978,79 +3131,85 @@
       <c r="B43" s="8">
         <v>300200</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C43" s="8">
+        <v>3</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E43" s="9">
+        <v>300200006</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G43" s="1">
+        <v>3</v>
+      </c>
+      <c r="H43" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="I43" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J43" s="1">
+        <v>0</v>
+      </c>
+      <c r="K43" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="D43" s="9">
-        <v>300200006</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F43" s="1">
-        <v>3</v>
-      </c>
-      <c r="G43" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="H43" s="1">
-        <v>-1</v>
-      </c>
-      <c r="I43" s="1">
-        <v>0</v>
-      </c>
-      <c r="J43" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="K43" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="L43">
+      <c r="L43" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="M43">
         <v>2000000</v>
       </c>
-      <c r="M43"/>
-    </row>
-    <row r="44" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="N43"/>
+    </row>
+    <row r="44" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A44" s="1">
-        <f t="shared" ref="A44:A50" si="4">B44*100+F44</f>
+        <f t="shared" ref="A44:A50" si="4">B44*100+G44</f>
         <v>20010010</v>
       </c>
       <c r="B44" s="9">
         <v>200100</v>
       </c>
-      <c r="C44" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D44" s="9">
+      <c r="C44" s="9">
+        <v>2</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E44" s="9">
         <v>200100038</v>
       </c>
-      <c r="E44" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="F44" s="11">
+      <c r="F44" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G44" s="11">
         <v>10</v>
       </c>
-      <c r="G44" s="11">
-        <v>0</v>
-      </c>
       <c r="H44" s="11">
-        <v>-1</v>
-      </c>
-      <c r="I44" s="1">
-        <v>0</v>
-      </c>
-      <c r="J44" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K44" s="11">
-        <v>0</v>
-      </c>
-      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="I44" s="11">
+        <v>-1</v>
+      </c>
+      <c r="J44" s="1">
+        <v>0</v>
+      </c>
+      <c r="K44" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="L44" s="11">
+        <v>0</v>
+      </c>
+      <c r="M44">
         <v>100</v>
       </c>
-      <c r="M44"/>
-    </row>
-    <row r="45" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="N44"/>
+    </row>
+    <row r="45" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A45" s="1">
         <f t="shared" si="4"/>
         <v>20010011</v>
@@ -3058,39 +3217,42 @@
       <c r="B45" s="9">
         <v>200100</v>
       </c>
-      <c r="C45" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D45" s="9">
+      <c r="C45" s="9">
+        <v>2</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E45" s="9">
         <v>200100038</v>
       </c>
-      <c r="E45" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="F45" s="11">
+      <c r="F45" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G45" s="11">
         <v>11</v>
       </c>
-      <c r="G45" s="11">
-        <v>0</v>
-      </c>
       <c r="H45" s="11">
-        <v>-1</v>
-      </c>
-      <c r="I45" s="1">
-        <v>0</v>
-      </c>
-      <c r="J45" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K45" s="11">
-        <v>0</v>
-      </c>
-      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="I45" s="11">
+        <v>-1</v>
+      </c>
+      <c r="J45" s="1">
+        <v>0</v>
+      </c>
+      <c r="K45" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="L45" s="11">
+        <v>0</v>
+      </c>
+      <c r="M45">
         <v>100</v>
       </c>
-      <c r="M45"/>
-    </row>
-    <row r="46" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="N45"/>
+    </row>
+    <row r="46" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A46" s="1">
         <f t="shared" si="4"/>
         <v>20010012</v>
@@ -3098,39 +3260,42 @@
       <c r="B46" s="9">
         <v>200100</v>
       </c>
-      <c r="C46" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D46" s="9">
+      <c r="C46" s="9">
+        <v>2</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E46" s="9">
         <v>200100038</v>
       </c>
-      <c r="E46" s="11" t="s">
+      <c r="F46" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G46" s="11">
+        <v>12</v>
+      </c>
+      <c r="H46" s="11">
+        <v>0</v>
+      </c>
+      <c r="I46" s="11">
+        <v>-1</v>
+      </c>
+      <c r="J46" s="1">
+        <v>0</v>
+      </c>
+      <c r="K46" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="F46" s="11">
-        <v>12</v>
-      </c>
-      <c r="G46" s="11">
-        <v>0</v>
-      </c>
-      <c r="H46" s="11">
-        <v>-1</v>
-      </c>
-      <c r="I46" s="1">
-        <v>0</v>
-      </c>
-      <c r="J46" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K46" s="11">
-        <v>0</v>
-      </c>
-      <c r="L46">
+      <c r="L46" s="11">
+        <v>0</v>
+      </c>
+      <c r="M46">
         <v>100</v>
       </c>
-      <c r="M46"/>
-    </row>
-    <row r="47" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="N46"/>
+    </row>
+    <row r="47" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A47" s="1">
         <f t="shared" si="4"/>
         <v>20010110</v>
@@ -3138,39 +3303,42 @@
       <c r="B47" s="9">
         <v>200101</v>
       </c>
-      <c r="C47" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D47" s="9">
+      <c r="C47" s="9">
+        <v>2</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E47" s="9">
         <v>200101001</v>
       </c>
-      <c r="E47" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="F47" s="11">
+      <c r="F47" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G47" s="11">
         <v>10</v>
       </c>
-      <c r="G47" s="11">
-        <v>0</v>
-      </c>
       <c r="H47" s="11">
-        <v>-1</v>
-      </c>
-      <c r="I47" s="1">
-        <v>0</v>
-      </c>
-      <c r="J47" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K47" s="11">
-        <v>0</v>
-      </c>
-      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="I47" s="11">
+        <v>-1</v>
+      </c>
+      <c r="J47" s="1">
+        <v>0</v>
+      </c>
+      <c r="K47" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="L47" s="11">
+        <v>0</v>
+      </c>
+      <c r="M47">
         <v>100</v>
       </c>
-      <c r="M47"/>
-    </row>
-    <row r="48" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="N47"/>
+    </row>
+    <row r="48" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A48" s="1">
         <f t="shared" si="4"/>
         <v>20010111</v>
@@ -3178,39 +3346,42 @@
       <c r="B48" s="9">
         <v>200101</v>
       </c>
-      <c r="C48" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D48" s="9">
+      <c r="C48" s="9">
+        <v>2</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E48" s="9">
         <v>200101001</v>
       </c>
-      <c r="E48" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="F48" s="11">
+      <c r="F48" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G48" s="11">
         <v>11</v>
       </c>
-      <c r="G48" s="11">
-        <v>0</v>
-      </c>
       <c r="H48" s="11">
-        <v>-1</v>
-      </c>
-      <c r="I48" s="1">
-        <v>0</v>
-      </c>
-      <c r="J48" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K48" s="11">
-        <v>0</v>
-      </c>
-      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="I48" s="11">
+        <v>-1</v>
+      </c>
+      <c r="J48" s="1">
+        <v>0</v>
+      </c>
+      <c r="K48" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="L48" s="11">
+        <v>0</v>
+      </c>
+      <c r="M48">
         <v>100</v>
       </c>
-      <c r="M48"/>
-    </row>
-    <row r="49" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="N48"/>
+    </row>
+    <row r="49" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A49" s="1">
         <f t="shared" si="4"/>
         <v>20010112</v>
@@ -3218,39 +3389,42 @@
       <c r="B49" s="9">
         <v>200101</v>
       </c>
-      <c r="C49" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D49" s="9">
+      <c r="C49" s="9">
+        <v>2</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E49" s="9">
         <v>200101001</v>
       </c>
-      <c r="E49" s="11" t="s">
+      <c r="F49" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G49" s="11">
+        <v>12</v>
+      </c>
+      <c r="H49" s="11">
+        <v>0</v>
+      </c>
+      <c r="I49" s="11">
+        <v>-1</v>
+      </c>
+      <c r="J49" s="1">
+        <v>0</v>
+      </c>
+      <c r="K49" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="F49" s="11">
-        <v>12</v>
-      </c>
-      <c r="G49" s="11">
-        <v>0</v>
-      </c>
-      <c r="H49" s="11">
-        <v>-1</v>
-      </c>
-      <c r="I49" s="1">
-        <v>0</v>
-      </c>
-      <c r="J49" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K49" s="11">
-        <v>0</v>
-      </c>
-      <c r="L49">
+      <c r="L49" s="11">
+        <v>0</v>
+      </c>
+      <c r="M49">
         <v>100</v>
       </c>
-      <c r="M49"/>
-    </row>
-    <row r="50" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="N49"/>
+    </row>
+    <row r="50" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A50" s="1">
         <f t="shared" si="4"/>
         <v>20030010</v>
@@ -3258,79 +3432,85 @@
       <c r="B50" s="9">
         <v>200300</v>
       </c>
-      <c r="C50" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D50" s="9">
+      <c r="C50" s="9">
+        <v>2</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E50" s="9">
         <v>200300001</v>
       </c>
-      <c r="E50" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="F50" s="11">
+      <c r="F50" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G50" s="11">
         <v>10</v>
       </c>
-      <c r="G50" s="11">
-        <v>0</v>
-      </c>
       <c r="H50" s="11">
-        <v>-1</v>
-      </c>
-      <c r="I50" s="1">
-        <v>0</v>
-      </c>
-      <c r="J50" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K50" s="11">
-        <v>0</v>
-      </c>
-      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="I50" s="11">
+        <v>-1</v>
+      </c>
+      <c r="J50" s="1">
+        <v>0</v>
+      </c>
+      <c r="K50" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="L50" s="11">
+        <v>0</v>
+      </c>
+      <c r="M50">
         <v>100</v>
       </c>
-      <c r="M50"/>
-    </row>
-    <row r="51" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="N50"/>
+    </row>
+    <row r="51" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A51" s="1">
-        <f t="shared" ref="A51:A59" si="5">B51*100+F51</f>
+        <f t="shared" ref="A51:A59" si="5">B51*100+G51</f>
         <v>20030011</v>
       </c>
       <c r="B51" s="9">
         <v>200300</v>
       </c>
-      <c r="C51" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D51" s="9">
+      <c r="C51" s="9">
+        <v>2</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E51" s="9">
         <v>200300001</v>
       </c>
-      <c r="E51" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="F51" s="11">
+      <c r="F51" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G51" s="11">
         <v>11</v>
       </c>
-      <c r="G51" s="11">
-        <v>0</v>
-      </c>
       <c r="H51" s="11">
-        <v>-1</v>
-      </c>
-      <c r="I51" s="1">
-        <v>0</v>
-      </c>
-      <c r="J51" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K51" s="11">
-        <v>0</v>
-      </c>
-      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="I51" s="11">
+        <v>-1</v>
+      </c>
+      <c r="J51" s="1">
+        <v>0</v>
+      </c>
+      <c r="K51" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="L51" s="11">
+        <v>0</v>
+      </c>
+      <c r="M51">
         <v>100</v>
       </c>
-      <c r="M51"/>
-    </row>
-    <row r="52" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="N51"/>
+    </row>
+    <row r="52" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A52" s="1">
         <f t="shared" si="5"/>
         <v>20030012</v>
@@ -3338,39 +3518,42 @@
       <c r="B52" s="9">
         <v>200300</v>
       </c>
-      <c r="C52" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D52" s="9">
+      <c r="C52" s="9">
+        <v>2</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E52" s="9">
         <v>200300001</v>
       </c>
-      <c r="E52" s="11" t="s">
+      <c r="F52" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G52" s="11">
+        <v>12</v>
+      </c>
+      <c r="H52" s="11">
+        <v>0</v>
+      </c>
+      <c r="I52" s="11">
+        <v>-1</v>
+      </c>
+      <c r="J52" s="1">
+        <v>0</v>
+      </c>
+      <c r="K52" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="F52" s="11">
-        <v>12</v>
-      </c>
-      <c r="G52" s="11">
-        <v>0</v>
-      </c>
-      <c r="H52" s="11">
-        <v>-1</v>
-      </c>
-      <c r="I52" s="1">
-        <v>0</v>
-      </c>
-      <c r="J52" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K52" s="11">
-        <v>0</v>
-      </c>
-      <c r="L52">
+      <c r="L52" s="11">
+        <v>0</v>
+      </c>
+      <c r="M52">
         <v>100</v>
       </c>
-      <c r="M52"/>
-    </row>
-    <row r="53" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="N52"/>
+    </row>
+    <row r="53" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A53" s="1">
         <f t="shared" si="5"/>
         <v>20040010</v>
@@ -3378,39 +3561,42 @@
       <c r="B53" s="9">
         <v>200400</v>
       </c>
-      <c r="C53" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D53" s="9">
+      <c r="C53" s="9">
+        <v>2</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E53" s="9">
         <v>200400009</v>
       </c>
-      <c r="E53" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="F53" s="11">
+      <c r="F53" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G53" s="11">
         <v>10</v>
       </c>
-      <c r="G53" s="11">
-        <v>0</v>
-      </c>
       <c r="H53" s="11">
-        <v>-1</v>
-      </c>
-      <c r="I53" s="1">
-        <v>0</v>
-      </c>
-      <c r="J53" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K53" s="11">
-        <v>0</v>
-      </c>
-      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="I53" s="11">
+        <v>-1</v>
+      </c>
+      <c r="J53" s="1">
+        <v>0</v>
+      </c>
+      <c r="K53" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="L53" s="11">
+        <v>0</v>
+      </c>
+      <c r="M53">
         <v>100</v>
       </c>
-      <c r="M53"/>
-    </row>
-    <row r="54" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="N53"/>
+    </row>
+    <row r="54" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A54" s="1">
         <f t="shared" si="5"/>
         <v>20040011</v>
@@ -3418,39 +3604,42 @@
       <c r="B54" s="9">
         <v>200400</v>
       </c>
-      <c r="C54" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D54" s="9">
+      <c r="C54" s="9">
+        <v>2</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E54" s="9">
         <v>200400009</v>
       </c>
-      <c r="E54" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="F54" s="11">
+      <c r="F54" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G54" s="11">
         <v>11</v>
       </c>
-      <c r="G54" s="11">
-        <v>0</v>
-      </c>
       <c r="H54" s="11">
-        <v>-1</v>
-      </c>
-      <c r="I54" s="1">
-        <v>0</v>
-      </c>
-      <c r="J54" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K54" s="11">
-        <v>0</v>
-      </c>
-      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="I54" s="11">
+        <v>-1</v>
+      </c>
+      <c r="J54" s="1">
+        <v>0</v>
+      </c>
+      <c r="K54" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="L54" s="11">
+        <v>0</v>
+      </c>
+      <c r="M54">
         <v>100</v>
       </c>
-      <c r="M54"/>
-    </row>
-    <row r="55" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="N54"/>
+    </row>
+    <row r="55" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A55" s="1">
         <f t="shared" si="5"/>
         <v>20040012</v>
@@ -3458,39 +3647,42 @@
       <c r="B55" s="9">
         <v>200400</v>
       </c>
-      <c r="C55" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D55" s="9">
+      <c r="C55" s="9">
+        <v>2</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E55" s="9">
         <v>200400009</v>
       </c>
-      <c r="E55" s="11" t="s">
+      <c r="F55" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G55" s="11">
+        <v>12</v>
+      </c>
+      <c r="H55" s="11">
+        <v>0</v>
+      </c>
+      <c r="I55" s="11">
+        <v>-1</v>
+      </c>
+      <c r="J55" s="1">
+        <v>0</v>
+      </c>
+      <c r="K55" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="F55" s="11">
-        <v>12</v>
-      </c>
-      <c r="G55" s="11">
-        <v>0</v>
-      </c>
-      <c r="H55" s="11">
-        <v>-1</v>
-      </c>
-      <c r="I55" s="1">
-        <v>0</v>
-      </c>
-      <c r="J55" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K55" s="11">
-        <v>0</v>
-      </c>
-      <c r="L55">
+      <c r="L55" s="11">
+        <v>0</v>
+      </c>
+      <c r="M55">
         <v>100</v>
       </c>
-      <c r="M55"/>
-    </row>
-    <row r="56" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="N55"/>
+    </row>
+    <row r="56" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A56" s="1">
         <f t="shared" si="5"/>
         <v>20050010</v>
@@ -3498,39 +3690,42 @@
       <c r="B56" s="9">
         <v>200500</v>
       </c>
-      <c r="C56" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D56" s="9">
+      <c r="C56" s="9">
+        <v>2</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E56" s="9">
         <v>200500025</v>
       </c>
-      <c r="E56" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="F56" s="11">
+      <c r="F56" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G56" s="11">
         <v>10</v>
       </c>
-      <c r="G56" s="11">
-        <v>0</v>
-      </c>
       <c r="H56" s="11">
-        <v>-1</v>
-      </c>
-      <c r="I56" s="1">
-        <v>0</v>
-      </c>
-      <c r="J56" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K56" s="11">
-        <v>0</v>
-      </c>
-      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="I56" s="11">
+        <v>-1</v>
+      </c>
+      <c r="J56" s="1">
+        <v>0</v>
+      </c>
+      <c r="K56" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="L56" s="11">
+        <v>0</v>
+      </c>
+      <c r="M56">
         <v>100</v>
       </c>
-      <c r="M56"/>
-    </row>
-    <row r="57" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="N56"/>
+    </row>
+    <row r="57" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A57" s="1">
         <f t="shared" si="5"/>
         <v>20050011</v>
@@ -3538,39 +3733,42 @@
       <c r="B57" s="9">
         <v>200500</v>
       </c>
-      <c r="C57" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D57" s="9">
+      <c r="C57" s="9">
+        <v>2</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E57" s="9">
         <v>200500025</v>
       </c>
-      <c r="E57" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="F57" s="11">
+      <c r="F57" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G57" s="11">
         <v>11</v>
       </c>
-      <c r="G57" s="11">
-        <v>0</v>
-      </c>
       <c r="H57" s="11">
-        <v>-1</v>
-      </c>
-      <c r="I57" s="1">
-        <v>0</v>
-      </c>
-      <c r="J57" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K57" s="11">
-        <v>0</v>
-      </c>
-      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="I57" s="11">
+        <v>-1</v>
+      </c>
+      <c r="J57" s="1">
+        <v>0</v>
+      </c>
+      <c r="K57" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="L57" s="11">
+        <v>0</v>
+      </c>
+      <c r="M57">
         <v>100</v>
       </c>
-      <c r="M57"/>
-    </row>
-    <row r="58" s="1" customFormat="1" ht="16.5" spans="1:13">
+      <c r="N57"/>
+    </row>
+    <row r="58" s="1" customFormat="1" ht="16.5" spans="1:14">
       <c r="A58" s="1">
         <f t="shared" si="5"/>
         <v>20050012</v>
@@ -3578,39 +3776,42 @@
       <c r="B58" s="9">
         <v>200500</v>
       </c>
-      <c r="C58" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D58" s="9">
+      <c r="C58" s="9">
+        <v>2</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E58" s="9">
         <v>200500025</v>
       </c>
-      <c r="E58" s="11" t="s">
+      <c r="F58" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G58" s="11">
+        <v>12</v>
+      </c>
+      <c r="H58" s="11">
+        <v>0</v>
+      </c>
+      <c r="I58" s="11">
+        <v>-1</v>
+      </c>
+      <c r="J58" s="1">
+        <v>0</v>
+      </c>
+      <c r="K58" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="F58" s="11">
-        <v>12</v>
-      </c>
-      <c r="G58" s="11">
-        <v>0</v>
-      </c>
-      <c r="H58" s="11">
-        <v>-1</v>
-      </c>
-      <c r="I58" s="1">
-        <v>0</v>
-      </c>
-      <c r="J58" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K58" s="11">
-        <v>0</v>
-      </c>
-      <c r="L58">
+      <c r="L58" s="11">
+        <v>0</v>
+      </c>
+      <c r="M58">
         <v>100</v>
       </c>
-      <c r="M58"/>
-    </row>
-    <row r="59" ht="16.5" spans="1:12">
+      <c r="N58"/>
+    </row>
+    <row r="59" ht="16.5" spans="1:13">
       <c r="A59" s="1">
         <f t="shared" si="5"/>
         <v>20060010</v>
@@ -3618,77 +3819,83 @@
       <c r="B59" s="9">
         <v>200600</v>
       </c>
-      <c r="C59" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D59" s="9">
+      <c r="C59" s="9">
+        <v>2</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E59" s="9">
         <v>200600001</v>
       </c>
-      <c r="E59" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="F59" s="11">
+      <c r="F59" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G59" s="11">
         <v>10</v>
       </c>
-      <c r="G59" s="11">
-        <v>0</v>
-      </c>
       <c r="H59" s="11">
-        <v>-1</v>
-      </c>
-      <c r="I59" s="1">
-        <v>0</v>
-      </c>
-      <c r="J59" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K59" s="11">
-        <v>0</v>
-      </c>
-      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="I59" s="11">
+        <v>-1</v>
+      </c>
+      <c r="J59" s="1">
+        <v>0</v>
+      </c>
+      <c r="K59" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="L59" s="11">
+        <v>0</v>
+      </c>
+      <c r="M59">
         <v>100</v>
       </c>
     </row>
-    <row r="60" ht="16.5" spans="1:12">
+    <row r="60" ht="16.5" spans="1:13">
       <c r="A60" s="1">
-        <f t="shared" ref="A60:A70" si="6">B60*100+F60</f>
+        <f t="shared" ref="A60:A70" si="6">B60*100+G60</f>
         <v>20060011</v>
       </c>
       <c r="B60" s="9">
         <v>200600</v>
       </c>
-      <c r="C60" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D60" s="9">
+      <c r="C60" s="9">
+        <v>2</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E60" s="9">
         <v>200600001</v>
       </c>
-      <c r="E60" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="F60" s="11">
+      <c r="F60" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G60" s="11">
         <v>11</v>
       </c>
-      <c r="G60" s="11">
-        <v>0</v>
-      </c>
       <c r="H60" s="11">
-        <v>-1</v>
-      </c>
-      <c r="I60" s="1">
-        <v>0</v>
-      </c>
-      <c r="J60" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K60" s="11">
-        <v>0</v>
-      </c>
-      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="I60" s="11">
+        <v>-1</v>
+      </c>
+      <c r="J60" s="1">
+        <v>0</v>
+      </c>
+      <c r="K60" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="L60" s="11">
+        <v>0</v>
+      </c>
+      <c r="M60">
         <v>100</v>
       </c>
     </row>
-    <row r="61" ht="16.5" spans="1:12">
+    <row r="61" ht="16.5" spans="1:13">
       <c r="A61" s="1">
         <f t="shared" si="6"/>
         <v>20060012</v>
@@ -3696,38 +3903,41 @@
       <c r="B61" s="9">
         <v>200600</v>
       </c>
-      <c r="C61" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D61" s="9">
+      <c r="C61" s="9">
+        <v>2</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E61" s="9">
         <v>200600001</v>
       </c>
-      <c r="E61" s="11" t="s">
+      <c r="F61" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G61" s="11">
+        <v>12</v>
+      </c>
+      <c r="H61" s="11">
+        <v>0</v>
+      </c>
+      <c r="I61" s="11">
+        <v>-1</v>
+      </c>
+      <c r="J61" s="1">
+        <v>0</v>
+      </c>
+      <c r="K61" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="F61" s="11">
-        <v>12</v>
-      </c>
-      <c r="G61" s="11">
-        <v>0</v>
-      </c>
-      <c r="H61" s="11">
-        <v>-1</v>
-      </c>
-      <c r="I61" s="1">
-        <v>0</v>
-      </c>
-      <c r="J61" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K61" s="11">
-        <v>0</v>
-      </c>
-      <c r="L61">
+      <c r="L61" s="11">
+        <v>0</v>
+      </c>
+      <c r="M61">
         <v>100</v>
       </c>
     </row>
-    <row r="62" ht="16.5" spans="1:12">
+    <row r="62" ht="16.5" spans="1:13">
       <c r="A62" s="1">
         <f t="shared" si="6"/>
         <v>20070010</v>
@@ -3735,38 +3945,41 @@
       <c r="B62" s="9">
         <v>200700</v>
       </c>
-      <c r="C62" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D62" s="9">
+      <c r="C62" s="9">
+        <v>2</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E62" s="9">
         <v>200700001</v>
       </c>
-      <c r="E62" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="F62" s="11">
+      <c r="F62" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G62" s="11">
         <v>10</v>
       </c>
-      <c r="G62" s="11">
-        <v>0</v>
-      </c>
       <c r="H62" s="11">
-        <v>-1</v>
-      </c>
-      <c r="I62" s="1">
-        <v>0</v>
-      </c>
-      <c r="J62" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K62" s="11">
-        <v>0</v>
-      </c>
-      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="I62" s="11">
+        <v>-1</v>
+      </c>
+      <c r="J62" s="1">
+        <v>0</v>
+      </c>
+      <c r="K62" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="L62" s="11">
+        <v>0</v>
+      </c>
+      <c r="M62">
         <v>100</v>
       </c>
     </row>
-    <row r="63" ht="16.5" spans="1:12">
+    <row r="63" ht="16.5" spans="1:13">
       <c r="A63" s="1">
         <f t="shared" si="6"/>
         <v>20070011</v>
@@ -3774,38 +3987,41 @@
       <c r="B63" s="9">
         <v>200700</v>
       </c>
-      <c r="C63" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D63" s="9">
+      <c r="C63" s="9">
+        <v>2</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E63" s="9">
         <v>200700001</v>
       </c>
-      <c r="E63" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="F63" s="11">
+      <c r="F63" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G63" s="11">
         <v>11</v>
       </c>
-      <c r="G63" s="11">
-        <v>0</v>
-      </c>
       <c r="H63" s="11">
-        <v>-1</v>
-      </c>
-      <c r="I63" s="1">
-        <v>0</v>
-      </c>
-      <c r="J63" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K63" s="11">
-        <v>0</v>
-      </c>
-      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="I63" s="11">
+        <v>-1</v>
+      </c>
+      <c r="J63" s="1">
+        <v>0</v>
+      </c>
+      <c r="K63" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="L63" s="11">
+        <v>0</v>
+      </c>
+      <c r="M63">
         <v>100</v>
       </c>
     </row>
-    <row r="64" ht="16.5" spans="1:12">
+    <row r="64" ht="16.5" spans="1:13">
       <c r="A64" s="1">
         <f t="shared" si="6"/>
         <v>20070012</v>
@@ -3813,38 +4029,41 @@
       <c r="B64" s="9">
         <v>200700</v>
       </c>
-      <c r="C64" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D64" s="9">
+      <c r="C64" s="9">
+        <v>2</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E64" s="9">
         <v>200700001</v>
       </c>
-      <c r="E64" s="11" t="s">
+      <c r="F64" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G64" s="11">
+        <v>12</v>
+      </c>
+      <c r="H64" s="11">
+        <v>0</v>
+      </c>
+      <c r="I64" s="11">
+        <v>-1</v>
+      </c>
+      <c r="J64" s="1">
+        <v>0</v>
+      </c>
+      <c r="K64" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="F64" s="11">
-        <v>12</v>
-      </c>
-      <c r="G64" s="11">
-        <v>0</v>
-      </c>
-      <c r="H64" s="11">
-        <v>-1</v>
-      </c>
-      <c r="I64" s="1">
-        <v>0</v>
-      </c>
-      <c r="J64" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K64" s="11">
-        <v>0</v>
-      </c>
-      <c r="L64">
+      <c r="L64" s="11">
+        <v>0</v>
+      </c>
+      <c r="M64">
         <v>100</v>
       </c>
     </row>
-    <row r="65" ht="16.5" spans="1:12">
+    <row r="65" ht="16.5" spans="1:13">
       <c r="A65" s="1">
         <f t="shared" si="6"/>
         <v>20080010</v>
@@ -3852,38 +4071,41 @@
       <c r="B65" s="9">
         <v>200800</v>
       </c>
-      <c r="C65" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D65" s="9">
+      <c r="C65" s="9">
+        <v>2</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E65" s="9">
         <v>200800001</v>
       </c>
-      <c r="E65" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="F65" s="11">
+      <c r="F65" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G65" s="11">
         <v>10</v>
       </c>
-      <c r="G65" s="11">
-        <v>0</v>
-      </c>
       <c r="H65" s="11">
-        <v>-1</v>
-      </c>
-      <c r="I65" s="1">
-        <v>0</v>
-      </c>
-      <c r="J65" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K65" s="11">
-        <v>0</v>
-      </c>
-      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="I65" s="11">
+        <v>-1</v>
+      </c>
+      <c r="J65" s="1">
+        <v>0</v>
+      </c>
+      <c r="K65" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="L65" s="11">
+        <v>0</v>
+      </c>
+      <c r="M65">
         <v>100</v>
       </c>
     </row>
-    <row r="66" ht="16.5" spans="1:12">
+    <row r="66" ht="16.5" spans="1:13">
       <c r="A66" s="1">
         <f t="shared" si="6"/>
         <v>20080011</v>
@@ -3891,38 +4113,41 @@
       <c r="B66" s="9">
         <v>200800</v>
       </c>
-      <c r="C66" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D66" s="9">
+      <c r="C66" s="9">
+        <v>2</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E66" s="9">
         <v>200800001</v>
       </c>
-      <c r="E66" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="F66" s="11">
+      <c r="F66" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G66" s="11">
         <v>11</v>
       </c>
-      <c r="G66" s="11">
-        <v>0</v>
-      </c>
       <c r="H66" s="11">
-        <v>-1</v>
-      </c>
-      <c r="I66" s="1">
-        <v>0</v>
-      </c>
-      <c r="J66" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K66" s="11">
-        <v>0</v>
-      </c>
-      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="I66" s="11">
+        <v>-1</v>
+      </c>
+      <c r="J66" s="1">
+        <v>0</v>
+      </c>
+      <c r="K66" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="L66" s="11">
+        <v>0</v>
+      </c>
+      <c r="M66">
         <v>100</v>
       </c>
     </row>
-    <row r="67" ht="16.5" spans="1:12">
+    <row r="67" ht="16.5" spans="1:13">
       <c r="A67" s="1">
         <f t="shared" si="6"/>
         <v>20080012</v>
@@ -3930,38 +4155,41 @@
       <c r="B67" s="9">
         <v>200800</v>
       </c>
-      <c r="C67" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D67" s="9">
+      <c r="C67" s="9">
+        <v>2</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E67" s="9">
         <v>200800001</v>
       </c>
-      <c r="E67" s="11" t="s">
+      <c r="F67" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G67" s="11">
+        <v>12</v>
+      </c>
+      <c r="H67" s="11">
+        <v>0</v>
+      </c>
+      <c r="I67" s="11">
+        <v>-1</v>
+      </c>
+      <c r="J67" s="1">
+        <v>0</v>
+      </c>
+      <c r="K67" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="F67" s="11">
-        <v>12</v>
-      </c>
-      <c r="G67" s="11">
-        <v>0</v>
-      </c>
-      <c r="H67" s="11">
-        <v>-1</v>
-      </c>
-      <c r="I67" s="1">
-        <v>0</v>
-      </c>
-      <c r="J67" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K67" s="11">
-        <v>0</v>
-      </c>
-      <c r="L67">
+      <c r="L67" s="11">
+        <v>0</v>
+      </c>
+      <c r="M67">
         <v>100</v>
       </c>
     </row>
-    <row r="68" ht="16.5" spans="1:12">
+    <row r="68" ht="16.5" spans="1:13">
       <c r="A68" s="1">
         <f t="shared" si="6"/>
         <v>20090010</v>
@@ -3969,38 +4197,41 @@
       <c r="B68" s="9">
         <v>200900</v>
       </c>
-      <c r="C68" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D68" s="9">
+      <c r="C68" s="9">
+        <v>2</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E68" s="9">
         <v>200900001</v>
       </c>
-      <c r="E68" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="F68" s="11">
+      <c r="F68" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G68" s="11">
         <v>10</v>
       </c>
-      <c r="G68" s="11">
-        <v>0</v>
-      </c>
       <c r="H68" s="11">
-        <v>-1</v>
-      </c>
-      <c r="I68" s="1">
-        <v>0</v>
-      </c>
-      <c r="J68" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K68" s="11">
-        <v>0</v>
-      </c>
-      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="I68" s="11">
+        <v>-1</v>
+      </c>
+      <c r="J68" s="1">
+        <v>0</v>
+      </c>
+      <c r="K68" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="L68" s="11">
+        <v>0</v>
+      </c>
+      <c r="M68">
         <v>100</v>
       </c>
     </row>
-    <row r="69" ht="16.5" spans="1:12">
+    <row r="69" ht="16.5" spans="1:13">
       <c r="A69" s="1">
         <f t="shared" si="6"/>
         <v>20090011</v>
@@ -4008,38 +4239,41 @@
       <c r="B69" s="9">
         <v>200900</v>
       </c>
-      <c r="C69" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D69" s="9">
+      <c r="C69" s="9">
+        <v>2</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E69" s="9">
         <v>200900001</v>
       </c>
-      <c r="E69" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="F69" s="11">
+      <c r="F69" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G69" s="11">
         <v>11</v>
       </c>
-      <c r="G69" s="11">
-        <v>0</v>
-      </c>
       <c r="H69" s="11">
-        <v>-1</v>
-      </c>
-      <c r="I69" s="1">
-        <v>0</v>
-      </c>
-      <c r="J69" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K69" s="11">
-        <v>0</v>
-      </c>
-      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="I69" s="11">
+        <v>-1</v>
+      </c>
+      <c r="J69" s="1">
+        <v>0</v>
+      </c>
+      <c r="K69" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="L69" s="11">
+        <v>0</v>
+      </c>
+      <c r="M69">
         <v>100</v>
       </c>
     </row>
-    <row r="70" ht="16.5" spans="1:12">
+    <row r="70" ht="16.5" spans="1:13">
       <c r="A70" s="1">
         <f t="shared" si="6"/>
         <v>20090012</v>
@@ -4047,34 +4281,37 @@
       <c r="B70" s="9">
         <v>200900</v>
       </c>
-      <c r="C70" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D70" s="9">
+      <c r="C70" s="9">
+        <v>2</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E70" s="9">
         <v>200900001</v>
       </c>
-      <c r="E70" s="11" t="s">
+      <c r="F70" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G70" s="11">
+        <v>12</v>
+      </c>
+      <c r="H70" s="11">
+        <v>0</v>
+      </c>
+      <c r="I70" s="11">
+        <v>-1</v>
+      </c>
+      <c r="J70" s="1">
+        <v>0</v>
+      </c>
+      <c r="K70" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="F70" s="11">
-        <v>12</v>
-      </c>
-      <c r="G70" s="11">
-        <v>0</v>
-      </c>
-      <c r="H70" s="11">
-        <v>-1</v>
-      </c>
-      <c r="I70" s="1">
-        <v>0</v>
-      </c>
-      <c r="J70" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="K70" s="11">
-        <v>0</v>
-      </c>
-      <c r="L70">
+      <c r="L70" s="11">
+        <v>0</v>
+      </c>
+      <c r="M70">
         <v>100</v>
       </c>
     </row>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -155,7 +155,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="75">
   <si>
     <t>sid</t>
   </si>
@@ -268,6 +268,24 @@
     <t>SuperStar</t>
   </si>
   <si>
+    <t>麻将胡了</t>
+  </si>
+  <si>
+    <t>MahjongWays</t>
+  </si>
+  <si>
+    <t>财神</t>
+  </si>
+  <si>
+    <t>GodOfWealth</t>
+  </si>
+  <si>
+    <t>埃及艳后</t>
+  </si>
+  <si>
+    <t>Cleopatra</t>
+  </si>
+  <si>
     <t>紅黑大戰</t>
   </si>
   <si>
@@ -359,6 +377,9 @@
   </si>
   <si>
     <t>房间场-高级</t>
+  </si>
+  <si>
+    <t>9:999</t>
   </si>
 </sst>
 </file>
@@ -1453,7 +1474,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S73"/>
+  <dimension ref="A1:S85"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="3" width="9.375" style="1"/>
@@ -1464,7 +1485,7 @@
     <col min="8" max="9" width="9" style="1"/>
     <col min="10" max="10" width="11.25" style="1" customWidth="1"/>
     <col min="11" max="11" width="9.25833333333333" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.7" style="1" customWidth="1"/>
+    <col min="12" max="12" width="17.05" style="1" customWidth="1"/>
     <col min="13" max="13" width="13.9666666666667" style="1" customWidth="1"/>
     <col min="14" max="14" width="13.675" customWidth="1"/>
     <col min="15" max="15" width="8.96666666666667" customWidth="1"/>
@@ -1880,20 +1901,20 @@
     </row>
     <row r="11" ht="16.5" spans="1:14">
       <c r="A11" s="1">
-        <f t="shared" ref="A11:A57" si="2">B11*10+H11</f>
-        <v>2001001</v>
+        <f t="shared" ref="A11:A22" si="2">B11*10+H11</f>
+        <v>1007004</v>
       </c>
       <c r="B11" s="9">
-        <v>200100</v>
+        <v>100700</v>
       </c>
       <c r="C11" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>37</v>
       </c>
       <c r="E11" s="10">
-        <v>200100038</v>
+        <v>100700001</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>38</v>
@@ -1902,13 +1923,13 @@
         <v>30</v>
       </c>
       <c r="H11" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J11" s="1">
-        <v>5000000</v>
+        <v>-1</v>
       </c>
       <c r="K11" s="1">
         <v>0</v>
@@ -1926,35 +1947,36 @@
     <row r="12" ht="16.5" spans="1:14">
       <c r="A12" s="1">
         <f t="shared" si="2"/>
-        <v>2001002</v>
+        <v>1007005</v>
       </c>
       <c r="B12" s="9">
-        <v>200100</v>
+        <v>100700</v>
       </c>
       <c r="C12" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" s="9" t="str">
         <f>D11</f>
-        <v>紅黑大戰</v>
+        <v>麻将胡了</v>
       </c>
       <c r="E12" s="10">
-        <v>200100038</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>38</v>
+        <v>100700001</v>
+      </c>
+      <c r="F12" s="10" t="str">
+        <f>F11</f>
+        <v>MahjongWays</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H12" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I12" s="1">
-        <v>10000</v>
+        <v>50</v>
       </c>
       <c r="J12" s="1">
-        <v>500000000</v>
+        <v>-1</v>
       </c>
       <c r="K12" s="1">
         <v>0</v>
@@ -1969,35 +1991,36 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="13" ht="16.5" spans="1:17">
+    <row r="13" ht="16.5" spans="1:14">
       <c r="A13" s="1">
         <f t="shared" si="2"/>
-        <v>2001003</v>
+        <v>1007006</v>
       </c>
       <c r="B13" s="9">
-        <v>200100</v>
+        <v>100700</v>
       </c>
       <c r="C13" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="9" t="str">
         <f>D12</f>
-        <v>紅黑大戰</v>
+        <v>麻将胡了</v>
       </c>
       <c r="E13" s="10">
-        <v>200100038</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>38</v>
+        <v>100700001</v>
+      </c>
+      <c r="F13" s="10" t="str">
+        <f>F12</f>
+        <v>MahjongWays</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>34</v>
       </c>
       <c r="H13" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I13" s="1">
-        <v>1000000</v>
+        <v>100</v>
       </c>
       <c r="J13" s="1">
         <v>-1</v>
@@ -2014,24 +2037,23 @@
       <c r="N13">
         <v>10000000</v>
       </c>
-      <c r="Q13"/>
     </row>
     <row r="14" ht="16.5" spans="1:14">
       <c r="A14" s="1">
         <f t="shared" si="2"/>
-        <v>2001011</v>
+        <v>1012007</v>
       </c>
       <c r="B14" s="9">
-        <v>200101</v>
+        <v>101200</v>
       </c>
       <c r="C14" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>39</v>
       </c>
       <c r="E14" s="10">
-        <v>200101001</v>
+        <v>101200001</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>40</v>
@@ -2040,13 +2062,13 @@
         <v>30</v>
       </c>
       <c r="H14" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J14" s="1">
-        <v>5000000</v>
+        <v>-1</v>
       </c>
       <c r="K14" s="1">
         <v>0</v>
@@ -2061,38 +2083,39 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="16.5" spans="1:19">
+    <row r="15" ht="16.5" spans="1:14">
       <c r="A15" s="1">
         <f t="shared" si="2"/>
-        <v>2001012</v>
+        <v>1012008</v>
       </c>
       <c r="B15" s="9">
-        <v>200101</v>
+        <v>101200</v>
       </c>
       <c r="C15" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="9" t="str">
-        <f t="shared" ref="D15:D19" si="3">D14</f>
-        <v>龍虎鬥</v>
+        <f>D14</f>
+        <v>财神</v>
       </c>
       <c r="E15" s="10">
-        <v>200101001</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>40</v>
+        <v>101200001</v>
+      </c>
+      <c r="F15" s="10" t="str">
+        <f>F14</f>
+        <v>GodOfWealth</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H15" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I15" s="1">
-        <v>10000</v>
+        <v>50</v>
       </c>
       <c r="J15" s="1">
-        <v>500000000</v>
+        <v>-1</v>
       </c>
       <c r="K15" s="1">
         <v>0</v>
@@ -2106,38 +2129,37 @@
       <c r="N15">
         <v>100000</v>
       </c>
-      <c r="O15"/>
-      <c r="S15" s="2"/>
-    </row>
-    <row r="16" s="1" customFormat="1" ht="16.5" spans="1:19">
+    </row>
+    <row r="16" ht="16.5" spans="1:14">
       <c r="A16" s="1">
         <f t="shared" si="2"/>
-        <v>2001013</v>
+        <v>1012009</v>
       </c>
       <c r="B16" s="9">
-        <v>200101</v>
+        <v>101200</v>
       </c>
       <c r="C16" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>龍虎鬥</v>
+        <f>D15</f>
+        <v>财神</v>
       </c>
       <c r="E16" s="10">
-        <v>200101001</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>40</v>
+        <v>101200001</v>
+      </c>
+      <c r="F16" s="10" t="str">
+        <f>F15</f>
+        <v>GodOfWealth</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>34</v>
       </c>
       <c r="H16" s="1">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I16" s="1">
-        <v>1000000</v>
+        <v>100</v>
       </c>
       <c r="J16" s="1">
         <v>-1</v>
@@ -2154,25 +2176,23 @@
       <c r="N16">
         <v>10000000</v>
       </c>
-      <c r="O16"/>
-      <c r="S16" s="2"/>
     </row>
     <row r="17" ht="16.5" spans="1:14">
       <c r="A17" s="1">
         <f t="shared" si="2"/>
-        <v>2003001</v>
+        <v>1014010</v>
       </c>
       <c r="B17" s="9">
-        <v>200300</v>
+        <v>101400</v>
       </c>
       <c r="C17" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>41</v>
       </c>
       <c r="E17" s="10">
-        <v>200300001</v>
+        <v>101400001</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>42</v>
@@ -2181,13 +2201,13 @@
         <v>30</v>
       </c>
       <c r="H17" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J17" s="1">
-        <v>5000000</v>
+        <v>-1</v>
       </c>
       <c r="K17" s="1">
         <v>0</v>
@@ -2202,38 +2222,39 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="16.5" spans="1:19">
+    <row r="18" ht="16.5" spans="1:14">
       <c r="A18" s="1">
         <f t="shared" si="2"/>
-        <v>2003002</v>
+        <v>1014011</v>
       </c>
       <c r="B18" s="9">
-        <v>200300</v>
+        <v>101400</v>
       </c>
       <c r="C18" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>飛禽走獸</v>
+        <f>D17</f>
+        <v>埃及艳后</v>
       </c>
       <c r="E18" s="10">
-        <v>200300001</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>42</v>
+        <v>101400001</v>
+      </c>
+      <c r="F18" s="10" t="str">
+        <f>F17</f>
+        <v>Cleopatra</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H18" s="1">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I18" s="1">
-        <v>10000</v>
+        <v>50</v>
       </c>
       <c r="J18" s="1">
-        <v>500000000</v>
+        <v>-1</v>
       </c>
       <c r="K18" s="1">
         <v>0</v>
@@ -2247,40 +2268,37 @@
       <c r="N18">
         <v>100000</v>
       </c>
-      <c r="O18"/>
-      <c r="Q18" s="2"/>
-      <c r="R18" s="9"/>
-      <c r="S18" s="2"/>
-    </row>
-    <row r="19" s="1" customFormat="1" ht="16.5" spans="1:19">
+    </row>
+    <row r="19" ht="16.5" spans="1:14">
       <c r="A19" s="1">
         <f t="shared" si="2"/>
-        <v>2003003</v>
+        <v>1014012</v>
       </c>
       <c r="B19" s="9">
-        <v>200300</v>
+        <v>101400</v>
       </c>
       <c r="C19" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>飛禽走獸</v>
+        <f>D18</f>
+        <v>埃及艳后</v>
       </c>
       <c r="E19" s="10">
-        <v>200300001</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>42</v>
+        <v>101400001</v>
+      </c>
+      <c r="F19" s="10" t="str">
+        <f>F18</f>
+        <v>Cleopatra</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>34</v>
       </c>
       <c r="H19" s="1">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I19" s="1">
-        <v>1000000</v>
+        <v>100</v>
       </c>
       <c r="J19" s="1">
         <v>-1</v>
@@ -2297,27 +2315,23 @@
       <c r="N19">
         <v>10000000</v>
       </c>
-      <c r="O19"/>
-      <c r="Q19" s="2"/>
-      <c r="R19" s="11"/>
-      <c r="S19" s="11"/>
-    </row>
-    <row r="20" ht="16.5" spans="1:19">
+    </row>
+    <row r="20" ht="16.5" spans="1:14">
       <c r="A20" s="1">
-        <f t="shared" si="2"/>
-        <v>2004001</v>
+        <f t="shared" ref="A20:A66" si="3">B20*10+H20</f>
+        <v>2001001</v>
       </c>
       <c r="B20" s="9">
-        <v>200400</v>
+        <v>200100</v>
       </c>
       <c r="C20" s="9">
         <v>2</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="9" t="s">
         <v>43</v>
       </c>
       <c r="E20" s="10">
-        <v>200400009</v>
+        <v>200100038</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>44</v>
@@ -2346,26 +2360,24 @@
       <c r="N20">
         <v>1000</v>
       </c>
-      <c r="Q20" s="2"/>
-      <c r="R20" s="11"/>
-      <c r="S20" s="11"/>
-    </row>
-    <row r="21" s="1" customFormat="1" ht="16.5" spans="1:19">
+    </row>
+    <row r="21" ht="16.5" spans="1:14">
       <c r="A21" s="1">
-        <f t="shared" si="2"/>
-        <v>2004002</v>
+        <f t="shared" si="3"/>
+        <v>2001002</v>
       </c>
       <c r="B21" s="9">
-        <v>200400</v>
+        <v>200100</v>
       </c>
       <c r="C21" s="9">
         <v>2</v>
       </c>
-      <c r="D21" s="11" t="s">
-        <v>43</v>
+      <c r="D21" s="9" t="str">
+        <f>D20</f>
+        <v>紅黑大戰</v>
       </c>
       <c r="E21" s="10">
-        <v>200400009</v>
+        <v>200100038</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>44</v>
@@ -2394,27 +2406,24 @@
       <c r="N21">
         <v>100000</v>
       </c>
-      <c r="O21"/>
-      <c r="Q21" s="2"/>
-      <c r="R21" s="11"/>
-      <c r="S21" s="11"/>
-    </row>
-    <row r="22" s="1" customFormat="1" ht="16.5" spans="1:19">
+    </row>
+    <row r="22" ht="16.5" spans="1:17">
       <c r="A22" s="1">
-        <f t="shared" si="2"/>
-        <v>2004003</v>
+        <f t="shared" si="3"/>
+        <v>2001003</v>
       </c>
       <c r="B22" s="9">
-        <v>200400</v>
+        <v>200100</v>
       </c>
       <c r="C22" s="9">
         <v>2</v>
       </c>
-      <c r="D22" s="11" t="s">
-        <v>43</v>
+      <c r="D22" s="9" t="str">
+        <f>D21</f>
+        <v>紅黑大戰</v>
       </c>
       <c r="E22" s="10">
-        <v>200400009</v>
+        <v>200100038</v>
       </c>
       <c r="F22" s="10" t="s">
         <v>44</v>
@@ -2443,18 +2452,15 @@
       <c r="N22">
         <v>10000000</v>
       </c>
-      <c r="O22"/>
-      <c r="Q22" s="2"/>
-      <c r="R22" s="11"/>
-      <c r="S22" s="11"/>
-    </row>
-    <row r="23" ht="16.5" spans="1:19">
+      <c r="Q22"/>
+    </row>
+    <row r="23" ht="16.5" spans="1:14">
       <c r="A23" s="1">
-        <f t="shared" si="2"/>
-        <v>2005001</v>
+        <f t="shared" si="3"/>
+        <v>2001011</v>
       </c>
       <c r="B23" s="9">
-        <v>200500</v>
+        <v>200101</v>
       </c>
       <c r="C23" s="9">
         <v>2</v>
@@ -2463,7 +2469,7 @@
         <v>45</v>
       </c>
       <c r="E23" s="10">
-        <v>200500025</v>
+        <v>200101001</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>46</v>
@@ -2487,31 +2493,29 @@
         <v>31</v>
       </c>
       <c r="M23" s="16" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="N23">
         <v>1000</v>
       </c>
-      <c r="Q23" s="2"/>
-      <c r="R23" s="11"/>
-      <c r="S23" s="11"/>
-    </row>
-    <row r="24" ht="16.5" spans="1:19">
+    </row>
+    <row r="24" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A24" s="1">
-        <f t="shared" si="2"/>
-        <v>2005002</v>
+        <f t="shared" si="3"/>
+        <v>2001012</v>
       </c>
       <c r="B24" s="9">
-        <v>200500</v>
+        <v>200101</v>
       </c>
       <c r="C24" s="9">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="s">
-        <v>45</v>
+      <c r="D24" s="9" t="str">
+        <f t="shared" ref="D24:D28" si="4">D23</f>
+        <v>龍虎鬥</v>
       </c>
       <c r="E24" s="10">
-        <v>200500025</v>
+        <v>200101001</v>
       </c>
       <c r="F24" s="10" t="s">
         <v>46</v>
@@ -2535,31 +2539,31 @@
         <v>31</v>
       </c>
       <c r="M24" s="16" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="N24">
         <v>100000</v>
       </c>
-      <c r="Q24" s="2"/>
-      <c r="R24" s="11"/>
-      <c r="S24" s="11"/>
-    </row>
-    <row r="25" ht="16.5" spans="1:19">
+      <c r="O24"/>
+      <c r="S24" s="2"/>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A25" s="1">
-        <f t="shared" si="2"/>
-        <v>2005003</v>
+        <f t="shared" si="3"/>
+        <v>2001013</v>
       </c>
       <c r="B25" s="9">
-        <v>200500</v>
+        <v>200101</v>
       </c>
       <c r="C25" s="9">
         <v>2</v>
       </c>
-      <c r="D25" s="9" t="s">
-        <v>45</v>
+      <c r="D25" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>龍虎鬥</v>
       </c>
       <c r="E25" s="10">
-        <v>200500025</v>
+        <v>200101001</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>46</v>
@@ -2583,34 +2587,33 @@
         <v>31</v>
       </c>
       <c r="M25" s="16" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="N25">
         <v>10000000</v>
       </c>
-      <c r="Q25" s="2"/>
-      <c r="R25" s="11"/>
-      <c r="S25" s="11"/>
-    </row>
-    <row r="26" ht="16.5" spans="1:19">
+      <c r="O25"/>
+      <c r="S25" s="2"/>
+    </row>
+    <row r="26" ht="16.5" spans="1:14">
       <c r="A26" s="1">
-        <f t="shared" si="2"/>
-        <v>2006001</v>
+        <f t="shared" si="3"/>
+        <v>2003001</v>
       </c>
       <c r="B26" s="9">
-        <v>200600</v>
+        <v>200300</v>
       </c>
       <c r="C26" s="9">
         <v>2</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E26" s="10">
+        <v>200300001</v>
+      </c>
+      <c r="F26" s="10" t="s">
         <v>48</v>
-      </c>
-      <c r="E26" s="10">
-        <v>200600001</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>49</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>30</v>
@@ -2636,29 +2639,27 @@
       <c r="N26">
         <v>1000</v>
       </c>
-      <c r="Q26" s="2"/>
-      <c r="R26" s="11"/>
-      <c r="S26" s="11"/>
     </row>
     <row r="27" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A27" s="1">
-        <f t="shared" si="2"/>
-        <v>2006002</v>
+        <f t="shared" si="3"/>
+        <v>2003002</v>
       </c>
       <c r="B27" s="9">
-        <v>200600</v>
+        <v>200300</v>
       </c>
       <c r="C27" s="9">
         <v>2</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>飛禽走獸</v>
+      </c>
+      <c r="E27" s="10">
+        <v>200300001</v>
+      </c>
+      <c r="F27" s="10" t="s">
         <v>48</v>
-      </c>
-      <c r="E27" s="10">
-        <v>200600001</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>49</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>33</v>
@@ -2686,28 +2687,29 @@
       </c>
       <c r="O27"/>
       <c r="Q27" s="2"/>
-      <c r="R27" s="11"/>
-      <c r="S27" s="11"/>
+      <c r="R27" s="9"/>
+      <c r="S27" s="2"/>
     </row>
     <row r="28" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A28" s="1">
-        <f t="shared" si="2"/>
-        <v>2006003</v>
+        <f t="shared" si="3"/>
+        <v>2003003</v>
       </c>
       <c r="B28" s="9">
-        <v>200600</v>
+        <v>200300</v>
       </c>
       <c r="C28" s="9">
         <v>2</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>飛禽走獸</v>
+      </c>
+      <c r="E28" s="10">
+        <v>200300001</v>
+      </c>
+      <c r="F28" s="10" t="s">
         <v>48</v>
-      </c>
-      <c r="E28" s="10">
-        <v>200600001</v>
-      </c>
-      <c r="F28" s="10" t="s">
-        <v>49</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>34</v>
@@ -2735,28 +2737,28 @@
       </c>
       <c r="O28"/>
       <c r="Q28" s="2"/>
-      <c r="R28"/>
+      <c r="R28" s="11"/>
       <c r="S28" s="11"/>
     </row>
     <row r="29" ht="16.5" spans="1:19">
       <c r="A29" s="1">
-        <f t="shared" si="2"/>
-        <v>2007001</v>
+        <f t="shared" si="3"/>
+        <v>2004001</v>
       </c>
       <c r="B29" s="9">
-        <v>200700</v>
+        <v>200400</v>
       </c>
       <c r="C29" s="9">
         <v>2</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E29" s="10">
+        <v>200400009</v>
+      </c>
+      <c r="F29" s="10" t="s">
         <v>50</v>
-      </c>
-      <c r="E29" s="10">
-        <v>200700001</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>51</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>30</v>
@@ -2788,24 +2790,23 @@
     </row>
     <row r="30" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A30" s="1">
-        <f t="shared" si="2"/>
-        <v>2007002</v>
+        <f t="shared" si="3"/>
+        <v>2004002</v>
       </c>
       <c r="B30" s="9">
-        <v>200700</v>
+        <v>200400</v>
       </c>
       <c r="C30" s="9">
         <v>2</v>
       </c>
-      <c r="D30" s="9" t="str">
-        <f t="shared" ref="D27:D31" si="4">D29</f>
-        <v>越南色碟</v>
+      <c r="D30" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="E30" s="10">
-        <v>200700001</v>
+        <v>200400009</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>33</v>
@@ -2838,24 +2839,23 @@
     </row>
     <row r="31" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A31" s="1">
-        <f t="shared" si="2"/>
-        <v>2007003</v>
+        <f t="shared" si="3"/>
+        <v>2004003</v>
       </c>
       <c r="B31" s="9">
-        <v>200700</v>
+        <v>200400</v>
       </c>
       <c r="C31" s="9">
         <v>2</v>
       </c>
-      <c r="D31" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v>越南色碟</v>
+      <c r="D31" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="E31" s="10">
-        <v>200700001</v>
+        <v>200400009</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>34</v>
@@ -2882,27 +2882,29 @@
         <v>10000000</v>
       </c>
       <c r="O31"/>
-      <c r="S31" s="2"/>
-    </row>
-    <row r="32" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="Q31" s="2"/>
+      <c r="R31" s="11"/>
+      <c r="S31" s="11"/>
+    </row>
+    <row r="32" ht="16.5" spans="1:19">
       <c r="A32" s="1">
-        <f t="shared" si="2"/>
-        <v>2008001</v>
+        <f t="shared" si="3"/>
+        <v>2005001</v>
       </c>
       <c r="B32" s="9">
-        <v>200800</v>
+        <v>200500</v>
       </c>
       <c r="C32" s="9">
         <v>2</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D32" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E32" s="10">
+        <v>200500025</v>
+      </c>
+      <c r="F32" s="10" t="s">
         <v>52</v>
-      </c>
-      <c r="E32" s="10">
-        <v>200800001</v>
-      </c>
-      <c r="F32" s="10" t="s">
-        <v>53</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>30</v>
@@ -2923,33 +2925,34 @@
         <v>31</v>
       </c>
       <c r="M32" s="16" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="N32">
         <v>1000</v>
       </c>
-      <c r="O32"/>
-      <c r="S32" s="2"/>
-    </row>
-    <row r="33" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="Q32" s="2"/>
+      <c r="R32" s="11"/>
+      <c r="S32" s="11"/>
+    </row>
+    <row r="33" ht="16.5" spans="1:19">
       <c r="A33" s="1">
-        <f t="shared" si="2"/>
-        <v>2008002</v>
+        <f t="shared" si="3"/>
+        <v>2005002</v>
       </c>
       <c r="B33" s="9">
-        <v>200800</v>
+        <v>200500</v>
       </c>
       <c r="C33" s="9">
         <v>2</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="D33" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E33" s="10">
+        <v>200500025</v>
+      </c>
+      <c r="F33" s="10" t="s">
         <v>52</v>
-      </c>
-      <c r="E33" s="10">
-        <v>200800001</v>
-      </c>
-      <c r="F33" s="10" t="s">
-        <v>53</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>33</v>
@@ -2970,33 +2973,34 @@
         <v>31</v>
       </c>
       <c r="M33" s="16" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="N33">
         <v>100000</v>
       </c>
-      <c r="O33"/>
-      <c r="S33" s="2"/>
-    </row>
-    <row r="34" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="Q33" s="2"/>
+      <c r="R33" s="11"/>
+      <c r="S33" s="11"/>
+    </row>
+    <row r="34" ht="16.5" spans="1:19">
       <c r="A34" s="1">
-        <f t="shared" si="2"/>
-        <v>2008003</v>
+        <f t="shared" si="3"/>
+        <v>2005003</v>
       </c>
       <c r="B34" s="9">
-        <v>200800</v>
+        <v>200500</v>
       </c>
       <c r="C34" s="9">
         <v>2</v>
       </c>
-      <c r="D34" s="10" t="s">
+      <c r="D34" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E34" s="10">
+        <v>200500025</v>
+      </c>
+      <c r="F34" s="10" t="s">
         <v>52</v>
-      </c>
-      <c r="E34" s="10">
-        <v>200800001</v>
-      </c>
-      <c r="F34" s="10" t="s">
-        <v>53</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>34</v>
@@ -3017,30 +3021,31 @@
         <v>31</v>
       </c>
       <c r="M34" s="16" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="N34">
         <v>10000000</v>
       </c>
-      <c r="O34"/>
-      <c r="S34" s="2"/>
-    </row>
-    <row r="35" ht="16.5" spans="1:14">
+      <c r="Q34" s="2"/>
+      <c r="R34" s="11"/>
+      <c r="S34" s="11"/>
+    </row>
+    <row r="35" ht="16.5" spans="1:19">
       <c r="A35" s="1">
-        <f t="shared" si="2"/>
-        <v>2009001</v>
-      </c>
-      <c r="B35" s="12">
-        <v>200900</v>
+        <f t="shared" si="3"/>
+        <v>2006001</v>
+      </c>
+      <c r="B35" s="9">
+        <v>200600</v>
       </c>
       <c r="C35" s="9">
         <v>2</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="D35" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E35" s="10">
-        <v>200900001</v>
+        <v>200600001</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>55</v>
@@ -3069,24 +3074,26 @@
       <c r="N35">
         <v>1000</v>
       </c>
-    </row>
-    <row r="36" ht="16.5" spans="1:14">
+      <c r="Q35" s="2"/>
+      <c r="R35" s="11"/>
+      <c r="S35" s="11"/>
+    </row>
+    <row r="36" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A36" s="1">
-        <f t="shared" si="2"/>
-        <v>2009002</v>
+        <f t="shared" si="3"/>
+        <v>2006002</v>
       </c>
       <c r="B36" s="9">
-        <v>200900</v>
+        <v>200600</v>
       </c>
       <c r="C36" s="9">
         <v>2</v>
       </c>
-      <c r="D36" s="9" t="str">
-        <f>D35</f>
-        <v>魚蝦蟹</v>
+      <c r="D36" s="10" t="s">
+        <v>54</v>
       </c>
       <c r="E36" s="10">
-        <v>200900001</v>
+        <v>200600001</v>
       </c>
       <c r="F36" s="10" t="s">
         <v>55</v>
@@ -3115,24 +3122,27 @@
       <c r="N36">
         <v>100000</v>
       </c>
-    </row>
-    <row r="37" ht="16.5" spans="1:14">
+      <c r="O36"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="11"/>
+      <c r="S36" s="11"/>
+    </row>
+    <row r="37" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A37" s="1">
-        <f t="shared" si="2"/>
-        <v>2009003</v>
+        <f t="shared" si="3"/>
+        <v>2006003</v>
       </c>
       <c r="B37" s="9">
-        <v>200900</v>
+        <v>200600</v>
       </c>
       <c r="C37" s="9">
         <v>2</v>
       </c>
-      <c r="D37" s="9" t="str">
-        <f>D36</f>
-        <v>魚蝦蟹</v>
+      <c r="D37" s="10" t="s">
+        <v>54</v>
       </c>
       <c r="E37" s="10">
-        <v>200900001</v>
+        <v>200600001</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>55</v>
@@ -3161,14 +3171,18 @@
       <c r="N37">
         <v>10000000</v>
       </c>
-    </row>
-    <row r="38" ht="16.5" spans="1:14">
+      <c r="O37"/>
+      <c r="Q37" s="2"/>
+      <c r="R37"/>
+      <c r="S37" s="11"/>
+    </row>
+    <row r="38" ht="16.5" spans="1:19">
       <c r="A38" s="1">
-        <f t="shared" si="2"/>
-        <v>2010001</v>
+        <f t="shared" si="3"/>
+        <v>2007001</v>
       </c>
       <c r="B38" s="9">
-        <v>201000</v>
+        <v>200700</v>
       </c>
       <c r="C38" s="9">
         <v>2</v>
@@ -3177,9 +3191,11 @@
         <v>56</v>
       </c>
       <c r="E38" s="10">
-        <v>101000006</v>
-      </c>
-      <c r="F38" s="10"/>
+        <v>200700001</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>57</v>
+      </c>
       <c r="G38" s="1" t="s">
         <v>30</v>
       </c>
@@ -3204,25 +3220,31 @@
       <c r="N38">
         <v>1000</v>
       </c>
-    </row>
-    <row r="39" ht="16.5" spans="1:14">
+      <c r="Q38" s="2"/>
+      <c r="R38" s="11"/>
+      <c r="S38" s="11"/>
+    </row>
+    <row r="39" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A39" s="1">
-        <f t="shared" si="2"/>
-        <v>2010002</v>
+        <f t="shared" si="3"/>
+        <v>2007002</v>
       </c>
       <c r="B39" s="9">
-        <v>201000</v>
+        <v>200700</v>
       </c>
       <c r="C39" s="9">
         <v>2</v>
       </c>
-      <c r="D39" s="9" t="s">
-        <v>56</v>
+      <c r="D39" s="9" t="str">
+        <f t="shared" ref="D36:D40" si="5">D38</f>
+        <v>越南色碟</v>
       </c>
       <c r="E39" s="10">
-        <v>101000006</v>
-      </c>
-      <c r="F39" s="10"/>
+        <v>200700001</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>57</v>
+      </c>
       <c r="G39" s="1" t="s">
         <v>33</v>
       </c>
@@ -3247,25 +3269,32 @@
       <c r="N39">
         <v>100000</v>
       </c>
-    </row>
-    <row r="40" ht="16.5" spans="1:14">
+      <c r="O39"/>
+      <c r="Q39" s="2"/>
+      <c r="R39" s="11"/>
+      <c r="S39" s="11"/>
+    </row>
+    <row r="40" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A40" s="1">
-        <f t="shared" si="2"/>
-        <v>2010003</v>
+        <f t="shared" si="3"/>
+        <v>2007003</v>
       </c>
       <c r="B40" s="9">
-        <v>201000</v>
+        <v>200700</v>
       </c>
       <c r="C40" s="9">
         <v>2</v>
       </c>
-      <c r="D40" s="9" t="s">
-        <v>56</v>
+      <c r="D40" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v>越南色碟</v>
       </c>
       <c r="E40" s="10">
-        <v>101000006</v>
-      </c>
-      <c r="F40" s="10"/>
+        <v>200700001</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>57</v>
+      </c>
       <c r="G40" s="1" t="s">
         <v>34</v>
       </c>
@@ -3290,26 +3319,28 @@
       <c r="N40">
         <v>10000000</v>
       </c>
-    </row>
-    <row r="41" ht="16.5" spans="1:14">
+      <c r="O40"/>
+      <c r="S40" s="2"/>
+    </row>
+    <row r="41" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A41" s="1">
-        <f t="shared" si="2"/>
-        <v>3001001</v>
+        <f t="shared" si="3"/>
+        <v>2008001</v>
       </c>
       <c r="B41" s="9">
-        <v>300100</v>
+        <v>200800</v>
       </c>
       <c r="C41" s="9">
-        <v>3</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>57</v>
+        <v>2</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="E41" s="10">
-        <v>300100001</v>
+        <v>200800001</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>30</v>
@@ -3321,40 +3352,42 @@
         <v>100</v>
       </c>
       <c r="J41" s="1">
-        <v>-1</v>
+        <v>5000000</v>
       </c>
       <c r="K41" s="1">
         <v>0</v>
       </c>
-      <c r="L41" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="M41" s="17" t="s">
-        <v>60</v>
+      <c r="L41" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>32</v>
       </c>
       <c r="N41">
-        <v>500</v>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="O41"/>
+      <c r="S41" s="2"/>
     </row>
     <row r="42" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A42" s="1">
-        <f t="shared" si="2"/>
-        <v>3001002</v>
+        <f t="shared" si="3"/>
+        <v>2008002</v>
       </c>
       <c r="B42" s="9">
-        <v>300100</v>
+        <v>200800</v>
       </c>
       <c r="C42" s="9">
-        <v>3</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>57</v>
+        <v>2</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="E42" s="10">
-        <v>300100001</v>
+        <v>200800001</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>33</v>
@@ -3366,42 +3399,42 @@
         <v>10000</v>
       </c>
       <c r="J42" s="1">
-        <v>-1</v>
+        <v>500000000</v>
       </c>
       <c r="K42" s="1">
         <v>0</v>
       </c>
-      <c r="L42" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="M42" s="17" t="s">
-        <v>60</v>
+      <c r="L42" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>32</v>
       </c>
       <c r="N42">
-        <v>20000</v>
+        <v>100000</v>
       </c>
       <c r="O42"/>
       <c r="S42" s="2"/>
     </row>
     <row r="43" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A43" s="1">
-        <f t="shared" si="2"/>
-        <v>3001003</v>
+        <f t="shared" si="3"/>
+        <v>2008003</v>
       </c>
       <c r="B43" s="9">
-        <v>300100</v>
+        <v>200800</v>
       </c>
       <c r="C43" s="9">
-        <v>3</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>57</v>
+        <v>2</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="E43" s="10">
-        <v>300100001</v>
+        <v>200800001</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>34</v>
@@ -3418,37 +3451,37 @@
       <c r="K43" s="1">
         <v>0</v>
       </c>
-      <c r="L43" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="M43" s="17" t="s">
-        <v>60</v>
+      <c r="L43" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>32</v>
       </c>
       <c r="N43">
-        <v>2000000</v>
+        <v>10000000</v>
       </c>
       <c r="O43"/>
       <c r="S43" s="2"/>
     </row>
-    <row r="44" s="1" customFormat="1" ht="16.5" spans="1:19">
+    <row r="44" ht="16.5" spans="1:14">
       <c r="A44" s="1">
-        <f t="shared" si="2"/>
-        <v>3002001</v>
-      </c>
-      <c r="B44" s="9">
-        <v>300200</v>
+        <f t="shared" si="3"/>
+        <v>2009001</v>
+      </c>
+      <c r="B44" s="12">
+        <v>200900</v>
       </c>
       <c r="C44" s="9">
-        <v>3</v>
-      </c>
-      <c r="D44" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E44" s="10">
+        <v>200900001</v>
+      </c>
+      <c r="F44" s="10" t="s">
         <v>61</v>
-      </c>
-      <c r="E44" s="10">
-        <v>300200006</v>
-      </c>
-      <c r="F44" s="10" t="s">
-        <v>62</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>30</v>
@@ -3460,42 +3493,41 @@
         <v>100</v>
       </c>
       <c r="J44" s="1">
-        <v>-1</v>
+        <v>5000000</v>
       </c>
       <c r="K44" s="1">
         <v>0</v>
       </c>
-      <c r="L44" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="M44" s="17" t="s">
-        <v>60</v>
+      <c r="L44" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>32</v>
       </c>
       <c r="N44">
-        <v>500</v>
-      </c>
-      <c r="O44"/>
-      <c r="S44" s="2"/>
-    </row>
-    <row r="45" s="1" customFormat="1" ht="16.5" spans="1:19">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="45" ht="16.5" spans="1:14">
       <c r="A45" s="1">
-        <f t="shared" si="2"/>
-        <v>3002002</v>
+        <f t="shared" si="3"/>
+        <v>2009002</v>
       </c>
       <c r="B45" s="9">
-        <v>300200</v>
+        <v>200900</v>
       </c>
       <c r="C45" s="9">
-        <v>3</v>
-      </c>
-      <c r="D45" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D45" s="9" t="str">
+        <f>D44</f>
+        <v>魚蝦蟹</v>
+      </c>
+      <c r="E45" s="10">
+        <v>200900001</v>
+      </c>
+      <c r="F45" s="10" t="s">
         <v>61</v>
-      </c>
-      <c r="E45" s="10">
-        <v>300200006</v>
-      </c>
-      <c r="F45" s="10" t="s">
-        <v>62</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>33</v>
@@ -3507,42 +3539,41 @@
         <v>10000</v>
       </c>
       <c r="J45" s="1">
-        <v>-1</v>
+        <v>500000000</v>
       </c>
       <c r="K45" s="1">
         <v>0</v>
       </c>
-      <c r="L45" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="M45" s="17" t="s">
-        <v>60</v>
+      <c r="L45" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>32</v>
       </c>
       <c r="N45">
-        <v>20000</v>
-      </c>
-      <c r="O45"/>
-      <c r="S45" s="2"/>
-    </row>
-    <row r="46" s="1" customFormat="1" ht="16.5" spans="1:19">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="46" ht="16.5" spans="1:14">
       <c r="A46" s="1">
-        <f t="shared" si="2"/>
-        <v>3002003</v>
+        <f t="shared" si="3"/>
+        <v>2009003</v>
       </c>
       <c r="B46" s="9">
-        <v>300200</v>
+        <v>200900</v>
       </c>
       <c r="C46" s="9">
-        <v>3</v>
-      </c>
-      <c r="D46" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D46" s="9" t="str">
+        <f>D45</f>
+        <v>魚蝦蟹</v>
+      </c>
+      <c r="E46" s="10">
+        <v>200900001</v>
+      </c>
+      <c r="F46" s="10" t="s">
         <v>61</v>
-      </c>
-      <c r="E46" s="10">
-        <v>300200006</v>
-      </c>
-      <c r="F46" s="10" t="s">
-        <v>62</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>34</v>
@@ -3559,463 +3590,447 @@
       <c r="K46" s="1">
         <v>0</v>
       </c>
-      <c r="L46" s="17" t="s">
+      <c r="L46" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="N46">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="47" ht="16.5" spans="1:14">
+      <c r="A47" s="1">
+        <f t="shared" si="3"/>
+        <v>2010001</v>
+      </c>
+      <c r="B47" s="9">
+        <v>201000</v>
+      </c>
+      <c r="C47" s="9">
+        <v>2</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E47" s="10">
+        <v>101000006</v>
+      </c>
+      <c r="F47" s="10"/>
+      <c r="G47" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H47" s="1">
+        <v>1</v>
+      </c>
+      <c r="I47" s="1">
+        <v>100</v>
+      </c>
+      <c r="J47" s="1">
+        <v>5000000</v>
+      </c>
+      <c r="K47" s="1">
+        <v>0</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="N47">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="48" ht="16.5" spans="1:14">
+      <c r="A48" s="1">
+        <f t="shared" si="3"/>
+        <v>2010002</v>
+      </c>
+      <c r="B48" s="9">
+        <v>201000</v>
+      </c>
+      <c r="C48" s="9">
+        <v>2</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E48" s="10">
+        <v>101000006</v>
+      </c>
+      <c r="F48" s="10"/>
+      <c r="G48" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H48" s="1">
+        <v>2</v>
+      </c>
+      <c r="I48" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J48" s="1">
+        <v>500000000</v>
+      </c>
+      <c r="K48" s="1">
+        <v>0</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="N48">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="49" ht="16.5" spans="1:14">
+      <c r="A49" s="1">
+        <f t="shared" si="3"/>
+        <v>2010003</v>
+      </c>
+      <c r="B49" s="9">
+        <v>201000</v>
+      </c>
+      <c r="C49" s="9">
+        <v>2</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E49" s="10">
+        <v>101000006</v>
+      </c>
+      <c r="F49" s="10"/>
+      <c r="G49" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H49" s="1">
+        <v>3</v>
+      </c>
+      <c r="I49" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="J49" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K49" s="1">
+        <v>0</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="N49">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="50" ht="16.5" spans="1:14">
+      <c r="A50" s="1">
+        <f t="shared" si="3"/>
+        <v>3001001</v>
+      </c>
+      <c r="B50" s="9">
+        <v>300100</v>
+      </c>
+      <c r="C50" s="9">
+        <v>3</v>
+      </c>
+      <c r="D50" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="M46" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="N46">
-        <v>2000000</v>
-      </c>
-      <c r="O46"/>
-      <c r="S46" s="2"/>
-    </row>
-    <row r="47" s="1" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A47" s="1">
-        <f t="shared" ref="A47:A53" si="5">B47*100+H47</f>
-        <v>20010010</v>
-      </c>
-      <c r="B47" s="10">
-        <v>200100</v>
-      </c>
-      <c r="C47" s="10">
-        <v>2</v>
-      </c>
-      <c r="D47" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="E47" s="10">
-        <v>200100038</v>
-      </c>
-      <c r="F47" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="G47" s="13" t="s">
+      <c r="E50" s="10">
+        <v>300100001</v>
+      </c>
+      <c r="F50" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="H47" s="13">
-        <v>10</v>
-      </c>
-      <c r="I47" s="13">
-        <v>0</v>
-      </c>
-      <c r="J47" s="13">
-        <v>-1</v>
-      </c>
-      <c r="K47" s="1">
-        <v>0</v>
-      </c>
-      <c r="L47" s="13" t="s">
+      <c r="G50" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H50" s="1">
+        <v>1</v>
+      </c>
+      <c r="I50" s="1">
+        <v>100</v>
+      </c>
+      <c r="J50" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K50" s="1">
+        <v>0</v>
+      </c>
+      <c r="L50" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="M47" s="13">
-        <v>0</v>
-      </c>
-      <c r="N47">
-        <v>100</v>
-      </c>
-      <c r="O47"/>
-      <c r="S47" s="2"/>
-    </row>
-    <row r="48" s="1" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A48" s="1">
-        <f t="shared" si="5"/>
-        <v>20010011</v>
-      </c>
-      <c r="B48" s="10">
-        <v>200100</v>
-      </c>
-      <c r="C48" s="10">
-        <v>2</v>
-      </c>
-      <c r="D48" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="E48" s="10">
-        <v>200100038</v>
-      </c>
-      <c r="F48" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="G48" s="13" t="s">
+      <c r="M50" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="H48" s="13">
-        <v>11</v>
-      </c>
-      <c r="I48" s="13">
-        <v>0</v>
-      </c>
-      <c r="J48" s="13">
-        <v>-1</v>
-      </c>
-      <c r="K48" s="1">
-        <v>0</v>
-      </c>
-      <c r="L48" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="M48" s="13">
-        <v>0</v>
-      </c>
-      <c r="N48">
-        <v>100</v>
-      </c>
-      <c r="O48"/>
-      <c r="S48" s="2"/>
-    </row>
-    <row r="49" s="1" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A49" s="1">
-        <f t="shared" si="5"/>
-        <v>20010012</v>
-      </c>
-      <c r="B49" s="10">
-        <v>200100</v>
-      </c>
-      <c r="C49" s="10">
-        <v>2</v>
-      </c>
-      <c r="D49" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="E49" s="10">
-        <v>200100038</v>
-      </c>
-      <c r="F49" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="G49" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="H49" s="13">
-        <v>12</v>
-      </c>
-      <c r="I49" s="13">
-        <v>0</v>
-      </c>
-      <c r="J49" s="13">
-        <v>-1</v>
-      </c>
-      <c r="K49" s="1">
-        <v>0</v>
-      </c>
-      <c r="L49" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="M49" s="13">
-        <v>0</v>
-      </c>
-      <c r="N49">
-        <v>100</v>
-      </c>
-      <c r="O49"/>
-      <c r="S49" s="2"/>
-    </row>
-    <row r="50" s="1" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A50" s="1">
-        <f t="shared" si="5"/>
-        <v>20010110</v>
-      </c>
-      <c r="B50" s="10">
-        <v>200101</v>
-      </c>
-      <c r="C50" s="10">
-        <v>2</v>
-      </c>
-      <c r="D50" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E50" s="10">
-        <v>200101001</v>
-      </c>
-      <c r="F50" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="G50" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="H50" s="13">
-        <v>10</v>
-      </c>
-      <c r="I50" s="13">
-        <v>0</v>
-      </c>
-      <c r="J50" s="13">
-        <v>-1</v>
-      </c>
-      <c r="K50" s="1">
-        <v>0</v>
-      </c>
-      <c r="L50" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="M50" s="13">
-        <v>0</v>
-      </c>
       <c r="N50">
-        <v>100</v>
-      </c>
-      <c r="O50"/>
-      <c r="S50" s="2"/>
+        <v>500</v>
+      </c>
     </row>
     <row r="51" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A51" s="1">
-        <f t="shared" si="5"/>
-        <v>20010111</v>
-      </c>
-      <c r="B51" s="10">
-        <v>200101</v>
-      </c>
-      <c r="C51" s="10">
-        <v>2</v>
-      </c>
-      <c r="D51" s="10" t="s">
-        <v>39</v>
+        <f t="shared" si="3"/>
+        <v>3001002</v>
+      </c>
+      <c r="B51" s="9">
+        <v>300100</v>
+      </c>
+      <c r="C51" s="9">
+        <v>3</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>63</v>
       </c>
       <c r="E51" s="10">
-        <v>200101001</v>
+        <v>300100001</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="G51" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H51" s="1">
+        <v>2</v>
+      </c>
+      <c r="I51" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J51" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K51" s="1">
+        <v>0</v>
+      </c>
+      <c r="L51" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="M51" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="H51" s="13">
-        <v>11</v>
-      </c>
-      <c r="I51" s="13">
-        <v>0</v>
-      </c>
-      <c r="J51" s="13">
-        <v>-1</v>
-      </c>
-      <c r="K51" s="1">
-        <v>0</v>
-      </c>
-      <c r="L51" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="M51" s="13">
-        <v>0</v>
-      </c>
       <c r="N51">
-        <v>100</v>
+        <v>20000</v>
       </c>
       <c r="O51"/>
       <c r="S51" s="2"/>
     </row>
     <row r="52" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A52" s="1">
-        <f t="shared" si="5"/>
-        <v>20010112</v>
-      </c>
-      <c r="B52" s="10">
-        <v>200101</v>
-      </c>
-      <c r="C52" s="10">
-        <v>2</v>
-      </c>
-      <c r="D52" s="10" t="s">
-        <v>39</v>
+        <f t="shared" si="3"/>
+        <v>3001003</v>
+      </c>
+      <c r="B52" s="9">
+        <v>300100</v>
+      </c>
+      <c r="C52" s="9">
+        <v>3</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>63</v>
       </c>
       <c r="E52" s="10">
-        <v>200101001</v>
+        <v>300100001</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="G52" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="H52" s="13">
-        <v>12</v>
-      </c>
-      <c r="I52" s="13">
-        <v>0</v>
-      </c>
-      <c r="J52" s="13">
+        <v>64</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H52" s="1">
+        <v>3</v>
+      </c>
+      <c r="I52" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="J52" s="1">
         <v>-1</v>
       </c>
       <c r="K52" s="1">
         <v>0</v>
       </c>
-      <c r="L52" s="13" t="s">
+      <c r="L52" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="M52" s="13">
-        <v>0</v>
+      <c r="M52" s="17" t="s">
+        <v>66</v>
       </c>
       <c r="N52">
-        <v>100</v>
+        <v>2000000</v>
       </c>
       <c r="O52"/>
       <c r="S52" s="2"/>
     </row>
     <row r="53" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A53" s="1">
-        <f t="shared" si="5"/>
-        <v>20030010</v>
-      </c>
-      <c r="B53" s="10">
-        <v>200300</v>
-      </c>
-      <c r="C53" s="10">
-        <v>2</v>
-      </c>
-      <c r="D53" s="10" t="s">
-        <v>41</v>
+        <f t="shared" si="3"/>
+        <v>3002001</v>
+      </c>
+      <c r="B53" s="9">
+        <v>300200</v>
+      </c>
+      <c r="C53" s="9">
+        <v>3</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>67</v>
       </c>
       <c r="E53" s="10">
-        <v>200300001</v>
+        <v>300200006</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="G53" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="H53" s="13">
-        <v>10</v>
-      </c>
-      <c r="I53" s="13">
-        <v>0</v>
-      </c>
-      <c r="J53" s="13">
+        <v>68</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H53" s="1">
+        <v>1</v>
+      </c>
+      <c r="I53" s="1">
+        <v>100</v>
+      </c>
+      <c r="J53" s="1">
         <v>-1</v>
       </c>
       <c r="K53" s="1">
         <v>0</v>
       </c>
-      <c r="L53" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="M53" s="13">
-        <v>0</v>
+      <c r="L53" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="M53" s="17" t="s">
+        <v>66</v>
       </c>
       <c r="N53">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="O53"/>
       <c r="S53" s="2"/>
     </row>
     <row r="54" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A54" s="1">
-        <f t="shared" ref="A54:A62" si="6">B54*100+H54</f>
-        <v>20030011</v>
-      </c>
-      <c r="B54" s="10">
-        <v>200300</v>
-      </c>
-      <c r="C54" s="10">
-        <v>2</v>
-      </c>
-      <c r="D54" s="10" t="s">
-        <v>41</v>
+        <f t="shared" si="3"/>
+        <v>3002002</v>
+      </c>
+      <c r="B54" s="9">
+        <v>300200</v>
+      </c>
+      <c r="C54" s="9">
+        <v>3</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>67</v>
       </c>
       <c r="E54" s="10">
-        <v>200300001</v>
+        <v>300200006</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="G54" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H54" s="1">
+        <v>2</v>
+      </c>
+      <c r="I54" s="1">
+        <v>10000</v>
+      </c>
+      <c r="J54" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K54" s="1">
+        <v>0</v>
+      </c>
+      <c r="L54" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="M54" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="H54" s="13">
-        <v>11</v>
-      </c>
-      <c r="I54" s="13">
-        <v>0</v>
-      </c>
-      <c r="J54" s="13">
-        <v>-1</v>
-      </c>
-      <c r="K54" s="1">
-        <v>0</v>
-      </c>
-      <c r="L54" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="M54" s="13">
-        <v>0</v>
-      </c>
       <c r="N54">
-        <v>100</v>
+        <v>20000</v>
       </c>
       <c r="O54"/>
       <c r="S54" s="2"/>
     </row>
     <row r="55" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A55" s="1">
-        <f t="shared" si="6"/>
-        <v>20030012</v>
-      </c>
-      <c r="B55" s="10">
-        <v>200300</v>
-      </c>
-      <c r="C55" s="10">
-        <v>2</v>
-      </c>
-      <c r="D55" s="10" t="s">
-        <v>41</v>
+        <f t="shared" si="3"/>
+        <v>3002003</v>
+      </c>
+      <c r="B55" s="9">
+        <v>300200</v>
+      </c>
+      <c r="C55" s="9">
+        <v>3</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>67</v>
       </c>
       <c r="E55" s="10">
-        <v>200300001</v>
+        <v>300200006</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="G55" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="H55" s="13">
-        <v>12</v>
-      </c>
-      <c r="I55" s="13">
-        <v>0</v>
-      </c>
-      <c r="J55" s="13">
+        <v>68</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H55" s="1">
+        <v>3</v>
+      </c>
+      <c r="I55" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="J55" s="1">
         <v>-1</v>
       </c>
       <c r="K55" s="1">
         <v>0</v>
       </c>
-      <c r="L55" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="M55" s="13">
-        <v>0</v>
+      <c r="L55" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="M55" s="17" t="s">
+        <v>66</v>
       </c>
       <c r="N55">
-        <v>100</v>
+        <v>2000000</v>
       </c>
       <c r="O55"/>
       <c r="S55" s="2"/>
     </row>
     <row r="56" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A56" s="1">
-        <f t="shared" si="6"/>
-        <v>20040010</v>
+        <f t="shared" ref="A56:A62" si="6">B56*100+H56</f>
+        <v>20010010</v>
       </c>
       <c r="B56" s="10">
-        <v>200400</v>
+        <v>200100</v>
       </c>
       <c r="C56" s="10">
         <v>2</v>
       </c>
-      <c r="D56" s="11" t="s">
+      <c r="D56" s="10" t="s">
         <v>43</v>
       </c>
       <c r="E56" s="10">
-        <v>200400009</v>
+        <v>200100038</v>
       </c>
       <c r="F56" s="10" t="s">
         <v>44</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="H56" s="13">
         <v>10</v>
@@ -4030,7 +4045,7 @@
         <v>0</v>
       </c>
       <c r="L56" s="13" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M56" s="13">
         <v>0</v>
@@ -4044,25 +4059,25 @@
     <row r="57" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A57" s="1">
         <f t="shared" si="6"/>
-        <v>20040011</v>
+        <v>20010011</v>
       </c>
       <c r="B57" s="10">
-        <v>200400</v>
+        <v>200100</v>
       </c>
       <c r="C57" s="10">
         <v>2</v>
       </c>
-      <c r="D57" s="11" t="s">
+      <c r="D57" s="10" t="s">
         <v>43</v>
       </c>
       <c r="E57" s="10">
-        <v>200400009</v>
+        <v>200100038</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>44</v>
       </c>
       <c r="G57" s="13" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H57" s="13">
         <v>11</v>
@@ -4077,7 +4092,7 @@
         <v>0</v>
       </c>
       <c r="L57" s="13" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M57" s="13">
         <v>0</v>
@@ -4091,25 +4106,25 @@
     <row r="58" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A58" s="1">
         <f t="shared" si="6"/>
-        <v>20040012</v>
+        <v>20010012</v>
       </c>
       <c r="B58" s="10">
-        <v>200400</v>
+        <v>200100</v>
       </c>
       <c r="C58" s="10">
         <v>2</v>
       </c>
-      <c r="D58" s="11" t="s">
+      <c r="D58" s="10" t="s">
         <v>43</v>
       </c>
       <c r="E58" s="10">
-        <v>200400009</v>
+        <v>200100038</v>
       </c>
       <c r="F58" s="10" t="s">
         <v>44</v>
       </c>
       <c r="G58" s="13" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H58" s="13">
         <v>12</v>
@@ -4124,7 +4139,7 @@
         <v>0</v>
       </c>
       <c r="L58" s="13" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M58" s="13">
         <v>0</v>
@@ -4138,10 +4153,10 @@
     <row r="59" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A59" s="1">
         <f t="shared" si="6"/>
-        <v>20050010</v>
+        <v>20010110</v>
       </c>
       <c r="B59" s="10">
-        <v>200500</v>
+        <v>200101</v>
       </c>
       <c r="C59" s="10">
         <v>2</v>
@@ -4150,13 +4165,13 @@
         <v>45</v>
       </c>
       <c r="E59" s="10">
-        <v>200500025</v>
+        <v>200101001</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>46</v>
       </c>
       <c r="G59" s="13" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="H59" s="13">
         <v>10</v>
@@ -4171,7 +4186,7 @@
         <v>0</v>
       </c>
       <c r="L59" s="13" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M59" s="13">
         <v>0</v>
@@ -4185,10 +4200,10 @@
     <row r="60" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A60" s="1">
         <f t="shared" si="6"/>
-        <v>20050011</v>
+        <v>20010111</v>
       </c>
       <c r="B60" s="10">
-        <v>200500</v>
+        <v>200101</v>
       </c>
       <c r="C60" s="10">
         <v>2</v>
@@ -4197,13 +4212,13 @@
         <v>45</v>
       </c>
       <c r="E60" s="10">
-        <v>200500025</v>
+        <v>200101001</v>
       </c>
       <c r="F60" s="10" t="s">
         <v>46</v>
       </c>
       <c r="G60" s="13" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H60" s="13">
         <v>11</v>
@@ -4218,7 +4233,7 @@
         <v>0</v>
       </c>
       <c r="L60" s="13" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M60" s="13">
         <v>0</v>
@@ -4232,10 +4247,10 @@
     <row r="61" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A61" s="1">
         <f t="shared" si="6"/>
-        <v>20050012</v>
+        <v>20010112</v>
       </c>
       <c r="B61" s="10">
-        <v>200500</v>
+        <v>200101</v>
       </c>
       <c r="C61" s="10">
         <v>2</v>
@@ -4244,13 +4259,13 @@
         <v>45</v>
       </c>
       <c r="E61" s="10">
-        <v>200500025</v>
+        <v>200101001</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>46</v>
       </c>
       <c r="G61" s="13" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H61" s="13">
         <v>12</v>
@@ -4265,7 +4280,7 @@
         <v>0</v>
       </c>
       <c r="L61" s="13" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M61" s="13">
         <v>0</v>
@@ -4276,28 +4291,28 @@
       <c r="O61"/>
       <c r="S61" s="2"/>
     </row>
-    <row r="62" ht="16.5" spans="1:14">
+    <row r="62" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A62" s="1">
         <f t="shared" si="6"/>
-        <v>20060010</v>
+        <v>20030010</v>
       </c>
       <c r="B62" s="10">
-        <v>200600</v>
+        <v>200300</v>
       </c>
       <c r="C62" s="10">
         <v>2</v>
       </c>
       <c r="D62" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E62" s="10">
+        <v>200300001</v>
+      </c>
+      <c r="F62" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E62" s="10">
-        <v>200600001</v>
-      </c>
-      <c r="F62" s="10" t="s">
-        <v>49</v>
-      </c>
       <c r="G62" s="13" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="H62" s="13">
         <v>10</v>
@@ -4312,7 +4327,7 @@
         <v>0</v>
       </c>
       <c r="L62" s="13" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M62" s="13">
         <v>0</v>
@@ -4320,29 +4335,31 @@
       <c r="N62">
         <v>100</v>
       </c>
-    </row>
-    <row r="63" ht="16.5" spans="1:14">
+      <c r="O62"/>
+      <c r="S62" s="2"/>
+    </row>
+    <row r="63" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A63" s="1">
-        <f t="shared" ref="A63:A73" si="7">B63*100+H63</f>
-        <v>20060011</v>
+        <f t="shared" ref="A63:A71" si="7">B63*100+H63</f>
+        <v>20030011</v>
       </c>
       <c r="B63" s="10">
-        <v>200600</v>
+        <v>200300</v>
       </c>
       <c r="C63" s="10">
         <v>2</v>
       </c>
       <c r="D63" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E63" s="10">
+        <v>200300001</v>
+      </c>
+      <c r="F63" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E63" s="10">
-        <v>200600001</v>
-      </c>
-      <c r="F63" s="10" t="s">
-        <v>49</v>
-      </c>
       <c r="G63" s="13" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H63" s="13">
         <v>11</v>
@@ -4357,7 +4374,7 @@
         <v>0</v>
       </c>
       <c r="L63" s="13" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M63" s="13">
         <v>0</v>
@@ -4365,29 +4382,31 @@
       <c r="N63">
         <v>100</v>
       </c>
-    </row>
-    <row r="64" ht="16.5" spans="1:14">
+      <c r="O63"/>
+      <c r="S63" s="2"/>
+    </row>
+    <row r="64" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A64" s="1">
         <f t="shared" si="7"/>
-        <v>20060012</v>
+        <v>20030012</v>
       </c>
       <c r="B64" s="10">
-        <v>200600</v>
+        <v>200300</v>
       </c>
       <c r="C64" s="10">
         <v>2</v>
       </c>
       <c r="D64" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E64" s="10">
+        <v>200300001</v>
+      </c>
+      <c r="F64" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E64" s="10">
-        <v>200600001</v>
-      </c>
-      <c r="F64" s="10" t="s">
-        <v>49</v>
-      </c>
       <c r="G64" s="13" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H64" s="13">
         <v>12</v>
@@ -4402,7 +4421,7 @@
         <v>0</v>
       </c>
       <c r="L64" s="13" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M64" s="13">
         <v>0</v>
@@ -4410,29 +4429,31 @@
       <c r="N64">
         <v>100</v>
       </c>
-    </row>
-    <row r="65" ht="16.5" spans="1:14">
+      <c r="O64"/>
+      <c r="S64" s="2"/>
+    </row>
+    <row r="65" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A65" s="1">
         <f t="shared" si="7"/>
-        <v>20070010</v>
+        <v>20040010</v>
       </c>
       <c r="B65" s="10">
-        <v>200700</v>
+        <v>200400</v>
       </c>
       <c r="C65" s="10">
         <v>2</v>
       </c>
-      <c r="D65" s="9" t="s">
+      <c r="D65" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E65" s="10">
+        <v>200400009</v>
+      </c>
+      <c r="F65" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E65" s="10">
-        <v>200700001</v>
-      </c>
-      <c r="F65" s="10" t="s">
-        <v>51</v>
-      </c>
       <c r="G65" s="13" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="H65" s="13">
         <v>10</v>
@@ -4447,7 +4468,7 @@
         <v>0</v>
       </c>
       <c r="L65" s="13" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M65" s="13">
         <v>0</v>
@@ -4455,30 +4476,31 @@
       <c r="N65">
         <v>100</v>
       </c>
-    </row>
-    <row r="66" ht="16.5" spans="1:14">
+      <c r="O65"/>
+      <c r="S65" s="2"/>
+    </row>
+    <row r="66" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A66" s="1">
         <f t="shared" si="7"/>
-        <v>20070011</v>
+        <v>20040011</v>
       </c>
       <c r="B66" s="10">
-        <v>200700</v>
+        <v>200400</v>
       </c>
       <c r="C66" s="10">
         <v>2</v>
       </c>
-      <c r="D66" s="9" t="str">
-        <f>D65</f>
-        <v>越南色碟</v>
+      <c r="D66" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="E66" s="10">
-        <v>200700001</v>
+        <v>200400009</v>
       </c>
       <c r="F66" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G66" s="13" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H66" s="13">
         <v>11</v>
@@ -4493,7 +4515,7 @@
         <v>0</v>
       </c>
       <c r="L66" s="13" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M66" s="13">
         <v>0</v>
@@ -4501,30 +4523,31 @@
       <c r="N66">
         <v>100</v>
       </c>
-    </row>
-    <row r="67" ht="16.5" spans="1:14">
+      <c r="O66"/>
+      <c r="S66" s="2"/>
+    </row>
+    <row r="67" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A67" s="1">
         <f t="shared" si="7"/>
-        <v>20070012</v>
+        <v>20040012</v>
       </c>
       <c r="B67" s="10">
-        <v>200700</v>
+        <v>200400</v>
       </c>
       <c r="C67" s="10">
         <v>2</v>
       </c>
-      <c r="D67" s="9" t="str">
-        <f>D66</f>
-        <v>越南色碟</v>
+      <c r="D67" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="E67" s="10">
-        <v>200700001</v>
+        <v>200400009</v>
       </c>
       <c r="F67" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G67" s="13" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H67" s="13">
         <v>12</v>
@@ -4539,7 +4562,7 @@
         <v>0</v>
       </c>
       <c r="L67" s="13" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M67" s="13">
         <v>0</v>
@@ -4547,29 +4570,31 @@
       <c r="N67">
         <v>100</v>
       </c>
-    </row>
-    <row r="68" ht="16.5" spans="1:14">
+      <c r="O67"/>
+      <c r="S67" s="2"/>
+    </row>
+    <row r="68" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A68" s="1">
         <f t="shared" si="7"/>
-        <v>20080010</v>
+        <v>20050010</v>
       </c>
       <c r="B68" s="10">
-        <v>200800</v>
+        <v>200500</v>
       </c>
       <c r="C68" s="10">
         <v>2</v>
       </c>
       <c r="D68" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E68" s="10">
+        <v>200500025</v>
+      </c>
+      <c r="F68" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="E68" s="10">
-        <v>200800001</v>
-      </c>
-      <c r="F68" s="10" t="s">
-        <v>53</v>
-      </c>
       <c r="G68" s="13" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="H68" s="13">
         <v>10</v>
@@ -4584,7 +4609,7 @@
         <v>0</v>
       </c>
       <c r="L68" s="13" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M68" s="13">
         <v>0</v>
@@ -4592,29 +4617,31 @@
       <c r="N68">
         <v>100</v>
       </c>
-    </row>
-    <row r="69" ht="16.5" spans="1:14">
+      <c r="O68"/>
+      <c r="S68" s="2"/>
+    </row>
+    <row r="69" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A69" s="1">
         <f t="shared" si="7"/>
-        <v>20080011</v>
+        <v>20050011</v>
       </c>
       <c r="B69" s="10">
-        <v>200800</v>
+        <v>200500</v>
       </c>
       <c r="C69" s="10">
         <v>2</v>
       </c>
       <c r="D69" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E69" s="10">
+        <v>200500025</v>
+      </c>
+      <c r="F69" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="E69" s="10">
-        <v>200800001</v>
-      </c>
-      <c r="F69" s="10" t="s">
-        <v>53</v>
-      </c>
       <c r="G69" s="13" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H69" s="13">
         <v>11</v>
@@ -4629,7 +4656,7 @@
         <v>0</v>
       </c>
       <c r="L69" s="13" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M69" s="13">
         <v>0</v>
@@ -4637,29 +4664,31 @@
       <c r="N69">
         <v>100</v>
       </c>
-    </row>
-    <row r="70" ht="16.5" spans="1:14">
+      <c r="O69"/>
+      <c r="S69" s="2"/>
+    </row>
+    <row r="70" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A70" s="1">
         <f t="shared" si="7"/>
-        <v>20080012</v>
+        <v>20050012</v>
       </c>
       <c r="B70" s="10">
-        <v>200800</v>
+        <v>200500</v>
       </c>
       <c r="C70" s="10">
         <v>2</v>
       </c>
       <c r="D70" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E70" s="10">
+        <v>200500025</v>
+      </c>
+      <c r="F70" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="E70" s="10">
-        <v>200800001</v>
-      </c>
-      <c r="F70" s="10" t="s">
-        <v>53</v>
-      </c>
       <c r="G70" s="13" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H70" s="13">
         <v>12</v>
@@ -4674,7 +4703,7 @@
         <v>0</v>
       </c>
       <c r="L70" s="13" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M70" s="13">
         <v>0</v>
@@ -4682,14 +4711,16 @@
       <c r="N70">
         <v>100</v>
       </c>
+      <c r="O70"/>
+      <c r="S70" s="2"/>
     </row>
     <row r="71" ht="16.5" spans="1:14">
       <c r="A71" s="1">
         <f t="shared" si="7"/>
-        <v>20090010</v>
+        <v>20060010</v>
       </c>
       <c r="B71" s="10">
-        <v>200900</v>
+        <v>200600</v>
       </c>
       <c r="C71" s="10">
         <v>2</v>
@@ -4698,13 +4729,13 @@
         <v>54</v>
       </c>
       <c r="E71" s="10">
-        <v>200900001</v>
+        <v>200600001</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>55</v>
       </c>
       <c r="G71" s="13" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="H71" s="13">
         <v>10</v>
@@ -4719,7 +4750,7 @@
         <v>0</v>
       </c>
       <c r="L71" s="13" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M71" s="13">
         <v>0</v>
@@ -4730,11 +4761,11 @@
     </row>
     <row r="72" ht="16.5" spans="1:14">
       <c r="A72" s="1">
-        <f t="shared" si="7"/>
-        <v>20090011</v>
+        <f t="shared" ref="A72:A82" si="8">B72*100+H72</f>
+        <v>20060011</v>
       </c>
       <c r="B72" s="10">
-        <v>200900</v>
+        <v>200600</v>
       </c>
       <c r="C72" s="10">
         <v>2</v>
@@ -4743,13 +4774,13 @@
         <v>54</v>
       </c>
       <c r="E72" s="10">
-        <v>200900001</v>
+        <v>200600001</v>
       </c>
       <c r="F72" s="10" t="s">
         <v>55</v>
       </c>
       <c r="G72" s="13" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H72" s="13">
         <v>11</v>
@@ -4764,7 +4795,7 @@
         <v>0</v>
       </c>
       <c r="L72" s="13" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M72" s="13">
         <v>0</v>
@@ -4775,11 +4806,11 @@
     </row>
     <row r="73" ht="16.5" spans="1:14">
       <c r="A73" s="1">
-        <f t="shared" si="7"/>
-        <v>20090012</v>
+        <f t="shared" si="8"/>
+        <v>20060012</v>
       </c>
       <c r="B73" s="10">
-        <v>200900</v>
+        <v>200600</v>
       </c>
       <c r="C73" s="10">
         <v>2</v>
@@ -4788,13 +4819,13 @@
         <v>54</v>
       </c>
       <c r="E73" s="10">
-        <v>200900001</v>
+        <v>200600001</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>55</v>
       </c>
       <c r="G73" s="13" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H73" s="13">
         <v>12</v>
@@ -4809,7 +4840,7 @@
         <v>0</v>
       </c>
       <c r="L73" s="13" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M73" s="13">
         <v>0</v>
@@ -4817,6 +4848,554 @@
       <c r="N73">
         <v>100</v>
       </c>
+    </row>
+    <row r="74" ht="16.5" spans="1:14">
+      <c r="A74" s="1">
+        <f t="shared" si="8"/>
+        <v>20070010</v>
+      </c>
+      <c r="B74" s="10">
+        <v>200700</v>
+      </c>
+      <c r="C74" s="10">
+        <v>2</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E74" s="10">
+        <v>200700001</v>
+      </c>
+      <c r="F74" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G74" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="H74" s="13">
+        <v>10</v>
+      </c>
+      <c r="I74" s="13">
+        <v>0</v>
+      </c>
+      <c r="J74" s="13">
+        <v>-1</v>
+      </c>
+      <c r="K74" s="1">
+        <v>0</v>
+      </c>
+      <c r="L74" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="M74" s="13">
+        <v>0</v>
+      </c>
+      <c r="N74">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="75" ht="16.5" spans="1:14">
+      <c r="A75" s="1">
+        <f t="shared" si="8"/>
+        <v>20070011</v>
+      </c>
+      <c r="B75" s="10">
+        <v>200700</v>
+      </c>
+      <c r="C75" s="10">
+        <v>2</v>
+      </c>
+      <c r="D75" s="9" t="str">
+        <f>D74</f>
+        <v>越南色碟</v>
+      </c>
+      <c r="E75" s="10">
+        <v>200700001</v>
+      </c>
+      <c r="F75" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G75" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="H75" s="13">
+        <v>11</v>
+      </c>
+      <c r="I75" s="13">
+        <v>0</v>
+      </c>
+      <c r="J75" s="13">
+        <v>-1</v>
+      </c>
+      <c r="K75" s="1">
+        <v>0</v>
+      </c>
+      <c r="L75" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="M75" s="13">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="76" ht="16.5" spans="1:14">
+      <c r="A76" s="1">
+        <f t="shared" si="8"/>
+        <v>20070012</v>
+      </c>
+      <c r="B76" s="10">
+        <v>200700</v>
+      </c>
+      <c r="C76" s="10">
+        <v>2</v>
+      </c>
+      <c r="D76" s="9" t="str">
+        <f>D75</f>
+        <v>越南色碟</v>
+      </c>
+      <c r="E76" s="10">
+        <v>200700001</v>
+      </c>
+      <c r="F76" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G76" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="H76" s="13">
+        <v>12</v>
+      </c>
+      <c r="I76" s="13">
+        <v>0</v>
+      </c>
+      <c r="J76" s="13">
+        <v>-1</v>
+      </c>
+      <c r="K76" s="1">
+        <v>0</v>
+      </c>
+      <c r="L76" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="M76" s="13">
+        <v>0</v>
+      </c>
+      <c r="N76">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="77" ht="16.5" spans="1:14">
+      <c r="A77" s="1">
+        <f t="shared" si="8"/>
+        <v>20080010</v>
+      </c>
+      <c r="B77" s="10">
+        <v>200800</v>
+      </c>
+      <c r="C77" s="10">
+        <v>2</v>
+      </c>
+      <c r="D77" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E77" s="10">
+        <v>200800001</v>
+      </c>
+      <c r="F77" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G77" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="H77" s="13">
+        <v>10</v>
+      </c>
+      <c r="I77" s="13">
+        <v>0</v>
+      </c>
+      <c r="J77" s="13">
+        <v>-1</v>
+      </c>
+      <c r="K77" s="1">
+        <v>0</v>
+      </c>
+      <c r="L77" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="M77" s="13">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="78" ht="16.5" spans="1:14">
+      <c r="A78" s="1">
+        <f t="shared" si="8"/>
+        <v>20080011</v>
+      </c>
+      <c r="B78" s="10">
+        <v>200800</v>
+      </c>
+      <c r="C78" s="10">
+        <v>2</v>
+      </c>
+      <c r="D78" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E78" s="10">
+        <v>200800001</v>
+      </c>
+      <c r="F78" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G78" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="H78" s="13">
+        <v>11</v>
+      </c>
+      <c r="I78" s="13">
+        <v>0</v>
+      </c>
+      <c r="J78" s="13">
+        <v>-1</v>
+      </c>
+      <c r="K78" s="1">
+        <v>0</v>
+      </c>
+      <c r="L78" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="M78" s="13">
+        <v>0</v>
+      </c>
+      <c r="N78">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="79" ht="16.5" spans="1:14">
+      <c r="A79" s="1">
+        <f t="shared" si="8"/>
+        <v>20080012</v>
+      </c>
+      <c r="B79" s="10">
+        <v>200800</v>
+      </c>
+      <c r="C79" s="10">
+        <v>2</v>
+      </c>
+      <c r="D79" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E79" s="10">
+        <v>200800001</v>
+      </c>
+      <c r="F79" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G79" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="H79" s="13">
+        <v>12</v>
+      </c>
+      <c r="I79" s="13">
+        <v>0</v>
+      </c>
+      <c r="J79" s="13">
+        <v>-1</v>
+      </c>
+      <c r="K79" s="1">
+        <v>0</v>
+      </c>
+      <c r="L79" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="M79" s="13">
+        <v>0</v>
+      </c>
+      <c r="N79">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="80" ht="16.5" spans="1:14">
+      <c r="A80" s="1">
+        <f t="shared" si="8"/>
+        <v>20090010</v>
+      </c>
+      <c r="B80" s="10">
+        <v>200900</v>
+      </c>
+      <c r="C80" s="10">
+        <v>2</v>
+      </c>
+      <c r="D80" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="E80" s="10">
+        <v>200900001</v>
+      </c>
+      <c r="F80" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="G80" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="H80" s="13">
+        <v>10</v>
+      </c>
+      <c r="I80" s="13">
+        <v>0</v>
+      </c>
+      <c r="J80" s="13">
+        <v>-1</v>
+      </c>
+      <c r="K80" s="1">
+        <v>0</v>
+      </c>
+      <c r="L80" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="M80" s="13">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81" ht="16.5" spans="1:14">
+      <c r="A81" s="1">
+        <f t="shared" si="8"/>
+        <v>20090011</v>
+      </c>
+      <c r="B81" s="10">
+        <v>200900</v>
+      </c>
+      <c r="C81" s="10">
+        <v>2</v>
+      </c>
+      <c r="D81" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="E81" s="10">
+        <v>200900001</v>
+      </c>
+      <c r="F81" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="G81" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="H81" s="13">
+        <v>11</v>
+      </c>
+      <c r="I81" s="13">
+        <v>0</v>
+      </c>
+      <c r="J81" s="13">
+        <v>-1</v>
+      </c>
+      <c r="K81" s="1">
+        <v>0</v>
+      </c>
+      <c r="L81" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="M81" s="13">
+        <v>0</v>
+      </c>
+      <c r="N81">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82" ht="16.5" spans="1:14">
+      <c r="A82" s="1">
+        <f t="shared" si="8"/>
+        <v>20090012</v>
+      </c>
+      <c r="B82" s="10">
+        <v>200900</v>
+      </c>
+      <c r="C82" s="10">
+        <v>2</v>
+      </c>
+      <c r="D82" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="E82" s="10">
+        <v>200900001</v>
+      </c>
+      <c r="F82" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="G82" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="H82" s="13">
+        <v>12</v>
+      </c>
+      <c r="I82" s="13">
+        <v>0</v>
+      </c>
+      <c r="J82" s="13">
+        <v>-1</v>
+      </c>
+      <c r="K82" s="1">
+        <v>0</v>
+      </c>
+      <c r="L82" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="M82" s="13">
+        <v>0</v>
+      </c>
+      <c r="N82">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="83" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A83" s="1">
+        <f t="shared" ref="A83:A85" si="9">B83*10+H83</f>
+        <v>3002010</v>
+      </c>
+      <c r="B83" s="9">
+        <v>300200</v>
+      </c>
+      <c r="C83" s="9">
+        <v>3</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E83" s="10">
+        <v>300200006</v>
+      </c>
+      <c r="F83" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="G83" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="H83" s="13">
+        <v>10</v>
+      </c>
+      <c r="I83" s="13">
+        <v>0</v>
+      </c>
+      <c r="J83" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K83" s="1">
+        <v>0</v>
+      </c>
+      <c r="L83" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="M83" s="13">
+        <v>0</v>
+      </c>
+      <c r="N83">
+        <v>500</v>
+      </c>
+      <c r="O83"/>
+      <c r="S83" s="2"/>
+    </row>
+    <row r="84" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A84" s="1">
+        <f t="shared" si="9"/>
+        <v>3002011</v>
+      </c>
+      <c r="B84" s="9">
+        <v>300200</v>
+      </c>
+      <c r="C84" s="9">
+        <v>3</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E84" s="10">
+        <v>300200006</v>
+      </c>
+      <c r="F84" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="G84" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="H84" s="13">
+        <v>11</v>
+      </c>
+      <c r="I84" s="13">
+        <v>0</v>
+      </c>
+      <c r="J84" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K84" s="1">
+        <v>0</v>
+      </c>
+      <c r="L84" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="M84" s="13">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <v>20000</v>
+      </c>
+      <c r="O84"/>
+      <c r="S84" s="2"/>
+    </row>
+    <row r="85" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A85" s="1">
+        <f t="shared" si="9"/>
+        <v>3002012</v>
+      </c>
+      <c r="B85" s="9">
+        <v>300200</v>
+      </c>
+      <c r="C85" s="9">
+        <v>3</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E85" s="10">
+        <v>300200006</v>
+      </c>
+      <c r="F85" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="G85" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="H85" s="13">
+        <v>12</v>
+      </c>
+      <c r="I85" s="13">
+        <v>0</v>
+      </c>
+      <c r="J85" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K85" s="1">
+        <v>0</v>
+      </c>
+      <c r="L85" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="M85" s="13">
+        <v>0</v>
+      </c>
+      <c r="N85">
+        <v>2000000</v>
+      </c>
+      <c r="O85"/>
+      <c r="S85" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -1902,7 +1902,7 @@
     <row r="11" ht="16.5" spans="1:14">
       <c r="A11" s="1">
         <f t="shared" ref="A11:A22" si="2">B11*10+H11</f>
-        <v>1007004</v>
+        <v>1007001</v>
       </c>
       <c r="B11" s="9">
         <v>100700</v>
@@ -1923,7 +1923,7 @@
         <v>30</v>
       </c>
       <c r="H11" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I11" s="1">
         <v>0</v>
@@ -1947,7 +1947,7 @@
     <row r="12" ht="16.5" spans="1:14">
       <c r="A12" s="1">
         <f t="shared" si="2"/>
-        <v>1007005</v>
+        <v>1007002</v>
       </c>
       <c r="B12" s="9">
         <v>100700</v>
@@ -1970,7 +1970,7 @@
         <v>33</v>
       </c>
       <c r="H12" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I12" s="1">
         <v>50</v>
@@ -1994,7 +1994,7 @@
     <row r="13" ht="16.5" spans="1:14">
       <c r="A13" s="1">
         <f t="shared" si="2"/>
-        <v>1007006</v>
+        <v>1007003</v>
       </c>
       <c r="B13" s="9">
         <v>100700</v>
@@ -2017,7 +2017,7 @@
         <v>34</v>
       </c>
       <c r="H13" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I13" s="1">
         <v>100</v>
@@ -2041,7 +2041,7 @@
     <row r="14" ht="16.5" spans="1:14">
       <c r="A14" s="1">
         <f t="shared" si="2"/>
-        <v>1012007</v>
+        <v>1012001</v>
       </c>
       <c r="B14" s="9">
         <v>101200</v>
@@ -2062,7 +2062,7 @@
         <v>30</v>
       </c>
       <c r="H14" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I14" s="1">
         <v>0</v>
@@ -2086,7 +2086,7 @@
     <row r="15" ht="16.5" spans="1:14">
       <c r="A15" s="1">
         <f t="shared" si="2"/>
-        <v>1012008</v>
+        <v>1012002</v>
       </c>
       <c r="B15" s="9">
         <v>101200</v>
@@ -2109,7 +2109,7 @@
         <v>33</v>
       </c>
       <c r="H15" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I15" s="1">
         <v>50</v>
@@ -2133,7 +2133,7 @@
     <row r="16" ht="16.5" spans="1:14">
       <c r="A16" s="1">
         <f t="shared" si="2"/>
-        <v>1012009</v>
+        <v>1012003</v>
       </c>
       <c r="B16" s="9">
         <v>101200</v>
@@ -2156,7 +2156,7 @@
         <v>34</v>
       </c>
       <c r="H16" s="1">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I16" s="1">
         <v>100</v>
@@ -2180,7 +2180,7 @@
     <row r="17" ht="16.5" spans="1:14">
       <c r="A17" s="1">
         <f t="shared" si="2"/>
-        <v>1014010</v>
+        <v>1014001</v>
       </c>
       <c r="B17" s="9">
         <v>101400</v>
@@ -2201,7 +2201,7 @@
         <v>30</v>
       </c>
       <c r="H17" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I17" s="1">
         <v>0</v>
@@ -2225,7 +2225,7 @@
     <row r="18" ht="16.5" spans="1:14">
       <c r="A18" s="1">
         <f t="shared" si="2"/>
-        <v>1014011</v>
+        <v>1014002</v>
       </c>
       <c r="B18" s="9">
         <v>101400</v>
@@ -2248,7 +2248,7 @@
         <v>33</v>
       </c>
       <c r="H18" s="1">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I18" s="1">
         <v>50</v>
@@ -2272,7 +2272,7 @@
     <row r="19" ht="16.5" spans="1:14">
       <c r="A19" s="1">
         <f t="shared" si="2"/>
-        <v>1014012</v>
+        <v>1014003</v>
       </c>
       <c r="B19" s="9">
         <v>101400</v>
@@ -2295,7 +2295,7 @@
         <v>34</v>
       </c>
       <c r="H19" s="1">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="I19" s="1">
         <v>100</v>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -5213,7 +5213,7 @@
     </row>
     <row r="82" ht="16.5" spans="1:14">
       <c r="A82" s="1">
-        <f t="shared" si="8"/>
+        <f>B82*100+H82</f>
         <v>20090012</v>
       </c>
       <c r="B82" s="10">
@@ -5258,8 +5258,8 @@
     </row>
     <row r="83" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A83" s="1">
-        <f t="shared" ref="A83:A85" si="9">B83*10+H83</f>
-        <v>3002010</v>
+        <f>B83*100+H83</f>
+        <v>30020010</v>
       </c>
       <c r="B83" s="9">
         <v>300200</v>
@@ -5305,8 +5305,8 @@
     </row>
     <row r="84" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A84" s="1">
-        <f t="shared" si="9"/>
-        <v>3002011</v>
+        <f>B84*100+H84</f>
+        <v>30020011</v>
       </c>
       <c r="B84" s="9">
         <v>300200</v>
@@ -5352,8 +5352,8 @@
     </row>
     <row r="85" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A85" s="1">
-        <f t="shared" si="9"/>
-        <v>3002012</v>
+        <f>B85*100+H85</f>
+        <v>30020012</v>
       </c>
       <c r="B85" s="9">
         <v>300200</v>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -155,7 +155,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="77">
   <si>
     <t>sid</t>
   </si>
@@ -193,6 +193,9 @@
     <t>倍场显示默认押注</t>
   </si>
   <si>
+    <t>交易项目ID</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -236,6 +239,9 @@
   </si>
   <si>
     <t>betShow</t>
+  </si>
+  <si>
+    <t>transactionItemId</t>
   </si>
   <si>
     <t>client</t>
@@ -392,13 +398,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -415,18 +427,18 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -597,7 +609,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -613,6 +625,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799340800195319"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799340800195319"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -942,185 +972,188 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -1135,8 +1168,20 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1475,7 +1520,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:S85"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="3" width="9.375" style="1"/>
     <col min="4" max="4" width="10.875" style="1" customWidth="1"/>
@@ -1488,16 +1533,16 @@
     <col min="12" max="12" width="17.05" style="1" customWidth="1"/>
     <col min="13" max="13" width="13.9666666666667" style="1" customWidth="1"/>
     <col min="14" max="14" width="13.675" customWidth="1"/>
-    <col min="15" max="15" width="8.96666666666667" customWidth="1"/>
+    <col min="15" max="15" width="21.025" style="2" customWidth="1"/>
     <col min="16" max="16" width="9" style="1"/>
     <col min="17" max="17" width="27.875" style="1" customWidth="1"/>
     <col min="18" max="18" width="9" style="1"/>
-    <col min="19" max="19" width="17.375" style="2" customWidth="1"/>
+    <col min="19" max="19" width="17.375" style="3" customWidth="1"/>
     <col min="20" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:14">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:15">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -1521,13 +1566,13 @@
       <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="15" t="s">
         <v>8</v>
       </c>
       <c r="L1" s="1" t="s">
@@ -1539,112 +1584,124 @@
       <c r="N1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:14">
-      <c r="A2" s="4" t="s">
+      <c r="O1" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="7" t="s">
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>12</v>
+      <c r="B2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="6"/>
+      <c r="E2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="6"/>
+      <c r="H2" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="L2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:14">
-      <c r="A3" s="3" t="s">
-        <v>15</v>
+      <c r="O2" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="H3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="I3" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="J3" s="9" t="s">
         <v>23</v>
       </c>
+      <c r="K3" s="9" t="s">
+        <v>24</v>
+      </c>
       <c r="L3" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3" s="8" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="4" spans="6:6">
+      <c r="N3" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25" spans="6:15">
       <c r="F4" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" ht="16.5" spans="1:14">
+        <v>29</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="1">
         <f t="shared" ref="A5:A10" si="0">B5*10+H5</f>
         <v>1001001</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="10">
         <v>100100</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="10">
         <v>1</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="10">
+      <c r="D5" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="11">
         <v>100100026</v>
       </c>
-      <c r="F5" s="10" t="s">
-        <v>29</v>
+      <c r="F5" s="11" t="s">
+        <v>31</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H5" s="1">
         <v>1</v>
@@ -1659,38 +1716,41 @@
         <v>0</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M5" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M5" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N5">
         <v>1000</v>
       </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:14">
+      <c r="O5" s="18">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>1001002</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="10">
         <v>100100</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="10">
         <v>1</v>
       </c>
-      <c r="D6" s="9" t="str">
+      <c r="D6" s="10" t="str">
         <f t="shared" ref="D6:D10" si="1">D5</f>
         <v>金礦大亨</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="11">
         <v>100100026</v>
       </c>
-      <c r="F6" s="10" t="s">
-        <v>29</v>
+      <c r="F6" s="11" t="s">
+        <v>31</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H6" s="1">
         <v>2</v>
@@ -1705,38 +1765,41 @@
         <v>0</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M6" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M6" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N6">
         <v>100000</v>
       </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:14">
+      <c r="O6" s="18">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>1001003</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="10">
         <v>100100</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="10">
         <v>1</v>
       </c>
-      <c r="D7" s="9" t="str">
+      <c r="D7" s="10" t="str">
         <f t="shared" si="1"/>
         <v>金礦大亨</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="11">
         <v>100100026</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>29</v>
+      <c r="F7" s="11" t="s">
+        <v>31</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H7" s="1">
         <v>3</v>
@@ -1751,37 +1814,40 @@
         <v>0</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M7" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M7" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N7">
         <v>10000000</v>
       </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:14">
+      <c r="O7" s="18">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>1003001</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="10">
         <v>100300</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="10">
         <v>1</v>
       </c>
-      <c r="D8" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="10">
+      <c r="D8" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="11">
         <v>100300001</v>
       </c>
-      <c r="F8" s="10" t="s">
-        <v>36</v>
+      <c r="F8" s="11" t="s">
+        <v>38</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H8" s="1">
         <v>1</v>
@@ -1796,39 +1862,42 @@
         <v>0</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M8" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M8" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N8">
         <v>1000</v>
       </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:14">
+      <c r="O8" s="18">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>1003002</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="10">
         <v>100300</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="10">
         <v>1</v>
       </c>
-      <c r="D9" s="9" t="str">
+      <c r="D9" s="10" t="str">
         <f t="shared" si="1"/>
         <v>超级明星</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="11">
         <v>100300001</v>
       </c>
-      <c r="F9" s="10" t="str">
+      <c r="F9" s="11" t="str">
         <f>F8</f>
         <v>SuperStar</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H9" s="1">
         <v>2</v>
@@ -1843,39 +1912,42 @@
         <v>0</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M9" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M9" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N9">
         <v>100000</v>
       </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:14">
+      <c r="O9" s="18">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>1003003</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="10">
         <v>100300</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="10">
         <v>1</v>
       </c>
-      <c r="D10" s="9" t="str">
+      <c r="D10" s="10" t="str">
         <f t="shared" si="1"/>
         <v>超级明星</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="11">
         <v>100300001</v>
       </c>
-      <c r="F10" s="10" t="str">
+      <c r="F10" s="11" t="str">
         <f>F9</f>
         <v>SuperStar</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H10" s="1">
         <v>3</v>
@@ -1890,37 +1962,40 @@
         <v>0</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M10" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M10" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N10">
         <v>10000000</v>
       </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:14">
+      <c r="O10" s="18">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="1">
         <f t="shared" ref="A11:A22" si="2">B11*10+H11</f>
         <v>1007001</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="10">
         <v>100700</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="10">
         <v>1</v>
       </c>
-      <c r="D11" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" s="10">
+      <c r="D11" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="11">
         <v>100700001</v>
       </c>
-      <c r="F11" s="10" t="s">
-        <v>38</v>
+      <c r="F11" s="11" t="s">
+        <v>40</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H11" s="1">
         <v>1</v>
@@ -1935,39 +2010,42 @@
         <v>0</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M11" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M11" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N11">
         <v>1000</v>
       </c>
-    </row>
-    <row r="12" ht="16.5" spans="1:14">
+      <c r="O11" s="18">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="1">
         <f t="shared" si="2"/>
         <v>1007002</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="10">
         <v>100700</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="10">
         <v>1</v>
       </c>
-      <c r="D12" s="9" t="str">
+      <c r="D12" s="10" t="str">
         <f>D11</f>
         <v>麻将胡了</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="11">
         <v>100700001</v>
       </c>
-      <c r="F12" s="10" t="str">
+      <c r="F12" s="11" t="str">
         <f>F11</f>
         <v>MahjongWays</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H12" s="1">
         <v>2</v>
@@ -1982,39 +2060,42 @@
         <v>0</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M12" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M12" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N12">
         <v>100000</v>
       </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:14">
+      <c r="O12" s="18">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="1">
         <f t="shared" si="2"/>
         <v>1007003</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="10">
         <v>100700</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="10">
         <v>1</v>
       </c>
-      <c r="D13" s="9" t="str">
+      <c r="D13" s="10" t="str">
         <f>D12</f>
         <v>麻将胡了</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="11">
         <v>100700001</v>
       </c>
-      <c r="F13" s="10" t="str">
+      <c r="F13" s="11" t="str">
         <f>F12</f>
         <v>MahjongWays</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H13" s="1">
         <v>3</v>
@@ -2029,37 +2110,40 @@
         <v>0</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M13" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M13" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N13">
         <v>10000000</v>
       </c>
-    </row>
-    <row r="14" ht="16.5" spans="1:14">
+      <c r="O13" s="18">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" s="1">
         <f t="shared" si="2"/>
         <v>1012001</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="10">
         <v>101200</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="10">
         <v>1</v>
       </c>
-      <c r="D14" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="10">
+      <c r="D14" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" s="11">
         <v>101200001</v>
       </c>
-      <c r="F14" s="10" t="s">
-        <v>40</v>
+      <c r="F14" s="11" t="s">
+        <v>42</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H14" s="1">
         <v>1</v>
@@ -2074,39 +2158,42 @@
         <v>0</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M14" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M14" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N14">
         <v>1000</v>
       </c>
-    </row>
-    <row r="15" ht="16.5" spans="1:14">
+      <c r="O14" s="18">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" s="1">
         <f t="shared" si="2"/>
         <v>1012002</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B15" s="10">
         <v>101200</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="10">
         <v>1</v>
       </c>
-      <c r="D15" s="9" t="str">
+      <c r="D15" s="10" t="str">
         <f>D14</f>
         <v>财神</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="11">
         <v>101200001</v>
       </c>
-      <c r="F15" s="10" t="str">
+      <c r="F15" s="11" t="str">
         <f>F14</f>
         <v>GodOfWealth</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H15" s="1">
         <v>2</v>
@@ -2121,39 +2208,42 @@
         <v>0</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M15" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M15" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N15">
         <v>100000</v>
       </c>
-    </row>
-    <row r="16" ht="16.5" spans="1:14">
+      <c r="O15" s="18">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" s="1">
         <f t="shared" si="2"/>
         <v>1012003</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="10">
         <v>101200</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="10">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="str">
+      <c r="D16" s="10" t="str">
         <f>D15</f>
         <v>财神</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="11">
         <v>101200001</v>
       </c>
-      <c r="F16" s="10" t="str">
+      <c r="F16" s="11" t="str">
         <f>F15</f>
         <v>GodOfWealth</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H16" s="1">
         <v>3</v>
@@ -2168,37 +2258,40 @@
         <v>0</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M16" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M16" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N16">
         <v>10000000</v>
       </c>
-    </row>
-    <row r="17" ht="16.5" spans="1:14">
+      <c r="O16" s="18">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17" s="1">
         <f t="shared" si="2"/>
         <v>1014001</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B17" s="10">
         <v>101400</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C17" s="10">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E17" s="10">
+      <c r="D17" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="11">
         <v>101400001</v>
       </c>
-      <c r="F17" s="10" t="s">
-        <v>42</v>
+      <c r="F17" s="11" t="s">
+        <v>44</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H17" s="1">
         <v>1</v>
@@ -2213,39 +2306,42 @@
         <v>0</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M17" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M17" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N17">
         <v>1000</v>
       </c>
-    </row>
-    <row r="18" ht="16.5" spans="1:14">
+      <c r="O17" s="18">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18" s="1">
         <f t="shared" si="2"/>
         <v>1014002</v>
       </c>
-      <c r="B18" s="9">
+      <c r="B18" s="10">
         <v>101400</v>
       </c>
-      <c r="C18" s="9">
+      <c r="C18" s="10">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="str">
+      <c r="D18" s="10" t="str">
         <f>D17</f>
         <v>埃及艳后</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="11">
         <v>101400001</v>
       </c>
-      <c r="F18" s="10" t="str">
+      <c r="F18" s="11" t="str">
         <f>F17</f>
         <v>Cleopatra</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H18" s="1">
         <v>2</v>
@@ -2260,39 +2356,42 @@
         <v>0</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M18" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M18" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N18">
         <v>100000</v>
       </c>
-    </row>
-    <row r="19" ht="16.5" spans="1:14">
+      <c r="O18" s="18">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" s="1">
         <f t="shared" si="2"/>
         <v>1014003</v>
       </c>
-      <c r="B19" s="9">
+      <c r="B19" s="10">
         <v>101400</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="10">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="str">
+      <c r="D19" s="10" t="str">
         <f>D18</f>
         <v>埃及艳后</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="11">
         <v>101400001</v>
       </c>
-      <c r="F19" s="10" t="str">
+      <c r="F19" s="11" t="str">
         <f>F18</f>
         <v>Cleopatra</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H19" s="1">
         <v>3</v>
@@ -2307,37 +2406,40 @@
         <v>0</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M19" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M19" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N19">
         <v>10000000</v>
       </c>
-    </row>
-    <row r="20" ht="16.5" spans="1:14">
+      <c r="O19" s="18">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20" s="1">
         <f t="shared" ref="A20:A66" si="3">B20*10+H20</f>
         <v>2001001</v>
       </c>
-      <c r="B20" s="9">
+      <c r="B20" s="10">
         <v>200100</v>
       </c>
-      <c r="C20" s="9">
-        <v>2</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E20" s="10">
+      <c r="C20" s="10">
+        <v>2</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20" s="11">
         <v>200100038</v>
       </c>
-      <c r="F20" s="10" t="s">
-        <v>44</v>
+      <c r="F20" s="11" t="s">
+        <v>46</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H20" s="1">
         <v>1</v>
@@ -2352,38 +2454,41 @@
         <v>0</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M20" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M20" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N20">
         <v>1000</v>
       </c>
-    </row>
-    <row r="21" ht="16.5" spans="1:14">
+      <c r="O20" s="18">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" s="1">
         <f t="shared" si="3"/>
         <v>2001002</v>
       </c>
-      <c r="B21" s="9">
+      <c r="B21" s="10">
         <v>200100</v>
       </c>
-      <c r="C21" s="9">
-        <v>2</v>
-      </c>
-      <c r="D21" s="9" t="str">
+      <c r="C21" s="10">
+        <v>2</v>
+      </c>
+      <c r="D21" s="10" t="str">
         <f>D20</f>
         <v>紅黑大戰</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="11">
         <v>200100038</v>
       </c>
-      <c r="F21" s="10" t="s">
-        <v>44</v>
+      <c r="F21" s="11" t="s">
+        <v>46</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H21" s="1">
         <v>2</v>
@@ -2398,38 +2503,41 @@
         <v>0</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M21" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M21" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N21">
         <v>100000</v>
       </c>
-    </row>
-    <row r="22" ht="16.5" spans="1:17">
+      <c r="O21" s="18">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17">
       <c r="A22" s="1">
         <f t="shared" si="3"/>
         <v>2001003</v>
       </c>
-      <c r="B22" s="9">
+      <c r="B22" s="10">
         <v>200100</v>
       </c>
-      <c r="C22" s="9">
-        <v>2</v>
-      </c>
-      <c r="D22" s="9" t="str">
+      <c r="C22" s="10">
+        <v>2</v>
+      </c>
+      <c r="D22" s="10" t="str">
         <f>D21</f>
         <v>紅黑大戰</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="11">
         <v>200100038</v>
       </c>
-      <c r="F22" s="10" t="s">
-        <v>44</v>
+      <c r="F22" s="11" t="s">
+        <v>46</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H22" s="1">
         <v>3</v>
@@ -2444,38 +2552,41 @@
         <v>0</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M22" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M22" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N22">
         <v>10000000</v>
       </c>
+      <c r="O22" s="18">
+        <v>1990000</v>
+      </c>
       <c r="Q22"/>
     </row>
-    <row r="23" ht="16.5" spans="1:14">
+    <row r="23" spans="1:15">
       <c r="A23" s="1">
         <f t="shared" si="3"/>
         <v>2001011</v>
       </c>
-      <c r="B23" s="9">
+      <c r="B23" s="10">
         <v>200101</v>
       </c>
-      <c r="C23" s="9">
-        <v>2</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="E23" s="10">
+      <c r="C23" s="10">
+        <v>2</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E23" s="11">
         <v>200101001</v>
       </c>
-      <c r="F23" s="10" t="s">
-        <v>46</v>
+      <c r="F23" s="11" t="s">
+        <v>48</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H23" s="1">
         <v>1</v>
@@ -2490,38 +2601,41 @@
         <v>0</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M23" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M23" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N23">
         <v>1000</v>
       </c>
-    </row>
-    <row r="24" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="O23" s="18">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:19">
       <c r="A24" s="1">
         <f t="shared" si="3"/>
         <v>2001012</v>
       </c>
-      <c r="B24" s="9">
+      <c r="B24" s="10">
         <v>200101</v>
       </c>
-      <c r="C24" s="9">
-        <v>2</v>
-      </c>
-      <c r="D24" s="9" t="str">
+      <c r="C24" s="10">
+        <v>2</v>
+      </c>
+      <c r="D24" s="10" t="str">
         <f t="shared" ref="D24:D28" si="4">D23</f>
         <v>龍虎鬥</v>
       </c>
-      <c r="E24" s="10">
+      <c r="E24" s="11">
         <v>200101001</v>
       </c>
-      <c r="F24" s="10" t="s">
-        <v>46</v>
+      <c r="F24" s="11" t="s">
+        <v>48</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H24" s="1">
         <v>2</v>
@@ -2536,40 +2650,42 @@
         <v>0</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M24" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M24" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N24">
         <v>100000</v>
       </c>
-      <c r="O24"/>
-      <c r="S24" s="2"/>
-    </row>
-    <row r="25" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="O24" s="18">
+        <v>1990000</v>
+      </c>
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:19">
       <c r="A25" s="1">
         <f t="shared" si="3"/>
         <v>2001013</v>
       </c>
-      <c r="B25" s="9">
+      <c r="B25" s="10">
         <v>200101</v>
       </c>
-      <c r="C25" s="9">
-        <v>2</v>
-      </c>
-      <c r="D25" s="9" t="str">
+      <c r="C25" s="10">
+        <v>2</v>
+      </c>
+      <c r="D25" s="10" t="str">
         <f t="shared" si="4"/>
         <v>龍虎鬥</v>
       </c>
-      <c r="E25" s="10">
+      <c r="E25" s="11">
         <v>200101001</v>
       </c>
-      <c r="F25" s="10" t="s">
-        <v>46</v>
+      <c r="F25" s="11" t="s">
+        <v>48</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H25" s="1">
         <v>3</v>
@@ -2584,39 +2700,41 @@
         <v>0</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M25" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M25" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N25">
         <v>10000000</v>
       </c>
-      <c r="O25"/>
-      <c r="S25" s="2"/>
-    </row>
-    <row r="26" ht="16.5" spans="1:14">
+      <c r="O25" s="18">
+        <v>1990000</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="1:15">
       <c r="A26" s="1">
         <f t="shared" si="3"/>
         <v>2003001</v>
       </c>
-      <c r="B26" s="9">
+      <c r="B26" s="10">
         <v>200300</v>
       </c>
-      <c r="C26" s="9">
-        <v>2</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E26" s="10">
+      <c r="C26" s="10">
+        <v>2</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="E26" s="11">
         <v>200300001</v>
       </c>
-      <c r="F26" s="10" t="s">
-        <v>48</v>
+      <c r="F26" s="11" t="s">
+        <v>50</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H26" s="1">
         <v>1</v>
@@ -2631,38 +2749,41 @@
         <v>0</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M26" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M26" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N26">
         <v>1000</v>
       </c>
-    </row>
-    <row r="27" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="O26" s="18">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="1:19">
       <c r="A27" s="1">
         <f t="shared" si="3"/>
         <v>2003002</v>
       </c>
-      <c r="B27" s="9">
+      <c r="B27" s="10">
         <v>200300</v>
       </c>
-      <c r="C27" s="9">
-        <v>2</v>
-      </c>
-      <c r="D27" s="9" t="str">
+      <c r="C27" s="10">
+        <v>2</v>
+      </c>
+      <c r="D27" s="10" t="str">
         <f t="shared" si="4"/>
         <v>飛禽走獸</v>
       </c>
-      <c r="E27" s="10">
+      <c r="E27" s="11">
         <v>200300001</v>
       </c>
-      <c r="F27" s="10" t="s">
-        <v>48</v>
+      <c r="F27" s="11" t="s">
+        <v>50</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H27" s="1">
         <v>2</v>
@@ -2677,42 +2798,44 @@
         <v>0</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M27" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M27" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N27">
         <v>100000</v>
       </c>
-      <c r="O27"/>
-      <c r="Q27" s="2"/>
-      <c r="R27" s="9"/>
-      <c r="S27" s="2"/>
-    </row>
-    <row r="28" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="O27" s="18">
+        <v>1990000</v>
+      </c>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="10"/>
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="1:19">
       <c r="A28" s="1">
         <f t="shared" si="3"/>
         <v>2003003</v>
       </c>
-      <c r="B28" s="9">
+      <c r="B28" s="10">
         <v>200300</v>
       </c>
-      <c r="C28" s="9">
-        <v>2</v>
-      </c>
-      <c r="D28" s="9" t="str">
+      <c r="C28" s="10">
+        <v>2</v>
+      </c>
+      <c r="D28" s="10" t="str">
         <f t="shared" si="4"/>
         <v>飛禽走獸</v>
       </c>
-      <c r="E28" s="10">
+      <c r="E28" s="11">
         <v>200300001</v>
       </c>
-      <c r="F28" s="10" t="s">
-        <v>48</v>
+      <c r="F28" s="11" t="s">
+        <v>50</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H28" s="1">
         <v>3</v>
@@ -2727,41 +2850,43 @@
         <v>0</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M28" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M28" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N28">
         <v>10000000</v>
       </c>
-      <c r="O28"/>
-      <c r="Q28" s="2"/>
-      <c r="R28" s="11"/>
-      <c r="S28" s="11"/>
-    </row>
-    <row r="29" ht="16.5" spans="1:19">
+      <c r="O28" s="18">
+        <v>1990000</v>
+      </c>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="12"/>
+      <c r="S28" s="12"/>
+    </row>
+    <row r="29" spans="1:19">
       <c r="A29" s="1">
         <f t="shared" si="3"/>
         <v>2004001</v>
       </c>
-      <c r="B29" s="9">
+      <c r="B29" s="10">
         <v>200400</v>
       </c>
-      <c r="C29" s="9">
-        <v>2</v>
-      </c>
-      <c r="D29" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E29" s="10">
+      <c r="C29" s="10">
+        <v>2</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E29" s="11">
         <v>200400009</v>
       </c>
-      <c r="F29" s="10" t="s">
-        <v>50</v>
+      <c r="F29" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H29" s="1">
         <v>1</v>
@@ -2776,40 +2901,43 @@
         <v>0</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M29" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M29" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N29">
         <v>1000</v>
       </c>
-      <c r="Q29" s="2"/>
-      <c r="R29" s="11"/>
-      <c r="S29" s="11"/>
-    </row>
-    <row r="30" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="O29" s="18">
+        <v>1990000</v>
+      </c>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="12"/>
+      <c r="S29" s="12"/>
+    </row>
+    <row r="30" s="1" customFormat="1" spans="1:19">
       <c r="A30" s="1">
         <f t="shared" si="3"/>
         <v>2004002</v>
       </c>
-      <c r="B30" s="9">
+      <c r="B30" s="10">
         <v>200400</v>
       </c>
-      <c r="C30" s="9">
-        <v>2</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E30" s="10">
+      <c r="C30" s="10">
+        <v>2</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E30" s="11">
         <v>200400009</v>
       </c>
-      <c r="F30" s="10" t="s">
-        <v>50</v>
+      <c r="F30" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H30" s="1">
         <v>2</v>
@@ -2824,41 +2952,43 @@
         <v>0</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M30" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M30" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N30">
         <v>100000</v>
       </c>
-      <c r="O30"/>
-      <c r="Q30" s="2"/>
-      <c r="R30" s="11"/>
-      <c r="S30" s="11"/>
-    </row>
-    <row r="31" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="O30" s="18">
+        <v>1990000</v>
+      </c>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="12"/>
+      <c r="S30" s="12"/>
+    </row>
+    <row r="31" s="1" customFormat="1" spans="1:19">
       <c r="A31" s="1">
         <f t="shared" si="3"/>
         <v>2004003</v>
       </c>
-      <c r="B31" s="9">
+      <c r="B31" s="10">
         <v>200400</v>
       </c>
-      <c r="C31" s="9">
-        <v>2</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E31" s="10">
+      <c r="C31" s="10">
+        <v>2</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31" s="11">
         <v>200400009</v>
       </c>
-      <c r="F31" s="10" t="s">
-        <v>50</v>
+      <c r="F31" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H31" s="1">
         <v>3</v>
@@ -2873,41 +3003,43 @@
         <v>0</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M31" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M31" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N31">
         <v>10000000</v>
       </c>
-      <c r="O31"/>
-      <c r="Q31" s="2"/>
-      <c r="R31" s="11"/>
-      <c r="S31" s="11"/>
-    </row>
-    <row r="32" ht="16.5" spans="1:19">
+      <c r="O31" s="18">
+        <v>1990000</v>
+      </c>
+      <c r="Q31" s="3"/>
+      <c r="R31" s="12"/>
+      <c r="S31" s="12"/>
+    </row>
+    <row r="32" spans="1:19">
       <c r="A32" s="1">
         <f t="shared" si="3"/>
         <v>2005001</v>
       </c>
-      <c r="B32" s="9">
+      <c r="B32" s="10">
         <v>200500</v>
       </c>
-      <c r="C32" s="9">
-        <v>2</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E32" s="10">
+      <c r="C32" s="10">
+        <v>2</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E32" s="11">
         <v>200500025</v>
       </c>
-      <c r="F32" s="10" t="s">
-        <v>52</v>
+      <c r="F32" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H32" s="1">
         <v>1</v>
@@ -2922,40 +3054,43 @@
         <v>0</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M32" s="16" t="s">
-        <v>53</v>
+        <v>33</v>
+      </c>
+      <c r="M32" s="20" t="s">
+        <v>55</v>
       </c>
       <c r="N32">
         <v>1000</v>
       </c>
-      <c r="Q32" s="2"/>
-      <c r="R32" s="11"/>
-      <c r="S32" s="11"/>
-    </row>
-    <row r="33" ht="16.5" spans="1:19">
+      <c r="O32" s="18">
+        <v>1990000</v>
+      </c>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="12"/>
+      <c r="S32" s="12"/>
+    </row>
+    <row r="33" spans="1:19">
       <c r="A33" s="1">
         <f t="shared" si="3"/>
         <v>2005002</v>
       </c>
-      <c r="B33" s="9">
+      <c r="B33" s="10">
         <v>200500</v>
       </c>
-      <c r="C33" s="9">
-        <v>2</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E33" s="10">
+      <c r="C33" s="10">
+        <v>2</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E33" s="11">
         <v>200500025</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>52</v>
+      <c r="F33" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H33" s="1">
         <v>2</v>
@@ -2970,40 +3105,43 @@
         <v>0</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M33" s="16" t="s">
-        <v>53</v>
+        <v>33</v>
+      </c>
+      <c r="M33" s="20" t="s">
+        <v>55</v>
       </c>
       <c r="N33">
         <v>100000</v>
       </c>
-      <c r="Q33" s="2"/>
-      <c r="R33" s="11"/>
-      <c r="S33" s="11"/>
-    </row>
-    <row r="34" ht="16.5" spans="1:19">
+      <c r="O33" s="18">
+        <v>1990000</v>
+      </c>
+      <c r="Q33" s="3"/>
+      <c r="R33" s="12"/>
+      <c r="S33" s="12"/>
+    </row>
+    <row r="34" spans="1:19">
       <c r="A34" s="1">
         <f t="shared" si="3"/>
         <v>2005003</v>
       </c>
-      <c r="B34" s="9">
+      <c r="B34" s="10">
         <v>200500</v>
       </c>
-      <c r="C34" s="9">
-        <v>2</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E34" s="10">
+      <c r="C34" s="10">
+        <v>2</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E34" s="11">
         <v>200500025</v>
       </c>
-      <c r="F34" s="10" t="s">
-        <v>52</v>
+      <c r="F34" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H34" s="1">
         <v>3</v>
@@ -3018,40 +3156,43 @@
         <v>0</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M34" s="16" t="s">
-        <v>53</v>
+        <v>33</v>
+      </c>
+      <c r="M34" s="20" t="s">
+        <v>55</v>
       </c>
       <c r="N34">
         <v>10000000</v>
       </c>
-      <c r="Q34" s="2"/>
-      <c r="R34" s="11"/>
-      <c r="S34" s="11"/>
-    </row>
-    <row r="35" ht="16.5" spans="1:19">
+      <c r="O34" s="18">
+        <v>1990000</v>
+      </c>
+      <c r="Q34" s="3"/>
+      <c r="R34" s="12"/>
+      <c r="S34" s="12"/>
+    </row>
+    <row r="35" spans="1:19">
       <c r="A35" s="1">
         <f t="shared" si="3"/>
         <v>2006001</v>
       </c>
-      <c r="B35" s="9">
+      <c r="B35" s="10">
         <v>200600</v>
       </c>
-      <c r="C35" s="9">
-        <v>2</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E35" s="10">
+      <c r="C35" s="10">
+        <v>2</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E35" s="11">
         <v>200600001</v>
       </c>
-      <c r="F35" s="10" t="s">
-        <v>55</v>
+      <c r="F35" s="11" t="s">
+        <v>57</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H35" s="1">
         <v>1</v>
@@ -3066,40 +3207,43 @@
         <v>0</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M35" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M35" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N35">
         <v>1000</v>
       </c>
-      <c r="Q35" s="2"/>
-      <c r="R35" s="11"/>
-      <c r="S35" s="11"/>
-    </row>
-    <row r="36" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="O35" s="18">
+        <v>1990000</v>
+      </c>
+      <c r="Q35" s="3"/>
+      <c r="R35" s="12"/>
+      <c r="S35" s="12"/>
+    </row>
+    <row r="36" s="1" customFormat="1" spans="1:19">
       <c r="A36" s="1">
         <f t="shared" si="3"/>
         <v>2006002</v>
       </c>
-      <c r="B36" s="9">
+      <c r="B36" s="10">
         <v>200600</v>
       </c>
-      <c r="C36" s="9">
-        <v>2</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E36" s="10">
+      <c r="C36" s="10">
+        <v>2</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E36" s="11">
         <v>200600001</v>
       </c>
-      <c r="F36" s="10" t="s">
-        <v>55</v>
+      <c r="F36" s="11" t="s">
+        <v>57</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H36" s="1">
         <v>2</v>
@@ -3114,41 +3258,43 @@
         <v>0</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M36" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M36" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N36">
         <v>100000</v>
       </c>
-      <c r="O36"/>
-      <c r="Q36" s="2"/>
-      <c r="R36" s="11"/>
-      <c r="S36" s="11"/>
-    </row>
-    <row r="37" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="O36" s="18">
+        <v>1990000</v>
+      </c>
+      <c r="Q36" s="3"/>
+      <c r="R36" s="12"/>
+      <c r="S36" s="12"/>
+    </row>
+    <row r="37" s="1" customFormat="1" spans="1:19">
       <c r="A37" s="1">
         <f t="shared" si="3"/>
         <v>2006003</v>
       </c>
-      <c r="B37" s="9">
+      <c r="B37" s="10">
         <v>200600</v>
       </c>
-      <c r="C37" s="9">
-        <v>2</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E37" s="10">
+      <c r="C37" s="10">
+        <v>2</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E37" s="11">
         <v>200600001</v>
       </c>
-      <c r="F37" s="10" t="s">
-        <v>55</v>
+      <c r="F37" s="11" t="s">
+        <v>57</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H37" s="1">
         <v>3</v>
@@ -3163,41 +3309,43 @@
         <v>0</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M37" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M37" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N37">
         <v>10000000</v>
       </c>
-      <c r="O37"/>
-      <c r="Q37" s="2"/>
+      <c r="O37" s="18">
+        <v>1990000</v>
+      </c>
+      <c r="Q37" s="3"/>
       <c r="R37"/>
-      <c r="S37" s="11"/>
-    </row>
-    <row r="38" ht="16.5" spans="1:19">
+      <c r="S37" s="12"/>
+    </row>
+    <row r="38" spans="1:19">
       <c r="A38" s="1">
         <f t="shared" si="3"/>
         <v>2007001</v>
       </c>
-      <c r="B38" s="9">
+      <c r="B38" s="10">
         <v>200700</v>
       </c>
-      <c r="C38" s="9">
-        <v>2</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="E38" s="10">
+      <c r="C38" s="10">
+        <v>2</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E38" s="11">
         <v>200700001</v>
       </c>
-      <c r="F38" s="10" t="s">
-        <v>57</v>
+      <c r="F38" s="11" t="s">
+        <v>59</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H38" s="1">
         <v>1</v>
@@ -3212,41 +3360,44 @@
         <v>0</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M38" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M38" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N38">
         <v>1000</v>
       </c>
-      <c r="Q38" s="2"/>
-      <c r="R38" s="11"/>
-      <c r="S38" s="11"/>
-    </row>
-    <row r="39" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="O38" s="18">
+        <v>1990000</v>
+      </c>
+      <c r="Q38" s="3"/>
+      <c r="R38" s="12"/>
+      <c r="S38" s="12"/>
+    </row>
+    <row r="39" s="1" customFormat="1" spans="1:19">
       <c r="A39" s="1">
         <f t="shared" si="3"/>
         <v>2007002</v>
       </c>
-      <c r="B39" s="9">
+      <c r="B39" s="10">
         <v>200700</v>
       </c>
-      <c r="C39" s="9">
-        <v>2</v>
-      </c>
-      <c r="D39" s="9" t="str">
+      <c r="C39" s="10">
+        <v>2</v>
+      </c>
+      <c r="D39" s="10" t="str">
         <f t="shared" ref="D36:D40" si="5">D38</f>
         <v>越南色碟</v>
       </c>
-      <c r="E39" s="10">
+      <c r="E39" s="11">
         <v>200700001</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>57</v>
+      <c r="F39" s="11" t="s">
+        <v>59</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H39" s="1">
         <v>2</v>
@@ -3261,42 +3412,44 @@
         <v>0</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M39" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M39" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N39">
         <v>100000</v>
       </c>
-      <c r="O39"/>
-      <c r="Q39" s="2"/>
-      <c r="R39" s="11"/>
-      <c r="S39" s="11"/>
-    </row>
-    <row r="40" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="O39" s="18">
+        <v>1990000</v>
+      </c>
+      <c r="Q39" s="3"/>
+      <c r="R39" s="12"/>
+      <c r="S39" s="12"/>
+    </row>
+    <row r="40" s="1" customFormat="1" spans="1:19">
       <c r="A40" s="1">
         <f t="shared" si="3"/>
         <v>2007003</v>
       </c>
-      <c r="B40" s="9">
+      <c r="B40" s="10">
         <v>200700</v>
       </c>
-      <c r="C40" s="9">
-        <v>2</v>
-      </c>
-      <c r="D40" s="9" t="str">
+      <c r="C40" s="10">
+        <v>2</v>
+      </c>
+      <c r="D40" s="10" t="str">
         <f t="shared" si="5"/>
         <v>越南色碟</v>
       </c>
-      <c r="E40" s="10">
+      <c r="E40" s="11">
         <v>200700001</v>
       </c>
-      <c r="F40" s="10" t="s">
-        <v>57</v>
+      <c r="F40" s="11" t="s">
+        <v>59</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H40" s="1">
         <v>3</v>
@@ -3311,39 +3464,41 @@
         <v>0</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M40" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M40" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N40">
         <v>10000000</v>
       </c>
-      <c r="O40"/>
-      <c r="S40" s="2"/>
-    </row>
-    <row r="41" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="O40" s="18">
+        <v>1990000</v>
+      </c>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" s="1" customFormat="1" spans="1:19">
       <c r="A41" s="1">
         <f t="shared" si="3"/>
         <v>2008001</v>
       </c>
-      <c r="B41" s="9">
+      <c r="B41" s="10">
         <v>200800</v>
       </c>
-      <c r="C41" s="9">
-        <v>2</v>
-      </c>
-      <c r="D41" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="E41" s="10">
+      <c r="C41" s="10">
+        <v>2</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E41" s="11">
         <v>200800001</v>
       </c>
-      <c r="F41" s="10" t="s">
-        <v>59</v>
+      <c r="F41" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H41" s="1">
         <v>1</v>
@@ -3358,39 +3513,41 @@
         <v>0</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M41" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M41" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N41">
         <v>1000</v>
       </c>
-      <c r="O41"/>
-      <c r="S41" s="2"/>
-    </row>
-    <row r="42" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="O41" s="18">
+        <v>1990000</v>
+      </c>
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" s="1" customFormat="1" spans="1:19">
       <c r="A42" s="1">
         <f t="shared" si="3"/>
         <v>2008002</v>
       </c>
-      <c r="B42" s="9">
+      <c r="B42" s="10">
         <v>200800</v>
       </c>
-      <c r="C42" s="9">
-        <v>2</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="E42" s="10">
+      <c r="C42" s="10">
+        <v>2</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E42" s="11">
         <v>200800001</v>
       </c>
-      <c r="F42" s="10" t="s">
-        <v>59</v>
+      <c r="F42" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H42" s="1">
         <v>2</v>
@@ -3405,39 +3562,41 @@
         <v>0</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M42" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M42" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N42">
         <v>100000</v>
       </c>
-      <c r="O42"/>
-      <c r="S42" s="2"/>
-    </row>
-    <row r="43" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="O42" s="18">
+        <v>1990000</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" s="1" customFormat="1" spans="1:19">
       <c r="A43" s="1">
         <f t="shared" si="3"/>
         <v>2008003</v>
       </c>
-      <c r="B43" s="9">
+      <c r="B43" s="10">
         <v>200800</v>
       </c>
-      <c r="C43" s="9">
-        <v>2</v>
-      </c>
-      <c r="D43" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="E43" s="10">
+      <c r="C43" s="10">
+        <v>2</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E43" s="11">
         <v>200800001</v>
       </c>
-      <c r="F43" s="10" t="s">
-        <v>59</v>
+      <c r="F43" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H43" s="1">
         <v>3</v>
@@ -3452,39 +3611,41 @@
         <v>0</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M43" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M43" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N43">
         <v>10000000</v>
       </c>
-      <c r="O43"/>
-      <c r="S43" s="2"/>
-    </row>
-    <row r="44" ht="16.5" spans="1:14">
+      <c r="O43" s="18">
+        <v>1990000</v>
+      </c>
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="1:15">
       <c r="A44" s="1">
         <f t="shared" si="3"/>
         <v>2009001</v>
       </c>
-      <c r="B44" s="12">
+      <c r="B44" s="13">
         <v>200900</v>
       </c>
-      <c r="C44" s="9">
-        <v>2</v>
-      </c>
-      <c r="D44" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="E44" s="10">
+      <c r="C44" s="10">
+        <v>2</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E44" s="11">
         <v>200900001</v>
       </c>
-      <c r="F44" s="10" t="s">
-        <v>61</v>
+      <c r="F44" s="11" t="s">
+        <v>63</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H44" s="1">
         <v>1</v>
@@ -3499,38 +3660,41 @@
         <v>0</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M44" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M44" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N44">
         <v>1000</v>
       </c>
-    </row>
-    <row r="45" ht="16.5" spans="1:14">
+      <c r="O44" s="18">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15">
       <c r="A45" s="1">
         <f t="shared" si="3"/>
         <v>2009002</v>
       </c>
-      <c r="B45" s="9">
+      <c r="B45" s="10">
         <v>200900</v>
       </c>
-      <c r="C45" s="9">
-        <v>2</v>
-      </c>
-      <c r="D45" s="9" t="str">
+      <c r="C45" s="10">
+        <v>2</v>
+      </c>
+      <c r="D45" s="10" t="str">
         <f>D44</f>
         <v>魚蝦蟹</v>
       </c>
-      <c r="E45" s="10">
+      <c r="E45" s="11">
         <v>200900001</v>
       </c>
-      <c r="F45" s="10" t="s">
-        <v>61</v>
+      <c r="F45" s="11" t="s">
+        <v>63</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H45" s="1">
         <v>2</v>
@@ -3545,38 +3709,41 @@
         <v>0</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M45" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M45" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N45">
         <v>100000</v>
       </c>
-    </row>
-    <row r="46" ht="16.5" spans="1:14">
+      <c r="O45" s="18">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15">
       <c r="A46" s="1">
         <f t="shared" si="3"/>
         <v>2009003</v>
       </c>
-      <c r="B46" s="9">
+      <c r="B46" s="10">
         <v>200900</v>
       </c>
-      <c r="C46" s="9">
-        <v>2</v>
-      </c>
-      <c r="D46" s="9" t="str">
+      <c r="C46" s="10">
+        <v>2</v>
+      </c>
+      <c r="D46" s="10" t="str">
         <f>D45</f>
         <v>魚蝦蟹</v>
       </c>
-      <c r="E46" s="10">
+      <c r="E46" s="11">
         <v>200900001</v>
       </c>
-      <c r="F46" s="10" t="s">
-        <v>61</v>
+      <c r="F46" s="11" t="s">
+        <v>63</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H46" s="1">
         <v>3</v>
@@ -3591,35 +3758,38 @@
         <v>0</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M46" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M46" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N46">
         <v>10000000</v>
       </c>
-    </row>
-    <row r="47" ht="16.5" spans="1:14">
+      <c r="O46" s="18">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15">
       <c r="A47" s="1">
         <f t="shared" si="3"/>
         <v>2010001</v>
       </c>
-      <c r="B47" s="9">
+      <c r="B47" s="10">
         <v>201000</v>
       </c>
-      <c r="C47" s="9">
-        <v>2</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E47" s="10">
+      <c r="C47" s="10">
+        <v>2</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E47" s="11">
         <v>101000006</v>
       </c>
-      <c r="F47" s="10"/>
+      <c r="F47" s="11"/>
       <c r="G47" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H47" s="1">
         <v>1</v>
@@ -3634,35 +3804,38 @@
         <v>0</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M47" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M47" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N47">
         <v>1000</v>
       </c>
-    </row>
-    <row r="48" ht="16.5" spans="1:14">
+      <c r="O47" s="18">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15">
       <c r="A48" s="1">
         <f t="shared" si="3"/>
         <v>2010002</v>
       </c>
-      <c r="B48" s="9">
+      <c r="B48" s="10">
         <v>201000</v>
       </c>
-      <c r="C48" s="9">
-        <v>2</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E48" s="10">
+      <c r="C48" s="10">
+        <v>2</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E48" s="11">
         <v>101000006</v>
       </c>
-      <c r="F48" s="10"/>
+      <c r="F48" s="11"/>
       <c r="G48" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H48" s="1">
         <v>2</v>
@@ -3677,35 +3850,38 @@
         <v>0</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M48" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M48" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N48">
         <v>100000</v>
       </c>
-    </row>
-    <row r="49" ht="16.5" spans="1:14">
+      <c r="O48" s="18">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15">
       <c r="A49" s="1">
         <f t="shared" si="3"/>
         <v>2010003</v>
       </c>
-      <c r="B49" s="9">
+      <c r="B49" s="10">
         <v>201000</v>
       </c>
-      <c r="C49" s="9">
-        <v>2</v>
-      </c>
-      <c r="D49" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E49" s="10">
+      <c r="C49" s="10">
+        <v>2</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E49" s="11">
         <v>101000006</v>
       </c>
-      <c r="F49" s="10"/>
+      <c r="F49" s="11"/>
       <c r="G49" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H49" s="1">
         <v>3</v>
@@ -3720,37 +3896,40 @@
         <v>0</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M49" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="M49" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N49">
         <v>10000000</v>
       </c>
-    </row>
-    <row r="50" ht="16.5" spans="1:14">
+      <c r="O49" s="18">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15">
       <c r="A50" s="1">
         <f t="shared" si="3"/>
         <v>3001001</v>
       </c>
-      <c r="B50" s="9">
+      <c r="B50" s="10">
         <v>300100</v>
       </c>
-      <c r="C50" s="9">
+      <c r="C50" s="10">
         <v>3</v>
       </c>
-      <c r="D50" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E50" s="10">
+      <c r="D50" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E50" s="11">
         <v>300100001</v>
       </c>
-      <c r="F50" s="10" t="s">
-        <v>64</v>
+      <c r="F50" s="11" t="s">
+        <v>66</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H50" s="1">
         <v>1</v>
@@ -3764,38 +3943,41 @@
       <c r="K50" s="1">
         <v>0</v>
       </c>
-      <c r="L50" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="M50" s="17" t="s">
-        <v>66</v>
+      <c r="L50" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="M50" s="21" t="s">
+        <v>68</v>
       </c>
       <c r="N50">
         <v>500</v>
       </c>
-    </row>
-    <row r="51" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="O50" s="18">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="51" s="1" customFormat="1" spans="1:19">
       <c r="A51" s="1">
         <f t="shared" si="3"/>
         <v>3001002</v>
       </c>
-      <c r="B51" s="9">
+      <c r="B51" s="10">
         <v>300100</v>
       </c>
-      <c r="C51" s="9">
+      <c r="C51" s="10">
         <v>3</v>
       </c>
-      <c r="D51" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E51" s="10">
+      <c r="D51" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E51" s="11">
         <v>300100001</v>
       </c>
-      <c r="F51" s="10" t="s">
-        <v>64</v>
+      <c r="F51" s="11" t="s">
+        <v>66</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H51" s="1">
         <v>2</v>
@@ -3809,40 +3991,42 @@
       <c r="K51" s="1">
         <v>0</v>
       </c>
-      <c r="L51" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="M51" s="17" t="s">
-        <v>66</v>
+      <c r="L51" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="M51" s="21" t="s">
+        <v>68</v>
       </c>
       <c r="N51">
         <v>20000</v>
       </c>
-      <c r="O51"/>
-      <c r="S51" s="2"/>
-    </row>
-    <row r="52" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="O51" s="18">
+        <v>1990000</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" s="1" customFormat="1" spans="1:19">
       <c r="A52" s="1">
         <f t="shared" si="3"/>
         <v>3001003</v>
       </c>
-      <c r="B52" s="9">
+      <c r="B52" s="10">
         <v>300100</v>
       </c>
-      <c r="C52" s="9">
+      <c r="C52" s="10">
         <v>3</v>
       </c>
-      <c r="D52" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E52" s="10">
+      <c r="D52" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E52" s="11">
         <v>300100001</v>
       </c>
-      <c r="F52" s="10" t="s">
-        <v>64</v>
+      <c r="F52" s="11" t="s">
+        <v>66</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H52" s="1">
         <v>3</v>
@@ -3856,40 +4040,42 @@
       <c r="K52" s="1">
         <v>0</v>
       </c>
-      <c r="L52" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="M52" s="17" t="s">
-        <v>66</v>
+      <c r="L52" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="M52" s="21" t="s">
+        <v>68</v>
       </c>
       <c r="N52">
         <v>2000000</v>
       </c>
-      <c r="O52"/>
-      <c r="S52" s="2"/>
-    </row>
-    <row r="53" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="O52" s="18">
+        <v>1990000</v>
+      </c>
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" s="1" customFormat="1" spans="1:19">
       <c r="A53" s="1">
         <f t="shared" si="3"/>
         <v>3002001</v>
       </c>
-      <c r="B53" s="9">
+      <c r="B53" s="10">
         <v>300200</v>
       </c>
-      <c r="C53" s="9">
+      <c r="C53" s="10">
         <v>3</v>
       </c>
-      <c r="D53" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E53" s="10">
+      <c r="D53" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E53" s="11">
         <v>300200006</v>
       </c>
-      <c r="F53" s="10" t="s">
-        <v>68</v>
+      <c r="F53" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H53" s="1">
         <v>1</v>
@@ -3903,40 +4089,42 @@
       <c r="K53" s="1">
         <v>0</v>
       </c>
-      <c r="L53" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="M53" s="17" t="s">
-        <v>66</v>
+      <c r="L53" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="M53" s="21" t="s">
+        <v>68</v>
       </c>
       <c r="N53">
         <v>500</v>
       </c>
-      <c r="O53"/>
-      <c r="S53" s="2"/>
-    </row>
-    <row r="54" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="O53" s="18">
+        <v>1990000</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" s="1" customFormat="1" spans="1:19">
       <c r="A54" s="1">
         <f t="shared" si="3"/>
         <v>3002002</v>
       </c>
-      <c r="B54" s="9">
+      <c r="B54" s="10">
         <v>300200</v>
       </c>
-      <c r="C54" s="9">
+      <c r="C54" s="10">
         <v>3</v>
       </c>
-      <c r="D54" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E54" s="10">
+      <c r="D54" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E54" s="11">
         <v>300200006</v>
       </c>
-      <c r="F54" s="10" t="s">
-        <v>68</v>
+      <c r="F54" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H54" s="1">
         <v>2</v>
@@ -3950,40 +4138,42 @@
       <c r="K54" s="1">
         <v>0</v>
       </c>
-      <c r="L54" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="M54" s="17" t="s">
-        <v>66</v>
+      <c r="L54" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="M54" s="21" t="s">
+        <v>68</v>
       </c>
       <c r="N54">
         <v>20000</v>
       </c>
-      <c r="O54"/>
-      <c r="S54" s="2"/>
-    </row>
-    <row r="55" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="O54" s="18">
+        <v>1990000</v>
+      </c>
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" s="1" customFormat="1" spans="1:19">
       <c r="A55" s="1">
         <f t="shared" si="3"/>
         <v>3002003</v>
       </c>
-      <c r="B55" s="9">
+      <c r="B55" s="10">
         <v>300200</v>
       </c>
-      <c r="C55" s="9">
+      <c r="C55" s="10">
         <v>3</v>
       </c>
-      <c r="D55" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E55" s="10">
+      <c r="D55" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E55" s="11">
         <v>300200006</v>
       </c>
-      <c r="F55" s="10" t="s">
-        <v>68</v>
+      <c r="F55" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H55" s="1">
         <v>3</v>
@@ -3997,1292 +4187,1360 @@
       <c r="K55" s="1">
         <v>0</v>
       </c>
-      <c r="L55" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="M55" s="17" t="s">
-        <v>66</v>
+      <c r="L55" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="M55" s="21" t="s">
+        <v>68</v>
       </c>
       <c r="N55">
         <v>2000000</v>
       </c>
-      <c r="O55"/>
-      <c r="S55" s="2"/>
-    </row>
-    <row r="56" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="O55" s="18">
+        <v>1990000</v>
+      </c>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" s="1" customFormat="1" spans="1:19">
       <c r="A56" s="1">
         <f t="shared" ref="A56:A62" si="6">B56*100+H56</f>
         <v>20010010</v>
       </c>
-      <c r="B56" s="10">
+      <c r="B56" s="11">
         <v>200100</v>
       </c>
-      <c r="C56" s="10">
-        <v>2</v>
-      </c>
-      <c r="D56" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E56" s="10">
+      <c r="C56" s="11">
+        <v>2</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E56" s="11">
         <v>200100038</v>
       </c>
-      <c r="F56" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="G56" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="H56" s="13">
+      <c r="F56" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G56" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="H56" s="14">
         <v>10</v>
       </c>
-      <c r="I56" s="13">
-        <v>0</v>
-      </c>
-      <c r="J56" s="13">
+      <c r="I56" s="14">
+        <v>0</v>
+      </c>
+      <c r="J56" s="14">
         <v>-1</v>
       </c>
       <c r="K56" s="1">
         <v>0</v>
       </c>
-      <c r="L56" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="M56" s="13">
+      <c r="L56" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="M56" s="14">
         <v>0</v>
       </c>
       <c r="N56">
         <v>100</v>
       </c>
-      <c r="O56"/>
-      <c r="S56" s="2"/>
-    </row>
-    <row r="57" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="O56" s="19">
+        <v>1980000</v>
+      </c>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" s="1" customFormat="1" spans="1:19">
       <c r="A57" s="1">
         <f t="shared" si="6"/>
         <v>20010011</v>
       </c>
-      <c r="B57" s="10">
+      <c r="B57" s="11">
         <v>200100</v>
       </c>
-      <c r="C57" s="10">
-        <v>2</v>
-      </c>
-      <c r="D57" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E57" s="10">
+      <c r="C57" s="11">
+        <v>2</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E57" s="11">
         <v>200100038</v>
       </c>
-      <c r="F57" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="G57" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="H57" s="13">
+      <c r="F57" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G57" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="H57" s="14">
         <v>11</v>
       </c>
-      <c r="I57" s="13">
-        <v>0</v>
-      </c>
-      <c r="J57" s="13">
+      <c r="I57" s="14">
+        <v>0</v>
+      </c>
+      <c r="J57" s="14">
         <v>-1</v>
       </c>
       <c r="K57" s="1">
         <v>0</v>
       </c>
-      <c r="L57" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="M57" s="13">
+      <c r="L57" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="M57" s="14">
         <v>0</v>
       </c>
       <c r="N57">
         <v>100</v>
       </c>
-      <c r="O57"/>
-      <c r="S57" s="2"/>
-    </row>
-    <row r="58" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="O57" s="19">
+        <v>1980000</v>
+      </c>
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" s="1" customFormat="1" spans="1:19">
       <c r="A58" s="1">
         <f t="shared" si="6"/>
         <v>20010012</v>
       </c>
-      <c r="B58" s="10">
+      <c r="B58" s="11">
         <v>200100</v>
       </c>
-      <c r="C58" s="10">
-        <v>2</v>
-      </c>
-      <c r="D58" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E58" s="10">
+      <c r="C58" s="11">
+        <v>2</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E58" s="11">
         <v>200100038</v>
       </c>
-      <c r="F58" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="G58" s="13" t="s">
+      <c r="F58" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G58" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="H58" s="14">
+        <v>12</v>
+      </c>
+      <c r="I58" s="14">
+        <v>0</v>
+      </c>
+      <c r="J58" s="14">
+        <v>-1</v>
+      </c>
+      <c r="K58" s="1">
+        <v>0</v>
+      </c>
+      <c r="L58" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="H58" s="13">
-        <v>12</v>
-      </c>
-      <c r="I58" s="13">
-        <v>0</v>
-      </c>
-      <c r="J58" s="13">
-        <v>-1</v>
-      </c>
-      <c r="K58" s="1">
-        <v>0</v>
-      </c>
-      <c r="L58" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="M58" s="13">
+      <c r="M58" s="14">
         <v>0</v>
       </c>
       <c r="N58">
         <v>100</v>
       </c>
-      <c r="O58"/>
-      <c r="S58" s="2"/>
-    </row>
-    <row r="59" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="O58" s="19">
+        <v>1980000</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" s="1" customFormat="1" spans="1:19">
       <c r="A59" s="1">
         <f t="shared" si="6"/>
         <v>20010110</v>
       </c>
-      <c r="B59" s="10">
+      <c r="B59" s="11">
         <v>200101</v>
       </c>
-      <c r="C59" s="10">
-        <v>2</v>
-      </c>
-      <c r="D59" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="E59" s="10">
+      <c r="C59" s="11">
+        <v>2</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E59" s="11">
         <v>200101001</v>
       </c>
-      <c r="F59" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G59" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="H59" s="13">
+      <c r="F59" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G59" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="H59" s="14">
         <v>10</v>
       </c>
-      <c r="I59" s="13">
-        <v>0</v>
-      </c>
-      <c r="J59" s="13">
+      <c r="I59" s="14">
+        <v>0</v>
+      </c>
+      <c r="J59" s="14">
         <v>-1</v>
       </c>
       <c r="K59" s="1">
         <v>0</v>
       </c>
-      <c r="L59" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="M59" s="13">
+      <c r="L59" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="M59" s="14">
         <v>0</v>
       </c>
       <c r="N59">
         <v>100</v>
       </c>
-      <c r="O59"/>
-      <c r="S59" s="2"/>
-    </row>
-    <row r="60" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="O59" s="19">
+        <v>1980000</v>
+      </c>
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" s="1" customFormat="1" spans="1:19">
       <c r="A60" s="1">
         <f t="shared" si="6"/>
         <v>20010111</v>
       </c>
-      <c r="B60" s="10">
+      <c r="B60" s="11">
         <v>200101</v>
       </c>
-      <c r="C60" s="10">
-        <v>2</v>
-      </c>
-      <c r="D60" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="E60" s="10">
+      <c r="C60" s="11">
+        <v>2</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E60" s="11">
         <v>200101001</v>
       </c>
-      <c r="F60" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G60" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="H60" s="13">
+      <c r="F60" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G60" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="H60" s="14">
         <v>11</v>
       </c>
-      <c r="I60" s="13">
-        <v>0</v>
-      </c>
-      <c r="J60" s="13">
+      <c r="I60" s="14">
+        <v>0</v>
+      </c>
+      <c r="J60" s="14">
         <v>-1</v>
       </c>
       <c r="K60" s="1">
         <v>0</v>
       </c>
-      <c r="L60" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="M60" s="13">
+      <c r="L60" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="M60" s="14">
         <v>0</v>
       </c>
       <c r="N60">
         <v>100</v>
       </c>
-      <c r="O60"/>
-      <c r="S60" s="2"/>
-    </row>
-    <row r="61" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="O60" s="19">
+        <v>1980000</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" s="1" customFormat="1" spans="1:19">
       <c r="A61" s="1">
         <f t="shared" si="6"/>
         <v>20010112</v>
       </c>
-      <c r="B61" s="10">
+      <c r="B61" s="11">
         <v>200101</v>
       </c>
-      <c r="C61" s="10">
-        <v>2</v>
-      </c>
-      <c r="D61" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="E61" s="10">
+      <c r="C61" s="11">
+        <v>2</v>
+      </c>
+      <c r="D61" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E61" s="11">
         <v>200101001</v>
       </c>
-      <c r="F61" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G61" s="13" t="s">
+      <c r="F61" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G61" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="H61" s="14">
+        <v>12</v>
+      </c>
+      <c r="I61" s="14">
+        <v>0</v>
+      </c>
+      <c r="J61" s="14">
+        <v>-1</v>
+      </c>
+      <c r="K61" s="1">
+        <v>0</v>
+      </c>
+      <c r="L61" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="H61" s="13">
-        <v>12</v>
-      </c>
-      <c r="I61" s="13">
-        <v>0</v>
-      </c>
-      <c r="J61" s="13">
-        <v>-1</v>
-      </c>
-      <c r="K61" s="1">
-        <v>0</v>
-      </c>
-      <c r="L61" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="M61" s="13">
+      <c r="M61" s="14">
         <v>0</v>
       </c>
       <c r="N61">
         <v>100</v>
       </c>
-      <c r="O61"/>
-      <c r="S61" s="2"/>
-    </row>
-    <row r="62" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="O61" s="19">
+        <v>1980000</v>
+      </c>
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" s="1" customFormat="1" spans="1:19">
       <c r="A62" s="1">
         <f t="shared" si="6"/>
         <v>20030010</v>
       </c>
-      <c r="B62" s="10">
+      <c r="B62" s="11">
         <v>200300</v>
       </c>
-      <c r="C62" s="10">
-        <v>2</v>
-      </c>
-      <c r="D62" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E62" s="10">
+      <c r="C62" s="11">
+        <v>2</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E62" s="11">
         <v>200300001</v>
       </c>
-      <c r="F62" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="G62" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="H62" s="13">
+      <c r="F62" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="G62" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="H62" s="14">
         <v>10</v>
       </c>
-      <c r="I62" s="13">
-        <v>0</v>
-      </c>
-      <c r="J62" s="13">
+      <c r="I62" s="14">
+        <v>0</v>
+      </c>
+      <c r="J62" s="14">
         <v>-1</v>
       </c>
       <c r="K62" s="1">
         <v>0</v>
       </c>
-      <c r="L62" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="M62" s="13">
+      <c r="L62" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="M62" s="14">
         <v>0</v>
       </c>
       <c r="N62">
         <v>100</v>
       </c>
-      <c r="O62"/>
-      <c r="S62" s="2"/>
-    </row>
-    <row r="63" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="O62" s="19">
+        <v>1980000</v>
+      </c>
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" s="1" customFormat="1" spans="1:19">
       <c r="A63" s="1">
         <f t="shared" ref="A63:A71" si="7">B63*100+H63</f>
         <v>20030011</v>
       </c>
-      <c r="B63" s="10">
+      <c r="B63" s="11">
         <v>200300</v>
       </c>
-      <c r="C63" s="10">
-        <v>2</v>
-      </c>
-      <c r="D63" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E63" s="10">
+      <c r="C63" s="11">
+        <v>2</v>
+      </c>
+      <c r="D63" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E63" s="11">
         <v>200300001</v>
       </c>
-      <c r="F63" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="G63" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="H63" s="13">
+      <c r="F63" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="G63" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="H63" s="14">
         <v>11</v>
       </c>
-      <c r="I63" s="13">
-        <v>0</v>
-      </c>
-      <c r="J63" s="13">
+      <c r="I63" s="14">
+        <v>0</v>
+      </c>
+      <c r="J63" s="14">
         <v>-1</v>
       </c>
       <c r="K63" s="1">
         <v>0</v>
       </c>
-      <c r="L63" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="M63" s="13">
+      <c r="L63" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="M63" s="14">
         <v>0</v>
       </c>
       <c r="N63">
         <v>100</v>
       </c>
-      <c r="O63"/>
-      <c r="S63" s="2"/>
-    </row>
-    <row r="64" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="O63" s="19">
+        <v>1980000</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" s="1" customFormat="1" spans="1:19">
       <c r="A64" s="1">
         <f t="shared" si="7"/>
         <v>20030012</v>
       </c>
-      <c r="B64" s="10">
+      <c r="B64" s="11">
         <v>200300</v>
       </c>
-      <c r="C64" s="10">
-        <v>2</v>
-      </c>
-      <c r="D64" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E64" s="10">
+      <c r="C64" s="11">
+        <v>2</v>
+      </c>
+      <c r="D64" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E64" s="11">
         <v>200300001</v>
       </c>
-      <c r="F64" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="G64" s="13" t="s">
+      <c r="F64" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="G64" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="H64" s="14">
+        <v>12</v>
+      </c>
+      <c r="I64" s="14">
+        <v>0</v>
+      </c>
+      <c r="J64" s="14">
+        <v>-1</v>
+      </c>
+      <c r="K64" s="1">
+        <v>0</v>
+      </c>
+      <c r="L64" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="H64" s="13">
-        <v>12</v>
-      </c>
-      <c r="I64" s="13">
-        <v>0</v>
-      </c>
-      <c r="J64" s="13">
-        <v>-1</v>
-      </c>
-      <c r="K64" s="1">
-        <v>0</v>
-      </c>
-      <c r="L64" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="M64" s="13">
+      <c r="M64" s="14">
         <v>0</v>
       </c>
       <c r="N64">
         <v>100</v>
       </c>
-      <c r="O64"/>
-      <c r="S64" s="2"/>
-    </row>
-    <row r="65" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="O64" s="19">
+        <v>1980000</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" s="1" customFormat="1" spans="1:19">
       <c r="A65" s="1">
         <f t="shared" si="7"/>
         <v>20040010</v>
       </c>
-      <c r="B65" s="10">
+      <c r="B65" s="11">
         <v>200400</v>
       </c>
-      <c r="C65" s="10">
-        <v>2</v>
-      </c>
-      <c r="D65" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E65" s="10">
+      <c r="C65" s="11">
+        <v>2</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E65" s="11">
         <v>200400009</v>
       </c>
-      <c r="F65" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="G65" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="H65" s="13">
+      <c r="F65" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="G65" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="H65" s="14">
         <v>10</v>
       </c>
-      <c r="I65" s="13">
-        <v>0</v>
-      </c>
-      <c r="J65" s="13">
+      <c r="I65" s="14">
+        <v>0</v>
+      </c>
+      <c r="J65" s="14">
         <v>-1</v>
       </c>
       <c r="K65" s="1">
         <v>0</v>
       </c>
-      <c r="L65" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="M65" s="13">
+      <c r="L65" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="M65" s="14">
         <v>0</v>
       </c>
       <c r="N65">
         <v>100</v>
       </c>
-      <c r="O65"/>
-      <c r="S65" s="2"/>
-    </row>
-    <row r="66" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="O65" s="19">
+        <v>1980000</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" s="1" customFormat="1" spans="1:19">
       <c r="A66" s="1">
         <f t="shared" si="7"/>
         <v>20040011</v>
       </c>
-      <c r="B66" s="10">
+      <c r="B66" s="11">
         <v>200400</v>
       </c>
-      <c r="C66" s="10">
-        <v>2</v>
-      </c>
-      <c r="D66" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E66" s="10">
+      <c r="C66" s="11">
+        <v>2</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E66" s="11">
         <v>200400009</v>
       </c>
-      <c r="F66" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="G66" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="H66" s="13">
+      <c r="F66" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="G66" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="H66" s="14">
         <v>11</v>
       </c>
-      <c r="I66" s="13">
-        <v>0</v>
-      </c>
-      <c r="J66" s="13">
+      <c r="I66" s="14">
+        <v>0</v>
+      </c>
+      <c r="J66" s="14">
         <v>-1</v>
       </c>
       <c r="K66" s="1">
         <v>0</v>
       </c>
-      <c r="L66" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="M66" s="13">
+      <c r="L66" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="M66" s="14">
         <v>0</v>
       </c>
       <c r="N66">
         <v>100</v>
       </c>
-      <c r="O66"/>
-      <c r="S66" s="2"/>
-    </row>
-    <row r="67" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="O66" s="19">
+        <v>1980000</v>
+      </c>
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" s="1" customFormat="1" spans="1:19">
       <c r="A67" s="1">
         <f t="shared" si="7"/>
         <v>20040012</v>
       </c>
-      <c r="B67" s="10">
+      <c r="B67" s="11">
         <v>200400</v>
       </c>
-      <c r="C67" s="10">
-        <v>2</v>
-      </c>
-      <c r="D67" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E67" s="10">
+      <c r="C67" s="11">
+        <v>2</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E67" s="11">
         <v>200400009</v>
       </c>
-      <c r="F67" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="G67" s="13" t="s">
+      <c r="F67" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="G67" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="H67" s="14">
+        <v>12</v>
+      </c>
+      <c r="I67" s="14">
+        <v>0</v>
+      </c>
+      <c r="J67" s="14">
+        <v>-1</v>
+      </c>
+      <c r="K67" s="1">
+        <v>0</v>
+      </c>
+      <c r="L67" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="H67" s="13">
-        <v>12</v>
-      </c>
-      <c r="I67" s="13">
-        <v>0</v>
-      </c>
-      <c r="J67" s="13">
-        <v>-1</v>
-      </c>
-      <c r="K67" s="1">
-        <v>0</v>
-      </c>
-      <c r="L67" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="M67" s="13">
+      <c r="M67" s="14">
         <v>0</v>
       </c>
       <c r="N67">
         <v>100</v>
       </c>
-      <c r="O67"/>
-      <c r="S67" s="2"/>
-    </row>
-    <row r="68" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="O67" s="19">
+        <v>1980000</v>
+      </c>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" s="1" customFormat="1" spans="1:19">
       <c r="A68" s="1">
         <f t="shared" si="7"/>
         <v>20050010</v>
       </c>
-      <c r="B68" s="10">
+      <c r="B68" s="11">
         <v>200500</v>
       </c>
-      <c r="C68" s="10">
-        <v>2</v>
-      </c>
-      <c r="D68" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="E68" s="10">
+      <c r="C68" s="11">
+        <v>2</v>
+      </c>
+      <c r="D68" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E68" s="11">
         <v>200500025</v>
       </c>
-      <c r="F68" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="G68" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="H68" s="13">
+      <c r="F68" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G68" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="H68" s="14">
         <v>10</v>
       </c>
-      <c r="I68" s="13">
-        <v>0</v>
-      </c>
-      <c r="J68" s="13">
+      <c r="I68" s="14">
+        <v>0</v>
+      </c>
+      <c r="J68" s="14">
         <v>-1</v>
       </c>
       <c r="K68" s="1">
         <v>0</v>
       </c>
-      <c r="L68" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="M68" s="13">
+      <c r="L68" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="M68" s="14">
         <v>0</v>
       </c>
       <c r="N68">
         <v>100</v>
       </c>
-      <c r="O68"/>
-      <c r="S68" s="2"/>
-    </row>
-    <row r="69" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="O68" s="19">
+        <v>1980000</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" s="1" customFormat="1" spans="1:19">
       <c r="A69" s="1">
         <f t="shared" si="7"/>
         <v>20050011</v>
       </c>
-      <c r="B69" s="10">
+      <c r="B69" s="11">
         <v>200500</v>
       </c>
-      <c r="C69" s="10">
-        <v>2</v>
-      </c>
-      <c r="D69" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="E69" s="10">
+      <c r="C69" s="11">
+        <v>2</v>
+      </c>
+      <c r="D69" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E69" s="11">
         <v>200500025</v>
       </c>
-      <c r="F69" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="G69" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="H69" s="13">
+      <c r="F69" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G69" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="H69" s="14">
         <v>11</v>
       </c>
-      <c r="I69" s="13">
-        <v>0</v>
-      </c>
-      <c r="J69" s="13">
+      <c r="I69" s="14">
+        <v>0</v>
+      </c>
+      <c r="J69" s="14">
         <v>-1</v>
       </c>
       <c r="K69" s="1">
         <v>0</v>
       </c>
-      <c r="L69" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="M69" s="13">
+      <c r="L69" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="M69" s="14">
         <v>0</v>
       </c>
       <c r="N69">
         <v>100</v>
       </c>
-      <c r="O69"/>
-      <c r="S69" s="2"/>
-    </row>
-    <row r="70" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="O69" s="19">
+        <v>1980000</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" s="1" customFormat="1" spans="1:19">
       <c r="A70" s="1">
         <f t="shared" si="7"/>
         <v>20050012</v>
       </c>
-      <c r="B70" s="10">
+      <c r="B70" s="11">
         <v>200500</v>
       </c>
-      <c r="C70" s="10">
-        <v>2</v>
-      </c>
-      <c r="D70" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="E70" s="10">
+      <c r="C70" s="11">
+        <v>2</v>
+      </c>
+      <c r="D70" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E70" s="11">
         <v>200500025</v>
       </c>
-      <c r="F70" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="G70" s="13" t="s">
+      <c r="F70" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G70" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="H70" s="14">
+        <v>12</v>
+      </c>
+      <c r="I70" s="14">
+        <v>0</v>
+      </c>
+      <c r="J70" s="14">
+        <v>-1</v>
+      </c>
+      <c r="K70" s="1">
+        <v>0</v>
+      </c>
+      <c r="L70" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="H70" s="13">
-        <v>12</v>
-      </c>
-      <c r="I70" s="13">
-        <v>0</v>
-      </c>
-      <c r="J70" s="13">
-        <v>-1</v>
-      </c>
-      <c r="K70" s="1">
-        <v>0</v>
-      </c>
-      <c r="L70" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="M70" s="13">
+      <c r="M70" s="14">
         <v>0</v>
       </c>
       <c r="N70">
         <v>100</v>
       </c>
-      <c r="O70"/>
-      <c r="S70" s="2"/>
-    </row>
-    <row r="71" ht="16.5" spans="1:14">
+      <c r="O70" s="19">
+        <v>1980000</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="1:15">
       <c r="A71" s="1">
         <f t="shared" si="7"/>
         <v>20060010</v>
       </c>
-      <c r="B71" s="10">
+      <c r="B71" s="11">
         <v>200600</v>
       </c>
-      <c r="C71" s="10">
-        <v>2</v>
-      </c>
-      <c r="D71" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E71" s="10">
+      <c r="C71" s="11">
+        <v>2</v>
+      </c>
+      <c r="D71" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E71" s="11">
         <v>200600001</v>
       </c>
-      <c r="F71" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="G71" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="H71" s="13">
+      <c r="F71" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="G71" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="H71" s="14">
         <v>10</v>
       </c>
-      <c r="I71" s="13">
-        <v>0</v>
-      </c>
-      <c r="J71" s="13">
+      <c r="I71" s="14">
+        <v>0</v>
+      </c>
+      <c r="J71" s="14">
         <v>-1</v>
       </c>
       <c r="K71" s="1">
         <v>0</v>
       </c>
-      <c r="L71" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="M71" s="13">
+      <c r="L71" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="M71" s="14">
         <v>0</v>
       </c>
       <c r="N71">
         <v>100</v>
       </c>
-    </row>
-    <row r="72" ht="16.5" spans="1:14">
+      <c r="O71" s="19">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15">
       <c r="A72" s="1">
-        <f t="shared" ref="A72:A82" si="8">B72*100+H72</f>
+        <f t="shared" ref="A72:A85" si="8">B72*100+H72</f>
         <v>20060011</v>
       </c>
-      <c r="B72" s="10">
+      <c r="B72" s="11">
         <v>200600</v>
       </c>
-      <c r="C72" s="10">
-        <v>2</v>
-      </c>
-      <c r="D72" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E72" s="10">
+      <c r="C72" s="11">
+        <v>2</v>
+      </c>
+      <c r="D72" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E72" s="11">
         <v>200600001</v>
       </c>
-      <c r="F72" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="G72" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="H72" s="13">
+      <c r="F72" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="G72" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="H72" s="14">
         <v>11</v>
       </c>
-      <c r="I72" s="13">
-        <v>0</v>
-      </c>
-      <c r="J72" s="13">
+      <c r="I72" s="14">
+        <v>0</v>
+      </c>
+      <c r="J72" s="14">
         <v>-1</v>
       </c>
       <c r="K72" s="1">
         <v>0</v>
       </c>
-      <c r="L72" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="M72" s="13">
+      <c r="L72" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="M72" s="14">
         <v>0</v>
       </c>
       <c r="N72">
         <v>100</v>
       </c>
-    </row>
-    <row r="73" ht="16.5" spans="1:14">
+      <c r="O72" s="19">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15">
       <c r="A73" s="1">
         <f t="shared" si="8"/>
         <v>20060012</v>
       </c>
-      <c r="B73" s="10">
+      <c r="B73" s="11">
         <v>200600</v>
       </c>
-      <c r="C73" s="10">
-        <v>2</v>
-      </c>
-      <c r="D73" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E73" s="10">
+      <c r="C73" s="11">
+        <v>2</v>
+      </c>
+      <c r="D73" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E73" s="11">
         <v>200600001</v>
       </c>
-      <c r="F73" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="G73" s="13" t="s">
+      <c r="F73" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="G73" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="H73" s="14">
+        <v>12</v>
+      </c>
+      <c r="I73" s="14">
+        <v>0</v>
+      </c>
+      <c r="J73" s="14">
+        <v>-1</v>
+      </c>
+      <c r="K73" s="1">
+        <v>0</v>
+      </c>
+      <c r="L73" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="H73" s="13">
-        <v>12</v>
-      </c>
-      <c r="I73" s="13">
-        <v>0</v>
-      </c>
-      <c r="J73" s="13">
-        <v>-1</v>
-      </c>
-      <c r="K73" s="1">
-        <v>0</v>
-      </c>
-      <c r="L73" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="M73" s="13">
+      <c r="M73" s="14">
         <v>0</v>
       </c>
       <c r="N73">
         <v>100</v>
       </c>
-    </row>
-    <row r="74" ht="16.5" spans="1:14">
+      <c r="O73" s="19">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15">
       <c r="A74" s="1">
         <f t="shared" si="8"/>
         <v>20070010</v>
       </c>
-      <c r="B74" s="10">
+      <c r="B74" s="11">
         <v>200700</v>
       </c>
-      <c r="C74" s="10">
-        <v>2</v>
-      </c>
-      <c r="D74" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="E74" s="10">
+      <c r="C74" s="11">
+        <v>2</v>
+      </c>
+      <c r="D74" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E74" s="11">
         <v>200700001</v>
       </c>
-      <c r="F74" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="G74" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="H74" s="13">
+      <c r="F74" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="G74" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="H74" s="14">
         <v>10</v>
       </c>
-      <c r="I74" s="13">
-        <v>0</v>
-      </c>
-      <c r="J74" s="13">
+      <c r="I74" s="14">
+        <v>0</v>
+      </c>
+      <c r="J74" s="14">
         <v>-1</v>
       </c>
       <c r="K74" s="1">
         <v>0</v>
       </c>
-      <c r="L74" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="M74" s="13">
+      <c r="L74" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="M74" s="14">
         <v>0</v>
       </c>
       <c r="N74">
         <v>100</v>
       </c>
-    </row>
-    <row r="75" ht="16.5" spans="1:14">
+      <c r="O74" s="19">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15">
       <c r="A75" s="1">
         <f t="shared" si="8"/>
         <v>20070011</v>
       </c>
-      <c r="B75" s="10">
+      <c r="B75" s="11">
         <v>200700</v>
       </c>
-      <c r="C75" s="10">
-        <v>2</v>
-      </c>
-      <c r="D75" s="9" t="str">
+      <c r="C75" s="11">
+        <v>2</v>
+      </c>
+      <c r="D75" s="10" t="str">
         <f>D74</f>
         <v>越南色碟</v>
       </c>
-      <c r="E75" s="10">
+      <c r="E75" s="11">
         <v>200700001</v>
       </c>
-      <c r="F75" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="G75" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="H75" s="13">
+      <c r="F75" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="G75" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="H75" s="14">
         <v>11</v>
       </c>
-      <c r="I75" s="13">
-        <v>0</v>
-      </c>
-      <c r="J75" s="13">
+      <c r="I75" s="14">
+        <v>0</v>
+      </c>
+      <c r="J75" s="14">
         <v>-1</v>
       </c>
       <c r="K75" s="1">
         <v>0</v>
       </c>
-      <c r="L75" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="M75" s="13">
+      <c r="L75" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="M75" s="14">
         <v>0</v>
       </c>
       <c r="N75">
         <v>100</v>
       </c>
-    </row>
-    <row r="76" ht="16.5" spans="1:14">
+      <c r="O75" s="19">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15">
       <c r="A76" s="1">
         <f t="shared" si="8"/>
         <v>20070012</v>
       </c>
-      <c r="B76" s="10">
+      <c r="B76" s="11">
         <v>200700</v>
       </c>
-      <c r="C76" s="10">
-        <v>2</v>
-      </c>
-      <c r="D76" s="9" t="str">
+      <c r="C76" s="11">
+        <v>2</v>
+      </c>
+      <c r="D76" s="10" t="str">
         <f>D75</f>
         <v>越南色碟</v>
       </c>
-      <c r="E76" s="10">
+      <c r="E76" s="11">
         <v>200700001</v>
       </c>
-      <c r="F76" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="G76" s="13" t="s">
+      <c r="F76" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="G76" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="H76" s="14">
+        <v>12</v>
+      </c>
+      <c r="I76" s="14">
+        <v>0</v>
+      </c>
+      <c r="J76" s="14">
+        <v>-1</v>
+      </c>
+      <c r="K76" s="1">
+        <v>0</v>
+      </c>
+      <c r="L76" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="H76" s="13">
-        <v>12</v>
-      </c>
-      <c r="I76" s="13">
-        <v>0</v>
-      </c>
-      <c r="J76" s="13">
-        <v>-1</v>
-      </c>
-      <c r="K76" s="1">
-        <v>0</v>
-      </c>
-      <c r="L76" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="M76" s="13">
+      <c r="M76" s="14">
         <v>0</v>
       </c>
       <c r="N76">
         <v>100</v>
       </c>
-    </row>
-    <row r="77" ht="16.5" spans="1:14">
+      <c r="O76" s="19">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15">
       <c r="A77" s="1">
         <f t="shared" si="8"/>
         <v>20080010</v>
       </c>
-      <c r="B77" s="10">
+      <c r="B77" s="11">
         <v>200800</v>
       </c>
-      <c r="C77" s="10">
-        <v>2</v>
-      </c>
-      <c r="D77" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="E77" s="10">
+      <c r="C77" s="11">
+        <v>2</v>
+      </c>
+      <c r="D77" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E77" s="11">
         <v>200800001</v>
       </c>
-      <c r="F77" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="G77" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="H77" s="13">
+      <c r="F77" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="G77" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="H77" s="14">
         <v>10</v>
       </c>
-      <c r="I77" s="13">
-        <v>0</v>
-      </c>
-      <c r="J77" s="13">
+      <c r="I77" s="14">
+        <v>0</v>
+      </c>
+      <c r="J77" s="14">
         <v>-1</v>
       </c>
       <c r="K77" s="1">
         <v>0</v>
       </c>
-      <c r="L77" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="M77" s="13">
+      <c r="L77" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="M77" s="14">
         <v>0</v>
       </c>
       <c r="N77">
         <v>100</v>
       </c>
-    </row>
-    <row r="78" ht="16.5" spans="1:14">
+      <c r="O77" s="19">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15">
       <c r="A78" s="1">
         <f t="shared" si="8"/>
         <v>20080011</v>
       </c>
-      <c r="B78" s="10">
+      <c r="B78" s="11">
         <v>200800</v>
       </c>
-      <c r="C78" s="10">
-        <v>2</v>
-      </c>
-      <c r="D78" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="E78" s="10">
+      <c r="C78" s="11">
+        <v>2</v>
+      </c>
+      <c r="D78" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E78" s="11">
         <v>200800001</v>
       </c>
-      <c r="F78" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="G78" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="H78" s="13">
+      <c r="F78" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="G78" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="H78" s="14">
         <v>11</v>
       </c>
-      <c r="I78" s="13">
-        <v>0</v>
-      </c>
-      <c r="J78" s="13">
+      <c r="I78" s="14">
+        <v>0</v>
+      </c>
+      <c r="J78" s="14">
         <v>-1</v>
       </c>
       <c r="K78" s="1">
         <v>0</v>
       </c>
-      <c r="L78" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="M78" s="13">
+      <c r="L78" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="M78" s="14">
         <v>0</v>
       </c>
       <c r="N78">
         <v>100</v>
       </c>
-    </row>
-    <row r="79" ht="16.5" spans="1:14">
+      <c r="O78" s="19">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15">
       <c r="A79" s="1">
         <f t="shared" si="8"/>
         <v>20080012</v>
       </c>
-      <c r="B79" s="10">
+      <c r="B79" s="11">
         <v>200800</v>
       </c>
-      <c r="C79" s="10">
-        <v>2</v>
-      </c>
-      <c r="D79" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="E79" s="10">
+      <c r="C79" s="11">
+        <v>2</v>
+      </c>
+      <c r="D79" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E79" s="11">
         <v>200800001</v>
       </c>
-      <c r="F79" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="G79" s="13" t="s">
+      <c r="F79" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="G79" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="H79" s="14">
+        <v>12</v>
+      </c>
+      <c r="I79" s="14">
+        <v>0</v>
+      </c>
+      <c r="J79" s="14">
+        <v>-1</v>
+      </c>
+      <c r="K79" s="1">
+        <v>0</v>
+      </c>
+      <c r="L79" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="H79" s="13">
-        <v>12</v>
-      </c>
-      <c r="I79" s="13">
-        <v>0</v>
-      </c>
-      <c r="J79" s="13">
-        <v>-1</v>
-      </c>
-      <c r="K79" s="1">
-        <v>0</v>
-      </c>
-      <c r="L79" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="M79" s="13">
+      <c r="M79" s="14">
         <v>0</v>
       </c>
       <c r="N79">
         <v>100</v>
       </c>
-    </row>
-    <row r="80" ht="16.5" spans="1:14">
+      <c r="O79" s="19">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15">
       <c r="A80" s="1">
         <f t="shared" si="8"/>
         <v>20090010</v>
       </c>
-      <c r="B80" s="10">
+      <c r="B80" s="11">
         <v>200900</v>
       </c>
-      <c r="C80" s="10">
-        <v>2</v>
-      </c>
-      <c r="D80" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="E80" s="10">
+      <c r="C80" s="11">
+        <v>2</v>
+      </c>
+      <c r="D80" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E80" s="11">
         <v>200900001</v>
       </c>
-      <c r="F80" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="G80" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="H80" s="13">
+      <c r="F80" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="G80" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="H80" s="14">
         <v>10</v>
       </c>
-      <c r="I80" s="13">
-        <v>0</v>
-      </c>
-      <c r="J80" s="13">
+      <c r="I80" s="14">
+        <v>0</v>
+      </c>
+      <c r="J80" s="14">
         <v>-1</v>
       </c>
       <c r="K80" s="1">
         <v>0</v>
       </c>
-      <c r="L80" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="M80" s="13">
+      <c r="L80" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="M80" s="14">
         <v>0</v>
       </c>
       <c r="N80">
         <v>100</v>
       </c>
-    </row>
-    <row r="81" ht="16.5" spans="1:14">
+      <c r="O80" s="19">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15">
       <c r="A81" s="1">
         <f t="shared" si="8"/>
         <v>20090011</v>
       </c>
-      <c r="B81" s="10">
+      <c r="B81" s="11">
         <v>200900</v>
       </c>
-      <c r="C81" s="10">
-        <v>2</v>
-      </c>
-      <c r="D81" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="E81" s="10">
+      <c r="C81" s="11">
+        <v>2</v>
+      </c>
+      <c r="D81" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E81" s="11">
         <v>200900001</v>
       </c>
-      <c r="F81" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="G81" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="H81" s="13">
+      <c r="F81" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="G81" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="H81" s="14">
         <v>11</v>
       </c>
-      <c r="I81" s="13">
-        <v>0</v>
-      </c>
-      <c r="J81" s="13">
+      <c r="I81" s="14">
+        <v>0</v>
+      </c>
+      <c r="J81" s="14">
         <v>-1</v>
       </c>
       <c r="K81" s="1">
         <v>0</v>
       </c>
-      <c r="L81" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="M81" s="13">
+      <c r="L81" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="M81" s="14">
         <v>0</v>
       </c>
       <c r="N81">
         <v>100</v>
       </c>
-    </row>
-    <row r="82" ht="16.5" spans="1:14">
+      <c r="O81" s="19">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15">
       <c r="A82" s="1">
         <f t="shared" si="8"/>
         <v>20090012</v>
       </c>
-      <c r="B82" s="10">
+      <c r="B82" s="11">
         <v>200900</v>
       </c>
-      <c r="C82" s="10">
-        <v>2</v>
-      </c>
-      <c r="D82" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="E82" s="10">
+      <c r="C82" s="11">
+        <v>2</v>
+      </c>
+      <c r="D82" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E82" s="11">
         <v>200900001</v>
       </c>
-      <c r="F82" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="G82" s="13" t="s">
+      <c r="F82" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="G82" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="H82" s="14">
+        <v>12</v>
+      </c>
+      <c r="I82" s="14">
+        <v>0</v>
+      </c>
+      <c r="J82" s="14">
+        <v>-1</v>
+      </c>
+      <c r="K82" s="1">
+        <v>0</v>
+      </c>
+      <c r="L82" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="H82" s="13">
-        <v>12</v>
-      </c>
-      <c r="I82" s="13">
-        <v>0</v>
-      </c>
-      <c r="J82" s="13">
-        <v>-1</v>
-      </c>
-      <c r="K82" s="1">
-        <v>0</v>
-      </c>
-      <c r="L82" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="M82" s="13">
+      <c r="M82" s="14">
         <v>0</v>
       </c>
       <c r="N82">
         <v>100</v>
       </c>
-    </row>
-    <row r="83" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="O82" s="19">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="83" s="1" customFormat="1" spans="1:19">
       <c r="A83" s="1">
-        <f t="shared" ref="A83:A85" si="9">B83*10+H83</f>
-        <v>3002010</v>
-      </c>
-      <c r="B83" s="9">
+        <f t="shared" si="8"/>
+        <v>30020010</v>
+      </c>
+      <c r="B83" s="10">
         <v>300200</v>
       </c>
-      <c r="C83" s="9">
+      <c r="C83" s="10">
         <v>3</v>
       </c>
-      <c r="D83" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E83" s="10">
+      <c r="D83" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E83" s="11">
         <v>300200006</v>
       </c>
-      <c r="F83" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="G83" s="13" t="s">
+      <c r="F83" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="H83" s="13">
+      <c r="G83" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="H83" s="14">
         <v>10</v>
       </c>
-      <c r="I83" s="13">
+      <c r="I83" s="14">
         <v>0</v>
       </c>
       <c r="J83" s="1">
@@ -5291,45 +5549,47 @@
       <c r="K83" s="1">
         <v>0</v>
       </c>
-      <c r="L83" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="M83" s="13">
+      <c r="L83" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="M83" s="14">
         <v>0</v>
       </c>
       <c r="N83">
         <v>500</v>
       </c>
-      <c r="O83"/>
-      <c r="S83" s="2"/>
-    </row>
-    <row r="84" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="O83" s="19">
+        <v>1980000</v>
+      </c>
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" s="1" customFormat="1" spans="1:19">
       <c r="A84" s="1">
-        <f t="shared" si="9"/>
-        <v>3002011</v>
-      </c>
-      <c r="B84" s="9">
+        <f t="shared" si="8"/>
+        <v>30020011</v>
+      </c>
+      <c r="B84" s="10">
         <v>300200</v>
       </c>
-      <c r="C84" s="9">
+      <c r="C84" s="10">
         <v>3</v>
       </c>
-      <c r="D84" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E84" s="10">
+      <c r="D84" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E84" s="11">
         <v>300200006</v>
       </c>
-      <c r="F84" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="G84" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="H84" s="13">
+      <c r="F84" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="G84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="H84" s="14">
         <v>11</v>
       </c>
-      <c r="I84" s="13">
+      <c r="I84" s="14">
         <v>0</v>
       </c>
       <c r="J84" s="1">
@@ -5338,45 +5598,47 @@
       <c r="K84" s="1">
         <v>0</v>
       </c>
-      <c r="L84" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="M84" s="13">
+      <c r="L84" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="M84" s="14">
         <v>0</v>
       </c>
       <c r="N84">
         <v>20000</v>
       </c>
-      <c r="O84"/>
-      <c r="S84" s="2"/>
-    </row>
-    <row r="85" s="1" customFormat="1" ht="16.5" spans="1:19">
+      <c r="O84" s="19">
+        <v>1980000</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" s="1" customFormat="1" spans="1:19">
       <c r="A85" s="1">
-        <f t="shared" si="9"/>
-        <v>3002012</v>
-      </c>
-      <c r="B85" s="9">
+        <f t="shared" si="8"/>
+        <v>30020012</v>
+      </c>
+      <c r="B85" s="10">
         <v>300200</v>
       </c>
-      <c r="C85" s="9">
+      <c r="C85" s="10">
         <v>3</v>
       </c>
-      <c r="D85" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E85" s="10">
+      <c r="D85" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E85" s="11">
         <v>300200006</v>
       </c>
-      <c r="F85" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="G85" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="H85" s="13">
+      <c r="F85" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="G85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="H85" s="14">
         <v>12</v>
       </c>
-      <c r="I85" s="13">
+      <c r="I85" s="14">
         <v>0</v>
       </c>
       <c r="J85" s="1">
@@ -5385,17 +5647,19 @@
       <c r="K85" s="1">
         <v>0</v>
       </c>
-      <c r="L85" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="M85" s="13">
+      <c r="L85" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="M85" s="14">
         <v>0</v>
       </c>
       <c r="N85">
         <v>2000000</v>
       </c>
-      <c r="O85"/>
-      <c r="S85" s="2"/>
+      <c r="O85" s="19">
+        <v>1980000</v>
+      </c>
+      <c r="S85" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -283,7 +283,7 @@
     <t>财神</t>
   </si>
   <si>
-    <t>GodOfWealth</t>
+    <t>Godofwealth</t>
   </si>
   <si>
     <t>埃及艳后</t>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="F15" s="11" t="str">
         <f>F14</f>
-        <v>GodOfWealth</v>
+        <v>Godofwealth</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>35</v>
@@ -2240,7 +2240,7 @@
       </c>
       <c r="F16" s="11" t="str">
         <f>F15</f>
-        <v>GodOfWealth</v>
+        <v>Godofwealth</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>36</v>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -52,7 +52,8 @@
           <t xml:space="preserve">
 1： Slot 电子拉霸
 2： 百人押注
-3： 激情对战</t>
+3： 激情对战
+4:  快捷小游戏</t>
         </r>
       </text>
     </comment>
@@ -4986,7 +4987,7 @@
     </row>
     <row r="72" spans="1:15">
       <c r="A72" s="1">
-        <f t="shared" ref="A72:A85" si="8">B72*100+H72</f>
+        <f t="shared" ref="A72:A86" si="8">B72*100+H72</f>
         <v>20060011</v>
       </c>
       <c r="B72" s="11">

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -5557,7 +5557,7 @@
         <v>0</v>
       </c>
       <c r="N83">
-        <v>500</v>
+        <v>2</v>
       </c>
       <c r="O83" s="19">
         <v>1980000</v>
@@ -5606,7 +5606,7 @@
         <v>0</v>
       </c>
       <c r="N84">
-        <v>20000</v>
+        <v>4</v>
       </c>
       <c r="O84" s="19">
         <v>1980000</v>
@@ -5655,7 +5655,7 @@
         <v>0</v>
       </c>
       <c r="N85">
-        <v>2000000</v>
+        <v>8</v>
       </c>
       <c r="O85" s="19">
         <v>1980000</v>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gamedoc\游戏配置表\common\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B1B608-EB38-4333-A8CE-84FF7DA92A6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="794"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="794" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Warehouse" sheetId="42" r:id="rId1"/>
@@ -27,18 +33,19 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -47,6 +54,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -57,13 +65,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -72,6 +81,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -79,13 +89,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -94,6 +105,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -102,37 +114,40 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>最小准入金币</t>
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>-1 表示无上限</t>
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0">
+    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -141,6 +156,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -156,7 +172,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="77">
   <si>
     <t>sid</t>
   </si>
@@ -392,14 +408,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="30">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -444,173 +454,45 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Noto Sans CJK SC Regular"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="38">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -619,222 +501,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.6"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799340800195319"/>
+        <fgColor theme="5" tint="0.7993408001953185"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799340800195319"/>
+        <fgColor theme="4" tint="0.7993408001953185"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.6"/>
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -857,406 +553,108 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="60">
+  <cellStyleXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="60">
+  <cellStyles count="12">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 2" xfId="49"/>
-    <cellStyle name="常规 2 2" xfId="50"/>
-    <cellStyle name="常规 2 2 2" xfId="51"/>
-    <cellStyle name="常规 3" xfId="52"/>
-    <cellStyle name="常规 3 2" xfId="53"/>
-    <cellStyle name="常规 4" xfId="54"/>
-    <cellStyle name="常规 5" xfId="55"/>
-    <cellStyle name="常规 6" xfId="56"/>
-    <cellStyle name="常规 6 2" xfId="57"/>
-    <cellStyle name="常规 6 2 2" xfId="58"/>
-    <cellStyle name="常规 7" xfId="59"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="常规 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="常规 2 2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="常规 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
+    <cellStyle name="常规 3 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
+    <cellStyle name="常规 4" xfId="6" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
+    <cellStyle name="常规 5" xfId="7" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
+    <cellStyle name="常规 6" xfId="8" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
+    <cellStyle name="常规 6 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
+    <cellStyle name="常规 6 2 2" xfId="10" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
+    <cellStyle name="常规 7" xfId="11" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1514,12 +912,12 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S85"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
@@ -1530,11 +928,11 @@
     <col min="7" max="7" width="12" style="1" customWidth="1"/>
     <col min="8" max="9" width="9" style="1"/>
     <col min="10" max="10" width="11.25" style="1" customWidth="1"/>
-    <col min="11" max="11" width="9.25833333333333" style="1" customWidth="1"/>
-    <col min="12" max="12" width="17.05" style="1" customWidth="1"/>
-    <col min="13" max="13" width="13.9666666666667" style="1" customWidth="1"/>
-    <col min="14" max="14" width="13.675" customWidth="1"/>
-    <col min="15" max="15" width="21.025" style="2" customWidth="1"/>
+    <col min="11" max="11" width="9.25" style="1" customWidth="1"/>
+    <col min="12" max="12" width="17" style="1" customWidth="1"/>
+    <col min="13" max="13" width="14" style="1" customWidth="1"/>
+    <col min="14" max="14" width="13.625" customWidth="1"/>
+    <col min="15" max="15" width="21" style="2" customWidth="1"/>
     <col min="16" max="16" width="9" style="1"/>
     <col min="17" max="17" width="27.875" style="1" customWidth="1"/>
     <col min="18" max="18" width="9" style="1"/>
@@ -1567,13 +965,13 @@
       <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="J1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="K1" s="12" t="s">
         <v>8</v>
       </c>
       <c r="L1" s="1" t="s">
@@ -1585,7 +983,7 @@
       <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="O1" s="13" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1603,20 +1001,20 @@
       <c r="E2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G2" s="6"/>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="K2" s="8" t="s">
         <v>13</v>
       </c>
       <c r="L2" s="1" t="s">
@@ -1625,7 +1023,7 @@
       <c r="M2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="N2" s="8" t="s">
         <v>13</v>
       </c>
       <c r="O2" s="2" t="s">
@@ -1648,16 +1046,16 @@
       <c r="F3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L3" s="1" t="s">
@@ -1666,39 +1064,37 @@
       <c r="M3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="N3" s="8" t="s">
         <v>27</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="14.25" spans="6:15">
+    <row r="4" spans="1:15" ht="14.25">
       <c r="F4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O4" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="O4" s="1"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="1">
         <f t="shared" ref="A5:A10" si="0">B5*10+H5</f>
         <v>1001001</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="2">
         <v>100100</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="2">
         <v>1</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="9">
         <v>100100026</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="9" t="s">
         <v>31</v>
       </c>
       <c r="G5" s="1" t="s">
@@ -1719,13 +1115,13 @@
       <c r="L5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M5" s="20" t="s">
+      <c r="M5" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N5">
         <v>1000</v>
       </c>
-      <c r="O5" s="18">
+      <c r="O5" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -1734,20 +1130,20 @@
         <f t="shared" si="0"/>
         <v>1001002</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="2">
         <v>100100</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="2">
         <v>1</v>
       </c>
-      <c r="D6" s="10" t="str">
+      <c r="D6" s="2" t="str">
         <f t="shared" ref="D6:D10" si="1">D5</f>
         <v>金礦大亨</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="9">
         <v>100100026</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="9" t="s">
         <v>31</v>
       </c>
       <c r="G6" s="1" t="s">
@@ -1768,13 +1164,13 @@
       <c r="L6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M6" s="20" t="s">
+      <c r="M6" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N6">
         <v>100000</v>
       </c>
-      <c r="O6" s="18">
+      <c r="O6" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -1783,20 +1179,20 @@
         <f t="shared" si="0"/>
         <v>1001003</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="2">
         <v>100100</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="2">
         <v>1</v>
       </c>
-      <c r="D7" s="10" t="str">
+      <c r="D7" s="2" t="str">
         <f t="shared" si="1"/>
         <v>金礦大亨</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="9">
         <v>100100026</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="9" t="s">
         <v>31</v>
       </c>
       <c r="G7" s="1" t="s">
@@ -1817,13 +1213,13 @@
       <c r="L7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M7" s="20" t="s">
+      <c r="M7" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N7">
         <v>10000000</v>
       </c>
-      <c r="O7" s="18">
+      <c r="O7" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -1832,19 +1228,19 @@
         <f t="shared" si="0"/>
         <v>1003001</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="2">
         <v>100300</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="2">
         <v>1</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="9">
         <v>100300001</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="9" t="s">
         <v>38</v>
       </c>
       <c r="G8" s="1" t="s">
@@ -1865,13 +1261,13 @@
       <c r="L8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M8" s="20" t="s">
+      <c r="M8" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N8">
         <v>1000</v>
       </c>
-      <c r="O8" s="18">
+      <c r="O8" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -1880,20 +1276,20 @@
         <f t="shared" si="0"/>
         <v>1003002</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="2">
         <v>100300</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="2">
         <v>1</v>
       </c>
-      <c r="D9" s="10" t="str">
+      <c r="D9" s="2" t="str">
         <f t="shared" si="1"/>
         <v>超级明星</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="9">
         <v>100300001</v>
       </c>
-      <c r="F9" s="11" t="str">
+      <c r="F9" s="9" t="str">
         <f>F8</f>
         <v>SuperStar</v>
       </c>
@@ -1915,13 +1311,13 @@
       <c r="L9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M9" s="20" t="s">
+      <c r="M9" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N9">
         <v>100000</v>
       </c>
-      <c r="O9" s="18">
+      <c r="O9" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -1930,20 +1326,20 @@
         <f t="shared" si="0"/>
         <v>1003003</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="2">
         <v>100300</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="2">
         <v>1</v>
       </c>
-      <c r="D10" s="10" t="str">
+      <c r="D10" s="2" t="str">
         <f t="shared" si="1"/>
         <v>超级明星</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="9">
         <v>100300001</v>
       </c>
-      <c r="F10" s="11" t="str">
+      <c r="F10" s="9" t="str">
         <f>F9</f>
         <v>SuperStar</v>
       </c>
@@ -1965,34 +1361,34 @@
       <c r="L10" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M10" s="20" t="s">
+      <c r="M10" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N10">
         <v>10000000</v>
       </c>
-      <c r="O10" s="18">
+      <c r="O10" s="14">
         <v>1990000</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="1">
-        <f t="shared" ref="A11:A22" si="2">B11*10+H11</f>
+        <f t="shared" ref="A11:A19" si="2">B11*10+H11</f>
         <v>1007001</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="2">
         <v>100700</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="2">
         <v>1</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="9">
         <v>100700001</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="9" t="s">
         <v>40</v>
       </c>
       <c r="G11" s="1" t="s">
@@ -2013,13 +1409,13 @@
       <c r="L11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M11" s="20" t="s">
+      <c r="M11" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N11">
         <v>1000</v>
       </c>
-      <c r="O11" s="18">
+      <c r="O11" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -2028,20 +1424,20 @@
         <f t="shared" si="2"/>
         <v>1007002</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="2">
         <v>100700</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="2">
         <v>1</v>
       </c>
-      <c r="D12" s="10" t="str">
+      <c r="D12" s="2" t="str">
         <f>D11</f>
         <v>麻将胡了</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="9">
         <v>100700001</v>
       </c>
-      <c r="F12" s="11" t="str">
+      <c r="F12" s="9" t="str">
         <f>F11</f>
         <v>MahjongWays</v>
       </c>
@@ -2063,13 +1459,13 @@
       <c r="L12" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M12" s="20" t="s">
+      <c r="M12" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N12">
         <v>100000</v>
       </c>
-      <c r="O12" s="18">
+      <c r="O12" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -2078,20 +1474,20 @@
         <f t="shared" si="2"/>
         <v>1007003</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="2">
         <v>100700</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="2">
         <v>1</v>
       </c>
-      <c r="D13" s="10" t="str">
+      <c r="D13" s="2" t="str">
         <f>D12</f>
         <v>麻将胡了</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="9">
         <v>100700001</v>
       </c>
-      <c r="F13" s="11" t="str">
+      <c r="F13" s="9" t="str">
         <f>F12</f>
         <v>MahjongWays</v>
       </c>
@@ -2113,13 +1509,13 @@
       <c r="L13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M13" s="20" t="s">
+      <c r="M13" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N13">
         <v>10000000</v>
       </c>
-      <c r="O13" s="18">
+      <c r="O13" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -2128,19 +1524,19 @@
         <f t="shared" si="2"/>
         <v>1012001</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="2">
         <v>101200</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="2">
         <v>1</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="9">
         <v>101200001</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="9" t="s">
         <v>42</v>
       </c>
       <c r="G14" s="1" t="s">
@@ -2161,13 +1557,13 @@
       <c r="L14" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M14" s="20" t="s">
+      <c r="M14" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N14">
         <v>1000</v>
       </c>
-      <c r="O14" s="18">
+      <c r="O14" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -2176,20 +1572,20 @@
         <f t="shared" si="2"/>
         <v>1012002</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="2">
         <v>101200</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="2">
         <v>1</v>
       </c>
-      <c r="D15" s="10" t="str">
+      <c r="D15" s="2" t="str">
         <f>D14</f>
         <v>财神</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="9">
         <v>101200001</v>
       </c>
-      <c r="F15" s="11" t="str">
+      <c r="F15" s="9" t="str">
         <f>F14</f>
         <v>Godofwealth</v>
       </c>
@@ -2211,13 +1607,13 @@
       <c r="L15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M15" s="20" t="s">
+      <c r="M15" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N15">
         <v>100000</v>
       </c>
-      <c r="O15" s="18">
+      <c r="O15" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -2226,20 +1622,20 @@
         <f t="shared" si="2"/>
         <v>1012003</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="2">
         <v>101200</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="2">
         <v>1</v>
       </c>
-      <c r="D16" s="10" t="str">
+      <c r="D16" s="2" t="str">
         <f>D15</f>
         <v>财神</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="9">
         <v>101200001</v>
       </c>
-      <c r="F16" s="11" t="str">
+      <c r="F16" s="9" t="str">
         <f>F15</f>
         <v>Godofwealth</v>
       </c>
@@ -2261,34 +1657,34 @@
       <c r="L16" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M16" s="20" t="s">
+      <c r="M16" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N16">
         <v>10000000</v>
       </c>
-      <c r="O16" s="18">
+      <c r="O16" s="14">
         <v>1990000</v>
       </c>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:18">
       <c r="A17" s="1">
         <f t="shared" si="2"/>
         <v>1014001</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="2">
         <v>101400</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="2">
         <v>1</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="9">
         <v>101400001</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="9" t="s">
         <v>44</v>
       </c>
       <c r="G17" s="1" t="s">
@@ -2309,35 +1705,35 @@
       <c r="L17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M17" s="20" t="s">
+      <c r="M17" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N17">
         <v>1000</v>
       </c>
-      <c r="O17" s="18">
+      <c r="O17" s="14">
         <v>1990000</v>
       </c>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:18">
       <c r="A18" s="1">
         <f t="shared" si="2"/>
         <v>1014002</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="2">
         <v>101400</v>
       </c>
-      <c r="C18" s="10">
+      <c r="C18" s="2">
         <v>1</v>
       </c>
-      <c r="D18" s="10" t="str">
+      <c r="D18" s="2" t="str">
         <f>D17</f>
         <v>埃及艳后</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="9">
         <v>101400001</v>
       </c>
-      <c r="F18" s="11" t="str">
+      <c r="F18" s="9" t="str">
         <f>F17</f>
         <v>Cleopatra</v>
       </c>
@@ -2359,35 +1755,35 @@
       <c r="L18" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M18" s="20" t="s">
+      <c r="M18" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N18">
         <v>100000</v>
       </c>
-      <c r="O18" s="18">
+      <c r="O18" s="14">
         <v>1990000</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:18">
       <c r="A19" s="1">
         <f t="shared" si="2"/>
         <v>1014003</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="2">
         <v>101400</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="2">
         <v>1</v>
       </c>
-      <c r="D19" s="10" t="str">
+      <c r="D19" s="2" t="str">
         <f>D18</f>
         <v>埃及艳后</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="9">
         <v>101400001</v>
       </c>
-      <c r="F19" s="11" t="str">
+      <c r="F19" s="9" t="str">
         <f>F18</f>
         <v>Cleopatra</v>
       </c>
@@ -2409,34 +1805,34 @@
       <c r="L19" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M19" s="20" t="s">
+      <c r="M19" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N19">
         <v>10000000</v>
       </c>
-      <c r="O19" s="18">
+      <c r="O19" s="14">
         <v>1990000</v>
       </c>
     </row>
-    <row r="20" spans="1:15">
+    <row r="20" spans="1:18">
       <c r="A20" s="1">
-        <f t="shared" ref="A20:A66" si="3">B20*10+H20</f>
+        <f t="shared" ref="A20:A55" si="3">B20*10+H20</f>
         <v>2001001</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="2">
         <v>200100</v>
       </c>
-      <c r="C20" s="10">
-        <v>2</v>
-      </c>
-      <c r="D20" s="10" t="s">
+      <c r="C20" s="2">
+        <v>2</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E20" s="9">
         <v>200100038</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="F20" s="9" t="s">
         <v>46</v>
       </c>
       <c r="G20" s="1" t="s">
@@ -2457,35 +1853,35 @@
       <c r="L20" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M20" s="20" t="s">
+      <c r="M20" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N20">
         <v>1000</v>
       </c>
-      <c r="O20" s="18">
+      <c r="O20" s="14">
         <v>1990000</v>
       </c>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" spans="1:18">
       <c r="A21" s="1">
         <f t="shared" si="3"/>
         <v>2001002</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="2">
         <v>200100</v>
       </c>
-      <c r="C21" s="10">
-        <v>2</v>
-      </c>
-      <c r="D21" s="10" t="str">
+      <c r="C21" s="2">
+        <v>2</v>
+      </c>
+      <c r="D21" s="2" t="str">
         <f>D20</f>
         <v>紅黑大戰</v>
       </c>
-      <c r="E21" s="11">
+      <c r="E21" s="9">
         <v>200100038</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="F21" s="9" t="s">
         <v>46</v>
       </c>
       <c r="G21" s="1" t="s">
@@ -2506,35 +1902,35 @@
       <c r="L21" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M21" s="20" t="s">
+      <c r="M21" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N21">
         <v>100000</v>
       </c>
-      <c r="O21" s="18">
+      <c r="O21" s="14">
         <v>1990000</v>
       </c>
     </row>
-    <row r="22" spans="1:17">
+    <row r="22" spans="1:18">
       <c r="A22" s="1">
         <f t="shared" si="3"/>
         <v>2001003</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="2">
         <v>200100</v>
       </c>
-      <c r="C22" s="10">
-        <v>2</v>
-      </c>
-      <c r="D22" s="10" t="str">
+      <c r="C22" s="2">
+        <v>2</v>
+      </c>
+      <c r="D22" s="2" t="str">
         <f>D21</f>
         <v>紅黑大戰</v>
       </c>
-      <c r="E22" s="11">
+      <c r="E22" s="9">
         <v>200100038</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" s="9" t="s">
         <v>46</v>
       </c>
       <c r="G22" s="1" t="s">
@@ -2555,35 +1951,35 @@
       <c r="L22" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M22" s="20" t="s">
+      <c r="M22" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N22">
         <v>10000000</v>
       </c>
-      <c r="O22" s="18">
+      <c r="O22" s="14">
         <v>1990000</v>
       </c>
       <c r="Q22"/>
     </row>
-    <row r="23" spans="1:15">
+    <row r="23" spans="1:18">
       <c r="A23" s="1">
         <f t="shared" si="3"/>
         <v>2001011</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="2">
         <v>200101</v>
       </c>
-      <c r="C23" s="10">
-        <v>2</v>
-      </c>
-      <c r="D23" s="10" t="s">
+      <c r="C23" s="2">
+        <v>2</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E23" s="11">
+      <c r="E23" s="9">
         <v>200101001</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F23" s="9" t="s">
         <v>48</v>
       </c>
       <c r="G23" s="1" t="s">
@@ -2604,35 +2000,35 @@
       <c r="L23" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M23" s="20" t="s">
+      <c r="M23" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N23">
         <v>1000</v>
       </c>
-      <c r="O23" s="18">
+      <c r="O23" s="14">
         <v>1990000</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" spans="1:19">
+    <row r="24" spans="1:18">
       <c r="A24" s="1">
         <f t="shared" si="3"/>
         <v>2001012</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="2">
         <v>200101</v>
       </c>
-      <c r="C24" s="10">
-        <v>2</v>
-      </c>
-      <c r="D24" s="10" t="str">
+      <c r="C24" s="2">
+        <v>2</v>
+      </c>
+      <c r="D24" s="2" t="str">
         <f t="shared" ref="D24:D28" si="4">D23</f>
         <v>龍虎鬥</v>
       </c>
-      <c r="E24" s="11">
+      <c r="E24" s="9">
         <v>200101001</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="9" t="s">
         <v>48</v>
       </c>
       <c r="G24" s="1" t="s">
@@ -2653,36 +2049,35 @@
       <c r="L24" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M24" s="20" t="s">
+      <c r="M24" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N24">
         <v>100000</v>
       </c>
-      <c r="O24" s="18">
+      <c r="O24" s="14">
         <v>1990000</v>
       </c>
-      <c r="S24" s="3"/>
-    </row>
-    <row r="25" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="25" spans="1:18">
       <c r="A25" s="1">
         <f t="shared" si="3"/>
         <v>2001013</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="2">
         <v>200101</v>
       </c>
-      <c r="C25" s="10">
-        <v>2</v>
-      </c>
-      <c r="D25" s="10" t="str">
+      <c r="C25" s="2">
+        <v>2</v>
+      </c>
+      <c r="D25" s="2" t="str">
         <f t="shared" si="4"/>
         <v>龍虎鬥</v>
       </c>
-      <c r="E25" s="11">
+      <c r="E25" s="9">
         <v>200101001</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F25" s="9" t="s">
         <v>48</v>
       </c>
       <c r="G25" s="1" t="s">
@@ -2703,35 +2098,34 @@
       <c r="L25" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M25" s="20" t="s">
+      <c r="M25" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N25">
         <v>10000000</v>
       </c>
-      <c r="O25" s="18">
+      <c r="O25" s="14">
         <v>1990000</v>
       </c>
-      <c r="S25" s="3"/>
-    </row>
-    <row r="26" spans="1:15">
+    </row>
+    <row r="26" spans="1:18">
       <c r="A26" s="1">
         <f t="shared" si="3"/>
         <v>2003001</v>
       </c>
-      <c r="B26" s="10">
+      <c r="B26" s="2">
         <v>200300</v>
       </c>
-      <c r="C26" s="10">
-        <v>2</v>
-      </c>
-      <c r="D26" s="10" t="s">
+      <c r="C26" s="2">
+        <v>2</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E26" s="11">
+      <c r="E26" s="9">
         <v>200300001</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="F26" s="9" t="s">
         <v>50</v>
       </c>
       <c r="G26" s="1" t="s">
@@ -2752,35 +2146,35 @@
       <c r="L26" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M26" s="20" t="s">
+      <c r="M26" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N26">
         <v>1000</v>
       </c>
-      <c r="O26" s="18">
+      <c r="O26" s="14">
         <v>1990000</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" spans="1:19">
+    <row r="27" spans="1:18">
       <c r="A27" s="1">
         <f t="shared" si="3"/>
         <v>2003002</v>
       </c>
-      <c r="B27" s="10">
+      <c r="B27" s="2">
         <v>200300</v>
       </c>
-      <c r="C27" s="10">
-        <v>2</v>
-      </c>
-      <c r="D27" s="10" t="str">
+      <c r="C27" s="2">
+        <v>2</v>
+      </c>
+      <c r="D27" s="2" t="str">
         <f t="shared" si="4"/>
         <v>飛禽走獸</v>
       </c>
-      <c r="E27" s="11">
+      <c r="E27" s="9">
         <v>200300001</v>
       </c>
-      <c r="F27" s="11" t="s">
+      <c r="F27" s="9" t="s">
         <v>50</v>
       </c>
       <c r="G27" s="1" t="s">
@@ -2801,38 +2195,37 @@
       <c r="L27" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M27" s="20" t="s">
+      <c r="M27" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N27">
         <v>100000</v>
       </c>
-      <c r="O27" s="18">
+      <c r="O27" s="14">
         <v>1990000</v>
       </c>
       <c r="Q27" s="3"/>
-      <c r="R27" s="10"/>
-      <c r="S27" s="3"/>
-    </row>
-    <row r="28" s="1" customFormat="1" spans="1:19">
+      <c r="R27" s="2"/>
+    </row>
+    <row r="28" spans="1:18">
       <c r="A28" s="1">
         <f t="shared" si="3"/>
         <v>2003003</v>
       </c>
-      <c r="B28" s="10">
+      <c r="B28" s="2">
         <v>200300</v>
       </c>
-      <c r="C28" s="10">
-        <v>2</v>
-      </c>
-      <c r="D28" s="10" t="str">
+      <c r="C28" s="2">
+        <v>2</v>
+      </c>
+      <c r="D28" s="2" t="str">
         <f t="shared" si="4"/>
         <v>飛禽走獸</v>
       </c>
-      <c r="E28" s="11">
+      <c r="E28" s="9">
         <v>200300001</v>
       </c>
-      <c r="F28" s="11" t="s">
+      <c r="F28" s="9" t="s">
         <v>50</v>
       </c>
       <c r="G28" s="1" t="s">
@@ -2853,37 +2246,36 @@
       <c r="L28" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M28" s="20" t="s">
+      <c r="M28" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N28">
         <v>10000000</v>
       </c>
-      <c r="O28" s="18">
+      <c r="O28" s="14">
         <v>1990000</v>
       </c>
       <c r="Q28" s="3"/>
-      <c r="R28" s="12"/>
-      <c r="S28" s="12"/>
-    </row>
-    <row r="29" spans="1:19">
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="1:18">
       <c r="A29" s="1">
         <f t="shared" si="3"/>
         <v>2004001</v>
       </c>
-      <c r="B29" s="10">
+      <c r="B29" s="2">
         <v>200400</v>
       </c>
-      <c r="C29" s="10">
-        <v>2</v>
-      </c>
-      <c r="D29" s="12" t="s">
+      <c r="C29" s="2">
+        <v>2</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E29" s="11">
+      <c r="E29" s="9">
         <v>200400009</v>
       </c>
-      <c r="F29" s="11" t="s">
+      <c r="F29" s="9" t="s">
         <v>52</v>
       </c>
       <c r="G29" s="1" t="s">
@@ -2904,37 +2296,36 @@
       <c r="L29" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M29" s="20" t="s">
+      <c r="M29" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N29">
         <v>1000</v>
       </c>
-      <c r="O29" s="18">
+      <c r="O29" s="14">
         <v>1990000</v>
       </c>
       <c r="Q29" s="3"/>
-      <c r="R29" s="12"/>
-      <c r="S29" s="12"/>
-    </row>
-    <row r="30" s="1" customFormat="1" spans="1:19">
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="1:18">
       <c r="A30" s="1">
         <f t="shared" si="3"/>
         <v>2004002</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B30" s="2">
         <v>200400</v>
       </c>
-      <c r="C30" s="10">
-        <v>2</v>
-      </c>
-      <c r="D30" s="12" t="s">
+      <c r="C30" s="2">
+        <v>2</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E30" s="11">
+      <c r="E30" s="9">
         <v>200400009</v>
       </c>
-      <c r="F30" s="11" t="s">
+      <c r="F30" s="9" t="s">
         <v>52</v>
       </c>
       <c r="G30" s="1" t="s">
@@ -2955,37 +2346,36 @@
       <c r="L30" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M30" s="20" t="s">
+      <c r="M30" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N30">
         <v>100000</v>
       </c>
-      <c r="O30" s="18">
+      <c r="O30" s="14">
         <v>1990000</v>
       </c>
       <c r="Q30" s="3"/>
-      <c r="R30" s="12"/>
-      <c r="S30" s="12"/>
-    </row>
-    <row r="31" s="1" customFormat="1" spans="1:19">
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="1:18">
       <c r="A31" s="1">
         <f t="shared" si="3"/>
         <v>2004003</v>
       </c>
-      <c r="B31" s="10">
+      <c r="B31" s="2">
         <v>200400</v>
       </c>
-      <c r="C31" s="10">
-        <v>2</v>
-      </c>
-      <c r="D31" s="12" t="s">
+      <c r="C31" s="2">
+        <v>2</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E31" s="11">
+      <c r="E31" s="9">
         <v>200400009</v>
       </c>
-      <c r="F31" s="11" t="s">
+      <c r="F31" s="9" t="s">
         <v>52</v>
       </c>
       <c r="G31" s="1" t="s">
@@ -3006,37 +2396,36 @@
       <c r="L31" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M31" s="20" t="s">
+      <c r="M31" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N31">
         <v>10000000</v>
       </c>
-      <c r="O31" s="18">
+      <c r="O31" s="14">
         <v>1990000</v>
       </c>
       <c r="Q31" s="3"/>
-      <c r="R31" s="12"/>
-      <c r="S31" s="12"/>
-    </row>
-    <row r="32" spans="1:19">
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="1:18">
       <c r="A32" s="1">
         <f t="shared" si="3"/>
         <v>2005001</v>
       </c>
-      <c r="B32" s="10">
+      <c r="B32" s="2">
         <v>200500</v>
       </c>
-      <c r="C32" s="10">
-        <v>2</v>
-      </c>
-      <c r="D32" s="10" t="s">
+      <c r="C32" s="2">
+        <v>2</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E32" s="11">
+      <c r="E32" s="9">
         <v>200500025</v>
       </c>
-      <c r="F32" s="11" t="s">
+      <c r="F32" s="9" t="s">
         <v>54</v>
       </c>
       <c r="G32" s="1" t="s">
@@ -3057,37 +2446,36 @@
       <c r="L32" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M32" s="20" t="s">
+      <c r="M32" s="16" t="s">
         <v>55</v>
       </c>
       <c r="N32">
         <v>1000</v>
       </c>
-      <c r="O32" s="18">
+      <c r="O32" s="14">
         <v>1990000</v>
       </c>
       <c r="Q32" s="3"/>
-      <c r="R32" s="12"/>
-      <c r="S32" s="12"/>
-    </row>
-    <row r="33" spans="1:19">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="1:18">
       <c r="A33" s="1">
         <f t="shared" si="3"/>
         <v>2005002</v>
       </c>
-      <c r="B33" s="10">
+      <c r="B33" s="2">
         <v>200500</v>
       </c>
-      <c r="C33" s="10">
-        <v>2</v>
-      </c>
-      <c r="D33" s="10" t="s">
+      <c r="C33" s="2">
+        <v>2</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E33" s="11">
+      <c r="E33" s="9">
         <v>200500025</v>
       </c>
-      <c r="F33" s="11" t="s">
+      <c r="F33" s="9" t="s">
         <v>54</v>
       </c>
       <c r="G33" s="1" t="s">
@@ -3108,37 +2496,36 @@
       <c r="L33" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M33" s="20" t="s">
+      <c r="M33" s="16" t="s">
         <v>55</v>
       </c>
       <c r="N33">
         <v>100000</v>
       </c>
-      <c r="O33" s="18">
+      <c r="O33" s="14">
         <v>1990000</v>
       </c>
       <c r="Q33" s="3"/>
-      <c r="R33" s="12"/>
-      <c r="S33" s="12"/>
-    </row>
-    <row r="34" spans="1:19">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="1:18">
       <c r="A34" s="1">
         <f t="shared" si="3"/>
         <v>2005003</v>
       </c>
-      <c r="B34" s="10">
+      <c r="B34" s="2">
         <v>200500</v>
       </c>
-      <c r="C34" s="10">
-        <v>2</v>
-      </c>
-      <c r="D34" s="10" t="s">
+      <c r="C34" s="2">
+        <v>2</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E34" s="11">
+      <c r="E34" s="9">
         <v>200500025</v>
       </c>
-      <c r="F34" s="11" t="s">
+      <c r="F34" s="9" t="s">
         <v>54</v>
       </c>
       <c r="G34" s="1" t="s">
@@ -3159,37 +2546,36 @@
       <c r="L34" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M34" s="20" t="s">
+      <c r="M34" s="16" t="s">
         <v>55</v>
       </c>
       <c r="N34">
         <v>10000000</v>
       </c>
-      <c r="O34" s="18">
+      <c r="O34" s="14">
         <v>1990000</v>
       </c>
       <c r="Q34" s="3"/>
-      <c r="R34" s="12"/>
-      <c r="S34" s="12"/>
-    </row>
-    <row r="35" spans="1:19">
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="1:18">
       <c r="A35" s="1">
         <f t="shared" si="3"/>
         <v>2006001</v>
       </c>
-      <c r="B35" s="10">
+      <c r="B35" s="2">
         <v>200600</v>
       </c>
-      <c r="C35" s="10">
-        <v>2</v>
-      </c>
-      <c r="D35" s="11" t="s">
+      <c r="C35" s="2">
+        <v>2</v>
+      </c>
+      <c r="D35" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="E35" s="11">
+      <c r="E35" s="9">
         <v>200600001</v>
       </c>
-      <c r="F35" s="11" t="s">
+      <c r="F35" s="9" t="s">
         <v>57</v>
       </c>
       <c r="G35" s="1" t="s">
@@ -3210,37 +2596,36 @@
       <c r="L35" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M35" s="20" t="s">
+      <c r="M35" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N35">
         <v>1000</v>
       </c>
-      <c r="O35" s="18">
+      <c r="O35" s="14">
         <v>1990000</v>
       </c>
       <c r="Q35" s="3"/>
-      <c r="R35" s="12"/>
-      <c r="S35" s="12"/>
-    </row>
-    <row r="36" s="1" customFormat="1" spans="1:19">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="36" spans="1:18">
       <c r="A36" s="1">
         <f t="shared" si="3"/>
         <v>2006002</v>
       </c>
-      <c r="B36" s="10">
+      <c r="B36" s="2">
         <v>200600</v>
       </c>
-      <c r="C36" s="10">
-        <v>2</v>
-      </c>
-      <c r="D36" s="11" t="s">
+      <c r="C36" s="2">
+        <v>2</v>
+      </c>
+      <c r="D36" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="E36" s="11">
+      <c r="E36" s="9">
         <v>200600001</v>
       </c>
-      <c r="F36" s="11" t="s">
+      <c r="F36" s="9" t="s">
         <v>57</v>
       </c>
       <c r="G36" s="1" t="s">
@@ -3261,37 +2646,36 @@
       <c r="L36" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M36" s="20" t="s">
+      <c r="M36" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N36">
         <v>100000</v>
       </c>
-      <c r="O36" s="18">
+      <c r="O36" s="14">
         <v>1990000</v>
       </c>
       <c r="Q36" s="3"/>
-      <c r="R36" s="12"/>
-      <c r="S36" s="12"/>
-    </row>
-    <row r="37" s="1" customFormat="1" spans="1:19">
+      <c r="R36" s="3"/>
+    </row>
+    <row r="37" spans="1:18">
       <c r="A37" s="1">
         <f t="shared" si="3"/>
         <v>2006003</v>
       </c>
-      <c r="B37" s="10">
+      <c r="B37" s="2">
         <v>200600</v>
       </c>
-      <c r="C37" s="10">
-        <v>2</v>
-      </c>
-      <c r="D37" s="11" t="s">
+      <c r="C37" s="2">
+        <v>2</v>
+      </c>
+      <c r="D37" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="E37" s="11">
+      <c r="E37" s="9">
         <v>200600001</v>
       </c>
-      <c r="F37" s="11" t="s">
+      <c r="F37" s="9" t="s">
         <v>57</v>
       </c>
       <c r="G37" s="1" t="s">
@@ -3312,37 +2696,36 @@
       <c r="L37" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M37" s="20" t="s">
+      <c r="M37" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N37">
         <v>10000000</v>
       </c>
-      <c r="O37" s="18">
+      <c r="O37" s="14">
         <v>1990000</v>
       </c>
       <c r="Q37" s="3"/>
       <c r="R37"/>
-      <c r="S37" s="12"/>
-    </row>
-    <row r="38" spans="1:19">
+    </row>
+    <row r="38" spans="1:18">
       <c r="A38" s="1">
         <f t="shared" si="3"/>
         <v>2007001</v>
       </c>
-      <c r="B38" s="10">
+      <c r="B38" s="2">
         <v>200700</v>
       </c>
-      <c r="C38" s="10">
-        <v>2</v>
-      </c>
-      <c r="D38" s="10" t="s">
+      <c r="C38" s="2">
+        <v>2</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E38" s="11">
+      <c r="E38" s="9">
         <v>200700001</v>
       </c>
-      <c r="F38" s="11" t="s">
+      <c r="F38" s="9" t="s">
         <v>59</v>
       </c>
       <c r="G38" s="1" t="s">
@@ -3363,38 +2746,37 @@
       <c r="L38" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M38" s="20" t="s">
+      <c r="M38" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N38">
         <v>1000</v>
       </c>
-      <c r="O38" s="18">
+      <c r="O38" s="14">
         <v>1990000</v>
       </c>
       <c r="Q38" s="3"/>
-      <c r="R38" s="12"/>
-      <c r="S38" s="12"/>
-    </row>
-    <row r="39" s="1" customFormat="1" spans="1:19">
+      <c r="R38" s="3"/>
+    </row>
+    <row r="39" spans="1:18">
       <c r="A39" s="1">
         <f t="shared" si="3"/>
         <v>2007002</v>
       </c>
-      <c r="B39" s="10">
+      <c r="B39" s="2">
         <v>200700</v>
       </c>
-      <c r="C39" s="10">
-        <v>2</v>
-      </c>
-      <c r="D39" s="10" t="str">
-        <f t="shared" ref="D36:D40" si="5">D38</f>
+      <c r="C39" s="2">
+        <v>2</v>
+      </c>
+      <c r="D39" s="2" t="str">
+        <f t="shared" ref="D39:D40" si="5">D38</f>
         <v>越南色碟</v>
       </c>
-      <c r="E39" s="11">
+      <c r="E39" s="9">
         <v>200700001</v>
       </c>
-      <c r="F39" s="11" t="s">
+      <c r="F39" s="9" t="s">
         <v>59</v>
       </c>
       <c r="G39" s="1" t="s">
@@ -3415,38 +2797,37 @@
       <c r="L39" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M39" s="20" t="s">
+      <c r="M39" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N39">
         <v>100000</v>
       </c>
-      <c r="O39" s="18">
+      <c r="O39" s="14">
         <v>1990000</v>
       </c>
       <c r="Q39" s="3"/>
-      <c r="R39" s="12"/>
-      <c r="S39" s="12"/>
-    </row>
-    <row r="40" s="1" customFormat="1" spans="1:19">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="1:18">
       <c r="A40" s="1">
         <f t="shared" si="3"/>
         <v>2007003</v>
       </c>
-      <c r="B40" s="10">
+      <c r="B40" s="2">
         <v>200700</v>
       </c>
-      <c r="C40" s="10">
-        <v>2</v>
-      </c>
-      <c r="D40" s="10" t="str">
+      <c r="C40" s="2">
+        <v>2</v>
+      </c>
+      <c r="D40" s="2" t="str">
         <f t="shared" si="5"/>
         <v>越南色碟</v>
       </c>
-      <c r="E40" s="11">
+      <c r="E40" s="9">
         <v>200700001</v>
       </c>
-      <c r="F40" s="11" t="s">
+      <c r="F40" s="9" t="s">
         <v>59</v>
       </c>
       <c r="G40" s="1" t="s">
@@ -3467,35 +2848,34 @@
       <c r="L40" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M40" s="20" t="s">
+      <c r="M40" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N40">
         <v>10000000</v>
       </c>
-      <c r="O40" s="18">
+      <c r="O40" s="14">
         <v>1990000</v>
       </c>
-      <c r="S40" s="3"/>
-    </row>
-    <row r="41" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="41" spans="1:18">
       <c r="A41" s="1">
         <f t="shared" si="3"/>
         <v>2008001</v>
       </c>
-      <c r="B41" s="10">
+      <c r="B41" s="2">
         <v>200800</v>
       </c>
-      <c r="C41" s="10">
-        <v>2</v>
-      </c>
-      <c r="D41" s="11" t="s">
+      <c r="C41" s="2">
+        <v>2</v>
+      </c>
+      <c r="D41" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E41" s="11">
+      <c r="E41" s="9">
         <v>200800001</v>
       </c>
-      <c r="F41" s="11" t="s">
+      <c r="F41" s="9" t="s">
         <v>61</v>
       </c>
       <c r="G41" s="1" t="s">
@@ -3516,35 +2896,34 @@
       <c r="L41" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M41" s="20" t="s">
+      <c r="M41" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N41">
         <v>1000</v>
       </c>
-      <c r="O41" s="18">
+      <c r="O41" s="14">
         <v>1990000</v>
       </c>
-      <c r="S41" s="3"/>
-    </row>
-    <row r="42" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="42" spans="1:18">
       <c r="A42" s="1">
         <f t="shared" si="3"/>
         <v>2008002</v>
       </c>
-      <c r="B42" s="10">
+      <c r="B42" s="2">
         <v>200800</v>
       </c>
-      <c r="C42" s="10">
-        <v>2</v>
-      </c>
-      <c r="D42" s="11" t="s">
+      <c r="C42" s="2">
+        <v>2</v>
+      </c>
+      <c r="D42" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E42" s="11">
+      <c r="E42" s="9">
         <v>200800001</v>
       </c>
-      <c r="F42" s="11" t="s">
+      <c r="F42" s="9" t="s">
         <v>61</v>
       </c>
       <c r="G42" s="1" t="s">
@@ -3565,35 +2944,34 @@
       <c r="L42" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M42" s="20" t="s">
+      <c r="M42" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N42">
         <v>100000</v>
       </c>
-      <c r="O42" s="18">
+      <c r="O42" s="14">
         <v>1990000</v>
       </c>
-      <c r="S42" s="3"/>
-    </row>
-    <row r="43" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="43" spans="1:18">
       <c r="A43" s="1">
         <f t="shared" si="3"/>
         <v>2008003</v>
       </c>
-      <c r="B43" s="10">
+      <c r="B43" s="2">
         <v>200800</v>
       </c>
-      <c r="C43" s="10">
-        <v>2</v>
-      </c>
-      <c r="D43" s="11" t="s">
+      <c r="C43" s="2">
+        <v>2</v>
+      </c>
+      <c r="D43" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E43" s="11">
+      <c r="E43" s="9">
         <v>200800001</v>
       </c>
-      <c r="F43" s="11" t="s">
+      <c r="F43" s="9" t="s">
         <v>61</v>
       </c>
       <c r="G43" s="1" t="s">
@@ -3614,35 +2992,34 @@
       <c r="L43" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M43" s="20" t="s">
+      <c r="M43" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N43">
         <v>10000000</v>
       </c>
-      <c r="O43" s="18">
+      <c r="O43" s="14">
         <v>1990000</v>
       </c>
-      <c r="S43" s="3"/>
-    </row>
-    <row r="44" spans="1:15">
+    </row>
+    <row r="44" spans="1:18">
       <c r="A44" s="1">
         <f t="shared" si="3"/>
         <v>2009001</v>
       </c>
-      <c r="B44" s="13">
+      <c r="B44" s="10">
         <v>200900</v>
       </c>
-      <c r="C44" s="10">
-        <v>2</v>
-      </c>
-      <c r="D44" s="13" t="s">
+      <c r="C44" s="2">
+        <v>2</v>
+      </c>
+      <c r="D44" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="E44" s="11">
+      <c r="E44" s="9">
         <v>200900001</v>
       </c>
-      <c r="F44" s="11" t="s">
+      <c r="F44" s="9" t="s">
         <v>63</v>
       </c>
       <c r="G44" s="1" t="s">
@@ -3663,35 +3040,35 @@
       <c r="L44" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M44" s="20" t="s">
+      <c r="M44" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N44">
         <v>1000</v>
       </c>
-      <c r="O44" s="18">
+      <c r="O44" s="14">
         <v>1990000</v>
       </c>
     </row>
-    <row r="45" spans="1:15">
+    <row r="45" spans="1:18">
       <c r="A45" s="1">
         <f t="shared" si="3"/>
         <v>2009002</v>
       </c>
-      <c r="B45" s="10">
+      <c r="B45" s="2">
         <v>200900</v>
       </c>
-      <c r="C45" s="10">
-        <v>2</v>
-      </c>
-      <c r="D45" s="10" t="str">
+      <c r="C45" s="2">
+        <v>2</v>
+      </c>
+      <c r="D45" s="2" t="str">
         <f>D44</f>
         <v>魚蝦蟹</v>
       </c>
-      <c r="E45" s="11">
+      <c r="E45" s="9">
         <v>200900001</v>
       </c>
-      <c r="F45" s="11" t="s">
+      <c r="F45" s="9" t="s">
         <v>63</v>
       </c>
       <c r="G45" s="1" t="s">
@@ -3712,35 +3089,35 @@
       <c r="L45" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M45" s="20" t="s">
+      <c r="M45" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N45">
         <v>100000</v>
       </c>
-      <c r="O45" s="18">
+      <c r="O45" s="14">
         <v>1990000</v>
       </c>
     </row>
-    <row r="46" spans="1:15">
+    <row r="46" spans="1:18">
       <c r="A46" s="1">
         <f t="shared" si="3"/>
         <v>2009003</v>
       </c>
-      <c r="B46" s="10">
+      <c r="B46" s="2">
         <v>200900</v>
       </c>
-      <c r="C46" s="10">
-        <v>2</v>
-      </c>
-      <c r="D46" s="10" t="str">
+      <c r="C46" s="2">
+        <v>2</v>
+      </c>
+      <c r="D46" s="2" t="str">
         <f>D45</f>
         <v>魚蝦蟹</v>
       </c>
-      <c r="E46" s="11">
+      <c r="E46" s="9">
         <v>200900001</v>
       </c>
-      <c r="F46" s="11" t="s">
+      <c r="F46" s="9" t="s">
         <v>63</v>
       </c>
       <c r="G46" s="1" t="s">
@@ -3761,34 +3138,34 @@
       <c r="L46" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M46" s="20" t="s">
+      <c r="M46" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N46">
         <v>10000000</v>
       </c>
-      <c r="O46" s="18">
+      <c r="O46" s="14">
         <v>1990000</v>
       </c>
     </row>
-    <row r="47" spans="1:15">
+    <row r="47" spans="1:18">
       <c r="A47" s="1">
         <f t="shared" si="3"/>
         <v>2010001</v>
       </c>
-      <c r="B47" s="10">
+      <c r="B47" s="2">
         <v>201000</v>
       </c>
-      <c r="C47" s="10">
-        <v>2</v>
-      </c>
-      <c r="D47" s="10" t="s">
+      <c r="C47" s="2">
+        <v>2</v>
+      </c>
+      <c r="D47" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E47" s="11">
+      <c r="E47" s="9">
         <v>101000006</v>
       </c>
-      <c r="F47" s="11"/>
+      <c r="F47" s="9"/>
       <c r="G47" s="1" t="s">
         <v>32</v>
       </c>
@@ -3807,34 +3184,34 @@
       <c r="L47" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M47" s="20" t="s">
+      <c r="M47" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N47">
         <v>1000</v>
       </c>
-      <c r="O47" s="18">
+      <c r="O47" s="14">
         <v>1990000</v>
       </c>
     </row>
-    <row r="48" spans="1:15">
+    <row r="48" spans="1:18">
       <c r="A48" s="1">
         <f t="shared" si="3"/>
         <v>2010002</v>
       </c>
-      <c r="B48" s="10">
+      <c r="B48" s="2">
         <v>201000</v>
       </c>
-      <c r="C48" s="10">
-        <v>2</v>
-      </c>
-      <c r="D48" s="10" t="s">
+      <c r="C48" s="2">
+        <v>2</v>
+      </c>
+      <c r="D48" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E48" s="11">
+      <c r="E48" s="9">
         <v>101000006</v>
       </c>
-      <c r="F48" s="11"/>
+      <c r="F48" s="9"/>
       <c r="G48" s="1" t="s">
         <v>35</v>
       </c>
@@ -3853,13 +3230,13 @@
       <c r="L48" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M48" s="20" t="s">
+      <c r="M48" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N48">
         <v>100000</v>
       </c>
-      <c r="O48" s="18">
+      <c r="O48" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -3868,19 +3245,19 @@
         <f t="shared" si="3"/>
         <v>2010003</v>
       </c>
-      <c r="B49" s="10">
+      <c r="B49" s="2">
         <v>201000</v>
       </c>
-      <c r="C49" s="10">
-        <v>2</v>
-      </c>
-      <c r="D49" s="10" t="s">
+      <c r="C49" s="2">
+        <v>2</v>
+      </c>
+      <c r="D49" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E49" s="11">
+      <c r="E49" s="9">
         <v>101000006</v>
       </c>
-      <c r="F49" s="11"/>
+      <c r="F49" s="9"/>
       <c r="G49" s="1" t="s">
         <v>36</v>
       </c>
@@ -3899,13 +3276,13 @@
       <c r="L49" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M49" s="20" t="s">
+      <c r="M49" s="16" t="s">
         <v>34</v>
       </c>
       <c r="N49">
         <v>10000000</v>
       </c>
-      <c r="O49" s="18">
+      <c r="O49" s="14">
         <v>1990000</v>
       </c>
     </row>
@@ -3914,19 +3291,19 @@
         <f t="shared" si="3"/>
         <v>3001001</v>
       </c>
-      <c r="B50" s="10">
+      <c r="B50" s="2">
         <v>300100</v>
       </c>
-      <c r="C50" s="10">
+      <c r="C50" s="2">
         <v>3</v>
       </c>
-      <c r="D50" s="10" t="s">
+      <c r="D50" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E50" s="11">
+      <c r="E50" s="9">
         <v>300100001</v>
       </c>
-      <c r="F50" s="11" t="s">
+      <c r="F50" s="9" t="s">
         <v>66</v>
       </c>
       <c r="G50" s="1" t="s">
@@ -3944,37 +3321,37 @@
       <c r="K50" s="1">
         <v>0</v>
       </c>
-      <c r="L50" s="21" t="s">
+      <c r="L50" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="M50" s="21" t="s">
+      <c r="M50" s="17" t="s">
         <v>68</v>
       </c>
       <c r="N50">
         <v>500</v>
       </c>
-      <c r="O50" s="18">
+      <c r="O50" s="14">
         <v>1990000</v>
       </c>
     </row>
-    <row r="51" s="1" customFormat="1" spans="1:19">
+    <row r="51" spans="1:15">
       <c r="A51" s="1">
         <f t="shared" si="3"/>
         <v>3001002</v>
       </c>
-      <c r="B51" s="10">
+      <c r="B51" s="2">
         <v>300100</v>
       </c>
-      <c r="C51" s="10">
+      <c r="C51" s="2">
         <v>3</v>
       </c>
-      <c r="D51" s="10" t="s">
+      <c r="D51" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E51" s="11">
+      <c r="E51" s="9">
         <v>300100001</v>
       </c>
-      <c r="F51" s="11" t="s">
+      <c r="F51" s="9" t="s">
         <v>66</v>
       </c>
       <c r="G51" s="1" t="s">
@@ -3992,38 +3369,37 @@
       <c r="K51" s="1">
         <v>0</v>
       </c>
-      <c r="L51" s="21" t="s">
+      <c r="L51" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="M51" s="21" t="s">
+      <c r="M51" s="17" t="s">
         <v>68</v>
       </c>
       <c r="N51">
         <v>20000</v>
       </c>
-      <c r="O51" s="18">
+      <c r="O51" s="14">
         <v>1990000</v>
       </c>
-      <c r="S51" s="3"/>
-    </row>
-    <row r="52" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="52" spans="1:15">
       <c r="A52" s="1">
         <f t="shared" si="3"/>
         <v>3001003</v>
       </c>
-      <c r="B52" s="10">
+      <c r="B52" s="2">
         <v>300100</v>
       </c>
-      <c r="C52" s="10">
+      <c r="C52" s="2">
         <v>3</v>
       </c>
-      <c r="D52" s="10" t="s">
+      <c r="D52" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E52" s="11">
+      <c r="E52" s="9">
         <v>300100001</v>
       </c>
-      <c r="F52" s="11" t="s">
+      <c r="F52" s="9" t="s">
         <v>66</v>
       </c>
       <c r="G52" s="1" t="s">
@@ -4041,38 +3417,37 @@
       <c r="K52" s="1">
         <v>0</v>
       </c>
-      <c r="L52" s="21" t="s">
+      <c r="L52" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="M52" s="21" t="s">
+      <c r="M52" s="17" t="s">
         <v>68</v>
       </c>
       <c r="N52">
         <v>2000000</v>
       </c>
-      <c r="O52" s="18">
+      <c r="O52" s="14">
         <v>1990000</v>
       </c>
-      <c r="S52" s="3"/>
-    </row>
-    <row r="53" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="53" spans="1:15">
       <c r="A53" s="1">
         <f t="shared" si="3"/>
         <v>3002001</v>
       </c>
-      <c r="B53" s="10">
+      <c r="B53" s="2">
         <v>300200</v>
       </c>
-      <c r="C53" s="10">
+      <c r="C53" s="2">
         <v>3</v>
       </c>
-      <c r="D53" s="10" t="s">
+      <c r="D53" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E53" s="11">
+      <c r="E53" s="9">
         <v>300200006</v>
       </c>
-      <c r="F53" s="11" t="s">
+      <c r="F53" s="9" t="s">
         <v>70</v>
       </c>
       <c r="G53" s="1" t="s">
@@ -4090,38 +3465,37 @@
       <c r="K53" s="1">
         <v>0</v>
       </c>
-      <c r="L53" s="21" t="s">
+      <c r="L53" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="M53" s="21" t="s">
+      <c r="M53" s="17" t="s">
         <v>68</v>
       </c>
       <c r="N53">
         <v>500</v>
       </c>
-      <c r="O53" s="18">
+      <c r="O53" s="14">
         <v>1990000</v>
       </c>
-      <c r="S53" s="3"/>
-    </row>
-    <row r="54" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="54" spans="1:15">
       <c r="A54" s="1">
         <f t="shared" si="3"/>
         <v>3002002</v>
       </c>
-      <c r="B54" s="10">
+      <c r="B54" s="2">
         <v>300200</v>
       </c>
-      <c r="C54" s="10">
+      <c r="C54" s="2">
         <v>3</v>
       </c>
-      <c r="D54" s="10" t="s">
+      <c r="D54" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E54" s="11">
+      <c r="E54" s="9">
         <v>300200006</v>
       </c>
-      <c r="F54" s="11" t="s">
+      <c r="F54" s="9" t="s">
         <v>70</v>
       </c>
       <c r="G54" s="1" t="s">
@@ -4139,38 +3513,37 @@
       <c r="K54" s="1">
         <v>0</v>
       </c>
-      <c r="L54" s="21" t="s">
+      <c r="L54" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="M54" s="21" t="s">
+      <c r="M54" s="17" t="s">
         <v>68</v>
       </c>
       <c r="N54">
         <v>20000</v>
       </c>
-      <c r="O54" s="18">
+      <c r="O54" s="14">
         <v>1990000</v>
       </c>
-      <c r="S54" s="3"/>
-    </row>
-    <row r="55" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="55" spans="1:15">
       <c r="A55" s="1">
         <f t="shared" si="3"/>
         <v>3002003</v>
       </c>
-      <c r="B55" s="10">
+      <c r="B55" s="2">
         <v>300200</v>
       </c>
-      <c r="C55" s="10">
+      <c r="C55" s="2">
         <v>3</v>
       </c>
-      <c r="D55" s="10" t="s">
+      <c r="D55" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E55" s="11">
+      <c r="E55" s="9">
         <v>300200006</v>
       </c>
-      <c r="F55" s="11" t="s">
+      <c r="F55" s="9" t="s">
         <v>70</v>
       </c>
       <c r="G55" s="1" t="s">
@@ -4188,848 +3561,832 @@
       <c r="K55" s="1">
         <v>0</v>
       </c>
-      <c r="L55" s="21" t="s">
+      <c r="L55" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="M55" s="21" t="s">
+      <c r="M55" s="17" t="s">
         <v>68</v>
       </c>
       <c r="N55">
         <v>2000000</v>
       </c>
-      <c r="O55" s="18">
+      <c r="O55" s="14">
         <v>1990000</v>
       </c>
-      <c r="S55" s="3"/>
-    </row>
-    <row r="56" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="56" spans="1:15">
       <c r="A56" s="1">
         <f t="shared" ref="A56:A62" si="6">B56*100+H56</f>
         <v>20010010</v>
       </c>
-      <c r="B56" s="11">
+      <c r="B56" s="9">
         <v>200100</v>
       </c>
-      <c r="C56" s="11">
-        <v>2</v>
-      </c>
-      <c r="D56" s="11" t="s">
+      <c r="C56" s="9">
+        <v>2</v>
+      </c>
+      <c r="D56" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="E56" s="11">
+      <c r="E56" s="9">
         <v>200100038</v>
       </c>
-      <c r="F56" s="11" t="s">
+      <c r="F56" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G56" s="14" t="s">
+      <c r="G56" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="H56" s="14">
+      <c r="H56" s="11">
         <v>10</v>
       </c>
-      <c r="I56" s="14">
-        <v>0</v>
-      </c>
-      <c r="J56" s="14">
+      <c r="I56" s="11">
+        <v>0</v>
+      </c>
+      <c r="J56" s="11">
         <v>-1</v>
       </c>
       <c r="K56" s="1">
         <v>0</v>
       </c>
-      <c r="L56" s="14" t="s">
+      <c r="L56" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="M56" s="14">
+      <c r="M56" s="11">
         <v>0</v>
       </c>
       <c r="N56">
         <v>100</v>
       </c>
-      <c r="O56" s="19">
+      <c r="O56" s="15">
         <v>1980000</v>
       </c>
-      <c r="S56" s="3"/>
-    </row>
-    <row r="57" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="57" spans="1:15">
       <c r="A57" s="1">
         <f t="shared" si="6"/>
         <v>20010011</v>
       </c>
-      <c r="B57" s="11">
+      <c r="B57" s="9">
         <v>200100</v>
       </c>
-      <c r="C57" s="11">
-        <v>2</v>
-      </c>
-      <c r="D57" s="11" t="s">
+      <c r="C57" s="9">
+        <v>2</v>
+      </c>
+      <c r="D57" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="E57" s="11">
+      <c r="E57" s="9">
         <v>200100038</v>
       </c>
-      <c r="F57" s="11" t="s">
+      <c r="F57" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G57" s="14" t="s">
+      <c r="G57" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="H57" s="14">
+      <c r="H57" s="11">
         <v>11</v>
       </c>
-      <c r="I57" s="14">
-        <v>0</v>
-      </c>
-      <c r="J57" s="14">
+      <c r="I57" s="11">
+        <v>0</v>
+      </c>
+      <c r="J57" s="11">
         <v>-1</v>
       </c>
       <c r="K57" s="1">
         <v>0</v>
       </c>
-      <c r="L57" s="14" t="s">
+      <c r="L57" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="M57" s="14">
+      <c r="M57" s="11">
         <v>0</v>
       </c>
       <c r="N57">
         <v>100</v>
       </c>
-      <c r="O57" s="19">
+      <c r="O57" s="15">
         <v>1980000</v>
       </c>
-      <c r="S57" s="3"/>
-    </row>
-    <row r="58" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="58" spans="1:15">
       <c r="A58" s="1">
         <f t="shared" si="6"/>
         <v>20010012</v>
       </c>
-      <c r="B58" s="11">
+      <c r="B58" s="9">
         <v>200100</v>
       </c>
-      <c r="C58" s="11">
-        <v>2</v>
-      </c>
-      <c r="D58" s="11" t="s">
+      <c r="C58" s="9">
+        <v>2</v>
+      </c>
+      <c r="D58" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="E58" s="11">
+      <c r="E58" s="9">
         <v>200100038</v>
       </c>
-      <c r="F58" s="11" t="s">
+      <c r="F58" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G58" s="14" t="s">
+      <c r="G58" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="H58" s="14">
+      <c r="H58" s="11">
         <v>12</v>
       </c>
-      <c r="I58" s="14">
-        <v>0</v>
-      </c>
-      <c r="J58" s="14">
+      <c r="I58" s="11">
+        <v>0</v>
+      </c>
+      <c r="J58" s="11">
         <v>-1</v>
       </c>
       <c r="K58" s="1">
         <v>0</v>
       </c>
-      <c r="L58" s="14" t="s">
+      <c r="L58" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="M58" s="14">
+      <c r="M58" s="11">
         <v>0</v>
       </c>
       <c r="N58">
         <v>100</v>
       </c>
-      <c r="O58" s="19">
+      <c r="O58" s="15">
         <v>1980000</v>
       </c>
-      <c r="S58" s="3"/>
-    </row>
-    <row r="59" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="59" spans="1:15">
       <c r="A59" s="1">
         <f t="shared" si="6"/>
         <v>20010110</v>
       </c>
-      <c r="B59" s="11">
+      <c r="B59" s="9">
         <v>200101</v>
       </c>
-      <c r="C59" s="11">
-        <v>2</v>
-      </c>
-      <c r="D59" s="11" t="s">
+      <c r="C59" s="9">
+        <v>2</v>
+      </c>
+      <c r="D59" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E59" s="11">
+      <c r="E59" s="9">
         <v>200101001</v>
       </c>
-      <c r="F59" s="11" t="s">
+      <c r="F59" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="G59" s="14" t="s">
+      <c r="G59" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="H59" s="14">
+      <c r="H59" s="11">
         <v>10</v>
       </c>
-      <c r="I59" s="14">
-        <v>0</v>
-      </c>
-      <c r="J59" s="14">
+      <c r="I59" s="11">
+        <v>0</v>
+      </c>
+      <c r="J59" s="11">
         <v>-1</v>
       </c>
       <c r="K59" s="1">
         <v>0</v>
       </c>
-      <c r="L59" s="14" t="s">
+      <c r="L59" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="M59" s="14">
+      <c r="M59" s="11">
         <v>0</v>
       </c>
       <c r="N59">
         <v>100</v>
       </c>
-      <c r="O59" s="19">
+      <c r="O59" s="15">
         <v>1980000</v>
       </c>
-      <c r="S59" s="3"/>
-    </row>
-    <row r="60" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="60" spans="1:15">
       <c r="A60" s="1">
         <f t="shared" si="6"/>
         <v>20010111</v>
       </c>
-      <c r="B60" s="11">
+      <c r="B60" s="9">
         <v>200101</v>
       </c>
-      <c r="C60" s="11">
-        <v>2</v>
-      </c>
-      <c r="D60" s="11" t="s">
+      <c r="C60" s="9">
+        <v>2</v>
+      </c>
+      <c r="D60" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E60" s="11">
+      <c r="E60" s="9">
         <v>200101001</v>
       </c>
-      <c r="F60" s="11" t="s">
+      <c r="F60" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="G60" s="14" t="s">
+      <c r="G60" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="H60" s="14">
+      <c r="H60" s="11">
         <v>11</v>
       </c>
-      <c r="I60" s="14">
-        <v>0</v>
-      </c>
-      <c r="J60" s="14">
+      <c r="I60" s="11">
+        <v>0</v>
+      </c>
+      <c r="J60" s="11">
         <v>-1</v>
       </c>
       <c r="K60" s="1">
         <v>0</v>
       </c>
-      <c r="L60" s="14" t="s">
+      <c r="L60" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="M60" s="14">
+      <c r="M60" s="11">
         <v>0</v>
       </c>
       <c r="N60">
         <v>100</v>
       </c>
-      <c r="O60" s="19">
+      <c r="O60" s="15">
         <v>1980000</v>
       </c>
-      <c r="S60" s="3"/>
-    </row>
-    <row r="61" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="61" spans="1:15">
       <c r="A61" s="1">
         <f t="shared" si="6"/>
         <v>20010112</v>
       </c>
-      <c r="B61" s="11">
+      <c r="B61" s="9">
         <v>200101</v>
       </c>
-      <c r="C61" s="11">
-        <v>2</v>
-      </c>
-      <c r="D61" s="11" t="s">
+      <c r="C61" s="9">
+        <v>2</v>
+      </c>
+      <c r="D61" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E61" s="11">
+      <c r="E61" s="9">
         <v>200101001</v>
       </c>
-      <c r="F61" s="11" t="s">
+      <c r="F61" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="G61" s="14" t="s">
+      <c r="G61" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="H61" s="14">
+      <c r="H61" s="11">
         <v>12</v>
       </c>
-      <c r="I61" s="14">
-        <v>0</v>
-      </c>
-      <c r="J61" s="14">
+      <c r="I61" s="11">
+        <v>0</v>
+      </c>
+      <c r="J61" s="11">
         <v>-1</v>
       </c>
       <c r="K61" s="1">
         <v>0</v>
       </c>
-      <c r="L61" s="14" t="s">
+      <c r="L61" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="M61" s="14">
+      <c r="M61" s="11">
         <v>0</v>
       </c>
       <c r="N61">
         <v>100</v>
       </c>
-      <c r="O61" s="19">
+      <c r="O61" s="15">
         <v>1980000</v>
       </c>
-      <c r="S61" s="3"/>
-    </row>
-    <row r="62" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="62" spans="1:15">
       <c r="A62" s="1">
         <f t="shared" si="6"/>
         <v>20030010</v>
       </c>
-      <c r="B62" s="11">
+      <c r="B62" s="9">
         <v>200300</v>
       </c>
-      <c r="C62" s="11">
-        <v>2</v>
-      </c>
-      <c r="D62" s="11" t="s">
+      <c r="C62" s="9">
+        <v>2</v>
+      </c>
+      <c r="D62" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="E62" s="11">
+      <c r="E62" s="9">
         <v>200300001</v>
       </c>
-      <c r="F62" s="11" t="s">
+      <c r="F62" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="G62" s="14" t="s">
+      <c r="G62" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="H62" s="14">
+      <c r="H62" s="11">
         <v>10</v>
       </c>
-      <c r="I62" s="14">
-        <v>0</v>
-      </c>
-      <c r="J62" s="14">
+      <c r="I62" s="11">
+        <v>0</v>
+      </c>
+      <c r="J62" s="11">
         <v>-1</v>
       </c>
       <c r="K62" s="1">
         <v>0</v>
       </c>
-      <c r="L62" s="14" t="s">
+      <c r="L62" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="M62" s="14">
+      <c r="M62" s="11">
         <v>0</v>
       </c>
       <c r="N62">
         <v>100</v>
       </c>
-      <c r="O62" s="19">
+      <c r="O62" s="15">
         <v>1980000</v>
       </c>
-      <c r="S62" s="3"/>
-    </row>
-    <row r="63" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="63" spans="1:15">
       <c r="A63" s="1">
         <f t="shared" ref="A63:A71" si="7">B63*100+H63</f>
         <v>20030011</v>
       </c>
-      <c r="B63" s="11">
+      <c r="B63" s="9">
         <v>200300</v>
       </c>
-      <c r="C63" s="11">
-        <v>2</v>
-      </c>
-      <c r="D63" s="11" t="s">
+      <c r="C63" s="9">
+        <v>2</v>
+      </c>
+      <c r="D63" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="E63" s="11">
+      <c r="E63" s="9">
         <v>200300001</v>
       </c>
-      <c r="F63" s="11" t="s">
+      <c r="F63" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="G63" s="14" t="s">
+      <c r="G63" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="H63" s="14">
+      <c r="H63" s="11">
         <v>11</v>
       </c>
-      <c r="I63" s="14">
-        <v>0</v>
-      </c>
-      <c r="J63" s="14">
+      <c r="I63" s="11">
+        <v>0</v>
+      </c>
+      <c r="J63" s="11">
         <v>-1</v>
       </c>
       <c r="K63" s="1">
         <v>0</v>
       </c>
-      <c r="L63" s="14" t="s">
+      <c r="L63" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="M63" s="14">
+      <c r="M63" s="11">
         <v>0</v>
       </c>
       <c r="N63">
         <v>100</v>
       </c>
-      <c r="O63" s="19">
+      <c r="O63" s="15">
         <v>1980000</v>
       </c>
-      <c r="S63" s="3"/>
-    </row>
-    <row r="64" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="64" spans="1:15">
       <c r="A64" s="1">
         <f t="shared" si="7"/>
         <v>20030012</v>
       </c>
-      <c r="B64" s="11">
+      <c r="B64" s="9">
         <v>200300</v>
       </c>
-      <c r="C64" s="11">
-        <v>2</v>
-      </c>
-      <c r="D64" s="11" t="s">
+      <c r="C64" s="9">
+        <v>2</v>
+      </c>
+      <c r="D64" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="E64" s="11">
+      <c r="E64" s="9">
         <v>200300001</v>
       </c>
-      <c r="F64" s="11" t="s">
+      <c r="F64" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="G64" s="14" t="s">
+      <c r="G64" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="H64" s="14">
+      <c r="H64" s="11">
         <v>12</v>
       </c>
-      <c r="I64" s="14">
-        <v>0</v>
-      </c>
-      <c r="J64" s="14">
+      <c r="I64" s="11">
+        <v>0</v>
+      </c>
+      <c r="J64" s="11">
         <v>-1</v>
       </c>
       <c r="K64" s="1">
         <v>0</v>
       </c>
-      <c r="L64" s="14" t="s">
+      <c r="L64" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="M64" s="14">
+      <c r="M64" s="11">
         <v>0</v>
       </c>
       <c r="N64">
         <v>100</v>
       </c>
-      <c r="O64" s="19">
+      <c r="O64" s="15">
         <v>1980000</v>
       </c>
-      <c r="S64" s="3"/>
-    </row>
-    <row r="65" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="65" spans="1:15">
       <c r="A65" s="1">
         <f t="shared" si="7"/>
         <v>20040010</v>
       </c>
-      <c r="B65" s="11">
+      <c r="B65" s="9">
         <v>200400</v>
       </c>
-      <c r="C65" s="11">
-        <v>2</v>
-      </c>
-      <c r="D65" s="12" t="s">
+      <c r="C65" s="9">
+        <v>2</v>
+      </c>
+      <c r="D65" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E65" s="11">
+      <c r="E65" s="9">
         <v>200400009</v>
       </c>
-      <c r="F65" s="11" t="s">
+      <c r="F65" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="G65" s="14" t="s">
+      <c r="G65" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="H65" s="14">
+      <c r="H65" s="11">
         <v>10</v>
       </c>
-      <c r="I65" s="14">
-        <v>0</v>
-      </c>
-      <c r="J65" s="14">
+      <c r="I65" s="11">
+        <v>0</v>
+      </c>
+      <c r="J65" s="11">
         <v>-1</v>
       </c>
       <c r="K65" s="1">
         <v>0</v>
       </c>
-      <c r="L65" s="14" t="s">
+      <c r="L65" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="M65" s="14">
+      <c r="M65" s="11">
         <v>0</v>
       </c>
       <c r="N65">
         <v>100</v>
       </c>
-      <c r="O65" s="19">
+      <c r="O65" s="15">
         <v>1980000</v>
       </c>
-      <c r="S65" s="3"/>
-    </row>
-    <row r="66" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="66" spans="1:15">
       <c r="A66" s="1">
         <f t="shared" si="7"/>
         <v>20040011</v>
       </c>
-      <c r="B66" s="11">
+      <c r="B66" s="9">
         <v>200400</v>
       </c>
-      <c r="C66" s="11">
-        <v>2</v>
-      </c>
-      <c r="D66" s="12" t="s">
+      <c r="C66" s="9">
+        <v>2</v>
+      </c>
+      <c r="D66" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E66" s="11">
+      <c r="E66" s="9">
         <v>200400009</v>
       </c>
-      <c r="F66" s="11" t="s">
+      <c r="F66" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="G66" s="14" t="s">
+      <c r="G66" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="H66" s="14">
+      <c r="H66" s="11">
         <v>11</v>
       </c>
-      <c r="I66" s="14">
-        <v>0</v>
-      </c>
-      <c r="J66" s="14">
+      <c r="I66" s="11">
+        <v>0</v>
+      </c>
+      <c r="J66" s="11">
         <v>-1</v>
       </c>
       <c r="K66" s="1">
         <v>0</v>
       </c>
-      <c r="L66" s="14" t="s">
+      <c r="L66" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="M66" s="14">
+      <c r="M66" s="11">
         <v>0</v>
       </c>
       <c r="N66">
         <v>100</v>
       </c>
-      <c r="O66" s="19">
+      <c r="O66" s="15">
         <v>1980000</v>
       </c>
-      <c r="S66" s="3"/>
-    </row>
-    <row r="67" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="67" spans="1:15">
       <c r="A67" s="1">
         <f t="shared" si="7"/>
         <v>20040012</v>
       </c>
-      <c r="B67" s="11">
+      <c r="B67" s="9">
         <v>200400</v>
       </c>
-      <c r="C67" s="11">
-        <v>2</v>
-      </c>
-      <c r="D67" s="12" t="s">
+      <c r="C67" s="9">
+        <v>2</v>
+      </c>
+      <c r="D67" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E67" s="11">
+      <c r="E67" s="9">
         <v>200400009</v>
       </c>
-      <c r="F67" s="11" t="s">
+      <c r="F67" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="G67" s="14" t="s">
+      <c r="G67" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="H67" s="14">
+      <c r="H67" s="11">
         <v>12</v>
       </c>
-      <c r="I67" s="14">
-        <v>0</v>
-      </c>
-      <c r="J67" s="14">
+      <c r="I67" s="11">
+        <v>0</v>
+      </c>
+      <c r="J67" s="11">
         <v>-1</v>
       </c>
       <c r="K67" s="1">
         <v>0</v>
       </c>
-      <c r="L67" s="14" t="s">
+      <c r="L67" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="M67" s="14">
+      <c r="M67" s="11">
         <v>0</v>
       </c>
       <c r="N67">
         <v>100</v>
       </c>
-      <c r="O67" s="19">
+      <c r="O67" s="15">
         <v>1980000</v>
       </c>
-      <c r="S67" s="3"/>
-    </row>
-    <row r="68" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="68" spans="1:15">
       <c r="A68" s="1">
         <f t="shared" si="7"/>
         <v>20050010</v>
       </c>
-      <c r="B68" s="11">
+      <c r="B68" s="9">
         <v>200500</v>
       </c>
-      <c r="C68" s="11">
-        <v>2</v>
-      </c>
-      <c r="D68" s="11" t="s">
+      <c r="C68" s="9">
+        <v>2</v>
+      </c>
+      <c r="D68" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E68" s="11">
+      <c r="E68" s="9">
         <v>200500025</v>
       </c>
-      <c r="F68" s="11" t="s">
+      <c r="F68" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="G68" s="14" t="s">
+      <c r="G68" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="H68" s="14">
+      <c r="H68" s="11">
         <v>10</v>
       </c>
-      <c r="I68" s="14">
-        <v>0</v>
-      </c>
-      <c r="J68" s="14">
+      <c r="I68" s="11">
+        <v>0</v>
+      </c>
+      <c r="J68" s="11">
         <v>-1</v>
       </c>
       <c r="K68" s="1">
         <v>0</v>
       </c>
-      <c r="L68" s="14" t="s">
+      <c r="L68" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="M68" s="14">
+      <c r="M68" s="11">
         <v>0</v>
       </c>
       <c r="N68">
         <v>100</v>
       </c>
-      <c r="O68" s="19">
+      <c r="O68" s="15">
         <v>1980000</v>
       </c>
-      <c r="S68" s="3"/>
-    </row>
-    <row r="69" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="69" spans="1:15">
       <c r="A69" s="1">
         <f t="shared" si="7"/>
         <v>20050011</v>
       </c>
-      <c r="B69" s="11">
+      <c r="B69" s="9">
         <v>200500</v>
       </c>
-      <c r="C69" s="11">
-        <v>2</v>
-      </c>
-      <c r="D69" s="11" t="s">
+      <c r="C69" s="9">
+        <v>2</v>
+      </c>
+      <c r="D69" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E69" s="11">
+      <c r="E69" s="9">
         <v>200500025</v>
       </c>
-      <c r="F69" s="11" t="s">
+      <c r="F69" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="G69" s="14" t="s">
+      <c r="G69" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="H69" s="14">
+      <c r="H69" s="11">
         <v>11</v>
       </c>
-      <c r="I69" s="14">
-        <v>0</v>
-      </c>
-      <c r="J69" s="14">
+      <c r="I69" s="11">
+        <v>0</v>
+      </c>
+      <c r="J69" s="11">
         <v>-1</v>
       </c>
       <c r="K69" s="1">
         <v>0</v>
       </c>
-      <c r="L69" s="14" t="s">
+      <c r="L69" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="M69" s="14">
+      <c r="M69" s="11">
         <v>0</v>
       </c>
       <c r="N69">
         <v>100</v>
       </c>
-      <c r="O69" s="19">
+      <c r="O69" s="15">
         <v>1980000</v>
       </c>
-      <c r="S69" s="3"/>
-    </row>
-    <row r="70" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="70" spans="1:15">
       <c r="A70" s="1">
         <f t="shared" si="7"/>
         <v>20050012</v>
       </c>
-      <c r="B70" s="11">
+      <c r="B70" s="9">
         <v>200500</v>
       </c>
-      <c r="C70" s="11">
-        <v>2</v>
-      </c>
-      <c r="D70" s="11" t="s">
+      <c r="C70" s="9">
+        <v>2</v>
+      </c>
+      <c r="D70" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E70" s="11">
+      <c r="E70" s="9">
         <v>200500025</v>
       </c>
-      <c r="F70" s="11" t="s">
+      <c r="F70" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="G70" s="14" t="s">
+      <c r="G70" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="H70" s="14">
+      <c r="H70" s="11">
         <v>12</v>
       </c>
-      <c r="I70" s="14">
-        <v>0</v>
-      </c>
-      <c r="J70" s="14">
+      <c r="I70" s="11">
+        <v>0</v>
+      </c>
+      <c r="J70" s="11">
         <v>-1</v>
       </c>
       <c r="K70" s="1">
         <v>0</v>
       </c>
-      <c r="L70" s="14" t="s">
+      <c r="L70" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="M70" s="14">
+      <c r="M70" s="11">
         <v>0</v>
       </c>
       <c r="N70">
         <v>100</v>
       </c>
-      <c r="O70" s="19">
+      <c r="O70" s="15">
         <v>1980000</v>
       </c>
-      <c r="S70" s="3"/>
     </row>
     <row r="71" spans="1:15">
       <c r="A71" s="1">
         <f t="shared" si="7"/>
         <v>20060010</v>
       </c>
-      <c r="B71" s="11">
+      <c r="B71" s="9">
         <v>200600</v>
       </c>
-      <c r="C71" s="11">
-        <v>2</v>
-      </c>
-      <c r="D71" s="11" t="s">
+      <c r="C71" s="9">
+        <v>2</v>
+      </c>
+      <c r="D71" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="E71" s="11">
+      <c r="E71" s="9">
         <v>200600001</v>
       </c>
-      <c r="F71" s="11" t="s">
+      <c r="F71" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G71" s="14" t="s">
+      <c r="G71" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="H71" s="14">
+      <c r="H71" s="11">
         <v>10</v>
       </c>
-      <c r="I71" s="14">
-        <v>0</v>
-      </c>
-      <c r="J71" s="14">
+      <c r="I71" s="11">
+        <v>0</v>
+      </c>
+      <c r="J71" s="11">
         <v>-1</v>
       </c>
       <c r="K71" s="1">
         <v>0</v>
       </c>
-      <c r="L71" s="14" t="s">
+      <c r="L71" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="M71" s="14">
+      <c r="M71" s="11">
         <v>0</v>
       </c>
       <c r="N71">
         <v>100</v>
       </c>
-      <c r="O71" s="19">
+      <c r="O71" s="15">
         <v>1980000</v>
       </c>
     </row>
     <row r="72" spans="1:15">
       <c r="A72" s="1">
-        <f t="shared" ref="A72:A86" si="8">B72*100+H72</f>
+        <f t="shared" ref="A72:A85" si="8">B72*100+H72</f>
         <v>20060011</v>
       </c>
-      <c r="B72" s="11">
+      <c r="B72" s="9">
         <v>200600</v>
       </c>
-      <c r="C72" s="11">
-        <v>2</v>
-      </c>
-      <c r="D72" s="11" t="s">
+      <c r="C72" s="9">
+        <v>2</v>
+      </c>
+      <c r="D72" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="E72" s="11">
+      <c r="E72" s="9">
         <v>200600001</v>
       </c>
-      <c r="F72" s="11" t="s">
+      <c r="F72" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G72" s="14" t="s">
+      <c r="G72" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="H72" s="14">
+      <c r="H72" s="11">
         <v>11</v>
       </c>
-      <c r="I72" s="14">
-        <v>0</v>
-      </c>
-      <c r="J72" s="14">
+      <c r="I72" s="11">
+        <v>0</v>
+      </c>
+      <c r="J72" s="11">
         <v>-1</v>
       </c>
       <c r="K72" s="1">
         <v>0</v>
       </c>
-      <c r="L72" s="14" t="s">
+      <c r="L72" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="M72" s="14">
+      <c r="M72" s="11">
         <v>0</v>
       </c>
       <c r="N72">
         <v>100</v>
       </c>
-      <c r="O72" s="19">
+      <c r="O72" s="15">
         <v>1980000</v>
       </c>
     </row>
@@ -5038,46 +4395,46 @@
         <f t="shared" si="8"/>
         <v>20060012</v>
       </c>
-      <c r="B73" s="11">
+      <c r="B73" s="9">
         <v>200600</v>
       </c>
-      <c r="C73" s="11">
-        <v>2</v>
-      </c>
-      <c r="D73" s="11" t="s">
+      <c r="C73" s="9">
+        <v>2</v>
+      </c>
+      <c r="D73" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="E73" s="11">
+      <c r="E73" s="9">
         <v>200600001</v>
       </c>
-      <c r="F73" s="11" t="s">
+      <c r="F73" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G73" s="14" t="s">
+      <c r="G73" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="H73" s="14">
+      <c r="H73" s="11">
         <v>12</v>
       </c>
-      <c r="I73" s="14">
-        <v>0</v>
-      </c>
-      <c r="J73" s="14">
+      <c r="I73" s="11">
+        <v>0</v>
+      </c>
+      <c r="J73" s="11">
         <v>-1</v>
       </c>
       <c r="K73" s="1">
         <v>0</v>
       </c>
-      <c r="L73" s="14" t="s">
+      <c r="L73" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="M73" s="14">
+      <c r="M73" s="11">
         <v>0</v>
       </c>
       <c r="N73">
         <v>100</v>
       </c>
-      <c r="O73" s="19">
+      <c r="O73" s="15">
         <v>1980000</v>
       </c>
     </row>
@@ -5086,46 +4443,46 @@
         <f t="shared" si="8"/>
         <v>20070010</v>
       </c>
-      <c r="B74" s="11">
+      <c r="B74" s="9">
         <v>200700</v>
       </c>
-      <c r="C74" s="11">
-        <v>2</v>
-      </c>
-      <c r="D74" s="10" t="s">
+      <c r="C74" s="9">
+        <v>2</v>
+      </c>
+      <c r="D74" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E74" s="11">
+      <c r="E74" s="9">
         <v>200700001</v>
       </c>
-      <c r="F74" s="11" t="s">
+      <c r="F74" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G74" s="14" t="s">
+      <c r="G74" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="H74" s="14">
+      <c r="H74" s="11">
         <v>10</v>
       </c>
-      <c r="I74" s="14">
-        <v>0</v>
-      </c>
-      <c r="J74" s="14">
+      <c r="I74" s="11">
+        <v>0</v>
+      </c>
+      <c r="J74" s="11">
         <v>-1</v>
       </c>
       <c r="K74" s="1">
         <v>0</v>
       </c>
-      <c r="L74" s="14" t="s">
+      <c r="L74" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="M74" s="14">
+      <c r="M74" s="11">
         <v>0</v>
       </c>
       <c r="N74">
         <v>100</v>
       </c>
-      <c r="O74" s="19">
+      <c r="O74" s="15">
         <v>1980000</v>
       </c>
     </row>
@@ -5134,47 +4491,47 @@
         <f t="shared" si="8"/>
         <v>20070011</v>
       </c>
-      <c r="B75" s="11">
+      <c r="B75" s="9">
         <v>200700</v>
       </c>
-      <c r="C75" s="11">
-        <v>2</v>
-      </c>
-      <c r="D75" s="10" t="str">
+      <c r="C75" s="9">
+        <v>2</v>
+      </c>
+      <c r="D75" s="2" t="str">
         <f>D74</f>
         <v>越南色碟</v>
       </c>
-      <c r="E75" s="11">
+      <c r="E75" s="9">
         <v>200700001</v>
       </c>
-      <c r="F75" s="11" t="s">
+      <c r="F75" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G75" s="14" t="s">
+      <c r="G75" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="H75" s="14">
+      <c r="H75" s="11">
         <v>11</v>
       </c>
-      <c r="I75" s="14">
-        <v>0</v>
-      </c>
-      <c r="J75" s="14">
+      <c r="I75" s="11">
+        <v>0</v>
+      </c>
+      <c r="J75" s="11">
         <v>-1</v>
       </c>
       <c r="K75" s="1">
         <v>0</v>
       </c>
-      <c r="L75" s="14" t="s">
+      <c r="L75" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="M75" s="14">
+      <c r="M75" s="11">
         <v>0</v>
       </c>
       <c r="N75">
         <v>100</v>
       </c>
-      <c r="O75" s="19">
+      <c r="O75" s="15">
         <v>1980000</v>
       </c>
     </row>
@@ -5183,47 +4540,47 @@
         <f t="shared" si="8"/>
         <v>20070012</v>
       </c>
-      <c r="B76" s="11">
+      <c r="B76" s="9">
         <v>200700</v>
       </c>
-      <c r="C76" s="11">
-        <v>2</v>
-      </c>
-      <c r="D76" s="10" t="str">
+      <c r="C76" s="9">
+        <v>2</v>
+      </c>
+      <c r="D76" s="2" t="str">
         <f>D75</f>
         <v>越南色碟</v>
       </c>
-      <c r="E76" s="11">
+      <c r="E76" s="9">
         <v>200700001</v>
       </c>
-      <c r="F76" s="11" t="s">
+      <c r="F76" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G76" s="14" t="s">
+      <c r="G76" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="H76" s="14">
+      <c r="H76" s="11">
         <v>12</v>
       </c>
-      <c r="I76" s="14">
-        <v>0</v>
-      </c>
-      <c r="J76" s="14">
+      <c r="I76" s="11">
+        <v>0</v>
+      </c>
+      <c r="J76" s="11">
         <v>-1</v>
       </c>
       <c r="K76" s="1">
         <v>0</v>
       </c>
-      <c r="L76" s="14" t="s">
+      <c r="L76" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="M76" s="14">
+      <c r="M76" s="11">
         <v>0</v>
       </c>
       <c r="N76">
         <v>100</v>
       </c>
-      <c r="O76" s="19">
+      <c r="O76" s="15">
         <v>1980000</v>
       </c>
     </row>
@@ -5232,46 +4589,46 @@
         <f t="shared" si="8"/>
         <v>20080010</v>
       </c>
-      <c r="B77" s="11">
+      <c r="B77" s="9">
         <v>200800</v>
       </c>
-      <c r="C77" s="11">
-        <v>2</v>
-      </c>
-      <c r="D77" s="11" t="s">
+      <c r="C77" s="9">
+        <v>2</v>
+      </c>
+      <c r="D77" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E77" s="11">
+      <c r="E77" s="9">
         <v>200800001</v>
       </c>
-      <c r="F77" s="11" t="s">
+      <c r="F77" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G77" s="14" t="s">
+      <c r="G77" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="H77" s="14">
+      <c r="H77" s="11">
         <v>10</v>
       </c>
-      <c r="I77" s="14">
-        <v>0</v>
-      </c>
-      <c r="J77" s="14">
+      <c r="I77" s="11">
+        <v>0</v>
+      </c>
+      <c r="J77" s="11">
         <v>-1</v>
       </c>
       <c r="K77" s="1">
         <v>0</v>
       </c>
-      <c r="L77" s="14" t="s">
+      <c r="L77" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="M77" s="14">
+      <c r="M77" s="11">
         <v>0</v>
       </c>
       <c r="N77">
         <v>100</v>
       </c>
-      <c r="O77" s="19">
+      <c r="O77" s="15">
         <v>1980000</v>
       </c>
     </row>
@@ -5280,46 +4637,46 @@
         <f t="shared" si="8"/>
         <v>20080011</v>
       </c>
-      <c r="B78" s="11">
+      <c r="B78" s="9">
         <v>200800</v>
       </c>
-      <c r="C78" s="11">
-        <v>2</v>
-      </c>
-      <c r="D78" s="11" t="s">
+      <c r="C78" s="9">
+        <v>2</v>
+      </c>
+      <c r="D78" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E78" s="11">
+      <c r="E78" s="9">
         <v>200800001</v>
       </c>
-      <c r="F78" s="11" t="s">
+      <c r="F78" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G78" s="14" t="s">
+      <c r="G78" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="H78" s="14">
+      <c r="H78" s="11">
         <v>11</v>
       </c>
-      <c r="I78" s="14">
-        <v>0</v>
-      </c>
-      <c r="J78" s="14">
+      <c r="I78" s="11">
+        <v>0</v>
+      </c>
+      <c r="J78" s="11">
         <v>-1</v>
       </c>
       <c r="K78" s="1">
         <v>0</v>
       </c>
-      <c r="L78" s="14" t="s">
+      <c r="L78" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="M78" s="14">
+      <c r="M78" s="11">
         <v>0</v>
       </c>
       <c r="N78">
         <v>100</v>
       </c>
-      <c r="O78" s="19">
+      <c r="O78" s="15">
         <v>1980000</v>
       </c>
     </row>
@@ -5328,46 +4685,46 @@
         <f t="shared" si="8"/>
         <v>20080012</v>
       </c>
-      <c r="B79" s="11">
+      <c r="B79" s="9">
         <v>200800</v>
       </c>
-      <c r="C79" s="11">
-        <v>2</v>
-      </c>
-      <c r="D79" s="11" t="s">
+      <c r="C79" s="9">
+        <v>2</v>
+      </c>
+      <c r="D79" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E79" s="11">
+      <c r="E79" s="9">
         <v>200800001</v>
       </c>
-      <c r="F79" s="11" t="s">
+      <c r="F79" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G79" s="14" t="s">
+      <c r="G79" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="H79" s="14">
+      <c r="H79" s="11">
         <v>12</v>
       </c>
-      <c r="I79" s="14">
-        <v>0</v>
-      </c>
-      <c r="J79" s="14">
+      <c r="I79" s="11">
+        <v>0</v>
+      </c>
+      <c r="J79" s="11">
         <v>-1</v>
       </c>
       <c r="K79" s="1">
         <v>0</v>
       </c>
-      <c r="L79" s="14" t="s">
+      <c r="L79" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="M79" s="14">
+      <c r="M79" s="11">
         <v>0</v>
       </c>
       <c r="N79">
         <v>100</v>
       </c>
-      <c r="O79" s="19">
+      <c r="O79" s="15">
         <v>1980000</v>
       </c>
     </row>
@@ -5376,46 +4733,46 @@
         <f t="shared" si="8"/>
         <v>20090010</v>
       </c>
-      <c r="B80" s="11">
+      <c r="B80" s="9">
         <v>200900</v>
       </c>
-      <c r="C80" s="11">
-        <v>2</v>
-      </c>
-      <c r="D80" s="11" t="s">
+      <c r="C80" s="9">
+        <v>2</v>
+      </c>
+      <c r="D80" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="E80" s="11">
+      <c r="E80" s="9">
         <v>200900001</v>
       </c>
-      <c r="F80" s="11" t="s">
+      <c r="F80" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="G80" s="14" t="s">
+      <c r="G80" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="H80" s="14">
+      <c r="H80" s="11">
         <v>10</v>
       </c>
-      <c r="I80" s="14">
-        <v>0</v>
-      </c>
-      <c r="J80" s="14">
+      <c r="I80" s="11">
+        <v>0</v>
+      </c>
+      <c r="J80" s="11">
         <v>-1</v>
       </c>
       <c r="K80" s="1">
         <v>0</v>
       </c>
-      <c r="L80" s="14" t="s">
+      <c r="L80" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="M80" s="14">
+      <c r="M80" s="11">
         <v>0</v>
       </c>
       <c r="N80">
         <v>100</v>
       </c>
-      <c r="O80" s="19">
+      <c r="O80" s="15">
         <v>1980000</v>
       </c>
     </row>
@@ -5424,46 +4781,46 @@
         <f t="shared" si="8"/>
         <v>20090011</v>
       </c>
-      <c r="B81" s="11">
+      <c r="B81" s="9">
         <v>200900</v>
       </c>
-      <c r="C81" s="11">
-        <v>2</v>
-      </c>
-      <c r="D81" s="11" t="s">
+      <c r="C81" s="9">
+        <v>2</v>
+      </c>
+      <c r="D81" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="E81" s="11">
+      <c r="E81" s="9">
         <v>200900001</v>
       </c>
-      <c r="F81" s="11" t="s">
+      <c r="F81" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="G81" s="14" t="s">
+      <c r="G81" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="H81" s="14">
+      <c r="H81" s="11">
         <v>11</v>
       </c>
-      <c r="I81" s="14">
-        <v>0</v>
-      </c>
-      <c r="J81" s="14">
+      <c r="I81" s="11">
+        <v>0</v>
+      </c>
+      <c r="J81" s="11">
         <v>-1</v>
       </c>
       <c r="K81" s="1">
         <v>0</v>
       </c>
-      <c r="L81" s="14" t="s">
+      <c r="L81" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="M81" s="14">
+      <c r="M81" s="11">
         <v>0</v>
       </c>
       <c r="N81">
         <v>100</v>
       </c>
-      <c r="O81" s="19">
+      <c r="O81" s="15">
         <v>1980000</v>
       </c>
     </row>
@@ -5472,76 +4829,76 @@
         <f t="shared" si="8"/>
         <v>20090012</v>
       </c>
-      <c r="B82" s="11">
+      <c r="B82" s="9">
         <v>200900</v>
       </c>
-      <c r="C82" s="11">
-        <v>2</v>
-      </c>
-      <c r="D82" s="11" t="s">
+      <c r="C82" s="9">
+        <v>2</v>
+      </c>
+      <c r="D82" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="E82" s="11">
+      <c r="E82" s="9">
         <v>200900001</v>
       </c>
-      <c r="F82" s="11" t="s">
+      <c r="F82" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="G82" s="14" t="s">
+      <c r="G82" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="H82" s="14">
+      <c r="H82" s="11">
         <v>12</v>
       </c>
-      <c r="I82" s="14">
-        <v>0</v>
-      </c>
-      <c r="J82" s="14">
+      <c r="I82" s="11">
+        <v>0</v>
+      </c>
+      <c r="J82" s="11">
         <v>-1</v>
       </c>
       <c r="K82" s="1">
         <v>0</v>
       </c>
-      <c r="L82" s="14" t="s">
+      <c r="L82" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="M82" s="14">
+      <c r="M82" s="11">
         <v>0</v>
       </c>
       <c r="N82">
         <v>100</v>
       </c>
-      <c r="O82" s="19">
+      <c r="O82" s="15">
         <v>1980000</v>
       </c>
     </row>
-    <row r="83" s="1" customFormat="1" spans="1:19">
+    <row r="83" spans="1:15">
       <c r="A83" s="1">
         <f t="shared" si="8"/>
         <v>30020010</v>
       </c>
-      <c r="B83" s="10">
+      <c r="B83" s="2">
         <v>300200</v>
       </c>
-      <c r="C83" s="10">
+      <c r="C83" s="2">
         <v>3</v>
       </c>
-      <c r="D83" s="10" t="s">
+      <c r="D83" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E83" s="11">
+      <c r="E83" s="9">
         <v>300200006</v>
       </c>
-      <c r="F83" s="11" t="s">
+      <c r="F83" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="G83" s="14" t="s">
+      <c r="G83" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="H83" s="14">
+      <c r="H83" s="11">
         <v>10</v>
       </c>
-      <c r="I83" s="14">
+      <c r="I83" s="11">
         <v>0</v>
       </c>
       <c r="J83" s="1">
@@ -5550,47 +4907,46 @@
       <c r="K83" s="1">
         <v>0</v>
       </c>
-      <c r="L83" s="21" t="s">
+      <c r="L83" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="M83" s="14">
+      <c r="M83" s="11">
         <v>0</v>
       </c>
       <c r="N83">
         <v>2</v>
       </c>
-      <c r="O83" s="19">
+      <c r="O83" s="15">
         <v>1980000</v>
       </c>
-      <c r="S83" s="3"/>
-    </row>
-    <row r="84" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="84" spans="1:15">
       <c r="A84" s="1">
         <f t="shared" si="8"/>
         <v>30020011</v>
       </c>
-      <c r="B84" s="10">
+      <c r="B84" s="2">
         <v>300200</v>
       </c>
-      <c r="C84" s="10">
+      <c r="C84" s="2">
         <v>3</v>
       </c>
-      <c r="D84" s="10" t="s">
+      <c r="D84" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E84" s="11">
+      <c r="E84" s="9">
         <v>300200006</v>
       </c>
-      <c r="F84" s="11" t="s">
+      <c r="F84" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="G84" s="14" t="s">
+      <c r="G84" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="H84" s="14">
+      <c r="H84" s="11">
         <v>11</v>
       </c>
-      <c r="I84" s="14">
+      <c r="I84" s="11">
         <v>0</v>
       </c>
       <c r="J84" s="1">
@@ -5599,47 +4955,46 @@
       <c r="K84" s="1">
         <v>0</v>
       </c>
-      <c r="L84" s="21" t="s">
+      <c r="L84" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="M84" s="14">
+      <c r="M84" s="11">
         <v>0</v>
       </c>
       <c r="N84">
         <v>4</v>
       </c>
-      <c r="O84" s="19">
+      <c r="O84" s="15">
         <v>1980000</v>
       </c>
-      <c r="S84" s="3"/>
-    </row>
-    <row r="85" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="85" spans="1:15">
       <c r="A85" s="1">
         <f t="shared" si="8"/>
         <v>30020012</v>
       </c>
-      <c r="B85" s="10">
+      <c r="B85" s="2">
         <v>300200</v>
       </c>
-      <c r="C85" s="10">
+      <c r="C85" s="2">
         <v>3</v>
       </c>
-      <c r="D85" s="10" t="s">
+      <c r="D85" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E85" s="11">
+      <c r="E85" s="9">
         <v>300200006</v>
       </c>
-      <c r="F85" s="11" t="s">
+      <c r="F85" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="G85" s="14" t="s">
+      <c r="G85" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="H85" s="14">
+      <c r="H85" s="11">
         <v>12</v>
       </c>
-      <c r="I85" s="14">
+      <c r="I85" s="11">
         <v>0</v>
       </c>
       <c r="J85" s="1">
@@ -5648,23 +5003,22 @@
       <c r="K85" s="1">
         <v>0</v>
       </c>
-      <c r="L85" s="21" t="s">
+      <c r="L85" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="M85" s="14">
+      <c r="M85" s="11">
         <v>0</v>
       </c>
       <c r="N85">
         <v>8</v>
       </c>
-      <c r="O85" s="19">
+      <c r="O85" s="15">
         <v>1980000</v>
       </c>
-      <c r="S85" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gamedoc\游戏配置表\common\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B1B608-EB38-4333-A8CE-84FF7DA92A6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="794" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Warehouse" sheetId="42" r:id="rId1"/>
@@ -33,19 +27,18 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="C1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -54,7 +47,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -65,14 +57,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -81,7 +72,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -89,14 +79,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -105,7 +94,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -114,40 +102,37 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>最小准入金币</t>
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>-1 表示无上限</t>
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="M1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -156,7 +141,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -408,8 +392,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -454,45 +444,173 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Noto Sans CJK SC Regular"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -501,36 +619,222 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7993408001953185"/>
+        <fgColor theme="5" tint="0.799340800195319"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.7993408001953185"/>
+        <fgColor theme="4" tint="0.799340800195319"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="7" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
+        <fgColor theme="4" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -553,108 +857,406 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="12">
+  <cellStyleXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="12">
+  <cellStyles count="60">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="常规 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="常规 2 2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
-    <cellStyle name="常规 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
-    <cellStyle name="常规 3 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
-    <cellStyle name="常规 4" xfId="6" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
-    <cellStyle name="常规 5" xfId="7" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
-    <cellStyle name="常规 6" xfId="8" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
-    <cellStyle name="常规 6 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
-    <cellStyle name="常规 6 2 2" xfId="10" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
-    <cellStyle name="常规 7" xfId="11" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
+    <cellStyle name="常规 2 2" xfId="50"/>
+    <cellStyle name="常规 2 2 2" xfId="51"/>
+    <cellStyle name="常规 3" xfId="52"/>
+    <cellStyle name="常规 3 2" xfId="53"/>
+    <cellStyle name="常规 4" xfId="54"/>
+    <cellStyle name="常规 5" xfId="55"/>
+    <cellStyle name="常规 6" xfId="56"/>
+    <cellStyle name="常规 6 2" xfId="57"/>
+    <cellStyle name="常规 6 2 2" xfId="58"/>
+    <cellStyle name="常规 7" xfId="59"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -912,12 +1514,12 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:S85"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
@@ -926,13 +1528,14 @@
     <col min="5" max="5" width="11.625" style="1"/>
     <col min="6" max="6" width="19.125" style="1" customWidth="1"/>
     <col min="7" max="7" width="12" style="1" customWidth="1"/>
-    <col min="8" max="9" width="9" style="1"/>
+    <col min="8" max="8" width="9" style="1"/>
+    <col min="9" max="9" width="9.375" style="1"/>
     <col min="10" max="10" width="11.25" style="1" customWidth="1"/>
-    <col min="11" max="11" width="9.25" style="1" customWidth="1"/>
-    <col min="12" max="12" width="17" style="1" customWidth="1"/>
-    <col min="13" max="13" width="14" style="1" customWidth="1"/>
-    <col min="14" max="14" width="13.625" customWidth="1"/>
-    <col min="15" max="15" width="21" style="2" customWidth="1"/>
+    <col min="11" max="11" width="9.25833333333333" style="1" customWidth="1"/>
+    <col min="12" max="12" width="17.05" style="1" customWidth="1"/>
+    <col min="13" max="13" width="13.9666666666667" style="1" customWidth="1"/>
+    <col min="14" max="14" width="17.125" customWidth="1"/>
+    <col min="15" max="15" width="21.025" style="2" customWidth="1"/>
     <col min="16" max="16" width="9" style="1"/>
     <col min="17" max="17" width="27.875" style="1" customWidth="1"/>
     <col min="18" max="18" width="9" style="1"/>
@@ -965,13 +1568,13 @@
       <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="15" t="s">
         <v>8</v>
       </c>
       <c r="L1" s="1" t="s">
@@ -983,7 +1586,7 @@
       <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="13" t="s">
+      <c r="O1" s="16" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1001,20 +1604,20 @@
       <c r="E2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G2" s="6"/>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="9" t="s">
         <v>13</v>
       </c>
       <c r="L2" s="1" t="s">
@@ -1023,7 +1626,7 @@
       <c r="M2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="N2" s="9" t="s">
         <v>13</v>
       </c>
       <c r="O2" s="2" t="s">
@@ -1046,16 +1649,16 @@
       <c r="F3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="9" t="s">
         <v>24</v>
       </c>
       <c r="L3" s="1" t="s">
@@ -1064,14 +1667,14 @@
       <c r="M3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="N3" s="9" t="s">
         <v>27</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="14.25">
+    <row r="4" spans="6:15">
       <c r="F4" s="1" t="s">
         <v>29</v>
       </c>
@@ -1082,19 +1685,19 @@
         <f t="shared" ref="A5:A10" si="0">B5*10+H5</f>
         <v>1001001</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="10">
         <v>100100</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="10">
         <v>1</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="11">
         <v>100100026</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="11" t="s">
         <v>31</v>
       </c>
       <c r="G5" s="1" t="s">
@@ -1115,13 +1718,13 @@
       <c r="L5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M5" s="16" t="s">
+      <c r="M5" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N5">
         <v>1000</v>
       </c>
-      <c r="O5" s="14">
+      <c r="O5" s="18">
         <v>1990000</v>
       </c>
     </row>
@@ -1130,20 +1733,20 @@
         <f t="shared" si="0"/>
         <v>1001002</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="10">
         <v>100100</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="10">
         <v>1</v>
       </c>
-      <c r="D6" s="2" t="str">
+      <c r="D6" s="10" t="str">
         <f t="shared" ref="D6:D10" si="1">D5</f>
         <v>金礦大亨</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="11">
         <v>100100026</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="11" t="s">
         <v>31</v>
       </c>
       <c r="G6" s="1" t="s">
@@ -1164,13 +1767,13 @@
       <c r="L6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M6" s="16" t="s">
+      <c r="M6" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N6">
         <v>100000</v>
       </c>
-      <c r="O6" s="14">
+      <c r="O6" s="18">
         <v>1990000</v>
       </c>
     </row>
@@ -1179,20 +1782,20 @@
         <f t="shared" si="0"/>
         <v>1001003</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="10">
         <v>100100</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="10">
         <v>1</v>
       </c>
-      <c r="D7" s="2" t="str">
+      <c r="D7" s="10" t="str">
         <f t="shared" si="1"/>
         <v>金礦大亨</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="11">
         <v>100100026</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="11" t="s">
         <v>31</v>
       </c>
       <c r="G7" s="1" t="s">
@@ -1213,13 +1816,13 @@
       <c r="L7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M7" s="16" t="s">
+      <c r="M7" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N7">
         <v>10000000</v>
       </c>
-      <c r="O7" s="14">
+      <c r="O7" s="18">
         <v>1990000</v>
       </c>
     </row>
@@ -1228,19 +1831,19 @@
         <f t="shared" si="0"/>
         <v>1003001</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="10">
         <v>100300</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="10">
         <v>1</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="11">
         <v>100300001</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="11" t="s">
         <v>38</v>
       </c>
       <c r="G8" s="1" t="s">
@@ -1261,13 +1864,13 @@
       <c r="L8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M8" s="16" t="s">
+      <c r="M8" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N8">
         <v>1000</v>
       </c>
-      <c r="O8" s="14">
+      <c r="O8" s="18">
         <v>1990000</v>
       </c>
     </row>
@@ -1276,20 +1879,20 @@
         <f t="shared" si="0"/>
         <v>1003002</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="10">
         <v>100300</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="10">
         <v>1</v>
       </c>
-      <c r="D9" s="2" t="str">
+      <c r="D9" s="10" t="str">
         <f t="shared" si="1"/>
         <v>超级明星</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="11">
         <v>100300001</v>
       </c>
-      <c r="F9" s="9" t="str">
+      <c r="F9" s="11" t="str">
         <f>F8</f>
         <v>SuperStar</v>
       </c>
@@ -1311,13 +1914,13 @@
       <c r="L9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M9" s="16" t="s">
+      <c r="M9" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N9">
         <v>100000</v>
       </c>
-      <c r="O9" s="14">
+      <c r="O9" s="18">
         <v>1990000</v>
       </c>
     </row>
@@ -1326,20 +1929,20 @@
         <f t="shared" si="0"/>
         <v>1003003</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="10">
         <v>100300</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="10">
         <v>1</v>
       </c>
-      <c r="D10" s="2" t="str">
+      <c r="D10" s="10" t="str">
         <f t="shared" si="1"/>
         <v>超级明星</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="11">
         <v>100300001</v>
       </c>
-      <c r="F10" s="9" t="str">
+      <c r="F10" s="11" t="str">
         <f>F9</f>
         <v>SuperStar</v>
       </c>
@@ -1361,34 +1964,34 @@
       <c r="L10" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M10" s="16" t="s">
+      <c r="M10" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N10">
         <v>10000000</v>
       </c>
-      <c r="O10" s="14">
+      <c r="O10" s="18">
         <v>1990000</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="1">
-        <f t="shared" ref="A11:A19" si="2">B11*10+H11</f>
+        <f t="shared" ref="A11:A22" si="2">B11*10+H11</f>
         <v>1007001</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="10">
         <v>100700</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="10">
         <v>1</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="11">
         <v>100700001</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="11" t="s">
         <v>40</v>
       </c>
       <c r="G11" s="1" t="s">
@@ -1409,13 +2012,13 @@
       <c r="L11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M11" s="16" t="s">
+      <c r="M11" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N11">
         <v>1000</v>
       </c>
-      <c r="O11" s="14">
+      <c r="O11" s="18">
         <v>1990000</v>
       </c>
     </row>
@@ -1424,20 +2027,20 @@
         <f t="shared" si="2"/>
         <v>1007002</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="10">
         <v>100700</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="10">
         <v>1</v>
       </c>
-      <c r="D12" s="2" t="str">
+      <c r="D12" s="10" t="str">
         <f>D11</f>
         <v>麻将胡了</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="11">
         <v>100700001</v>
       </c>
-      <c r="F12" s="9" t="str">
+      <c r="F12" s="11" t="str">
         <f>F11</f>
         <v>MahjongWays</v>
       </c>
@@ -1459,13 +2062,13 @@
       <c r="L12" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M12" s="16" t="s">
+      <c r="M12" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N12">
         <v>100000</v>
       </c>
-      <c r="O12" s="14">
+      <c r="O12" s="18">
         <v>1990000</v>
       </c>
     </row>
@@ -1474,20 +2077,20 @@
         <f t="shared" si="2"/>
         <v>1007003</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="10">
         <v>100700</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="10">
         <v>1</v>
       </c>
-      <c r="D13" s="2" t="str">
+      <c r="D13" s="10" t="str">
         <f>D12</f>
         <v>麻将胡了</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="11">
         <v>100700001</v>
       </c>
-      <c r="F13" s="9" t="str">
+      <c r="F13" s="11" t="str">
         <f>F12</f>
         <v>MahjongWays</v>
       </c>
@@ -1509,13 +2112,13 @@
       <c r="L13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M13" s="16" t="s">
+      <c r="M13" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N13">
         <v>10000000</v>
       </c>
-      <c r="O13" s="14">
+      <c r="O13" s="18">
         <v>1990000</v>
       </c>
     </row>
@@ -1524,19 +2127,19 @@
         <f t="shared" si="2"/>
         <v>1012001</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="10">
         <v>101200</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="10">
         <v>1</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="11">
         <v>101200001</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G14" s="1" t="s">
@@ -1557,13 +2160,13 @@
       <c r="L14" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M14" s="16" t="s">
+      <c r="M14" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N14">
         <v>1000</v>
       </c>
-      <c r="O14" s="14">
+      <c r="O14" s="18">
         <v>1990000</v>
       </c>
     </row>
@@ -1572,20 +2175,20 @@
         <f t="shared" si="2"/>
         <v>1012002</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="10">
         <v>101200</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="10">
         <v>1</v>
       </c>
-      <c r="D15" s="2" t="str">
+      <c r="D15" s="10" t="str">
         <f>D14</f>
         <v>财神</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="11">
         <v>101200001</v>
       </c>
-      <c r="F15" s="9" t="str">
+      <c r="F15" s="11" t="str">
         <f>F14</f>
         <v>Godofwealth</v>
       </c>
@@ -1607,13 +2210,13 @@
       <c r="L15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M15" s="16" t="s">
+      <c r="M15" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N15">
         <v>100000</v>
       </c>
-      <c r="O15" s="14">
+      <c r="O15" s="18">
         <v>1990000</v>
       </c>
     </row>
@@ -1622,20 +2225,20 @@
         <f t="shared" si="2"/>
         <v>1012003</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="10">
         <v>101200</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="10">
         <v>1</v>
       </c>
-      <c r="D16" s="2" t="str">
+      <c r="D16" s="10" t="str">
         <f>D15</f>
         <v>财神</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="11">
         <v>101200001</v>
       </c>
-      <c r="F16" s="9" t="str">
+      <c r="F16" s="11" t="str">
         <f>F15</f>
         <v>Godofwealth</v>
       </c>
@@ -1657,34 +2260,34 @@
       <c r="L16" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M16" s="16" t="s">
+      <c r="M16" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N16">
         <v>10000000</v>
       </c>
-      <c r="O16" s="14">
+      <c r="O16" s="18">
         <v>1990000</v>
       </c>
     </row>
-    <row r="17" spans="1:18">
+    <row r="17" spans="1:15">
       <c r="A17" s="1">
         <f t="shared" si="2"/>
         <v>1014001</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="10">
         <v>101400</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="10">
         <v>1</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="11">
         <v>101400001</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="11" t="s">
         <v>44</v>
       </c>
       <c r="G17" s="1" t="s">
@@ -1705,35 +2308,35 @@
       <c r="L17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M17" s="16" t="s">
+      <c r="M17" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N17">
         <v>1000</v>
       </c>
-      <c r="O17" s="14">
+      <c r="O17" s="18">
         <v>1990000</v>
       </c>
     </row>
-    <row r="18" spans="1:18">
+    <row r="18" spans="1:15">
       <c r="A18" s="1">
         <f t="shared" si="2"/>
         <v>1014002</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="10">
         <v>101400</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="10">
         <v>1</v>
       </c>
-      <c r="D18" s="2" t="str">
+      <c r="D18" s="10" t="str">
         <f>D17</f>
         <v>埃及艳后</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="11">
         <v>101400001</v>
       </c>
-      <c r="F18" s="9" t="str">
+      <c r="F18" s="11" t="str">
         <f>F17</f>
         <v>Cleopatra</v>
       </c>
@@ -1755,35 +2358,35 @@
       <c r="L18" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M18" s="16" t="s">
+      <c r="M18" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N18">
         <v>100000</v>
       </c>
-      <c r="O18" s="14">
+      <c r="O18" s="18">
         <v>1990000</v>
       </c>
     </row>
-    <row r="19" spans="1:18">
+    <row r="19" spans="1:15">
       <c r="A19" s="1">
         <f t="shared" si="2"/>
         <v>1014003</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="10">
         <v>101400</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="10">
         <v>1</v>
       </c>
-      <c r="D19" s="2" t="str">
+      <c r="D19" s="10" t="str">
         <f>D18</f>
         <v>埃及艳后</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="11">
         <v>101400001</v>
       </c>
-      <c r="F19" s="9" t="str">
+      <c r="F19" s="11" t="str">
         <f>F18</f>
         <v>Cleopatra</v>
       </c>
@@ -1805,34 +2408,34 @@
       <c r="L19" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M19" s="16" t="s">
+      <c r="M19" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N19">
         <v>10000000</v>
       </c>
-      <c r="O19" s="14">
+      <c r="O19" s="18">
         <v>1990000</v>
       </c>
     </row>
-    <row r="20" spans="1:18">
+    <row r="20" spans="1:15">
       <c r="A20" s="1">
-        <f t="shared" ref="A20:A55" si="3">B20*10+H20</f>
+        <f t="shared" ref="A20:A66" si="3">B20*10+H20</f>
         <v>2001001</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="10">
         <v>200100</v>
       </c>
-      <c r="C20" s="2">
-        <v>2</v>
-      </c>
-      <c r="D20" s="2" t="s">
+      <c r="C20" s="10">
+        <v>2</v>
+      </c>
+      <c r="D20" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="11">
         <v>200100038</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="11" t="s">
         <v>46</v>
       </c>
       <c r="G20" s="1" t="s">
@@ -1842,7 +2445,8 @@
         <v>1</v>
       </c>
       <c r="I20" s="1">
-        <v>100</v>
+        <f>N20</f>
+        <v>1000</v>
       </c>
       <c r="J20" s="1">
         <v>5000000</v>
@@ -1853,35 +2457,35 @@
       <c r="L20" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M20" s="16" t="s">
+      <c r="M20" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N20">
         <v>1000</v>
       </c>
-      <c r="O20" s="14">
+      <c r="O20" s="18">
         <v>1990000</v>
       </c>
     </row>
-    <row r="21" spans="1:18">
+    <row r="21" spans="1:15">
       <c r="A21" s="1">
         <f t="shared" si="3"/>
         <v>2001002</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="10">
         <v>200100</v>
       </c>
-      <c r="C21" s="2">
-        <v>2</v>
-      </c>
-      <c r="D21" s="2" t="str">
+      <c r="C21" s="10">
+        <v>2</v>
+      </c>
+      <c r="D21" s="10" t="str">
         <f>D20</f>
         <v>紅黑大戰</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="11">
         <v>200100038</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F21" s="11" t="s">
         <v>46</v>
       </c>
       <c r="G21" s="1" t="s">
@@ -1891,7 +2495,8 @@
         <v>2</v>
       </c>
       <c r="I21" s="1">
-        <v>10000</v>
+        <f t="shared" ref="I21:I55" si="4">N21</f>
+        <v>100000</v>
       </c>
       <c r="J21" s="1">
         <v>500000000</v>
@@ -1902,35 +2507,35 @@
       <c r="L21" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M21" s="16" t="s">
+      <c r="M21" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N21">
         <v>100000</v>
       </c>
-      <c r="O21" s="14">
+      <c r="O21" s="18">
         <v>1990000</v>
       </c>
     </row>
-    <row r="22" spans="1:18">
+    <row r="22" spans="1:17">
       <c r="A22" s="1">
         <f t="shared" si="3"/>
         <v>2001003</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="10">
         <v>200100</v>
       </c>
-      <c r="C22" s="2">
-        <v>2</v>
-      </c>
-      <c r="D22" s="2" t="str">
+      <c r="C22" s="10">
+        <v>2</v>
+      </c>
+      <c r="D22" s="10" t="str">
         <f>D21</f>
         <v>紅黑大戰</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="11">
         <v>200100038</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="F22" s="11" t="s">
         <v>46</v>
       </c>
       <c r="G22" s="1" t="s">
@@ -1940,7 +2545,8 @@
         <v>3</v>
       </c>
       <c r="I22" s="1">
-        <v>1000000</v>
+        <f t="shared" si="4"/>
+        <v>10000000</v>
       </c>
       <c r="J22" s="1">
         <v>-1</v>
@@ -1951,35 +2557,35 @@
       <c r="L22" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M22" s="16" t="s">
+      <c r="M22" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N22">
         <v>10000000</v>
       </c>
-      <c r="O22" s="14">
+      <c r="O22" s="18">
         <v>1990000</v>
       </c>
       <c r="Q22"/>
     </row>
-    <row r="23" spans="1:18">
+    <row r="23" spans="1:15">
       <c r="A23" s="1">
         <f t="shared" si="3"/>
         <v>2001011</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="10">
         <v>200101</v>
       </c>
-      <c r="C23" s="2">
-        <v>2</v>
-      </c>
-      <c r="D23" s="2" t="s">
+      <c r="C23" s="10">
+        <v>2</v>
+      </c>
+      <c r="D23" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="11">
         <v>200101001</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" s="11" t="s">
         <v>48</v>
       </c>
       <c r="G23" s="1" t="s">
@@ -1989,7 +2595,8 @@
         <v>1</v>
       </c>
       <c r="I23" s="1">
-        <v>100</v>
+        <f t="shared" si="4"/>
+        <v>1000</v>
       </c>
       <c r="J23" s="1">
         <v>5000000</v>
@@ -2000,35 +2607,35 @@
       <c r="L23" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M23" s="16" t="s">
+      <c r="M23" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N23">
         <v>1000</v>
       </c>
-      <c r="O23" s="14">
+      <c r="O23" s="18">
         <v>1990000</v>
       </c>
     </row>
-    <row r="24" spans="1:18">
+    <row r="24" s="1" customFormat="1" spans="1:19">
       <c r="A24" s="1">
         <f t="shared" si="3"/>
         <v>2001012</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="10">
         <v>200101</v>
       </c>
-      <c r="C24" s="2">
-        <v>2</v>
-      </c>
-      <c r="D24" s="2" t="str">
-        <f t="shared" ref="D24:D28" si="4">D23</f>
+      <c r="C24" s="10">
+        <v>2</v>
+      </c>
+      <c r="D24" s="10" t="str">
+        <f t="shared" ref="D24:D28" si="5">D23</f>
         <v>龍虎鬥</v>
       </c>
-      <c r="E24" s="9">
+      <c r="E24" s="11">
         <v>200101001</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F24" s="11" t="s">
         <v>48</v>
       </c>
       <c r="G24" s="1" t="s">
@@ -2038,7 +2645,8 @@
         <v>2</v>
       </c>
       <c r="I24" s="1">
-        <v>10000</v>
+        <f t="shared" si="4"/>
+        <v>100000</v>
       </c>
       <c r="J24" s="1">
         <v>500000000</v>
@@ -2049,35 +2657,36 @@
       <c r="L24" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M24" s="16" t="s">
+      <c r="M24" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N24">
         <v>100000</v>
       </c>
-      <c r="O24" s="14">
+      <c r="O24" s="18">
         <v>1990000</v>
       </c>
-    </row>
-    <row r="25" spans="1:18">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:19">
       <c r="A25" s="1">
         <f t="shared" si="3"/>
         <v>2001013</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="10">
         <v>200101</v>
       </c>
-      <c r="C25" s="2">
-        <v>2</v>
-      </c>
-      <c r="D25" s="2" t="str">
-        <f t="shared" si="4"/>
+      <c r="C25" s="10">
+        <v>2</v>
+      </c>
+      <c r="D25" s="10" t="str">
+        <f t="shared" si="5"/>
         <v>龍虎鬥</v>
       </c>
-      <c r="E25" s="9">
+      <c r="E25" s="11">
         <v>200101001</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="F25" s="11" t="s">
         <v>48</v>
       </c>
       <c r="G25" s="1" t="s">
@@ -2087,7 +2696,8 @@
         <v>3</v>
       </c>
       <c r="I25" s="1">
-        <v>1000000</v>
+        <f t="shared" si="4"/>
+        <v>10000000</v>
       </c>
       <c r="J25" s="1">
         <v>-1</v>
@@ -2098,34 +2708,35 @@
       <c r="L25" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M25" s="16" t="s">
+      <c r="M25" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N25">
         <v>10000000</v>
       </c>
-      <c r="O25" s="14">
+      <c r="O25" s="18">
         <v>1990000</v>
       </c>
-    </row>
-    <row r="26" spans="1:18">
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="1:15">
       <c r="A26" s="1">
         <f t="shared" si="3"/>
         <v>2003001</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" s="10">
         <v>200300</v>
       </c>
-      <c r="C26" s="2">
-        <v>2</v>
-      </c>
-      <c r="D26" s="2" t="s">
+      <c r="C26" s="10">
+        <v>2</v>
+      </c>
+      <c r="D26" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="E26" s="9">
+      <c r="E26" s="11">
         <v>200300001</v>
       </c>
-      <c r="F26" s="9" t="s">
+      <c r="F26" s="11" t="s">
         <v>50</v>
       </c>
       <c r="G26" s="1" t="s">
@@ -2135,7 +2746,8 @@
         <v>1</v>
       </c>
       <c r="I26" s="1">
-        <v>100</v>
+        <f t="shared" si="4"/>
+        <v>1000</v>
       </c>
       <c r="J26" s="1">
         <v>5000000</v>
@@ -2146,35 +2758,35 @@
       <c r="L26" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M26" s="16" t="s">
+      <c r="M26" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N26">
         <v>1000</v>
       </c>
-      <c r="O26" s="14">
+      <c r="O26" s="18">
         <v>1990000</v>
       </c>
     </row>
-    <row r="27" spans="1:18">
+    <row r="27" s="1" customFormat="1" spans="1:19">
       <c r="A27" s="1">
         <f t="shared" si="3"/>
         <v>2003002</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" s="10">
         <v>200300</v>
       </c>
-      <c r="C27" s="2">
-        <v>2</v>
-      </c>
-      <c r="D27" s="2" t="str">
-        <f t="shared" si="4"/>
+      <c r="C27" s="10">
+        <v>2</v>
+      </c>
+      <c r="D27" s="10" t="str">
+        <f t="shared" si="5"/>
         <v>飛禽走獸</v>
       </c>
-      <c r="E27" s="9">
+      <c r="E27" s="11">
         <v>200300001</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="F27" s="11" t="s">
         <v>50</v>
       </c>
       <c r="G27" s="1" t="s">
@@ -2184,7 +2796,8 @@
         <v>2</v>
       </c>
       <c r="I27" s="1">
-        <v>10000</v>
+        <f t="shared" si="4"/>
+        <v>100000</v>
       </c>
       <c r="J27" s="1">
         <v>500000000</v>
@@ -2195,37 +2808,38 @@
       <c r="L27" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M27" s="16" t="s">
+      <c r="M27" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N27">
         <v>100000</v>
       </c>
-      <c r="O27" s="14">
+      <c r="O27" s="18">
         <v>1990000</v>
       </c>
       <c r="Q27" s="3"/>
-      <c r="R27" s="2"/>
-    </row>
-    <row r="28" spans="1:18">
+      <c r="R27" s="10"/>
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="1:19">
       <c r="A28" s="1">
         <f t="shared" si="3"/>
         <v>2003003</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B28" s="10">
         <v>200300</v>
       </c>
-      <c r="C28" s="2">
-        <v>2</v>
-      </c>
-      <c r="D28" s="2" t="str">
-        <f t="shared" si="4"/>
+      <c r="C28" s="10">
+        <v>2</v>
+      </c>
+      <c r="D28" s="10" t="str">
+        <f t="shared" si="5"/>
         <v>飛禽走獸</v>
       </c>
-      <c r="E28" s="9">
+      <c r="E28" s="11">
         <v>200300001</v>
       </c>
-      <c r="F28" s="9" t="s">
+      <c r="F28" s="11" t="s">
         <v>50</v>
       </c>
       <c r="G28" s="1" t="s">
@@ -2235,7 +2849,8 @@
         <v>3</v>
       </c>
       <c r="I28" s="1">
-        <v>1000000</v>
+        <f t="shared" si="4"/>
+        <v>10000000</v>
       </c>
       <c r="J28" s="1">
         <v>-1</v>
@@ -2246,36 +2861,37 @@
       <c r="L28" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M28" s="16" t="s">
+      <c r="M28" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N28">
         <v>10000000</v>
       </c>
-      <c r="O28" s="14">
+      <c r="O28" s="18">
         <v>1990000</v>
       </c>
       <c r="Q28" s="3"/>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="1:18">
+      <c r="R28" s="12"/>
+      <c r="S28" s="12"/>
+    </row>
+    <row r="29" spans="1:19">
       <c r="A29" s="1">
         <f t="shared" si="3"/>
         <v>2004001</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B29" s="10">
         <v>200400</v>
       </c>
-      <c r="C29" s="2">
-        <v>2</v>
-      </c>
-      <c r="D29" s="3" t="s">
+      <c r="C29" s="10">
+        <v>2</v>
+      </c>
+      <c r="D29" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E29" s="11">
         <v>200400009</v>
       </c>
-      <c r="F29" s="9" t="s">
+      <c r="F29" s="11" t="s">
         <v>52</v>
       </c>
       <c r="G29" s="1" t="s">
@@ -2285,7 +2901,8 @@
         <v>1</v>
       </c>
       <c r="I29" s="1">
-        <v>100</v>
+        <f t="shared" si="4"/>
+        <v>1000</v>
       </c>
       <c r="J29" s="1">
         <v>5000000</v>
@@ -2296,36 +2913,37 @@
       <c r="L29" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M29" s="16" t="s">
+      <c r="M29" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N29">
         <v>1000</v>
       </c>
-      <c r="O29" s="14">
+      <c r="O29" s="18">
         <v>1990000</v>
       </c>
       <c r="Q29" s="3"/>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="1:18">
+      <c r="R29" s="12"/>
+      <c r="S29" s="12"/>
+    </row>
+    <row r="30" s="1" customFormat="1" spans="1:19">
       <c r="A30" s="1">
         <f t="shared" si="3"/>
         <v>2004002</v>
       </c>
-      <c r="B30" s="2">
+      <c r="B30" s="10">
         <v>200400</v>
       </c>
-      <c r="C30" s="2">
-        <v>2</v>
-      </c>
-      <c r="D30" s="3" t="s">
+      <c r="C30" s="10">
+        <v>2</v>
+      </c>
+      <c r="D30" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="E30" s="9">
+      <c r="E30" s="11">
         <v>200400009</v>
       </c>
-      <c r="F30" s="9" t="s">
+      <c r="F30" s="11" t="s">
         <v>52</v>
       </c>
       <c r="G30" s="1" t="s">
@@ -2335,7 +2953,8 @@
         <v>2</v>
       </c>
       <c r="I30" s="1">
-        <v>10000</v>
+        <f t="shared" si="4"/>
+        <v>100000</v>
       </c>
       <c r="J30" s="1">
         <v>500000000</v>
@@ -2346,36 +2965,37 @@
       <c r="L30" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M30" s="16" t="s">
+      <c r="M30" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N30">
         <v>100000</v>
       </c>
-      <c r="O30" s="14">
+      <c r="O30" s="18">
         <v>1990000</v>
       </c>
       <c r="Q30" s="3"/>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="1:18">
+      <c r="R30" s="12"/>
+      <c r="S30" s="12"/>
+    </row>
+    <row r="31" s="1" customFormat="1" spans="1:19">
       <c r="A31" s="1">
         <f t="shared" si="3"/>
         <v>2004003</v>
       </c>
-      <c r="B31" s="2">
+      <c r="B31" s="10">
         <v>200400</v>
       </c>
-      <c r="C31" s="2">
-        <v>2</v>
-      </c>
-      <c r="D31" s="3" t="s">
+      <c r="C31" s="10">
+        <v>2</v>
+      </c>
+      <c r="D31" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="E31" s="9">
+      <c r="E31" s="11">
         <v>200400009</v>
       </c>
-      <c r="F31" s="9" t="s">
+      <c r="F31" s="11" t="s">
         <v>52</v>
       </c>
       <c r="G31" s="1" t="s">
@@ -2385,7 +3005,8 @@
         <v>3</v>
       </c>
       <c r="I31" s="1">
-        <v>1000000</v>
+        <f t="shared" si="4"/>
+        <v>10000000</v>
       </c>
       <c r="J31" s="1">
         <v>-1</v>
@@ -2396,36 +3017,37 @@
       <c r="L31" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M31" s="16" t="s">
+      <c r="M31" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N31">
         <v>10000000</v>
       </c>
-      <c r="O31" s="14">
+      <c r="O31" s="18">
         <v>1990000</v>
       </c>
       <c r="Q31" s="3"/>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="1:18">
+      <c r="R31" s="12"/>
+      <c r="S31" s="12"/>
+    </row>
+    <row r="32" spans="1:19">
       <c r="A32" s="1">
         <f t="shared" si="3"/>
         <v>2005001</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B32" s="10">
         <v>200500</v>
       </c>
-      <c r="C32" s="2">
-        <v>2</v>
-      </c>
-      <c r="D32" s="2" t="s">
+      <c r="C32" s="10">
+        <v>2</v>
+      </c>
+      <c r="D32" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E32" s="9">
+      <c r="E32" s="11">
         <v>200500025</v>
       </c>
-      <c r="F32" s="9" t="s">
+      <c r="F32" s="11" t="s">
         <v>54</v>
       </c>
       <c r="G32" s="1" t="s">
@@ -2435,7 +3057,8 @@
         <v>1</v>
       </c>
       <c r="I32" s="1">
-        <v>100</v>
+        <f t="shared" si="4"/>
+        <v>1000</v>
       </c>
       <c r="J32" s="1">
         <v>5000000</v>
@@ -2446,36 +3069,37 @@
       <c r="L32" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M32" s="16" t="s">
+      <c r="M32" s="20" t="s">
         <v>55</v>
       </c>
       <c r="N32">
         <v>1000</v>
       </c>
-      <c r="O32" s="14">
+      <c r="O32" s="18">
         <v>1990000</v>
       </c>
       <c r="Q32" s="3"/>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="1:18">
+      <c r="R32" s="12"/>
+      <c r="S32" s="12"/>
+    </row>
+    <row r="33" spans="1:19">
       <c r="A33" s="1">
         <f t="shared" si="3"/>
         <v>2005002</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33" s="10">
         <v>200500</v>
       </c>
-      <c r="C33" s="2">
-        <v>2</v>
-      </c>
-      <c r="D33" s="2" t="s">
+      <c r="C33" s="10">
+        <v>2</v>
+      </c>
+      <c r="D33" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E33" s="9">
+      <c r="E33" s="11">
         <v>200500025</v>
       </c>
-      <c r="F33" s="9" t="s">
+      <c r="F33" s="11" t="s">
         <v>54</v>
       </c>
       <c r="G33" s="1" t="s">
@@ -2485,7 +3109,8 @@
         <v>2</v>
       </c>
       <c r="I33" s="1">
-        <v>10000</v>
+        <f t="shared" si="4"/>
+        <v>100000</v>
       </c>
       <c r="J33" s="1">
         <v>500000000</v>
@@ -2496,36 +3121,37 @@
       <c r="L33" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M33" s="16" t="s">
+      <c r="M33" s="20" t="s">
         <v>55</v>
       </c>
       <c r="N33">
         <v>100000</v>
       </c>
-      <c r="O33" s="14">
+      <c r="O33" s="18">
         <v>1990000</v>
       </c>
       <c r="Q33" s="3"/>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="1:18">
+      <c r="R33" s="12"/>
+      <c r="S33" s="12"/>
+    </row>
+    <row r="34" spans="1:19">
       <c r="A34" s="1">
         <f t="shared" si="3"/>
         <v>2005003</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34" s="10">
         <v>200500</v>
       </c>
-      <c r="C34" s="2">
-        <v>2</v>
-      </c>
-      <c r="D34" s="2" t="s">
+      <c r="C34" s="10">
+        <v>2</v>
+      </c>
+      <c r="D34" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E34" s="9">
+      <c r="E34" s="11">
         <v>200500025</v>
       </c>
-      <c r="F34" s="9" t="s">
+      <c r="F34" s="11" t="s">
         <v>54</v>
       </c>
       <c r="G34" s="1" t="s">
@@ -2535,7 +3161,8 @@
         <v>3</v>
       </c>
       <c r="I34" s="1">
-        <v>1000000</v>
+        <f t="shared" si="4"/>
+        <v>10000000</v>
       </c>
       <c r="J34" s="1">
         <v>-1</v>
@@ -2546,36 +3173,37 @@
       <c r="L34" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M34" s="16" t="s">
+      <c r="M34" s="20" t="s">
         <v>55</v>
       </c>
       <c r="N34">
         <v>10000000</v>
       </c>
-      <c r="O34" s="14">
+      <c r="O34" s="18">
         <v>1990000</v>
       </c>
       <c r="Q34" s="3"/>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="1:18">
+      <c r="R34" s="12"/>
+      <c r="S34" s="12"/>
+    </row>
+    <row r="35" spans="1:19">
       <c r="A35" s="1">
         <f t="shared" si="3"/>
         <v>2006001</v>
       </c>
-      <c r="B35" s="2">
+      <c r="B35" s="10">
         <v>200600</v>
       </c>
-      <c r="C35" s="2">
-        <v>2</v>
-      </c>
-      <c r="D35" s="9" t="s">
+      <c r="C35" s="10">
+        <v>2</v>
+      </c>
+      <c r="D35" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="E35" s="9">
+      <c r="E35" s="11">
         <v>200600001</v>
       </c>
-      <c r="F35" s="9" t="s">
+      <c r="F35" s="11" t="s">
         <v>57</v>
       </c>
       <c r="G35" s="1" t="s">
@@ -2585,7 +3213,8 @@
         <v>1</v>
       </c>
       <c r="I35" s="1">
-        <v>100</v>
+        <f t="shared" si="4"/>
+        <v>1000</v>
       </c>
       <c r="J35" s="1">
         <v>5000000</v>
@@ -2596,36 +3225,37 @@
       <c r="L35" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M35" s="16" t="s">
+      <c r="M35" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N35">
         <v>1000</v>
       </c>
-      <c r="O35" s="14">
+      <c r="O35" s="18">
         <v>1990000</v>
       </c>
       <c r="Q35" s="3"/>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="36" spans="1:18">
+      <c r="R35" s="12"/>
+      <c r="S35" s="12"/>
+    </row>
+    <row r="36" s="1" customFormat="1" spans="1:19">
       <c r="A36" s="1">
         <f t="shared" si="3"/>
         <v>2006002</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B36" s="10">
         <v>200600</v>
       </c>
-      <c r="C36" s="2">
-        <v>2</v>
-      </c>
-      <c r="D36" s="9" t="s">
+      <c r="C36" s="10">
+        <v>2</v>
+      </c>
+      <c r="D36" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="E36" s="9">
+      <c r="E36" s="11">
         <v>200600001</v>
       </c>
-      <c r="F36" s="9" t="s">
+      <c r="F36" s="11" t="s">
         <v>57</v>
       </c>
       <c r="G36" s="1" t="s">
@@ -2635,7 +3265,8 @@
         <v>2</v>
       </c>
       <c r="I36" s="1">
-        <v>10000</v>
+        <f t="shared" si="4"/>
+        <v>100000</v>
       </c>
       <c r="J36" s="1">
         <v>500000000</v>
@@ -2646,36 +3277,37 @@
       <c r="L36" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M36" s="16" t="s">
+      <c r="M36" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N36">
         <v>100000</v>
       </c>
-      <c r="O36" s="14">
+      <c r="O36" s="18">
         <v>1990000</v>
       </c>
       <c r="Q36" s="3"/>
-      <c r="R36" s="3"/>
-    </row>
-    <row r="37" spans="1:18">
+      <c r="R36" s="12"/>
+      <c r="S36" s="12"/>
+    </row>
+    <row r="37" s="1" customFormat="1" spans="1:19">
       <c r="A37" s="1">
         <f t="shared" si="3"/>
         <v>2006003</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B37" s="10">
         <v>200600</v>
       </c>
-      <c r="C37" s="2">
-        <v>2</v>
-      </c>
-      <c r="D37" s="9" t="s">
+      <c r="C37" s="10">
+        <v>2</v>
+      </c>
+      <c r="D37" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="E37" s="9">
+      <c r="E37" s="11">
         <v>200600001</v>
       </c>
-      <c r="F37" s="9" t="s">
+      <c r="F37" s="11" t="s">
         <v>57</v>
       </c>
       <c r="G37" s="1" t="s">
@@ -2685,7 +3317,8 @@
         <v>3</v>
       </c>
       <c r="I37" s="1">
-        <v>1000000</v>
+        <f t="shared" si="4"/>
+        <v>10000000</v>
       </c>
       <c r="J37" s="1">
         <v>-1</v>
@@ -2696,36 +3329,37 @@
       <c r="L37" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M37" s="16" t="s">
+      <c r="M37" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N37">
         <v>10000000</v>
       </c>
-      <c r="O37" s="14">
+      <c r="O37" s="18">
         <v>1990000</v>
       </c>
       <c r="Q37" s="3"/>
       <c r="R37"/>
-    </row>
-    <row r="38" spans="1:18">
+      <c r="S37" s="12"/>
+    </row>
+    <row r="38" spans="1:19">
       <c r="A38" s="1">
         <f t="shared" si="3"/>
         <v>2007001</v>
       </c>
-      <c r="B38" s="2">
+      <c r="B38" s="10">
         <v>200700</v>
       </c>
-      <c r="C38" s="2">
-        <v>2</v>
-      </c>
-      <c r="D38" s="2" t="s">
+      <c r="C38" s="10">
+        <v>2</v>
+      </c>
+      <c r="D38" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="E38" s="9">
+      <c r="E38" s="11">
         <v>200700001</v>
       </c>
-      <c r="F38" s="9" t="s">
+      <c r="F38" s="11" t="s">
         <v>59</v>
       </c>
       <c r="G38" s="1" t="s">
@@ -2735,7 +3369,8 @@
         <v>1</v>
       </c>
       <c r="I38" s="1">
-        <v>100</v>
+        <f t="shared" si="4"/>
+        <v>1000</v>
       </c>
       <c r="J38" s="1">
         <v>5000000</v>
@@ -2746,37 +3381,38 @@
       <c r="L38" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M38" s="16" t="s">
+      <c r="M38" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N38">
         <v>1000</v>
       </c>
-      <c r="O38" s="14">
+      <c r="O38" s="18">
         <v>1990000</v>
       </c>
       <c r="Q38" s="3"/>
-      <c r="R38" s="3"/>
-    </row>
-    <row r="39" spans="1:18">
+      <c r="R38" s="12"/>
+      <c r="S38" s="12"/>
+    </row>
+    <row r="39" s="1" customFormat="1" spans="1:19">
       <c r="A39" s="1">
         <f t="shared" si="3"/>
         <v>2007002</v>
       </c>
-      <c r="B39" s="2">
+      <c r="B39" s="10">
         <v>200700</v>
       </c>
-      <c r="C39" s="2">
-        <v>2</v>
-      </c>
-      <c r="D39" s="2" t="str">
-        <f t="shared" ref="D39:D40" si="5">D38</f>
+      <c r="C39" s="10">
+        <v>2</v>
+      </c>
+      <c r="D39" s="10" t="str">
+        <f t="shared" ref="D36:D40" si="6">D38</f>
         <v>越南色碟</v>
       </c>
-      <c r="E39" s="9">
+      <c r="E39" s="11">
         <v>200700001</v>
       </c>
-      <c r="F39" s="9" t="s">
+      <c r="F39" s="11" t="s">
         <v>59</v>
       </c>
       <c r="G39" s="1" t="s">
@@ -2786,7 +3422,8 @@
         <v>2</v>
       </c>
       <c r="I39" s="1">
-        <v>10000</v>
+        <f t="shared" si="4"/>
+        <v>100000</v>
       </c>
       <c r="J39" s="1">
         <v>500000000</v>
@@ -2797,37 +3434,38 @@
       <c r="L39" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M39" s="16" t="s">
+      <c r="M39" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N39">
         <v>100000</v>
       </c>
-      <c r="O39" s="14">
+      <c r="O39" s="18">
         <v>1990000</v>
       </c>
       <c r="Q39" s="3"/>
-      <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="1:18">
+      <c r="R39" s="12"/>
+      <c r="S39" s="12"/>
+    </row>
+    <row r="40" s="1" customFormat="1" spans="1:19">
       <c r="A40" s="1">
         <f t="shared" si="3"/>
         <v>2007003</v>
       </c>
-      <c r="B40" s="2">
+      <c r="B40" s="10">
         <v>200700</v>
       </c>
-      <c r="C40" s="2">
-        <v>2</v>
-      </c>
-      <c r="D40" s="2" t="str">
-        <f t="shared" si="5"/>
+      <c r="C40" s="10">
+        <v>2</v>
+      </c>
+      <c r="D40" s="10" t="str">
+        <f t="shared" si="6"/>
         <v>越南色碟</v>
       </c>
-      <c r="E40" s="9">
+      <c r="E40" s="11">
         <v>200700001</v>
       </c>
-      <c r="F40" s="9" t="s">
+      <c r="F40" s="11" t="s">
         <v>59</v>
       </c>
       <c r="G40" s="1" t="s">
@@ -2837,7 +3475,8 @@
         <v>3</v>
       </c>
       <c r="I40" s="1">
-        <v>1000000</v>
+        <f t="shared" si="4"/>
+        <v>10000000</v>
       </c>
       <c r="J40" s="1">
         <v>-1</v>
@@ -2848,34 +3487,35 @@
       <c r="L40" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M40" s="16" t="s">
+      <c r="M40" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N40">
         <v>10000000</v>
       </c>
-      <c r="O40" s="14">
+      <c r="O40" s="18">
         <v>1990000</v>
       </c>
-    </row>
-    <row r="41" spans="1:18">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" s="1" customFormat="1" spans="1:19">
       <c r="A41" s="1">
         <f t="shared" si="3"/>
         <v>2008001</v>
       </c>
-      <c r="B41" s="2">
+      <c r="B41" s="10">
         <v>200800</v>
       </c>
-      <c r="C41" s="2">
-        <v>2</v>
-      </c>
-      <c r="D41" s="9" t="s">
+      <c r="C41" s="10">
+        <v>2</v>
+      </c>
+      <c r="D41" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E41" s="9">
+      <c r="E41" s="11">
         <v>200800001</v>
       </c>
-      <c r="F41" s="9" t="s">
+      <c r="F41" s="11" t="s">
         <v>61</v>
       </c>
       <c r="G41" s="1" t="s">
@@ -2885,7 +3525,8 @@
         <v>1</v>
       </c>
       <c r="I41" s="1">
-        <v>100</v>
+        <f t="shared" si="4"/>
+        <v>1000</v>
       </c>
       <c r="J41" s="1">
         <v>5000000</v>
@@ -2896,34 +3537,35 @@
       <c r="L41" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M41" s="16" t="s">
+      <c r="M41" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N41">
         <v>1000</v>
       </c>
-      <c r="O41" s="14">
+      <c r="O41" s="18">
         <v>1990000</v>
       </c>
-    </row>
-    <row r="42" spans="1:18">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" s="1" customFormat="1" spans="1:19">
       <c r="A42" s="1">
         <f t="shared" si="3"/>
         <v>2008002</v>
       </c>
-      <c r="B42" s="2">
+      <c r="B42" s="10">
         <v>200800</v>
       </c>
-      <c r="C42" s="2">
-        <v>2</v>
-      </c>
-      <c r="D42" s="9" t="s">
+      <c r="C42" s="10">
+        <v>2</v>
+      </c>
+      <c r="D42" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E42" s="9">
+      <c r="E42" s="11">
         <v>200800001</v>
       </c>
-      <c r="F42" s="9" t="s">
+      <c r="F42" s="11" t="s">
         <v>61</v>
       </c>
       <c r="G42" s="1" t="s">
@@ -2933,7 +3575,8 @@
         <v>2</v>
       </c>
       <c r="I42" s="1">
-        <v>10000</v>
+        <f t="shared" si="4"/>
+        <v>100000</v>
       </c>
       <c r="J42" s="1">
         <v>500000000</v>
@@ -2944,34 +3587,35 @@
       <c r="L42" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M42" s="16" t="s">
+      <c r="M42" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N42">
         <v>100000</v>
       </c>
-      <c r="O42" s="14">
+      <c r="O42" s="18">
         <v>1990000</v>
       </c>
-    </row>
-    <row r="43" spans="1:18">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" s="1" customFormat="1" spans="1:19">
       <c r="A43" s="1">
         <f t="shared" si="3"/>
         <v>2008003</v>
       </c>
-      <c r="B43" s="2">
+      <c r="B43" s="10">
         <v>200800</v>
       </c>
-      <c r="C43" s="2">
-        <v>2</v>
-      </c>
-      <c r="D43" s="9" t="s">
+      <c r="C43" s="10">
+        <v>2</v>
+      </c>
+      <c r="D43" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E43" s="9">
+      <c r="E43" s="11">
         <v>200800001</v>
       </c>
-      <c r="F43" s="9" t="s">
+      <c r="F43" s="11" t="s">
         <v>61</v>
       </c>
       <c r="G43" s="1" t="s">
@@ -2981,7 +3625,8 @@
         <v>3</v>
       </c>
       <c r="I43" s="1">
-        <v>1000000</v>
+        <f t="shared" si="4"/>
+        <v>10000000</v>
       </c>
       <c r="J43" s="1">
         <v>-1</v>
@@ -2992,34 +3637,35 @@
       <c r="L43" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M43" s="16" t="s">
+      <c r="M43" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N43">
         <v>10000000</v>
       </c>
-      <c r="O43" s="14">
+      <c r="O43" s="18">
         <v>1990000</v>
       </c>
-    </row>
-    <row r="44" spans="1:18">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="1:15">
       <c r="A44" s="1">
         <f t="shared" si="3"/>
         <v>2009001</v>
       </c>
-      <c r="B44" s="10">
+      <c r="B44" s="13">
         <v>200900</v>
       </c>
-      <c r="C44" s="2">
-        <v>2</v>
-      </c>
-      <c r="D44" s="10" t="s">
+      <c r="C44" s="10">
+        <v>2</v>
+      </c>
+      <c r="D44" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="E44" s="9">
+      <c r="E44" s="11">
         <v>200900001</v>
       </c>
-      <c r="F44" s="9" t="s">
+      <c r="F44" s="11" t="s">
         <v>63</v>
       </c>
       <c r="G44" s="1" t="s">
@@ -3029,7 +3675,8 @@
         <v>1</v>
       </c>
       <c r="I44" s="1">
-        <v>100</v>
+        <f t="shared" si="4"/>
+        <v>1000</v>
       </c>
       <c r="J44" s="1">
         <v>5000000</v>
@@ -3040,35 +3687,35 @@
       <c r="L44" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M44" s="16" t="s">
+      <c r="M44" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N44">
         <v>1000</v>
       </c>
-      <c r="O44" s="14">
+      <c r="O44" s="18">
         <v>1990000</v>
       </c>
     </row>
-    <row r="45" spans="1:18">
+    <row r="45" spans="1:15">
       <c r="A45" s="1">
         <f t="shared" si="3"/>
         <v>2009002</v>
       </c>
-      <c r="B45" s="2">
+      <c r="B45" s="10">
         <v>200900</v>
       </c>
-      <c r="C45" s="2">
-        <v>2</v>
-      </c>
-      <c r="D45" s="2" t="str">
+      <c r="C45" s="10">
+        <v>2</v>
+      </c>
+      <c r="D45" s="10" t="str">
         <f>D44</f>
         <v>魚蝦蟹</v>
       </c>
-      <c r="E45" s="9">
+      <c r="E45" s="11">
         <v>200900001</v>
       </c>
-      <c r="F45" s="9" t="s">
+      <c r="F45" s="11" t="s">
         <v>63</v>
       </c>
       <c r="G45" s="1" t="s">
@@ -3078,7 +3725,8 @@
         <v>2</v>
       </c>
       <c r="I45" s="1">
-        <v>10000</v>
+        <f t="shared" si="4"/>
+        <v>100000</v>
       </c>
       <c r="J45" s="1">
         <v>500000000</v>
@@ -3089,35 +3737,35 @@
       <c r="L45" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M45" s="16" t="s">
+      <c r="M45" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N45">
         <v>100000</v>
       </c>
-      <c r="O45" s="14">
+      <c r="O45" s="18">
         <v>1990000</v>
       </c>
     </row>
-    <row r="46" spans="1:18">
+    <row r="46" spans="1:15">
       <c r="A46" s="1">
         <f t="shared" si="3"/>
         <v>2009003</v>
       </c>
-      <c r="B46" s="2">
+      <c r="B46" s="10">
         <v>200900</v>
       </c>
-      <c r="C46" s="2">
-        <v>2</v>
-      </c>
-      <c r="D46" s="2" t="str">
+      <c r="C46" s="10">
+        <v>2</v>
+      </c>
+      <c r="D46" s="10" t="str">
         <f>D45</f>
         <v>魚蝦蟹</v>
       </c>
-      <c r="E46" s="9">
+      <c r="E46" s="11">
         <v>200900001</v>
       </c>
-      <c r="F46" s="9" t="s">
+      <c r="F46" s="11" t="s">
         <v>63</v>
       </c>
       <c r="G46" s="1" t="s">
@@ -3127,7 +3775,8 @@
         <v>3</v>
       </c>
       <c r="I46" s="1">
-        <v>1000000</v>
+        <f t="shared" si="4"/>
+        <v>10000000</v>
       </c>
       <c r="J46" s="1">
         <v>-1</v>
@@ -3138,34 +3787,34 @@
       <c r="L46" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M46" s="16" t="s">
+      <c r="M46" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N46">
         <v>10000000</v>
       </c>
-      <c r="O46" s="14">
+      <c r="O46" s="18">
         <v>1990000</v>
       </c>
     </row>
-    <row r="47" spans="1:18">
+    <row r="47" spans="1:15">
       <c r="A47" s="1">
         <f t="shared" si="3"/>
         <v>2010001</v>
       </c>
-      <c r="B47" s="2">
+      <c r="B47" s="10">
         <v>201000</v>
       </c>
-      <c r="C47" s="2">
-        <v>2</v>
-      </c>
-      <c r="D47" s="2" t="s">
+      <c r="C47" s="10">
+        <v>2</v>
+      </c>
+      <c r="D47" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="E47" s="9">
+      <c r="E47" s="11">
         <v>101000006</v>
       </c>
-      <c r="F47" s="9"/>
+      <c r="F47" s="11"/>
       <c r="G47" s="1" t="s">
         <v>32</v>
       </c>
@@ -3173,7 +3822,8 @@
         <v>1</v>
       </c>
       <c r="I47" s="1">
-        <v>100</v>
+        <f t="shared" si="4"/>
+        <v>1000</v>
       </c>
       <c r="J47" s="1">
         <v>5000000</v>
@@ -3184,34 +3834,34 @@
       <c r="L47" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M47" s="16" t="s">
+      <c r="M47" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N47">
         <v>1000</v>
       </c>
-      <c r="O47" s="14">
+      <c r="O47" s="18">
         <v>1990000</v>
       </c>
     </row>
-    <row r="48" spans="1:18">
+    <row r="48" spans="1:15">
       <c r="A48" s="1">
         <f t="shared" si="3"/>
         <v>2010002</v>
       </c>
-      <c r="B48" s="2">
+      <c r="B48" s="10">
         <v>201000</v>
       </c>
-      <c r="C48" s="2">
-        <v>2</v>
-      </c>
-      <c r="D48" s="2" t="s">
+      <c r="C48" s="10">
+        <v>2</v>
+      </c>
+      <c r="D48" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="E48" s="9">
+      <c r="E48" s="11">
         <v>101000006</v>
       </c>
-      <c r="F48" s="9"/>
+      <c r="F48" s="11"/>
       <c r="G48" s="1" t="s">
         <v>35</v>
       </c>
@@ -3219,7 +3869,8 @@
         <v>2</v>
       </c>
       <c r="I48" s="1">
-        <v>10000</v>
+        <f t="shared" si="4"/>
+        <v>100000</v>
       </c>
       <c r="J48" s="1">
         <v>500000000</v>
@@ -3230,13 +3881,13 @@
       <c r="L48" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M48" s="16" t="s">
+      <c r="M48" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N48">
         <v>100000</v>
       </c>
-      <c r="O48" s="14">
+      <c r="O48" s="18">
         <v>1990000</v>
       </c>
     </row>
@@ -3245,19 +3896,19 @@
         <f t="shared" si="3"/>
         <v>2010003</v>
       </c>
-      <c r="B49" s="2">
+      <c r="B49" s="10">
         <v>201000</v>
       </c>
-      <c r="C49" s="2">
-        <v>2</v>
-      </c>
-      <c r="D49" s="2" t="s">
+      <c r="C49" s="10">
+        <v>2</v>
+      </c>
+      <c r="D49" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="E49" s="9">
+      <c r="E49" s="11">
         <v>101000006</v>
       </c>
-      <c r="F49" s="9"/>
+      <c r="F49" s="11"/>
       <c r="G49" s="1" t="s">
         <v>36</v>
       </c>
@@ -3265,7 +3916,8 @@
         <v>3</v>
       </c>
       <c r="I49" s="1">
-        <v>1000000</v>
+        <f t="shared" si="4"/>
+        <v>10000000</v>
       </c>
       <c r="J49" s="1">
         <v>-1</v>
@@ -3276,13 +3928,13 @@
       <c r="L49" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M49" s="16" t="s">
+      <c r="M49" s="20" t="s">
         <v>34</v>
       </c>
       <c r="N49">
         <v>10000000</v>
       </c>
-      <c r="O49" s="14">
+      <c r="O49" s="18">
         <v>1990000</v>
       </c>
     </row>
@@ -3291,19 +3943,19 @@
         <f t="shared" si="3"/>
         <v>3001001</v>
       </c>
-      <c r="B50" s="2">
+      <c r="B50" s="10">
         <v>300100</v>
       </c>
-      <c r="C50" s="2">
+      <c r="C50" s="10">
         <v>3</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D50" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="E50" s="9">
+      <c r="E50" s="11">
         <v>300100001</v>
       </c>
-      <c r="F50" s="9" t="s">
+      <c r="F50" s="11" t="s">
         <v>66</v>
       </c>
       <c r="G50" s="1" t="s">
@@ -3313,7 +3965,8 @@
         <v>1</v>
       </c>
       <c r="I50" s="1">
-        <v>100</v>
+        <f t="shared" si="4"/>
+        <v>1000</v>
       </c>
       <c r="J50" s="1">
         <v>-1</v>
@@ -3321,37 +3974,37 @@
       <c r="K50" s="1">
         <v>0</v>
       </c>
-      <c r="L50" s="17" t="s">
+      <c r="L50" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="M50" s="17" t="s">
+      <c r="M50" s="21" t="s">
         <v>68</v>
       </c>
       <c r="N50">
-        <v>500</v>
-      </c>
-      <c r="O50" s="14">
+        <v>1000</v>
+      </c>
+      <c r="O50" s="18">
         <v>1990000</v>
       </c>
     </row>
-    <row r="51" spans="1:15">
+    <row r="51" s="1" customFormat="1" spans="1:19">
       <c r="A51" s="1">
         <f t="shared" si="3"/>
         <v>3001002</v>
       </c>
-      <c r="B51" s="2">
+      <c r="B51" s="10">
         <v>300100</v>
       </c>
-      <c r="C51" s="2">
+      <c r="C51" s="10">
         <v>3</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="D51" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="E51" s="9">
+      <c r="E51" s="11">
         <v>300100001</v>
       </c>
-      <c r="F51" s="9" t="s">
+      <c r="F51" s="11" t="s">
         <v>66</v>
       </c>
       <c r="G51" s="1" t="s">
@@ -3361,7 +4014,8 @@
         <v>2</v>
       </c>
       <c r="I51" s="1">
-        <v>10000</v>
+        <f t="shared" si="4"/>
+        <v>100000</v>
       </c>
       <c r="J51" s="1">
         <v>-1</v>
@@ -3369,37 +4023,38 @@
       <c r="K51" s="1">
         <v>0</v>
       </c>
-      <c r="L51" s="17" t="s">
+      <c r="L51" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="M51" s="17" t="s">
+      <c r="M51" s="21" t="s">
         <v>68</v>
       </c>
       <c r="N51">
-        <v>20000</v>
-      </c>
-      <c r="O51" s="14">
+        <v>100000</v>
+      </c>
+      <c r="O51" s="18">
         <v>1990000</v>
       </c>
-    </row>
-    <row r="52" spans="1:15">
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" s="1" customFormat="1" spans="1:19">
       <c r="A52" s="1">
         <f t="shared" si="3"/>
         <v>3001003</v>
       </c>
-      <c r="B52" s="2">
+      <c r="B52" s="10">
         <v>300100</v>
       </c>
-      <c r="C52" s="2">
+      <c r="C52" s="10">
         <v>3</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="D52" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="E52" s="9">
+      <c r="E52" s="11">
         <v>300100001</v>
       </c>
-      <c r="F52" s="9" t="s">
+      <c r="F52" s="11" t="s">
         <v>66</v>
       </c>
       <c r="G52" s="1" t="s">
@@ -3409,7 +4064,8 @@
         <v>3</v>
       </c>
       <c r="I52" s="1">
-        <v>1000000</v>
+        <f t="shared" si="4"/>
+        <v>10000000</v>
       </c>
       <c r="J52" s="1">
         <v>-1</v>
@@ -3417,37 +4073,38 @@
       <c r="K52" s="1">
         <v>0</v>
       </c>
-      <c r="L52" s="17" t="s">
+      <c r="L52" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="M52" s="17" t="s">
+      <c r="M52" s="21" t="s">
         <v>68</v>
       </c>
       <c r="N52">
-        <v>2000000</v>
-      </c>
-      <c r="O52" s="14">
+        <v>10000000</v>
+      </c>
+      <c r="O52" s="18">
         <v>1990000</v>
       </c>
-    </row>
-    <row r="53" spans="1:15">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" s="1" customFormat="1" spans="1:19">
       <c r="A53" s="1">
         <f t="shared" si="3"/>
         <v>3002001</v>
       </c>
-      <c r="B53" s="2">
+      <c r="B53" s="10">
         <v>300200</v>
       </c>
-      <c r="C53" s="2">
+      <c r="C53" s="10">
         <v>3</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="D53" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="E53" s="9">
+      <c r="E53" s="11">
         <v>300200006</v>
       </c>
-      <c r="F53" s="9" t="s">
+      <c r="F53" s="11" t="s">
         <v>70</v>
       </c>
       <c r="G53" s="1" t="s">
@@ -3457,7 +4114,8 @@
         <v>1</v>
       </c>
       <c r="I53" s="1">
-        <v>100</v>
+        <f t="shared" si="4"/>
+        <v>2000</v>
       </c>
       <c r="J53" s="1">
         <v>-1</v>
@@ -3465,37 +4123,38 @@
       <c r="K53" s="1">
         <v>0</v>
       </c>
-      <c r="L53" s="17" t="s">
+      <c r="L53" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="M53" s="17" t="s">
+      <c r="M53" s="21" t="s">
         <v>68</v>
       </c>
       <c r="N53">
-        <v>500</v>
-      </c>
-      <c r="O53" s="14">
+        <v>2000</v>
+      </c>
+      <c r="O53" s="18">
         <v>1990000</v>
       </c>
-    </row>
-    <row r="54" spans="1:15">
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" s="1" customFormat="1" spans="1:19">
       <c r="A54" s="1">
         <f t="shared" si="3"/>
         <v>3002002</v>
       </c>
-      <c r="B54" s="2">
+      <c r="B54" s="10">
         <v>300200</v>
       </c>
-      <c r="C54" s="2">
+      <c r="C54" s="10">
         <v>3</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="D54" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="E54" s="9">
+      <c r="E54" s="11">
         <v>300200006</v>
       </c>
-      <c r="F54" s="9" t="s">
+      <c r="F54" s="11" t="s">
         <v>70</v>
       </c>
       <c r="G54" s="1" t="s">
@@ -3505,7 +4164,8 @@
         <v>2</v>
       </c>
       <c r="I54" s="1">
-        <v>10000</v>
+        <f t="shared" si="4"/>
+        <v>200000</v>
       </c>
       <c r="J54" s="1">
         <v>-1</v>
@@ -3513,37 +4173,38 @@
       <c r="K54" s="1">
         <v>0</v>
       </c>
-      <c r="L54" s="17" t="s">
+      <c r="L54" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="M54" s="17" t="s">
+      <c r="M54" s="21" t="s">
         <v>68</v>
       </c>
       <c r="N54">
-        <v>20000</v>
-      </c>
-      <c r="O54" s="14">
+        <v>200000</v>
+      </c>
+      <c r="O54" s="18">
         <v>1990000</v>
       </c>
-    </row>
-    <row r="55" spans="1:15">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" s="1" customFormat="1" spans="1:19">
       <c r="A55" s="1">
         <f t="shared" si="3"/>
         <v>3002003</v>
       </c>
-      <c r="B55" s="2">
+      <c r="B55" s="10">
         <v>300200</v>
       </c>
-      <c r="C55" s="2">
+      <c r="C55" s="10">
         <v>3</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="D55" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="E55" s="9">
+      <c r="E55" s="11">
         <v>300200006</v>
       </c>
-      <c r="F55" s="9" t="s">
+      <c r="F55" s="11" t="s">
         <v>70</v>
       </c>
       <c r="G55" s="1" t="s">
@@ -3553,7 +4214,8 @@
         <v>3</v>
       </c>
       <c r="I55" s="1">
-        <v>1000000</v>
+        <f t="shared" si="4"/>
+        <v>20000000</v>
       </c>
       <c r="J55" s="1">
         <v>-1</v>
@@ -3561,1344 +4223,1360 @@
       <c r="K55" s="1">
         <v>0</v>
       </c>
-      <c r="L55" s="17" t="s">
+      <c r="L55" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="M55" s="17" t="s">
+      <c r="M55" s="21" t="s">
         <v>68</v>
       </c>
       <c r="N55">
-        <v>2000000</v>
-      </c>
-      <c r="O55" s="14">
+        <v>20000000</v>
+      </c>
+      <c r="O55" s="18">
         <v>1990000</v>
       </c>
-    </row>
-    <row r="56" spans="1:15">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" s="1" customFormat="1" spans="1:19">
       <c r="A56" s="1">
-        <f t="shared" ref="A56:A62" si="6">B56*100+H56</f>
+        <f t="shared" ref="A56:A62" si="7">B56*100+H56</f>
         <v>20010010</v>
       </c>
-      <c r="B56" s="9">
+      <c r="B56" s="11">
         <v>200100</v>
       </c>
-      <c r="C56" s="9">
-        <v>2</v>
-      </c>
-      <c r="D56" s="9" t="s">
+      <c r="C56" s="11">
+        <v>2</v>
+      </c>
+      <c r="D56" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="E56" s="9">
+      <c r="E56" s="11">
         <v>200100038</v>
       </c>
-      <c r="F56" s="9" t="s">
+      <c r="F56" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="G56" s="11" t="s">
+      <c r="G56" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="H56" s="11">
+      <c r="H56" s="14">
         <v>10</v>
       </c>
-      <c r="I56" s="11">
-        <v>0</v>
-      </c>
-      <c r="J56" s="11">
+      <c r="I56" s="14">
+        <v>0</v>
+      </c>
+      <c r="J56" s="14">
         <v>-1</v>
       </c>
       <c r="K56" s="1">
         <v>0</v>
       </c>
-      <c r="L56" s="11" t="s">
+      <c r="L56" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="M56" s="11">
+      <c r="M56" s="14">
         <v>0</v>
       </c>
       <c r="N56">
-        <v>100</v>
-      </c>
-      <c r="O56" s="15">
+        <v>10</v>
+      </c>
+      <c r="O56" s="19">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="57" spans="1:15">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" s="1" customFormat="1" spans="1:19">
       <c r="A57" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>20010011</v>
       </c>
-      <c r="B57" s="9">
+      <c r="B57" s="11">
         <v>200100</v>
       </c>
-      <c r="C57" s="9">
-        <v>2</v>
-      </c>
-      <c r="D57" s="9" t="s">
+      <c r="C57" s="11">
+        <v>2</v>
+      </c>
+      <c r="D57" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="E57" s="9">
+      <c r="E57" s="11">
         <v>200100038</v>
       </c>
-      <c r="F57" s="9" t="s">
+      <c r="F57" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="G57" s="11" t="s">
+      <c r="G57" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="H57" s="11">
+      <c r="H57" s="14">
         <v>11</v>
       </c>
-      <c r="I57" s="11">
-        <v>0</v>
-      </c>
-      <c r="J57" s="11">
+      <c r="I57" s="14">
+        <v>0</v>
+      </c>
+      <c r="J57" s="14">
         <v>-1</v>
       </c>
       <c r="K57" s="1">
         <v>0</v>
       </c>
-      <c r="L57" s="11" t="s">
+      <c r="L57" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="M57" s="11">
+      <c r="M57" s="14">
         <v>0</v>
       </c>
       <c r="N57">
-        <v>100</v>
-      </c>
-      <c r="O57" s="15">
+        <v>1000</v>
+      </c>
+      <c r="O57" s="19">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="58" spans="1:15">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" s="1" customFormat="1" spans="1:19">
       <c r="A58" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>20010012</v>
       </c>
-      <c r="B58" s="9">
+      <c r="B58" s="11">
         <v>200100</v>
       </c>
-      <c r="C58" s="9">
-        <v>2</v>
-      </c>
-      <c r="D58" s="9" t="s">
+      <c r="C58" s="11">
+        <v>2</v>
+      </c>
+      <c r="D58" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="E58" s="9">
+      <c r="E58" s="11">
         <v>200100038</v>
       </c>
-      <c r="F58" s="9" t="s">
+      <c r="F58" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="G58" s="11" t="s">
+      <c r="G58" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="H58" s="11">
+      <c r="H58" s="14">
         <v>12</v>
       </c>
-      <c r="I58" s="11">
-        <v>0</v>
-      </c>
-      <c r="J58" s="11">
+      <c r="I58" s="14">
+        <v>0</v>
+      </c>
+      <c r="J58" s="14">
         <v>-1</v>
       </c>
       <c r="K58" s="1">
         <v>0</v>
       </c>
-      <c r="L58" s="11" t="s">
+      <c r="L58" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="M58" s="11">
+      <c r="M58" s="14">
         <v>0</v>
       </c>
       <c r="N58">
-        <v>100</v>
-      </c>
-      <c r="O58" s="15">
+        <v>100000</v>
+      </c>
+      <c r="O58" s="19">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="59" spans="1:15">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" s="1" customFormat="1" spans="1:19">
       <c r="A59" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>20010110</v>
       </c>
-      <c r="B59" s="9">
+      <c r="B59" s="11">
         <v>200101</v>
       </c>
-      <c r="C59" s="9">
-        <v>2</v>
-      </c>
-      <c r="D59" s="9" t="s">
+      <c r="C59" s="11">
+        <v>2</v>
+      </c>
+      <c r="D59" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="E59" s="9">
+      <c r="E59" s="11">
         <v>200101001</v>
       </c>
-      <c r="F59" s="9" t="s">
+      <c r="F59" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="G59" s="11" t="s">
+      <c r="G59" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="H59" s="11">
+      <c r="H59" s="14">
         <v>10</v>
       </c>
-      <c r="I59" s="11">
-        <v>0</v>
-      </c>
-      <c r="J59" s="11">
+      <c r="I59" s="14">
+        <v>0</v>
+      </c>
+      <c r="J59" s="14">
         <v>-1</v>
       </c>
       <c r="K59" s="1">
         <v>0</v>
       </c>
-      <c r="L59" s="11" t="s">
+      <c r="L59" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="M59" s="11">
+      <c r="M59" s="14">
         <v>0</v>
       </c>
       <c r="N59">
-        <v>100</v>
-      </c>
-      <c r="O59" s="15">
+        <v>10</v>
+      </c>
+      <c r="O59" s="19">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="60" spans="1:15">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" s="1" customFormat="1" spans="1:19">
       <c r="A60" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>20010111</v>
       </c>
-      <c r="B60" s="9">
+      <c r="B60" s="11">
         <v>200101</v>
       </c>
-      <c r="C60" s="9">
-        <v>2</v>
-      </c>
-      <c r="D60" s="9" t="s">
+      <c r="C60" s="11">
+        <v>2</v>
+      </c>
+      <c r="D60" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="E60" s="9">
+      <c r="E60" s="11">
         <v>200101001</v>
       </c>
-      <c r="F60" s="9" t="s">
+      <c r="F60" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="G60" s="11" t="s">
+      <c r="G60" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="H60" s="11">
+      <c r="H60" s="14">
         <v>11</v>
       </c>
-      <c r="I60" s="11">
-        <v>0</v>
-      </c>
-      <c r="J60" s="11">
+      <c r="I60" s="14">
+        <v>0</v>
+      </c>
+      <c r="J60" s="14">
         <v>-1</v>
       </c>
       <c r="K60" s="1">
         <v>0</v>
       </c>
-      <c r="L60" s="11" t="s">
+      <c r="L60" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="M60" s="11">
+      <c r="M60" s="14">
         <v>0</v>
       </c>
       <c r="N60">
-        <v>100</v>
-      </c>
-      <c r="O60" s="15">
+        <v>1000</v>
+      </c>
+      <c r="O60" s="19">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="61" spans="1:15">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" s="1" customFormat="1" spans="1:19">
       <c r="A61" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>20010112</v>
       </c>
-      <c r="B61" s="9">
+      <c r="B61" s="11">
         <v>200101</v>
       </c>
-      <c r="C61" s="9">
-        <v>2</v>
-      </c>
-      <c r="D61" s="9" t="s">
+      <c r="C61" s="11">
+        <v>2</v>
+      </c>
+      <c r="D61" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="E61" s="9">
+      <c r="E61" s="11">
         <v>200101001</v>
       </c>
-      <c r="F61" s="9" t="s">
+      <c r="F61" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="G61" s="11" t="s">
+      <c r="G61" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="H61" s="11">
+      <c r="H61" s="14">
         <v>12</v>
       </c>
-      <c r="I61" s="11">
-        <v>0</v>
-      </c>
-      <c r="J61" s="11">
+      <c r="I61" s="14">
+        <v>0</v>
+      </c>
+      <c r="J61" s="14">
         <v>-1</v>
       </c>
       <c r="K61" s="1">
         <v>0</v>
       </c>
-      <c r="L61" s="11" t="s">
+      <c r="L61" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="M61" s="11">
+      <c r="M61" s="14">
         <v>0</v>
       </c>
       <c r="N61">
-        <v>100</v>
-      </c>
-      <c r="O61" s="15">
+        <v>100000</v>
+      </c>
+      <c r="O61" s="19">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="62" spans="1:15">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" s="1" customFormat="1" spans="1:19">
       <c r="A62" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>20030010</v>
       </c>
-      <c r="B62" s="9">
+      <c r="B62" s="11">
         <v>200300</v>
       </c>
-      <c r="C62" s="9">
-        <v>2</v>
-      </c>
-      <c r="D62" s="9" t="s">
+      <c r="C62" s="11">
+        <v>2</v>
+      </c>
+      <c r="D62" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="E62" s="9">
+      <c r="E62" s="11">
         <v>200300001</v>
       </c>
-      <c r="F62" s="9" t="s">
+      <c r="F62" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="G62" s="11" t="s">
+      <c r="G62" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="H62" s="11">
+      <c r="H62" s="14">
         <v>10</v>
       </c>
-      <c r="I62" s="11">
-        <v>0</v>
-      </c>
-      <c r="J62" s="11">
+      <c r="I62" s="14">
+        <v>0</v>
+      </c>
+      <c r="J62" s="14">
         <v>-1</v>
       </c>
       <c r="K62" s="1">
         <v>0</v>
       </c>
-      <c r="L62" s="11" t="s">
+      <c r="L62" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="M62" s="11">
+      <c r="M62" s="14">
         <v>0</v>
       </c>
       <c r="N62">
-        <v>100</v>
-      </c>
-      <c r="O62" s="15">
+        <v>10</v>
+      </c>
+      <c r="O62" s="19">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="63" spans="1:15">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" s="1" customFormat="1" spans="1:19">
       <c r="A63" s="1">
-        <f t="shared" ref="A63:A71" si="7">B63*100+H63</f>
+        <f t="shared" ref="A63:A71" si="8">B63*100+H63</f>
         <v>20030011</v>
       </c>
-      <c r="B63" s="9">
+      <c r="B63" s="11">
         <v>200300</v>
       </c>
-      <c r="C63" s="9">
-        <v>2</v>
-      </c>
-      <c r="D63" s="9" t="s">
+      <c r="C63" s="11">
+        <v>2</v>
+      </c>
+      <c r="D63" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="E63" s="9">
+      <c r="E63" s="11">
         <v>200300001</v>
       </c>
-      <c r="F63" s="9" t="s">
+      <c r="F63" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="G63" s="11" t="s">
+      <c r="G63" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="H63" s="11">
+      <c r="H63" s="14">
         <v>11</v>
       </c>
-      <c r="I63" s="11">
-        <v>0</v>
-      </c>
-      <c r="J63" s="11">
+      <c r="I63" s="14">
+        <v>0</v>
+      </c>
+      <c r="J63" s="14">
         <v>-1</v>
       </c>
       <c r="K63" s="1">
         <v>0</v>
       </c>
-      <c r="L63" s="11" t="s">
+      <c r="L63" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="M63" s="11">
+      <c r="M63" s="14">
         <v>0</v>
       </c>
       <c r="N63">
-        <v>100</v>
-      </c>
-      <c r="O63" s="15">
+        <v>1000</v>
+      </c>
+      <c r="O63" s="19">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="64" spans="1:15">
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" s="1" customFormat="1" spans="1:19">
       <c r="A64" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>20030012</v>
       </c>
-      <c r="B64" s="9">
+      <c r="B64" s="11">
         <v>200300</v>
       </c>
-      <c r="C64" s="9">
-        <v>2</v>
-      </c>
-      <c r="D64" s="9" t="s">
+      <c r="C64" s="11">
+        <v>2</v>
+      </c>
+      <c r="D64" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="E64" s="9">
+      <c r="E64" s="11">
         <v>200300001</v>
       </c>
-      <c r="F64" s="9" t="s">
+      <c r="F64" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="G64" s="11" t="s">
+      <c r="G64" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="H64" s="11">
+      <c r="H64" s="14">
         <v>12</v>
       </c>
-      <c r="I64" s="11">
-        <v>0</v>
-      </c>
-      <c r="J64" s="11">
+      <c r="I64" s="14">
+        <v>0</v>
+      </c>
+      <c r="J64" s="14">
         <v>-1</v>
       </c>
       <c r="K64" s="1">
         <v>0</v>
       </c>
-      <c r="L64" s="11" t="s">
+      <c r="L64" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="M64" s="11">
+      <c r="M64" s="14">
         <v>0</v>
       </c>
       <c r="N64">
-        <v>100</v>
-      </c>
-      <c r="O64" s="15">
+        <v>100000</v>
+      </c>
+      <c r="O64" s="19">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="65" spans="1:15">
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" s="1" customFormat="1" spans="1:19">
       <c r="A65" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>20040010</v>
       </c>
-      <c r="B65" s="9">
+      <c r="B65" s="11">
         <v>200400</v>
       </c>
-      <c r="C65" s="9">
-        <v>2</v>
-      </c>
-      <c r="D65" s="3" t="s">
+      <c r="C65" s="11">
+        <v>2</v>
+      </c>
+      <c r="D65" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="E65" s="9">
+      <c r="E65" s="11">
         <v>200400009</v>
       </c>
-      <c r="F65" s="9" t="s">
+      <c r="F65" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="G65" s="11" t="s">
+      <c r="G65" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="H65" s="11">
+      <c r="H65" s="14">
         <v>10</v>
       </c>
-      <c r="I65" s="11">
-        <v>0</v>
-      </c>
-      <c r="J65" s="11">
+      <c r="I65" s="14">
+        <v>0</v>
+      </c>
+      <c r="J65" s="14">
         <v>-1</v>
       </c>
       <c r="K65" s="1">
         <v>0</v>
       </c>
-      <c r="L65" s="11" t="s">
+      <c r="L65" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="M65" s="11">
+      <c r="M65" s="14">
         <v>0</v>
       </c>
       <c r="N65">
-        <v>100</v>
-      </c>
-      <c r="O65" s="15">
+        <v>10</v>
+      </c>
+      <c r="O65" s="19">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="66" spans="1:15">
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" s="1" customFormat="1" spans="1:19">
       <c r="A66" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>20040011</v>
       </c>
-      <c r="B66" s="9">
+      <c r="B66" s="11">
         <v>200400</v>
       </c>
-      <c r="C66" s="9">
-        <v>2</v>
-      </c>
-      <c r="D66" s="3" t="s">
+      <c r="C66" s="11">
+        <v>2</v>
+      </c>
+      <c r="D66" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="E66" s="9">
+      <c r="E66" s="11">
         <v>200400009</v>
       </c>
-      <c r="F66" s="9" t="s">
+      <c r="F66" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="G66" s="11" t="s">
+      <c r="G66" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="H66" s="11">
+      <c r="H66" s="14">
         <v>11</v>
       </c>
-      <c r="I66" s="11">
-        <v>0</v>
-      </c>
-      <c r="J66" s="11">
+      <c r="I66" s="14">
+        <v>0</v>
+      </c>
+      <c r="J66" s="14">
         <v>-1</v>
       </c>
       <c r="K66" s="1">
         <v>0</v>
       </c>
-      <c r="L66" s="11" t="s">
+      <c r="L66" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="M66" s="11">
+      <c r="M66" s="14">
         <v>0</v>
       </c>
       <c r="N66">
-        <v>100</v>
-      </c>
-      <c r="O66" s="15">
+        <v>1000</v>
+      </c>
+      <c r="O66" s="19">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="67" spans="1:15">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" s="1" customFormat="1" spans="1:19">
       <c r="A67" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>20040012</v>
       </c>
-      <c r="B67" s="9">
+      <c r="B67" s="11">
         <v>200400</v>
       </c>
-      <c r="C67" s="9">
-        <v>2</v>
-      </c>
-      <c r="D67" s="3" t="s">
+      <c r="C67" s="11">
+        <v>2</v>
+      </c>
+      <c r="D67" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="E67" s="9">
+      <c r="E67" s="11">
         <v>200400009</v>
       </c>
-      <c r="F67" s="9" t="s">
+      <c r="F67" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="G67" s="11" t="s">
+      <c r="G67" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="H67" s="11">
+      <c r="H67" s="14">
         <v>12</v>
       </c>
-      <c r="I67" s="11">
-        <v>0</v>
-      </c>
-      <c r="J67" s="11">
+      <c r="I67" s="14">
+        <v>0</v>
+      </c>
+      <c r="J67" s="14">
         <v>-1</v>
       </c>
       <c r="K67" s="1">
         <v>0</v>
       </c>
-      <c r="L67" s="11" t="s">
+      <c r="L67" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="M67" s="11">
+      <c r="M67" s="14">
         <v>0</v>
       </c>
       <c r="N67">
-        <v>100</v>
-      </c>
-      <c r="O67" s="15">
+        <v>100000</v>
+      </c>
+      <c r="O67" s="19">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="68" spans="1:15">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" s="1" customFormat="1" spans="1:19">
       <c r="A68" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>20050010</v>
       </c>
-      <c r="B68" s="9">
+      <c r="B68" s="11">
         <v>200500</v>
       </c>
-      <c r="C68" s="9">
-        <v>2</v>
-      </c>
-      <c r="D68" s="9" t="s">
+      <c r="C68" s="11">
+        <v>2</v>
+      </c>
+      <c r="D68" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="E68" s="9">
+      <c r="E68" s="11">
         <v>200500025</v>
       </c>
-      <c r="F68" s="9" t="s">
+      <c r="F68" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="G68" s="11" t="s">
+      <c r="G68" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="H68" s="11">
+      <c r="H68" s="14">
         <v>10</v>
       </c>
-      <c r="I68" s="11">
-        <v>0</v>
-      </c>
-      <c r="J68" s="11">
+      <c r="I68" s="14">
+        <v>0</v>
+      </c>
+      <c r="J68" s="14">
         <v>-1</v>
       </c>
       <c r="K68" s="1">
         <v>0</v>
       </c>
-      <c r="L68" s="11" t="s">
+      <c r="L68" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="M68" s="11">
+      <c r="M68" s="14">
         <v>0</v>
       </c>
       <c r="N68">
-        <v>100</v>
-      </c>
-      <c r="O68" s="15">
+        <v>10</v>
+      </c>
+      <c r="O68" s="19">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="69" spans="1:15">
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" s="1" customFormat="1" spans="1:19">
       <c r="A69" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>20050011</v>
       </c>
-      <c r="B69" s="9">
+      <c r="B69" s="11">
         <v>200500</v>
       </c>
-      <c r="C69" s="9">
-        <v>2</v>
-      </c>
-      <c r="D69" s="9" t="s">
+      <c r="C69" s="11">
+        <v>2</v>
+      </c>
+      <c r="D69" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="E69" s="9">
+      <c r="E69" s="11">
         <v>200500025</v>
       </c>
-      <c r="F69" s="9" t="s">
+      <c r="F69" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="G69" s="11" t="s">
+      <c r="G69" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="H69" s="11">
+      <c r="H69" s="14">
         <v>11</v>
       </c>
-      <c r="I69" s="11">
-        <v>0</v>
-      </c>
-      <c r="J69" s="11">
+      <c r="I69" s="14">
+        <v>0</v>
+      </c>
+      <c r="J69" s="14">
         <v>-1</v>
       </c>
       <c r="K69" s="1">
         <v>0</v>
       </c>
-      <c r="L69" s="11" t="s">
+      <c r="L69" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="M69" s="11">
+      <c r="M69" s="14">
         <v>0</v>
       </c>
       <c r="N69">
-        <v>100</v>
-      </c>
-      <c r="O69" s="15">
+        <v>1000</v>
+      </c>
+      <c r="O69" s="19">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="70" spans="1:15">
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" s="1" customFormat="1" spans="1:19">
       <c r="A70" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>20050012</v>
       </c>
-      <c r="B70" s="9">
+      <c r="B70" s="11">
         <v>200500</v>
       </c>
-      <c r="C70" s="9">
-        <v>2</v>
-      </c>
-      <c r="D70" s="9" t="s">
+      <c r="C70" s="11">
+        <v>2</v>
+      </c>
+      <c r="D70" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="E70" s="9">
+      <c r="E70" s="11">
         <v>200500025</v>
       </c>
-      <c r="F70" s="9" t="s">
+      <c r="F70" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="G70" s="11" t="s">
+      <c r="G70" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="H70" s="11">
+      <c r="H70" s="14">
         <v>12</v>
       </c>
-      <c r="I70" s="11">
-        <v>0</v>
-      </c>
-      <c r="J70" s="11">
+      <c r="I70" s="14">
+        <v>0</v>
+      </c>
+      <c r="J70" s="14">
         <v>-1</v>
       </c>
       <c r="K70" s="1">
         <v>0</v>
       </c>
-      <c r="L70" s="11" t="s">
+      <c r="L70" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="M70" s="11">
+      <c r="M70" s="14">
         <v>0</v>
       </c>
       <c r="N70">
-        <v>100</v>
-      </c>
-      <c r="O70" s="15">
+        <v>100000</v>
+      </c>
+      <c r="O70" s="19">
         <v>1980000</v>
       </c>
+      <c r="S70" s="3"/>
     </row>
     <row r="71" spans="1:15">
       <c r="A71" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>20060010</v>
       </c>
-      <c r="B71" s="9">
+      <c r="B71" s="11">
         <v>200600</v>
       </c>
-      <c r="C71" s="9">
-        <v>2</v>
-      </c>
-      <c r="D71" s="9" t="s">
+      <c r="C71" s="11">
+        <v>2</v>
+      </c>
+      <c r="D71" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="E71" s="9">
+      <c r="E71" s="11">
         <v>200600001</v>
       </c>
-      <c r="F71" s="9" t="s">
+      <c r="F71" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G71" s="11" t="s">
+      <c r="G71" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="H71" s="11">
+      <c r="H71" s="14">
         <v>10</v>
       </c>
-      <c r="I71" s="11">
-        <v>0</v>
-      </c>
-      <c r="J71" s="11">
+      <c r="I71" s="14">
+        <v>0</v>
+      </c>
+      <c r="J71" s="14">
         <v>-1</v>
       </c>
       <c r="K71" s="1">
         <v>0</v>
       </c>
-      <c r="L71" s="11" t="s">
+      <c r="L71" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="M71" s="11">
+      <c r="M71" s="14">
         <v>0</v>
       </c>
       <c r="N71">
-        <v>100</v>
-      </c>
-      <c r="O71" s="15">
+        <v>10</v>
+      </c>
+      <c r="O71" s="19">
         <v>1980000</v>
       </c>
     </row>
     <row r="72" spans="1:15">
       <c r="A72" s="1">
-        <f t="shared" ref="A72:A85" si="8">B72*100+H72</f>
+        <f t="shared" ref="A72:A86" si="9">B72*100+H72</f>
         <v>20060011</v>
       </c>
-      <c r="B72" s="9">
+      <c r="B72" s="11">
         <v>200600</v>
       </c>
-      <c r="C72" s="9">
-        <v>2</v>
-      </c>
-      <c r="D72" s="9" t="s">
+      <c r="C72" s="11">
+        <v>2</v>
+      </c>
+      <c r="D72" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="E72" s="9">
+      <c r="E72" s="11">
         <v>200600001</v>
       </c>
-      <c r="F72" s="9" t="s">
+      <c r="F72" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G72" s="11" t="s">
+      <c r="G72" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="H72" s="11">
+      <c r="H72" s="14">
         <v>11</v>
       </c>
-      <c r="I72" s="11">
-        <v>0</v>
-      </c>
-      <c r="J72" s="11">
+      <c r="I72" s="14">
+        <v>0</v>
+      </c>
+      <c r="J72" s="14">
         <v>-1</v>
       </c>
       <c r="K72" s="1">
         <v>0</v>
       </c>
-      <c r="L72" s="11" t="s">
+      <c r="L72" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="M72" s="11">
+      <c r="M72" s="14">
         <v>0</v>
       </c>
       <c r="N72">
-        <v>100</v>
-      </c>
-      <c r="O72" s="15">
+        <v>1000</v>
+      </c>
+      <c r="O72" s="19">
         <v>1980000</v>
       </c>
     </row>
     <row r="73" spans="1:15">
       <c r="A73" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>20060012</v>
       </c>
-      <c r="B73" s="9">
+      <c r="B73" s="11">
         <v>200600</v>
       </c>
-      <c r="C73" s="9">
-        <v>2</v>
-      </c>
-      <c r="D73" s="9" t="s">
+      <c r="C73" s="11">
+        <v>2</v>
+      </c>
+      <c r="D73" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="E73" s="9">
+      <c r="E73" s="11">
         <v>200600001</v>
       </c>
-      <c r="F73" s="9" t="s">
+      <c r="F73" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G73" s="11" t="s">
+      <c r="G73" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="H73" s="11">
+      <c r="H73" s="14">
         <v>12</v>
       </c>
-      <c r="I73" s="11">
-        <v>0</v>
-      </c>
-      <c r="J73" s="11">
+      <c r="I73" s="14">
+        <v>0</v>
+      </c>
+      <c r="J73" s="14">
         <v>-1</v>
       </c>
       <c r="K73" s="1">
         <v>0</v>
       </c>
-      <c r="L73" s="11" t="s">
+      <c r="L73" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="M73" s="11">
+      <c r="M73" s="14">
         <v>0</v>
       </c>
       <c r="N73">
-        <v>100</v>
-      </c>
-      <c r="O73" s="15">
+        <v>100000</v>
+      </c>
+      <c r="O73" s="19">
         <v>1980000</v>
       </c>
     </row>
     <row r="74" spans="1:15">
       <c r="A74" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>20070010</v>
       </c>
-      <c r="B74" s="9">
+      <c r="B74" s="11">
         <v>200700</v>
       </c>
-      <c r="C74" s="9">
-        <v>2</v>
-      </c>
-      <c r="D74" s="2" t="s">
+      <c r="C74" s="11">
+        <v>2</v>
+      </c>
+      <c r="D74" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="E74" s="9">
+      <c r="E74" s="11">
         <v>200700001</v>
       </c>
-      <c r="F74" s="9" t="s">
+      <c r="F74" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="G74" s="11" t="s">
+      <c r="G74" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="H74" s="11">
+      <c r="H74" s="14">
         <v>10</v>
       </c>
-      <c r="I74" s="11">
-        <v>0</v>
-      </c>
-      <c r="J74" s="11">
+      <c r="I74" s="14">
+        <v>0</v>
+      </c>
+      <c r="J74" s="14">
         <v>-1</v>
       </c>
       <c r="K74" s="1">
         <v>0</v>
       </c>
-      <c r="L74" s="11" t="s">
+      <c r="L74" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="M74" s="11">
+      <c r="M74" s="14">
         <v>0</v>
       </c>
       <c r="N74">
-        <v>100</v>
-      </c>
-      <c r="O74" s="15">
+        <v>10</v>
+      </c>
+      <c r="O74" s="19">
         <v>1980000</v>
       </c>
     </row>
     <row r="75" spans="1:15">
       <c r="A75" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>20070011</v>
       </c>
-      <c r="B75" s="9">
+      <c r="B75" s="11">
         <v>200700</v>
       </c>
-      <c r="C75" s="9">
-        <v>2</v>
-      </c>
-      <c r="D75" s="2" t="str">
+      <c r="C75" s="11">
+        <v>2</v>
+      </c>
+      <c r="D75" s="10" t="str">
         <f>D74</f>
         <v>越南色碟</v>
       </c>
-      <c r="E75" s="9">
+      <c r="E75" s="11">
         <v>200700001</v>
       </c>
-      <c r="F75" s="9" t="s">
+      <c r="F75" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="G75" s="11" t="s">
+      <c r="G75" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="H75" s="11">
+      <c r="H75" s="14">
         <v>11</v>
       </c>
-      <c r="I75" s="11">
-        <v>0</v>
-      </c>
-      <c r="J75" s="11">
+      <c r="I75" s="14">
+        <v>0</v>
+      </c>
+      <c r="J75" s="14">
         <v>-1</v>
       </c>
       <c r="K75" s="1">
         <v>0</v>
       </c>
-      <c r="L75" s="11" t="s">
+      <c r="L75" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="M75" s="11">
+      <c r="M75" s="14">
         <v>0</v>
       </c>
       <c r="N75">
-        <v>100</v>
-      </c>
-      <c r="O75" s="15">
+        <v>1000</v>
+      </c>
+      <c r="O75" s="19">
         <v>1980000</v>
       </c>
     </row>
     <row r="76" spans="1:15">
       <c r="A76" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>20070012</v>
       </c>
-      <c r="B76" s="9">
+      <c r="B76" s="11">
         <v>200700</v>
       </c>
-      <c r="C76" s="9">
-        <v>2</v>
-      </c>
-      <c r="D76" s="2" t="str">
+      <c r="C76" s="11">
+        <v>2</v>
+      </c>
+      <c r="D76" s="10" t="str">
         <f>D75</f>
         <v>越南色碟</v>
       </c>
-      <c r="E76" s="9">
+      <c r="E76" s="11">
         <v>200700001</v>
       </c>
-      <c r="F76" s="9" t="s">
+      <c r="F76" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="G76" s="11" t="s">
+      <c r="G76" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="H76" s="11">
+      <c r="H76" s="14">
         <v>12</v>
       </c>
-      <c r="I76" s="11">
-        <v>0</v>
-      </c>
-      <c r="J76" s="11">
+      <c r="I76" s="14">
+        <v>0</v>
+      </c>
+      <c r="J76" s="14">
         <v>-1</v>
       </c>
       <c r="K76" s="1">
         <v>0</v>
       </c>
-      <c r="L76" s="11" t="s">
+      <c r="L76" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="M76" s="11">
+      <c r="M76" s="14">
         <v>0</v>
       </c>
       <c r="N76">
-        <v>100</v>
-      </c>
-      <c r="O76" s="15">
+        <v>100000</v>
+      </c>
+      <c r="O76" s="19">
         <v>1980000</v>
       </c>
     </row>
     <row r="77" spans="1:15">
       <c r="A77" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>20080010</v>
       </c>
-      <c r="B77" s="9">
+      <c r="B77" s="11">
         <v>200800</v>
       </c>
-      <c r="C77" s="9">
-        <v>2</v>
-      </c>
-      <c r="D77" s="9" t="s">
+      <c r="C77" s="11">
+        <v>2</v>
+      </c>
+      <c r="D77" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E77" s="9">
+      <c r="E77" s="11">
         <v>200800001</v>
       </c>
-      <c r="F77" s="9" t="s">
+      <c r="F77" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="G77" s="11" t="s">
+      <c r="G77" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="H77" s="11">
+      <c r="H77" s="14">
         <v>10</v>
       </c>
-      <c r="I77" s="11">
-        <v>0</v>
-      </c>
-      <c r="J77" s="11">
+      <c r="I77" s="14">
+        <v>0</v>
+      </c>
+      <c r="J77" s="14">
         <v>-1</v>
       </c>
       <c r="K77" s="1">
         <v>0</v>
       </c>
-      <c r="L77" s="11" t="s">
+      <c r="L77" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="M77" s="11">
+      <c r="M77" s="14">
         <v>0</v>
       </c>
       <c r="N77">
-        <v>100</v>
-      </c>
-      <c r="O77" s="15">
+        <v>10</v>
+      </c>
+      <c r="O77" s="19">
         <v>1980000</v>
       </c>
     </row>
     <row r="78" spans="1:15">
       <c r="A78" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>20080011</v>
       </c>
-      <c r="B78" s="9">
+      <c r="B78" s="11">
         <v>200800</v>
       </c>
-      <c r="C78" s="9">
-        <v>2</v>
-      </c>
-      <c r="D78" s="9" t="s">
+      <c r="C78" s="11">
+        <v>2</v>
+      </c>
+      <c r="D78" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E78" s="9">
+      <c r="E78" s="11">
         <v>200800001</v>
       </c>
-      <c r="F78" s="9" t="s">
+      <c r="F78" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="G78" s="11" t="s">
+      <c r="G78" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="H78" s="11">
+      <c r="H78" s="14">
         <v>11</v>
       </c>
-      <c r="I78" s="11">
-        <v>0</v>
-      </c>
-      <c r="J78" s="11">
+      <c r="I78" s="14">
+        <v>0</v>
+      </c>
+      <c r="J78" s="14">
         <v>-1</v>
       </c>
       <c r="K78" s="1">
         <v>0</v>
       </c>
-      <c r="L78" s="11" t="s">
+      <c r="L78" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="M78" s="11">
+      <c r="M78" s="14">
         <v>0</v>
       </c>
       <c r="N78">
-        <v>100</v>
-      </c>
-      <c r="O78" s="15">
+        <v>1000</v>
+      </c>
+      <c r="O78" s="19">
         <v>1980000</v>
       </c>
     </row>
     <row r="79" spans="1:15">
       <c r="A79" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>20080012</v>
       </c>
-      <c r="B79" s="9">
+      <c r="B79" s="11">
         <v>200800</v>
       </c>
-      <c r="C79" s="9">
-        <v>2</v>
-      </c>
-      <c r="D79" s="9" t="s">
+      <c r="C79" s="11">
+        <v>2</v>
+      </c>
+      <c r="D79" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E79" s="9">
+      <c r="E79" s="11">
         <v>200800001</v>
       </c>
-      <c r="F79" s="9" t="s">
+      <c r="F79" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="G79" s="11" t="s">
+      <c r="G79" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="H79" s="11">
+      <c r="H79" s="14">
         <v>12</v>
       </c>
-      <c r="I79" s="11">
-        <v>0</v>
-      </c>
-      <c r="J79" s="11">
+      <c r="I79" s="14">
+        <v>0</v>
+      </c>
+      <c r="J79" s="14">
         <v>-1</v>
       </c>
       <c r="K79" s="1">
         <v>0</v>
       </c>
-      <c r="L79" s="11" t="s">
+      <c r="L79" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="M79" s="11">
+      <c r="M79" s="14">
         <v>0</v>
       </c>
       <c r="N79">
-        <v>100</v>
-      </c>
-      <c r="O79" s="15">
+        <v>100000</v>
+      </c>
+      <c r="O79" s="19">
         <v>1980000</v>
       </c>
     </row>
     <row r="80" spans="1:15">
       <c r="A80" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>20090010</v>
       </c>
-      <c r="B80" s="9">
+      <c r="B80" s="11">
         <v>200900</v>
       </c>
-      <c r="C80" s="9">
-        <v>2</v>
-      </c>
-      <c r="D80" s="9" t="s">
+      <c r="C80" s="11">
+        <v>2</v>
+      </c>
+      <c r="D80" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="E80" s="9">
+      <c r="E80" s="11">
         <v>200900001</v>
       </c>
-      <c r="F80" s="9" t="s">
+      <c r="F80" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="G80" s="11" t="s">
+      <c r="G80" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="H80" s="11">
+      <c r="H80" s="14">
         <v>10</v>
       </c>
-      <c r="I80" s="11">
-        <v>0</v>
-      </c>
-      <c r="J80" s="11">
+      <c r="I80" s="14">
+        <v>0</v>
+      </c>
+      <c r="J80" s="14">
         <v>-1</v>
       </c>
       <c r="K80" s="1">
         <v>0</v>
       </c>
-      <c r="L80" s="11" t="s">
+      <c r="L80" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="M80" s="11">
+      <c r="M80" s="14">
         <v>0</v>
       </c>
       <c r="N80">
-        <v>100</v>
-      </c>
-      <c r="O80" s="15">
+        <v>10</v>
+      </c>
+      <c r="O80" s="19">
         <v>1980000</v>
       </c>
     </row>
     <row r="81" spans="1:15">
       <c r="A81" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>20090011</v>
       </c>
-      <c r="B81" s="9">
+      <c r="B81" s="11">
         <v>200900</v>
       </c>
-      <c r="C81" s="9">
-        <v>2</v>
-      </c>
-      <c r="D81" s="9" t="s">
+      <c r="C81" s="11">
+        <v>2</v>
+      </c>
+      <c r="D81" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="E81" s="9">
+      <c r="E81" s="11">
         <v>200900001</v>
       </c>
-      <c r="F81" s="9" t="s">
+      <c r="F81" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="G81" s="11" t="s">
+      <c r="G81" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="H81" s="11">
+      <c r="H81" s="14">
         <v>11</v>
       </c>
-      <c r="I81" s="11">
-        <v>0</v>
-      </c>
-      <c r="J81" s="11">
+      <c r="I81" s="14">
+        <v>0</v>
+      </c>
+      <c r="J81" s="14">
         <v>-1</v>
       </c>
       <c r="K81" s="1">
         <v>0</v>
       </c>
-      <c r="L81" s="11" t="s">
+      <c r="L81" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="M81" s="11">
+      <c r="M81" s="14">
         <v>0</v>
       </c>
       <c r="N81">
-        <v>100</v>
-      </c>
-      <c r="O81" s="15">
+        <v>1000</v>
+      </c>
+      <c r="O81" s="19">
         <v>1980000</v>
       </c>
     </row>
     <row r="82" spans="1:15">
       <c r="A82" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>20090012</v>
       </c>
-      <c r="B82" s="9">
+      <c r="B82" s="11">
         <v>200900</v>
       </c>
-      <c r="C82" s="9">
-        <v>2</v>
-      </c>
-      <c r="D82" s="9" t="s">
+      <c r="C82" s="11">
+        <v>2</v>
+      </c>
+      <c r="D82" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="E82" s="9">
+      <c r="E82" s="11">
         <v>200900001</v>
       </c>
-      <c r="F82" s="9" t="s">
+      <c r="F82" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="G82" s="11" t="s">
+      <c r="G82" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="H82" s="11">
+      <c r="H82" s="14">
         <v>12</v>
       </c>
-      <c r="I82" s="11">
-        <v>0</v>
-      </c>
-      <c r="J82" s="11">
+      <c r="I82" s="14">
+        <v>0</v>
+      </c>
+      <c r="J82" s="14">
         <v>-1</v>
       </c>
       <c r="K82" s="1">
         <v>0</v>
       </c>
-      <c r="L82" s="11" t="s">
+      <c r="L82" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="M82" s="11">
+      <c r="M82" s="14">
         <v>0</v>
       </c>
       <c r="N82">
-        <v>100</v>
-      </c>
-      <c r="O82" s="15">
+        <v>100000</v>
+      </c>
+      <c r="O82" s="19">
         <v>1980000</v>
       </c>
     </row>
-    <row r="83" spans="1:15">
+    <row r="83" s="1" customFormat="1" spans="1:19">
       <c r="A83" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>30020010</v>
       </c>
-      <c r="B83" s="2">
+      <c r="B83" s="10">
         <v>300200</v>
       </c>
-      <c r="C83" s="2">
+      <c r="C83" s="10">
         <v>3</v>
       </c>
-      <c r="D83" s="2" t="s">
+      <c r="D83" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="E83" s="9">
+      <c r="E83" s="11">
         <v>300200006</v>
       </c>
-      <c r="F83" s="9" t="s">
+      <c r="F83" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="G83" s="11" t="s">
+      <c r="G83" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="H83" s="11">
+      <c r="H83" s="14">
         <v>10</v>
       </c>
-      <c r="I83" s="11">
+      <c r="I83" s="14">
         <v>0</v>
       </c>
       <c r="J83" s="1">
@@ -4907,46 +5585,47 @@
       <c r="K83" s="1">
         <v>0</v>
       </c>
-      <c r="L83" s="17" t="s">
+      <c r="L83" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="M83" s="11">
+      <c r="M83" s="14">
         <v>0</v>
       </c>
       <c r="N83">
-        <v>2</v>
-      </c>
-      <c r="O83" s="15">
+        <v>40</v>
+      </c>
+      <c r="O83" s="19">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="84" spans="1:15">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" s="1" customFormat="1" spans="1:19">
       <c r="A84" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>30020011</v>
       </c>
-      <c r="B84" s="2">
+      <c r="B84" s="10">
         <v>300200</v>
       </c>
-      <c r="C84" s="2">
+      <c r="C84" s="10">
         <v>3</v>
       </c>
-      <c r="D84" s="2" t="s">
+      <c r="D84" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="E84" s="9">
+      <c r="E84" s="11">
         <v>300200006</v>
       </c>
-      <c r="F84" s="9" t="s">
+      <c r="F84" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="G84" s="11" t="s">
+      <c r="G84" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="H84" s="11">
+      <c r="H84" s="14">
         <v>11</v>
       </c>
-      <c r="I84" s="11">
+      <c r="I84" s="14">
         <v>0</v>
       </c>
       <c r="J84" s="1">
@@ -4955,46 +5634,47 @@
       <c r="K84" s="1">
         <v>0</v>
       </c>
-      <c r="L84" s="17" t="s">
+      <c r="L84" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="M84" s="11">
+      <c r="M84" s="14">
         <v>0</v>
       </c>
       <c r="N84">
-        <v>4</v>
-      </c>
-      <c r="O84" s="15">
+        <v>4000</v>
+      </c>
+      <c r="O84" s="19">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="85" spans="1:15">
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" s="1" customFormat="1" spans="1:19">
       <c r="A85" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>30020012</v>
       </c>
-      <c r="B85" s="2">
+      <c r="B85" s="10">
         <v>300200</v>
       </c>
-      <c r="C85" s="2">
+      <c r="C85" s="10">
         <v>3</v>
       </c>
-      <c r="D85" s="2" t="s">
+      <c r="D85" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="E85" s="9">
+      <c r="E85" s="11">
         <v>300200006</v>
       </c>
-      <c r="F85" s="9" t="s">
+      <c r="F85" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="G85" s="11" t="s">
+      <c r="G85" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="H85" s="11">
+      <c r="H85" s="14">
         <v>12</v>
       </c>
-      <c r="I85" s="11">
+      <c r="I85" s="14">
         <v>0</v>
       </c>
       <c r="J85" s="1">
@@ -5003,22 +5683,23 @@
       <c r="K85" s="1">
         <v>0</v>
       </c>
-      <c r="L85" s="17" t="s">
+      <c r="L85" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="M85" s="11">
+      <c r="M85" s="14">
         <v>0</v>
       </c>
       <c r="N85">
-        <v>8</v>
-      </c>
-      <c r="O85" s="15">
+        <v>400000</v>
+      </c>
+      <c r="O85" s="19">
         <v>1980000</v>
       </c>
+      <c r="S85" s="3"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -1674,7 +1674,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="6:15">
+    <row r="4" ht="14.25" spans="6:15">
       <c r="F4" s="1" t="s">
         <v>29</v>
       </c>
@@ -2449,7 +2449,7 @@
         <v>1000</v>
       </c>
       <c r="J20" s="1">
-        <v>5000000</v>
+        <v>-1</v>
       </c>
       <c r="K20" s="1">
         <v>0</v>
@@ -2499,7 +2499,7 @@
         <v>100000</v>
       </c>
       <c r="J21" s="1">
-        <v>500000000</v>
+        <v>-1</v>
       </c>
       <c r="K21" s="1">
         <v>0</v>
@@ -2599,7 +2599,7 @@
         <v>1000</v>
       </c>
       <c r="J23" s="1">
-        <v>5000000</v>
+        <v>-1</v>
       </c>
       <c r="K23" s="1">
         <v>0</v>
@@ -2649,7 +2649,7 @@
         <v>100000</v>
       </c>
       <c r="J24" s="1">
-        <v>500000000</v>
+        <v>-1</v>
       </c>
       <c r="K24" s="1">
         <v>0</v>
@@ -2750,7 +2750,7 @@
         <v>1000</v>
       </c>
       <c r="J26" s="1">
-        <v>5000000</v>
+        <v>-1</v>
       </c>
       <c r="K26" s="1">
         <v>0</v>
@@ -2800,7 +2800,7 @@
         <v>100000</v>
       </c>
       <c r="J27" s="1">
-        <v>500000000</v>
+        <v>-1</v>
       </c>
       <c r="K27" s="1">
         <v>0</v>
@@ -2905,7 +2905,7 @@
         <v>1000</v>
       </c>
       <c r="J29" s="1">
-        <v>5000000</v>
+        <v>-1</v>
       </c>
       <c r="K29" s="1">
         <v>0</v>
@@ -2957,7 +2957,7 @@
         <v>100000</v>
       </c>
       <c r="J30" s="1">
-        <v>500000000</v>
+        <v>-1</v>
       </c>
       <c r="K30" s="1">
         <v>0</v>
@@ -3061,7 +3061,7 @@
         <v>1000</v>
       </c>
       <c r="J32" s="1">
-        <v>5000000</v>
+        <v>-1</v>
       </c>
       <c r="K32" s="1">
         <v>0</v>
@@ -3113,7 +3113,7 @@
         <v>100000</v>
       </c>
       <c r="J33" s="1">
-        <v>500000000</v>
+        <v>-1</v>
       </c>
       <c r="K33" s="1">
         <v>0</v>
@@ -3217,7 +3217,7 @@
         <v>1000</v>
       </c>
       <c r="J35" s="1">
-        <v>5000000</v>
+        <v>-1</v>
       </c>
       <c r="K35" s="1">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>100000</v>
       </c>
       <c r="J36" s="1">
-        <v>500000000</v>
+        <v>-1</v>
       </c>
       <c r="K36" s="1">
         <v>0</v>
@@ -3373,7 +3373,7 @@
         <v>1000</v>
       </c>
       <c r="J38" s="1">
-        <v>5000000</v>
+        <v>-1</v>
       </c>
       <c r="K38" s="1">
         <v>0</v>
@@ -3426,7 +3426,7 @@
         <v>100000</v>
       </c>
       <c r="J39" s="1">
-        <v>500000000</v>
+        <v>-1</v>
       </c>
       <c r="K39" s="1">
         <v>0</v>
@@ -3529,7 +3529,7 @@
         <v>1000</v>
       </c>
       <c r="J41" s="1">
-        <v>5000000</v>
+        <v>-1</v>
       </c>
       <c r="K41" s="1">
         <v>0</v>
@@ -3579,7 +3579,7 @@
         <v>100000</v>
       </c>
       <c r="J42" s="1">
-        <v>500000000</v>
+        <v>-1</v>
       </c>
       <c r="K42" s="1">
         <v>0</v>
@@ -3679,7 +3679,7 @@
         <v>1000</v>
       </c>
       <c r="J44" s="1">
-        <v>5000000</v>
+        <v>-1</v>
       </c>
       <c r="K44" s="1">
         <v>0</v>
@@ -3729,7 +3729,7 @@
         <v>100000</v>
       </c>
       <c r="J45" s="1">
-        <v>500000000</v>
+        <v>-1</v>
       </c>
       <c r="K45" s="1">
         <v>0</v>
@@ -3826,7 +3826,7 @@
         <v>1000</v>
       </c>
       <c r="J47" s="1">
-        <v>5000000</v>
+        <v>-1</v>
       </c>
       <c r="K47" s="1">
         <v>0</v>
@@ -3873,7 +3873,7 @@
         <v>100000</v>
       </c>
       <c r="J48" s="1">
-        <v>500000000</v>
+        <v>-1</v>
       </c>
       <c r="K48" s="1">
         <v>0</v>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -599,12 +599,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1531,7 +1531,7 @@
     <col min="8" max="8" width="9" style="1"/>
     <col min="9" max="9" width="9.375" style="1"/>
     <col min="10" max="10" width="11.25" style="1" customWidth="1"/>
-    <col min="11" max="11" width="9.25833333333333" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.2333333333333" style="1" customWidth="1"/>
     <col min="12" max="12" width="17.05" style="1" customWidth="1"/>
     <col min="13" max="13" width="13.9666666666667" style="1" customWidth="1"/>
     <col min="14" max="14" width="17.125" customWidth="1"/>
@@ -1756,13 +1756,13 @@
         <v>2</v>
       </c>
       <c r="I6" s="1">
-        <v>50</v>
+        <v>50000</v>
       </c>
       <c r="J6" s="1">
         <v>-1</v>
       </c>
       <c r="K6" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>33</v>
@@ -1805,13 +1805,13 @@
         <v>3</v>
       </c>
       <c r="I7" s="1">
-        <v>100</v>
+        <v>5000000</v>
       </c>
       <c r="J7" s="1">
         <v>-1</v>
       </c>
       <c r="K7" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L7" s="1" t="s">
         <v>33</v>
@@ -1903,13 +1903,13 @@
         <v>2</v>
       </c>
       <c r="I9" s="1">
-        <v>50</v>
+        <v>50000</v>
       </c>
       <c r="J9" s="1">
         <v>-1</v>
       </c>
       <c r="K9" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>33</v>
@@ -1953,13 +1953,13 @@
         <v>3</v>
       </c>
       <c r="I10" s="1">
-        <v>100</v>
+        <v>5000000</v>
       </c>
       <c r="J10" s="1">
         <v>-1</v>
       </c>
       <c r="K10" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>33</v>
@@ -2051,13 +2051,13 @@
         <v>2</v>
       </c>
       <c r="I12" s="1">
-        <v>50</v>
+        <v>50000</v>
       </c>
       <c r="J12" s="1">
         <v>-1</v>
       </c>
       <c r="K12" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>33</v>
@@ -2101,13 +2101,13 @@
         <v>3</v>
       </c>
       <c r="I13" s="1">
-        <v>100</v>
+        <v>5000000</v>
       </c>
       <c r="J13" s="1">
         <v>-1</v>
       </c>
       <c r="K13" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>33</v>
@@ -2199,13 +2199,13 @@
         <v>2</v>
       </c>
       <c r="I15" s="1">
-        <v>50</v>
+        <v>50000</v>
       </c>
       <c r="J15" s="1">
         <v>-1</v>
       </c>
       <c r="K15" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>33</v>
@@ -2249,13 +2249,13 @@
         <v>3</v>
       </c>
       <c r="I16" s="1">
-        <v>100</v>
+        <v>5000000</v>
       </c>
       <c r="J16" s="1">
         <v>-1</v>
       </c>
       <c r="K16" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L16" s="1" t="s">
         <v>33</v>
@@ -2347,13 +2347,13 @@
         <v>2</v>
       </c>
       <c r="I18" s="1">
-        <v>50</v>
+        <v>50000</v>
       </c>
       <c r="J18" s="1">
         <v>-1</v>
       </c>
       <c r="K18" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L18" s="1" t="s">
         <v>33</v>
@@ -2397,13 +2397,13 @@
         <v>3</v>
       </c>
       <c r="I19" s="1">
-        <v>100</v>
+        <v>5000000</v>
       </c>
       <c r="J19" s="1">
         <v>-1</v>
       </c>
       <c r="K19" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L19" s="1" t="s">
         <v>33</v>
@@ -2445,8 +2445,7 @@
         <v>1</v>
       </c>
       <c r="I20" s="1">
-        <f>N20</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J20" s="1">
         <v>-1</v>
@@ -2495,14 +2494,13 @@
         <v>2</v>
       </c>
       <c r="I21" s="1">
-        <f t="shared" ref="I21:I55" si="4">N21</f>
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="J21" s="1">
         <v>-1</v>
       </c>
       <c r="K21" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L21" s="1" t="s">
         <v>33</v>
@@ -2545,14 +2543,13 @@
         <v>3</v>
       </c>
       <c r="I22" s="1">
-        <f t="shared" si="4"/>
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
       <c r="J22" s="1">
         <v>-1</v>
       </c>
       <c r="K22" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L22" s="1" t="s">
         <v>33</v>
@@ -2595,8 +2592,7 @@
         <v>1</v>
       </c>
       <c r="I23" s="1">
-        <f t="shared" si="4"/>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J23" s="1">
         <v>-1</v>
@@ -2629,7 +2625,7 @@
         <v>2</v>
       </c>
       <c r="D24" s="10" t="str">
-        <f t="shared" ref="D24:D28" si="5">D23</f>
+        <f t="shared" ref="D24:D28" si="4">D23</f>
         <v>龍虎鬥</v>
       </c>
       <c r="E24" s="11">
@@ -2645,14 +2641,13 @@
         <v>2</v>
       </c>
       <c r="I24" s="1">
-        <f t="shared" si="4"/>
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="J24" s="1">
         <v>-1</v>
       </c>
       <c r="K24" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L24" s="1" t="s">
         <v>33</v>
@@ -2680,7 +2675,7 @@
         <v>2</v>
       </c>
       <c r="D25" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>龍虎鬥</v>
       </c>
       <c r="E25" s="11">
@@ -2696,14 +2691,13 @@
         <v>3</v>
       </c>
       <c r="I25" s="1">
-        <f t="shared" si="4"/>
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
       <c r="J25" s="1">
         <v>-1</v>
       </c>
       <c r="K25" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L25" s="1" t="s">
         <v>33</v>
@@ -2746,8 +2740,7 @@
         <v>1</v>
       </c>
       <c r="I26" s="1">
-        <f t="shared" si="4"/>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J26" s="1">
         <v>-1</v>
@@ -2780,7 +2773,7 @@
         <v>2</v>
       </c>
       <c r="D27" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>飛禽走獸</v>
       </c>
       <c r="E27" s="11">
@@ -2796,14 +2789,13 @@
         <v>2</v>
       </c>
       <c r="I27" s="1">
-        <f t="shared" si="4"/>
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="J27" s="1">
         <v>-1</v>
       </c>
       <c r="K27" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L27" s="1" t="s">
         <v>33</v>
@@ -2833,7 +2825,7 @@
         <v>2</v>
       </c>
       <c r="D28" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>飛禽走獸</v>
       </c>
       <c r="E28" s="11">
@@ -2849,14 +2841,13 @@
         <v>3</v>
       </c>
       <c r="I28" s="1">
-        <f t="shared" si="4"/>
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
       <c r="J28" s="1">
         <v>-1</v>
       </c>
       <c r="K28" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L28" s="1" t="s">
         <v>33</v>
@@ -2901,8 +2892,7 @@
         <v>1</v>
       </c>
       <c r="I29" s="1">
-        <f t="shared" si="4"/>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J29" s="1">
         <v>-1</v>
@@ -2953,14 +2943,13 @@
         <v>2</v>
       </c>
       <c r="I30" s="1">
-        <f t="shared" si="4"/>
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="J30" s="1">
         <v>-1</v>
       </c>
       <c r="K30" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L30" s="1" t="s">
         <v>33</v>
@@ -3005,14 +2994,13 @@
         <v>3</v>
       </c>
       <c r="I31" s="1">
-        <f t="shared" si="4"/>
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
       <c r="J31" s="1">
         <v>-1</v>
       </c>
       <c r="K31" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L31" s="1" t="s">
         <v>33</v>
@@ -3057,8 +3045,7 @@
         <v>1</v>
       </c>
       <c r="I32" s="1">
-        <f t="shared" si="4"/>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J32" s="1">
         <v>-1</v>
@@ -3109,14 +3096,13 @@
         <v>2</v>
       </c>
       <c r="I33" s="1">
-        <f t="shared" si="4"/>
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="J33" s="1">
         <v>-1</v>
       </c>
       <c r="K33" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L33" s="1" t="s">
         <v>33</v>
@@ -3161,14 +3147,13 @@
         <v>3</v>
       </c>
       <c r="I34" s="1">
-        <f t="shared" si="4"/>
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
       <c r="J34" s="1">
         <v>-1</v>
       </c>
       <c r="K34" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L34" s="1" t="s">
         <v>33</v>
@@ -3213,8 +3198,7 @@
         <v>1</v>
       </c>
       <c r="I35" s="1">
-        <f t="shared" si="4"/>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J35" s="1">
         <v>-1</v>
@@ -3265,14 +3249,13 @@
         <v>2</v>
       </c>
       <c r="I36" s="1">
-        <f t="shared" si="4"/>
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="J36" s="1">
         <v>-1</v>
       </c>
       <c r="K36" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L36" s="1" t="s">
         <v>33</v>
@@ -3317,14 +3300,13 @@
         <v>3</v>
       </c>
       <c r="I37" s="1">
-        <f t="shared" si="4"/>
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
       <c r="J37" s="1">
         <v>-1</v>
       </c>
       <c r="K37" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L37" s="1" t="s">
         <v>33</v>
@@ -3369,8 +3351,7 @@
         <v>1</v>
       </c>
       <c r="I38" s="1">
-        <f t="shared" si="4"/>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J38" s="1">
         <v>-1</v>
@@ -3406,7 +3387,7 @@
         <v>2</v>
       </c>
       <c r="D39" s="10" t="str">
-        <f t="shared" ref="D36:D40" si="6">D38</f>
+        <f t="shared" ref="D36:D40" si="5">D38</f>
         <v>越南色碟</v>
       </c>
       <c r="E39" s="11">
@@ -3422,14 +3403,13 @@
         <v>2</v>
       </c>
       <c r="I39" s="1">
-        <f t="shared" si="4"/>
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="J39" s="1">
         <v>-1</v>
       </c>
       <c r="K39" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>33</v>
@@ -3459,7 +3439,7 @@
         <v>2</v>
       </c>
       <c r="D40" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>越南色碟</v>
       </c>
       <c r="E40" s="11">
@@ -3475,14 +3455,13 @@
         <v>3</v>
       </c>
       <c r="I40" s="1">
-        <f t="shared" si="4"/>
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
       <c r="J40" s="1">
         <v>-1</v>
       </c>
       <c r="K40" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L40" s="1" t="s">
         <v>33</v>
@@ -3525,8 +3504,7 @@
         <v>1</v>
       </c>
       <c r="I41" s="1">
-        <f t="shared" si="4"/>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J41" s="1">
         <v>-1</v>
@@ -3575,14 +3553,13 @@
         <v>2</v>
       </c>
       <c r="I42" s="1">
-        <f t="shared" si="4"/>
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="J42" s="1">
         <v>-1</v>
       </c>
       <c r="K42" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L42" s="1" t="s">
         <v>33</v>
@@ -3625,14 +3602,13 @@
         <v>3</v>
       </c>
       <c r="I43" s="1">
-        <f t="shared" si="4"/>
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
       <c r="J43" s="1">
         <v>-1</v>
       </c>
       <c r="K43" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L43" s="1" t="s">
         <v>33</v>
@@ -3675,8 +3651,7 @@
         <v>1</v>
       </c>
       <c r="I44" s="1">
-        <f t="shared" si="4"/>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J44" s="1">
         <v>-1</v>
@@ -3725,14 +3700,13 @@
         <v>2</v>
       </c>
       <c r="I45" s="1">
-        <f t="shared" si="4"/>
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="J45" s="1">
         <v>-1</v>
       </c>
       <c r="K45" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L45" s="1" t="s">
         <v>33</v>
@@ -3775,14 +3749,13 @@
         <v>3</v>
       </c>
       <c r="I46" s="1">
-        <f t="shared" si="4"/>
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
       <c r="J46" s="1">
         <v>-1</v>
       </c>
       <c r="K46" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L46" s="1" t="s">
         <v>33</v>
@@ -3822,8 +3795,7 @@
         <v>1</v>
       </c>
       <c r="I47" s="1">
-        <f t="shared" si="4"/>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J47" s="1">
         <v>-1</v>
@@ -3869,14 +3841,13 @@
         <v>2</v>
       </c>
       <c r="I48" s="1">
-        <f t="shared" si="4"/>
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="J48" s="1">
         <v>-1</v>
       </c>
       <c r="K48" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L48" s="1" t="s">
         <v>33</v>
@@ -3916,14 +3887,13 @@
         <v>3</v>
       </c>
       <c r="I49" s="1">
-        <f t="shared" si="4"/>
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
       <c r="J49" s="1">
         <v>-1</v>
       </c>
       <c r="K49" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L49" s="1" t="s">
         <v>33</v>
@@ -3965,7 +3935,7 @@
         <v>1</v>
       </c>
       <c r="I50" s="1">
-        <f t="shared" si="4"/>
+        <f>N50</f>
         <v>1000</v>
       </c>
       <c r="J50" s="1">
@@ -4014,14 +3984,14 @@
         <v>2</v>
       </c>
       <c r="I51" s="1">
-        <f t="shared" si="4"/>
+        <f>N51</f>
         <v>100000</v>
       </c>
       <c r="J51" s="1">
         <v>-1</v>
       </c>
       <c r="K51" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L51" s="21" t="s">
         <v>67</v>
@@ -4064,14 +4034,14 @@
         <v>3</v>
       </c>
       <c r="I52" s="1">
-        <f t="shared" si="4"/>
+        <f>N52</f>
         <v>10000000</v>
       </c>
       <c r="J52" s="1">
         <v>-1</v>
       </c>
       <c r="K52" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L52" s="21" t="s">
         <v>67</v>
@@ -4114,7 +4084,7 @@
         <v>1</v>
       </c>
       <c r="I53" s="1">
-        <f t="shared" si="4"/>
+        <f>N53</f>
         <v>2000</v>
       </c>
       <c r="J53" s="1">
@@ -4164,14 +4134,14 @@
         <v>2</v>
       </c>
       <c r="I54" s="1">
-        <f t="shared" si="4"/>
+        <f>N54</f>
         <v>200000</v>
       </c>
       <c r="J54" s="1">
         <v>-1</v>
       </c>
       <c r="K54" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L54" s="21" t="s">
         <v>71</v>
@@ -4214,14 +4184,14 @@
         <v>3</v>
       </c>
       <c r="I55" s="1">
-        <f t="shared" si="4"/>
+        <f>N55</f>
         <v>20000000</v>
       </c>
       <c r="J55" s="1">
         <v>-1</v>
       </c>
       <c r="K55" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L55" s="21" t="s">
         <v>71</v>
@@ -4239,7 +4209,7 @@
     </row>
     <row r="56" s="1" customFormat="1" spans="1:19">
       <c r="A56" s="1">
-        <f t="shared" ref="A56:A62" si="7">B56*100+H56</f>
+        <f t="shared" ref="A56:A62" si="6">B56*100+H56</f>
         <v>20010010</v>
       </c>
       <c r="B56" s="11">
@@ -4288,7 +4258,7 @@
     </row>
     <row r="57" s="1" customFormat="1" spans="1:19">
       <c r="A57" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>20010011</v>
       </c>
       <c r="B57" s="11">
@@ -4337,7 +4307,7 @@
     </row>
     <row r="58" s="1" customFormat="1" spans="1:19">
       <c r="A58" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>20010012</v>
       </c>
       <c r="B58" s="11">
@@ -4386,7 +4356,7 @@
     </row>
     <row r="59" s="1" customFormat="1" spans="1:19">
       <c r="A59" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>20010110</v>
       </c>
       <c r="B59" s="11">
@@ -4435,7 +4405,7 @@
     </row>
     <row r="60" s="1" customFormat="1" spans="1:19">
       <c r="A60" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>20010111</v>
       </c>
       <c r="B60" s="11">
@@ -4484,7 +4454,7 @@
     </row>
     <row r="61" s="1" customFormat="1" spans="1:19">
       <c r="A61" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>20010112</v>
       </c>
       <c r="B61" s="11">
@@ -4533,7 +4503,7 @@
     </row>
     <row r="62" s="1" customFormat="1" spans="1:19">
       <c r="A62" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>20030010</v>
       </c>
       <c r="B62" s="11">
@@ -4582,7 +4552,7 @@
     </row>
     <row r="63" s="1" customFormat="1" spans="1:19">
       <c r="A63" s="1">
-        <f t="shared" ref="A63:A71" si="8">B63*100+H63</f>
+        <f t="shared" ref="A63:A71" si="7">B63*100+H63</f>
         <v>20030011</v>
       </c>
       <c r="B63" s="11">
@@ -4631,7 +4601,7 @@
     </row>
     <row r="64" s="1" customFormat="1" spans="1:19">
       <c r="A64" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>20030012</v>
       </c>
       <c r="B64" s="11">
@@ -4680,7 +4650,7 @@
     </row>
     <row r="65" s="1" customFormat="1" spans="1:19">
       <c r="A65" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>20040010</v>
       </c>
       <c r="B65" s="11">
@@ -4729,7 +4699,7 @@
     </row>
     <row r="66" s="1" customFormat="1" spans="1:19">
       <c r="A66" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>20040011</v>
       </c>
       <c r="B66" s="11">
@@ -4778,7 +4748,7 @@
     </row>
     <row r="67" s="1" customFormat="1" spans="1:19">
       <c r="A67" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>20040012</v>
       </c>
       <c r="B67" s="11">
@@ -4827,7 +4797,7 @@
     </row>
     <row r="68" s="1" customFormat="1" spans="1:19">
       <c r="A68" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>20050010</v>
       </c>
       <c r="B68" s="11">
@@ -4876,7 +4846,7 @@
     </row>
     <row r="69" s="1" customFormat="1" spans="1:19">
       <c r="A69" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>20050011</v>
       </c>
       <c r="B69" s="11">
@@ -4925,7 +4895,7 @@
     </row>
     <row r="70" s="1" customFormat="1" spans="1:19">
       <c r="A70" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>20050012</v>
       </c>
       <c r="B70" s="11">
@@ -4974,7 +4944,7 @@
     </row>
     <row r="71" spans="1:15">
       <c r="A71" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>20060010</v>
       </c>
       <c r="B71" s="11">
@@ -5022,7 +4992,7 @@
     </row>
     <row r="72" spans="1:15">
       <c r="A72" s="1">
-        <f t="shared" ref="A72:A86" si="9">B72*100+H72</f>
+        <f t="shared" ref="A72:A86" si="8">B72*100+H72</f>
         <v>20060011</v>
       </c>
       <c r="B72" s="11">
@@ -5070,7 +5040,7 @@
     </row>
     <row r="73" spans="1:15">
       <c r="A73" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>20060012</v>
       </c>
       <c r="B73" s="11">
@@ -5118,7 +5088,7 @@
     </row>
     <row r="74" spans="1:15">
       <c r="A74" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>20070010</v>
       </c>
       <c r="B74" s="11">
@@ -5166,7 +5136,7 @@
     </row>
     <row r="75" spans="1:15">
       <c r="A75" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>20070011</v>
       </c>
       <c r="B75" s="11">
@@ -5215,7 +5185,7 @@
     </row>
     <row r="76" spans="1:15">
       <c r="A76" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>20070012</v>
       </c>
       <c r="B76" s="11">
@@ -5264,7 +5234,7 @@
     </row>
     <row r="77" spans="1:15">
       <c r="A77" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>20080010</v>
       </c>
       <c r="B77" s="11">
@@ -5312,7 +5282,7 @@
     </row>
     <row r="78" spans="1:15">
       <c r="A78" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>20080011</v>
       </c>
       <c r="B78" s="11">
@@ -5360,7 +5330,7 @@
     </row>
     <row r="79" spans="1:15">
       <c r="A79" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>20080012</v>
       </c>
       <c r="B79" s="11">
@@ -5408,7 +5378,7 @@
     </row>
     <row r="80" spans="1:15">
       <c r="A80" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>20090010</v>
       </c>
       <c r="B80" s="11">
@@ -5456,7 +5426,7 @@
     </row>
     <row r="81" spans="1:15">
       <c r="A81" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>20090011</v>
       </c>
       <c r="B81" s="11">
@@ -5504,7 +5474,7 @@
     </row>
     <row r="82" spans="1:15">
       <c r="A82" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>20090012</v>
       </c>
       <c r="B82" s="11">
@@ -5552,7 +5522,7 @@
     </row>
     <row r="83" s="1" customFormat="1" spans="1:19">
       <c r="A83" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>30020010</v>
       </c>
       <c r="B83" s="10">
@@ -5601,7 +5571,7 @@
     </row>
     <row r="84" s="1" customFormat="1" spans="1:19">
       <c r="A84" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>30020011</v>
       </c>
       <c r="B84" s="10">
@@ -5650,7 +5620,7 @@
     </row>
     <row r="85" s="1" customFormat="1" spans="1:19">
       <c r="A85" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>30020012</v>
       </c>
       <c r="B85" s="10">

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -1531,7 +1531,7 @@
     <col min="8" max="8" width="9" style="1"/>
     <col min="9" max="9" width="9.375" style="1"/>
     <col min="10" max="10" width="11.25" style="1" customWidth="1"/>
-    <col min="11" max="11" width="9.25833333333333" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.2333333333333" style="1" customWidth="1"/>
     <col min="12" max="12" width="17.05" style="1" customWidth="1"/>
     <col min="13" max="13" width="13.9666666666667" style="1" customWidth="1"/>
     <col min="14" max="14" width="17.125" customWidth="1"/>
@@ -1756,13 +1756,13 @@
         <v>2</v>
       </c>
       <c r="I6" s="1">
-        <v>50</v>
+        <v>50000</v>
       </c>
       <c r="J6" s="1">
         <v>-1</v>
       </c>
       <c r="K6" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>33</v>
@@ -1805,13 +1805,13 @@
         <v>3</v>
       </c>
       <c r="I7" s="1">
-        <v>100</v>
+        <v>5000000</v>
       </c>
       <c r="J7" s="1">
         <v>-1</v>
       </c>
       <c r="K7" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L7" s="1" t="s">
         <v>33</v>
@@ -1903,13 +1903,13 @@
         <v>2</v>
       </c>
       <c r="I9" s="1">
-        <v>50</v>
+        <v>50000</v>
       </c>
       <c r="J9" s="1">
         <v>-1</v>
       </c>
       <c r="K9" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>33</v>
@@ -1953,13 +1953,13 @@
         <v>3</v>
       </c>
       <c r="I10" s="1">
-        <v>100</v>
+        <v>5000000</v>
       </c>
       <c r="J10" s="1">
         <v>-1</v>
       </c>
       <c r="K10" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>33</v>
@@ -2051,13 +2051,13 @@
         <v>2</v>
       </c>
       <c r="I12" s="1">
-        <v>50</v>
+        <v>50000</v>
       </c>
       <c r="J12" s="1">
         <v>-1</v>
       </c>
       <c r="K12" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>33</v>
@@ -2101,13 +2101,13 @@
         <v>3</v>
       </c>
       <c r="I13" s="1">
-        <v>100</v>
+        <v>5000000</v>
       </c>
       <c r="J13" s="1">
         <v>-1</v>
       </c>
       <c r="K13" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>33</v>
@@ -2199,13 +2199,13 @@
         <v>2</v>
       </c>
       <c r="I15" s="1">
-        <v>50</v>
+        <v>50000</v>
       </c>
       <c r="J15" s="1">
         <v>-1</v>
       </c>
       <c r="K15" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>33</v>
@@ -2249,13 +2249,13 @@
         <v>3</v>
       </c>
       <c r="I16" s="1">
-        <v>100</v>
+        <v>5000000</v>
       </c>
       <c r="J16" s="1">
         <v>-1</v>
       </c>
       <c r="K16" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L16" s="1" t="s">
         <v>33</v>
@@ -2347,13 +2347,13 @@
         <v>2</v>
       </c>
       <c r="I18" s="1">
-        <v>50</v>
+        <v>50000</v>
       </c>
       <c r="J18" s="1">
         <v>-1</v>
       </c>
       <c r="K18" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L18" s="1" t="s">
         <v>33</v>
@@ -2397,13 +2397,13 @@
         <v>3</v>
       </c>
       <c r="I19" s="1">
-        <v>100</v>
+        <v>5000000</v>
       </c>
       <c r="J19" s="1">
         <v>-1</v>
       </c>
       <c r="K19" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L19" s="1" t="s">
         <v>33</v>
@@ -2445,8 +2445,7 @@
         <v>1</v>
       </c>
       <c r="I20" s="1">
-        <f>N20</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J20" s="1">
         <v>-1</v>
@@ -2495,14 +2494,13 @@
         <v>2</v>
       </c>
       <c r="I21" s="1">
-        <f t="shared" ref="I21:I55" si="4">N21</f>
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="J21" s="1">
         <v>-1</v>
       </c>
       <c r="K21" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L21" s="1" t="s">
         <v>33</v>
@@ -2545,14 +2543,13 @@
         <v>3</v>
       </c>
       <c r="I22" s="1">
-        <f t="shared" si="4"/>
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
       <c r="J22" s="1">
         <v>-1</v>
       </c>
       <c r="K22" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L22" s="1" t="s">
         <v>33</v>
@@ -2595,8 +2592,7 @@
         <v>1</v>
       </c>
       <c r="I23" s="1">
-        <f t="shared" si="4"/>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J23" s="1">
         <v>-1</v>
@@ -2629,7 +2625,7 @@
         <v>2</v>
       </c>
       <c r="D24" s="10" t="str">
-        <f t="shared" ref="D24:D28" si="5">D23</f>
+        <f t="shared" ref="D24:D28" si="4">D23</f>
         <v>龍虎鬥</v>
       </c>
       <c r="E24" s="11">
@@ -2645,14 +2641,13 @@
         <v>2</v>
       </c>
       <c r="I24" s="1">
-        <f t="shared" si="4"/>
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="J24" s="1">
         <v>-1</v>
       </c>
       <c r="K24" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L24" s="1" t="s">
         <v>33</v>
@@ -2680,7 +2675,7 @@
         <v>2</v>
       </c>
       <c r="D25" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>龍虎鬥</v>
       </c>
       <c r="E25" s="11">
@@ -2696,14 +2691,13 @@
         <v>3</v>
       </c>
       <c r="I25" s="1">
-        <f t="shared" si="4"/>
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
       <c r="J25" s="1">
         <v>-1</v>
       </c>
       <c r="K25" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L25" s="1" t="s">
         <v>33</v>
@@ -2746,8 +2740,7 @@
         <v>1</v>
       </c>
       <c r="I26" s="1">
-        <f t="shared" si="4"/>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J26" s="1">
         <v>-1</v>
@@ -2780,7 +2773,7 @@
         <v>2</v>
       </c>
       <c r="D27" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>飛禽走獸</v>
       </c>
       <c r="E27" s="11">
@@ -2796,14 +2789,13 @@
         <v>2</v>
       </c>
       <c r="I27" s="1">
-        <f t="shared" si="4"/>
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="J27" s="1">
         <v>-1</v>
       </c>
       <c r="K27" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L27" s="1" t="s">
         <v>33</v>
@@ -2833,7 +2825,7 @@
         <v>2</v>
       </c>
       <c r="D28" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>飛禽走獸</v>
       </c>
       <c r="E28" s="11">
@@ -2849,14 +2841,13 @@
         <v>3</v>
       </c>
       <c r="I28" s="1">
-        <f t="shared" si="4"/>
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
       <c r="J28" s="1">
         <v>-1</v>
       </c>
       <c r="K28" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L28" s="1" t="s">
         <v>33</v>
@@ -2901,8 +2892,7 @@
         <v>1</v>
       </c>
       <c r="I29" s="1">
-        <f t="shared" si="4"/>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J29" s="1">
         <v>-1</v>
@@ -2953,14 +2943,13 @@
         <v>2</v>
       </c>
       <c r="I30" s="1">
-        <f t="shared" si="4"/>
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="J30" s="1">
         <v>-1</v>
       </c>
       <c r="K30" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L30" s="1" t="s">
         <v>33</v>
@@ -3005,14 +2994,13 @@
         <v>3</v>
       </c>
       <c r="I31" s="1">
-        <f t="shared" si="4"/>
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
       <c r="J31" s="1">
         <v>-1</v>
       </c>
       <c r="K31" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L31" s="1" t="s">
         <v>33</v>
@@ -3057,8 +3045,7 @@
         <v>1</v>
       </c>
       <c r="I32" s="1">
-        <f t="shared" si="4"/>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J32" s="1">
         <v>-1</v>
@@ -3109,14 +3096,13 @@
         <v>2</v>
       </c>
       <c r="I33" s="1">
-        <f t="shared" si="4"/>
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="J33" s="1">
         <v>-1</v>
       </c>
       <c r="K33" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L33" s="1" t="s">
         <v>33</v>
@@ -3161,14 +3147,13 @@
         <v>3</v>
       </c>
       <c r="I34" s="1">
-        <f t="shared" si="4"/>
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
       <c r="J34" s="1">
         <v>-1</v>
       </c>
       <c r="K34" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L34" s="1" t="s">
         <v>33</v>
@@ -3213,8 +3198,7 @@
         <v>1</v>
       </c>
       <c r="I35" s="1">
-        <f t="shared" si="4"/>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J35" s="1">
         <v>-1</v>
@@ -3265,14 +3249,13 @@
         <v>2</v>
       </c>
       <c r="I36" s="1">
-        <f t="shared" si="4"/>
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="J36" s="1">
         <v>-1</v>
       </c>
       <c r="K36" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L36" s="1" t="s">
         <v>33</v>
@@ -3317,14 +3300,13 @@
         <v>3</v>
       </c>
       <c r="I37" s="1">
-        <f t="shared" si="4"/>
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
       <c r="J37" s="1">
         <v>-1</v>
       </c>
       <c r="K37" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L37" s="1" t="s">
         <v>33</v>
@@ -3369,8 +3351,7 @@
         <v>1</v>
       </c>
       <c r="I38" s="1">
-        <f t="shared" si="4"/>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J38" s="1">
         <v>-1</v>
@@ -3406,7 +3387,7 @@
         <v>2</v>
       </c>
       <c r="D39" s="10" t="str">
-        <f t="shared" ref="D36:D40" si="6">D38</f>
+        <f t="shared" ref="D36:D40" si="5">D38</f>
         <v>越南色碟</v>
       </c>
       <c r="E39" s="11">
@@ -3422,14 +3403,13 @@
         <v>2</v>
       </c>
       <c r="I39" s="1">
-        <f t="shared" si="4"/>
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="J39" s="1">
         <v>-1</v>
       </c>
       <c r="K39" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>33</v>
@@ -3459,7 +3439,7 @@
         <v>2</v>
       </c>
       <c r="D40" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>越南色碟</v>
       </c>
       <c r="E40" s="11">
@@ -3475,14 +3455,13 @@
         <v>3</v>
       </c>
       <c r="I40" s="1">
-        <f t="shared" si="4"/>
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
       <c r="J40" s="1">
         <v>-1</v>
       </c>
       <c r="K40" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L40" s="1" t="s">
         <v>33</v>
@@ -3525,8 +3504,7 @@
         <v>1</v>
       </c>
       <c r="I41" s="1">
-        <f t="shared" si="4"/>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J41" s="1">
         <v>-1</v>
@@ -3575,14 +3553,13 @@
         <v>2</v>
       </c>
       <c r="I42" s="1">
-        <f t="shared" si="4"/>
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="J42" s="1">
         <v>-1</v>
       </c>
       <c r="K42" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L42" s="1" t="s">
         <v>33</v>
@@ -3625,14 +3602,13 @@
         <v>3</v>
       </c>
       <c r="I43" s="1">
-        <f t="shared" si="4"/>
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
       <c r="J43" s="1">
         <v>-1</v>
       </c>
       <c r="K43" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L43" s="1" t="s">
         <v>33</v>
@@ -3675,8 +3651,7 @@
         <v>1</v>
       </c>
       <c r="I44" s="1">
-        <f t="shared" si="4"/>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J44" s="1">
         <v>-1</v>
@@ -3725,14 +3700,13 @@
         <v>2</v>
       </c>
       <c r="I45" s="1">
-        <f t="shared" si="4"/>
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="J45" s="1">
         <v>-1</v>
       </c>
       <c r="K45" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L45" s="1" t="s">
         <v>33</v>
@@ -3775,14 +3749,13 @@
         <v>3</v>
       </c>
       <c r="I46" s="1">
-        <f t="shared" si="4"/>
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
       <c r="J46" s="1">
         <v>-1</v>
       </c>
       <c r="K46" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L46" s="1" t="s">
         <v>33</v>
@@ -3822,8 +3795,7 @@
         <v>1</v>
       </c>
       <c r="I47" s="1">
-        <f t="shared" si="4"/>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J47" s="1">
         <v>-1</v>
@@ -3869,14 +3841,13 @@
         <v>2</v>
       </c>
       <c r="I48" s="1">
-        <f t="shared" si="4"/>
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="J48" s="1">
         <v>-1</v>
       </c>
       <c r="K48" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L48" s="1" t="s">
         <v>33</v>
@@ -3916,14 +3887,13 @@
         <v>3</v>
       </c>
       <c r="I49" s="1">
-        <f t="shared" si="4"/>
-        <v>10000000</v>
+        <v>5000000</v>
       </c>
       <c r="J49" s="1">
         <v>-1</v>
       </c>
       <c r="K49" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L49" s="1" t="s">
         <v>33</v>
@@ -3965,7 +3935,7 @@
         <v>1</v>
       </c>
       <c r="I50" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I50:I55" si="6">N50</f>
         <v>1000</v>
       </c>
       <c r="J50" s="1">
@@ -4014,14 +3984,14 @@
         <v>2</v>
       </c>
       <c r="I51" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>100000</v>
       </c>
       <c r="J51" s="1">
         <v>-1</v>
       </c>
       <c r="K51" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L51" s="21" t="s">
         <v>67</v>
@@ -4064,14 +4034,14 @@
         <v>3</v>
       </c>
       <c r="I52" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>10000000</v>
       </c>
       <c r="J52" s="1">
         <v>-1</v>
       </c>
       <c r="K52" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L52" s="21" t="s">
         <v>67</v>
@@ -4114,8 +4084,8 @@
         <v>1</v>
       </c>
       <c r="I53" s="1">
-        <f t="shared" si="4"/>
-        <v>2000</v>
+        <f t="shared" si="6"/>
+        <v>1000</v>
       </c>
       <c r="J53" s="1">
         <v>-1</v>
@@ -4130,7 +4100,7 @@
         <v>68</v>
       </c>
       <c r="N53">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="O53" s="18">
         <v>1990000</v>
@@ -4164,14 +4134,14 @@
         <v>2</v>
       </c>
       <c r="I54" s="1">
-        <f t="shared" si="4"/>
-        <v>200000</v>
+        <f t="shared" si="6"/>
+        <v>100000</v>
       </c>
       <c r="J54" s="1">
         <v>-1</v>
       </c>
       <c r="K54" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L54" s="21" t="s">
         <v>71</v>
@@ -4180,7 +4150,7 @@
         <v>68</v>
       </c>
       <c r="N54">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="O54" s="18">
         <v>1990000</v>
@@ -4214,14 +4184,14 @@
         <v>3</v>
       </c>
       <c r="I55" s="1">
-        <f t="shared" si="4"/>
-        <v>20000000</v>
+        <f t="shared" si="6"/>
+        <v>10000000</v>
       </c>
       <c r="J55" s="1">
         <v>-1</v>
       </c>
       <c r="K55" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L55" s="21" t="s">
         <v>71</v>
@@ -4230,7 +4200,7 @@
         <v>68</v>
       </c>
       <c r="N55">
-        <v>20000000</v>
+        <v>10000000</v>
       </c>
       <c r="O55" s="18">
         <v>1990000</v>
@@ -4279,7 +4249,7 @@
         <v>0</v>
       </c>
       <c r="N56">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="O56" s="19">
         <v>1980000</v>
@@ -4328,7 +4298,7 @@
         <v>0</v>
       </c>
       <c r="N57">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="O57" s="19">
         <v>1980000</v>
@@ -4426,7 +4396,7 @@
         <v>0</v>
       </c>
       <c r="N59">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="O59" s="19">
         <v>1980000</v>
@@ -4475,7 +4445,7 @@
         <v>0</v>
       </c>
       <c r="N60">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="O60" s="19">
         <v>1980000</v>
@@ -4573,7 +4543,7 @@
         <v>0</v>
       </c>
       <c r="N62">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="O62" s="19">
         <v>1980000</v>
@@ -4622,7 +4592,7 @@
         <v>0</v>
       </c>
       <c r="N63">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="O63" s="19">
         <v>1980000</v>
@@ -4720,7 +4690,7 @@
         <v>0</v>
       </c>
       <c r="N65">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="O65" s="19">
         <v>1980000</v>
@@ -4769,7 +4739,7 @@
         <v>0</v>
       </c>
       <c r="N66">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="O66" s="19">
         <v>1980000</v>
@@ -4867,7 +4837,7 @@
         <v>0</v>
       </c>
       <c r="N68">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="O68" s="19">
         <v>1980000</v>
@@ -4916,7 +4886,7 @@
         <v>0</v>
       </c>
       <c r="N69">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="O69" s="19">
         <v>1980000</v>
@@ -5014,7 +4984,7 @@
         <v>0</v>
       </c>
       <c r="N71">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="O71" s="19">
         <v>1980000</v>
@@ -5062,7 +5032,7 @@
         <v>0</v>
       </c>
       <c r="N72">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="O72" s="19">
         <v>1980000</v>
@@ -5158,7 +5128,7 @@
         <v>0</v>
       </c>
       <c r="N74">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="O74" s="19">
         <v>1980000</v>
@@ -5207,7 +5177,7 @@
         <v>0</v>
       </c>
       <c r="N75">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="O75" s="19">
         <v>1980000</v>
@@ -5304,7 +5274,7 @@
         <v>0</v>
       </c>
       <c r="N77">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="O77" s="19">
         <v>1980000</v>
@@ -5352,7 +5322,7 @@
         <v>0</v>
       </c>
       <c r="N78">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="O78" s="19">
         <v>1980000</v>
@@ -5448,7 +5418,7 @@
         <v>0</v>
       </c>
       <c r="N80">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="O80" s="19">
         <v>1980000</v>
@@ -5496,7 +5466,7 @@
         <v>0</v>
       </c>
       <c r="N81">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="O81" s="19">
         <v>1980000</v>
@@ -5592,7 +5562,7 @@
         <v>0</v>
       </c>
       <c r="N83">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="O83" s="19">
         <v>1980000</v>
@@ -5641,7 +5611,7 @@
         <v>0</v>
       </c>
       <c r="N84">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="O84" s="19">
         <v>1980000</v>
@@ -5690,7 +5660,7 @@
         <v>0</v>
       </c>
       <c r="N85">
-        <v>400000</v>
+        <v>100000</v>
       </c>
       <c r="O85" s="19">
         <v>1980000</v>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -182,7 +182,7 @@
     <t>最大准入分数</t>
   </si>
   <si>
-    <t>VIP等级限制</t>
+    <t>角色等级限制</t>
   </si>
   <si>
     <t>房间最大人数:达到X人时创建新房间</t>
@@ -230,7 +230,7 @@
     <t>enterMax</t>
   </si>
   <si>
-    <t>vipLvLimit</t>
+    <t>playerLvLimit</t>
   </si>
   <si>
     <t>participants_max</t>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -1762,7 +1762,7 @@
         <v>-1</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>33</v>
@@ -1811,7 +1811,7 @@
         <v>-1</v>
       </c>
       <c r="K7" s="1">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="L7" s="1" t="s">
         <v>33</v>
@@ -1909,7 +1909,7 @@
         <v>-1</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>33</v>
@@ -1959,7 +1959,7 @@
         <v>-1</v>
       </c>
       <c r="K10" s="1">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>33</v>
@@ -2057,7 +2057,7 @@
         <v>-1</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>33</v>
@@ -2107,7 +2107,7 @@
         <v>-1</v>
       </c>
       <c r="K13" s="1">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>33</v>
@@ -2205,7 +2205,7 @@
         <v>-1</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>33</v>
@@ -2255,7 +2255,7 @@
         <v>-1</v>
       </c>
       <c r="K16" s="1">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="L16" s="1" t="s">
         <v>33</v>
@@ -2353,7 +2353,7 @@
         <v>-1</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="L18" s="1" t="s">
         <v>33</v>
@@ -2403,7 +2403,7 @@
         <v>-1</v>
       </c>
       <c r="K19" s="1">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="L19" s="1" t="s">
         <v>33</v>
@@ -2500,7 +2500,7 @@
         <v>-1</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="L21" s="1" t="s">
         <v>33</v>
@@ -2549,7 +2549,7 @@
         <v>-1</v>
       </c>
       <c r="K22" s="1">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="L22" s="1" t="s">
         <v>33</v>
@@ -2647,7 +2647,7 @@
         <v>-1</v>
       </c>
       <c r="K24" s="1">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="L24" s="1" t="s">
         <v>33</v>
@@ -2697,7 +2697,7 @@
         <v>-1</v>
       </c>
       <c r="K25" s="1">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="L25" s="1" t="s">
         <v>33</v>
@@ -2795,7 +2795,7 @@
         <v>-1</v>
       </c>
       <c r="K27" s="1">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="L27" s="1" t="s">
         <v>33</v>
@@ -2847,7 +2847,7 @@
         <v>-1</v>
       </c>
       <c r="K28" s="1">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="L28" s="1" t="s">
         <v>33</v>
@@ -2949,7 +2949,7 @@
         <v>-1</v>
       </c>
       <c r="K30" s="1">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="L30" s="1" t="s">
         <v>33</v>
@@ -3000,7 +3000,7 @@
         <v>-1</v>
       </c>
       <c r="K31" s="1">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="L31" s="1" t="s">
         <v>33</v>
@@ -3102,7 +3102,7 @@
         <v>-1</v>
       </c>
       <c r="K33" s="1">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="L33" s="1" t="s">
         <v>33</v>
@@ -3153,7 +3153,7 @@
         <v>-1</v>
       </c>
       <c r="K34" s="1">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="L34" s="1" t="s">
         <v>33</v>
@@ -3255,7 +3255,7 @@
         <v>-1</v>
       </c>
       <c r="K36" s="1">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="L36" s="1" t="s">
         <v>33</v>
@@ -3306,7 +3306,7 @@
         <v>-1</v>
       </c>
       <c r="K37" s="1">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="L37" s="1" t="s">
         <v>33</v>
@@ -3409,7 +3409,7 @@
         <v>-1</v>
       </c>
       <c r="K39" s="1">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>33</v>
@@ -3461,7 +3461,7 @@
         <v>-1</v>
       </c>
       <c r="K40" s="1">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="L40" s="1" t="s">
         <v>33</v>
@@ -3559,7 +3559,7 @@
         <v>-1</v>
       </c>
       <c r="K42" s="1">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="L42" s="1" t="s">
         <v>33</v>
@@ -3608,7 +3608,7 @@
         <v>-1</v>
       </c>
       <c r="K43" s="1">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="L43" s="1" t="s">
         <v>33</v>
@@ -3706,7 +3706,7 @@
         <v>-1</v>
       </c>
       <c r="K45" s="1">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="L45" s="1" t="s">
         <v>33</v>
@@ -3755,7 +3755,7 @@
         <v>-1</v>
       </c>
       <c r="K46" s="1">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="L46" s="1" t="s">
         <v>33</v>
@@ -3847,7 +3847,7 @@
         <v>-1</v>
       </c>
       <c r="K48" s="1">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="L48" s="1" t="s">
         <v>33</v>
@@ -3893,7 +3893,7 @@
         <v>-1</v>
       </c>
       <c r="K49" s="1">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="L49" s="1" t="s">
         <v>33</v>
@@ -3991,7 +3991,7 @@
         <v>-1</v>
       </c>
       <c r="K51" s="1">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="L51" s="21" t="s">
         <v>67</v>
@@ -4041,7 +4041,7 @@
         <v>-1</v>
       </c>
       <c r="K52" s="1">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="L52" s="21" t="s">
         <v>67</v>
@@ -4141,7 +4141,7 @@
         <v>-1</v>
       </c>
       <c r="K54" s="1">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="L54" s="21" t="s">
         <v>71</v>
@@ -4191,7 +4191,7 @@
         <v>-1</v>
       </c>
       <c r="K55" s="1">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="L55" s="21" t="s">
         <v>71</v>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="794"/>
+    <workbookView windowWidth="27945" windowHeight="11925" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Warehouse" sheetId="42" r:id="rId1"/>
@@ -362,7 +362,7 @@
     <t>5:5</t>
   </si>
   <si>
-    <t>0:0</t>
+    <t>2:0</t>
   </si>
   <si>
     <t>德州</t>
@@ -1533,7 +1533,7 @@
     <col min="10" max="10" width="11.25" style="1" customWidth="1"/>
     <col min="11" max="11" width="13.2333333333333" style="1" customWidth="1"/>
     <col min="12" max="12" width="17.05" style="1" customWidth="1"/>
-    <col min="13" max="13" width="13.9666666666667" style="1" customWidth="1"/>
+    <col min="13" max="13" width="24.1166666666667" style="1" customWidth="1"/>
     <col min="14" max="14" width="17.125" customWidth="1"/>
     <col min="15" max="15" width="21.025" style="2" customWidth="1"/>
     <col min="16" max="16" width="9" style="1"/>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -156,7 +156,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="78">
   <si>
     <t>sid</t>
   </si>
@@ -291,6 +291,9 @@
   </si>
   <si>
     <t>Cleopatra</t>
+  </si>
+  <si>
+    <t>财富银行</t>
   </si>
   <si>
     <t>紅黑大戰</t>
@@ -1520,7 +1523,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S85"/>
+  <dimension ref="A1:S88"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="3" width="9.375" style="1"/>
@@ -1722,7 +1725,7 @@
         <v>34</v>
       </c>
       <c r="N5">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="O5" s="18">
         <v>1990000</v>
@@ -1756,13 +1759,13 @@
         <v>2</v>
       </c>
       <c r="I6" s="1">
-        <v>50000</v>
+        <v>500000</v>
       </c>
       <c r="J6" s="1">
         <v>-1</v>
       </c>
       <c r="K6" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>33</v>
@@ -1771,7 +1774,7 @@
         <v>34</v>
       </c>
       <c r="N6">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="O6" s="18">
         <v>1990000</v>
@@ -1805,13 +1808,13 @@
         <v>3</v>
       </c>
       <c r="I7" s="1">
-        <v>5000000</v>
+        <v>50000000</v>
       </c>
       <c r="J7" s="1">
         <v>-1</v>
       </c>
       <c r="K7" s="1">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="L7" s="1" t="s">
         <v>33</v>
@@ -1820,7 +1823,7 @@
         <v>34</v>
       </c>
       <c r="N7">
-        <v>10000000</v>
+        <v>50000000</v>
       </c>
       <c r="O7" s="18">
         <v>1990000</v>
@@ -1868,7 +1871,7 @@
         <v>34</v>
       </c>
       <c r="N8">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="O8" s="18">
         <v>1990000</v>
@@ -1903,13 +1906,13 @@
         <v>2</v>
       </c>
       <c r="I9" s="1">
-        <v>50000</v>
+        <v>500000</v>
       </c>
       <c r="J9" s="1">
         <v>-1</v>
       </c>
       <c r="K9" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>33</v>
@@ -1918,7 +1921,7 @@
         <v>34</v>
       </c>
       <c r="N9">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="O9" s="18">
         <v>1990000</v>
@@ -1953,13 +1956,13 @@
         <v>3</v>
       </c>
       <c r="I10" s="1">
-        <v>5000000</v>
+        <v>50000000</v>
       </c>
       <c r="J10" s="1">
         <v>-1</v>
       </c>
       <c r="K10" s="1">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>33</v>
@@ -1968,7 +1971,7 @@
         <v>34</v>
       </c>
       <c r="N10">
-        <v>10000000</v>
+        <v>50000000</v>
       </c>
       <c r="O10" s="18">
         <v>1990000</v>
@@ -2016,7 +2019,7 @@
         <v>34</v>
       </c>
       <c r="N11">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="O11" s="18">
         <v>1990000</v>
@@ -2051,13 +2054,13 @@
         <v>2</v>
       </c>
       <c r="I12" s="1">
-        <v>50000</v>
+        <v>500000</v>
       </c>
       <c r="J12" s="1">
         <v>-1</v>
       </c>
       <c r="K12" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>33</v>
@@ -2066,7 +2069,7 @@
         <v>34</v>
       </c>
       <c r="N12">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="O12" s="18">
         <v>1990000</v>
@@ -2101,13 +2104,13 @@
         <v>3</v>
       </c>
       <c r="I13" s="1">
-        <v>5000000</v>
+        <v>50000000</v>
       </c>
       <c r="J13" s="1">
         <v>-1</v>
       </c>
       <c r="K13" s="1">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>33</v>
@@ -2116,7 +2119,7 @@
         <v>34</v>
       </c>
       <c r="N13">
-        <v>10000000</v>
+        <v>50000000</v>
       </c>
       <c r="O13" s="18">
         <v>1990000</v>
@@ -2164,7 +2167,7 @@
         <v>34</v>
       </c>
       <c r="N14">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="O14" s="18">
         <v>1990000</v>
@@ -2199,13 +2202,13 @@
         <v>2</v>
       </c>
       <c r="I15" s="1">
-        <v>50000</v>
+        <v>500000</v>
       </c>
       <c r="J15" s="1">
         <v>-1</v>
       </c>
       <c r="K15" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>33</v>
@@ -2214,7 +2217,7 @@
         <v>34</v>
       </c>
       <c r="N15">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="O15" s="18">
         <v>1990000</v>
@@ -2232,7 +2235,7 @@
         <v>1</v>
       </c>
       <c r="D16" s="10" t="str">
-        <f>D15</f>
+        <f t="shared" ref="D16:D22" si="3">D15</f>
         <v>财神</v>
       </c>
       <c r="E16" s="11">
@@ -2249,13 +2252,13 @@
         <v>3</v>
       </c>
       <c r="I16" s="1">
-        <v>5000000</v>
+        <v>50000000</v>
       </c>
       <c r="J16" s="1">
         <v>-1</v>
       </c>
       <c r="K16" s="1">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="L16" s="1" t="s">
         <v>33</v>
@@ -2264,7 +2267,7 @@
         <v>34</v>
       </c>
       <c r="N16">
-        <v>10000000</v>
+        <v>50000000</v>
       </c>
       <c r="O16" s="18">
         <v>1990000</v>
@@ -2312,7 +2315,7 @@
         <v>34</v>
       </c>
       <c r="N17">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="O17" s="18">
         <v>1990000</v>
@@ -2330,7 +2333,7 @@
         <v>1</v>
       </c>
       <c r="D18" s="10" t="str">
-        <f>D17</f>
+        <f t="shared" si="3"/>
         <v>埃及艳后</v>
       </c>
       <c r="E18" s="11">
@@ -2347,13 +2350,13 @@
         <v>2</v>
       </c>
       <c r="I18" s="1">
-        <v>50000</v>
+        <v>500000</v>
       </c>
       <c r="J18" s="1">
         <v>-1</v>
       </c>
       <c r="K18" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L18" s="1" t="s">
         <v>33</v>
@@ -2362,7 +2365,7 @@
         <v>34</v>
       </c>
       <c r="N18">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="O18" s="18">
         <v>1990000</v>
@@ -2380,7 +2383,7 @@
         <v>1</v>
       </c>
       <c r="D19" s="10" t="str">
-        <f>D18</f>
+        <f t="shared" si="3"/>
         <v>埃及艳后</v>
       </c>
       <c r="E19" s="11">
@@ -2397,13 +2400,13 @@
         <v>3</v>
       </c>
       <c r="I19" s="1">
-        <v>5000000</v>
+        <v>50000000</v>
       </c>
       <c r="J19" s="1">
         <v>-1</v>
       </c>
       <c r="K19" s="1">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="L19" s="1" t="s">
         <v>33</v>
@@ -2412,7 +2415,7 @@
         <v>34</v>
       </c>
       <c r="N19">
-        <v>10000000</v>
+        <v>50000000</v>
       </c>
       <c r="O19" s="18">
         <v>1990000</v>
@@ -2420,23 +2423,23 @@
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="1">
-        <f t="shared" ref="A20:A66" si="3">B20*10+H20</f>
-        <v>2001001</v>
+        <f t="shared" si="2"/>
+        <v>1024001</v>
       </c>
       <c r="B20" s="10">
-        <v>200100</v>
+        <v>102400</v>
       </c>
       <c r="C20" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="10" t="s">
         <v>45</v>
       </c>
       <c r="E20" s="11">
-        <v>200100038</v>
+        <v>102400026</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>32</v>
@@ -2460,7 +2463,7 @@
         <v>34</v>
       </c>
       <c r="N20">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="O20" s="18">
         <v>1990000</v>
@@ -2468,24 +2471,24 @@
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="1">
+        <f t="shared" si="2"/>
+        <v>1024002</v>
+      </c>
+      <c r="B21" s="10">
+        <v>102400</v>
+      </c>
+      <c r="C21" s="10">
+        <v>1</v>
+      </c>
+      <c r="D21" s="10" t="str">
         <f t="shared" si="3"/>
-        <v>2001002</v>
-      </c>
-      <c r="B21" s="10">
-        <v>200100</v>
-      </c>
-      <c r="C21" s="10">
-        <v>2</v>
-      </c>
-      <c r="D21" s="10" t="str">
-        <f>D20</f>
-        <v>紅黑大戰</v>
+        <v>财富银行</v>
       </c>
       <c r="E21" s="11">
-        <v>200100038</v>
+        <v>102400026</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>35</v>
@@ -2494,13 +2497,13 @@
         <v>2</v>
       </c>
       <c r="I21" s="1">
-        <v>50000</v>
+        <v>500000</v>
       </c>
       <c r="J21" s="1">
         <v>-1</v>
       </c>
       <c r="K21" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L21" s="1" t="s">
         <v>33</v>
@@ -2509,32 +2512,32 @@
         <v>34</v>
       </c>
       <c r="N21">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="O21" s="18">
         <v>1990000</v>
       </c>
     </row>
-    <row r="22" spans="1:17">
+    <row r="22" spans="1:15">
       <c r="A22" s="1">
+        <f t="shared" si="2"/>
+        <v>1024003</v>
+      </c>
+      <c r="B22" s="10">
+        <v>102400</v>
+      </c>
+      <c r="C22" s="10">
+        <v>1</v>
+      </c>
+      <c r="D22" s="10" t="str">
         <f t="shared" si="3"/>
-        <v>2001003</v>
-      </c>
-      <c r="B22" s="10">
-        <v>200100</v>
-      </c>
-      <c r="C22" s="10">
-        <v>2</v>
-      </c>
-      <c r="D22" s="10" t="str">
-        <f>D21</f>
-        <v>紅黑大戰</v>
+        <v>财富银行</v>
       </c>
       <c r="E22" s="11">
-        <v>200100038</v>
+        <v>102400026</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>36</v>
@@ -2543,13 +2546,13 @@
         <v>3</v>
       </c>
       <c r="I22" s="1">
-        <v>5000000</v>
+        <v>50000000</v>
       </c>
       <c r="J22" s="1">
         <v>-1</v>
       </c>
       <c r="K22" s="1">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="L22" s="1" t="s">
         <v>33</v>
@@ -2558,32 +2561,31 @@
         <v>34</v>
       </c>
       <c r="N22">
-        <v>10000000</v>
+        <v>50000000</v>
       </c>
       <c r="O22" s="18">
         <v>1990000</v>
       </c>
-      <c r="Q22"/>
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="1">
-        <f t="shared" si="3"/>
-        <v>2001011</v>
+        <f t="shared" ref="A23:A69" si="4">B23*10+H23</f>
+        <v>2001001</v>
       </c>
       <c r="B23" s="10">
-        <v>200101</v>
+        <v>200100</v>
       </c>
       <c r="C23" s="10">
         <v>2</v>
       </c>
       <c r="D23" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E23" s="11">
+        <v>200100038</v>
+      </c>
+      <c r="F23" s="11" t="s">
         <v>47</v>
-      </c>
-      <c r="E23" s="11">
-        <v>200101001</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>48</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>32</v>
@@ -2607,32 +2609,32 @@
         <v>34</v>
       </c>
       <c r="N23">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="O23" s="18">
         <v>1990000</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" spans="1:19">
+    <row r="24" spans="1:15">
       <c r="A24" s="1">
-        <f t="shared" si="3"/>
-        <v>2001012</v>
+        <f t="shared" si="4"/>
+        <v>2001002</v>
       </c>
       <c r="B24" s="10">
-        <v>200101</v>
+        <v>200100</v>
       </c>
       <c r="C24" s="10">
         <v>2</v>
       </c>
       <c r="D24" s="10" t="str">
-        <f t="shared" ref="D24:D28" si="4">D23</f>
-        <v>龍虎鬥</v>
+        <f>D23</f>
+        <v>紅黑大戰</v>
       </c>
       <c r="E24" s="11">
-        <v>200101001</v>
+        <v>200100038</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>35</v>
@@ -2641,13 +2643,13 @@
         <v>2</v>
       </c>
       <c r="I24" s="1">
-        <v>50000</v>
+        <v>500000</v>
       </c>
       <c r="J24" s="1">
         <v>-1</v>
       </c>
       <c r="K24" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L24" s="1" t="s">
         <v>33</v>
@@ -2656,33 +2658,32 @@
         <v>34</v>
       </c>
       <c r="N24">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="O24" s="18">
         <v>1990000</v>
       </c>
-      <c r="S24" s="3"/>
-    </row>
-    <row r="25" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="25" spans="1:17">
       <c r="A25" s="1">
-        <f t="shared" si="3"/>
-        <v>2001013</v>
+        <f t="shared" si="4"/>
+        <v>2001003</v>
       </c>
       <c r="B25" s="10">
-        <v>200101</v>
+        <v>200100</v>
       </c>
       <c r="C25" s="10">
         <v>2</v>
       </c>
       <c r="D25" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>龍虎鬥</v>
+        <f>D24</f>
+        <v>紅黑大戰</v>
       </c>
       <c r="E25" s="11">
-        <v>200101001</v>
+        <v>200100038</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>36</v>
@@ -2691,13 +2692,13 @@
         <v>3</v>
       </c>
       <c r="I25" s="1">
-        <v>5000000</v>
+        <v>50000000</v>
       </c>
       <c r="J25" s="1">
         <v>-1</v>
       </c>
       <c r="K25" s="1">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="L25" s="1" t="s">
         <v>33</v>
@@ -2706,32 +2707,32 @@
         <v>34</v>
       </c>
       <c r="N25">
-        <v>10000000</v>
+        <v>50000000</v>
       </c>
       <c r="O25" s="18">
         <v>1990000</v>
       </c>
-      <c r="S25" s="3"/>
+      <c r="Q25"/>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="1">
-        <f t="shared" si="3"/>
-        <v>2003001</v>
+        <f t="shared" si="4"/>
+        <v>2001011</v>
       </c>
       <c r="B26" s="10">
-        <v>200300</v>
+        <v>200101</v>
       </c>
       <c r="C26" s="10">
         <v>2</v>
       </c>
       <c r="D26" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E26" s="11">
+        <v>200101001</v>
+      </c>
+      <c r="F26" s="11" t="s">
         <v>49</v>
-      </c>
-      <c r="E26" s="11">
-        <v>200300001</v>
-      </c>
-      <c r="F26" s="11" t="s">
-        <v>50</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>32</v>
@@ -2755,7 +2756,7 @@
         <v>34</v>
       </c>
       <c r="N26">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="O26" s="18">
         <v>1990000</v>
@@ -2763,24 +2764,24 @@
     </row>
     <row r="27" s="1" customFormat="1" spans="1:19">
       <c r="A27" s="1">
-        <f t="shared" si="3"/>
-        <v>2003002</v>
+        <f t="shared" si="4"/>
+        <v>2001012</v>
       </c>
       <c r="B27" s="10">
-        <v>200300</v>
+        <v>200101</v>
       </c>
       <c r="C27" s="10">
         <v>2</v>
       </c>
       <c r="D27" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>飛禽走獸</v>
+        <f t="shared" ref="D27:D31" si="5">D26</f>
+        <v>龍虎鬥</v>
       </c>
       <c r="E27" s="11">
-        <v>200300001</v>
+        <v>200101001</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>35</v>
@@ -2789,13 +2790,13 @@
         <v>2</v>
       </c>
       <c r="I27" s="1">
-        <v>50000</v>
+        <v>500000</v>
       </c>
       <c r="J27" s="1">
         <v>-1</v>
       </c>
       <c r="K27" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L27" s="1" t="s">
         <v>33</v>
@@ -2804,35 +2805,33 @@
         <v>34</v>
       </c>
       <c r="N27">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="O27" s="18">
         <v>1990000</v>
       </c>
-      <c r="Q27" s="3"/>
-      <c r="R27" s="10"/>
       <c r="S27" s="3"/>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:19">
       <c r="A28" s="1">
-        <f t="shared" si="3"/>
-        <v>2003003</v>
+        <f t="shared" si="4"/>
+        <v>2001013</v>
       </c>
       <c r="B28" s="10">
-        <v>200300</v>
+        <v>200101</v>
       </c>
       <c r="C28" s="10">
         <v>2</v>
       </c>
       <c r="D28" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v>飛禽走獸</v>
+        <f t="shared" si="5"/>
+        <v>龍虎鬥</v>
       </c>
       <c r="E28" s="11">
-        <v>200300001</v>
+        <v>200101001</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>36</v>
@@ -2841,13 +2840,13 @@
         <v>3</v>
       </c>
       <c r="I28" s="1">
-        <v>5000000</v>
+        <v>50000000</v>
       </c>
       <c r="J28" s="1">
         <v>-1</v>
       </c>
       <c r="K28" s="1">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="L28" s="1" t="s">
         <v>33</v>
@@ -2856,34 +2855,32 @@
         <v>34</v>
       </c>
       <c r="N28">
-        <v>10000000</v>
+        <v>50000000</v>
       </c>
       <c r="O28" s="18">
         <v>1990000</v>
       </c>
-      <c r="Q28" s="3"/>
-      <c r="R28" s="12"/>
-      <c r="S28" s="12"/>
-    </row>
-    <row r="29" spans="1:19">
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="1:15">
       <c r="A29" s="1">
-        <f t="shared" si="3"/>
-        <v>2004001</v>
+        <f t="shared" si="4"/>
+        <v>2003001</v>
       </c>
       <c r="B29" s="10">
-        <v>200400</v>
+        <v>200300</v>
       </c>
       <c r="C29" s="10">
         <v>2</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E29" s="11">
+        <v>200300001</v>
+      </c>
+      <c r="F29" s="11" t="s">
         <v>51</v>
-      </c>
-      <c r="E29" s="11">
-        <v>200400009</v>
-      </c>
-      <c r="F29" s="11" t="s">
-        <v>52</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>32</v>
@@ -2907,34 +2904,32 @@
         <v>34</v>
       </c>
       <c r="N29">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="O29" s="18">
         <v>1990000</v>
       </c>
-      <c r="Q29" s="3"/>
-      <c r="R29" s="12"/>
-      <c r="S29" s="12"/>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:19">
       <c r="A30" s="1">
-        <f t="shared" si="3"/>
-        <v>2004002</v>
+        <f t="shared" si="4"/>
+        <v>2003002</v>
       </c>
       <c r="B30" s="10">
-        <v>200400</v>
+        <v>200300</v>
       </c>
       <c r="C30" s="10">
         <v>2</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D30" s="10" t="str">
+        <f t="shared" si="5"/>
+        <v>飛禽走獸</v>
+      </c>
+      <c r="E30" s="11">
+        <v>200300001</v>
+      </c>
+      <c r="F30" s="11" t="s">
         <v>51</v>
-      </c>
-      <c r="E30" s="11">
-        <v>200400009</v>
-      </c>
-      <c r="F30" s="11" t="s">
-        <v>52</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>35</v>
@@ -2943,13 +2938,13 @@
         <v>2</v>
       </c>
       <c r="I30" s="1">
-        <v>50000</v>
+        <v>500000</v>
       </c>
       <c r="J30" s="1">
         <v>-1</v>
       </c>
       <c r="K30" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L30" s="1" t="s">
         <v>33</v>
@@ -2958,34 +2953,35 @@
         <v>34</v>
       </c>
       <c r="N30">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="O30" s="18">
         <v>1990000</v>
       </c>
       <c r="Q30" s="3"/>
-      <c r="R30" s="12"/>
-      <c r="S30" s="12"/>
+      <c r="R30" s="10"/>
+      <c r="S30" s="3"/>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:19">
       <c r="A31" s="1">
-        <f t="shared" si="3"/>
-        <v>2004003</v>
+        <f t="shared" si="4"/>
+        <v>2003003</v>
       </c>
       <c r="B31" s="10">
-        <v>200400</v>
+        <v>200300</v>
       </c>
       <c r="C31" s="10">
         <v>2</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="D31" s="10" t="str">
+        <f t="shared" si="5"/>
+        <v>飛禽走獸</v>
+      </c>
+      <c r="E31" s="11">
+        <v>200300001</v>
+      </c>
+      <c r="F31" s="11" t="s">
         <v>51</v>
-      </c>
-      <c r="E31" s="11">
-        <v>200400009</v>
-      </c>
-      <c r="F31" s="11" t="s">
-        <v>52</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>36</v>
@@ -2994,13 +2990,13 @@
         <v>3</v>
       </c>
       <c r="I31" s="1">
-        <v>5000000</v>
+        <v>50000000</v>
       </c>
       <c r="J31" s="1">
         <v>-1</v>
       </c>
       <c r="K31" s="1">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="L31" s="1" t="s">
         <v>33</v>
@@ -3009,7 +3005,7 @@
         <v>34</v>
       </c>
       <c r="N31">
-        <v>10000000</v>
+        <v>50000000</v>
       </c>
       <c r="O31" s="18">
         <v>1990000</v>
@@ -3020,23 +3016,23 @@
     </row>
     <row r="32" spans="1:19">
       <c r="A32" s="1">
-        <f t="shared" si="3"/>
-        <v>2005001</v>
+        <f t="shared" si="4"/>
+        <v>2004001</v>
       </c>
       <c r="B32" s="10">
-        <v>200500</v>
+        <v>200400</v>
       </c>
       <c r="C32" s="10">
         <v>2</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D32" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E32" s="11">
+        <v>200400009</v>
+      </c>
+      <c r="F32" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="E32" s="11">
-        <v>200500025</v>
-      </c>
-      <c r="F32" s="11" t="s">
-        <v>54</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>32</v>
@@ -3057,10 +3053,10 @@
         <v>33</v>
       </c>
       <c r="M32" s="20" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="N32">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="O32" s="18">
         <v>1990000</v>
@@ -3069,25 +3065,25 @@
       <c r="R32" s="12"/>
       <c r="S32" s="12"/>
     </row>
-    <row r="33" spans="1:19">
+    <row r="33" s="1" customFormat="1" spans="1:19">
       <c r="A33" s="1">
-        <f t="shared" si="3"/>
-        <v>2005002</v>
+        <f t="shared" si="4"/>
+        <v>2004002</v>
       </c>
       <c r="B33" s="10">
-        <v>200500</v>
+        <v>200400</v>
       </c>
       <c r="C33" s="10">
         <v>2</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="D33" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E33" s="11">
+        <v>200400009</v>
+      </c>
+      <c r="F33" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="E33" s="11">
-        <v>200500025</v>
-      </c>
-      <c r="F33" s="11" t="s">
-        <v>54</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>35</v>
@@ -3096,22 +3092,22 @@
         <v>2</v>
       </c>
       <c r="I33" s="1">
-        <v>50000</v>
+        <v>500000</v>
       </c>
       <c r="J33" s="1">
         <v>-1</v>
       </c>
       <c r="K33" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L33" s="1" t="s">
         <v>33</v>
       </c>
       <c r="M33" s="20" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="N33">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="O33" s="18">
         <v>1990000</v>
@@ -3120,25 +3116,25 @@
       <c r="R33" s="12"/>
       <c r="S33" s="12"/>
     </row>
-    <row r="34" spans="1:19">
+    <row r="34" s="1" customFormat="1" spans="1:19">
       <c r="A34" s="1">
-        <f t="shared" si="3"/>
-        <v>2005003</v>
+        <f t="shared" si="4"/>
+        <v>2004003</v>
       </c>
       <c r="B34" s="10">
-        <v>200500</v>
+        <v>200400</v>
       </c>
       <c r="C34" s="10">
         <v>2</v>
       </c>
-      <c r="D34" s="10" t="s">
+      <c r="D34" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E34" s="11">
+        <v>200400009</v>
+      </c>
+      <c r="F34" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="E34" s="11">
-        <v>200500025</v>
-      </c>
-      <c r="F34" s="11" t="s">
-        <v>54</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>36</v>
@@ -3147,22 +3143,22 @@
         <v>3</v>
       </c>
       <c r="I34" s="1">
-        <v>5000000</v>
+        <v>50000000</v>
       </c>
       <c r="J34" s="1">
         <v>-1</v>
       </c>
       <c r="K34" s="1">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="L34" s="1" t="s">
         <v>33</v>
       </c>
       <c r="M34" s="20" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="N34">
-        <v>10000000</v>
+        <v>50000000</v>
       </c>
       <c r="O34" s="18">
         <v>1990000</v>
@@ -3173,23 +3169,23 @@
     </row>
     <row r="35" spans="1:19">
       <c r="A35" s="1">
-        <f t="shared" si="3"/>
-        <v>2006001</v>
+        <f t="shared" si="4"/>
+        <v>2005001</v>
       </c>
       <c r="B35" s="10">
-        <v>200600</v>
+        <v>200500</v>
       </c>
       <c r="C35" s="10">
         <v>2</v>
       </c>
-      <c r="D35" s="11" t="s">
-        <v>56</v>
+      <c r="D35" s="10" t="s">
+        <v>54</v>
       </c>
       <c r="E35" s="11">
-        <v>200600001</v>
+        <v>200500025</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>32</v>
@@ -3210,10 +3206,10 @@
         <v>33</v>
       </c>
       <c r="M35" s="20" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="N35">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="O35" s="18">
         <v>1990000</v>
@@ -3222,25 +3218,25 @@
       <c r="R35" s="12"/>
       <c r="S35" s="12"/>
     </row>
-    <row r="36" s="1" customFormat="1" spans="1:19">
+    <row r="36" spans="1:19">
       <c r="A36" s="1">
-        <f t="shared" si="3"/>
-        <v>2006002</v>
+        <f t="shared" si="4"/>
+        <v>2005002</v>
       </c>
       <c r="B36" s="10">
-        <v>200600</v>
+        <v>200500</v>
       </c>
       <c r="C36" s="10">
         <v>2</v>
       </c>
-      <c r="D36" s="11" t="s">
-        <v>56</v>
+      <c r="D36" s="10" t="s">
+        <v>54</v>
       </c>
       <c r="E36" s="11">
-        <v>200600001</v>
+        <v>200500025</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>35</v>
@@ -3249,22 +3245,22 @@
         <v>2</v>
       </c>
       <c r="I36" s="1">
-        <v>50000</v>
+        <v>500000</v>
       </c>
       <c r="J36" s="1">
         <v>-1</v>
       </c>
       <c r="K36" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L36" s="1" t="s">
         <v>33</v>
       </c>
       <c r="M36" s="20" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="N36">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="O36" s="18">
         <v>1990000</v>
@@ -3273,25 +3269,25 @@
       <c r="R36" s="12"/>
       <c r="S36" s="12"/>
     </row>
-    <row r="37" s="1" customFormat="1" spans="1:19">
+    <row r="37" spans="1:19">
       <c r="A37" s="1">
-        <f t="shared" si="3"/>
-        <v>2006003</v>
+        <f t="shared" si="4"/>
+        <v>2005003</v>
       </c>
       <c r="B37" s="10">
-        <v>200600</v>
+        <v>200500</v>
       </c>
       <c r="C37" s="10">
         <v>2</v>
       </c>
-      <c r="D37" s="11" t="s">
-        <v>56</v>
+      <c r="D37" s="10" t="s">
+        <v>54</v>
       </c>
       <c r="E37" s="11">
-        <v>200600001</v>
+        <v>200500025</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>36</v>
@@ -3300,49 +3296,49 @@
         <v>3</v>
       </c>
       <c r="I37" s="1">
-        <v>5000000</v>
+        <v>50000000</v>
       </c>
       <c r="J37" s="1">
         <v>-1</v>
       </c>
       <c r="K37" s="1">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="L37" s="1" t="s">
         <v>33</v>
       </c>
       <c r="M37" s="20" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="N37">
-        <v>10000000</v>
+        <v>50000000</v>
       </c>
       <c r="O37" s="18">
         <v>1990000</v>
       </c>
       <c r="Q37" s="3"/>
-      <c r="R37"/>
+      <c r="R37" s="12"/>
       <c r="S37" s="12"/>
     </row>
     <row r="38" spans="1:19">
       <c r="A38" s="1">
-        <f t="shared" si="3"/>
-        <v>2007001</v>
+        <f t="shared" si="4"/>
+        <v>2006001</v>
       </c>
       <c r="B38" s="10">
-        <v>200700</v>
+        <v>200600</v>
       </c>
       <c r="C38" s="10">
         <v>2</v>
       </c>
-      <c r="D38" s="10" t="s">
+      <c r="D38" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E38" s="11">
+        <v>200600001</v>
+      </c>
+      <c r="F38" s="11" t="s">
         <v>58</v>
-      </c>
-      <c r="E38" s="11">
-        <v>200700001</v>
-      </c>
-      <c r="F38" s="11" t="s">
-        <v>59</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>32</v>
@@ -3366,7 +3362,7 @@
         <v>34</v>
       </c>
       <c r="N38">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="O38" s="18">
         <v>1990000</v>
@@ -3377,24 +3373,23 @@
     </row>
     <row r="39" s="1" customFormat="1" spans="1:19">
       <c r="A39" s="1">
-        <f t="shared" si="3"/>
-        <v>2007002</v>
+        <f t="shared" si="4"/>
+        <v>2006002</v>
       </c>
       <c r="B39" s="10">
-        <v>200700</v>
+        <v>200600</v>
       </c>
       <c r="C39" s="10">
         <v>2</v>
       </c>
-      <c r="D39" s="10" t="str">
-        <f t="shared" ref="D36:D40" si="5">D38</f>
-        <v>越南色碟</v>
+      <c r="D39" s="11" t="s">
+        <v>57</v>
       </c>
       <c r="E39" s="11">
-        <v>200700001</v>
+        <v>200600001</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>35</v>
@@ -3403,13 +3398,13 @@
         <v>2</v>
       </c>
       <c r="I39" s="1">
-        <v>50000</v>
+        <v>500000</v>
       </c>
       <c r="J39" s="1">
         <v>-1</v>
       </c>
       <c r="K39" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>33</v>
@@ -3418,7 +3413,7 @@
         <v>34</v>
       </c>
       <c r="N39">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="O39" s="18">
         <v>1990000</v>
@@ -3429,24 +3424,23 @@
     </row>
     <row r="40" s="1" customFormat="1" spans="1:19">
       <c r="A40" s="1">
-        <f t="shared" si="3"/>
-        <v>2007003</v>
+        <f t="shared" si="4"/>
+        <v>2006003</v>
       </c>
       <c r="B40" s="10">
-        <v>200700</v>
+        <v>200600</v>
       </c>
       <c r="C40" s="10">
         <v>2</v>
       </c>
-      <c r="D40" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v>越南色碟</v>
+      <c r="D40" s="11" t="s">
+        <v>57</v>
       </c>
       <c r="E40" s="11">
-        <v>200700001</v>
+        <v>200600001</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>36</v>
@@ -3455,13 +3449,13 @@
         <v>3</v>
       </c>
       <c r="I40" s="1">
-        <v>5000000</v>
+        <v>50000000</v>
       </c>
       <c r="J40" s="1">
         <v>-1</v>
       </c>
       <c r="K40" s="1">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="L40" s="1" t="s">
         <v>33</v>
@@ -3470,32 +3464,34 @@
         <v>34</v>
       </c>
       <c r="N40">
-        <v>10000000</v>
+        <v>50000000</v>
       </c>
       <c r="O40" s="18">
         <v>1990000</v>
       </c>
-      <c r="S40" s="3"/>
-    </row>
-    <row r="41" s="1" customFormat="1" spans="1:19">
+      <c r="Q40" s="3"/>
+      <c r="R40"/>
+      <c r="S40" s="12"/>
+    </row>
+    <row r="41" spans="1:19">
       <c r="A41" s="1">
-        <f t="shared" si="3"/>
-        <v>2008001</v>
+        <f t="shared" si="4"/>
+        <v>2007001</v>
       </c>
       <c r="B41" s="10">
-        <v>200800</v>
+        <v>200700</v>
       </c>
       <c r="C41" s="10">
         <v>2</v>
       </c>
-      <c r="D41" s="11" t="s">
+      <c r="D41" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E41" s="11">
+        <v>200700001</v>
+      </c>
+      <c r="F41" s="11" t="s">
         <v>60</v>
-      </c>
-      <c r="E41" s="11">
-        <v>200800001</v>
-      </c>
-      <c r="F41" s="11" t="s">
-        <v>61</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>32</v>
@@ -3519,32 +3515,35 @@
         <v>34</v>
       </c>
       <c r="N41">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="O41" s="18">
         <v>1990000</v>
       </c>
-      <c r="S41" s="3"/>
+      <c r="Q41" s="3"/>
+      <c r="R41" s="12"/>
+      <c r="S41" s="12"/>
     </row>
     <row r="42" s="1" customFormat="1" spans="1:19">
       <c r="A42" s="1">
-        <f t="shared" si="3"/>
-        <v>2008002</v>
+        <f t="shared" si="4"/>
+        <v>2007002</v>
       </c>
       <c r="B42" s="10">
-        <v>200800</v>
+        <v>200700</v>
       </c>
       <c r="C42" s="10">
         <v>2</v>
       </c>
-      <c r="D42" s="11" t="s">
+      <c r="D42" s="10" t="str">
+        <f t="shared" ref="D39:D43" si="6">D41</f>
+        <v>越南色碟</v>
+      </c>
+      <c r="E42" s="11">
+        <v>200700001</v>
+      </c>
+      <c r="F42" s="11" t="s">
         <v>60</v>
-      </c>
-      <c r="E42" s="11">
-        <v>200800001</v>
-      </c>
-      <c r="F42" s="11" t="s">
-        <v>61</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>35</v>
@@ -3553,13 +3552,13 @@
         <v>2</v>
       </c>
       <c r="I42" s="1">
-        <v>50000</v>
+        <v>500000</v>
       </c>
       <c r="J42" s="1">
         <v>-1</v>
       </c>
       <c r="K42" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L42" s="1" t="s">
         <v>33</v>
@@ -3568,32 +3567,35 @@
         <v>34</v>
       </c>
       <c r="N42">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="O42" s="18">
         <v>1990000</v>
       </c>
-      <c r="S42" s="3"/>
+      <c r="Q42" s="3"/>
+      <c r="R42" s="12"/>
+      <c r="S42" s="12"/>
     </row>
     <row r="43" s="1" customFormat="1" spans="1:19">
       <c r="A43" s="1">
-        <f t="shared" si="3"/>
-        <v>2008003</v>
+        <f t="shared" si="4"/>
+        <v>2007003</v>
       </c>
       <c r="B43" s="10">
-        <v>200800</v>
+        <v>200700</v>
       </c>
       <c r="C43" s="10">
         <v>2</v>
       </c>
-      <c r="D43" s="11" t="s">
+      <c r="D43" s="10" t="str">
+        <f t="shared" si="6"/>
+        <v>越南色碟</v>
+      </c>
+      <c r="E43" s="11">
+        <v>200700001</v>
+      </c>
+      <c r="F43" s="11" t="s">
         <v>60</v>
-      </c>
-      <c r="E43" s="11">
-        <v>200800001</v>
-      </c>
-      <c r="F43" s="11" t="s">
-        <v>61</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>36</v>
@@ -3602,13 +3604,13 @@
         <v>3</v>
       </c>
       <c r="I43" s="1">
-        <v>5000000</v>
+        <v>50000000</v>
       </c>
       <c r="J43" s="1">
         <v>-1</v>
       </c>
       <c r="K43" s="1">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="L43" s="1" t="s">
         <v>33</v>
@@ -3617,32 +3619,32 @@
         <v>34</v>
       </c>
       <c r="N43">
-        <v>10000000</v>
+        <v>50000000</v>
       </c>
       <c r="O43" s="18">
         <v>1990000</v>
       </c>
       <c r="S43" s="3"/>
     </row>
-    <row r="44" spans="1:15">
+    <row r="44" s="1" customFormat="1" spans="1:19">
       <c r="A44" s="1">
-        <f t="shared" si="3"/>
-        <v>2009001</v>
-      </c>
-      <c r="B44" s="13">
-        <v>200900</v>
+        <f t="shared" si="4"/>
+        <v>2008001</v>
+      </c>
+      <c r="B44" s="10">
+        <v>200800</v>
       </c>
       <c r="C44" s="10">
         <v>2</v>
       </c>
-      <c r="D44" s="13" t="s">
+      <c r="D44" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E44" s="11">
+        <v>200800001</v>
+      </c>
+      <c r="F44" s="11" t="s">
         <v>62</v>
-      </c>
-      <c r="E44" s="11">
-        <v>200900001</v>
-      </c>
-      <c r="F44" s="11" t="s">
-        <v>63</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>32</v>
@@ -3666,32 +3668,32 @@
         <v>34</v>
       </c>
       <c r="N44">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="O44" s="18">
         <v>1990000</v>
       </c>
-    </row>
-    <row r="45" spans="1:15">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" s="1" customFormat="1" spans="1:19">
       <c r="A45" s="1">
-        <f t="shared" si="3"/>
-        <v>2009002</v>
+        <f t="shared" si="4"/>
+        <v>2008002</v>
       </c>
       <c r="B45" s="10">
-        <v>200900</v>
+        <v>200800</v>
       </c>
       <c r="C45" s="10">
         <v>2</v>
       </c>
-      <c r="D45" s="10" t="str">
-        <f>D44</f>
-        <v>魚蝦蟹</v>
+      <c r="D45" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="E45" s="11">
-        <v>200900001</v>
+        <v>200800001</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>35</v>
@@ -3700,13 +3702,13 @@
         <v>2</v>
       </c>
       <c r="I45" s="1">
-        <v>50000</v>
+        <v>500000</v>
       </c>
       <c r="J45" s="1">
         <v>-1</v>
       </c>
       <c r="K45" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L45" s="1" t="s">
         <v>33</v>
@@ -3715,32 +3717,32 @@
         <v>34</v>
       </c>
       <c r="N45">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="O45" s="18">
         <v>1990000</v>
       </c>
-    </row>
-    <row r="46" spans="1:15">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" s="1" customFormat="1" spans="1:19">
       <c r="A46" s="1">
-        <f t="shared" si="3"/>
-        <v>2009003</v>
+        <f t="shared" si="4"/>
+        <v>2008003</v>
       </c>
       <c r="B46" s="10">
-        <v>200900</v>
+        <v>200800</v>
       </c>
       <c r="C46" s="10">
         <v>2</v>
       </c>
-      <c r="D46" s="10" t="str">
-        <f>D45</f>
-        <v>魚蝦蟹</v>
+      <c r="D46" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="E46" s="11">
-        <v>200900001</v>
+        <v>200800001</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>36</v>
@@ -3749,13 +3751,13 @@
         <v>3</v>
       </c>
       <c r="I46" s="1">
-        <v>5000000</v>
+        <v>50000000</v>
       </c>
       <c r="J46" s="1">
         <v>-1</v>
       </c>
       <c r="K46" s="1">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="L46" s="1" t="s">
         <v>33</v>
@@ -3764,30 +3766,33 @@
         <v>34</v>
       </c>
       <c r="N46">
-        <v>10000000</v>
+        <v>50000000</v>
       </c>
       <c r="O46" s="18">
         <v>1990000</v>
       </c>
+      <c r="S46" s="3"/>
     </row>
     <row r="47" spans="1:15">
       <c r="A47" s="1">
-        <f t="shared" si="3"/>
-        <v>2010001</v>
-      </c>
-      <c r="B47" s="10">
-        <v>201000</v>
+        <f t="shared" si="4"/>
+        <v>2009001</v>
+      </c>
+      <c r="B47" s="13">
+        <v>200900</v>
       </c>
       <c r="C47" s="10">
         <v>2</v>
       </c>
-      <c r="D47" s="10" t="s">
+      <c r="D47" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="E47" s="11">
+        <v>200900001</v>
+      </c>
+      <c r="F47" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E47" s="11">
-        <v>101000006</v>
-      </c>
-      <c r="F47" s="11"/>
       <c r="G47" s="1" t="s">
         <v>32</v>
       </c>
@@ -3810,7 +3815,7 @@
         <v>34</v>
       </c>
       <c r="N47">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="O47" s="18">
         <v>1990000</v>
@@ -3818,22 +3823,25 @@
     </row>
     <row r="48" spans="1:15">
       <c r="A48" s="1">
-        <f t="shared" si="3"/>
-        <v>2010002</v>
+        <f t="shared" si="4"/>
+        <v>2009002</v>
       </c>
       <c r="B48" s="10">
-        <v>201000</v>
+        <v>200900</v>
       </c>
       <c r="C48" s="10">
         <v>2</v>
       </c>
-      <c r="D48" s="10" t="s">
+      <c r="D48" s="10" t="str">
+        <f>D47</f>
+        <v>魚蝦蟹</v>
+      </c>
+      <c r="E48" s="11">
+        <v>200900001</v>
+      </c>
+      <c r="F48" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E48" s="11">
-        <v>101000006</v>
-      </c>
-      <c r="F48" s="11"/>
       <c r="G48" s="1" t="s">
         <v>35</v>
       </c>
@@ -3841,13 +3849,13 @@
         <v>2</v>
       </c>
       <c r="I48" s="1">
-        <v>50000</v>
+        <v>500000</v>
       </c>
       <c r="J48" s="1">
         <v>-1</v>
       </c>
       <c r="K48" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L48" s="1" t="s">
         <v>33</v>
@@ -3856,7 +3864,7 @@
         <v>34</v>
       </c>
       <c r="N48">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="O48" s="18">
         <v>1990000</v>
@@ -3864,22 +3872,25 @@
     </row>
     <row r="49" spans="1:15">
       <c r="A49" s="1">
-        <f t="shared" si="3"/>
-        <v>2010003</v>
+        <f t="shared" si="4"/>
+        <v>2009003</v>
       </c>
       <c r="B49" s="10">
-        <v>201000</v>
+        <v>200900</v>
       </c>
       <c r="C49" s="10">
         <v>2</v>
       </c>
-      <c r="D49" s="10" t="s">
+      <c r="D49" s="10" t="str">
+        <f>D48</f>
+        <v>魚蝦蟹</v>
+      </c>
+      <c r="E49" s="11">
+        <v>200900001</v>
+      </c>
+      <c r="F49" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E49" s="11">
-        <v>101000006</v>
-      </c>
-      <c r="F49" s="11"/>
       <c r="G49" s="1" t="s">
         <v>36</v>
       </c>
@@ -3887,13 +3898,13 @@
         <v>3</v>
       </c>
       <c r="I49" s="1">
-        <v>5000000</v>
+        <v>50000000</v>
       </c>
       <c r="J49" s="1">
         <v>-1</v>
       </c>
       <c r="K49" s="1">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="L49" s="1" t="s">
         <v>33</v>
@@ -3902,7 +3913,7 @@
         <v>34</v>
       </c>
       <c r="N49">
-        <v>10000000</v>
+        <v>50000000</v>
       </c>
       <c r="O49" s="18">
         <v>1990000</v>
@@ -3910,24 +3921,22 @@
     </row>
     <row r="50" spans="1:15">
       <c r="A50" s="1">
-        <f t="shared" si="3"/>
-        <v>3001001</v>
+        <f t="shared" si="4"/>
+        <v>2010001</v>
       </c>
       <c r="B50" s="10">
-        <v>300100</v>
+        <v>201000</v>
       </c>
       <c r="C50" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D50" s="10" t="s">
         <v>65</v>
       </c>
       <c r="E50" s="11">
-        <v>300100001</v>
-      </c>
-      <c r="F50" s="11" t="s">
-        <v>66</v>
-      </c>
+        <v>101000006</v>
+      </c>
+      <c r="F50" s="11"/>
       <c r="G50" s="1" t="s">
         <v>32</v>
       </c>
@@ -3935,8 +3944,7 @@
         <v>1</v>
       </c>
       <c r="I50" s="1">
-        <f t="shared" ref="I50:I55" si="6">N50</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J50" s="1">
         <v>-1</v>
@@ -3944,39 +3952,37 @@
       <c r="K50" s="1">
         <v>0</v>
       </c>
-      <c r="L50" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="M50" s="21" t="s">
-        <v>68</v>
+      <c r="L50" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M50" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N50">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="O50" s="18">
         <v>1990000</v>
       </c>
     </row>
-    <row r="51" s="1" customFormat="1" spans="1:19">
+    <row r="51" spans="1:15">
       <c r="A51" s="1">
-        <f t="shared" si="3"/>
-        <v>3001002</v>
+        <f t="shared" si="4"/>
+        <v>2010002</v>
       </c>
       <c r="B51" s="10">
-        <v>300100</v>
+        <v>201000</v>
       </c>
       <c r="C51" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D51" s="10" t="s">
         <v>65</v>
       </c>
       <c r="E51" s="11">
-        <v>300100001</v>
-      </c>
-      <c r="F51" s="11" t="s">
-        <v>66</v>
-      </c>
+        <v>101000006</v>
+      </c>
+      <c r="F51" s="11"/>
       <c r="G51" s="1" t="s">
         <v>35</v>
       </c>
@@ -3984,49 +3990,45 @@
         <v>2</v>
       </c>
       <c r="I51" s="1">
-        <f t="shared" si="6"/>
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="J51" s="1">
         <v>-1</v>
       </c>
       <c r="K51" s="1">
-        <v>40</v>
-      </c>
-      <c r="L51" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="M51" s="21" t="s">
-        <v>68</v>
+        <v>0</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M51" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N51">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="O51" s="18">
         <v>1990000</v>
       </c>
-      <c r="S51" s="3"/>
-    </row>
-    <row r="52" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="52" spans="1:15">
       <c r="A52" s="1">
-        <f t="shared" si="3"/>
-        <v>3001003</v>
+        <f t="shared" si="4"/>
+        <v>2010003</v>
       </c>
       <c r="B52" s="10">
-        <v>300100</v>
+        <v>201000</v>
       </c>
       <c r="C52" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D52" s="10" t="s">
         <v>65</v>
       </c>
       <c r="E52" s="11">
-        <v>300100001</v>
-      </c>
-      <c r="F52" s="11" t="s">
-        <v>66</v>
-      </c>
+        <v>101000006</v>
+      </c>
+      <c r="F52" s="11"/>
       <c r="G52" s="1" t="s">
         <v>36</v>
       </c>
@@ -4034,48 +4036,46 @@
         <v>3</v>
       </c>
       <c r="I52" s="1">
-        <f t="shared" si="6"/>
-        <v>10000000</v>
+        <v>50000000</v>
       </c>
       <c r="J52" s="1">
         <v>-1</v>
       </c>
       <c r="K52" s="1">
-        <v>250</v>
-      </c>
-      <c r="L52" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="M52" s="21" t="s">
-        <v>68</v>
+        <v>0</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M52" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N52">
-        <v>10000000</v>
+        <v>50000000</v>
       </c>
       <c r="O52" s="18">
         <v>1990000</v>
       </c>
-      <c r="S52" s="3"/>
-    </row>
-    <row r="53" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="53" spans="1:15">
       <c r="A53" s="1">
-        <f t="shared" si="3"/>
-        <v>3002001</v>
+        <f t="shared" si="4"/>
+        <v>3001001</v>
       </c>
       <c r="B53" s="10">
-        <v>300200</v>
+        <v>300100</v>
       </c>
       <c r="C53" s="10">
         <v>3</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E53" s="11">
-        <v>300200006</v>
+        <v>300100001</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>32</v>
@@ -4084,8 +4084,7 @@
         <v>1</v>
       </c>
       <c r="I53" s="1">
-        <f t="shared" si="6"/>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J53" s="1">
         <v>-1</v>
@@ -4094,38 +4093,37 @@
         <v>0</v>
       </c>
       <c r="L53" s="21" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="M53" s="21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="N53">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="O53" s="18">
         <v>1990000</v>
       </c>
-      <c r="S53" s="3"/>
     </row>
     <row r="54" s="1" customFormat="1" spans="1:19">
       <c r="A54" s="1">
-        <f t="shared" si="3"/>
-        <v>3002002</v>
+        <f t="shared" si="4"/>
+        <v>3001002</v>
       </c>
       <c r="B54" s="10">
-        <v>300200</v>
+        <v>300100</v>
       </c>
       <c r="C54" s="10">
         <v>3</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E54" s="11">
-        <v>300200006</v>
+        <v>300100001</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>35</v>
@@ -4134,23 +4132,22 @@
         <v>2</v>
       </c>
       <c r="I54" s="1">
-        <f t="shared" si="6"/>
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="J54" s="1">
         <v>-1</v>
       </c>
       <c r="K54" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L54" s="21" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="M54" s="21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="N54">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="O54" s="18">
         <v>1990000</v>
@@ -4159,23 +4156,23 @@
     </row>
     <row r="55" s="1" customFormat="1" spans="1:19">
       <c r="A55" s="1">
-        <f t="shared" si="3"/>
-        <v>3002003</v>
+        <f t="shared" si="4"/>
+        <v>3001003</v>
       </c>
       <c r="B55" s="10">
-        <v>300200</v>
+        <v>300100</v>
       </c>
       <c r="C55" s="10">
         <v>3</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E55" s="11">
-        <v>300200006</v>
+        <v>300100001</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>36</v>
@@ -4184,23 +4181,22 @@
         <v>3</v>
       </c>
       <c r="I55" s="1">
-        <f t="shared" si="6"/>
-        <v>10000000</v>
+        <v>50000000</v>
       </c>
       <c r="J55" s="1">
         <v>-1</v>
       </c>
       <c r="K55" s="1">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="L55" s="21" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="M55" s="21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="N55">
-        <v>10000000</v>
+        <v>50000000</v>
       </c>
       <c r="O55" s="18">
         <v>1990000</v>
@@ -4209,173 +4205,173 @@
     </row>
     <row r="56" s="1" customFormat="1" spans="1:19">
       <c r="A56" s="1">
-        <f t="shared" ref="A56:A62" si="7">B56*100+H56</f>
-        <v>20010010</v>
-      </c>
-      <c r="B56" s="11">
-        <v>200100</v>
-      </c>
-      <c r="C56" s="11">
-        <v>2</v>
-      </c>
-      <c r="D56" s="11" t="s">
-        <v>45</v>
+        <f t="shared" si="4"/>
+        <v>3002001</v>
+      </c>
+      <c r="B56" s="10">
+        <v>300200</v>
+      </c>
+      <c r="C56" s="10">
+        <v>3</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>70</v>
       </c>
       <c r="E56" s="11">
-        <v>200100038</v>
+        <v>300200006</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="G56" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H56" s="1">
+        <v>1</v>
+      </c>
+      <c r="I56" s="1">
+        <v>0</v>
+      </c>
+      <c r="J56" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K56" s="1">
+        <v>0</v>
+      </c>
+      <c r="L56" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="H56" s="14">
-        <v>10</v>
-      </c>
-      <c r="I56" s="14">
-        <v>0</v>
-      </c>
-      <c r="J56" s="14">
-        <v>-1</v>
-      </c>
-      <c r="K56" s="1">
-        <v>0</v>
-      </c>
-      <c r="L56" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="M56" s="14">
-        <v>0</v>
+      <c r="M56" s="21" t="s">
+        <v>69</v>
       </c>
       <c r="N56">
-        <v>200</v>
-      </c>
-      <c r="O56" s="19">
-        <v>1980000</v>
+        <v>5000</v>
+      </c>
+      <c r="O56" s="18">
+        <v>1990000</v>
       </c>
       <c r="S56" s="3"/>
     </row>
     <row r="57" s="1" customFormat="1" spans="1:19">
       <c r="A57" s="1">
-        <f t="shared" si="7"/>
-        <v>20010011</v>
-      </c>
-      <c r="B57" s="11">
-        <v>200100</v>
-      </c>
-      <c r="C57" s="11">
-        <v>2</v>
-      </c>
-      <c r="D57" s="11" t="s">
-        <v>45</v>
+        <f t="shared" si="4"/>
+        <v>3002002</v>
+      </c>
+      <c r="B57" s="10">
+        <v>300200</v>
+      </c>
+      <c r="C57" s="10">
+        <v>3</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>70</v>
       </c>
       <c r="E57" s="11">
-        <v>200100038</v>
+        <v>300200006</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="G57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="H57" s="14">
-        <v>11</v>
-      </c>
-      <c r="I57" s="14">
-        <v>0</v>
-      </c>
-      <c r="J57" s="14">
+        <v>71</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H57" s="1">
+        <v>2</v>
+      </c>
+      <c r="I57" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J57" s="1">
         <v>-1</v>
       </c>
       <c r="K57" s="1">
         <v>0</v>
       </c>
-      <c r="L57" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="M57" s="14">
-        <v>0</v>
+      <c r="L57" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="M57" s="21" t="s">
+        <v>69</v>
       </c>
       <c r="N57">
-        <v>5000</v>
-      </c>
-      <c r="O57" s="19">
-        <v>1980000</v>
+        <v>500000</v>
+      </c>
+      <c r="O57" s="18">
+        <v>1990000</v>
       </c>
       <c r="S57" s="3"/>
     </row>
     <row r="58" s="1" customFormat="1" spans="1:19">
       <c r="A58" s="1">
-        <f t="shared" si="7"/>
-        <v>20010012</v>
-      </c>
-      <c r="B58" s="11">
-        <v>200100</v>
-      </c>
-      <c r="C58" s="11">
-        <v>2</v>
-      </c>
-      <c r="D58" s="11" t="s">
-        <v>45</v>
+        <f t="shared" si="4"/>
+        <v>3002003</v>
+      </c>
+      <c r="B58" s="10">
+        <v>300200</v>
+      </c>
+      <c r="C58" s="10">
+        <v>3</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>70</v>
       </c>
       <c r="E58" s="11">
-        <v>200100038</v>
+        <v>300200006</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="G58" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="H58" s="14">
-        <v>12</v>
-      </c>
-      <c r="I58" s="14">
-        <v>0</v>
-      </c>
-      <c r="J58" s="14">
+        <v>71</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H58" s="1">
+        <v>3</v>
+      </c>
+      <c r="I58" s="1">
+        <v>50000000</v>
+      </c>
+      <c r="J58" s="1">
         <v>-1</v>
       </c>
       <c r="K58" s="1">
         <v>0</v>
       </c>
-      <c r="L58" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="M58" s="14">
-        <v>0</v>
+      <c r="L58" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="M58" s="21" t="s">
+        <v>69</v>
       </c>
       <c r="N58">
-        <v>100000</v>
-      </c>
-      <c r="O58" s="19">
-        <v>1980000</v>
+        <v>50000000</v>
+      </c>
+      <c r="O58" s="18">
+        <v>1990000</v>
       </c>
       <c r="S58" s="3"/>
     </row>
     <row r="59" s="1" customFormat="1" spans="1:19">
       <c r="A59" s="1">
-        <f t="shared" si="7"/>
-        <v>20010110</v>
+        <f t="shared" ref="A59:A65" si="7">B59*100+H59</f>
+        <v>20010010</v>
       </c>
       <c r="B59" s="11">
-        <v>200101</v>
+        <v>200100</v>
       </c>
       <c r="C59" s="11">
         <v>2</v>
       </c>
       <c r="D59" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E59" s="11">
+        <v>200100038</v>
+      </c>
+      <c r="F59" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="E59" s="11">
-        <v>200101001</v>
-      </c>
-      <c r="F59" s="11" t="s">
-        <v>48</v>
-      </c>
       <c r="G59" s="14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H59" s="14">
         <v>10</v>
@@ -4390,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="L59" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M59" s="14">
         <v>0</v>
@@ -4406,25 +4402,25 @@
     <row r="60" s="1" customFormat="1" spans="1:19">
       <c r="A60" s="1">
         <f t="shared" si="7"/>
-        <v>20010111</v>
+        <v>20010011</v>
       </c>
       <c r="B60" s="11">
-        <v>200101</v>
+        <v>200100</v>
       </c>
       <c r="C60" s="11">
         <v>2</v>
       </c>
       <c r="D60" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E60" s="11">
+        <v>200100038</v>
+      </c>
+      <c r="F60" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="E60" s="11">
-        <v>200101001</v>
-      </c>
-      <c r="F60" s="11" t="s">
-        <v>48</v>
-      </c>
       <c r="G60" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H60" s="14">
         <v>11</v>
@@ -4439,7 +4435,7 @@
         <v>0</v>
       </c>
       <c r="L60" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M60" s="14">
         <v>0</v>
@@ -4455,25 +4451,25 @@
     <row r="61" s="1" customFormat="1" spans="1:19">
       <c r="A61" s="1">
         <f t="shared" si="7"/>
-        <v>20010112</v>
+        <v>20010012</v>
       </c>
       <c r="B61" s="11">
-        <v>200101</v>
+        <v>200100</v>
       </c>
       <c r="C61" s="11">
         <v>2</v>
       </c>
       <c r="D61" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E61" s="11">
+        <v>200100038</v>
+      </c>
+      <c r="F61" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="E61" s="11">
-        <v>200101001</v>
-      </c>
-      <c r="F61" s="11" t="s">
-        <v>48</v>
-      </c>
       <c r="G61" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H61" s="14">
         <v>12</v>
@@ -4488,7 +4484,7 @@
         <v>0</v>
       </c>
       <c r="L61" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M61" s="14">
         <v>0</v>
@@ -4504,25 +4500,25 @@
     <row r="62" s="1" customFormat="1" spans="1:19">
       <c r="A62" s="1">
         <f t="shared" si="7"/>
-        <v>20030010</v>
+        <v>20010110</v>
       </c>
       <c r="B62" s="11">
-        <v>200300</v>
+        <v>200101</v>
       </c>
       <c r="C62" s="11">
         <v>2</v>
       </c>
       <c r="D62" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E62" s="11">
+        <v>200101001</v>
+      </c>
+      <c r="F62" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="E62" s="11">
-        <v>200300001</v>
-      </c>
-      <c r="F62" s="11" t="s">
-        <v>50</v>
-      </c>
       <c r="G62" s="14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H62" s="14">
         <v>10</v>
@@ -4537,7 +4533,7 @@
         <v>0</v>
       </c>
       <c r="L62" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M62" s="14">
         <v>0</v>
@@ -4552,26 +4548,26 @@
     </row>
     <row r="63" s="1" customFormat="1" spans="1:19">
       <c r="A63" s="1">
-        <f t="shared" ref="A63:A71" si="8">B63*100+H63</f>
-        <v>20030011</v>
+        <f t="shared" si="7"/>
+        <v>20010111</v>
       </c>
       <c r="B63" s="11">
-        <v>200300</v>
+        <v>200101</v>
       </c>
       <c r="C63" s="11">
         <v>2</v>
       </c>
       <c r="D63" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E63" s="11">
+        <v>200101001</v>
+      </c>
+      <c r="F63" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="E63" s="11">
-        <v>200300001</v>
-      </c>
-      <c r="F63" s="11" t="s">
-        <v>50</v>
-      </c>
       <c r="G63" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H63" s="14">
         <v>11</v>
@@ -4586,7 +4582,7 @@
         <v>0</v>
       </c>
       <c r="L63" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M63" s="14">
         <v>0</v>
@@ -4601,26 +4597,26 @@
     </row>
     <row r="64" s="1" customFormat="1" spans="1:19">
       <c r="A64" s="1">
-        <f t="shared" si="8"/>
-        <v>20030012</v>
+        <f t="shared" si="7"/>
+        <v>20010112</v>
       </c>
       <c r="B64" s="11">
-        <v>200300</v>
+        <v>200101</v>
       </c>
       <c r="C64" s="11">
         <v>2</v>
       </c>
       <c r="D64" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E64" s="11">
+        <v>200101001</v>
+      </c>
+      <c r="F64" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="E64" s="11">
-        <v>200300001</v>
-      </c>
-      <c r="F64" s="11" t="s">
-        <v>50</v>
-      </c>
       <c r="G64" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H64" s="14">
         <v>12</v>
@@ -4635,7 +4631,7 @@
         <v>0</v>
       </c>
       <c r="L64" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M64" s="14">
         <v>0</v>
@@ -4650,26 +4646,26 @@
     </row>
     <row r="65" s="1" customFormat="1" spans="1:19">
       <c r="A65" s="1">
-        <f t="shared" si="8"/>
-        <v>20040010</v>
+        <f t="shared" si="7"/>
+        <v>20030010</v>
       </c>
       <c r="B65" s="11">
-        <v>200400</v>
+        <v>200300</v>
       </c>
       <c r="C65" s="11">
         <v>2</v>
       </c>
-      <c r="D65" s="12" t="s">
+      <c r="D65" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E65" s="11">
+        <v>200300001</v>
+      </c>
+      <c r="F65" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E65" s="11">
-        <v>200400009</v>
-      </c>
-      <c r="F65" s="11" t="s">
-        <v>52</v>
-      </c>
       <c r="G65" s="14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H65" s="14">
         <v>10</v>
@@ -4684,7 +4680,7 @@
         <v>0</v>
       </c>
       <c r="L65" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M65" s="14">
         <v>0</v>
@@ -4699,26 +4695,26 @@
     </row>
     <row r="66" s="1" customFormat="1" spans="1:19">
       <c r="A66" s="1">
-        <f t="shared" si="8"/>
-        <v>20040011</v>
+        <f t="shared" ref="A66:A74" si="8">B66*100+H66</f>
+        <v>20030011</v>
       </c>
       <c r="B66" s="11">
-        <v>200400</v>
+        <v>200300</v>
       </c>
       <c r="C66" s="11">
         <v>2</v>
       </c>
-      <c r="D66" s="12" t="s">
+      <c r="D66" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E66" s="11">
+        <v>200300001</v>
+      </c>
+      <c r="F66" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E66" s="11">
-        <v>200400009</v>
-      </c>
-      <c r="F66" s="11" t="s">
-        <v>52</v>
-      </c>
       <c r="G66" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H66" s="14">
         <v>11</v>
@@ -4733,7 +4729,7 @@
         <v>0</v>
       </c>
       <c r="L66" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M66" s="14">
         <v>0</v>
@@ -4749,25 +4745,25 @@
     <row r="67" s="1" customFormat="1" spans="1:19">
       <c r="A67" s="1">
         <f t="shared" si="8"/>
-        <v>20040012</v>
+        <v>20030012</v>
       </c>
       <c r="B67" s="11">
-        <v>200400</v>
+        <v>200300</v>
       </c>
       <c r="C67" s="11">
         <v>2</v>
       </c>
-      <c r="D67" s="12" t="s">
+      <c r="D67" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E67" s="11">
+        <v>200300001</v>
+      </c>
+      <c r="F67" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E67" s="11">
-        <v>200400009</v>
-      </c>
-      <c r="F67" s="11" t="s">
-        <v>52</v>
-      </c>
       <c r="G67" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H67" s="14">
         <v>12</v>
@@ -4782,7 +4778,7 @@
         <v>0</v>
       </c>
       <c r="L67" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M67" s="14">
         <v>0</v>
@@ -4798,25 +4794,25 @@
     <row r="68" s="1" customFormat="1" spans="1:19">
       <c r="A68" s="1">
         <f t="shared" si="8"/>
-        <v>20050010</v>
+        <v>20040010</v>
       </c>
       <c r="B68" s="11">
-        <v>200500</v>
+        <v>200400</v>
       </c>
       <c r="C68" s="11">
         <v>2</v>
       </c>
-      <c r="D68" s="11" t="s">
+      <c r="D68" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E68" s="11">
+        <v>200400009</v>
+      </c>
+      <c r="F68" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="E68" s="11">
-        <v>200500025</v>
-      </c>
-      <c r="F68" s="11" t="s">
-        <v>54</v>
-      </c>
       <c r="G68" s="14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H68" s="14">
         <v>10</v>
@@ -4831,7 +4827,7 @@
         <v>0</v>
       </c>
       <c r="L68" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M68" s="14">
         <v>0</v>
@@ -4847,25 +4843,25 @@
     <row r="69" s="1" customFormat="1" spans="1:19">
       <c r="A69" s="1">
         <f t="shared" si="8"/>
-        <v>20050011</v>
+        <v>20040011</v>
       </c>
       <c r="B69" s="11">
-        <v>200500</v>
+        <v>200400</v>
       </c>
       <c r="C69" s="11">
         <v>2</v>
       </c>
-      <c r="D69" s="11" t="s">
+      <c r="D69" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E69" s="11">
+        <v>200400009</v>
+      </c>
+      <c r="F69" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="E69" s="11">
-        <v>200500025</v>
-      </c>
-      <c r="F69" s="11" t="s">
-        <v>54</v>
-      </c>
       <c r="G69" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H69" s="14">
         <v>11</v>
@@ -4880,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="L69" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M69" s="14">
         <v>0</v>
@@ -4896,25 +4892,25 @@
     <row r="70" s="1" customFormat="1" spans="1:19">
       <c r="A70" s="1">
         <f t="shared" si="8"/>
-        <v>20050012</v>
+        <v>20040012</v>
       </c>
       <c r="B70" s="11">
-        <v>200500</v>
+        <v>200400</v>
       </c>
       <c r="C70" s="11">
         <v>2</v>
       </c>
-      <c r="D70" s="11" t="s">
+      <c r="D70" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E70" s="11">
+        <v>200400009</v>
+      </c>
+      <c r="F70" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="E70" s="11">
-        <v>200500025</v>
-      </c>
-      <c r="F70" s="11" t="s">
-        <v>54</v>
-      </c>
       <c r="G70" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H70" s="14">
         <v>12</v>
@@ -4929,7 +4925,7 @@
         <v>0</v>
       </c>
       <c r="L70" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M70" s="14">
         <v>0</v>
@@ -4942,28 +4938,28 @@
       </c>
       <c r="S70" s="3"/>
     </row>
-    <row r="71" spans="1:15">
+    <row r="71" s="1" customFormat="1" spans="1:19">
       <c r="A71" s="1">
         <f t="shared" si="8"/>
-        <v>20060010</v>
+        <v>20050010</v>
       </c>
       <c r="B71" s="11">
-        <v>200600</v>
+        <v>200500</v>
       </c>
       <c r="C71" s="11">
         <v>2</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E71" s="11">
-        <v>200600001</v>
+        <v>200500025</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G71" s="14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H71" s="14">
         <v>10</v>
@@ -4978,7 +4974,7 @@
         <v>0</v>
       </c>
       <c r="L71" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M71" s="14">
         <v>0</v>
@@ -4989,29 +4985,30 @@
       <c r="O71" s="19">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="72" spans="1:15">
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" s="1" customFormat="1" spans="1:19">
       <c r="A72" s="1">
-        <f t="shared" ref="A72:A86" si="9">B72*100+H72</f>
-        <v>20060011</v>
+        <f t="shared" si="8"/>
+        <v>20050011</v>
       </c>
       <c r="B72" s="11">
-        <v>200600</v>
+        <v>200500</v>
       </c>
       <c r="C72" s="11">
         <v>2</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E72" s="11">
-        <v>200600001</v>
+        <v>200500025</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G72" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H72" s="14">
         <v>11</v>
@@ -5026,7 +5023,7 @@
         <v>0</v>
       </c>
       <c r="L72" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M72" s="14">
         <v>0</v>
@@ -5037,29 +5034,30 @@
       <c r="O72" s="19">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="73" spans="1:15">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" s="1" customFormat="1" spans="1:19">
       <c r="A73" s="1">
-        <f t="shared" si="9"/>
-        <v>20060012</v>
+        <f t="shared" si="8"/>
+        <v>20050012</v>
       </c>
       <c r="B73" s="11">
-        <v>200600</v>
+        <v>200500</v>
       </c>
       <c r="C73" s="11">
         <v>2</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E73" s="11">
-        <v>200600001</v>
+        <v>200500025</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G73" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H73" s="14">
         <v>12</v>
@@ -5074,7 +5072,7 @@
         <v>0</v>
       </c>
       <c r="L73" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M73" s="14">
         <v>0</v>
@@ -5085,29 +5083,30 @@
       <c r="O73" s="19">
         <v>1980000</v>
       </c>
+      <c r="S73" s="3"/>
     </row>
     <row r="74" spans="1:15">
       <c r="A74" s="1">
-        <f t="shared" si="9"/>
-        <v>20070010</v>
+        <f t="shared" si="8"/>
+        <v>20060010</v>
       </c>
       <c r="B74" s="11">
-        <v>200700</v>
+        <v>200600</v>
       </c>
       <c r="C74" s="11">
         <v>2</v>
       </c>
-      <c r="D74" s="10" t="s">
+      <c r="D74" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E74" s="11">
+        <v>200600001</v>
+      </c>
+      <c r="F74" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="E74" s="11">
-        <v>200700001</v>
-      </c>
-      <c r="F74" s="11" t="s">
-        <v>59</v>
-      </c>
       <c r="G74" s="14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H74" s="14">
         <v>10</v>
@@ -5122,7 +5121,7 @@
         <v>0</v>
       </c>
       <c r="L74" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M74" s="14">
         <v>0</v>
@@ -5136,27 +5135,26 @@
     </row>
     <row r="75" spans="1:15">
       <c r="A75" s="1">
-        <f t="shared" si="9"/>
-        <v>20070011</v>
+        <f t="shared" ref="A75:A89" si="9">B75*100+H75</f>
+        <v>20060011</v>
       </c>
       <c r="B75" s="11">
-        <v>200700</v>
+        <v>200600</v>
       </c>
       <c r="C75" s="11">
         <v>2</v>
       </c>
-      <c r="D75" s="10" t="str">
-        <f>D74</f>
-        <v>越南色碟</v>
+      <c r="D75" s="11" t="s">
+        <v>57</v>
       </c>
       <c r="E75" s="11">
-        <v>200700001</v>
+        <v>200600001</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G75" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H75" s="14">
         <v>11</v>
@@ -5171,7 +5169,7 @@
         <v>0</v>
       </c>
       <c r="L75" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M75" s="14">
         <v>0</v>
@@ -5186,26 +5184,25 @@
     <row r="76" spans="1:15">
       <c r="A76" s="1">
         <f t="shared" si="9"/>
-        <v>20070012</v>
+        <v>20060012</v>
       </c>
       <c r="B76" s="11">
-        <v>200700</v>
+        <v>200600</v>
       </c>
       <c r="C76" s="11">
         <v>2</v>
       </c>
-      <c r="D76" s="10" t="str">
-        <f>D75</f>
-        <v>越南色碟</v>
+      <c r="D76" s="11" t="s">
+        <v>57</v>
       </c>
       <c r="E76" s="11">
-        <v>200700001</v>
+        <v>200600001</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G76" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H76" s="14">
         <v>12</v>
@@ -5220,7 +5217,7 @@
         <v>0</v>
       </c>
       <c r="L76" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M76" s="14">
         <v>0</v>
@@ -5235,25 +5232,25 @@
     <row r="77" spans="1:15">
       <c r="A77" s="1">
         <f t="shared" si="9"/>
-        <v>20080010</v>
+        <v>20070010</v>
       </c>
       <c r="B77" s="11">
-        <v>200800</v>
+        <v>200700</v>
       </c>
       <c r="C77" s="11">
         <v>2</v>
       </c>
-      <c r="D77" s="11" t="s">
+      <c r="D77" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E77" s="11">
+        <v>200700001</v>
+      </c>
+      <c r="F77" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E77" s="11">
-        <v>200800001</v>
-      </c>
-      <c r="F77" s="11" t="s">
-        <v>61</v>
-      </c>
       <c r="G77" s="14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H77" s="14">
         <v>10</v>
@@ -5268,7 +5265,7 @@
         <v>0</v>
       </c>
       <c r="L77" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M77" s="14">
         <v>0</v>
@@ -5283,25 +5280,26 @@
     <row r="78" spans="1:15">
       <c r="A78" s="1">
         <f t="shared" si="9"/>
-        <v>20080011</v>
+        <v>20070011</v>
       </c>
       <c r="B78" s="11">
-        <v>200800</v>
+        <v>200700</v>
       </c>
       <c r="C78" s="11">
         <v>2</v>
       </c>
-      <c r="D78" s="11" t="s">
+      <c r="D78" s="10" t="str">
+        <f>D77</f>
+        <v>越南色碟</v>
+      </c>
+      <c r="E78" s="11">
+        <v>200700001</v>
+      </c>
+      <c r="F78" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E78" s="11">
-        <v>200800001</v>
-      </c>
-      <c r="F78" s="11" t="s">
-        <v>61</v>
-      </c>
       <c r="G78" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H78" s="14">
         <v>11</v>
@@ -5316,7 +5314,7 @@
         <v>0</v>
       </c>
       <c r="L78" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M78" s="14">
         <v>0</v>
@@ -5331,25 +5329,26 @@
     <row r="79" spans="1:15">
       <c r="A79" s="1">
         <f t="shared" si="9"/>
-        <v>20080012</v>
+        <v>20070012</v>
       </c>
       <c r="B79" s="11">
-        <v>200800</v>
+        <v>200700</v>
       </c>
       <c r="C79" s="11">
         <v>2</v>
       </c>
-      <c r="D79" s="11" t="s">
+      <c r="D79" s="10" t="str">
+        <f>D78</f>
+        <v>越南色碟</v>
+      </c>
+      <c r="E79" s="11">
+        <v>200700001</v>
+      </c>
+      <c r="F79" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E79" s="11">
-        <v>200800001</v>
-      </c>
-      <c r="F79" s="11" t="s">
-        <v>61</v>
-      </c>
       <c r="G79" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H79" s="14">
         <v>12</v>
@@ -5364,7 +5363,7 @@
         <v>0</v>
       </c>
       <c r="L79" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M79" s="14">
         <v>0</v>
@@ -5379,25 +5378,25 @@
     <row r="80" spans="1:15">
       <c r="A80" s="1">
         <f t="shared" si="9"/>
-        <v>20090010</v>
+        <v>20080010</v>
       </c>
       <c r="B80" s="11">
-        <v>200900</v>
+        <v>200800</v>
       </c>
       <c r="C80" s="11">
         <v>2</v>
       </c>
       <c r="D80" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E80" s="11">
+        <v>200800001</v>
+      </c>
+      <c r="F80" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="E80" s="11">
-        <v>200900001</v>
-      </c>
-      <c r="F80" s="11" t="s">
-        <v>63</v>
-      </c>
       <c r="G80" s="14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H80" s="14">
         <v>10</v>
@@ -5412,7 +5411,7 @@
         <v>0</v>
       </c>
       <c r="L80" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M80" s="14">
         <v>0</v>
@@ -5427,25 +5426,25 @@
     <row r="81" spans="1:15">
       <c r="A81" s="1">
         <f t="shared" si="9"/>
-        <v>20090011</v>
+        <v>20080011</v>
       </c>
       <c r="B81" s="11">
-        <v>200900</v>
+        <v>200800</v>
       </c>
       <c r="C81" s="11">
         <v>2</v>
       </c>
       <c r="D81" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E81" s="11">
+        <v>200800001</v>
+      </c>
+      <c r="F81" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="E81" s="11">
-        <v>200900001</v>
-      </c>
-      <c r="F81" s="11" t="s">
-        <v>63</v>
-      </c>
       <c r="G81" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H81" s="14">
         <v>11</v>
@@ -5460,7 +5459,7 @@
         <v>0</v>
       </c>
       <c r="L81" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M81" s="14">
         <v>0</v>
@@ -5475,25 +5474,25 @@
     <row r="82" spans="1:15">
       <c r="A82" s="1">
         <f t="shared" si="9"/>
-        <v>20090012</v>
+        <v>20080012</v>
       </c>
       <c r="B82" s="11">
-        <v>200900</v>
+        <v>200800</v>
       </c>
       <c r="C82" s="11">
         <v>2</v>
       </c>
       <c r="D82" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E82" s="11">
+        <v>200800001</v>
+      </c>
+      <c r="F82" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="E82" s="11">
-        <v>200900001</v>
-      </c>
-      <c r="F82" s="11" t="s">
-        <v>63</v>
-      </c>
       <c r="G82" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H82" s="14">
         <v>12</v>
@@ -5508,7 +5507,7 @@
         <v>0</v>
       </c>
       <c r="L82" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M82" s="14">
         <v>0</v>
@@ -5520,28 +5519,28 @@
         <v>1980000</v>
       </c>
     </row>
-    <row r="83" s="1" customFormat="1" spans="1:19">
+    <row r="83" spans="1:15">
       <c r="A83" s="1">
         <f t="shared" si="9"/>
-        <v>30020010</v>
-      </c>
-      <c r="B83" s="10">
-        <v>300200</v>
-      </c>
-      <c r="C83" s="10">
-        <v>3</v>
-      </c>
-      <c r="D83" s="10" t="s">
-        <v>69</v>
+        <v>20090010</v>
+      </c>
+      <c r="B83" s="11">
+        <v>200900</v>
+      </c>
+      <c r="C83" s="11">
+        <v>2</v>
+      </c>
+      <c r="D83" s="11" t="s">
+        <v>63</v>
       </c>
       <c r="E83" s="11">
-        <v>300200006</v>
+        <v>200900001</v>
       </c>
       <c r="F83" s="11" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G83" s="14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H83" s="14">
         <v>10</v>
@@ -5549,14 +5548,14 @@
       <c r="I83" s="14">
         <v>0</v>
       </c>
-      <c r="J83" s="1">
+      <c r="J83" s="14">
         <v>-1</v>
       </c>
       <c r="K83" s="1">
         <v>0</v>
       </c>
-      <c r="L83" s="21" t="s">
-        <v>76</v>
+      <c r="L83" s="14" t="s">
+        <v>74</v>
       </c>
       <c r="M83" s="14">
         <v>0</v>
@@ -5567,30 +5566,29 @@
       <c r="O83" s="19">
         <v>1980000</v>
       </c>
-      <c r="S83" s="3"/>
-    </row>
-    <row r="84" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="84" spans="1:15">
       <c r="A84" s="1">
         <f t="shared" si="9"/>
-        <v>30020011</v>
-      </c>
-      <c r="B84" s="10">
-        <v>300200</v>
-      </c>
-      <c r="C84" s="10">
-        <v>3</v>
-      </c>
-      <c r="D84" s="10" t="s">
-        <v>69</v>
+        <v>20090011</v>
+      </c>
+      <c r="B84" s="11">
+        <v>200900</v>
+      </c>
+      <c r="C84" s="11">
+        <v>2</v>
+      </c>
+      <c r="D84" s="11" t="s">
+        <v>63</v>
       </c>
       <c r="E84" s="11">
-        <v>300200006</v>
+        <v>200900001</v>
       </c>
       <c r="F84" s="11" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G84" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H84" s="14">
         <v>11</v>
@@ -5598,14 +5596,14 @@
       <c r="I84" s="14">
         <v>0</v>
       </c>
-      <c r="J84" s="1">
+      <c r="J84" s="14">
         <v>-1</v>
       </c>
       <c r="K84" s="1">
         <v>0</v>
       </c>
-      <c r="L84" s="21" t="s">
-        <v>76</v>
+      <c r="L84" s="14" t="s">
+        <v>74</v>
       </c>
       <c r="M84" s="14">
         <v>0</v>
@@ -5616,30 +5614,29 @@
       <c r="O84" s="19">
         <v>1980000</v>
       </c>
-      <c r="S84" s="3"/>
-    </row>
-    <row r="85" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="85" spans="1:15">
       <c r="A85" s="1">
         <f t="shared" si="9"/>
-        <v>30020012</v>
-      </c>
-      <c r="B85" s="10">
-        <v>300200</v>
-      </c>
-      <c r="C85" s="10">
-        <v>3</v>
-      </c>
-      <c r="D85" s="10" t="s">
-        <v>69</v>
+        <v>20090012</v>
+      </c>
+      <c r="B85" s="11">
+        <v>200900</v>
+      </c>
+      <c r="C85" s="11">
+        <v>2</v>
+      </c>
+      <c r="D85" s="11" t="s">
+        <v>63</v>
       </c>
       <c r="E85" s="11">
-        <v>300200006</v>
+        <v>200900001</v>
       </c>
       <c r="F85" s="11" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G85" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H85" s="14">
         <v>12</v>
@@ -5647,14 +5644,14 @@
       <c r="I85" s="14">
         <v>0</v>
       </c>
-      <c r="J85" s="1">
+      <c r="J85" s="14">
         <v>-1</v>
       </c>
       <c r="K85" s="1">
         <v>0</v>
       </c>
-      <c r="L85" s="21" t="s">
-        <v>76</v>
+      <c r="L85" s="14" t="s">
+        <v>74</v>
       </c>
       <c r="M85" s="14">
         <v>0</v>
@@ -5665,7 +5662,153 @@
       <c r="O85" s="19">
         <v>1980000</v>
       </c>
-      <c r="S85" s="3"/>
+    </row>
+    <row r="86" s="1" customFormat="1" spans="1:19">
+      <c r="A86" s="1">
+        <f t="shared" si="9"/>
+        <v>30020010</v>
+      </c>
+      <c r="B86" s="10">
+        <v>300200</v>
+      </c>
+      <c r="C86" s="10">
+        <v>3</v>
+      </c>
+      <c r="D86" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E86" s="11">
+        <v>300200006</v>
+      </c>
+      <c r="F86" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="G86" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="H86" s="14">
+        <v>10</v>
+      </c>
+      <c r="I86" s="14">
+        <v>0</v>
+      </c>
+      <c r="J86" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K86" s="1">
+        <v>0</v>
+      </c>
+      <c r="L86" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="M86" s="14">
+        <v>0</v>
+      </c>
+      <c r="N86">
+        <v>200</v>
+      </c>
+      <c r="O86" s="19">
+        <v>1980000</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" s="1" customFormat="1" spans="1:19">
+      <c r="A87" s="1">
+        <f t="shared" si="9"/>
+        <v>30020011</v>
+      </c>
+      <c r="B87" s="10">
+        <v>300200</v>
+      </c>
+      <c r="C87" s="10">
+        <v>3</v>
+      </c>
+      <c r="D87" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E87" s="11">
+        <v>300200006</v>
+      </c>
+      <c r="F87" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="G87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="H87" s="14">
+        <v>11</v>
+      </c>
+      <c r="I87" s="14">
+        <v>0</v>
+      </c>
+      <c r="J87" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K87" s="1">
+        <v>0</v>
+      </c>
+      <c r="L87" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="M87" s="14">
+        <v>0</v>
+      </c>
+      <c r="N87">
+        <v>5000</v>
+      </c>
+      <c r="O87" s="19">
+        <v>1980000</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" s="1" customFormat="1" spans="1:19">
+      <c r="A88" s="1">
+        <f t="shared" si="9"/>
+        <v>30020012</v>
+      </c>
+      <c r="B88" s="10">
+        <v>300200</v>
+      </c>
+      <c r="C88" s="10">
+        <v>3</v>
+      </c>
+      <c r="D88" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E88" s="11">
+        <v>300200006</v>
+      </c>
+      <c r="F88" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="G88" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H88" s="14">
+        <v>12</v>
+      </c>
+      <c r="I88" s="14">
+        <v>0</v>
+      </c>
+      <c r="J88" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K88" s="1">
+        <v>0</v>
+      </c>
+      <c r="L88" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="M88" s="14">
+        <v>0</v>
+      </c>
+      <c r="N88">
+        <v>100000</v>
+      </c>
+      <c r="O88" s="19">
+        <v>1980000</v>
+      </c>
+      <c r="S88" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -418,6 +418,17 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
@@ -432,17 +443,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -602,12 +602,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -622,12 +622,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799340800195319"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -635,6 +629,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799340800195319"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1139,42 +1139,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="56" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="56" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1182,6 +1173,15 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -1571,13 +1571,13 @@
       <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="J1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="K1" s="5" t="s">
         <v>8</v>
       </c>
       <c r="L1" s="1" t="s">
@@ -1589,38 +1589,38 @@
       <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="O1" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:15">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="6"/>
-      <c r="E2" s="7" t="s">
+      <c r="D2" s="8"/>
+      <c r="E2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="9" t="s">
+      <c r="G2" s="8"/>
+      <c r="H2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="K2" s="11" t="s">
         <v>13</v>
       </c>
       <c r="L2" s="1" t="s">
@@ -1629,7 +1629,7 @@
       <c r="M2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="N2" s="11" t="s">
         <v>13</v>
       </c>
       <c r="O2" s="2" t="s">
@@ -1652,16 +1652,16 @@
       <c r="F3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="11" t="s">
         <v>24</v>
       </c>
       <c r="L3" s="1" t="s">
@@ -1670,14 +1670,14 @@
       <c r="M3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="N3" s="11" t="s">
         <v>27</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="14.25" spans="6:15">
+    <row r="4" ht="14.25" spans="1:15">
       <c r="F4" s="1" t="s">
         <v>29</v>
       </c>
@@ -1688,19 +1688,19 @@
         <f t="shared" ref="A5:A10" si="0">B5*10+H5</f>
         <v>1001001</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="12">
         <v>100100</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="12">
         <v>1</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="13">
         <v>100100026</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="13" t="s">
         <v>31</v>
       </c>
       <c r="G5" s="1" t="s">
@@ -1727,7 +1727,7 @@
       <c r="N5">
         <v>5000</v>
       </c>
-      <c r="O5" s="18">
+      <c r="O5" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -1736,20 +1736,20 @@
         <f t="shared" si="0"/>
         <v>1001002</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="12">
         <v>100100</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="12">
         <v>1</v>
       </c>
-      <c r="D6" s="10" t="str">
+      <c r="D6" s="12" t="str">
         <f t="shared" ref="D6:D10" si="1">D5</f>
         <v>金礦大亨</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="13">
         <v>100100026</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="13" t="s">
         <v>31</v>
       </c>
       <c r="G6" s="1" t="s">
@@ -1776,7 +1776,7 @@
       <c r="N6">
         <v>500000</v>
       </c>
-      <c r="O6" s="18">
+      <c r="O6" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -1785,20 +1785,20 @@
         <f t="shared" si="0"/>
         <v>1001003</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="12">
         <v>100100</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="12">
         <v>1</v>
       </c>
-      <c r="D7" s="10" t="str">
+      <c r="D7" s="12" t="str">
         <f t="shared" si="1"/>
         <v>金礦大亨</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="13">
         <v>100100026</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="13" t="s">
         <v>31</v>
       </c>
       <c r="G7" s="1" t="s">
@@ -1825,7 +1825,7 @@
       <c r="N7">
         <v>50000000</v>
       </c>
-      <c r="O7" s="18">
+      <c r="O7" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -1834,19 +1834,19 @@
         <f t="shared" si="0"/>
         <v>1003001</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="12">
         <v>100300</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="12">
         <v>1</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="13">
         <v>100300001</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="13" t="s">
         <v>38</v>
       </c>
       <c r="G8" s="1" t="s">
@@ -1873,7 +1873,7 @@
       <c r="N8">
         <v>5000</v>
       </c>
-      <c r="O8" s="18">
+      <c r="O8" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -1882,20 +1882,20 @@
         <f t="shared" si="0"/>
         <v>1003002</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="12">
         <v>100300</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="12">
         <v>1</v>
       </c>
-      <c r="D9" s="10" t="str">
+      <c r="D9" s="12" t="str">
         <f t="shared" si="1"/>
         <v>超级明星</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="13">
         <v>100300001</v>
       </c>
-      <c r="F9" s="11" t="str">
+      <c r="F9" s="13" t="str">
         <f>F8</f>
         <v>SuperStar</v>
       </c>
@@ -1923,7 +1923,7 @@
       <c r="N9">
         <v>500000</v>
       </c>
-      <c r="O9" s="18">
+      <c r="O9" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -1932,20 +1932,20 @@
         <f t="shared" si="0"/>
         <v>1003003</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="12">
         <v>100300</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="12">
         <v>1</v>
       </c>
-      <c r="D10" s="10" t="str">
+      <c r="D10" s="12" t="str">
         <f t="shared" si="1"/>
         <v>超级明星</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="13">
         <v>100300001</v>
       </c>
-      <c r="F10" s="11" t="str">
+      <c r="F10" s="13" t="str">
         <f>F9</f>
         <v>SuperStar</v>
       </c>
@@ -1973,7 +1973,7 @@
       <c r="N10">
         <v>50000000</v>
       </c>
-      <c r="O10" s="18">
+      <c r="O10" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -1982,19 +1982,19 @@
         <f t="shared" ref="A11:A22" si="2">B11*10+H11</f>
         <v>1007001</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="12">
         <v>100700</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="12">
         <v>1</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="13">
         <v>100700001</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="13" t="s">
         <v>40</v>
       </c>
       <c r="G11" s="1" t="s">
@@ -2021,7 +2021,7 @@
       <c r="N11">
         <v>5000</v>
       </c>
-      <c r="O11" s="18">
+      <c r="O11" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -2030,20 +2030,20 @@
         <f t="shared" si="2"/>
         <v>1007002</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="12">
         <v>100700</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="12">
         <v>1</v>
       </c>
-      <c r="D12" s="10" t="str">
+      <c r="D12" s="12" t="str">
         <f>D11</f>
         <v>麻将胡了</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="13">
         <v>100700001</v>
       </c>
-      <c r="F12" s="11" t="str">
+      <c r="F12" s="13" t="str">
         <f>F11</f>
         <v>MahjongWays</v>
       </c>
@@ -2071,7 +2071,7 @@
       <c r="N12">
         <v>500000</v>
       </c>
-      <c r="O12" s="18">
+      <c r="O12" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -2080,20 +2080,20 @@
         <f t="shared" si="2"/>
         <v>1007003</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="12">
         <v>100700</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="12">
         <v>1</v>
       </c>
-      <c r="D13" s="10" t="str">
+      <c r="D13" s="12" t="str">
         <f>D12</f>
         <v>麻将胡了</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="13">
         <v>100700001</v>
       </c>
-      <c r="F13" s="11" t="str">
+      <c r="F13" s="13" t="str">
         <f>F12</f>
         <v>MahjongWays</v>
       </c>
@@ -2121,7 +2121,7 @@
       <c r="N13">
         <v>50000000</v>
       </c>
-      <c r="O13" s="18">
+      <c r="O13" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -2130,19 +2130,19 @@
         <f t="shared" si="2"/>
         <v>1012001</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="12">
         <v>101200</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="12">
         <v>1</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="13">
         <v>101200001</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="13" t="s">
         <v>42</v>
       </c>
       <c r="G14" s="1" t="s">
@@ -2169,7 +2169,7 @@
       <c r="N14">
         <v>5000</v>
       </c>
-      <c r="O14" s="18">
+      <c r="O14" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -2178,20 +2178,20 @@
         <f t="shared" si="2"/>
         <v>1012002</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="12">
         <v>101200</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="12">
         <v>1</v>
       </c>
-      <c r="D15" s="10" t="str">
+      <c r="D15" s="12" t="str">
         <f>D14</f>
         <v>财神</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="13">
         <v>101200001</v>
       </c>
-      <c r="F15" s="11" t="str">
+      <c r="F15" s="13" t="str">
         <f>F14</f>
         <v>Godofwealth</v>
       </c>
@@ -2219,7 +2219,7 @@
       <c r="N15">
         <v>500000</v>
       </c>
-      <c r="O15" s="18">
+      <c r="O15" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -2228,20 +2228,20 @@
         <f t="shared" si="2"/>
         <v>1012003</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="12">
         <v>101200</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="12">
         <v>1</v>
       </c>
-      <c r="D16" s="10" t="str">
+      <c r="D16" s="12" t="str">
         <f t="shared" ref="D16:D22" si="3">D15</f>
         <v>财神</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="13">
         <v>101200001</v>
       </c>
-      <c r="F16" s="11" t="str">
+      <c r="F16" s="13" t="str">
         <f>F15</f>
         <v>Godofwealth</v>
       </c>
@@ -2269,28 +2269,28 @@
       <c r="N16">
         <v>50000000</v>
       </c>
-      <c r="O16" s="18">
+      <c r="O16" s="15">
         <v>1990000</v>
       </c>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:19">
       <c r="A17" s="1">
         <f t="shared" si="2"/>
         <v>1014001</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="12">
         <v>101400</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="12">
         <v>1</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="13">
         <v>101400001</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="13" t="s">
         <v>44</v>
       </c>
       <c r="G17" s="1" t="s">
@@ -2317,29 +2317,29 @@
       <c r="N17">
         <v>5000</v>
       </c>
-      <c r="O17" s="18">
+      <c r="O17" s="15">
         <v>1990000</v>
       </c>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:19">
       <c r="A18" s="1">
         <f t="shared" si="2"/>
         <v>1014002</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="12">
         <v>101400</v>
       </c>
-      <c r="C18" s="10">
+      <c r="C18" s="12">
         <v>1</v>
       </c>
-      <c r="D18" s="10" t="str">
+      <c r="D18" s="12" t="str">
         <f t="shared" si="3"/>
         <v>埃及艳后</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="13">
         <v>101400001</v>
       </c>
-      <c r="F18" s="11" t="str">
+      <c r="F18" s="13" t="str">
         <f>F17</f>
         <v>Cleopatra</v>
       </c>
@@ -2367,29 +2367,29 @@
       <c r="N18">
         <v>500000</v>
       </c>
-      <c r="O18" s="18">
+      <c r="O18" s="15">
         <v>1990000</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:19">
       <c r="A19" s="1">
         <f t="shared" si="2"/>
         <v>1014003</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="12">
         <v>101400</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="12">
         <v>1</v>
       </c>
-      <c r="D19" s="10" t="str">
+      <c r="D19" s="12" t="str">
         <f t="shared" si="3"/>
         <v>埃及艳后</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="13">
         <v>101400001</v>
       </c>
-      <c r="F19" s="11" t="str">
+      <c r="F19" s="13" t="str">
         <f>F18</f>
         <v>Cleopatra</v>
       </c>
@@ -2417,28 +2417,28 @@
       <c r="N19">
         <v>50000000</v>
       </c>
-      <c r="O19" s="18">
+      <c r="O19" s="15">
         <v>1990000</v>
       </c>
     </row>
-    <row r="20" spans="1:15">
+    <row r="20" spans="1:19">
       <c r="A20" s="1">
         <f t="shared" si="2"/>
         <v>1024001</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="12">
         <v>102400</v>
       </c>
-      <c r="C20" s="10">
+      <c r="C20" s="12">
         <v>1</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E20" s="13">
         <v>102400026</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="F20" s="13" t="s">
         <v>31</v>
       </c>
       <c r="G20" s="1" t="s">
@@ -2465,29 +2465,29 @@
       <c r="N20">
         <v>5000</v>
       </c>
-      <c r="O20" s="18">
+      <c r="O20" s="15">
         <v>1990000</v>
       </c>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" spans="1:19">
       <c r="A21" s="1">
         <f t="shared" si="2"/>
         <v>1024002</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="12">
         <v>102400</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="12">
         <v>1</v>
       </c>
-      <c r="D21" s="10" t="str">
+      <c r="D21" s="12" t="str">
         <f t="shared" si="3"/>
         <v>财富银行</v>
       </c>
-      <c r="E21" s="11">
+      <c r="E21" s="13">
         <v>102400026</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="F21" s="13" t="s">
         <v>31</v>
       </c>
       <c r="G21" s="1" t="s">
@@ -2514,29 +2514,29 @@
       <c r="N21">
         <v>500000</v>
       </c>
-      <c r="O21" s="18">
+      <c r="O21" s="15">
         <v>1990000</v>
       </c>
     </row>
-    <row r="22" spans="1:15">
+    <row r="22" spans="1:19">
       <c r="A22" s="1">
         <f t="shared" si="2"/>
         <v>1024003</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="12">
         <v>102400</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C22" s="12">
         <v>1</v>
       </c>
-      <c r="D22" s="10" t="str">
+      <c r="D22" s="12" t="str">
         <f t="shared" si="3"/>
         <v>财富银行</v>
       </c>
-      <c r="E22" s="11">
+      <c r="E22" s="13">
         <v>102400026</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" s="13" t="s">
         <v>31</v>
       </c>
       <c r="G22" s="1" t="s">
@@ -2563,28 +2563,28 @@
       <c r="N22">
         <v>50000000</v>
       </c>
-      <c r="O22" s="18">
+      <c r="O22" s="15">
         <v>1990000</v>
       </c>
     </row>
-    <row r="23" spans="1:15">
+    <row r="23" spans="1:19">
       <c r="A23" s="1">
         <f t="shared" ref="A23:A69" si="4">B23*10+H23</f>
         <v>2001001</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="12">
         <v>200100</v>
       </c>
-      <c r="C23" s="10">
-        <v>2</v>
-      </c>
-      <c r="D23" s="10" t="s">
+      <c r="C23" s="12">
+        <v>2</v>
+      </c>
+      <c r="D23" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E23" s="11">
+      <c r="E23" s="13">
         <v>200100038</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F23" s="13" t="s">
         <v>47</v>
       </c>
       <c r="G23" s="1" t="s">
@@ -2611,29 +2611,29 @@
       <c r="N23">
         <v>5000</v>
       </c>
-      <c r="O23" s="18">
+      <c r="O23" s="15">
         <v>1990000</v>
       </c>
     </row>
-    <row r="24" spans="1:15">
+    <row r="24" spans="1:19">
       <c r="A24" s="1">
         <f t="shared" si="4"/>
         <v>2001002</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="12">
         <v>200100</v>
       </c>
-      <c r="C24" s="10">
-        <v>2</v>
-      </c>
-      <c r="D24" s="10" t="str">
+      <c r="C24" s="12">
+        <v>2</v>
+      </c>
+      <c r="D24" s="12" t="str">
         <f>D23</f>
         <v>紅黑大戰</v>
       </c>
-      <c r="E24" s="11">
+      <c r="E24" s="13">
         <v>200100038</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="13" t="s">
         <v>47</v>
       </c>
       <c r="G24" s="1" t="s">
@@ -2660,29 +2660,29 @@
       <c r="N24">
         <v>500000</v>
       </c>
-      <c r="O24" s="18">
+      <c r="O24" s="15">
         <v>1990000</v>
       </c>
     </row>
-    <row r="25" spans="1:17">
+    <row r="25" spans="1:19">
       <c r="A25" s="1">
         <f t="shared" si="4"/>
         <v>2001003</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="12">
         <v>200100</v>
       </c>
-      <c r="C25" s="10">
-        <v>2</v>
-      </c>
-      <c r="D25" s="10" t="str">
+      <c r="C25" s="12">
+        <v>2</v>
+      </c>
+      <c r="D25" s="12" t="str">
         <f>D24</f>
         <v>紅黑大戰</v>
       </c>
-      <c r="E25" s="11">
+      <c r="E25" s="13">
         <v>200100038</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F25" s="13" t="s">
         <v>47</v>
       </c>
       <c r="G25" s="1" t="s">
@@ -2709,29 +2709,29 @@
       <c r="N25">
         <v>50000000</v>
       </c>
-      <c r="O25" s="18">
+      <c r="O25" s="15">
         <v>1990000</v>
       </c>
       <c r="Q25"/>
     </row>
-    <row r="26" spans="1:15">
+    <row r="26" spans="1:19">
       <c r="A26" s="1">
         <f t="shared" si="4"/>
         <v>2001011</v>
       </c>
-      <c r="B26" s="10">
+      <c r="B26" s="12">
         <v>200101</v>
       </c>
-      <c r="C26" s="10">
-        <v>2</v>
-      </c>
-      <c r="D26" s="10" t="s">
+      <c r="C26" s="12">
+        <v>2</v>
+      </c>
+      <c r="D26" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="E26" s="11">
+      <c r="E26" s="13">
         <v>200101001</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="F26" s="13" t="s">
         <v>49</v>
       </c>
       <c r="G26" s="1" t="s">
@@ -2758,7 +2758,7 @@
       <c r="N26">
         <v>5000</v>
       </c>
-      <c r="O26" s="18">
+      <c r="O26" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -2767,20 +2767,20 @@
         <f t="shared" si="4"/>
         <v>2001012</v>
       </c>
-      <c r="B27" s="10">
+      <c r="B27" s="12">
         <v>200101</v>
       </c>
-      <c r="C27" s="10">
-        <v>2</v>
-      </c>
-      <c r="D27" s="10" t="str">
+      <c r="C27" s="12">
+        <v>2</v>
+      </c>
+      <c r="D27" s="12" t="str">
         <f t="shared" ref="D27:D31" si="5">D26</f>
         <v>龍虎鬥</v>
       </c>
-      <c r="E27" s="11">
+      <c r="E27" s="13">
         <v>200101001</v>
       </c>
-      <c r="F27" s="11" t="s">
+      <c r="F27" s="13" t="s">
         <v>49</v>
       </c>
       <c r="G27" s="1" t="s">
@@ -2807,7 +2807,7 @@
       <c r="N27">
         <v>500000</v>
       </c>
-      <c r="O27" s="18">
+      <c r="O27" s="15">
         <v>1990000</v>
       </c>
       <c r="S27" s="3"/>
@@ -2817,20 +2817,20 @@
         <f t="shared" si="4"/>
         <v>2001013</v>
       </c>
-      <c r="B28" s="10">
+      <c r="B28" s="12">
         <v>200101</v>
       </c>
-      <c r="C28" s="10">
-        <v>2</v>
-      </c>
-      <c r="D28" s="10" t="str">
+      <c r="C28" s="12">
+        <v>2</v>
+      </c>
+      <c r="D28" s="12" t="str">
         <f t="shared" si="5"/>
         <v>龍虎鬥</v>
       </c>
-      <c r="E28" s="11">
+      <c r="E28" s="13">
         <v>200101001</v>
       </c>
-      <c r="F28" s="11" t="s">
+      <c r="F28" s="13" t="s">
         <v>49</v>
       </c>
       <c r="G28" s="1" t="s">
@@ -2857,29 +2857,29 @@
       <c r="N28">
         <v>50000000</v>
       </c>
-      <c r="O28" s="18">
+      <c r="O28" s="15">
         <v>1990000</v>
       </c>
       <c r="S28" s="3"/>
     </row>
-    <row r="29" spans="1:15">
+    <row r="29" spans="1:19">
       <c r="A29" s="1">
         <f t="shared" si="4"/>
         <v>2003001</v>
       </c>
-      <c r="B29" s="10">
+      <c r="B29" s="12">
         <v>200300</v>
       </c>
-      <c r="C29" s="10">
-        <v>2</v>
-      </c>
-      <c r="D29" s="10" t="s">
+      <c r="C29" s="12">
+        <v>2</v>
+      </c>
+      <c r="D29" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="E29" s="11">
+      <c r="E29" s="13">
         <v>200300001</v>
       </c>
-      <c r="F29" s="11" t="s">
+      <c r="F29" s="13" t="s">
         <v>51</v>
       </c>
       <c r="G29" s="1" t="s">
@@ -2906,7 +2906,7 @@
       <c r="N29">
         <v>5000</v>
       </c>
-      <c r="O29" s="18">
+      <c r="O29" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -2915,20 +2915,20 @@
         <f t="shared" si="4"/>
         <v>2003002</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B30" s="12">
         <v>200300</v>
       </c>
-      <c r="C30" s="10">
-        <v>2</v>
-      </c>
-      <c r="D30" s="10" t="str">
+      <c r="C30" s="12">
+        <v>2</v>
+      </c>
+      <c r="D30" s="12" t="str">
         <f t="shared" si="5"/>
         <v>飛禽走獸</v>
       </c>
-      <c r="E30" s="11">
+      <c r="E30" s="13">
         <v>200300001</v>
       </c>
-      <c r="F30" s="11" t="s">
+      <c r="F30" s="13" t="s">
         <v>51</v>
       </c>
       <c r="G30" s="1" t="s">
@@ -2955,11 +2955,11 @@
       <c r="N30">
         <v>500000</v>
       </c>
-      <c r="O30" s="18">
+      <c r="O30" s="15">
         <v>1990000</v>
       </c>
       <c r="Q30" s="3"/>
-      <c r="R30" s="10"/>
+      <c r="R30" s="12"/>
       <c r="S30" s="3"/>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:19">
@@ -2967,20 +2967,20 @@
         <f t="shared" si="4"/>
         <v>2003003</v>
       </c>
-      <c r="B31" s="10">
+      <c r="B31" s="12">
         <v>200300</v>
       </c>
-      <c r="C31" s="10">
-        <v>2</v>
-      </c>
-      <c r="D31" s="10" t="str">
+      <c r="C31" s="12">
+        <v>2</v>
+      </c>
+      <c r="D31" s="12" t="str">
         <f t="shared" si="5"/>
         <v>飛禽走獸</v>
       </c>
-      <c r="E31" s="11">
+      <c r="E31" s="13">
         <v>200300001</v>
       </c>
-      <c r="F31" s="11" t="s">
+      <c r="F31" s="13" t="s">
         <v>51</v>
       </c>
       <c r="G31" s="1" t="s">
@@ -3007,31 +3007,31 @@
       <c r="N31">
         <v>50000000</v>
       </c>
-      <c r="O31" s="18">
+      <c r="O31" s="15">
         <v>1990000</v>
       </c>
       <c r="Q31" s="3"/>
-      <c r="R31" s="12"/>
-      <c r="S31" s="12"/>
+      <c r="R31" s="16"/>
+      <c r="S31" s="16"/>
     </row>
     <row r="32" spans="1:19">
       <c r="A32" s="1">
         <f t="shared" si="4"/>
         <v>2004001</v>
       </c>
-      <c r="B32" s="10">
+      <c r="B32" s="12">
         <v>200400</v>
       </c>
-      <c r="C32" s="10">
-        <v>2</v>
-      </c>
-      <c r="D32" s="12" t="s">
+      <c r="C32" s="12">
+        <v>2</v>
+      </c>
+      <c r="D32" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="E32" s="11">
+      <c r="E32" s="13">
         <v>200400009</v>
       </c>
-      <c r="F32" s="11" t="s">
+      <c r="F32" s="13" t="s">
         <v>53</v>
       </c>
       <c r="G32" s="1" t="s">
@@ -3058,31 +3058,31 @@
       <c r="N32">
         <v>5000</v>
       </c>
-      <c r="O32" s="18">
+      <c r="O32" s="15">
         <v>1990000</v>
       </c>
       <c r="Q32" s="3"/>
-      <c r="R32" s="12"/>
-      <c r="S32" s="12"/>
+      <c r="R32" s="16"/>
+      <c r="S32" s="16"/>
     </row>
     <row r="33" s="1" customFormat="1" spans="1:19">
       <c r="A33" s="1">
         <f t="shared" si="4"/>
         <v>2004002</v>
       </c>
-      <c r="B33" s="10">
+      <c r="B33" s="12">
         <v>200400</v>
       </c>
-      <c r="C33" s="10">
-        <v>2</v>
-      </c>
-      <c r="D33" s="12" t="s">
+      <c r="C33" s="12">
+        <v>2</v>
+      </c>
+      <c r="D33" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="E33" s="11">
+      <c r="E33" s="13">
         <v>200400009</v>
       </c>
-      <c r="F33" s="11" t="s">
+      <c r="F33" s="13" t="s">
         <v>53</v>
       </c>
       <c r="G33" s="1" t="s">
@@ -3109,31 +3109,31 @@
       <c r="N33">
         <v>500000</v>
       </c>
-      <c r="O33" s="18">
+      <c r="O33" s="15">
         <v>1990000</v>
       </c>
       <c r="Q33" s="3"/>
-      <c r="R33" s="12"/>
-      <c r="S33" s="12"/>
+      <c r="R33" s="16"/>
+      <c r="S33" s="16"/>
     </row>
     <row r="34" s="1" customFormat="1" spans="1:19">
       <c r="A34" s="1">
         <f t="shared" si="4"/>
         <v>2004003</v>
       </c>
-      <c r="B34" s="10">
+      <c r="B34" s="12">
         <v>200400</v>
       </c>
-      <c r="C34" s="10">
-        <v>2</v>
-      </c>
-      <c r="D34" s="12" t="s">
+      <c r="C34" s="12">
+        <v>2</v>
+      </c>
+      <c r="D34" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="E34" s="11">
+      <c r="E34" s="13">
         <v>200400009</v>
       </c>
-      <c r="F34" s="11" t="s">
+      <c r="F34" s="13" t="s">
         <v>53</v>
       </c>
       <c r="G34" s="1" t="s">
@@ -3160,31 +3160,31 @@
       <c r="N34">
         <v>50000000</v>
       </c>
-      <c r="O34" s="18">
+      <c r="O34" s="15">
         <v>1990000</v>
       </c>
       <c r="Q34" s="3"/>
-      <c r="R34" s="12"/>
-      <c r="S34" s="12"/>
+      <c r="R34" s="16"/>
+      <c r="S34" s="16"/>
     </row>
     <row r="35" spans="1:19">
       <c r="A35" s="1">
         <f t="shared" si="4"/>
         <v>2005001</v>
       </c>
-      <c r="B35" s="10">
+      <c r="B35" s="12">
         <v>200500</v>
       </c>
-      <c r="C35" s="10">
-        <v>2</v>
-      </c>
-      <c r="D35" s="10" t="s">
+      <c r="C35" s="12">
+        <v>2</v>
+      </c>
+      <c r="D35" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="E35" s="11">
+      <c r="E35" s="13">
         <v>200500025</v>
       </c>
-      <c r="F35" s="11" t="s">
+      <c r="F35" s="13" t="s">
         <v>55</v>
       </c>
       <c r="G35" s="1" t="s">
@@ -3211,31 +3211,31 @@
       <c r="N35">
         <v>5000</v>
       </c>
-      <c r="O35" s="18">
+      <c r="O35" s="15">
         <v>1990000</v>
       </c>
       <c r="Q35" s="3"/>
-      <c r="R35" s="12"/>
-      <c r="S35" s="12"/>
+      <c r="R35" s="16"/>
+      <c r="S35" s="16"/>
     </row>
     <row r="36" spans="1:19">
       <c r="A36" s="1">
         <f t="shared" si="4"/>
         <v>2005002</v>
       </c>
-      <c r="B36" s="10">
+      <c r="B36" s="12">
         <v>200500</v>
       </c>
-      <c r="C36" s="10">
-        <v>2</v>
-      </c>
-      <c r="D36" s="10" t="s">
+      <c r="C36" s="12">
+        <v>2</v>
+      </c>
+      <c r="D36" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="E36" s="11">
+      <c r="E36" s="13">
         <v>200500025</v>
       </c>
-      <c r="F36" s="11" t="s">
+      <c r="F36" s="13" t="s">
         <v>55</v>
       </c>
       <c r="G36" s="1" t="s">
@@ -3262,31 +3262,31 @@
       <c r="N36">
         <v>500000</v>
       </c>
-      <c r="O36" s="18">
+      <c r="O36" s="15">
         <v>1990000</v>
       </c>
       <c r="Q36" s="3"/>
-      <c r="R36" s="12"/>
-      <c r="S36" s="12"/>
+      <c r="R36" s="16"/>
+      <c r="S36" s="16"/>
     </row>
     <row r="37" spans="1:19">
       <c r="A37" s="1">
         <f t="shared" si="4"/>
         <v>2005003</v>
       </c>
-      <c r="B37" s="10">
+      <c r="B37" s="12">
         <v>200500</v>
       </c>
-      <c r="C37" s="10">
-        <v>2</v>
-      </c>
-      <c r="D37" s="10" t="s">
+      <c r="C37" s="12">
+        <v>2</v>
+      </c>
+      <c r="D37" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="E37" s="11">
+      <c r="E37" s="13">
         <v>200500025</v>
       </c>
-      <c r="F37" s="11" t="s">
+      <c r="F37" s="13" t="s">
         <v>55</v>
       </c>
       <c r="G37" s="1" t="s">
@@ -3313,31 +3313,31 @@
       <c r="N37">
         <v>50000000</v>
       </c>
-      <c r="O37" s="18">
+      <c r="O37" s="15">
         <v>1990000</v>
       </c>
       <c r="Q37" s="3"/>
-      <c r="R37" s="12"/>
-      <c r="S37" s="12"/>
+      <c r="R37" s="16"/>
+      <c r="S37" s="16"/>
     </row>
     <row r="38" spans="1:19">
       <c r="A38" s="1">
         <f t="shared" si="4"/>
         <v>2006001</v>
       </c>
-      <c r="B38" s="10">
+      <c r="B38" s="12">
         <v>200600</v>
       </c>
-      <c r="C38" s="10">
-        <v>2</v>
-      </c>
-      <c r="D38" s="11" t="s">
+      <c r="C38" s="12">
+        <v>2</v>
+      </c>
+      <c r="D38" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="E38" s="11">
+      <c r="E38" s="13">
         <v>200600001</v>
       </c>
-      <c r="F38" s="11" t="s">
+      <c r="F38" s="13" t="s">
         <v>58</v>
       </c>
       <c r="G38" s="1" t="s">
@@ -3364,31 +3364,31 @@
       <c r="N38">
         <v>5000</v>
       </c>
-      <c r="O38" s="18">
+      <c r="O38" s="15">
         <v>1990000</v>
       </c>
       <c r="Q38" s="3"/>
-      <c r="R38" s="12"/>
-      <c r="S38" s="12"/>
+      <c r="R38" s="16"/>
+      <c r="S38" s="16"/>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:19">
       <c r="A39" s="1">
         <f t="shared" si="4"/>
         <v>2006002</v>
       </c>
-      <c r="B39" s="10">
+      <c r="B39" s="12">
         <v>200600</v>
       </c>
-      <c r="C39" s="10">
-        <v>2</v>
-      </c>
-      <c r="D39" s="11" t="s">
+      <c r="C39" s="12">
+        <v>2</v>
+      </c>
+      <c r="D39" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="E39" s="11">
+      <c r="E39" s="13">
         <v>200600001</v>
       </c>
-      <c r="F39" s="11" t="s">
+      <c r="F39" s="13" t="s">
         <v>58</v>
       </c>
       <c r="G39" s="1" t="s">
@@ -3415,31 +3415,31 @@
       <c r="N39">
         <v>500000</v>
       </c>
-      <c r="O39" s="18">
+      <c r="O39" s="15">
         <v>1990000</v>
       </c>
       <c r="Q39" s="3"/>
-      <c r="R39" s="12"/>
-      <c r="S39" s="12"/>
+      <c r="R39" s="16"/>
+      <c r="S39" s="16"/>
     </row>
     <row r="40" s="1" customFormat="1" spans="1:19">
       <c r="A40" s="1">
         <f t="shared" si="4"/>
         <v>2006003</v>
       </c>
-      <c r="B40" s="10">
+      <c r="B40" s="12">
         <v>200600</v>
       </c>
-      <c r="C40" s="10">
-        <v>2</v>
-      </c>
-      <c r="D40" s="11" t="s">
+      <c r="C40" s="12">
+        <v>2</v>
+      </c>
+      <c r="D40" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="E40" s="11">
+      <c r="E40" s="13">
         <v>200600001</v>
       </c>
-      <c r="F40" s="11" t="s">
+      <c r="F40" s="13" t="s">
         <v>58</v>
       </c>
       <c r="G40" s="1" t="s">
@@ -3466,31 +3466,31 @@
       <c r="N40">
         <v>50000000</v>
       </c>
-      <c r="O40" s="18">
+      <c r="O40" s="15">
         <v>1990000</v>
       </c>
       <c r="Q40" s="3"/>
       <c r="R40"/>
-      <c r="S40" s="12"/>
+      <c r="S40" s="16"/>
     </row>
     <row r="41" spans="1:19">
       <c r="A41" s="1">
         <f t="shared" si="4"/>
         <v>2007001</v>
       </c>
-      <c r="B41" s="10">
+      <c r="B41" s="12">
         <v>200700</v>
       </c>
-      <c r="C41" s="10">
-        <v>2</v>
-      </c>
-      <c r="D41" s="10" t="s">
+      <c r="C41" s="12">
+        <v>2</v>
+      </c>
+      <c r="D41" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E41" s="11">
+      <c r="E41" s="13">
         <v>200700001</v>
       </c>
-      <c r="F41" s="11" t="s">
+      <c r="F41" s="13" t="s">
         <v>60</v>
       </c>
       <c r="G41" s="1" t="s">
@@ -3517,32 +3517,32 @@
       <c r="N41">
         <v>5000</v>
       </c>
-      <c r="O41" s="18">
+      <c r="O41" s="15">
         <v>1990000</v>
       </c>
       <c r="Q41" s="3"/>
-      <c r="R41" s="12"/>
-      <c r="S41" s="12"/>
+      <c r="R41" s="16"/>
+      <c r="S41" s="16"/>
     </row>
     <row r="42" s="1" customFormat="1" spans="1:19">
       <c r="A42" s="1">
         <f t="shared" si="4"/>
         <v>2007002</v>
       </c>
-      <c r="B42" s="10">
+      <c r="B42" s="12">
         <v>200700</v>
       </c>
-      <c r="C42" s="10">
-        <v>2</v>
-      </c>
-      <c r="D42" s="10" t="str">
+      <c r="C42" s="12">
+        <v>2</v>
+      </c>
+      <c r="D42" s="12" t="str">
         <f t="shared" ref="D39:D43" si="6">D41</f>
         <v>越南色碟</v>
       </c>
-      <c r="E42" s="11">
+      <c r="E42" s="13">
         <v>200700001</v>
       </c>
-      <c r="F42" s="11" t="s">
+      <c r="F42" s="13" t="s">
         <v>60</v>
       </c>
       <c r="G42" s="1" t="s">
@@ -3569,32 +3569,32 @@
       <c r="N42">
         <v>500000</v>
       </c>
-      <c r="O42" s="18">
+      <c r="O42" s="15">
         <v>1990000</v>
       </c>
       <c r="Q42" s="3"/>
-      <c r="R42" s="12"/>
-      <c r="S42" s="12"/>
+      <c r="R42" s="16"/>
+      <c r="S42" s="16"/>
     </row>
     <row r="43" s="1" customFormat="1" spans="1:19">
       <c r="A43" s="1">
         <f t="shared" si="4"/>
         <v>2007003</v>
       </c>
-      <c r="B43" s="10">
+      <c r="B43" s="12">
         <v>200700</v>
       </c>
-      <c r="C43" s="10">
-        <v>2</v>
-      </c>
-      <c r="D43" s="10" t="str">
+      <c r="C43" s="12">
+        <v>2</v>
+      </c>
+      <c r="D43" s="12" t="str">
         <f t="shared" si="6"/>
         <v>越南色碟</v>
       </c>
-      <c r="E43" s="11">
+      <c r="E43" s="13">
         <v>200700001</v>
       </c>
-      <c r="F43" s="11" t="s">
+      <c r="F43" s="13" t="s">
         <v>60</v>
       </c>
       <c r="G43" s="1" t="s">
@@ -3621,7 +3621,7 @@
       <c r="N43">
         <v>50000000</v>
       </c>
-      <c r="O43" s="18">
+      <c r="O43" s="15">
         <v>1990000</v>
       </c>
       <c r="S43" s="3"/>
@@ -3631,19 +3631,19 @@
         <f t="shared" si="4"/>
         <v>2008001</v>
       </c>
-      <c r="B44" s="10">
+      <c r="B44" s="12">
         <v>200800</v>
       </c>
-      <c r="C44" s="10">
-        <v>2</v>
-      </c>
-      <c r="D44" s="11" t="s">
+      <c r="C44" s="12">
+        <v>2</v>
+      </c>
+      <c r="D44" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="E44" s="11">
+      <c r="E44" s="13">
         <v>200800001</v>
       </c>
-      <c r="F44" s="11" t="s">
+      <c r="F44" s="13" t="s">
         <v>62</v>
       </c>
       <c r="G44" s="1" t="s">
@@ -3670,7 +3670,7 @@
       <c r="N44">
         <v>5000</v>
       </c>
-      <c r="O44" s="18">
+      <c r="O44" s="15">
         <v>1990000</v>
       </c>
       <c r="S44" s="3"/>
@@ -3680,19 +3680,19 @@
         <f t="shared" si="4"/>
         <v>2008002</v>
       </c>
-      <c r="B45" s="10">
+      <c r="B45" s="12">
         <v>200800</v>
       </c>
-      <c r="C45" s="10">
-        <v>2</v>
-      </c>
-      <c r="D45" s="11" t="s">
+      <c r="C45" s="12">
+        <v>2</v>
+      </c>
+      <c r="D45" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="E45" s="11">
+      <c r="E45" s="13">
         <v>200800001</v>
       </c>
-      <c r="F45" s="11" t="s">
+      <c r="F45" s="13" t="s">
         <v>62</v>
       </c>
       <c r="G45" s="1" t="s">
@@ -3719,7 +3719,7 @@
       <c r="N45">
         <v>500000</v>
       </c>
-      <c r="O45" s="18">
+      <c r="O45" s="15">
         <v>1990000</v>
       </c>
       <c r="S45" s="3"/>
@@ -3729,19 +3729,19 @@
         <f t="shared" si="4"/>
         <v>2008003</v>
       </c>
-      <c r="B46" s="10">
+      <c r="B46" s="12">
         <v>200800</v>
       </c>
-      <c r="C46" s="10">
-        <v>2</v>
-      </c>
-      <c r="D46" s="11" t="s">
+      <c r="C46" s="12">
+        <v>2</v>
+      </c>
+      <c r="D46" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="E46" s="11">
+      <c r="E46" s="13">
         <v>200800001</v>
       </c>
-      <c r="F46" s="11" t="s">
+      <c r="F46" s="13" t="s">
         <v>62</v>
       </c>
       <c r="G46" s="1" t="s">
@@ -3768,29 +3768,29 @@
       <c r="N46">
         <v>50000000</v>
       </c>
-      <c r="O46" s="18">
+      <c r="O46" s="15">
         <v>1990000</v>
       </c>
       <c r="S46" s="3"/>
     </row>
-    <row r="47" spans="1:15">
+    <row r="47" spans="1:19">
       <c r="A47" s="1">
         <f t="shared" si="4"/>
         <v>2009001</v>
       </c>
-      <c r="B47" s="13">
+      <c r="B47" s="17">
         <v>200900</v>
       </c>
-      <c r="C47" s="10">
-        <v>2</v>
-      </c>
-      <c r="D47" s="13" t="s">
+      <c r="C47" s="12">
+        <v>2</v>
+      </c>
+      <c r="D47" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="E47" s="11">
+      <c r="E47" s="13">
         <v>200900001</v>
       </c>
-      <c r="F47" s="11" t="s">
+      <c r="F47" s="13" t="s">
         <v>64</v>
       </c>
       <c r="G47" s="1" t="s">
@@ -3817,29 +3817,29 @@
       <c r="N47">
         <v>5000</v>
       </c>
-      <c r="O47" s="18">
+      <c r="O47" s="15">
         <v>1990000</v>
       </c>
     </row>
-    <row r="48" spans="1:15">
+    <row r="48" spans="1:19">
       <c r="A48" s="1">
         <f t="shared" si="4"/>
         <v>2009002</v>
       </c>
-      <c r="B48" s="10">
+      <c r="B48" s="12">
         <v>200900</v>
       </c>
-      <c r="C48" s="10">
-        <v>2</v>
-      </c>
-      <c r="D48" s="10" t="str">
+      <c r="C48" s="12">
+        <v>2</v>
+      </c>
+      <c r="D48" s="12" t="str">
         <f>D47</f>
         <v>魚蝦蟹</v>
       </c>
-      <c r="E48" s="11">
+      <c r="E48" s="13">
         <v>200900001</v>
       </c>
-      <c r="F48" s="11" t="s">
+      <c r="F48" s="13" t="s">
         <v>64</v>
       </c>
       <c r="G48" s="1" t="s">
@@ -3866,29 +3866,29 @@
       <c r="N48">
         <v>500000</v>
       </c>
-      <c r="O48" s="18">
+      <c r="O48" s="15">
         <v>1990000</v>
       </c>
     </row>
-    <row r="49" spans="1:15">
+    <row r="49" spans="1:19">
       <c r="A49" s="1">
         <f t="shared" si="4"/>
         <v>2009003</v>
       </c>
-      <c r="B49" s="10">
+      <c r="B49" s="12">
         <v>200900</v>
       </c>
-      <c r="C49" s="10">
-        <v>2</v>
-      </c>
-      <c r="D49" s="10" t="str">
+      <c r="C49" s="12">
+        <v>2</v>
+      </c>
+      <c r="D49" s="12" t="str">
         <f>D48</f>
         <v>魚蝦蟹</v>
       </c>
-      <c r="E49" s="11">
+      <c r="E49" s="13">
         <v>200900001</v>
       </c>
-      <c r="F49" s="11" t="s">
+      <c r="F49" s="13" t="s">
         <v>64</v>
       </c>
       <c r="G49" s="1" t="s">
@@ -3915,28 +3915,28 @@
       <c r="N49">
         <v>50000000</v>
       </c>
-      <c r="O49" s="18">
+      <c r="O49" s="15">
         <v>1990000</v>
       </c>
     </row>
-    <row r="50" spans="1:15">
+    <row r="50" spans="1:19">
       <c r="A50" s="1">
         <f t="shared" si="4"/>
         <v>2010001</v>
       </c>
-      <c r="B50" s="10">
+      <c r="B50" s="12">
         <v>201000</v>
       </c>
-      <c r="C50" s="10">
-        <v>2</v>
-      </c>
-      <c r="D50" s="10" t="s">
+      <c r="C50" s="12">
+        <v>2</v>
+      </c>
+      <c r="D50" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E50" s="11">
+      <c r="E50" s="13">
         <v>101000006</v>
       </c>
-      <c r="F50" s="11"/>
+      <c r="F50" s="13"/>
       <c r="G50" s="1" t="s">
         <v>32</v>
       </c>
@@ -3961,28 +3961,28 @@
       <c r="N50">
         <v>5000</v>
       </c>
-      <c r="O50" s="18">
+      <c r="O50" s="15">
         <v>1990000</v>
       </c>
     </row>
-    <row r="51" spans="1:15">
+    <row r="51" spans="1:19">
       <c r="A51" s="1">
         <f t="shared" si="4"/>
         <v>2010002</v>
       </c>
-      <c r="B51" s="10">
+      <c r="B51" s="12">
         <v>201000</v>
       </c>
-      <c r="C51" s="10">
-        <v>2</v>
-      </c>
-      <c r="D51" s="10" t="s">
+      <c r="C51" s="12">
+        <v>2</v>
+      </c>
+      <c r="D51" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E51" s="11">
+      <c r="E51" s="13">
         <v>101000006</v>
       </c>
-      <c r="F51" s="11"/>
+      <c r="F51" s="13"/>
       <c r="G51" s="1" t="s">
         <v>35</v>
       </c>
@@ -4007,28 +4007,28 @@
       <c r="N51">
         <v>500000</v>
       </c>
-      <c r="O51" s="18">
+      <c r="O51" s="15">
         <v>1990000</v>
       </c>
     </row>
-    <row r="52" spans="1:15">
+    <row r="52" spans="1:19">
       <c r="A52" s="1">
         <f t="shared" si="4"/>
         <v>2010003</v>
       </c>
-      <c r="B52" s="10">
+      <c r="B52" s="12">
         <v>201000</v>
       </c>
-      <c r="C52" s="10">
-        <v>2</v>
-      </c>
-      <c r="D52" s="10" t="s">
+      <c r="C52" s="12">
+        <v>2</v>
+      </c>
+      <c r="D52" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E52" s="11">
+      <c r="E52" s="13">
         <v>101000006</v>
       </c>
-      <c r="F52" s="11"/>
+      <c r="F52" s="13"/>
       <c r="G52" s="1" t="s">
         <v>36</v>
       </c>
@@ -4053,28 +4053,28 @@
       <c r="N52">
         <v>50000000</v>
       </c>
-      <c r="O52" s="18">
+      <c r="O52" s="15">
         <v>1990000</v>
       </c>
     </row>
-    <row r="53" spans="1:15">
+    <row r="53" spans="1:19">
       <c r="A53" s="1">
         <f t="shared" si="4"/>
         <v>3001001</v>
       </c>
-      <c r="B53" s="10">
+      <c r="B53" s="12">
         <v>300100</v>
       </c>
-      <c r="C53" s="10">
+      <c r="C53" s="12">
         <v>3</v>
       </c>
-      <c r="D53" s="10" t="s">
+      <c r="D53" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="E53" s="11">
+      <c r="E53" s="13">
         <v>300100001</v>
       </c>
-      <c r="F53" s="11" t="s">
+      <c r="F53" s="13" t="s">
         <v>67</v>
       </c>
       <c r="G53" s="1" t="s">
@@ -4101,7 +4101,7 @@
       <c r="N53">
         <v>5000</v>
       </c>
-      <c r="O53" s="18">
+      <c r="O53" s="15">
         <v>1990000</v>
       </c>
     </row>
@@ -4110,19 +4110,19 @@
         <f t="shared" si="4"/>
         <v>3001002</v>
       </c>
-      <c r="B54" s="10">
+      <c r="B54" s="12">
         <v>300100</v>
       </c>
-      <c r="C54" s="10">
+      <c r="C54" s="12">
         <v>3</v>
       </c>
-      <c r="D54" s="10" t="s">
+      <c r="D54" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="E54" s="11">
+      <c r="E54" s="13">
         <v>300100001</v>
       </c>
-      <c r="F54" s="11" t="s">
+      <c r="F54" s="13" t="s">
         <v>67</v>
       </c>
       <c r="G54" s="1" t="s">
@@ -4149,7 +4149,7 @@
       <c r="N54">
         <v>500000</v>
       </c>
-      <c r="O54" s="18">
+      <c r="O54" s="15">
         <v>1990000</v>
       </c>
       <c r="S54" s="3"/>
@@ -4159,19 +4159,19 @@
         <f t="shared" si="4"/>
         <v>3001003</v>
       </c>
-      <c r="B55" s="10">
+      <c r="B55" s="12">
         <v>300100</v>
       </c>
-      <c r="C55" s="10">
+      <c r="C55" s="12">
         <v>3</v>
       </c>
-      <c r="D55" s="10" t="s">
+      <c r="D55" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="E55" s="11">
+      <c r="E55" s="13">
         <v>300100001</v>
       </c>
-      <c r="F55" s="11" t="s">
+      <c r="F55" s="13" t="s">
         <v>67</v>
       </c>
       <c r="G55" s="1" t="s">
@@ -4198,7 +4198,7 @@
       <c r="N55">
         <v>50000000</v>
       </c>
-      <c r="O55" s="18">
+      <c r="O55" s="15">
         <v>1990000</v>
       </c>
       <c r="S55" s="3"/>
@@ -4208,19 +4208,19 @@
         <f t="shared" si="4"/>
         <v>3002001</v>
       </c>
-      <c r="B56" s="10">
+      <c r="B56" s="12">
         <v>300200</v>
       </c>
-      <c r="C56" s="10">
+      <c r="C56" s="12">
         <v>3</v>
       </c>
-      <c r="D56" s="10" t="s">
+      <c r="D56" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="E56" s="11">
+      <c r="E56" s="13">
         <v>300200006</v>
       </c>
-      <c r="F56" s="11" t="s">
+      <c r="F56" s="13" t="s">
         <v>71</v>
       </c>
       <c r="G56" s="1" t="s">
@@ -4230,7 +4230,7 @@
         <v>1</v>
       </c>
       <c r="I56" s="1">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="J56" s="1">
         <v>-1</v>
@@ -4247,7 +4247,7 @@
       <c r="N56">
         <v>5000</v>
       </c>
-      <c r="O56" s="18">
+      <c r="O56" s="15">
         <v>1990000</v>
       </c>
       <c r="S56" s="3"/>
@@ -4257,19 +4257,19 @@
         <f t="shared" si="4"/>
         <v>3002002</v>
       </c>
-      <c r="B57" s="10">
+      <c r="B57" s="12">
         <v>300200</v>
       </c>
-      <c r="C57" s="10">
+      <c r="C57" s="12">
         <v>3</v>
       </c>
-      <c r="D57" s="10" t="s">
+      <c r="D57" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="E57" s="11">
+      <c r="E57" s="13">
         <v>300200006</v>
       </c>
-      <c r="F57" s="11" t="s">
+      <c r="F57" s="13" t="s">
         <v>71</v>
       </c>
       <c r="G57" s="1" t="s">
@@ -4296,7 +4296,7 @@
       <c r="N57">
         <v>500000</v>
       </c>
-      <c r="O57" s="18">
+      <c r="O57" s="15">
         <v>1990000</v>
       </c>
       <c r="S57" s="3"/>
@@ -4306,19 +4306,19 @@
         <f t="shared" si="4"/>
         <v>3002003</v>
       </c>
-      <c r="B58" s="10">
+      <c r="B58" s="12">
         <v>300200</v>
       </c>
-      <c r="C58" s="10">
+      <c r="C58" s="12">
         <v>3</v>
       </c>
-      <c r="D58" s="10" t="s">
+      <c r="D58" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="E58" s="11">
+      <c r="E58" s="13">
         <v>300200006</v>
       </c>
-      <c r="F58" s="11" t="s">
+      <c r="F58" s="13" t="s">
         <v>71</v>
       </c>
       <c r="G58" s="1" t="s">
@@ -4345,7 +4345,7 @@
       <c r="N58">
         <v>50000000</v>
       </c>
-      <c r="O58" s="18">
+      <c r="O58" s="15">
         <v>1990000</v>
       </c>
       <c r="S58" s="3"/>
@@ -4355,40 +4355,40 @@
         <f t="shared" ref="A59:A65" si="7">B59*100+H59</f>
         <v>20010010</v>
       </c>
-      <c r="B59" s="11">
+      <c r="B59" s="13">
         <v>200100</v>
       </c>
-      <c r="C59" s="11">
-        <v>2</v>
-      </c>
-      <c r="D59" s="11" t="s">
+      <c r="C59" s="13">
+        <v>2</v>
+      </c>
+      <c r="D59" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E59" s="11">
+      <c r="E59" s="13">
         <v>200100038</v>
       </c>
-      <c r="F59" s="11" t="s">
+      <c r="F59" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="G59" s="14" t="s">
+      <c r="G59" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="H59" s="14">
+      <c r="H59" s="18">
         <v>10</v>
       </c>
-      <c r="I59" s="14">
-        <v>0</v>
-      </c>
-      <c r="J59" s="14">
+      <c r="I59" s="18">
+        <v>0</v>
+      </c>
+      <c r="J59" s="18">
         <v>-1</v>
       </c>
       <c r="K59" s="1">
         <v>0</v>
       </c>
-      <c r="L59" s="14" t="s">
+      <c r="L59" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="M59" s="14">
+      <c r="M59" s="18">
         <v>0</v>
       </c>
       <c r="N59">
@@ -4404,40 +4404,40 @@
         <f t="shared" si="7"/>
         <v>20010011</v>
       </c>
-      <c r="B60" s="11">
+      <c r="B60" s="13">
         <v>200100</v>
       </c>
-      <c r="C60" s="11">
-        <v>2</v>
-      </c>
-      <c r="D60" s="11" t="s">
+      <c r="C60" s="13">
+        <v>2</v>
+      </c>
+      <c r="D60" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E60" s="11">
+      <c r="E60" s="13">
         <v>200100038</v>
       </c>
-      <c r="F60" s="11" t="s">
+      <c r="F60" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="G60" s="14" t="s">
+      <c r="G60" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="H60" s="14">
+      <c r="H60" s="18">
         <v>11</v>
       </c>
-      <c r="I60" s="14">
-        <v>0</v>
-      </c>
-      <c r="J60" s="14">
+      <c r="I60" s="18">
+        <v>0</v>
+      </c>
+      <c r="J60" s="18">
         <v>-1</v>
       </c>
       <c r="K60" s="1">
         <v>0</v>
       </c>
-      <c r="L60" s="14" t="s">
+      <c r="L60" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="M60" s="14">
+      <c r="M60" s="18">
         <v>0</v>
       </c>
       <c r="N60">
@@ -4453,40 +4453,40 @@
         <f t="shared" si="7"/>
         <v>20010012</v>
       </c>
-      <c r="B61" s="11">
+      <c r="B61" s="13">
         <v>200100</v>
       </c>
-      <c r="C61" s="11">
-        <v>2</v>
-      </c>
-      <c r="D61" s="11" t="s">
+      <c r="C61" s="13">
+        <v>2</v>
+      </c>
+      <c r="D61" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E61" s="11">
+      <c r="E61" s="13">
         <v>200100038</v>
       </c>
-      <c r="F61" s="11" t="s">
+      <c r="F61" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="G61" s="14" t="s">
+      <c r="G61" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="H61" s="14">
+      <c r="H61" s="18">
         <v>12</v>
       </c>
-      <c r="I61" s="14">
-        <v>0</v>
-      </c>
-      <c r="J61" s="14">
+      <c r="I61" s="18">
+        <v>0</v>
+      </c>
+      <c r="J61" s="18">
         <v>-1</v>
       </c>
       <c r="K61" s="1">
         <v>0</v>
       </c>
-      <c r="L61" s="14" t="s">
+      <c r="L61" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="M61" s="14">
+      <c r="M61" s="18">
         <v>0</v>
       </c>
       <c r="N61">
@@ -4502,40 +4502,40 @@
         <f t="shared" si="7"/>
         <v>20010110</v>
       </c>
-      <c r="B62" s="11">
+      <c r="B62" s="13">
         <v>200101</v>
       </c>
-      <c r="C62" s="11">
-        <v>2</v>
-      </c>
-      <c r="D62" s="11" t="s">
+      <c r="C62" s="13">
+        <v>2</v>
+      </c>
+      <c r="D62" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E62" s="11">
+      <c r="E62" s="13">
         <v>200101001</v>
       </c>
-      <c r="F62" s="11" t="s">
+      <c r="F62" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="G62" s="14" t="s">
+      <c r="G62" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="H62" s="14">
+      <c r="H62" s="18">
         <v>10</v>
       </c>
-      <c r="I62" s="14">
-        <v>0</v>
-      </c>
-      <c r="J62" s="14">
+      <c r="I62" s="18">
+        <v>0</v>
+      </c>
+      <c r="J62" s="18">
         <v>-1</v>
       </c>
       <c r="K62" s="1">
         <v>0</v>
       </c>
-      <c r="L62" s="14" t="s">
+      <c r="L62" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="M62" s="14">
+      <c r="M62" s="18">
         <v>0</v>
       </c>
       <c r="N62">
@@ -4551,40 +4551,40 @@
         <f t="shared" si="7"/>
         <v>20010111</v>
       </c>
-      <c r="B63" s="11">
+      <c r="B63" s="13">
         <v>200101</v>
       </c>
-      <c r="C63" s="11">
-        <v>2</v>
-      </c>
-      <c r="D63" s="11" t="s">
+      <c r="C63" s="13">
+        <v>2</v>
+      </c>
+      <c r="D63" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E63" s="11">
+      <c r="E63" s="13">
         <v>200101001</v>
       </c>
-      <c r="F63" s="11" t="s">
+      <c r="F63" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="G63" s="14" t="s">
+      <c r="G63" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="H63" s="14">
+      <c r="H63" s="18">
         <v>11</v>
       </c>
-      <c r="I63" s="14">
-        <v>0</v>
-      </c>
-      <c r="J63" s="14">
+      <c r="I63" s="18">
+        <v>0</v>
+      </c>
+      <c r="J63" s="18">
         <v>-1</v>
       </c>
       <c r="K63" s="1">
         <v>0</v>
       </c>
-      <c r="L63" s="14" t="s">
+      <c r="L63" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="M63" s="14">
+      <c r="M63" s="18">
         <v>0</v>
       </c>
       <c r="N63">
@@ -4600,40 +4600,40 @@
         <f t="shared" si="7"/>
         <v>20010112</v>
       </c>
-      <c r="B64" s="11">
+      <c r="B64" s="13">
         <v>200101</v>
       </c>
-      <c r="C64" s="11">
-        <v>2</v>
-      </c>
-      <c r="D64" s="11" t="s">
+      <c r="C64" s="13">
+        <v>2</v>
+      </c>
+      <c r="D64" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E64" s="11">
+      <c r="E64" s="13">
         <v>200101001</v>
       </c>
-      <c r="F64" s="11" t="s">
+      <c r="F64" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="G64" s="14" t="s">
+      <c r="G64" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="H64" s="14">
+      <c r="H64" s="18">
         <v>12</v>
       </c>
-      <c r="I64" s="14">
-        <v>0</v>
-      </c>
-      <c r="J64" s="14">
+      <c r="I64" s="18">
+        <v>0</v>
+      </c>
+      <c r="J64" s="18">
         <v>-1</v>
       </c>
       <c r="K64" s="1">
         <v>0</v>
       </c>
-      <c r="L64" s="14" t="s">
+      <c r="L64" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="M64" s="14">
+      <c r="M64" s="18">
         <v>0</v>
       </c>
       <c r="N64">
@@ -4649,40 +4649,40 @@
         <f t="shared" si="7"/>
         <v>20030010</v>
       </c>
-      <c r="B65" s="11">
+      <c r="B65" s="13">
         <v>200300</v>
       </c>
-      <c r="C65" s="11">
-        <v>2</v>
-      </c>
-      <c r="D65" s="11" t="s">
+      <c r="C65" s="13">
+        <v>2</v>
+      </c>
+      <c r="D65" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="E65" s="11">
+      <c r="E65" s="13">
         <v>200300001</v>
       </c>
-      <c r="F65" s="11" t="s">
+      <c r="F65" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="G65" s="14" t="s">
+      <c r="G65" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="H65" s="14">
+      <c r="H65" s="18">
         <v>10</v>
       </c>
-      <c r="I65" s="14">
-        <v>0</v>
-      </c>
-      <c r="J65" s="14">
+      <c r="I65" s="18">
+        <v>0</v>
+      </c>
+      <c r="J65" s="18">
         <v>-1</v>
       </c>
       <c r="K65" s="1">
         <v>0</v>
       </c>
-      <c r="L65" s="14" t="s">
+      <c r="L65" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="M65" s="14">
+      <c r="M65" s="18">
         <v>0</v>
       </c>
       <c r="N65">
@@ -4698,40 +4698,40 @@
         <f t="shared" ref="A66:A74" si="8">B66*100+H66</f>
         <v>20030011</v>
       </c>
-      <c r="B66" s="11">
+      <c r="B66" s="13">
         <v>200300</v>
       </c>
-      <c r="C66" s="11">
-        <v>2</v>
-      </c>
-      <c r="D66" s="11" t="s">
+      <c r="C66" s="13">
+        <v>2</v>
+      </c>
+      <c r="D66" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="E66" s="11">
+      <c r="E66" s="13">
         <v>200300001</v>
       </c>
-      <c r="F66" s="11" t="s">
+      <c r="F66" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="G66" s="14" t="s">
+      <c r="G66" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="H66" s="14">
+      <c r="H66" s="18">
         <v>11</v>
       </c>
-      <c r="I66" s="14">
-        <v>0</v>
-      </c>
-      <c r="J66" s="14">
+      <c r="I66" s="18">
+        <v>0</v>
+      </c>
+      <c r="J66" s="18">
         <v>-1</v>
       </c>
       <c r="K66" s="1">
         <v>0</v>
       </c>
-      <c r="L66" s="14" t="s">
+      <c r="L66" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="M66" s="14">
+      <c r="M66" s="18">
         <v>0</v>
       </c>
       <c r="N66">
@@ -4747,40 +4747,40 @@
         <f t="shared" si="8"/>
         <v>20030012</v>
       </c>
-      <c r="B67" s="11">
+      <c r="B67" s="13">
         <v>200300</v>
       </c>
-      <c r="C67" s="11">
-        <v>2</v>
-      </c>
-      <c r="D67" s="11" t="s">
+      <c r="C67" s="13">
+        <v>2</v>
+      </c>
+      <c r="D67" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="E67" s="11">
+      <c r="E67" s="13">
         <v>200300001</v>
       </c>
-      <c r="F67" s="11" t="s">
+      <c r="F67" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="G67" s="14" t="s">
+      <c r="G67" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="H67" s="14">
+      <c r="H67" s="18">
         <v>12</v>
       </c>
-      <c r="I67" s="14">
-        <v>0</v>
-      </c>
-      <c r="J67" s="14">
+      <c r="I67" s="18">
+        <v>0</v>
+      </c>
+      <c r="J67" s="18">
         <v>-1</v>
       </c>
       <c r="K67" s="1">
         <v>0</v>
       </c>
-      <c r="L67" s="14" t="s">
+      <c r="L67" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="M67" s="14">
+      <c r="M67" s="18">
         <v>0</v>
       </c>
       <c r="N67">
@@ -4796,40 +4796,40 @@
         <f t="shared" si="8"/>
         <v>20040010</v>
       </c>
-      <c r="B68" s="11">
+      <c r="B68" s="13">
         <v>200400</v>
       </c>
-      <c r="C68" s="11">
-        <v>2</v>
-      </c>
-      <c r="D68" s="12" t="s">
+      <c r="C68" s="13">
+        <v>2</v>
+      </c>
+      <c r="D68" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="E68" s="11">
+      <c r="E68" s="13">
         <v>200400009</v>
       </c>
-      <c r="F68" s="11" t="s">
+      <c r="F68" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="G68" s="14" t="s">
+      <c r="G68" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="H68" s="14">
+      <c r="H68" s="18">
         <v>10</v>
       </c>
-      <c r="I68" s="14">
-        <v>0</v>
-      </c>
-      <c r="J68" s="14">
+      <c r="I68" s="18">
+        <v>0</v>
+      </c>
+      <c r="J68" s="18">
         <v>-1</v>
       </c>
       <c r="K68" s="1">
         <v>0</v>
       </c>
-      <c r="L68" s="14" t="s">
+      <c r="L68" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="M68" s="14">
+      <c r="M68" s="18">
         <v>0</v>
       </c>
       <c r="N68">
@@ -4845,40 +4845,40 @@
         <f t="shared" si="8"/>
         <v>20040011</v>
       </c>
-      <c r="B69" s="11">
+      <c r="B69" s="13">
         <v>200400</v>
       </c>
-      <c r="C69" s="11">
-        <v>2</v>
-      </c>
-      <c r="D69" s="12" t="s">
+      <c r="C69" s="13">
+        <v>2</v>
+      </c>
+      <c r="D69" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="E69" s="11">
+      <c r="E69" s="13">
         <v>200400009</v>
       </c>
-      <c r="F69" s="11" t="s">
+      <c r="F69" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="G69" s="14" t="s">
+      <c r="G69" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="H69" s="14">
+      <c r="H69" s="18">
         <v>11</v>
       </c>
-      <c r="I69" s="14">
-        <v>0</v>
-      </c>
-      <c r="J69" s="14">
+      <c r="I69" s="18">
+        <v>0</v>
+      </c>
+      <c r="J69" s="18">
         <v>-1</v>
       </c>
       <c r="K69" s="1">
         <v>0</v>
       </c>
-      <c r="L69" s="14" t="s">
+      <c r="L69" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="M69" s="14">
+      <c r="M69" s="18">
         <v>0</v>
       </c>
       <c r="N69">
@@ -4894,40 +4894,40 @@
         <f t="shared" si="8"/>
         <v>20040012</v>
       </c>
-      <c r="B70" s="11">
+      <c r="B70" s="13">
         <v>200400</v>
       </c>
-      <c r="C70" s="11">
-        <v>2</v>
-      </c>
-      <c r="D70" s="12" t="s">
+      <c r="C70" s="13">
+        <v>2</v>
+      </c>
+      <c r="D70" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="E70" s="11">
+      <c r="E70" s="13">
         <v>200400009</v>
       </c>
-      <c r="F70" s="11" t="s">
+      <c r="F70" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="G70" s="14" t="s">
+      <c r="G70" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="H70" s="14">
+      <c r="H70" s="18">
         <v>12</v>
       </c>
-      <c r="I70" s="14">
-        <v>0</v>
-      </c>
-      <c r="J70" s="14">
+      <c r="I70" s="18">
+        <v>0</v>
+      </c>
+      <c r="J70" s="18">
         <v>-1</v>
       </c>
       <c r="K70" s="1">
         <v>0</v>
       </c>
-      <c r="L70" s="14" t="s">
+      <c r="L70" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="M70" s="14">
+      <c r="M70" s="18">
         <v>0</v>
       </c>
       <c r="N70">
@@ -4943,40 +4943,40 @@
         <f t="shared" si="8"/>
         <v>20050010</v>
       </c>
-      <c r="B71" s="11">
+      <c r="B71" s="13">
         <v>200500</v>
       </c>
-      <c r="C71" s="11">
-        <v>2</v>
-      </c>
-      <c r="D71" s="11" t="s">
+      <c r="C71" s="13">
+        <v>2</v>
+      </c>
+      <c r="D71" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="E71" s="11">
+      <c r="E71" s="13">
         <v>200500025</v>
       </c>
-      <c r="F71" s="11" t="s">
+      <c r="F71" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="G71" s="14" t="s">
+      <c r="G71" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="H71" s="14">
+      <c r="H71" s="18">
         <v>10</v>
       </c>
-      <c r="I71" s="14">
-        <v>0</v>
-      </c>
-      <c r="J71" s="14">
+      <c r="I71" s="18">
+        <v>0</v>
+      </c>
+      <c r="J71" s="18">
         <v>-1</v>
       </c>
       <c r="K71" s="1">
         <v>0</v>
       </c>
-      <c r="L71" s="14" t="s">
+      <c r="L71" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="M71" s="14">
+      <c r="M71" s="18">
         <v>0</v>
       </c>
       <c r="N71">
@@ -4992,40 +4992,40 @@
         <f t="shared" si="8"/>
         <v>20050011</v>
       </c>
-      <c r="B72" s="11">
+      <c r="B72" s="13">
         <v>200500</v>
       </c>
-      <c r="C72" s="11">
-        <v>2</v>
-      </c>
-      <c r="D72" s="11" t="s">
+      <c r="C72" s="13">
+        <v>2</v>
+      </c>
+      <c r="D72" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="E72" s="11">
+      <c r="E72" s="13">
         <v>200500025</v>
       </c>
-      <c r="F72" s="11" t="s">
+      <c r="F72" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="G72" s="14" t="s">
+      <c r="G72" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="H72" s="14">
+      <c r="H72" s="18">
         <v>11</v>
       </c>
-      <c r="I72" s="14">
-        <v>0</v>
-      </c>
-      <c r="J72" s="14">
+      <c r="I72" s="18">
+        <v>0</v>
+      </c>
+      <c r="J72" s="18">
         <v>-1</v>
       </c>
       <c r="K72" s="1">
         <v>0</v>
       </c>
-      <c r="L72" s="14" t="s">
+      <c r="L72" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="M72" s="14">
+      <c r="M72" s="18">
         <v>0</v>
       </c>
       <c r="N72">
@@ -5041,40 +5041,40 @@
         <f t="shared" si="8"/>
         <v>20050012</v>
       </c>
-      <c r="B73" s="11">
+      <c r="B73" s="13">
         <v>200500</v>
       </c>
-      <c r="C73" s="11">
-        <v>2</v>
-      </c>
-      <c r="D73" s="11" t="s">
+      <c r="C73" s="13">
+        <v>2</v>
+      </c>
+      <c r="D73" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="E73" s="11">
+      <c r="E73" s="13">
         <v>200500025</v>
       </c>
-      <c r="F73" s="11" t="s">
+      <c r="F73" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="G73" s="14" t="s">
+      <c r="G73" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="H73" s="14">
+      <c r="H73" s="18">
         <v>12</v>
       </c>
-      <c r="I73" s="14">
-        <v>0</v>
-      </c>
-      <c r="J73" s="14">
+      <c r="I73" s="18">
+        <v>0</v>
+      </c>
+      <c r="J73" s="18">
         <v>-1</v>
       </c>
       <c r="K73" s="1">
         <v>0</v>
       </c>
-      <c r="L73" s="14" t="s">
+      <c r="L73" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="M73" s="14">
+      <c r="M73" s="18">
         <v>0</v>
       </c>
       <c r="N73">
@@ -5085,45 +5085,45 @@
       </c>
       <c r="S73" s="3"/>
     </row>
-    <row r="74" spans="1:15">
+    <row r="74" spans="1:19">
       <c r="A74" s="1">
         <f t="shared" si="8"/>
         <v>20060010</v>
       </c>
-      <c r="B74" s="11">
+      <c r="B74" s="13">
         <v>200600</v>
       </c>
-      <c r="C74" s="11">
-        <v>2</v>
-      </c>
-      <c r="D74" s="11" t="s">
+      <c r="C74" s="13">
+        <v>2</v>
+      </c>
+      <c r="D74" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="E74" s="11">
+      <c r="E74" s="13">
         <v>200600001</v>
       </c>
-      <c r="F74" s="11" t="s">
+      <c r="F74" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="G74" s="14" t="s">
+      <c r="G74" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="H74" s="14">
+      <c r="H74" s="18">
         <v>10</v>
       </c>
-      <c r="I74" s="14">
-        <v>0</v>
-      </c>
-      <c r="J74" s="14">
+      <c r="I74" s="18">
+        <v>0</v>
+      </c>
+      <c r="J74" s="18">
         <v>-1</v>
       </c>
       <c r="K74" s="1">
         <v>0</v>
       </c>
-      <c r="L74" s="14" t="s">
+      <c r="L74" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="M74" s="14">
+      <c r="M74" s="18">
         <v>0</v>
       </c>
       <c r="N74">
@@ -5133,45 +5133,45 @@
         <v>1980000</v>
       </c>
     </row>
-    <row r="75" spans="1:15">
+    <row r="75" spans="1:19">
       <c r="A75" s="1">
         <f t="shared" ref="A75:A89" si="9">B75*100+H75</f>
         <v>20060011</v>
       </c>
-      <c r="B75" s="11">
+      <c r="B75" s="13">
         <v>200600</v>
       </c>
-      <c r="C75" s="11">
-        <v>2</v>
-      </c>
-      <c r="D75" s="11" t="s">
+      <c r="C75" s="13">
+        <v>2</v>
+      </c>
+      <c r="D75" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="E75" s="11">
+      <c r="E75" s="13">
         <v>200600001</v>
       </c>
-      <c r="F75" s="11" t="s">
+      <c r="F75" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="G75" s="14" t="s">
+      <c r="G75" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="H75" s="14">
+      <c r="H75" s="18">
         <v>11</v>
       </c>
-      <c r="I75" s="14">
-        <v>0</v>
-      </c>
-      <c r="J75" s="14">
+      <c r="I75" s="18">
+        <v>0</v>
+      </c>
+      <c r="J75" s="18">
         <v>-1</v>
       </c>
       <c r="K75" s="1">
         <v>0</v>
       </c>
-      <c r="L75" s="14" t="s">
+      <c r="L75" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="M75" s="14">
+      <c r="M75" s="18">
         <v>0</v>
       </c>
       <c r="N75">
@@ -5181,45 +5181,45 @@
         <v>1980000</v>
       </c>
     </row>
-    <row r="76" spans="1:15">
+    <row r="76" spans="1:19">
       <c r="A76" s="1">
         <f t="shared" si="9"/>
         <v>20060012</v>
       </c>
-      <c r="B76" s="11">
+      <c r="B76" s="13">
         <v>200600</v>
       </c>
-      <c r="C76" s="11">
-        <v>2</v>
-      </c>
-      <c r="D76" s="11" t="s">
+      <c r="C76" s="13">
+        <v>2</v>
+      </c>
+      <c r="D76" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="E76" s="11">
+      <c r="E76" s="13">
         <v>200600001</v>
       </c>
-      <c r="F76" s="11" t="s">
+      <c r="F76" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="G76" s="14" t="s">
+      <c r="G76" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="H76" s="14">
+      <c r="H76" s="18">
         <v>12</v>
       </c>
-      <c r="I76" s="14">
-        <v>0</v>
-      </c>
-      <c r="J76" s="14">
+      <c r="I76" s="18">
+        <v>0</v>
+      </c>
+      <c r="J76" s="18">
         <v>-1</v>
       </c>
       <c r="K76" s="1">
         <v>0</v>
       </c>
-      <c r="L76" s="14" t="s">
+      <c r="L76" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="M76" s="14">
+      <c r="M76" s="18">
         <v>0</v>
       </c>
       <c r="N76">
@@ -5229,45 +5229,45 @@
         <v>1980000</v>
       </c>
     </row>
-    <row r="77" spans="1:15">
+    <row r="77" spans="1:19">
       <c r="A77" s="1">
         <f t="shared" si="9"/>
         <v>20070010</v>
       </c>
-      <c r="B77" s="11">
+      <c r="B77" s="13">
         <v>200700</v>
       </c>
-      <c r="C77" s="11">
-        <v>2</v>
-      </c>
-      <c r="D77" s="10" t="s">
+      <c r="C77" s="13">
+        <v>2</v>
+      </c>
+      <c r="D77" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E77" s="11">
+      <c r="E77" s="13">
         <v>200700001</v>
       </c>
-      <c r="F77" s="11" t="s">
+      <c r="F77" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="G77" s="14" t="s">
+      <c r="G77" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="H77" s="14">
+      <c r="H77" s="18">
         <v>10</v>
       </c>
-      <c r="I77" s="14">
-        <v>0</v>
-      </c>
-      <c r="J77" s="14">
+      <c r="I77" s="18">
+        <v>0</v>
+      </c>
+      <c r="J77" s="18">
         <v>-1</v>
       </c>
       <c r="K77" s="1">
         <v>0</v>
       </c>
-      <c r="L77" s="14" t="s">
+      <c r="L77" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="M77" s="14">
+      <c r="M77" s="18">
         <v>0</v>
       </c>
       <c r="N77">
@@ -5277,46 +5277,46 @@
         <v>1980000</v>
       </c>
     </row>
-    <row r="78" spans="1:15">
+    <row r="78" spans="1:19">
       <c r="A78" s="1">
         <f t="shared" si="9"/>
         <v>20070011</v>
       </c>
-      <c r="B78" s="11">
+      <c r="B78" s="13">
         <v>200700</v>
       </c>
-      <c r="C78" s="11">
-        <v>2</v>
-      </c>
-      <c r="D78" s="10" t="str">
+      <c r="C78" s="13">
+        <v>2</v>
+      </c>
+      <c r="D78" s="12" t="str">
         <f>D77</f>
         <v>越南色碟</v>
       </c>
-      <c r="E78" s="11">
+      <c r="E78" s="13">
         <v>200700001</v>
       </c>
-      <c r="F78" s="11" t="s">
+      <c r="F78" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="G78" s="14" t="s">
+      <c r="G78" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="H78" s="14">
+      <c r="H78" s="18">
         <v>11</v>
       </c>
-      <c r="I78" s="14">
-        <v>0</v>
-      </c>
-      <c r="J78" s="14">
+      <c r="I78" s="18">
+        <v>0</v>
+      </c>
+      <c r="J78" s="18">
         <v>-1</v>
       </c>
       <c r="K78" s="1">
         <v>0</v>
       </c>
-      <c r="L78" s="14" t="s">
+      <c r="L78" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="M78" s="14">
+      <c r="M78" s="18">
         <v>0</v>
       </c>
       <c r="N78">
@@ -5326,46 +5326,46 @@
         <v>1980000</v>
       </c>
     </row>
-    <row r="79" spans="1:15">
+    <row r="79" spans="1:19">
       <c r="A79" s="1">
         <f t="shared" si="9"/>
         <v>20070012</v>
       </c>
-      <c r="B79" s="11">
+      <c r="B79" s="13">
         <v>200700</v>
       </c>
-      <c r="C79" s="11">
-        <v>2</v>
-      </c>
-      <c r="D79" s="10" t="str">
+      <c r="C79" s="13">
+        <v>2</v>
+      </c>
+      <c r="D79" s="12" t="str">
         <f>D78</f>
         <v>越南色碟</v>
       </c>
-      <c r="E79" s="11">
+      <c r="E79" s="13">
         <v>200700001</v>
       </c>
-      <c r="F79" s="11" t="s">
+      <c r="F79" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="G79" s="14" t="s">
+      <c r="G79" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="H79" s="14">
+      <c r="H79" s="18">
         <v>12</v>
       </c>
-      <c r="I79" s="14">
-        <v>0</v>
-      </c>
-      <c r="J79" s="14">
+      <c r="I79" s="18">
+        <v>0</v>
+      </c>
+      <c r="J79" s="18">
         <v>-1</v>
       </c>
       <c r="K79" s="1">
         <v>0</v>
       </c>
-      <c r="L79" s="14" t="s">
+      <c r="L79" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="M79" s="14">
+      <c r="M79" s="18">
         <v>0</v>
       </c>
       <c r="N79">
@@ -5375,45 +5375,45 @@
         <v>1980000</v>
       </c>
     </row>
-    <row r="80" spans="1:15">
+    <row r="80" spans="1:19">
       <c r="A80" s="1">
         <f t="shared" si="9"/>
         <v>20080010</v>
       </c>
-      <c r="B80" s="11">
+      <c r="B80" s="13">
         <v>200800</v>
       </c>
-      <c r="C80" s="11">
-        <v>2</v>
-      </c>
-      <c r="D80" s="11" t="s">
+      <c r="C80" s="13">
+        <v>2</v>
+      </c>
+      <c r="D80" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="E80" s="11">
+      <c r="E80" s="13">
         <v>200800001</v>
       </c>
-      <c r="F80" s="11" t="s">
+      <c r="F80" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="G80" s="14" t="s">
+      <c r="G80" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="H80" s="14">
+      <c r="H80" s="18">
         <v>10</v>
       </c>
-      <c r="I80" s="14">
-        <v>0</v>
-      </c>
-      <c r="J80" s="14">
+      <c r="I80" s="18">
+        <v>0</v>
+      </c>
+      <c r="J80" s="18">
         <v>-1</v>
       </c>
       <c r="K80" s="1">
         <v>0</v>
       </c>
-      <c r="L80" s="14" t="s">
+      <c r="L80" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="M80" s="14">
+      <c r="M80" s="18">
         <v>0</v>
       </c>
       <c r="N80">
@@ -5423,45 +5423,45 @@
         <v>1980000</v>
       </c>
     </row>
-    <row r="81" spans="1:15">
+    <row r="81" spans="1:19">
       <c r="A81" s="1">
         <f t="shared" si="9"/>
         <v>20080011</v>
       </c>
-      <c r="B81" s="11">
+      <c r="B81" s="13">
         <v>200800</v>
       </c>
-      <c r="C81" s="11">
-        <v>2</v>
-      </c>
-      <c r="D81" s="11" t="s">
+      <c r="C81" s="13">
+        <v>2</v>
+      </c>
+      <c r="D81" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="E81" s="11">
+      <c r="E81" s="13">
         <v>200800001</v>
       </c>
-      <c r="F81" s="11" t="s">
+      <c r="F81" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="G81" s="14" t="s">
+      <c r="G81" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="H81" s="14">
+      <c r="H81" s="18">
         <v>11</v>
       </c>
-      <c r="I81" s="14">
-        <v>0</v>
-      </c>
-      <c r="J81" s="14">
+      <c r="I81" s="18">
+        <v>0</v>
+      </c>
+      <c r="J81" s="18">
         <v>-1</v>
       </c>
       <c r="K81" s="1">
         <v>0</v>
       </c>
-      <c r="L81" s="14" t="s">
+      <c r="L81" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="M81" s="14">
+      <c r="M81" s="18">
         <v>0</v>
       </c>
       <c r="N81">
@@ -5471,45 +5471,45 @@
         <v>1980000</v>
       </c>
     </row>
-    <row r="82" spans="1:15">
+    <row r="82" spans="1:19">
       <c r="A82" s="1">
         <f t="shared" si="9"/>
         <v>20080012</v>
       </c>
-      <c r="B82" s="11">
+      <c r="B82" s="13">
         <v>200800</v>
       </c>
-      <c r="C82" s="11">
-        <v>2</v>
-      </c>
-      <c r="D82" s="11" t="s">
+      <c r="C82" s="13">
+        <v>2</v>
+      </c>
+      <c r="D82" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="E82" s="11">
+      <c r="E82" s="13">
         <v>200800001</v>
       </c>
-      <c r="F82" s="11" t="s">
+      <c r="F82" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="G82" s="14" t="s">
+      <c r="G82" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="H82" s="14">
+      <c r="H82" s="18">
         <v>12</v>
       </c>
-      <c r="I82" s="14">
-        <v>0</v>
-      </c>
-      <c r="J82" s="14">
+      <c r="I82" s="18">
+        <v>0</v>
+      </c>
+      <c r="J82" s="18">
         <v>-1</v>
       </c>
       <c r="K82" s="1">
         <v>0</v>
       </c>
-      <c r="L82" s="14" t="s">
+      <c r="L82" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="M82" s="14">
+      <c r="M82" s="18">
         <v>0</v>
       </c>
       <c r="N82">
@@ -5519,45 +5519,45 @@
         <v>1980000</v>
       </c>
     </row>
-    <row r="83" spans="1:15">
+    <row r="83" spans="1:19">
       <c r="A83" s="1">
         <f t="shared" si="9"/>
         <v>20090010</v>
       </c>
-      <c r="B83" s="11">
+      <c r="B83" s="13">
         <v>200900</v>
       </c>
-      <c r="C83" s="11">
-        <v>2</v>
-      </c>
-      <c r="D83" s="11" t="s">
+      <c r="C83" s="13">
+        <v>2</v>
+      </c>
+      <c r="D83" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="E83" s="11">
+      <c r="E83" s="13">
         <v>200900001</v>
       </c>
-      <c r="F83" s="11" t="s">
+      <c r="F83" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="G83" s="14" t="s">
+      <c r="G83" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="H83" s="14">
+      <c r="H83" s="18">
         <v>10</v>
       </c>
-      <c r="I83" s="14">
-        <v>0</v>
-      </c>
-      <c r="J83" s="14">
+      <c r="I83" s="18">
+        <v>0</v>
+      </c>
+      <c r="J83" s="18">
         <v>-1</v>
       </c>
       <c r="K83" s="1">
         <v>0</v>
       </c>
-      <c r="L83" s="14" t="s">
+      <c r="L83" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="M83" s="14">
+      <c r="M83" s="18">
         <v>0</v>
       </c>
       <c r="N83">
@@ -5567,45 +5567,45 @@
         <v>1980000</v>
       </c>
     </row>
-    <row r="84" spans="1:15">
+    <row r="84" spans="1:19">
       <c r="A84" s="1">
         <f t="shared" si="9"/>
         <v>20090011</v>
       </c>
-      <c r="B84" s="11">
+      <c r="B84" s="13">
         <v>200900</v>
       </c>
-      <c r="C84" s="11">
-        <v>2</v>
-      </c>
-      <c r="D84" s="11" t="s">
+      <c r="C84" s="13">
+        <v>2</v>
+      </c>
+      <c r="D84" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="E84" s="11">
+      <c r="E84" s="13">
         <v>200900001</v>
       </c>
-      <c r="F84" s="11" t="s">
+      <c r="F84" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="G84" s="14" t="s">
+      <c r="G84" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="H84" s="14">
+      <c r="H84" s="18">
         <v>11</v>
       </c>
-      <c r="I84" s="14">
-        <v>0</v>
-      </c>
-      <c r="J84" s="14">
+      <c r="I84" s="18">
+        <v>0</v>
+      </c>
+      <c r="J84" s="18">
         <v>-1</v>
       </c>
       <c r="K84" s="1">
         <v>0</v>
       </c>
-      <c r="L84" s="14" t="s">
+      <c r="L84" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="M84" s="14">
+      <c r="M84" s="18">
         <v>0</v>
       </c>
       <c r="N84">
@@ -5615,45 +5615,45 @@
         <v>1980000</v>
       </c>
     </row>
-    <row r="85" spans="1:15">
+    <row r="85" spans="1:19">
       <c r="A85" s="1">
         <f t="shared" si="9"/>
         <v>20090012</v>
       </c>
-      <c r="B85" s="11">
+      <c r="B85" s="13">
         <v>200900</v>
       </c>
-      <c r="C85" s="11">
-        <v>2</v>
-      </c>
-      <c r="D85" s="11" t="s">
+      <c r="C85" s="13">
+        <v>2</v>
+      </c>
+      <c r="D85" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="E85" s="11">
+      <c r="E85" s="13">
         <v>200900001</v>
       </c>
-      <c r="F85" s="11" t="s">
+      <c r="F85" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="G85" s="14" t="s">
+      <c r="G85" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="H85" s="14">
+      <c r="H85" s="18">
         <v>12</v>
       </c>
-      <c r="I85" s="14">
-        <v>0</v>
-      </c>
-      <c r="J85" s="14">
+      <c r="I85" s="18">
+        <v>0</v>
+      </c>
+      <c r="J85" s="18">
         <v>-1</v>
       </c>
       <c r="K85" s="1">
         <v>0</v>
       </c>
-      <c r="L85" s="14" t="s">
+      <c r="L85" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="M85" s="14">
+      <c r="M85" s="18">
         <v>0</v>
       </c>
       <c r="N85">
@@ -5668,28 +5668,28 @@
         <f t="shared" si="9"/>
         <v>30020010</v>
       </c>
-      <c r="B86" s="10">
+      <c r="B86" s="12">
         <v>300200</v>
       </c>
-      <c r="C86" s="10">
+      <c r="C86" s="12">
         <v>3</v>
       </c>
-      <c r="D86" s="10" t="s">
+      <c r="D86" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="E86" s="11">
+      <c r="E86" s="13">
         <v>300200006</v>
       </c>
-      <c r="F86" s="11" t="s">
+      <c r="F86" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="G86" s="14" t="s">
+      <c r="G86" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="H86" s="14">
+      <c r="H86" s="18">
         <v>10</v>
       </c>
-      <c r="I86" s="14">
+      <c r="I86" s="18">
         <v>0</v>
       </c>
       <c r="J86" s="1">
@@ -5701,7 +5701,7 @@
       <c r="L86" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="M86" s="14">
+      <c r="M86" s="18">
         <v>0</v>
       </c>
       <c r="N86">
@@ -5717,28 +5717,28 @@
         <f t="shared" si="9"/>
         <v>30020011</v>
       </c>
-      <c r="B87" s="10">
+      <c r="B87" s="12">
         <v>300200</v>
       </c>
-      <c r="C87" s="10">
+      <c r="C87" s="12">
         <v>3</v>
       </c>
-      <c r="D87" s="10" t="s">
+      <c r="D87" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="E87" s="11">
+      <c r="E87" s="13">
         <v>300200006</v>
       </c>
-      <c r="F87" s="11" t="s">
+      <c r="F87" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="G87" s="14" t="s">
+      <c r="G87" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="H87" s="14">
+      <c r="H87" s="18">
         <v>11</v>
       </c>
-      <c r="I87" s="14">
+      <c r="I87" s="18">
         <v>0</v>
       </c>
       <c r="J87" s="1">
@@ -5750,7 +5750,7 @@
       <c r="L87" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="M87" s="14">
+      <c r="M87" s="18">
         <v>0</v>
       </c>
       <c r="N87">
@@ -5766,28 +5766,28 @@
         <f t="shared" si="9"/>
         <v>30020012</v>
       </c>
-      <c r="B88" s="10">
+      <c r="B88" s="12">
         <v>300200</v>
       </c>
-      <c r="C88" s="10">
+      <c r="C88" s="12">
         <v>3</v>
       </c>
-      <c r="D88" s="10" t="s">
+      <c r="D88" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="E88" s="11">
+      <c r="E88" s="13">
         <v>300200006</v>
       </c>
-      <c r="F88" s="11" t="s">
+      <c r="F88" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="G88" s="14" t="s">
+      <c r="G88" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="H88" s="14">
+      <c r="H88" s="18">
         <v>12</v>
       </c>
-      <c r="I88" s="14">
+      <c r="I88" s="18">
         <v>0</v>
       </c>
       <c r="J88" s="1">
@@ -5799,7 +5799,7 @@
       <c r="L88" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="M88" s="14">
+      <c r="M88" s="18">
         <v>0</v>
       </c>
       <c r="N88">

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925" tabRatio="794"/>
+    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Warehouse" sheetId="42" r:id="rId1"/>
@@ -156,7 +156,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="79">
   <si>
     <t>sid</t>
   </si>
@@ -294,6 +294,9 @@
   </si>
   <si>
     <t>财富银行</t>
+  </si>
+  <si>
+    <t>WealthBank</t>
   </si>
   <si>
     <t>紅黑大戰</t>
@@ -602,12 +605,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2439,7 +2442,7 @@
         <v>102400026</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>32</v>
@@ -2488,7 +2491,7 @@
         <v>102400026</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>35</v>
@@ -2537,7 +2540,7 @@
         <v>102400026</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>36</v>
@@ -2579,13 +2582,13 @@
         <v>2</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E23" s="13">
         <v>200100038</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>32</v>
@@ -2634,7 +2637,7 @@
         <v>200100038</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>35</v>
@@ -2683,7 +2686,7 @@
         <v>200100038</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>36</v>
@@ -2726,13 +2729,13 @@
         <v>2</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E26" s="13">
         <v>200101001</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>32</v>
@@ -2781,7 +2784,7 @@
         <v>200101001</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>35</v>
@@ -2831,7 +2834,7 @@
         <v>200101001</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>36</v>
@@ -2874,13 +2877,13 @@
         <v>2</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E29" s="13">
         <v>200300001</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>32</v>
@@ -2929,7 +2932,7 @@
         <v>200300001</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>35</v>
@@ -2981,7 +2984,7 @@
         <v>200300001</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>36</v>
@@ -3026,13 +3029,13 @@
         <v>2</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E32" s="13">
         <v>200400009</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>32</v>
@@ -3077,13 +3080,13 @@
         <v>2</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E33" s="13">
         <v>200400009</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>35</v>
@@ -3128,13 +3131,13 @@
         <v>2</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E34" s="13">
         <v>200400009</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>36</v>
@@ -3179,13 +3182,13 @@
         <v>2</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E35" s="13">
         <v>200500025</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>32</v>
@@ -3206,7 +3209,7 @@
         <v>33</v>
       </c>
       <c r="M35" s="20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N35">
         <v>5000</v>
@@ -3230,13 +3233,13 @@
         <v>2</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E36" s="13">
         <v>200500025</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>35</v>
@@ -3257,7 +3260,7 @@
         <v>33</v>
       </c>
       <c r="M36" s="20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N36">
         <v>500000</v>
@@ -3281,13 +3284,13 @@
         <v>2</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E37" s="13">
         <v>200500025</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>36</v>
@@ -3308,7 +3311,7 @@
         <v>33</v>
       </c>
       <c r="M37" s="20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N37">
         <v>50000000</v>
@@ -3332,13 +3335,13 @@
         <v>2</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E38" s="13">
         <v>200600001</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>32</v>
@@ -3383,13 +3386,13 @@
         <v>2</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E39" s="13">
         <v>200600001</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>35</v>
@@ -3434,13 +3437,13 @@
         <v>2</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E40" s="13">
         <v>200600001</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>36</v>
@@ -3485,13 +3488,13 @@
         <v>2</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E41" s="13">
         <v>200700001</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>32</v>
@@ -3543,7 +3546,7 @@
         <v>200700001</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>35</v>
@@ -3595,7 +3598,7 @@
         <v>200700001</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>36</v>
@@ -3638,13 +3641,13 @@
         <v>2</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E44" s="13">
         <v>200800001</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>32</v>
@@ -3687,13 +3690,13 @@
         <v>2</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E45" s="13">
         <v>200800001</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>35</v>
@@ -3736,13 +3739,13 @@
         <v>2</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E46" s="13">
         <v>200800001</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>36</v>
@@ -3785,13 +3788,13 @@
         <v>2</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E47" s="13">
         <v>200900001</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>32</v>
@@ -3840,7 +3843,7 @@
         <v>200900001</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>35</v>
@@ -3889,7 +3892,7 @@
         <v>200900001</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>36</v>
@@ -3931,7 +3934,7 @@
         <v>2</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E50" s="13">
         <v>101000006</v>
@@ -3977,7 +3980,7 @@
         <v>2</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E51" s="13">
         <v>101000006</v>
@@ -4023,7 +4026,7 @@
         <v>2</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E52" s="13">
         <v>101000006</v>
@@ -4069,13 +4072,13 @@
         <v>3</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E53" s="13">
         <v>300100001</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>32</v>
@@ -4093,10 +4096,10 @@
         <v>0</v>
       </c>
       <c r="L53" s="21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M53" s="21" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N53">
         <v>5000</v>
@@ -4117,13 +4120,13 @@
         <v>3</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E54" s="13">
         <v>300100001</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>35</v>
@@ -4141,10 +4144,10 @@
         <v>0</v>
       </c>
       <c r="L54" s="21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M54" s="21" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N54">
         <v>500000</v>
@@ -4166,13 +4169,13 @@
         <v>3</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E55" s="13">
         <v>300100001</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>36</v>
@@ -4190,10 +4193,10 @@
         <v>0</v>
       </c>
       <c r="L55" s="21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M55" s="21" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N55">
         <v>50000000</v>
@@ -4215,13 +4218,13 @@
         <v>3</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E56" s="13">
         <v>300200006</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>32</v>
@@ -4239,10 +4242,10 @@
         <v>0</v>
       </c>
       <c r="L56" s="21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M56" s="21" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N56">
         <v>5000</v>
@@ -4264,13 +4267,13 @@
         <v>3</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E57" s="13">
         <v>300200006</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>35</v>
@@ -4288,10 +4291,10 @@
         <v>0</v>
       </c>
       <c r="L57" s="21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M57" s="21" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N57">
         <v>500000</v>
@@ -4313,13 +4316,13 @@
         <v>3</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E58" s="13">
         <v>300200006</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>36</v>
@@ -4337,10 +4340,10 @@
         <v>0</v>
       </c>
       <c r="L58" s="21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M58" s="21" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N58">
         <v>50000000</v>
@@ -4362,16 +4365,16 @@
         <v>2</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E59" s="13">
         <v>200100038</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G59" s="18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H59" s="18">
         <v>10</v>
@@ -4386,7 +4389,7 @@
         <v>0</v>
       </c>
       <c r="L59" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M59" s="18">
         <v>0</v>
@@ -4411,16 +4414,16 @@
         <v>2</v>
       </c>
       <c r="D60" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E60" s="13">
         <v>200100038</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G60" s="18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H60" s="18">
         <v>11</v>
@@ -4435,7 +4438,7 @@
         <v>0</v>
       </c>
       <c r="L60" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M60" s="18">
         <v>0</v>
@@ -4460,16 +4463,16 @@
         <v>2</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E61" s="13">
         <v>200100038</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G61" s="18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H61" s="18">
         <v>12</v>
@@ -4484,7 +4487,7 @@
         <v>0</v>
       </c>
       <c r="L61" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M61" s="18">
         <v>0</v>
@@ -4509,16 +4512,16 @@
         <v>2</v>
       </c>
       <c r="D62" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E62" s="13">
         <v>200101001</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G62" s="18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H62" s="18">
         <v>10</v>
@@ -4533,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="L62" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M62" s="18">
         <v>0</v>
@@ -4558,16 +4561,16 @@
         <v>2</v>
       </c>
       <c r="D63" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E63" s="13">
         <v>200101001</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G63" s="18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H63" s="18">
         <v>11</v>
@@ -4582,7 +4585,7 @@
         <v>0</v>
       </c>
       <c r="L63" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M63" s="18">
         <v>0</v>
@@ -4607,16 +4610,16 @@
         <v>2</v>
       </c>
       <c r="D64" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E64" s="13">
         <v>200101001</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G64" s="18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H64" s="18">
         <v>12</v>
@@ -4631,7 +4634,7 @@
         <v>0</v>
       </c>
       <c r="L64" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M64" s="18">
         <v>0</v>
@@ -4656,16 +4659,16 @@
         <v>2</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E65" s="13">
         <v>200300001</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G65" s="18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H65" s="18">
         <v>10</v>
@@ -4680,7 +4683,7 @@
         <v>0</v>
       </c>
       <c r="L65" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M65" s="18">
         <v>0</v>
@@ -4705,16 +4708,16 @@
         <v>2</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E66" s="13">
         <v>200300001</v>
       </c>
       <c r="F66" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G66" s="18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H66" s="18">
         <v>11</v>
@@ -4729,7 +4732,7 @@
         <v>0</v>
       </c>
       <c r="L66" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M66" s="18">
         <v>0</v>
@@ -4754,16 +4757,16 @@
         <v>2</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E67" s="13">
         <v>200300001</v>
       </c>
       <c r="F67" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G67" s="18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H67" s="18">
         <v>12</v>
@@ -4778,7 +4781,7 @@
         <v>0</v>
       </c>
       <c r="L67" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M67" s="18">
         <v>0</v>
@@ -4803,16 +4806,16 @@
         <v>2</v>
       </c>
       <c r="D68" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E68" s="13">
         <v>200400009</v>
       </c>
       <c r="F68" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G68" s="18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H68" s="18">
         <v>10</v>
@@ -4827,7 +4830,7 @@
         <v>0</v>
       </c>
       <c r="L68" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M68" s="18">
         <v>0</v>
@@ -4852,16 +4855,16 @@
         <v>2</v>
       </c>
       <c r="D69" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E69" s="13">
         <v>200400009</v>
       </c>
       <c r="F69" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G69" s="18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H69" s="18">
         <v>11</v>
@@ -4876,7 +4879,7 @@
         <v>0</v>
       </c>
       <c r="L69" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M69" s="18">
         <v>0</v>
@@ -4901,16 +4904,16 @@
         <v>2</v>
       </c>
       <c r="D70" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E70" s="13">
         <v>200400009</v>
       </c>
       <c r="F70" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G70" s="18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H70" s="18">
         <v>12</v>
@@ -4925,7 +4928,7 @@
         <v>0</v>
       </c>
       <c r="L70" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M70" s="18">
         <v>0</v>
@@ -4950,16 +4953,16 @@
         <v>2</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E71" s="13">
         <v>200500025</v>
       </c>
       <c r="F71" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G71" s="18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H71" s="18">
         <v>10</v>
@@ -4974,7 +4977,7 @@
         <v>0</v>
       </c>
       <c r="L71" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M71" s="18">
         <v>0</v>
@@ -4999,16 +5002,16 @@
         <v>2</v>
       </c>
       <c r="D72" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E72" s="13">
         <v>200500025</v>
       </c>
       <c r="F72" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G72" s="18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H72" s="18">
         <v>11</v>
@@ -5023,7 +5026,7 @@
         <v>0</v>
       </c>
       <c r="L72" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M72" s="18">
         <v>0</v>
@@ -5048,16 +5051,16 @@
         <v>2</v>
       </c>
       <c r="D73" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E73" s="13">
         <v>200500025</v>
       </c>
       <c r="F73" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G73" s="18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H73" s="18">
         <v>12</v>
@@ -5072,7 +5075,7 @@
         <v>0</v>
       </c>
       <c r="L73" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M73" s="18">
         <v>0</v>
@@ -5097,16 +5100,16 @@
         <v>2</v>
       </c>
       <c r="D74" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E74" s="13">
         <v>200600001</v>
       </c>
       <c r="F74" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G74" s="18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H74" s="18">
         <v>10</v>
@@ -5121,7 +5124,7 @@
         <v>0</v>
       </c>
       <c r="L74" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M74" s="18">
         <v>0</v>
@@ -5145,16 +5148,16 @@
         <v>2</v>
       </c>
       <c r="D75" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E75" s="13">
         <v>200600001</v>
       </c>
       <c r="F75" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G75" s="18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H75" s="18">
         <v>11</v>
@@ -5169,7 +5172,7 @@
         <v>0</v>
       </c>
       <c r="L75" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M75" s="18">
         <v>0</v>
@@ -5193,16 +5196,16 @@
         <v>2</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E76" s="13">
         <v>200600001</v>
       </c>
       <c r="F76" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G76" s="18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H76" s="18">
         <v>12</v>
@@ -5217,7 +5220,7 @@
         <v>0</v>
       </c>
       <c r="L76" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M76" s="18">
         <v>0</v>
@@ -5241,16 +5244,16 @@
         <v>2</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E77" s="13">
         <v>200700001</v>
       </c>
       <c r="F77" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G77" s="18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H77" s="18">
         <v>10</v>
@@ -5265,7 +5268,7 @@
         <v>0</v>
       </c>
       <c r="L77" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M77" s="18">
         <v>0</v>
@@ -5296,10 +5299,10 @@
         <v>200700001</v>
       </c>
       <c r="F78" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G78" s="18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H78" s="18">
         <v>11</v>
@@ -5314,7 +5317,7 @@
         <v>0</v>
       </c>
       <c r="L78" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M78" s="18">
         <v>0</v>
@@ -5345,10 +5348,10 @@
         <v>200700001</v>
       </c>
       <c r="F79" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G79" s="18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H79" s="18">
         <v>12</v>
@@ -5363,7 +5366,7 @@
         <v>0</v>
       </c>
       <c r="L79" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M79" s="18">
         <v>0</v>
@@ -5387,16 +5390,16 @@
         <v>2</v>
       </c>
       <c r="D80" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E80" s="13">
         <v>200800001</v>
       </c>
       <c r="F80" s="13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G80" s="18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H80" s="18">
         <v>10</v>
@@ -5411,7 +5414,7 @@
         <v>0</v>
       </c>
       <c r="L80" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M80" s="18">
         <v>0</v>
@@ -5435,16 +5438,16 @@
         <v>2</v>
       </c>
       <c r="D81" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E81" s="13">
         <v>200800001</v>
       </c>
       <c r="F81" s="13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G81" s="18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H81" s="18">
         <v>11</v>
@@ -5459,7 +5462,7 @@
         <v>0</v>
       </c>
       <c r="L81" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M81" s="18">
         <v>0</v>
@@ -5483,16 +5486,16 @@
         <v>2</v>
       </c>
       <c r="D82" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E82" s="13">
         <v>200800001</v>
       </c>
       <c r="F82" s="13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G82" s="18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H82" s="18">
         <v>12</v>
@@ -5507,7 +5510,7 @@
         <v>0</v>
       </c>
       <c r="L82" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M82" s="18">
         <v>0</v>
@@ -5531,16 +5534,16 @@
         <v>2</v>
       </c>
       <c r="D83" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E83" s="13">
         <v>200900001</v>
       </c>
       <c r="F83" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G83" s="18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H83" s="18">
         <v>10</v>
@@ -5555,7 +5558,7 @@
         <v>0</v>
       </c>
       <c r="L83" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M83" s="18">
         <v>0</v>
@@ -5579,16 +5582,16 @@
         <v>2</v>
       </c>
       <c r="D84" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E84" s="13">
         <v>200900001</v>
       </c>
       <c r="F84" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G84" s="18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H84" s="18">
         <v>11</v>
@@ -5603,7 +5606,7 @@
         <v>0</v>
       </c>
       <c r="L84" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M84" s="18">
         <v>0</v>
@@ -5627,16 +5630,16 @@
         <v>2</v>
       </c>
       <c r="D85" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E85" s="13">
         <v>200900001</v>
       </c>
       <c r="F85" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G85" s="18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H85" s="18">
         <v>12</v>
@@ -5651,7 +5654,7 @@
         <v>0</v>
       </c>
       <c r="L85" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M85" s="18">
         <v>0</v>
@@ -5675,16 +5678,16 @@
         <v>3</v>
       </c>
       <c r="D86" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E86" s="13">
         <v>300200006</v>
       </c>
       <c r="F86" s="13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G86" s="18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H86" s="18">
         <v>10</v>
@@ -5699,7 +5702,7 @@
         <v>0</v>
       </c>
       <c r="L86" s="21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M86" s="18">
         <v>0</v>
@@ -5724,16 +5727,16 @@
         <v>3</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E87" s="13">
         <v>300200006</v>
       </c>
       <c r="F87" s="13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G87" s="18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H87" s="18">
         <v>11</v>
@@ -5748,7 +5751,7 @@
         <v>0</v>
       </c>
       <c r="L87" s="21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M87" s="18">
         <v>0</v>
@@ -5773,16 +5776,16 @@
         <v>3</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E88" s="13">
         <v>300200006</v>
       </c>
       <c r="F88" s="13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G88" s="18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H88" s="18">
         <v>12</v>
@@ -5797,7 +5800,7 @@
         <v>0</v>
       </c>
       <c r="L88" s="21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M88" s="18">
         <v>0</v>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -156,7 +156,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="83">
   <si>
     <t>sid</t>
   </si>
@@ -297,6 +297,18 @@
   </si>
   <si>
     <t>WealthBank</t>
+  </si>
+  <si>
+    <t>雷神</t>
+  </si>
+  <si>
+    <t>leishen</t>
+  </si>
+  <si>
+    <t>圣诞狂欢夜</t>
+  </si>
+  <si>
+    <t>DazeBeforeChristmas</t>
   </si>
   <si>
     <t>紅黑大戰</t>
@@ -1526,7 +1538,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S88"/>
+  <dimension ref="A1:S94"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="3" width="9.375" style="1"/>
@@ -2276,7 +2288,7 @@
         <v>1990000</v>
       </c>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" spans="1:17">
       <c r="A17" s="1">
         <f t="shared" si="2"/>
         <v>1014001</v>
@@ -2324,7 +2336,7 @@
         <v>1990000</v>
       </c>
     </row>
-    <row r="18" spans="1:19">
+    <row r="18" spans="1:17">
       <c r="A18" s="1">
         <f t="shared" si="2"/>
         <v>1014002</v>
@@ -2374,7 +2386,7 @@
         <v>1990000</v>
       </c>
     </row>
-    <row r="19" spans="1:19">
+    <row r="19" spans="1:17">
       <c r="A19" s="1">
         <f t="shared" si="2"/>
         <v>1014003</v>
@@ -2424,7 +2436,7 @@
         <v>1990000</v>
       </c>
     </row>
-    <row r="20" spans="1:19">
+    <row r="20" spans="1:17">
       <c r="A20" s="1">
         <f t="shared" si="2"/>
         <v>1024001</v>
@@ -2472,7 +2484,7 @@
         <v>1990000</v>
       </c>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:17">
       <c r="A21" s="1">
         <f t="shared" si="2"/>
         <v>1024002</v>
@@ -2521,7 +2533,7 @@
         <v>1990000</v>
       </c>
     </row>
-    <row r="22" spans="1:19">
+    <row r="22" spans="1:17">
       <c r="A22" s="1">
         <f t="shared" si="2"/>
         <v>1024003</v>
@@ -2570,22 +2582,22 @@
         <v>1990000</v>
       </c>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:17">
       <c r="A23" s="1">
-        <f t="shared" ref="A23:A69" si="4">B23*10+H23</f>
-        <v>2001001</v>
+        <f t="shared" ref="A23:A28" si="4">B23*10+H23</f>
+        <v>1017001</v>
       </c>
       <c r="B23" s="12">
-        <v>200100</v>
+        <v>101700</v>
       </c>
       <c r="C23" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" s="12" t="s">
         <v>47</v>
       </c>
       <c r="E23" s="13">
-        <v>200100038</v>
+        <v>102200001</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>48</v>
@@ -2618,23 +2630,22 @@
         <v>1990000</v>
       </c>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:17">
       <c r="A24" s="1">
         <f t="shared" si="4"/>
-        <v>2001002</v>
+        <v>1017002</v>
       </c>
       <c r="B24" s="12">
-        <v>200100</v>
+        <v>101700</v>
       </c>
       <c r="C24" s="12">
-        <v>2</v>
-      </c>
-      <c r="D24" s="12" t="str">
-        <f>D23</f>
-        <v>紅黑大戰</v>
+        <v>1</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="E24" s="13">
-        <v>200100038</v>
+        <v>102200001</v>
       </c>
       <c r="F24" s="13" t="s">
         <v>48</v>
@@ -2667,23 +2678,22 @@
         <v>1990000</v>
       </c>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:17">
       <c r="A25" s="1">
         <f t="shared" si="4"/>
-        <v>2001003</v>
+        <v>1017003</v>
       </c>
       <c r="B25" s="12">
-        <v>200100</v>
+        <v>101700</v>
       </c>
       <c r="C25" s="12">
-        <v>2</v>
-      </c>
-      <c r="D25" s="12" t="str">
-        <f>D24</f>
-        <v>紅黑大戰</v>
+        <v>1</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="E25" s="13">
-        <v>200100038</v>
+        <v>102200001</v>
       </c>
       <c r="F25" s="13" t="s">
         <v>48</v>
@@ -2715,24 +2725,23 @@
       <c r="O25" s="15">
         <v>1990000</v>
       </c>
-      <c r="Q25"/>
-    </row>
-    <row r="26" spans="1:19">
+    </row>
+    <row r="26" spans="1:17">
       <c r="A26" s="1">
         <f t="shared" si="4"/>
-        <v>2001011</v>
+        <v>1022001</v>
       </c>
       <c r="B26" s="12">
-        <v>200101</v>
+        <v>102200</v>
       </c>
       <c r="C26" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" s="12" t="s">
         <v>49</v>
       </c>
       <c r="E26" s="13">
-        <v>200101001</v>
+        <v>101700001</v>
       </c>
       <c r="F26" s="13" t="s">
         <v>50</v>
@@ -2765,23 +2774,22 @@
         <v>1990000</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" spans="1:19">
+    <row r="27" spans="1:17">
       <c r="A27" s="1">
         <f t="shared" si="4"/>
-        <v>2001012</v>
+        <v>1022002</v>
       </c>
       <c r="B27" s="12">
-        <v>200101</v>
+        <v>102200</v>
       </c>
       <c r="C27" s="12">
-        <v>2</v>
-      </c>
-      <c r="D27" s="12" t="str">
-        <f t="shared" ref="D27:D31" si="5">D26</f>
-        <v>龍虎鬥</v>
+        <v>1</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="E27" s="13">
-        <v>200101001</v>
+        <v>101700001</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>50</v>
@@ -2813,25 +2821,23 @@
       <c r="O27" s="15">
         <v>1990000</v>
       </c>
-      <c r="S27" s="3"/>
-    </row>
-    <row r="28" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="28" spans="1:17">
       <c r="A28" s="1">
         <f t="shared" si="4"/>
-        <v>2001013</v>
+        <v>1022003</v>
       </c>
       <c r="B28" s="12">
-        <v>200101</v>
+        <v>102200</v>
       </c>
       <c r="C28" s="12">
-        <v>2</v>
-      </c>
-      <c r="D28" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v>龍虎鬥</v>
+        <v>1</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="E28" s="13">
-        <v>200101001</v>
+        <v>101700001</v>
       </c>
       <c r="F28" s="13" t="s">
         <v>50</v>
@@ -2863,15 +2869,14 @@
       <c r="O28" s="15">
         <v>1990000</v>
       </c>
-      <c r="S28" s="3"/>
-    </row>
-    <row r="29" spans="1:19">
+    </row>
+    <row r="29" spans="1:17">
       <c r="A29" s="1">
-        <f t="shared" si="4"/>
-        <v>2003001</v>
+        <f t="shared" ref="A29:A75" si="5">B29*10+H29</f>
+        <v>2001001</v>
       </c>
       <c r="B29" s="12">
-        <v>200300</v>
+        <v>200100</v>
       </c>
       <c r="C29" s="12">
         <v>2</v>
@@ -2880,7 +2885,7 @@
         <v>51</v>
       </c>
       <c r="E29" s="13">
-        <v>200300001</v>
+        <v>200100038</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>52</v>
@@ -2913,23 +2918,23 @@
         <v>1990000</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" spans="1:19">
+    <row r="30" spans="1:17">
       <c r="A30" s="1">
-        <f t="shared" si="4"/>
-        <v>2003002</v>
+        <f t="shared" si="5"/>
+        <v>2001002</v>
       </c>
       <c r="B30" s="12">
-        <v>200300</v>
+        <v>200100</v>
       </c>
       <c r="C30" s="12">
         <v>2</v>
       </c>
       <c r="D30" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v>飛禽走獸</v>
+        <f>D29</f>
+        <v>紅黑大戰</v>
       </c>
       <c r="E30" s="13">
-        <v>200300001</v>
+        <v>200100038</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>52</v>
@@ -2961,27 +2966,24 @@
       <c r="O30" s="15">
         <v>1990000</v>
       </c>
-      <c r="Q30" s="3"/>
-      <c r="R30" s="12"/>
-      <c r="S30" s="3"/>
-    </row>
-    <row r="31" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="31" spans="1:17">
       <c r="A31" s="1">
-        <f t="shared" si="4"/>
-        <v>2003003</v>
+        <f t="shared" si="5"/>
+        <v>2001003</v>
       </c>
       <c r="B31" s="12">
-        <v>200300</v>
+        <v>200100</v>
       </c>
       <c r="C31" s="12">
         <v>2</v>
       </c>
       <c r="D31" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v>飛禽走獸</v>
+        <f>D30</f>
+        <v>紅黑大戰</v>
       </c>
       <c r="E31" s="13">
-        <v>200300001</v>
+        <v>200100038</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>52</v>
@@ -3013,26 +3015,24 @@
       <c r="O31" s="15">
         <v>1990000</v>
       </c>
-      <c r="Q31" s="3"/>
-      <c r="R31" s="16"/>
-      <c r="S31" s="16"/>
-    </row>
-    <row r="32" spans="1:19">
+      <c r="Q31"/>
+    </row>
+    <row r="32" spans="1:17">
       <c r="A32" s="1">
-        <f t="shared" si="4"/>
-        <v>2004001</v>
+        <f t="shared" si="5"/>
+        <v>2001011</v>
       </c>
       <c r="B32" s="12">
-        <v>200400</v>
+        <v>200101</v>
       </c>
       <c r="C32" s="12">
         <v>2</v>
       </c>
-      <c r="D32" s="16" t="s">
+      <c r="D32" s="12" t="s">
         <v>53</v>
       </c>
       <c r="E32" s="13">
-        <v>200400009</v>
+        <v>200101001</v>
       </c>
       <c r="F32" s="13" t="s">
         <v>54</v>
@@ -3064,26 +3064,24 @@
       <c r="O32" s="15">
         <v>1990000</v>
       </c>
-      <c r="Q32" s="3"/>
-      <c r="R32" s="16"/>
-      <c r="S32" s="16"/>
     </row>
     <row r="33" s="1" customFormat="1" spans="1:19">
       <c r="A33" s="1">
-        <f t="shared" si="4"/>
-        <v>2004002</v>
+        <f t="shared" si="5"/>
+        <v>2001012</v>
       </c>
       <c r="B33" s="12">
-        <v>200400</v>
+        <v>200101</v>
       </c>
       <c r="C33" s="12">
         <v>2</v>
       </c>
-      <c r="D33" s="16" t="s">
-        <v>53</v>
+      <c r="D33" s="12" t="str">
+        <f t="shared" ref="D33:D37" si="6">D32</f>
+        <v>龍虎鬥</v>
       </c>
       <c r="E33" s="13">
-        <v>200400009</v>
+        <v>200101001</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>54</v>
@@ -3115,26 +3113,25 @@
       <c r="O33" s="15">
         <v>1990000</v>
       </c>
-      <c r="Q33" s="3"/>
-      <c r="R33" s="16"/>
-      <c r="S33" s="16"/>
+      <c r="S33" s="3"/>
     </row>
     <row r="34" s="1" customFormat="1" spans="1:19">
       <c r="A34" s="1">
-        <f t="shared" si="4"/>
-        <v>2004003</v>
+        <f t="shared" si="5"/>
+        <v>2001013</v>
       </c>
       <c r="B34" s="12">
-        <v>200400</v>
+        <v>200101</v>
       </c>
       <c r="C34" s="12">
         <v>2</v>
       </c>
-      <c r="D34" s="16" t="s">
-        <v>53</v>
+      <c r="D34" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>龍虎鬥</v>
       </c>
       <c r="E34" s="13">
-        <v>200400009</v>
+        <v>200101001</v>
       </c>
       <c r="F34" s="13" t="s">
         <v>54</v>
@@ -3166,17 +3163,15 @@
       <c r="O34" s="15">
         <v>1990000</v>
       </c>
-      <c r="Q34" s="3"/>
-      <c r="R34" s="16"/>
-      <c r="S34" s="16"/>
+      <c r="S34" s="3"/>
     </row>
     <row r="35" spans="1:19">
       <c r="A35" s="1">
-        <f t="shared" si="4"/>
-        <v>2005001</v>
+        <f t="shared" si="5"/>
+        <v>2003001</v>
       </c>
       <c r="B35" s="12">
-        <v>200500</v>
+        <v>200300</v>
       </c>
       <c r="C35" s="12">
         <v>2</v>
@@ -3185,7 +3180,7 @@
         <v>55</v>
       </c>
       <c r="E35" s="13">
-        <v>200500025</v>
+        <v>200300001</v>
       </c>
       <c r="F35" s="13" t="s">
         <v>56</v>
@@ -3209,7 +3204,7 @@
         <v>33</v>
       </c>
       <c r="M35" s="20" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="N35">
         <v>5000</v>
@@ -3217,26 +3212,24 @@
       <c r="O35" s="15">
         <v>1990000</v>
       </c>
-      <c r="Q35" s="3"/>
-      <c r="R35" s="16"/>
-      <c r="S35" s="16"/>
-    </row>
-    <row r="36" spans="1:19">
+    </row>
+    <row r="36" s="1" customFormat="1" spans="1:19">
       <c r="A36" s="1">
-        <f t="shared" si="4"/>
-        <v>2005002</v>
+        <f t="shared" si="5"/>
+        <v>2003002</v>
       </c>
       <c r="B36" s="12">
-        <v>200500</v>
+        <v>200300</v>
       </c>
       <c r="C36" s="12">
         <v>2</v>
       </c>
-      <c r="D36" s="12" t="s">
-        <v>55</v>
+      <c r="D36" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>飛禽走獸</v>
       </c>
       <c r="E36" s="13">
-        <v>200500025</v>
+        <v>200300001</v>
       </c>
       <c r="F36" s="13" t="s">
         <v>56</v>
@@ -3260,7 +3253,7 @@
         <v>33</v>
       </c>
       <c r="M36" s="20" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="N36">
         <v>500000</v>
@@ -3269,25 +3262,26 @@
         <v>1990000</v>
       </c>
       <c r="Q36" s="3"/>
-      <c r="R36" s="16"/>
-      <c r="S36" s="16"/>
-    </row>
-    <row r="37" spans="1:19">
+      <c r="R36" s="12"/>
+      <c r="S36" s="3"/>
+    </row>
+    <row r="37" s="1" customFormat="1" spans="1:19">
       <c r="A37" s="1">
-        <f t="shared" si="4"/>
-        <v>2005003</v>
+        <f t="shared" si="5"/>
+        <v>2003003</v>
       </c>
       <c r="B37" s="12">
-        <v>200500</v>
+        <v>200300</v>
       </c>
       <c r="C37" s="12">
         <v>2</v>
       </c>
-      <c r="D37" s="12" t="s">
-        <v>55</v>
+      <c r="D37" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>飛禽走獸</v>
       </c>
       <c r="E37" s="13">
-        <v>200500025</v>
+        <v>200300001</v>
       </c>
       <c r="F37" s="13" t="s">
         <v>56</v>
@@ -3311,7 +3305,7 @@
         <v>33</v>
       </c>
       <c r="M37" s="20" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="N37">
         <v>50000000</v>
@@ -3325,23 +3319,23 @@
     </row>
     <row r="38" spans="1:19">
       <c r="A38" s="1">
-        <f t="shared" si="4"/>
-        <v>2006001</v>
+        <f t="shared" si="5"/>
+        <v>2004001</v>
       </c>
       <c r="B38" s="12">
-        <v>200600</v>
+        <v>200400</v>
       </c>
       <c r="C38" s="12">
         <v>2</v>
       </c>
-      <c r="D38" s="13" t="s">
+      <c r="D38" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="E38" s="13">
+        <v>200400009</v>
+      </c>
+      <c r="F38" s="13" t="s">
         <v>58</v>
-      </c>
-      <c r="E38" s="13">
-        <v>200600001</v>
-      </c>
-      <c r="F38" s="13" t="s">
-        <v>59</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>32</v>
@@ -3376,23 +3370,23 @@
     </row>
     <row r="39" s="1" customFormat="1" spans="1:19">
       <c r="A39" s="1">
-        <f t="shared" si="4"/>
-        <v>2006002</v>
+        <f t="shared" si="5"/>
+        <v>2004002</v>
       </c>
       <c r="B39" s="12">
-        <v>200600</v>
+        <v>200400</v>
       </c>
       <c r="C39" s="12">
         <v>2</v>
       </c>
-      <c r="D39" s="13" t="s">
+      <c r="D39" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="E39" s="13">
+        <v>200400009</v>
+      </c>
+      <c r="F39" s="13" t="s">
         <v>58</v>
-      </c>
-      <c r="E39" s="13">
-        <v>200600001</v>
-      </c>
-      <c r="F39" s="13" t="s">
-        <v>59</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>35</v>
@@ -3427,23 +3421,23 @@
     </row>
     <row r="40" s="1" customFormat="1" spans="1:19">
       <c r="A40" s="1">
-        <f t="shared" si="4"/>
-        <v>2006003</v>
+        <f t="shared" si="5"/>
+        <v>2004003</v>
       </c>
       <c r="B40" s="12">
-        <v>200600</v>
+        <v>200400</v>
       </c>
       <c r="C40" s="12">
         <v>2</v>
       </c>
-      <c r="D40" s="13" t="s">
+      <c r="D40" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="E40" s="13">
+        <v>200400009</v>
+      </c>
+      <c r="F40" s="13" t="s">
         <v>58</v>
-      </c>
-      <c r="E40" s="13">
-        <v>200600001</v>
-      </c>
-      <c r="F40" s="13" t="s">
-        <v>59</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>36</v>
@@ -3473,28 +3467,28 @@
         <v>1990000</v>
       </c>
       <c r="Q40" s="3"/>
-      <c r="R40"/>
+      <c r="R40" s="16"/>
       <c r="S40" s="16"/>
     </row>
     <row r="41" spans="1:19">
       <c r="A41" s="1">
-        <f t="shared" si="4"/>
-        <v>2007001</v>
+        <f t="shared" si="5"/>
+        <v>2005001</v>
       </c>
       <c r="B41" s="12">
-        <v>200700</v>
+        <v>200500</v>
       </c>
       <c r="C41" s="12">
         <v>2</v>
       </c>
       <c r="D41" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E41" s="13">
+        <v>200500025</v>
+      </c>
+      <c r="F41" s="13" t="s">
         <v>60</v>
-      </c>
-      <c r="E41" s="13">
-        <v>200700001</v>
-      </c>
-      <c r="F41" s="13" t="s">
-        <v>61</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>32</v>
@@ -3515,7 +3509,7 @@
         <v>33</v>
       </c>
       <c r="M41" s="20" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="N41">
         <v>5000</v>
@@ -3527,26 +3521,25 @@
       <c r="R41" s="16"/>
       <c r="S41" s="16"/>
     </row>
-    <row r="42" s="1" customFormat="1" spans="1:19">
+    <row r="42" spans="1:19">
       <c r="A42" s="1">
-        <f t="shared" si="4"/>
-        <v>2007002</v>
+        <f t="shared" si="5"/>
+        <v>2005002</v>
       </c>
       <c r="B42" s="12">
-        <v>200700</v>
+        <v>200500</v>
       </c>
       <c r="C42" s="12">
         <v>2</v>
       </c>
-      <c r="D42" s="12" t="str">
-        <f t="shared" ref="D39:D43" si="6">D41</f>
-        <v>越南色碟</v>
+      <c r="D42" s="12" t="s">
+        <v>59</v>
       </c>
       <c r="E42" s="13">
-        <v>200700001</v>
+        <v>200500025</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>35</v>
@@ -3567,7 +3560,7 @@
         <v>33</v>
       </c>
       <c r="M42" s="20" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="N42">
         <v>500000</v>
@@ -3579,26 +3572,25 @@
       <c r="R42" s="16"/>
       <c r="S42" s="16"/>
     </row>
-    <row r="43" s="1" customFormat="1" spans="1:19">
+    <row r="43" spans="1:19">
       <c r="A43" s="1">
-        <f t="shared" si="4"/>
-        <v>2007003</v>
+        <f t="shared" si="5"/>
+        <v>2005003</v>
       </c>
       <c r="B43" s="12">
-        <v>200700</v>
+        <v>200500</v>
       </c>
       <c r="C43" s="12">
         <v>2</v>
       </c>
-      <c r="D43" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v>越南色碟</v>
+      <c r="D43" s="12" t="s">
+        <v>59</v>
       </c>
       <c r="E43" s="13">
-        <v>200700001</v>
+        <v>200500025</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>36</v>
@@ -3619,7 +3611,7 @@
         <v>33</v>
       </c>
       <c r="M43" s="20" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="N43">
         <v>50000000</v>
@@ -3627,15 +3619,17 @@
       <c r="O43" s="15">
         <v>1990000</v>
       </c>
-      <c r="S43" s="3"/>
-    </row>
-    <row r="44" s="1" customFormat="1" spans="1:19">
+      <c r="Q43" s="3"/>
+      <c r="R43" s="16"/>
+      <c r="S43" s="16"/>
+    </row>
+    <row r="44" spans="1:19">
       <c r="A44" s="1">
-        <f t="shared" si="4"/>
-        <v>2008001</v>
+        <f t="shared" si="5"/>
+        <v>2006001</v>
       </c>
       <c r="B44" s="12">
-        <v>200800</v>
+        <v>200600</v>
       </c>
       <c r="C44" s="12">
         <v>2</v>
@@ -3644,7 +3638,7 @@
         <v>62</v>
       </c>
       <c r="E44" s="13">
-        <v>200800001</v>
+        <v>200600001</v>
       </c>
       <c r="F44" s="13" t="s">
         <v>63</v>
@@ -3676,15 +3670,17 @@
       <c r="O44" s="15">
         <v>1990000</v>
       </c>
-      <c r="S44" s="3"/>
+      <c r="Q44" s="3"/>
+      <c r="R44" s="16"/>
+      <c r="S44" s="16"/>
     </row>
     <row r="45" s="1" customFormat="1" spans="1:19">
       <c r="A45" s="1">
-        <f t="shared" si="4"/>
-        <v>2008002</v>
+        <f t="shared" si="5"/>
+        <v>2006002</v>
       </c>
       <c r="B45" s="12">
-        <v>200800</v>
+        <v>200600</v>
       </c>
       <c r="C45" s="12">
         <v>2</v>
@@ -3693,7 +3689,7 @@
         <v>62</v>
       </c>
       <c r="E45" s="13">
-        <v>200800001</v>
+        <v>200600001</v>
       </c>
       <c r="F45" s="13" t="s">
         <v>63</v>
@@ -3725,15 +3721,17 @@
       <c r="O45" s="15">
         <v>1990000</v>
       </c>
-      <c r="S45" s="3"/>
+      <c r="Q45" s="3"/>
+      <c r="R45" s="16"/>
+      <c r="S45" s="16"/>
     </row>
     <row r="46" s="1" customFormat="1" spans="1:19">
       <c r="A46" s="1">
-        <f t="shared" si="4"/>
-        <v>2008003</v>
+        <f t="shared" si="5"/>
+        <v>2006003</v>
       </c>
       <c r="B46" s="12">
-        <v>200800</v>
+        <v>200600</v>
       </c>
       <c r="C46" s="12">
         <v>2</v>
@@ -3742,7 +3740,7 @@
         <v>62</v>
       </c>
       <c r="E46" s="13">
-        <v>200800001</v>
+        <v>200600001</v>
       </c>
       <c r="F46" s="13" t="s">
         <v>63</v>
@@ -3774,24 +3772,26 @@
       <c r="O46" s="15">
         <v>1990000</v>
       </c>
-      <c r="S46" s="3"/>
+      <c r="Q46" s="3"/>
+      <c r="R46"/>
+      <c r="S46" s="16"/>
     </row>
     <row r="47" spans="1:19">
       <c r="A47" s="1">
-        <f t="shared" si="4"/>
-        <v>2009001</v>
-      </c>
-      <c r="B47" s="17">
-        <v>200900</v>
+        <f t="shared" si="5"/>
+        <v>2007001</v>
+      </c>
+      <c r="B47" s="12">
+        <v>200700</v>
       </c>
       <c r="C47" s="12">
         <v>2</v>
       </c>
-      <c r="D47" s="17" t="s">
+      <c r="D47" s="12" t="s">
         <v>64</v>
       </c>
       <c r="E47" s="13">
-        <v>200900001</v>
+        <v>200700001</v>
       </c>
       <c r="F47" s="13" t="s">
         <v>65</v>
@@ -3823,24 +3823,27 @@
       <c r="O47" s="15">
         <v>1990000</v>
       </c>
-    </row>
-    <row r="48" spans="1:19">
+      <c r="Q47" s="3"/>
+      <c r="R47" s="16"/>
+      <c r="S47" s="16"/>
+    </row>
+    <row r="48" s="1" customFormat="1" spans="1:19">
       <c r="A48" s="1">
-        <f t="shared" si="4"/>
-        <v>2009002</v>
+        <f t="shared" si="5"/>
+        <v>2007002</v>
       </c>
       <c r="B48" s="12">
-        <v>200900</v>
+        <v>200700</v>
       </c>
       <c r="C48" s="12">
         <v>2</v>
       </c>
       <c r="D48" s="12" t="str">
-        <f>D47</f>
-        <v>魚蝦蟹</v>
+        <f t="shared" ref="D45:D49" si="7">D47</f>
+        <v>越南色碟</v>
       </c>
       <c r="E48" s="13">
-        <v>200900001</v>
+        <v>200700001</v>
       </c>
       <c r="F48" s="13" t="s">
         <v>65</v>
@@ -3872,24 +3875,27 @@
       <c r="O48" s="15">
         <v>1990000</v>
       </c>
-    </row>
-    <row r="49" spans="1:19">
+      <c r="Q48" s="3"/>
+      <c r="R48" s="16"/>
+      <c r="S48" s="16"/>
+    </row>
+    <row r="49" s="1" customFormat="1" spans="1:19">
       <c r="A49" s="1">
-        <f t="shared" si="4"/>
-        <v>2009003</v>
+        <f t="shared" si="5"/>
+        <v>2007003</v>
       </c>
       <c r="B49" s="12">
-        <v>200900</v>
+        <v>200700</v>
       </c>
       <c r="C49" s="12">
         <v>2</v>
       </c>
       <c r="D49" s="12" t="str">
-        <f>D48</f>
-        <v>魚蝦蟹</v>
+        <f t="shared" si="7"/>
+        <v>越南色碟</v>
       </c>
       <c r="E49" s="13">
-        <v>200900001</v>
+        <v>200700001</v>
       </c>
       <c r="F49" s="13" t="s">
         <v>65</v>
@@ -3921,25 +3927,28 @@
       <c r="O49" s="15">
         <v>1990000</v>
       </c>
-    </row>
-    <row r="50" spans="1:19">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" s="1" customFormat="1" spans="1:19">
       <c r="A50" s="1">
-        <f t="shared" si="4"/>
-        <v>2010001</v>
+        <f t="shared" si="5"/>
+        <v>2008001</v>
       </c>
       <c r="B50" s="12">
-        <v>201000</v>
+        <v>200800</v>
       </c>
       <c r="C50" s="12">
         <v>2</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D50" s="13" t="s">
         <v>66</v>
       </c>
       <c r="E50" s="13">
-        <v>101000006</v>
-      </c>
-      <c r="F50" s="13"/>
+        <v>200800001</v>
+      </c>
+      <c r="F50" s="13" t="s">
+        <v>67</v>
+      </c>
       <c r="G50" s="1" t="s">
         <v>32</v>
       </c>
@@ -3967,25 +3976,28 @@
       <c r="O50" s="15">
         <v>1990000</v>
       </c>
-    </row>
-    <row r="51" spans="1:19">
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" s="1" customFormat="1" spans="1:19">
       <c r="A51" s="1">
-        <f t="shared" si="4"/>
-        <v>2010002</v>
+        <f t="shared" si="5"/>
+        <v>2008002</v>
       </c>
       <c r="B51" s="12">
-        <v>201000</v>
+        <v>200800</v>
       </c>
       <c r="C51" s="12">
         <v>2</v>
       </c>
-      <c r="D51" s="12" t="s">
+      <c r="D51" s="13" t="s">
         <v>66</v>
       </c>
       <c r="E51" s="13">
-        <v>101000006</v>
-      </c>
-      <c r="F51" s="13"/>
+        <v>200800001</v>
+      </c>
+      <c r="F51" s="13" t="s">
+        <v>67</v>
+      </c>
       <c r="G51" s="1" t="s">
         <v>35</v>
       </c>
@@ -4013,25 +4025,28 @@
       <c r="O51" s="15">
         <v>1990000</v>
       </c>
-    </row>
-    <row r="52" spans="1:19">
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" s="1" customFormat="1" spans="1:19">
       <c r="A52" s="1">
-        <f t="shared" si="4"/>
-        <v>2010003</v>
+        <f t="shared" si="5"/>
+        <v>2008003</v>
       </c>
       <c r="B52" s="12">
-        <v>201000</v>
+        <v>200800</v>
       </c>
       <c r="C52" s="12">
         <v>2</v>
       </c>
-      <c r="D52" s="12" t="s">
+      <c r="D52" s="13" t="s">
         <v>66</v>
       </c>
       <c r="E52" s="13">
-        <v>101000006</v>
-      </c>
-      <c r="F52" s="13"/>
+        <v>200800001</v>
+      </c>
+      <c r="F52" s="13" t="s">
+        <v>67</v>
+      </c>
       <c r="G52" s="1" t="s">
         <v>36</v>
       </c>
@@ -4059,26 +4074,27 @@
       <c r="O52" s="15">
         <v>1990000</v>
       </c>
+      <c r="S52" s="3"/>
     </row>
     <row r="53" spans="1:19">
       <c r="A53" s="1">
-        <f t="shared" si="4"/>
-        <v>3001001</v>
-      </c>
-      <c r="B53" s="12">
-        <v>300100</v>
+        <f t="shared" si="5"/>
+        <v>2009001</v>
+      </c>
+      <c r="B53" s="17">
+        <v>200900</v>
       </c>
       <c r="C53" s="12">
-        <v>3</v>
-      </c>
-      <c r="D53" s="12" t="s">
-        <v>67</v>
+        <v>2</v>
+      </c>
+      <c r="D53" s="17" t="s">
+        <v>68</v>
       </c>
       <c r="E53" s="13">
-        <v>300100001</v>
+        <v>200900001</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>32</v>
@@ -4095,11 +4111,11 @@
       <c r="K53" s="1">
         <v>0</v>
       </c>
-      <c r="L53" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="M53" s="21" t="s">
-        <v>70</v>
+      <c r="L53" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M53" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N53">
         <v>5000</v>
@@ -4108,25 +4124,26 @@
         <v>1990000</v>
       </c>
     </row>
-    <row r="54" s="1" customFormat="1" spans="1:19">
+    <row r="54" spans="1:19">
       <c r="A54" s="1">
-        <f t="shared" si="4"/>
-        <v>3001002</v>
+        <f t="shared" si="5"/>
+        <v>2009002</v>
       </c>
       <c r="B54" s="12">
-        <v>300100</v>
+        <v>200900</v>
       </c>
       <c r="C54" s="12">
-        <v>3</v>
-      </c>
-      <c r="D54" s="12" t="s">
-        <v>67</v>
+        <v>2</v>
+      </c>
+      <c r="D54" s="12" t="str">
+        <f>D53</f>
+        <v>魚蝦蟹</v>
       </c>
       <c r="E54" s="13">
-        <v>300100001</v>
+        <v>200900001</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>35</v>
@@ -4143,11 +4160,11 @@
       <c r="K54" s="1">
         <v>0</v>
       </c>
-      <c r="L54" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="M54" s="21" t="s">
-        <v>70</v>
+      <c r="L54" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M54" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N54">
         <v>500000</v>
@@ -4155,27 +4172,27 @@
       <c r="O54" s="15">
         <v>1990000</v>
       </c>
-      <c r="S54" s="3"/>
-    </row>
-    <row r="55" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="55" spans="1:19">
       <c r="A55" s="1">
-        <f t="shared" si="4"/>
-        <v>3001003</v>
+        <f t="shared" si="5"/>
+        <v>2009003</v>
       </c>
       <c r="B55" s="12">
-        <v>300100</v>
+        <v>200900</v>
       </c>
       <c r="C55" s="12">
-        <v>3</v>
-      </c>
-      <c r="D55" s="12" t="s">
-        <v>67</v>
+        <v>2</v>
+      </c>
+      <c r="D55" s="12" t="str">
+        <f>D54</f>
+        <v>魚蝦蟹</v>
       </c>
       <c r="E55" s="13">
-        <v>300100001</v>
+        <v>200900001</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>36</v>
@@ -4192,11 +4209,11 @@
       <c r="K55" s="1">
         <v>0</v>
       </c>
-      <c r="L55" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="M55" s="21" t="s">
-        <v>70</v>
+      <c r="L55" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M55" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N55">
         <v>50000000</v>
@@ -4204,28 +4221,25 @@
       <c r="O55" s="15">
         <v>1990000</v>
       </c>
-      <c r="S55" s="3"/>
-    </row>
-    <row r="56" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="56" spans="1:19">
       <c r="A56" s="1">
-        <f t="shared" si="4"/>
-        <v>3002001</v>
+        <f t="shared" si="5"/>
+        <v>2010001</v>
       </c>
       <c r="B56" s="12">
-        <v>300200</v>
+        <v>201000</v>
       </c>
       <c r="C56" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E56" s="13">
-        <v>300200006</v>
-      </c>
-      <c r="F56" s="13" t="s">
-        <v>72</v>
-      </c>
+        <v>101000006</v>
+      </c>
+      <c r="F56" s="13"/>
       <c r="G56" s="1" t="s">
         <v>32</v>
       </c>
@@ -4233,7 +4247,7 @@
         <v>1</v>
       </c>
       <c r="I56" s="1">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="J56" s="1">
         <v>-1</v>
@@ -4241,11 +4255,11 @@
       <c r="K56" s="1">
         <v>0</v>
       </c>
-      <c r="L56" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="M56" s="21" t="s">
-        <v>70</v>
+      <c r="L56" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M56" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N56">
         <v>5000</v>
@@ -4253,28 +4267,25 @@
       <c r="O56" s="15">
         <v>1990000</v>
       </c>
-      <c r="S56" s="3"/>
-    </row>
-    <row r="57" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="57" spans="1:19">
       <c r="A57" s="1">
-        <f t="shared" si="4"/>
-        <v>3002002</v>
+        <f t="shared" si="5"/>
+        <v>2010002</v>
       </c>
       <c r="B57" s="12">
-        <v>300200</v>
+        <v>201000</v>
       </c>
       <c r="C57" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E57" s="13">
-        <v>300200006</v>
-      </c>
-      <c r="F57" s="13" t="s">
-        <v>72</v>
-      </c>
+        <v>101000006</v>
+      </c>
+      <c r="F57" s="13"/>
       <c r="G57" s="1" t="s">
         <v>35</v>
       </c>
@@ -4290,11 +4301,11 @@
       <c r="K57" s="1">
         <v>0</v>
       </c>
-      <c r="L57" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="M57" s="21" t="s">
-        <v>70</v>
+      <c r="L57" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M57" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N57">
         <v>500000</v>
@@ -4302,28 +4313,25 @@
       <c r="O57" s="15">
         <v>1990000</v>
       </c>
-      <c r="S57" s="3"/>
-    </row>
-    <row r="58" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="58" spans="1:19">
       <c r="A58" s="1">
-        <f t="shared" si="4"/>
-        <v>3002003</v>
+        <f t="shared" si="5"/>
+        <v>2010003</v>
       </c>
       <c r="B58" s="12">
-        <v>300200</v>
+        <v>201000</v>
       </c>
       <c r="C58" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E58" s="13">
-        <v>300200006</v>
-      </c>
-      <c r="F58" s="13" t="s">
-        <v>72</v>
-      </c>
+        <v>101000006</v>
+      </c>
+      <c r="F58" s="13"/>
       <c r="G58" s="1" t="s">
         <v>36</v>
       </c>
@@ -4339,11 +4347,11 @@
       <c r="K58" s="1">
         <v>0</v>
       </c>
-      <c r="L58" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="M58" s="21" t="s">
-        <v>70</v>
+      <c r="L58" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M58" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N58">
         <v>50000000</v>
@@ -4351,309 +4359,307 @@
       <c r="O58" s="15">
         <v>1990000</v>
       </c>
-      <c r="S58" s="3"/>
-    </row>
-    <row r="59" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="59" spans="1:19">
       <c r="A59" s="1">
-        <f t="shared" ref="A59:A65" si="7">B59*100+H59</f>
-        <v>20010010</v>
-      </c>
-      <c r="B59" s="13">
-        <v>200100</v>
-      </c>
-      <c r="C59" s="13">
-        <v>2</v>
-      </c>
-      <c r="D59" s="13" t="s">
-        <v>47</v>
+        <f t="shared" si="5"/>
+        <v>3001001</v>
+      </c>
+      <c r="B59" s="12">
+        <v>300100</v>
+      </c>
+      <c r="C59" s="12">
+        <v>3</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>71</v>
       </c>
       <c r="E59" s="13">
-        <v>200100038</v>
+        <v>300100001</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="G59" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H59" s="1">
+        <v>1</v>
+      </c>
+      <c r="I59" s="1">
+        <v>0</v>
+      </c>
+      <c r="J59" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K59" s="1">
+        <v>0</v>
+      </c>
+      <c r="L59" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="M59" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="H59" s="18">
-        <v>10</v>
-      </c>
-      <c r="I59" s="18">
-        <v>0</v>
-      </c>
-      <c r="J59" s="18">
-        <v>-1</v>
-      </c>
-      <c r="K59" s="1">
-        <v>0</v>
-      </c>
-      <c r="L59" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="M59" s="18">
-        <v>0</v>
-      </c>
       <c r="N59">
-        <v>200</v>
-      </c>
-      <c r="O59" s="19">
-        <v>1980000</v>
-      </c>
-      <c r="S59" s="3"/>
+        <v>5000</v>
+      </c>
+      <c r="O59" s="15">
+        <v>1990000</v>
+      </c>
     </row>
     <row r="60" s="1" customFormat="1" spans="1:19">
       <c r="A60" s="1">
-        <f t="shared" si="7"/>
-        <v>20010011</v>
-      </c>
-      <c r="B60" s="13">
-        <v>200100</v>
-      </c>
-      <c r="C60" s="13">
-        <v>2</v>
-      </c>
-      <c r="D60" s="13" t="s">
-        <v>47</v>
+        <f t="shared" si="5"/>
+        <v>3001002</v>
+      </c>
+      <c r="B60" s="12">
+        <v>300100</v>
+      </c>
+      <c r="C60" s="12">
+        <v>3</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>71</v>
       </c>
       <c r="E60" s="13">
-        <v>200100038</v>
+        <v>300100001</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="G60" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="H60" s="18">
-        <v>11</v>
-      </c>
-      <c r="I60" s="18">
-        <v>0</v>
-      </c>
-      <c r="J60" s="18">
+        <v>72</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H60" s="1">
+        <v>2</v>
+      </c>
+      <c r="I60" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J60" s="1">
         <v>-1</v>
       </c>
       <c r="K60" s="1">
         <v>0</v>
       </c>
-      <c r="L60" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="M60" s="18">
-        <v>0</v>
+      <c r="L60" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="M60" s="21" t="s">
+        <v>74</v>
       </c>
       <c r="N60">
-        <v>5000</v>
-      </c>
-      <c r="O60" s="19">
-        <v>1980000</v>
+        <v>500000</v>
+      </c>
+      <c r="O60" s="15">
+        <v>1990000</v>
       </c>
       <c r="S60" s="3"/>
     </row>
     <row r="61" s="1" customFormat="1" spans="1:19">
       <c r="A61" s="1">
-        <f t="shared" si="7"/>
-        <v>20010012</v>
-      </c>
-      <c r="B61" s="13">
-        <v>200100</v>
-      </c>
-      <c r="C61" s="13">
-        <v>2</v>
-      </c>
-      <c r="D61" s="13" t="s">
-        <v>47</v>
+        <f t="shared" si="5"/>
+        <v>3001003</v>
+      </c>
+      <c r="B61" s="12">
+        <v>300100</v>
+      </c>
+      <c r="C61" s="12">
+        <v>3</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>71</v>
       </c>
       <c r="E61" s="13">
-        <v>200100038</v>
+        <v>300100001</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="G61" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="H61" s="18">
-        <v>12</v>
-      </c>
-      <c r="I61" s="18">
-        <v>0</v>
-      </c>
-      <c r="J61" s="18">
+        <v>72</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H61" s="1">
+        <v>3</v>
+      </c>
+      <c r="I61" s="1">
+        <v>50000000</v>
+      </c>
+      <c r="J61" s="1">
         <v>-1</v>
       </c>
       <c r="K61" s="1">
         <v>0</v>
       </c>
-      <c r="L61" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="M61" s="18">
-        <v>0</v>
+      <c r="L61" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="M61" s="21" t="s">
+        <v>74</v>
       </c>
       <c r="N61">
-        <v>100000</v>
-      </c>
-      <c r="O61" s="19">
-        <v>1980000</v>
+        <v>50000000</v>
+      </c>
+      <c r="O61" s="15">
+        <v>1990000</v>
       </c>
       <c r="S61" s="3"/>
     </row>
     <row r="62" s="1" customFormat="1" spans="1:19">
       <c r="A62" s="1">
-        <f t="shared" si="7"/>
-        <v>20010110</v>
-      </c>
-      <c r="B62" s="13">
-        <v>200101</v>
-      </c>
-      <c r="C62" s="13">
-        <v>2</v>
-      </c>
-      <c r="D62" s="13" t="s">
-        <v>49</v>
+        <f t="shared" si="5"/>
+        <v>3002001</v>
+      </c>
+      <c r="B62" s="12">
+        <v>300200</v>
+      </c>
+      <c r="C62" s="12">
+        <v>3</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>75</v>
       </c>
       <c r="E62" s="13">
-        <v>200101001</v>
+        <v>300200006</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G62" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H62" s="1">
+        <v>1</v>
+      </c>
+      <c r="I62" s="1">
+        <v>2000</v>
+      </c>
+      <c r="J62" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K62" s="1">
+        <v>0</v>
+      </c>
+      <c r="L62" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="M62" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="H62" s="18">
-        <v>10</v>
-      </c>
-      <c r="I62" s="18">
-        <v>0</v>
-      </c>
-      <c r="J62" s="18">
-        <v>-1</v>
-      </c>
-      <c r="K62" s="1">
-        <v>0</v>
-      </c>
-      <c r="L62" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="M62" s="18">
-        <v>0</v>
-      </c>
       <c r="N62">
-        <v>200</v>
-      </c>
-      <c r="O62" s="19">
-        <v>1980000</v>
+        <v>5000</v>
+      </c>
+      <c r="O62" s="15">
+        <v>1990000</v>
       </c>
       <c r="S62" s="3"/>
     </row>
     <row r="63" s="1" customFormat="1" spans="1:19">
       <c r="A63" s="1">
-        <f t="shared" si="7"/>
-        <v>20010111</v>
-      </c>
-      <c r="B63" s="13">
-        <v>200101</v>
-      </c>
-      <c r="C63" s="13">
-        <v>2</v>
-      </c>
-      <c r="D63" s="13" t="s">
-        <v>49</v>
+        <f t="shared" si="5"/>
+        <v>3002002</v>
+      </c>
+      <c r="B63" s="12">
+        <v>300200</v>
+      </c>
+      <c r="C63" s="12">
+        <v>3</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>75</v>
       </c>
       <c r="E63" s="13">
-        <v>200101001</v>
+        <v>300200006</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G63" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="H63" s="18">
-        <v>11</v>
-      </c>
-      <c r="I63" s="18">
-        <v>0</v>
-      </c>
-      <c r="J63" s="18">
+      <c r="G63" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H63" s="1">
+        <v>2</v>
+      </c>
+      <c r="I63" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J63" s="1">
         <v>-1</v>
       </c>
       <c r="K63" s="1">
         <v>0</v>
       </c>
-      <c r="L63" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="M63" s="18">
-        <v>0</v>
+      <c r="L63" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="M63" s="21" t="s">
+        <v>74</v>
       </c>
       <c r="N63">
-        <v>5000</v>
-      </c>
-      <c r="O63" s="19">
-        <v>1980000</v>
+        <v>500000</v>
+      </c>
+      <c r="O63" s="15">
+        <v>1990000</v>
       </c>
       <c r="S63" s="3"/>
     </row>
     <row r="64" s="1" customFormat="1" spans="1:19">
       <c r="A64" s="1">
-        <f t="shared" si="7"/>
-        <v>20010112</v>
-      </c>
-      <c r="B64" s="13">
-        <v>200101</v>
-      </c>
-      <c r="C64" s="13">
-        <v>2</v>
-      </c>
-      <c r="D64" s="13" t="s">
-        <v>49</v>
+        <f t="shared" si="5"/>
+        <v>3002003</v>
+      </c>
+      <c r="B64" s="12">
+        <v>300200</v>
+      </c>
+      <c r="C64" s="12">
+        <v>3</v>
+      </c>
+      <c r="D64" s="12" t="s">
+        <v>75</v>
       </c>
       <c r="E64" s="13">
-        <v>200101001</v>
+        <v>300200006</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G64" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H64" s="1">
+        <v>3</v>
+      </c>
+      <c r="I64" s="1">
+        <v>50000000</v>
+      </c>
+      <c r="J64" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K64" s="1">
+        <v>0</v>
+      </c>
+      <c r="L64" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="H64" s="18">
-        <v>12</v>
-      </c>
-      <c r="I64" s="18">
-        <v>0</v>
-      </c>
-      <c r="J64" s="18">
-        <v>-1</v>
-      </c>
-      <c r="K64" s="1">
-        <v>0</v>
-      </c>
-      <c r="L64" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="M64" s="18">
-        <v>0</v>
+      <c r="M64" s="21" t="s">
+        <v>74</v>
       </c>
       <c r="N64">
-        <v>100000</v>
-      </c>
-      <c r="O64" s="19">
-        <v>1980000</v>
+        <v>50000000</v>
+      </c>
+      <c r="O64" s="15">
+        <v>1990000</v>
       </c>
       <c r="S64" s="3"/>
     </row>
     <row r="65" s="1" customFormat="1" spans="1:19">
       <c r="A65" s="1">
-        <f t="shared" si="7"/>
-        <v>20030010</v>
+        <f t="shared" ref="A65:A71" si="8">B65*100+H65</f>
+        <v>20010010</v>
       </c>
       <c r="B65" s="13">
-        <v>200300</v>
+        <v>200100</v>
       </c>
       <c r="C65" s="13">
         <v>2</v>
@@ -4662,13 +4668,13 @@
         <v>51</v>
       </c>
       <c r="E65" s="13">
-        <v>200300001</v>
+        <v>200100038</v>
       </c>
       <c r="F65" s="13" t="s">
         <v>52</v>
       </c>
       <c r="G65" s="18" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H65" s="18">
         <v>10</v>
@@ -4683,7 +4689,7 @@
         <v>0</v>
       </c>
       <c r="L65" s="18" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="M65" s="18">
         <v>0</v>
@@ -4698,11 +4704,11 @@
     </row>
     <row r="66" s="1" customFormat="1" spans="1:19">
       <c r="A66" s="1">
-        <f t="shared" ref="A66:A74" si="8">B66*100+H66</f>
-        <v>20030011</v>
+        <f t="shared" si="8"/>
+        <v>20010011</v>
       </c>
       <c r="B66" s="13">
-        <v>200300</v>
+        <v>200100</v>
       </c>
       <c r="C66" s="13">
         <v>2</v>
@@ -4711,13 +4717,13 @@
         <v>51</v>
       </c>
       <c r="E66" s="13">
-        <v>200300001</v>
+        <v>200100038</v>
       </c>
       <c r="F66" s="13" t="s">
         <v>52</v>
       </c>
       <c r="G66" s="18" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H66" s="18">
         <v>11</v>
@@ -4732,7 +4738,7 @@
         <v>0</v>
       </c>
       <c r="L66" s="18" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="M66" s="18">
         <v>0</v>
@@ -4748,10 +4754,10 @@
     <row r="67" s="1" customFormat="1" spans="1:19">
       <c r="A67" s="1">
         <f t="shared" si="8"/>
-        <v>20030012</v>
+        <v>20010012</v>
       </c>
       <c r="B67" s="13">
-        <v>200300</v>
+        <v>200100</v>
       </c>
       <c r="C67" s="13">
         <v>2</v>
@@ -4760,13 +4766,13 @@
         <v>51</v>
       </c>
       <c r="E67" s="13">
-        <v>200300001</v>
+        <v>200100038</v>
       </c>
       <c r="F67" s="13" t="s">
         <v>52</v>
       </c>
       <c r="G67" s="18" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="H67" s="18">
         <v>12</v>
@@ -4781,7 +4787,7 @@
         <v>0</v>
       </c>
       <c r="L67" s="18" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="M67" s="18">
         <v>0</v>
@@ -4797,25 +4803,25 @@
     <row r="68" s="1" customFormat="1" spans="1:19">
       <c r="A68" s="1">
         <f t="shared" si="8"/>
-        <v>20040010</v>
+        <v>20010110</v>
       </c>
       <c r="B68" s="13">
-        <v>200400</v>
+        <v>200101</v>
       </c>
       <c r="C68" s="13">
         <v>2</v>
       </c>
-      <c r="D68" s="16" t="s">
+      <c r="D68" s="13" t="s">
         <v>53</v>
       </c>
       <c r="E68" s="13">
-        <v>200400009</v>
+        <v>200101001</v>
       </c>
       <c r="F68" s="13" t="s">
         <v>54</v>
       </c>
       <c r="G68" s="18" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H68" s="18">
         <v>10</v>
@@ -4830,7 +4836,7 @@
         <v>0</v>
       </c>
       <c r="L68" s="18" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="M68" s="18">
         <v>0</v>
@@ -4846,25 +4852,25 @@
     <row r="69" s="1" customFormat="1" spans="1:19">
       <c r="A69" s="1">
         <f t="shared" si="8"/>
-        <v>20040011</v>
+        <v>20010111</v>
       </c>
       <c r="B69" s="13">
-        <v>200400</v>
+        <v>200101</v>
       </c>
       <c r="C69" s="13">
         <v>2</v>
       </c>
-      <c r="D69" s="16" t="s">
+      <c r="D69" s="13" t="s">
         <v>53</v>
       </c>
       <c r="E69" s="13">
-        <v>200400009</v>
+        <v>200101001</v>
       </c>
       <c r="F69" s="13" t="s">
         <v>54</v>
       </c>
       <c r="G69" s="18" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H69" s="18">
         <v>11</v>
@@ -4879,7 +4885,7 @@
         <v>0</v>
       </c>
       <c r="L69" s="18" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="M69" s="18">
         <v>0</v>
@@ -4895,25 +4901,25 @@
     <row r="70" s="1" customFormat="1" spans="1:19">
       <c r="A70" s="1">
         <f t="shared" si="8"/>
-        <v>20040012</v>
+        <v>20010112</v>
       </c>
       <c r="B70" s="13">
-        <v>200400</v>
+        <v>200101</v>
       </c>
       <c r="C70" s="13">
         <v>2</v>
       </c>
-      <c r="D70" s="16" t="s">
+      <c r="D70" s="13" t="s">
         <v>53</v>
       </c>
       <c r="E70" s="13">
-        <v>200400009</v>
+        <v>200101001</v>
       </c>
       <c r="F70" s="13" t="s">
         <v>54</v>
       </c>
       <c r="G70" s="18" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="H70" s="18">
         <v>12</v>
@@ -4928,7 +4934,7 @@
         <v>0</v>
       </c>
       <c r="L70" s="18" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="M70" s="18">
         <v>0</v>
@@ -4944,10 +4950,10 @@
     <row r="71" s="1" customFormat="1" spans="1:19">
       <c r="A71" s="1">
         <f t="shared" si="8"/>
-        <v>20050010</v>
+        <v>20030010</v>
       </c>
       <c r="B71" s="13">
-        <v>200500</v>
+        <v>200300</v>
       </c>
       <c r="C71" s="13">
         <v>2</v>
@@ -4956,13 +4962,13 @@
         <v>55</v>
       </c>
       <c r="E71" s="13">
-        <v>200500025</v>
+        <v>200300001</v>
       </c>
       <c r="F71" s="13" t="s">
         <v>56</v>
       </c>
       <c r="G71" s="18" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H71" s="18">
         <v>10</v>
@@ -4977,7 +4983,7 @@
         <v>0</v>
       </c>
       <c r="L71" s="18" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="M71" s="18">
         <v>0</v>
@@ -4992,11 +4998,11 @@
     </row>
     <row r="72" s="1" customFormat="1" spans="1:19">
       <c r="A72" s="1">
-        <f t="shared" si="8"/>
-        <v>20050011</v>
+        <f t="shared" ref="A72:A80" si="9">B72*100+H72</f>
+        <v>20030011</v>
       </c>
       <c r="B72" s="13">
-        <v>200500</v>
+        <v>200300</v>
       </c>
       <c r="C72" s="13">
         <v>2</v>
@@ -5005,13 +5011,13 @@
         <v>55</v>
       </c>
       <c r="E72" s="13">
-        <v>200500025</v>
+        <v>200300001</v>
       </c>
       <c r="F72" s="13" t="s">
         <v>56</v>
       </c>
       <c r="G72" s="18" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H72" s="18">
         <v>11</v>
@@ -5026,7 +5032,7 @@
         <v>0</v>
       </c>
       <c r="L72" s="18" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="M72" s="18">
         <v>0</v>
@@ -5041,11 +5047,11 @@
     </row>
     <row r="73" s="1" customFormat="1" spans="1:19">
       <c r="A73" s="1">
-        <f t="shared" si="8"/>
-        <v>20050012</v>
+        <f t="shared" si="9"/>
+        <v>20030012</v>
       </c>
       <c r="B73" s="13">
-        <v>200500</v>
+        <v>200300</v>
       </c>
       <c r="C73" s="13">
         <v>2</v>
@@ -5054,13 +5060,13 @@
         <v>55</v>
       </c>
       <c r="E73" s="13">
-        <v>200500025</v>
+        <v>200300001</v>
       </c>
       <c r="F73" s="13" t="s">
         <v>56</v>
       </c>
       <c r="G73" s="18" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="H73" s="18">
         <v>12</v>
@@ -5075,7 +5081,7 @@
         <v>0</v>
       </c>
       <c r="L73" s="18" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="M73" s="18">
         <v>0</v>
@@ -5088,28 +5094,28 @@
       </c>
       <c r="S73" s="3"/>
     </row>
-    <row r="74" spans="1:19">
+    <row r="74" s="1" customFormat="1" spans="1:19">
       <c r="A74" s="1">
-        <f t="shared" si="8"/>
-        <v>20060010</v>
+        <f t="shared" si="9"/>
+        <v>20040010</v>
       </c>
       <c r="B74" s="13">
-        <v>200600</v>
+        <v>200400</v>
       </c>
       <c r="C74" s="13">
         <v>2</v>
       </c>
-      <c r="D74" s="13" t="s">
+      <c r="D74" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="E74" s="13">
+        <v>200400009</v>
+      </c>
+      <c r="F74" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="E74" s="13">
-        <v>200600001</v>
-      </c>
-      <c r="F74" s="13" t="s">
-        <v>59</v>
-      </c>
       <c r="G74" s="18" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H74" s="18">
         <v>10</v>
@@ -5124,7 +5130,7 @@
         <v>0</v>
       </c>
       <c r="L74" s="18" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="M74" s="18">
         <v>0</v>
@@ -5135,29 +5141,30 @@
       <c r="O74" s="19">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="75" spans="1:19">
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" s="1" customFormat="1" spans="1:19">
       <c r="A75" s="1">
-        <f t="shared" ref="A75:A89" si="9">B75*100+H75</f>
-        <v>20060011</v>
+        <f t="shared" si="9"/>
+        <v>20040011</v>
       </c>
       <c r="B75" s="13">
-        <v>200600</v>
+        <v>200400</v>
       </c>
       <c r="C75" s="13">
         <v>2</v>
       </c>
-      <c r="D75" s="13" t="s">
+      <c r="D75" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="E75" s="13">
+        <v>200400009</v>
+      </c>
+      <c r="F75" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="E75" s="13">
-        <v>200600001</v>
-      </c>
-      <c r="F75" s="13" t="s">
-        <v>59</v>
-      </c>
       <c r="G75" s="18" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H75" s="18">
         <v>11</v>
@@ -5172,7 +5179,7 @@
         <v>0</v>
       </c>
       <c r="L75" s="18" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="M75" s="18">
         <v>0</v>
@@ -5183,29 +5190,30 @@
       <c r="O75" s="19">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="76" spans="1:19">
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" s="1" customFormat="1" spans="1:19">
       <c r="A76" s="1">
         <f t="shared" si="9"/>
-        <v>20060012</v>
+        <v>20040012</v>
       </c>
       <c r="B76" s="13">
-        <v>200600</v>
+        <v>200400</v>
       </c>
       <c r="C76" s="13">
         <v>2</v>
       </c>
-      <c r="D76" s="13" t="s">
+      <c r="D76" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="E76" s="13">
+        <v>200400009</v>
+      </c>
+      <c r="F76" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="E76" s="13">
-        <v>200600001</v>
-      </c>
-      <c r="F76" s="13" t="s">
-        <v>59</v>
-      </c>
       <c r="G76" s="18" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="H76" s="18">
         <v>12</v>
@@ -5220,7 +5228,7 @@
         <v>0</v>
       </c>
       <c r="L76" s="18" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="M76" s="18">
         <v>0</v>
@@ -5231,29 +5239,30 @@
       <c r="O76" s="19">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="77" spans="1:19">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" s="1" customFormat="1" spans="1:19">
       <c r="A77" s="1">
         <f t="shared" si="9"/>
-        <v>20070010</v>
+        <v>20050010</v>
       </c>
       <c r="B77" s="13">
-        <v>200700</v>
+        <v>200500</v>
       </c>
       <c r="C77" s="13">
         <v>2</v>
       </c>
-      <c r="D77" s="12" t="s">
+      <c r="D77" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E77" s="13">
+        <v>200500025</v>
+      </c>
+      <c r="F77" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="E77" s="13">
-        <v>200700001</v>
-      </c>
-      <c r="F77" s="13" t="s">
-        <v>61</v>
-      </c>
       <c r="G77" s="18" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H77" s="18">
         <v>10</v>
@@ -5268,7 +5277,7 @@
         <v>0</v>
       </c>
       <c r="L77" s="18" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="M77" s="18">
         <v>0</v>
@@ -5279,30 +5288,30 @@
       <c r="O77" s="19">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="78" spans="1:19">
+      <c r="S77" s="3"/>
+    </row>
+    <row r="78" s="1" customFormat="1" spans="1:19">
       <c r="A78" s="1">
         <f t="shared" si="9"/>
-        <v>20070011</v>
+        <v>20050011</v>
       </c>
       <c r="B78" s="13">
-        <v>200700</v>
+        <v>200500</v>
       </c>
       <c r="C78" s="13">
         <v>2</v>
       </c>
-      <c r="D78" s="12" t="str">
-        <f>D77</f>
-        <v>越南色碟</v>
+      <c r="D78" s="13" t="s">
+        <v>59</v>
       </c>
       <c r="E78" s="13">
-        <v>200700001</v>
+        <v>200500025</v>
       </c>
       <c r="F78" s="13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G78" s="18" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H78" s="18">
         <v>11</v>
@@ -5317,7 +5326,7 @@
         <v>0</v>
       </c>
       <c r="L78" s="18" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="M78" s="18">
         <v>0</v>
@@ -5328,30 +5337,30 @@
       <c r="O78" s="19">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="79" spans="1:19">
+      <c r="S78" s="3"/>
+    </row>
+    <row r="79" s="1" customFormat="1" spans="1:19">
       <c r="A79" s="1">
         <f t="shared" si="9"/>
-        <v>20070012</v>
+        <v>20050012</v>
       </c>
       <c r="B79" s="13">
-        <v>200700</v>
+        <v>200500</v>
       </c>
       <c r="C79" s="13">
         <v>2</v>
       </c>
-      <c r="D79" s="12" t="str">
-        <f>D78</f>
-        <v>越南色碟</v>
+      <c r="D79" s="13" t="s">
+        <v>59</v>
       </c>
       <c r="E79" s="13">
-        <v>200700001</v>
+        <v>200500025</v>
       </c>
       <c r="F79" s="13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G79" s="18" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="H79" s="18">
         <v>12</v>
@@ -5366,7 +5375,7 @@
         <v>0</v>
       </c>
       <c r="L79" s="18" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="M79" s="18">
         <v>0</v>
@@ -5377,14 +5386,15 @@
       <c r="O79" s="19">
         <v>1980000</v>
       </c>
+      <c r="S79" s="3"/>
     </row>
     <row r="80" spans="1:19">
       <c r="A80" s="1">
         <f t="shared" si="9"/>
-        <v>20080010</v>
+        <v>20060010</v>
       </c>
       <c r="B80" s="13">
-        <v>200800</v>
+        <v>200600</v>
       </c>
       <c r="C80" s="13">
         <v>2</v>
@@ -5393,13 +5403,13 @@
         <v>62</v>
       </c>
       <c r="E80" s="13">
-        <v>200800001</v>
+        <v>200600001</v>
       </c>
       <c r="F80" s="13" t="s">
         <v>63</v>
       </c>
       <c r="G80" s="18" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H80" s="18">
         <v>10</v>
@@ -5414,7 +5424,7 @@
         <v>0</v>
       </c>
       <c r="L80" s="18" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="M80" s="18">
         <v>0</v>
@@ -5428,11 +5438,11 @@
     </row>
     <row r="81" spans="1:19">
       <c r="A81" s="1">
-        <f t="shared" si="9"/>
-        <v>20080011</v>
+        <f t="shared" ref="A81:A95" si="10">B81*100+H81</f>
+        <v>20060011</v>
       </c>
       <c r="B81" s="13">
-        <v>200800</v>
+        <v>200600</v>
       </c>
       <c r="C81" s="13">
         <v>2</v>
@@ -5441,13 +5451,13 @@
         <v>62</v>
       </c>
       <c r="E81" s="13">
-        <v>200800001</v>
+        <v>200600001</v>
       </c>
       <c r="F81" s="13" t="s">
         <v>63</v>
       </c>
       <c r="G81" s="18" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H81" s="18">
         <v>11</v>
@@ -5462,7 +5472,7 @@
         <v>0</v>
       </c>
       <c r="L81" s="18" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="M81" s="18">
         <v>0</v>
@@ -5476,11 +5486,11 @@
     </row>
     <row r="82" spans="1:19">
       <c r="A82" s="1">
-        <f t="shared" si="9"/>
-        <v>20080012</v>
+        <f t="shared" si="10"/>
+        <v>20060012</v>
       </c>
       <c r="B82" s="13">
-        <v>200800</v>
+        <v>200600</v>
       </c>
       <c r="C82" s="13">
         <v>2</v>
@@ -5489,13 +5499,13 @@
         <v>62</v>
       </c>
       <c r="E82" s="13">
-        <v>200800001</v>
+        <v>200600001</v>
       </c>
       <c r="F82" s="13" t="s">
         <v>63</v>
       </c>
       <c r="G82" s="18" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="H82" s="18">
         <v>12</v>
@@ -5510,7 +5520,7 @@
         <v>0</v>
       </c>
       <c r="L82" s="18" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="M82" s="18">
         <v>0</v>
@@ -5524,26 +5534,26 @@
     </row>
     <row r="83" spans="1:19">
       <c r="A83" s="1">
-        <f t="shared" si="9"/>
-        <v>20090010</v>
+        <f t="shared" si="10"/>
+        <v>20070010</v>
       </c>
       <c r="B83" s="13">
-        <v>200900</v>
+        <v>200700</v>
       </c>
       <c r="C83" s="13">
         <v>2</v>
       </c>
-      <c r="D83" s="13" t="s">
+      <c r="D83" s="12" t="s">
         <v>64</v>
       </c>
       <c r="E83" s="13">
-        <v>200900001</v>
+        <v>200700001</v>
       </c>
       <c r="F83" s="13" t="s">
         <v>65</v>
       </c>
       <c r="G83" s="18" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H83" s="18">
         <v>10</v>
@@ -5558,7 +5568,7 @@
         <v>0</v>
       </c>
       <c r="L83" s="18" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="M83" s="18">
         <v>0</v>
@@ -5572,26 +5582,27 @@
     </row>
     <row r="84" spans="1:19">
       <c r="A84" s="1">
-        <f t="shared" si="9"/>
-        <v>20090011</v>
+        <f t="shared" si="10"/>
+        <v>20070011</v>
       </c>
       <c r="B84" s="13">
-        <v>200900</v>
+        <v>200700</v>
       </c>
       <c r="C84" s="13">
         <v>2</v>
       </c>
-      <c r="D84" s="13" t="s">
-        <v>64</v>
+      <c r="D84" s="12" t="str">
+        <f>D83</f>
+        <v>越南色碟</v>
       </c>
       <c r="E84" s="13">
-        <v>200900001</v>
+        <v>200700001</v>
       </c>
       <c r="F84" s="13" t="s">
         <v>65</v>
       </c>
       <c r="G84" s="18" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H84" s="18">
         <v>11</v>
@@ -5606,7 +5617,7 @@
         <v>0</v>
       </c>
       <c r="L84" s="18" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="M84" s="18">
         <v>0</v>
@@ -5620,26 +5631,27 @@
     </row>
     <row r="85" spans="1:19">
       <c r="A85" s="1">
-        <f t="shared" si="9"/>
-        <v>20090012</v>
+        <f t="shared" si="10"/>
+        <v>20070012</v>
       </c>
       <c r="B85" s="13">
-        <v>200900</v>
+        <v>200700</v>
       </c>
       <c r="C85" s="13">
         <v>2</v>
       </c>
-      <c r="D85" s="13" t="s">
-        <v>64</v>
+      <c r="D85" s="12" t="str">
+        <f>D84</f>
+        <v>越南色碟</v>
       </c>
       <c r="E85" s="13">
-        <v>200900001</v>
+        <v>200700001</v>
       </c>
       <c r="F85" s="13" t="s">
         <v>65</v>
       </c>
       <c r="G85" s="18" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="H85" s="18">
         <v>12</v>
@@ -5654,7 +5666,7 @@
         <v>0</v>
       </c>
       <c r="L85" s="18" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="M85" s="18">
         <v>0</v>
@@ -5666,28 +5678,28 @@
         <v>1980000</v>
       </c>
     </row>
-    <row r="86" s="1" customFormat="1" spans="1:19">
+    <row r="86" spans="1:19">
       <c r="A86" s="1">
-        <f t="shared" si="9"/>
-        <v>30020010</v>
-      </c>
-      <c r="B86" s="12">
-        <v>300200</v>
-      </c>
-      <c r="C86" s="12">
-        <v>3</v>
-      </c>
-      <c r="D86" s="12" t="s">
-        <v>71</v>
+        <f t="shared" si="10"/>
+        <v>20080010</v>
+      </c>
+      <c r="B86" s="13">
+        <v>200800</v>
+      </c>
+      <c r="C86" s="13">
+        <v>2</v>
+      </c>
+      <c r="D86" s="13" t="s">
+        <v>66</v>
       </c>
       <c r="E86" s="13">
-        <v>300200006</v>
+        <v>200800001</v>
       </c>
       <c r="F86" s="13" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G86" s="18" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H86" s="18">
         <v>10</v>
@@ -5695,14 +5707,14 @@
       <c r="I86" s="18">
         <v>0</v>
       </c>
-      <c r="J86" s="1">
+      <c r="J86" s="18">
         <v>-1</v>
       </c>
       <c r="K86" s="1">
         <v>0</v>
       </c>
-      <c r="L86" s="21" t="s">
-        <v>78</v>
+      <c r="L86" s="18" t="s">
+        <v>79</v>
       </c>
       <c r="M86" s="18">
         <v>0</v>
@@ -5713,30 +5725,29 @@
       <c r="O86" s="19">
         <v>1980000</v>
       </c>
-      <c r="S86" s="3"/>
-    </row>
-    <row r="87" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="87" spans="1:19">
       <c r="A87" s="1">
-        <f t="shared" si="9"/>
-        <v>30020011</v>
-      </c>
-      <c r="B87" s="12">
-        <v>300200</v>
-      </c>
-      <c r="C87" s="12">
-        <v>3</v>
-      </c>
-      <c r="D87" s="12" t="s">
-        <v>71</v>
+        <f t="shared" si="10"/>
+        <v>20080011</v>
+      </c>
+      <c r="B87" s="13">
+        <v>200800</v>
+      </c>
+      <c r="C87" s="13">
+        <v>2</v>
+      </c>
+      <c r="D87" s="13" t="s">
+        <v>66</v>
       </c>
       <c r="E87" s="13">
-        <v>300200006</v>
+        <v>200800001</v>
       </c>
       <c r="F87" s="13" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G87" s="18" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H87" s="18">
         <v>11</v>
@@ -5744,14 +5755,14 @@
       <c r="I87" s="18">
         <v>0</v>
       </c>
-      <c r="J87" s="1">
+      <c r="J87" s="18">
         <v>-1</v>
       </c>
       <c r="K87" s="1">
         <v>0</v>
       </c>
-      <c r="L87" s="21" t="s">
-        <v>78</v>
+      <c r="L87" s="18" t="s">
+        <v>79</v>
       </c>
       <c r="M87" s="18">
         <v>0</v>
@@ -5762,30 +5773,29 @@
       <c r="O87" s="19">
         <v>1980000</v>
       </c>
-      <c r="S87" s="3"/>
-    </row>
-    <row r="88" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="88" spans="1:19">
       <c r="A88" s="1">
-        <f t="shared" si="9"/>
-        <v>30020012</v>
-      </c>
-      <c r="B88" s="12">
-        <v>300200</v>
-      </c>
-      <c r="C88" s="12">
-        <v>3</v>
-      </c>
-      <c r="D88" s="12" t="s">
-        <v>71</v>
+        <f t="shared" si="10"/>
+        <v>20080012</v>
+      </c>
+      <c r="B88" s="13">
+        <v>200800</v>
+      </c>
+      <c r="C88" s="13">
+        <v>2</v>
+      </c>
+      <c r="D88" s="13" t="s">
+        <v>66</v>
       </c>
       <c r="E88" s="13">
-        <v>300200006</v>
+        <v>200800001</v>
       </c>
       <c r="F88" s="13" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G88" s="18" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="H88" s="18">
         <v>12</v>
@@ -5793,14 +5803,14 @@
       <c r="I88" s="18">
         <v>0</v>
       </c>
-      <c r="J88" s="1">
+      <c r="J88" s="18">
         <v>-1</v>
       </c>
       <c r="K88" s="1">
         <v>0</v>
       </c>
-      <c r="L88" s="21" t="s">
-        <v>78</v>
+      <c r="L88" s="18" t="s">
+        <v>79</v>
       </c>
       <c r="M88" s="18">
         <v>0</v>
@@ -5811,7 +5821,297 @@
       <c r="O88" s="19">
         <v>1980000</v>
       </c>
-      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="1:19">
+      <c r="A89" s="1">
+        <f t="shared" si="10"/>
+        <v>20090010</v>
+      </c>
+      <c r="B89" s="13">
+        <v>200900</v>
+      </c>
+      <c r="C89" s="13">
+        <v>2</v>
+      </c>
+      <c r="D89" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="E89" s="13">
+        <v>200900001</v>
+      </c>
+      <c r="F89" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="G89" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="H89" s="18">
+        <v>10</v>
+      </c>
+      <c r="I89" s="18">
+        <v>0</v>
+      </c>
+      <c r="J89" s="18">
+        <v>-1</v>
+      </c>
+      <c r="K89" s="1">
+        <v>0</v>
+      </c>
+      <c r="L89" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="M89" s="18">
+        <v>0</v>
+      </c>
+      <c r="N89">
+        <v>200</v>
+      </c>
+      <c r="O89" s="19">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19">
+      <c r="A90" s="1">
+        <f t="shared" si="10"/>
+        <v>20090011</v>
+      </c>
+      <c r="B90" s="13">
+        <v>200900</v>
+      </c>
+      <c r="C90" s="13">
+        <v>2</v>
+      </c>
+      <c r="D90" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="E90" s="13">
+        <v>200900001</v>
+      </c>
+      <c r="F90" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="G90" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="H90" s="18">
+        <v>11</v>
+      </c>
+      <c r="I90" s="18">
+        <v>0</v>
+      </c>
+      <c r="J90" s="18">
+        <v>-1</v>
+      </c>
+      <c r="K90" s="1">
+        <v>0</v>
+      </c>
+      <c r="L90" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="M90" s="18">
+        <v>0</v>
+      </c>
+      <c r="N90">
+        <v>5000</v>
+      </c>
+      <c r="O90" s="19">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19">
+      <c r="A91" s="1">
+        <f t="shared" si="10"/>
+        <v>20090012</v>
+      </c>
+      <c r="B91" s="13">
+        <v>200900</v>
+      </c>
+      <c r="C91" s="13">
+        <v>2</v>
+      </c>
+      <c r="D91" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="E91" s="13">
+        <v>200900001</v>
+      </c>
+      <c r="F91" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="G91" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="H91" s="18">
+        <v>12</v>
+      </c>
+      <c r="I91" s="18">
+        <v>0</v>
+      </c>
+      <c r="J91" s="18">
+        <v>-1</v>
+      </c>
+      <c r="K91" s="1">
+        <v>0</v>
+      </c>
+      <c r="L91" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="M91" s="18">
+        <v>0</v>
+      </c>
+      <c r="N91">
+        <v>100000</v>
+      </c>
+      <c r="O91" s="19">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="92" s="1" customFormat="1" spans="1:19">
+      <c r="A92" s="1">
+        <f t="shared" si="10"/>
+        <v>30020010</v>
+      </c>
+      <c r="B92" s="12">
+        <v>300200</v>
+      </c>
+      <c r="C92" s="12">
+        <v>3</v>
+      </c>
+      <c r="D92" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E92" s="13">
+        <v>300200006</v>
+      </c>
+      <c r="F92" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="G92" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="H92" s="18">
+        <v>10</v>
+      </c>
+      <c r="I92" s="18">
+        <v>0</v>
+      </c>
+      <c r="J92" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K92" s="1">
+        <v>0</v>
+      </c>
+      <c r="L92" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="M92" s="18">
+        <v>0</v>
+      </c>
+      <c r="N92">
+        <v>200</v>
+      </c>
+      <c r="O92" s="19">
+        <v>1980000</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" s="1" customFormat="1" spans="1:19">
+      <c r="A93" s="1">
+        <f t="shared" si="10"/>
+        <v>30020011</v>
+      </c>
+      <c r="B93" s="12">
+        <v>300200</v>
+      </c>
+      <c r="C93" s="12">
+        <v>3</v>
+      </c>
+      <c r="D93" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E93" s="13">
+        <v>300200006</v>
+      </c>
+      <c r="F93" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="G93" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="H93" s="18">
+        <v>11</v>
+      </c>
+      <c r="I93" s="18">
+        <v>0</v>
+      </c>
+      <c r="J93" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K93" s="1">
+        <v>0</v>
+      </c>
+      <c r="L93" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="M93" s="18">
+        <v>0</v>
+      </c>
+      <c r="N93">
+        <v>5000</v>
+      </c>
+      <c r="O93" s="19">
+        <v>1980000</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" s="1" customFormat="1" spans="1:19">
+      <c r="A94" s="1">
+        <f t="shared" si="10"/>
+        <v>30020012</v>
+      </c>
+      <c r="B94" s="12">
+        <v>300200</v>
+      </c>
+      <c r="C94" s="12">
+        <v>3</v>
+      </c>
+      <c r="D94" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E94" s="13">
+        <v>300200006</v>
+      </c>
+      <c r="F94" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="G94" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="H94" s="18">
+        <v>12</v>
+      </c>
+      <c r="I94" s="18">
+        <v>0</v>
+      </c>
+      <c r="J94" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K94" s="1">
+        <v>0</v>
+      </c>
+      <c r="L94" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="M94" s="18">
+        <v>0</v>
+      </c>
+      <c r="N94">
+        <v>100000</v>
+      </c>
+      <c r="O94" s="19">
+        <v>1980000</v>
+      </c>
+      <c r="S94" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -156,7 +156,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="84">
   <si>
     <t>sid</t>
   </si>
@@ -308,7 +308,10 @@
     <t>圣诞狂欢夜</t>
   </si>
   <si>
-    <t>DazeBeforeChristmas</t>
+    <t>Christmas</t>
+  </si>
+  <si>
+    <t>杰克船长</t>
   </si>
   <si>
     <t>紅黑大戰</t>
@@ -1538,7 +1541,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S94"/>
+  <dimension ref="A1:S97"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="3" width="9.375" style="1"/>
@@ -2288,7 +2291,7 @@
         <v>1990000</v>
       </c>
     </row>
-    <row r="17" spans="1:17">
+    <row r="17" spans="1:15">
       <c r="A17" s="1">
         <f t="shared" si="2"/>
         <v>1014001</v>
@@ -2336,7 +2339,7 @@
         <v>1990000</v>
       </c>
     </row>
-    <row r="18" spans="1:17">
+    <row r="18" spans="1:15">
       <c r="A18" s="1">
         <f t="shared" si="2"/>
         <v>1014002</v>
@@ -2386,7 +2389,7 @@
         <v>1990000</v>
       </c>
     </row>
-    <row r="19" spans="1:17">
+    <row r="19" spans="1:15">
       <c r="A19" s="1">
         <f t="shared" si="2"/>
         <v>1014003</v>
@@ -2436,7 +2439,7 @@
         <v>1990000</v>
       </c>
     </row>
-    <row r="20" spans="1:17">
+    <row r="20" spans="1:15">
       <c r="A20" s="1">
         <f t="shared" si="2"/>
         <v>1024001</v>
@@ -2484,7 +2487,7 @@
         <v>1990000</v>
       </c>
     </row>
-    <row r="21" spans="1:17">
+    <row r="21" spans="1:15">
       <c r="A21" s="1">
         <f t="shared" si="2"/>
         <v>1024002</v>
@@ -2533,7 +2536,7 @@
         <v>1990000</v>
       </c>
     </row>
-    <row r="22" spans="1:17">
+    <row r="22" spans="1:15">
       <c r="A22" s="1">
         <f t="shared" si="2"/>
         <v>1024003</v>
@@ -2582,13 +2585,13 @@
         <v>1990000</v>
       </c>
     </row>
-    <row r="23" spans="1:17">
+    <row r="23" spans="1:15">
       <c r="A23" s="1">
         <f t="shared" ref="A23:A28" si="4">B23*10+H23</f>
-        <v>1017001</v>
+        <v>1022001</v>
       </c>
       <c r="B23" s="12">
-        <v>101700</v>
+        <v>102200</v>
       </c>
       <c r="C23" s="12">
         <v>1</v>
@@ -2630,13 +2633,13 @@
         <v>1990000</v>
       </c>
     </row>
-    <row r="24" spans="1:17">
+    <row r="24" spans="1:15">
       <c r="A24" s="1">
         <f t="shared" si="4"/>
-        <v>1017002</v>
+        <v>1022002</v>
       </c>
       <c r="B24" s="12">
-        <v>101700</v>
+        <v>102200</v>
       </c>
       <c r="C24" s="12">
         <v>1</v>
@@ -2678,13 +2681,13 @@
         <v>1990000</v>
       </c>
     </row>
-    <row r="25" spans="1:17">
+    <row r="25" spans="1:15">
       <c r="A25" s="1">
         <f t="shared" si="4"/>
-        <v>1017003</v>
+        <v>1022003</v>
       </c>
       <c r="B25" s="12">
-        <v>101700</v>
+        <v>102200</v>
       </c>
       <c r="C25" s="12">
         <v>1</v>
@@ -2726,13 +2729,13 @@
         <v>1990000</v>
       </c>
     </row>
-    <row r="26" spans="1:17">
+    <row r="26" spans="1:15">
       <c r="A26" s="1">
         <f t="shared" si="4"/>
-        <v>1022001</v>
+        <v>1017001</v>
       </c>
       <c r="B26" s="12">
-        <v>102200</v>
+        <v>101700</v>
       </c>
       <c r="C26" s="12">
         <v>1</v>
@@ -2774,13 +2777,13 @@
         <v>1990000</v>
       </c>
     </row>
-    <row r="27" spans="1:17">
+    <row r="27" spans="1:15">
       <c r="A27" s="1">
         <f t="shared" si="4"/>
-        <v>1022002</v>
+        <v>1017002</v>
       </c>
       <c r="B27" s="12">
-        <v>102200</v>
+        <v>101700</v>
       </c>
       <c r="C27" s="12">
         <v>1</v>
@@ -2822,13 +2825,13 @@
         <v>1990000</v>
       </c>
     </row>
-    <row r="28" spans="1:17">
+    <row r="28" spans="1:15">
       <c r="A28" s="1">
         <f t="shared" si="4"/>
-        <v>1022003</v>
+        <v>1017003</v>
       </c>
       <c r="B28" s="12">
-        <v>102200</v>
+        <v>101700</v>
       </c>
       <c r="C28" s="12">
         <v>1</v>
@@ -2870,26 +2873,24 @@
         <v>1990000</v>
       </c>
     </row>
-    <row r="29" spans="1:17">
+    <row r="29" spans="1:15">
       <c r="A29" s="1">
-        <f t="shared" ref="A29:A75" si="5">B29*10+H29</f>
-        <v>2001001</v>
+        <f>B29*10+H29</f>
+        <v>1021001</v>
       </c>
       <c r="B29" s="12">
-        <v>200100</v>
+        <v>102100</v>
       </c>
       <c r="C29" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" s="12" t="s">
         <v>51</v>
       </c>
       <c r="E29" s="13">
-        <v>200100038</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>52</v>
-      </c>
+        <v>102100001</v>
+      </c>
+      <c r="F29" s="13"/>
       <c r="G29" s="1" t="s">
         <v>32</v>
       </c>
@@ -2918,223 +2919,215 @@
         <v>1990000</v>
       </c>
     </row>
-    <row r="30" spans="1:17">
+    <row r="30" spans="1:15">
       <c r="A30" s="1">
+        <f>B30*10+H30</f>
+        <v>1021002</v>
+      </c>
+      <c r="B30" s="12">
+        <v>102100</v>
+      </c>
+      <c r="C30" s="12">
+        <v>1</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E30" s="13">
+        <v>102100001</v>
+      </c>
+      <c r="F30" s="13"/>
+      <c r="G30" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H30" s="1">
+        <v>2</v>
+      </c>
+      <c r="I30" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J30" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K30" s="1">
+        <v>0</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M30" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="N30">
+        <v>500000</v>
+      </c>
+      <c r="O30" s="15">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="A31" s="1">
+        <f>B31*10+H31</f>
+        <v>1021003</v>
+      </c>
+      <c r="B31" s="12">
+        <v>102100</v>
+      </c>
+      <c r="C31" s="12">
+        <v>1</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31" s="13">
+        <v>102100001</v>
+      </c>
+      <c r="F31" s="13"/>
+      <c r="G31" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H31" s="1">
+        <v>3</v>
+      </c>
+      <c r="I31" s="1">
+        <v>50000000</v>
+      </c>
+      <c r="J31" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K31" s="1">
+        <v>0</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M31" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="N31">
+        <v>50000000</v>
+      </c>
+      <c r="O31" s="15">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
+      <c r="A32" s="1">
+        <f t="shared" ref="A32:A78" si="5">B32*10+H32</f>
+        <v>2001001</v>
+      </c>
+      <c r="B32" s="12">
+        <v>200100</v>
+      </c>
+      <c r="C32" s="12">
+        <v>2</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E32" s="13">
+        <v>200100038</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H32" s="1">
+        <v>1</v>
+      </c>
+      <c r="I32" s="1">
+        <v>0</v>
+      </c>
+      <c r="J32" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K32" s="1">
+        <v>0</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M32" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="N32">
+        <v>5000</v>
+      </c>
+      <c r="O32" s="15">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19">
+      <c r="A33" s="1">
         <f t="shared" si="5"/>
         <v>2001002</v>
       </c>
-      <c r="B30" s="12">
+      <c r="B33" s="12">
         <v>200100</v>
       </c>
-      <c r="C30" s="12">
-        <v>2</v>
-      </c>
-      <c r="D30" s="12" t="str">
-        <f>D29</f>
+      <c r="C33" s="12">
+        <v>2</v>
+      </c>
+      <c r="D33" s="12" t="str">
+        <f>D32</f>
         <v>紅黑大戰</v>
       </c>
-      <c r="E30" s="13">
+      <c r="E33" s="13">
         <v>200100038</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="G30" s="1" t="s">
+      <c r="F33" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="G33" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H30" s="1">
-        <v>2</v>
-      </c>
-      <c r="I30" s="1">
+      <c r="H33" s="1">
+        <v>2</v>
+      </c>
+      <c r="I33" s="1">
         <v>500000</v>
       </c>
-      <c r="J30" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K30" s="1">
-        <v>0</v>
-      </c>
-      <c r="L30" s="1" t="s">
+      <c r="J33" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K33" s="1">
+        <v>0</v>
+      </c>
+      <c r="L33" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M30" s="20" t="s">
+      <c r="M33" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="N30">
+      <c r="N33">
         <v>500000</v>
       </c>
-      <c r="O30" s="15">
+      <c r="O33" s="15">
         <v>1990000</v>
       </c>
     </row>
-    <row r="31" spans="1:17">
-      <c r="A31" s="1">
+    <row r="34" spans="1:19">
+      <c r="A34" s="1">
         <f t="shared" si="5"/>
         <v>2001003</v>
       </c>
-      <c r="B31" s="12">
+      <c r="B34" s="12">
         <v>200100</v>
       </c>
-      <c r="C31" s="12">
-        <v>2</v>
-      </c>
-      <c r="D31" s="12" t="str">
-        <f>D30</f>
+      <c r="C34" s="12">
+        <v>2</v>
+      </c>
+      <c r="D34" s="12" t="str">
+        <f>D33</f>
         <v>紅黑大戰</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E34" s="13">
         <v>200100038</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H31" s="1">
-        <v>3</v>
-      </c>
-      <c r="I31" s="1">
-        <v>50000000</v>
-      </c>
-      <c r="J31" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K31" s="1">
-        <v>0</v>
-      </c>
-      <c r="L31" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M31" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="N31">
-        <v>50000000</v>
-      </c>
-      <c r="O31" s="15">
-        <v>1990000</v>
-      </c>
-      <c r="Q31"/>
-    </row>
-    <row r="32" spans="1:17">
-      <c r="A32" s="1">
-        <f t="shared" si="5"/>
-        <v>2001011</v>
-      </c>
-      <c r="B32" s="12">
-        <v>200101</v>
-      </c>
-      <c r="C32" s="12">
-        <v>2</v>
-      </c>
-      <c r="D32" s="12" t="s">
+      <c r="F34" s="13" t="s">
         <v>53</v>
-      </c>
-      <c r="E32" s="13">
-        <v>200101001</v>
-      </c>
-      <c r="F32" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H32" s="1">
-        <v>1</v>
-      </c>
-      <c r="I32" s="1">
-        <v>0</v>
-      </c>
-      <c r="J32" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K32" s="1">
-        <v>0</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M32" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="N32">
-        <v>5000</v>
-      </c>
-      <c r="O32" s="15">
-        <v>1990000</v>
-      </c>
-    </row>
-    <row r="33" s="1" customFormat="1" spans="1:19">
-      <c r="A33" s="1">
-        <f t="shared" si="5"/>
-        <v>2001012</v>
-      </c>
-      <c r="B33" s="12">
-        <v>200101</v>
-      </c>
-      <c r="C33" s="12">
-        <v>2</v>
-      </c>
-      <c r="D33" s="12" t="str">
-        <f t="shared" ref="D33:D37" si="6">D32</f>
-        <v>龍虎鬥</v>
-      </c>
-      <c r="E33" s="13">
-        <v>200101001</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H33" s="1">
-        <v>2</v>
-      </c>
-      <c r="I33" s="1">
-        <v>500000</v>
-      </c>
-      <c r="J33" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K33" s="1">
-        <v>0</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M33" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="N33">
-        <v>500000</v>
-      </c>
-      <c r="O33" s="15">
-        <v>1990000</v>
-      </c>
-      <c r="S33" s="3"/>
-    </row>
-    <row r="34" s="1" customFormat="1" spans="1:19">
-      <c r="A34" s="1">
-        <f t="shared" si="5"/>
-        <v>2001013</v>
-      </c>
-      <c r="B34" s="12">
-        <v>200101</v>
-      </c>
-      <c r="C34" s="12">
-        <v>2</v>
-      </c>
-      <c r="D34" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v>龍虎鬥</v>
-      </c>
-      <c r="E34" s="13">
-        <v>200101001</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>54</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>36</v>
@@ -3163,27 +3156,27 @@
       <c r="O34" s="15">
         <v>1990000</v>
       </c>
-      <c r="S34" s="3"/>
+      <c r="Q34"/>
     </row>
     <row r="35" spans="1:19">
       <c r="A35" s="1">
         <f t="shared" si="5"/>
-        <v>2003001</v>
+        <v>2001011</v>
       </c>
       <c r="B35" s="12">
-        <v>200300</v>
+        <v>200101</v>
       </c>
       <c r="C35" s="12">
         <v>2</v>
       </c>
       <c r="D35" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="E35" s="13">
+        <v>200101001</v>
+      </c>
+      <c r="F35" s="13" t="s">
         <v>55</v>
-      </c>
-      <c r="E35" s="13">
-        <v>200300001</v>
-      </c>
-      <c r="F35" s="13" t="s">
-        <v>56</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>32</v>
@@ -3216,23 +3209,23 @@
     <row r="36" s="1" customFormat="1" spans="1:19">
       <c r="A36" s="1">
         <f t="shared" si="5"/>
-        <v>2003002</v>
+        <v>2001012</v>
       </c>
       <c r="B36" s="12">
-        <v>200300</v>
+        <v>200101</v>
       </c>
       <c r="C36" s="12">
         <v>2</v>
       </c>
       <c r="D36" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v>飛禽走獸</v>
+        <f t="shared" ref="D36:D40" si="6">D35</f>
+        <v>龍虎鬥</v>
       </c>
       <c r="E36" s="13">
-        <v>200300001</v>
+        <v>200101001</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>35</v>
@@ -3261,30 +3254,28 @@
       <c r="O36" s="15">
         <v>1990000</v>
       </c>
-      <c r="Q36" s="3"/>
-      <c r="R36" s="12"/>
       <c r="S36" s="3"/>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:19">
       <c r="A37" s="1">
         <f t="shared" si="5"/>
-        <v>2003003</v>
+        <v>2001013</v>
       </c>
       <c r="B37" s="12">
-        <v>200300</v>
+        <v>200101</v>
       </c>
       <c r="C37" s="12">
         <v>2</v>
       </c>
       <c r="D37" s="12" t="str">
         <f t="shared" si="6"/>
-        <v>飛禽走獸</v>
+        <v>龍虎鬥</v>
       </c>
       <c r="E37" s="13">
-        <v>200300001</v>
+        <v>200101001</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>36</v>
@@ -3313,29 +3304,27 @@
       <c r="O37" s="15">
         <v>1990000</v>
       </c>
-      <c r="Q37" s="3"/>
-      <c r="R37" s="16"/>
-      <c r="S37" s="16"/>
+      <c r="S37" s="3"/>
     </row>
     <row r="38" spans="1:19">
       <c r="A38" s="1">
         <f t="shared" si="5"/>
-        <v>2004001</v>
+        <v>2003001</v>
       </c>
       <c r="B38" s="12">
-        <v>200400</v>
+        <v>200300</v>
       </c>
       <c r="C38" s="12">
         <v>2</v>
       </c>
-      <c r="D38" s="16" t="s">
+      <c r="D38" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E38" s="13">
+        <v>200300001</v>
+      </c>
+      <c r="F38" s="13" t="s">
         <v>57</v>
-      </c>
-      <c r="E38" s="13">
-        <v>200400009</v>
-      </c>
-      <c r="F38" s="13" t="s">
-        <v>58</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>32</v>
@@ -3364,29 +3353,27 @@
       <c r="O38" s="15">
         <v>1990000</v>
       </c>
-      <c r="Q38" s="3"/>
-      <c r="R38" s="16"/>
-      <c r="S38" s="16"/>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:19">
       <c r="A39" s="1">
         <f t="shared" si="5"/>
-        <v>2004002</v>
+        <v>2003002</v>
       </c>
       <c r="B39" s="12">
-        <v>200400</v>
+        <v>200300</v>
       </c>
       <c r="C39" s="12">
         <v>2</v>
       </c>
-      <c r="D39" s="16" t="s">
+      <c r="D39" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>飛禽走獸</v>
+      </c>
+      <c r="E39" s="13">
+        <v>200300001</v>
+      </c>
+      <c r="F39" s="13" t="s">
         <v>57</v>
-      </c>
-      <c r="E39" s="13">
-        <v>200400009</v>
-      </c>
-      <c r="F39" s="13" t="s">
-        <v>58</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>35</v>
@@ -3416,28 +3403,29 @@
         <v>1990000</v>
       </c>
       <c r="Q39" s="3"/>
-      <c r="R39" s="16"/>
-      <c r="S39" s="16"/>
+      <c r="R39" s="12"/>
+      <c r="S39" s="3"/>
     </row>
     <row r="40" s="1" customFormat="1" spans="1:19">
       <c r="A40" s="1">
         <f t="shared" si="5"/>
-        <v>2004003</v>
+        <v>2003003</v>
       </c>
       <c r="B40" s="12">
-        <v>200400</v>
+        <v>200300</v>
       </c>
       <c r="C40" s="12">
         <v>2</v>
       </c>
-      <c r="D40" s="16" t="s">
+      <c r="D40" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>飛禽走獸</v>
+      </c>
+      <c r="E40" s="13">
+        <v>200300001</v>
+      </c>
+      <c r="F40" s="13" t="s">
         <v>57</v>
-      </c>
-      <c r="E40" s="13">
-        <v>200400009</v>
-      </c>
-      <c r="F40" s="13" t="s">
-        <v>58</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>36</v>
@@ -3473,22 +3461,22 @@
     <row r="41" spans="1:19">
       <c r="A41" s="1">
         <f t="shared" si="5"/>
-        <v>2005001</v>
+        <v>2004001</v>
       </c>
       <c r="B41" s="12">
-        <v>200500</v>
+        <v>200400</v>
       </c>
       <c r="C41" s="12">
         <v>2</v>
       </c>
-      <c r="D41" s="12" t="s">
+      <c r="D41" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E41" s="13">
+        <v>200400009</v>
+      </c>
+      <c r="F41" s="13" t="s">
         <v>59</v>
-      </c>
-      <c r="E41" s="13">
-        <v>200500025</v>
-      </c>
-      <c r="F41" s="13" t="s">
-        <v>60</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>32</v>
@@ -3509,7 +3497,7 @@
         <v>33</v>
       </c>
       <c r="M41" s="20" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="N41">
         <v>5000</v>
@@ -3521,25 +3509,25 @@
       <c r="R41" s="16"/>
       <c r="S41" s="16"/>
     </row>
-    <row r="42" spans="1:19">
+    <row r="42" s="1" customFormat="1" spans="1:19">
       <c r="A42" s="1">
         <f t="shared" si="5"/>
-        <v>2005002</v>
+        <v>2004002</v>
       </c>
       <c r="B42" s="12">
-        <v>200500</v>
+        <v>200400</v>
       </c>
       <c r="C42" s="12">
         <v>2</v>
       </c>
-      <c r="D42" s="12" t="s">
+      <c r="D42" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E42" s="13">
+        <v>200400009</v>
+      </c>
+      <c r="F42" s="13" t="s">
         <v>59</v>
-      </c>
-      <c r="E42" s="13">
-        <v>200500025</v>
-      </c>
-      <c r="F42" s="13" t="s">
-        <v>60</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>35</v>
@@ -3560,7 +3548,7 @@
         <v>33</v>
       </c>
       <c r="M42" s="20" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="N42">
         <v>500000</v>
@@ -3572,25 +3560,25 @@
       <c r="R42" s="16"/>
       <c r="S42" s="16"/>
     </row>
-    <row r="43" spans="1:19">
+    <row r="43" s="1" customFormat="1" spans="1:19">
       <c r="A43" s="1">
         <f t="shared" si="5"/>
-        <v>2005003</v>
+        <v>2004003</v>
       </c>
       <c r="B43" s="12">
-        <v>200500</v>
+        <v>200400</v>
       </c>
       <c r="C43" s="12">
         <v>2</v>
       </c>
-      <c r="D43" s="12" t="s">
+      <c r="D43" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E43" s="13">
+        <v>200400009</v>
+      </c>
+      <c r="F43" s="13" t="s">
         <v>59</v>
-      </c>
-      <c r="E43" s="13">
-        <v>200500025</v>
-      </c>
-      <c r="F43" s="13" t="s">
-        <v>60</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>36</v>
@@ -3611,7 +3599,7 @@
         <v>33</v>
       </c>
       <c r="M43" s="20" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="N43">
         <v>50000000</v>
@@ -3626,22 +3614,22 @@
     <row r="44" spans="1:19">
       <c r="A44" s="1">
         <f t="shared" si="5"/>
-        <v>2006001</v>
+        <v>2005001</v>
       </c>
       <c r="B44" s="12">
-        <v>200600</v>
+        <v>200500</v>
       </c>
       <c r="C44" s="12">
         <v>2</v>
       </c>
-      <c r="D44" s="13" t="s">
-        <v>62</v>
+      <c r="D44" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="E44" s="13">
-        <v>200600001</v>
+        <v>200500025</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>32</v>
@@ -3662,7 +3650,7 @@
         <v>33</v>
       </c>
       <c r="M44" s="20" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="N44">
         <v>5000</v>
@@ -3674,25 +3662,25 @@
       <c r="R44" s="16"/>
       <c r="S44" s="16"/>
     </row>
-    <row r="45" s="1" customFormat="1" spans="1:19">
+    <row r="45" spans="1:19">
       <c r="A45" s="1">
         <f t="shared" si="5"/>
-        <v>2006002</v>
+        <v>2005002</v>
       </c>
       <c r="B45" s="12">
-        <v>200600</v>
+        <v>200500</v>
       </c>
       <c r="C45" s="12">
         <v>2</v>
       </c>
-      <c r="D45" s="13" t="s">
-        <v>62</v>
+      <c r="D45" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="E45" s="13">
-        <v>200600001</v>
+        <v>200500025</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>35</v>
@@ -3713,7 +3701,7 @@
         <v>33</v>
       </c>
       <c r="M45" s="20" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="N45">
         <v>500000</v>
@@ -3725,25 +3713,25 @@
       <c r="R45" s="16"/>
       <c r="S45" s="16"/>
     </row>
-    <row r="46" s="1" customFormat="1" spans="1:19">
+    <row r="46" spans="1:19">
       <c r="A46" s="1">
         <f t="shared" si="5"/>
-        <v>2006003</v>
+        <v>2005003</v>
       </c>
       <c r="B46" s="12">
-        <v>200600</v>
+        <v>200500</v>
       </c>
       <c r="C46" s="12">
         <v>2</v>
       </c>
-      <c r="D46" s="13" t="s">
-        <v>62</v>
+      <c r="D46" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="E46" s="13">
-        <v>200600001</v>
+        <v>200500025</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>36</v>
@@ -3764,7 +3752,7 @@
         <v>33</v>
       </c>
       <c r="M46" s="20" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="N46">
         <v>50000000</v>
@@ -3773,28 +3761,28 @@
         <v>1990000</v>
       </c>
       <c r="Q46" s="3"/>
-      <c r="R46"/>
+      <c r="R46" s="16"/>
       <c r="S46" s="16"/>
     </row>
     <row r="47" spans="1:19">
       <c r="A47" s="1">
         <f t="shared" si="5"/>
-        <v>2007001</v>
+        <v>2006001</v>
       </c>
       <c r="B47" s="12">
-        <v>200700</v>
+        <v>200600</v>
       </c>
       <c r="C47" s="12">
         <v>2</v>
       </c>
-      <c r="D47" s="12" t="s">
+      <c r="D47" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="E47" s="13">
+        <v>200600001</v>
+      </c>
+      <c r="F47" s="13" t="s">
         <v>64</v>
-      </c>
-      <c r="E47" s="13">
-        <v>200700001</v>
-      </c>
-      <c r="F47" s="13" t="s">
-        <v>65</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>32</v>
@@ -3830,23 +3818,22 @@
     <row r="48" s="1" customFormat="1" spans="1:19">
       <c r="A48" s="1">
         <f t="shared" si="5"/>
-        <v>2007002</v>
+        <v>2006002</v>
       </c>
       <c r="B48" s="12">
-        <v>200700</v>
+        <v>200600</v>
       </c>
       <c r="C48" s="12">
         <v>2</v>
       </c>
-      <c r="D48" s="12" t="str">
-        <f t="shared" ref="D45:D49" si="7">D47</f>
-        <v>越南色碟</v>
+      <c r="D48" s="13" t="s">
+        <v>63</v>
       </c>
       <c r="E48" s="13">
-        <v>200700001</v>
+        <v>200600001</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>35</v>
@@ -3882,23 +3869,22 @@
     <row r="49" s="1" customFormat="1" spans="1:19">
       <c r="A49" s="1">
         <f t="shared" si="5"/>
-        <v>2007003</v>
+        <v>2006003</v>
       </c>
       <c r="B49" s="12">
-        <v>200700</v>
+        <v>200600</v>
       </c>
       <c r="C49" s="12">
         <v>2</v>
       </c>
-      <c r="D49" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v>越南色碟</v>
+      <c r="D49" s="13" t="s">
+        <v>63</v>
       </c>
       <c r="E49" s="13">
-        <v>200700001</v>
+        <v>200600001</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>36</v>
@@ -3927,27 +3913,29 @@
       <c r="O49" s="15">
         <v>1990000</v>
       </c>
-      <c r="S49" s="3"/>
-    </row>
-    <row r="50" s="1" customFormat="1" spans="1:19">
+      <c r="Q49" s="3"/>
+      <c r="R49"/>
+      <c r="S49" s="16"/>
+    </row>
+    <row r="50" spans="1:19">
       <c r="A50" s="1">
         <f t="shared" si="5"/>
-        <v>2008001</v>
+        <v>2007001</v>
       </c>
       <c r="B50" s="12">
-        <v>200800</v>
+        <v>200700</v>
       </c>
       <c r="C50" s="12">
         <v>2</v>
       </c>
-      <c r="D50" s="13" t="s">
+      <c r="D50" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E50" s="13">
+        <v>200700001</v>
+      </c>
+      <c r="F50" s="13" t="s">
         <v>66</v>
-      </c>
-      <c r="E50" s="13">
-        <v>200800001</v>
-      </c>
-      <c r="F50" s="13" t="s">
-        <v>67</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>32</v>
@@ -3976,27 +3964,30 @@
       <c r="O50" s="15">
         <v>1990000</v>
       </c>
-      <c r="S50" s="3"/>
+      <c r="Q50" s="3"/>
+      <c r="R50" s="16"/>
+      <c r="S50" s="16"/>
     </row>
     <row r="51" s="1" customFormat="1" spans="1:19">
       <c r="A51" s="1">
         <f t="shared" si="5"/>
-        <v>2008002</v>
+        <v>2007002</v>
       </c>
       <c r="B51" s="12">
-        <v>200800</v>
+        <v>200700</v>
       </c>
       <c r="C51" s="12">
         <v>2</v>
       </c>
-      <c r="D51" s="13" t="s">
+      <c r="D51" s="12" t="str">
+        <f t="shared" ref="D48:D52" si="7">D50</f>
+        <v>越南色碟</v>
+      </c>
+      <c r="E51" s="13">
+        <v>200700001</v>
+      </c>
+      <c r="F51" s="13" t="s">
         <v>66</v>
-      </c>
-      <c r="E51" s="13">
-        <v>200800001</v>
-      </c>
-      <c r="F51" s="13" t="s">
-        <v>67</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>35</v>
@@ -4025,27 +4016,30 @@
       <c r="O51" s="15">
         <v>1990000</v>
       </c>
-      <c r="S51" s="3"/>
+      <c r="Q51" s="3"/>
+      <c r="R51" s="16"/>
+      <c r="S51" s="16"/>
     </row>
     <row r="52" s="1" customFormat="1" spans="1:19">
       <c r="A52" s="1">
         <f t="shared" si="5"/>
-        <v>2008003</v>
+        <v>2007003</v>
       </c>
       <c r="B52" s="12">
-        <v>200800</v>
+        <v>200700</v>
       </c>
       <c r="C52" s="12">
         <v>2</v>
       </c>
-      <c r="D52" s="13" t="s">
+      <c r="D52" s="12" t="str">
+        <f t="shared" si="7"/>
+        <v>越南色碟</v>
+      </c>
+      <c r="E52" s="13">
+        <v>200700001</v>
+      </c>
+      <c r="F52" s="13" t="s">
         <v>66</v>
-      </c>
-      <c r="E52" s="13">
-        <v>200800001</v>
-      </c>
-      <c r="F52" s="13" t="s">
-        <v>67</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>36</v>
@@ -4076,25 +4070,25 @@
       </c>
       <c r="S52" s="3"/>
     </row>
-    <row r="53" spans="1:19">
+    <row r="53" s="1" customFormat="1" spans="1:19">
       <c r="A53" s="1">
         <f t="shared" si="5"/>
-        <v>2009001</v>
-      </c>
-      <c r="B53" s="17">
-        <v>200900</v>
+        <v>2008001</v>
+      </c>
+      <c r="B53" s="12">
+        <v>200800</v>
       </c>
       <c r="C53" s="12">
         <v>2</v>
       </c>
-      <c r="D53" s="17" t="s">
+      <c r="D53" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E53" s="13">
+        <v>200800001</v>
+      </c>
+      <c r="F53" s="13" t="s">
         <v>68</v>
-      </c>
-      <c r="E53" s="13">
-        <v>200900001</v>
-      </c>
-      <c r="F53" s="13" t="s">
-        <v>69</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>32</v>
@@ -4123,27 +4117,27 @@
       <c r="O53" s="15">
         <v>1990000</v>
       </c>
-    </row>
-    <row r="54" spans="1:19">
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" s="1" customFormat="1" spans="1:19">
       <c r="A54" s="1">
         <f t="shared" si="5"/>
-        <v>2009002</v>
+        <v>2008002</v>
       </c>
       <c r="B54" s="12">
-        <v>200900</v>
+        <v>200800</v>
       </c>
       <c r="C54" s="12">
         <v>2</v>
       </c>
-      <c r="D54" s="12" t="str">
-        <f>D53</f>
-        <v>魚蝦蟹</v>
+      <c r="D54" s="13" t="s">
+        <v>67</v>
       </c>
       <c r="E54" s="13">
-        <v>200900001</v>
+        <v>200800001</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>35</v>
@@ -4172,27 +4166,27 @@
       <c r="O54" s="15">
         <v>1990000</v>
       </c>
-    </row>
-    <row r="55" spans="1:19">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" s="1" customFormat="1" spans="1:19">
       <c r="A55" s="1">
         <f t="shared" si="5"/>
-        <v>2009003</v>
+        <v>2008003</v>
       </c>
       <c r="B55" s="12">
-        <v>200900</v>
+        <v>200800</v>
       </c>
       <c r="C55" s="12">
         <v>2</v>
       </c>
-      <c r="D55" s="12" t="str">
-        <f>D54</f>
-        <v>魚蝦蟹</v>
+      <c r="D55" s="13" t="s">
+        <v>67</v>
       </c>
       <c r="E55" s="13">
-        <v>200900001</v>
+        <v>200800001</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>36</v>
@@ -4221,25 +4215,28 @@
       <c r="O55" s="15">
         <v>1990000</v>
       </c>
+      <c r="S55" s="3"/>
     </row>
     <row r="56" spans="1:19">
       <c r="A56" s="1">
         <f t="shared" si="5"/>
-        <v>2010001</v>
-      </c>
-      <c r="B56" s="12">
-        <v>201000</v>
+        <v>2009001</v>
+      </c>
+      <c r="B56" s="17">
+        <v>200900</v>
       </c>
       <c r="C56" s="12">
         <v>2</v>
       </c>
-      <c r="D56" s="12" t="s">
+      <c r="D56" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E56" s="13">
+        <v>200900001</v>
+      </c>
+      <c r="F56" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="E56" s="13">
-        <v>101000006</v>
-      </c>
-      <c r="F56" s="13"/>
       <c r="G56" s="1" t="s">
         <v>32</v>
       </c>
@@ -4271,21 +4268,24 @@
     <row r="57" spans="1:19">
       <c r="A57" s="1">
         <f t="shared" si="5"/>
-        <v>2010002</v>
+        <v>2009002</v>
       </c>
       <c r="B57" s="12">
-        <v>201000</v>
+        <v>200900</v>
       </c>
       <c r="C57" s="12">
         <v>2</v>
       </c>
-      <c r="D57" s="12" t="s">
+      <c r="D57" s="12" t="str">
+        <f>D56</f>
+        <v>魚蝦蟹</v>
+      </c>
+      <c r="E57" s="13">
+        <v>200900001</v>
+      </c>
+      <c r="F57" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="E57" s="13">
-        <v>101000006</v>
-      </c>
-      <c r="F57" s="13"/>
       <c r="G57" s="1" t="s">
         <v>35</v>
       </c>
@@ -4317,21 +4317,24 @@
     <row r="58" spans="1:19">
       <c r="A58" s="1">
         <f t="shared" si="5"/>
-        <v>2010003</v>
+        <v>2009003</v>
       </c>
       <c r="B58" s="12">
-        <v>201000</v>
+        <v>200900</v>
       </c>
       <c r="C58" s="12">
         <v>2</v>
       </c>
-      <c r="D58" s="12" t="s">
+      <c r="D58" s="12" t="str">
+        <f>D57</f>
+        <v>魚蝦蟹</v>
+      </c>
+      <c r="E58" s="13">
+        <v>200900001</v>
+      </c>
+      <c r="F58" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="E58" s="13">
-        <v>101000006</v>
-      </c>
-      <c r="F58" s="13"/>
       <c r="G58" s="1" t="s">
         <v>36</v>
       </c>
@@ -4363,23 +4366,21 @@
     <row r="59" spans="1:19">
       <c r="A59" s="1">
         <f t="shared" si="5"/>
-        <v>3001001</v>
+        <v>2010001</v>
       </c>
       <c r="B59" s="12">
-        <v>300100</v>
+        <v>201000</v>
       </c>
       <c r="C59" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D59" s="12" t="s">
         <v>71</v>
       </c>
       <c r="E59" s="13">
-        <v>300100001</v>
-      </c>
-      <c r="F59" s="13" t="s">
-        <v>72</v>
-      </c>
+        <v>101000006</v>
+      </c>
+      <c r="F59" s="13"/>
       <c r="G59" s="1" t="s">
         <v>32</v>
       </c>
@@ -4395,11 +4396,11 @@
       <c r="K59" s="1">
         <v>0</v>
       </c>
-      <c r="L59" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="M59" s="21" t="s">
-        <v>74</v>
+      <c r="L59" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M59" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N59">
         <v>5000</v>
@@ -4408,26 +4409,24 @@
         <v>1990000</v>
       </c>
     </row>
-    <row r="60" s="1" customFormat="1" spans="1:19">
+    <row r="60" spans="1:19">
       <c r="A60" s="1">
         <f t="shared" si="5"/>
-        <v>3001002</v>
+        <v>2010002</v>
       </c>
       <c r="B60" s="12">
-        <v>300100</v>
+        <v>201000</v>
       </c>
       <c r="C60" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D60" s="12" t="s">
         <v>71</v>
       </c>
       <c r="E60" s="13">
-        <v>300100001</v>
-      </c>
-      <c r="F60" s="13" t="s">
-        <v>72</v>
-      </c>
+        <v>101000006</v>
+      </c>
+      <c r="F60" s="13"/>
       <c r="G60" s="1" t="s">
         <v>35</v>
       </c>
@@ -4443,11 +4442,11 @@
       <c r="K60" s="1">
         <v>0</v>
       </c>
-      <c r="L60" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="M60" s="21" t="s">
-        <v>74</v>
+      <c r="L60" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M60" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N60">
         <v>500000</v>
@@ -4455,28 +4454,25 @@
       <c r="O60" s="15">
         <v>1990000</v>
       </c>
-      <c r="S60" s="3"/>
-    </row>
-    <row r="61" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="61" spans="1:19">
       <c r="A61" s="1">
         <f t="shared" si="5"/>
-        <v>3001003</v>
+        <v>2010003</v>
       </c>
       <c r="B61" s="12">
-        <v>300100</v>
+        <v>201000</v>
       </c>
       <c r="C61" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D61" s="12" t="s">
         <v>71</v>
       </c>
       <c r="E61" s="13">
-        <v>300100001</v>
-      </c>
-      <c r="F61" s="13" t="s">
-        <v>72</v>
-      </c>
+        <v>101000006</v>
+      </c>
+      <c r="F61" s="13"/>
       <c r="G61" s="1" t="s">
         <v>36</v>
       </c>
@@ -4492,11 +4488,11 @@
       <c r="K61" s="1">
         <v>0</v>
       </c>
-      <c r="L61" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="M61" s="21" t="s">
-        <v>74</v>
+      <c r="L61" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M61" s="20" t="s">
+        <v>34</v>
       </c>
       <c r="N61">
         <v>50000000</v>
@@ -4504,27 +4500,26 @@
       <c r="O61" s="15">
         <v>1990000</v>
       </c>
-      <c r="S61" s="3"/>
-    </row>
-    <row r="62" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="62" spans="1:19">
       <c r="A62" s="1">
         <f t="shared" si="5"/>
-        <v>3002001</v>
+        <v>3001001</v>
       </c>
       <c r="B62" s="12">
-        <v>300200</v>
+        <v>300100</v>
       </c>
       <c r="C62" s="12">
         <v>3</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E62" s="13">
-        <v>300200006</v>
+        <v>300100001</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>32</v>
@@ -4533,7 +4528,7 @@
         <v>1</v>
       </c>
       <c r="I62" s="1">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="J62" s="1">
         <v>-1</v>
@@ -4542,10 +4537,10 @@
         <v>0</v>
       </c>
       <c r="L62" s="21" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="M62" s="21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N62">
         <v>5000</v>
@@ -4553,27 +4548,26 @@
       <c r="O62" s="15">
         <v>1990000</v>
       </c>
-      <c r="S62" s="3"/>
     </row>
     <row r="63" s="1" customFormat="1" spans="1:19">
       <c r="A63" s="1">
         <f t="shared" si="5"/>
-        <v>3002002</v>
+        <v>3001002</v>
       </c>
       <c r="B63" s="12">
-        <v>300200</v>
+        <v>300100</v>
       </c>
       <c r="C63" s="12">
         <v>3</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E63" s="13">
-        <v>300200006</v>
+        <v>300100001</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>35</v>
@@ -4591,10 +4585,10 @@
         <v>0</v>
       </c>
       <c r="L63" s="21" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="M63" s="21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N63">
         <v>500000</v>
@@ -4607,22 +4601,22 @@
     <row r="64" s="1" customFormat="1" spans="1:19">
       <c r="A64" s="1">
         <f t="shared" si="5"/>
-        <v>3002003</v>
+        <v>3001003</v>
       </c>
       <c r="B64" s="12">
-        <v>300200</v>
+        <v>300100</v>
       </c>
       <c r="C64" s="12">
         <v>3</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E64" s="13">
-        <v>300200006</v>
+        <v>300100001</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>36</v>
@@ -4640,10 +4634,10 @@
         <v>0</v>
       </c>
       <c r="L64" s="21" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="M64" s="21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N64">
         <v>50000000</v>
@@ -4655,173 +4649,173 @@
     </row>
     <row r="65" s="1" customFormat="1" spans="1:19">
       <c r="A65" s="1">
-        <f t="shared" ref="A65:A71" si="8">B65*100+H65</f>
-        <v>20010010</v>
-      </c>
-      <c r="B65" s="13">
-        <v>200100</v>
-      </c>
-      <c r="C65" s="13">
-        <v>2</v>
-      </c>
-      <c r="D65" s="13" t="s">
-        <v>51</v>
+        <f t="shared" si="5"/>
+        <v>3002001</v>
+      </c>
+      <c r="B65" s="12">
+        <v>300200</v>
+      </c>
+      <c r="C65" s="12">
+        <v>3</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>76</v>
       </c>
       <c r="E65" s="13">
-        <v>200100038</v>
+        <v>300200006</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="G65" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H65" s="1">
+        <v>1</v>
+      </c>
+      <c r="I65" s="1">
+        <v>2000</v>
+      </c>
+      <c r="J65" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K65" s="1">
+        <v>0</v>
+      </c>
+      <c r="L65" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="H65" s="18">
-        <v>10</v>
-      </c>
-      <c r="I65" s="18">
-        <v>0</v>
-      </c>
-      <c r="J65" s="18">
-        <v>-1</v>
-      </c>
-      <c r="K65" s="1">
-        <v>0</v>
-      </c>
-      <c r="L65" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="M65" s="18">
-        <v>0</v>
+      <c r="M65" s="21" t="s">
+        <v>75</v>
       </c>
       <c r="N65">
-        <v>200</v>
-      </c>
-      <c r="O65" s="19">
-        <v>1980000</v>
+        <v>5000</v>
+      </c>
+      <c r="O65" s="15">
+        <v>1990000</v>
       </c>
       <c r="S65" s="3"/>
     </row>
     <row r="66" s="1" customFormat="1" spans="1:19">
       <c r="A66" s="1">
-        <f t="shared" si="8"/>
-        <v>20010011</v>
-      </c>
-      <c r="B66" s="13">
-        <v>200100</v>
-      </c>
-      <c r="C66" s="13">
-        <v>2</v>
-      </c>
-      <c r="D66" s="13" t="s">
-        <v>51</v>
+        <f t="shared" si="5"/>
+        <v>3002002</v>
+      </c>
+      <c r="B66" s="12">
+        <v>300200</v>
+      </c>
+      <c r="C66" s="12">
+        <v>3</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>76</v>
       </c>
       <c r="E66" s="13">
-        <v>200100038</v>
+        <v>300200006</v>
       </c>
       <c r="F66" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="G66" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="H66" s="18">
-        <v>11</v>
-      </c>
-      <c r="I66" s="18">
-        <v>0</v>
-      </c>
-      <c r="J66" s="18">
+        <v>77</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H66" s="1">
+        <v>2</v>
+      </c>
+      <c r="I66" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J66" s="1">
         <v>-1</v>
       </c>
       <c r="K66" s="1">
         <v>0</v>
       </c>
-      <c r="L66" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="M66" s="18">
-        <v>0</v>
+      <c r="L66" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="M66" s="21" t="s">
+        <v>75</v>
       </c>
       <c r="N66">
-        <v>5000</v>
-      </c>
-      <c r="O66" s="19">
-        <v>1980000</v>
+        <v>500000</v>
+      </c>
+      <c r="O66" s="15">
+        <v>1990000</v>
       </c>
       <c r="S66" s="3"/>
     </row>
     <row r="67" s="1" customFormat="1" spans="1:19">
       <c r="A67" s="1">
-        <f t="shared" si="8"/>
-        <v>20010012</v>
-      </c>
-      <c r="B67" s="13">
-        <v>200100</v>
-      </c>
-      <c r="C67" s="13">
-        <v>2</v>
-      </c>
-      <c r="D67" s="13" t="s">
-        <v>51</v>
+        <f t="shared" si="5"/>
+        <v>3002003</v>
+      </c>
+      <c r="B67" s="12">
+        <v>300200</v>
+      </c>
+      <c r="C67" s="12">
+        <v>3</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>76</v>
       </c>
       <c r="E67" s="13">
-        <v>200100038</v>
+        <v>300200006</v>
       </c>
       <c r="F67" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="G67" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="H67" s="18">
-        <v>12</v>
-      </c>
-      <c r="I67" s="18">
-        <v>0</v>
-      </c>
-      <c r="J67" s="18">
+        <v>77</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H67" s="1">
+        <v>3</v>
+      </c>
+      <c r="I67" s="1">
+        <v>50000000</v>
+      </c>
+      <c r="J67" s="1">
         <v>-1</v>
       </c>
       <c r="K67" s="1">
         <v>0</v>
       </c>
-      <c r="L67" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="M67" s="18">
-        <v>0</v>
+      <c r="L67" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="M67" s="21" t="s">
+        <v>75</v>
       </c>
       <c r="N67">
-        <v>100000</v>
-      </c>
-      <c r="O67" s="19">
-        <v>1980000</v>
+        <v>50000000</v>
+      </c>
+      <c r="O67" s="15">
+        <v>1990000</v>
       </c>
       <c r="S67" s="3"/>
     </row>
     <row r="68" s="1" customFormat="1" spans="1:19">
       <c r="A68" s="1">
-        <f t="shared" si="8"/>
-        <v>20010110</v>
+        <f t="shared" ref="A68:A74" si="8">B68*100+H68</f>
+        <v>20010010</v>
       </c>
       <c r="B68" s="13">
-        <v>200101</v>
+        <v>200100</v>
       </c>
       <c r="C68" s="13">
         <v>2</v>
       </c>
       <c r="D68" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E68" s="13">
+        <v>200100038</v>
+      </c>
+      <c r="F68" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="E68" s="13">
-        <v>200101001</v>
-      </c>
-      <c r="F68" s="13" t="s">
-        <v>54</v>
-      </c>
       <c r="G68" s="18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H68" s="18">
         <v>10</v>
@@ -4836,7 +4830,7 @@
         <v>0</v>
       </c>
       <c r="L68" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M68" s="18">
         <v>0</v>
@@ -4852,25 +4846,25 @@
     <row r="69" s="1" customFormat="1" spans="1:19">
       <c r="A69" s="1">
         <f t="shared" si="8"/>
-        <v>20010111</v>
+        <v>20010011</v>
       </c>
       <c r="B69" s="13">
-        <v>200101</v>
+        <v>200100</v>
       </c>
       <c r="C69" s="13">
         <v>2</v>
       </c>
       <c r="D69" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E69" s="13">
+        <v>200100038</v>
+      </c>
+      <c r="F69" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="E69" s="13">
-        <v>200101001</v>
-      </c>
-      <c r="F69" s="13" t="s">
-        <v>54</v>
-      </c>
       <c r="G69" s="18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H69" s="18">
         <v>11</v>
@@ -4885,7 +4879,7 @@
         <v>0</v>
       </c>
       <c r="L69" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M69" s="18">
         <v>0</v>
@@ -4901,25 +4895,25 @@
     <row r="70" s="1" customFormat="1" spans="1:19">
       <c r="A70" s="1">
         <f t="shared" si="8"/>
-        <v>20010112</v>
+        <v>20010012</v>
       </c>
       <c r="B70" s="13">
-        <v>200101</v>
+        <v>200100</v>
       </c>
       <c r="C70" s="13">
         <v>2</v>
       </c>
       <c r="D70" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E70" s="13">
+        <v>200100038</v>
+      </c>
+      <c r="F70" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="E70" s="13">
-        <v>200101001</v>
-      </c>
-      <c r="F70" s="13" t="s">
-        <v>54</v>
-      </c>
       <c r="G70" s="18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H70" s="18">
         <v>12</v>
@@ -4934,7 +4928,7 @@
         <v>0</v>
       </c>
       <c r="L70" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M70" s="18">
         <v>0</v>
@@ -4950,25 +4944,25 @@
     <row r="71" s="1" customFormat="1" spans="1:19">
       <c r="A71" s="1">
         <f t="shared" si="8"/>
-        <v>20030010</v>
+        <v>20010110</v>
       </c>
       <c r="B71" s="13">
-        <v>200300</v>
+        <v>200101</v>
       </c>
       <c r="C71" s="13">
         <v>2</v>
       </c>
       <c r="D71" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E71" s="13">
+        <v>200101001</v>
+      </c>
+      <c r="F71" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="E71" s="13">
-        <v>200300001</v>
-      </c>
-      <c r="F71" s="13" t="s">
-        <v>56</v>
-      </c>
       <c r="G71" s="18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H71" s="18">
         <v>10</v>
@@ -4983,7 +4977,7 @@
         <v>0</v>
       </c>
       <c r="L71" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M71" s="18">
         <v>0</v>
@@ -4998,26 +4992,26 @@
     </row>
     <row r="72" s="1" customFormat="1" spans="1:19">
       <c r="A72" s="1">
-        <f t="shared" ref="A72:A80" si="9">B72*100+H72</f>
-        <v>20030011</v>
+        <f t="shared" si="8"/>
+        <v>20010111</v>
       </c>
       <c r="B72" s="13">
-        <v>200300</v>
+        <v>200101</v>
       </c>
       <c r="C72" s="13">
         <v>2</v>
       </c>
       <c r="D72" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E72" s="13">
+        <v>200101001</v>
+      </c>
+      <c r="F72" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="E72" s="13">
-        <v>200300001</v>
-      </c>
-      <c r="F72" s="13" t="s">
-        <v>56</v>
-      </c>
       <c r="G72" s="18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H72" s="18">
         <v>11</v>
@@ -5032,7 +5026,7 @@
         <v>0</v>
       </c>
       <c r="L72" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M72" s="18">
         <v>0</v>
@@ -5047,26 +5041,26 @@
     </row>
     <row r="73" s="1" customFormat="1" spans="1:19">
       <c r="A73" s="1">
-        <f t="shared" si="9"/>
-        <v>20030012</v>
+        <f t="shared" si="8"/>
+        <v>20010112</v>
       </c>
       <c r="B73" s="13">
-        <v>200300</v>
+        <v>200101</v>
       </c>
       <c r="C73" s="13">
         <v>2</v>
       </c>
       <c r="D73" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E73" s="13">
+        <v>200101001</v>
+      </c>
+      <c r="F73" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="E73" s="13">
-        <v>200300001</v>
-      </c>
-      <c r="F73" s="13" t="s">
-        <v>56</v>
-      </c>
       <c r="G73" s="18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H73" s="18">
         <v>12</v>
@@ -5081,7 +5075,7 @@
         <v>0</v>
       </c>
       <c r="L73" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M73" s="18">
         <v>0</v>
@@ -5096,26 +5090,26 @@
     </row>
     <row r="74" s="1" customFormat="1" spans="1:19">
       <c r="A74" s="1">
-        <f t="shared" si="9"/>
-        <v>20040010</v>
+        <f t="shared" si="8"/>
+        <v>20030010</v>
       </c>
       <c r="B74" s="13">
-        <v>200400</v>
+        <v>200300</v>
       </c>
       <c r="C74" s="13">
         <v>2</v>
       </c>
-      <c r="D74" s="16" t="s">
+      <c r="D74" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E74" s="13">
+        <v>200300001</v>
+      </c>
+      <c r="F74" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="E74" s="13">
-        <v>200400009</v>
-      </c>
-      <c r="F74" s="13" t="s">
-        <v>58</v>
-      </c>
       <c r="G74" s="18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H74" s="18">
         <v>10</v>
@@ -5130,7 +5124,7 @@
         <v>0</v>
       </c>
       <c r="L74" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M74" s="18">
         <v>0</v>
@@ -5145,26 +5139,26 @@
     </row>
     <row r="75" s="1" customFormat="1" spans="1:19">
       <c r="A75" s="1">
-        <f t="shared" si="9"/>
-        <v>20040011</v>
+        <f t="shared" ref="A75:A83" si="9">B75*100+H75</f>
+        <v>20030011</v>
       </c>
       <c r="B75" s="13">
-        <v>200400</v>
+        <v>200300</v>
       </c>
       <c r="C75" s="13">
         <v>2</v>
       </c>
-      <c r="D75" s="16" t="s">
+      <c r="D75" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E75" s="13">
+        <v>200300001</v>
+      </c>
+      <c r="F75" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="E75" s="13">
-        <v>200400009</v>
-      </c>
-      <c r="F75" s="13" t="s">
-        <v>58</v>
-      </c>
       <c r="G75" s="18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H75" s="18">
         <v>11</v>
@@ -5179,7 +5173,7 @@
         <v>0</v>
       </c>
       <c r="L75" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M75" s="18">
         <v>0</v>
@@ -5195,25 +5189,25 @@
     <row r="76" s="1" customFormat="1" spans="1:19">
       <c r="A76" s="1">
         <f t="shared" si="9"/>
-        <v>20040012</v>
+        <v>20030012</v>
       </c>
       <c r="B76" s="13">
-        <v>200400</v>
+        <v>200300</v>
       </c>
       <c r="C76" s="13">
         <v>2</v>
       </c>
-      <c r="D76" s="16" t="s">
+      <c r="D76" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E76" s="13">
+        <v>200300001</v>
+      </c>
+      <c r="F76" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="E76" s="13">
-        <v>200400009</v>
-      </c>
-      <c r="F76" s="13" t="s">
-        <v>58</v>
-      </c>
       <c r="G76" s="18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H76" s="18">
         <v>12</v>
@@ -5228,7 +5222,7 @@
         <v>0</v>
       </c>
       <c r="L76" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M76" s="18">
         <v>0</v>
@@ -5244,25 +5238,25 @@
     <row r="77" s="1" customFormat="1" spans="1:19">
       <c r="A77" s="1">
         <f t="shared" si="9"/>
-        <v>20050010</v>
+        <v>20040010</v>
       </c>
       <c r="B77" s="13">
-        <v>200500</v>
+        <v>200400</v>
       </c>
       <c r="C77" s="13">
         <v>2</v>
       </c>
-      <c r="D77" s="13" t="s">
+      <c r="D77" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E77" s="13">
+        <v>200400009</v>
+      </c>
+      <c r="F77" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E77" s="13">
-        <v>200500025</v>
-      </c>
-      <c r="F77" s="13" t="s">
-        <v>60</v>
-      </c>
       <c r="G77" s="18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H77" s="18">
         <v>10</v>
@@ -5277,7 +5271,7 @@
         <v>0</v>
       </c>
       <c r="L77" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M77" s="18">
         <v>0</v>
@@ -5293,25 +5287,25 @@
     <row r="78" s="1" customFormat="1" spans="1:19">
       <c r="A78" s="1">
         <f t="shared" si="9"/>
-        <v>20050011</v>
+        <v>20040011</v>
       </c>
       <c r="B78" s="13">
-        <v>200500</v>
+        <v>200400</v>
       </c>
       <c r="C78" s="13">
         <v>2</v>
       </c>
-      <c r="D78" s="13" t="s">
+      <c r="D78" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E78" s="13">
+        <v>200400009</v>
+      </c>
+      <c r="F78" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E78" s="13">
-        <v>200500025</v>
-      </c>
-      <c r="F78" s="13" t="s">
-        <v>60</v>
-      </c>
       <c r="G78" s="18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H78" s="18">
         <v>11</v>
@@ -5326,7 +5320,7 @@
         <v>0</v>
       </c>
       <c r="L78" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M78" s="18">
         <v>0</v>
@@ -5342,25 +5336,25 @@
     <row r="79" s="1" customFormat="1" spans="1:19">
       <c r="A79" s="1">
         <f t="shared" si="9"/>
-        <v>20050012</v>
+        <v>20040012</v>
       </c>
       <c r="B79" s="13">
-        <v>200500</v>
+        <v>200400</v>
       </c>
       <c r="C79" s="13">
         <v>2</v>
       </c>
-      <c r="D79" s="13" t="s">
+      <c r="D79" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E79" s="13">
+        <v>200400009</v>
+      </c>
+      <c r="F79" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E79" s="13">
-        <v>200500025</v>
-      </c>
-      <c r="F79" s="13" t="s">
-        <v>60</v>
-      </c>
       <c r="G79" s="18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H79" s="18">
         <v>12</v>
@@ -5375,7 +5369,7 @@
         <v>0</v>
       </c>
       <c r="L79" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M79" s="18">
         <v>0</v>
@@ -5388,28 +5382,28 @@
       </c>
       <c r="S79" s="3"/>
     </row>
-    <row r="80" spans="1:19">
+    <row r="80" s="1" customFormat="1" spans="1:19">
       <c r="A80" s="1">
         <f t="shared" si="9"/>
-        <v>20060010</v>
+        <v>20050010</v>
       </c>
       <c r="B80" s="13">
-        <v>200600</v>
+        <v>200500</v>
       </c>
       <c r="C80" s="13">
         <v>2</v>
       </c>
       <c r="D80" s="13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E80" s="13">
-        <v>200600001</v>
+        <v>200500025</v>
       </c>
       <c r="F80" s="13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G80" s="18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H80" s="18">
         <v>10</v>
@@ -5424,7 +5418,7 @@
         <v>0</v>
       </c>
       <c r="L80" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M80" s="18">
         <v>0</v>
@@ -5435,29 +5429,30 @@
       <c r="O80" s="19">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="81" spans="1:19">
+      <c r="S80" s="3"/>
+    </row>
+    <row r="81" s="1" customFormat="1" spans="1:19">
       <c r="A81" s="1">
-        <f t="shared" ref="A81:A95" si="10">B81*100+H81</f>
-        <v>20060011</v>
+        <f t="shared" si="9"/>
+        <v>20050011</v>
       </c>
       <c r="B81" s="13">
-        <v>200600</v>
+        <v>200500</v>
       </c>
       <c r="C81" s="13">
         <v>2</v>
       </c>
       <c r="D81" s="13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E81" s="13">
-        <v>200600001</v>
+        <v>200500025</v>
       </c>
       <c r="F81" s="13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G81" s="18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H81" s="18">
         <v>11</v>
@@ -5472,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="L81" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M81" s="18">
         <v>0</v>
@@ -5483,29 +5478,30 @@
       <c r="O81" s="19">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="82" spans="1:19">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" s="1" customFormat="1" spans="1:19">
       <c r="A82" s="1">
-        <f t="shared" si="10"/>
-        <v>20060012</v>
+        <f t="shared" si="9"/>
+        <v>20050012</v>
       </c>
       <c r="B82" s="13">
-        <v>200600</v>
+        <v>200500</v>
       </c>
       <c r="C82" s="13">
         <v>2</v>
       </c>
       <c r="D82" s="13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E82" s="13">
-        <v>200600001</v>
+        <v>200500025</v>
       </c>
       <c r="F82" s="13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G82" s="18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H82" s="18">
         <v>12</v>
@@ -5520,7 +5516,7 @@
         <v>0</v>
       </c>
       <c r="L82" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M82" s="18">
         <v>0</v>
@@ -5531,29 +5527,30 @@
       <c r="O82" s="19">
         <v>1980000</v>
       </c>
+      <c r="S82" s="3"/>
     </row>
     <row r="83" spans="1:19">
       <c r="A83" s="1">
-        <f t="shared" si="10"/>
-        <v>20070010</v>
+        <f t="shared" si="9"/>
+        <v>20060010</v>
       </c>
       <c r="B83" s="13">
-        <v>200700</v>
+        <v>200600</v>
       </c>
       <c r="C83" s="13">
         <v>2</v>
       </c>
-      <c r="D83" s="12" t="s">
+      <c r="D83" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="E83" s="13">
+        <v>200600001</v>
+      </c>
+      <c r="F83" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="E83" s="13">
-        <v>200700001</v>
-      </c>
-      <c r="F83" s="13" t="s">
-        <v>65</v>
-      </c>
       <c r="G83" s="18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H83" s="18">
         <v>10</v>
@@ -5568,7 +5565,7 @@
         <v>0</v>
       </c>
       <c r="L83" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M83" s="18">
         <v>0</v>
@@ -5582,27 +5579,26 @@
     </row>
     <row r="84" spans="1:19">
       <c r="A84" s="1">
-        <f t="shared" si="10"/>
-        <v>20070011</v>
+        <f t="shared" ref="A84:A98" si="10">B84*100+H84</f>
+        <v>20060011</v>
       </c>
       <c r="B84" s="13">
-        <v>200700</v>
+        <v>200600</v>
       </c>
       <c r="C84" s="13">
         <v>2</v>
       </c>
-      <c r="D84" s="12" t="str">
-        <f>D83</f>
-        <v>越南色碟</v>
+      <c r="D84" s="13" t="s">
+        <v>63</v>
       </c>
       <c r="E84" s="13">
-        <v>200700001</v>
+        <v>200600001</v>
       </c>
       <c r="F84" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G84" s="18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H84" s="18">
         <v>11</v>
@@ -5617,7 +5613,7 @@
         <v>0</v>
       </c>
       <c r="L84" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M84" s="18">
         <v>0</v>
@@ -5632,26 +5628,25 @@
     <row r="85" spans="1:19">
       <c r="A85" s="1">
         <f t="shared" si="10"/>
-        <v>20070012</v>
+        <v>20060012</v>
       </c>
       <c r="B85" s="13">
-        <v>200700</v>
+        <v>200600</v>
       </c>
       <c r="C85" s="13">
         <v>2</v>
       </c>
-      <c r="D85" s="12" t="str">
-        <f>D84</f>
-        <v>越南色碟</v>
+      <c r="D85" s="13" t="s">
+        <v>63</v>
       </c>
       <c r="E85" s="13">
-        <v>200700001</v>
+        <v>200600001</v>
       </c>
       <c r="F85" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G85" s="18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H85" s="18">
         <v>12</v>
@@ -5666,7 +5661,7 @@
         <v>0</v>
       </c>
       <c r="L85" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M85" s="18">
         <v>0</v>
@@ -5681,25 +5676,25 @@
     <row r="86" spans="1:19">
       <c r="A86" s="1">
         <f t="shared" si="10"/>
-        <v>20080010</v>
+        <v>20070010</v>
       </c>
       <c r="B86" s="13">
-        <v>200800</v>
+        <v>200700</v>
       </c>
       <c r="C86" s="13">
         <v>2</v>
       </c>
-      <c r="D86" s="13" t="s">
+      <c r="D86" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E86" s="13">
+        <v>200700001</v>
+      </c>
+      <c r="F86" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="E86" s="13">
-        <v>200800001</v>
-      </c>
-      <c r="F86" s="13" t="s">
-        <v>67</v>
-      </c>
       <c r="G86" s="18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H86" s="18">
         <v>10</v>
@@ -5714,7 +5709,7 @@
         <v>0</v>
       </c>
       <c r="L86" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M86" s="18">
         <v>0</v>
@@ -5729,25 +5724,26 @@
     <row r="87" spans="1:19">
       <c r="A87" s="1">
         <f t="shared" si="10"/>
-        <v>20080011</v>
+        <v>20070011</v>
       </c>
       <c r="B87" s="13">
-        <v>200800</v>
+        <v>200700</v>
       </c>
       <c r="C87" s="13">
         <v>2</v>
       </c>
-      <c r="D87" s="13" t="s">
+      <c r="D87" s="12" t="str">
+        <f>D86</f>
+        <v>越南色碟</v>
+      </c>
+      <c r="E87" s="13">
+        <v>200700001</v>
+      </c>
+      <c r="F87" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="E87" s="13">
-        <v>200800001</v>
-      </c>
-      <c r="F87" s="13" t="s">
-        <v>67</v>
-      </c>
       <c r="G87" s="18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H87" s="18">
         <v>11</v>
@@ -5762,7 +5758,7 @@
         <v>0</v>
       </c>
       <c r="L87" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M87" s="18">
         <v>0</v>
@@ -5777,25 +5773,26 @@
     <row r="88" spans="1:19">
       <c r="A88" s="1">
         <f t="shared" si="10"/>
-        <v>20080012</v>
+        <v>20070012</v>
       </c>
       <c r="B88" s="13">
-        <v>200800</v>
+        <v>200700</v>
       </c>
       <c r="C88" s="13">
         <v>2</v>
       </c>
-      <c r="D88" s="13" t="s">
+      <c r="D88" s="12" t="str">
+        <f>D87</f>
+        <v>越南色碟</v>
+      </c>
+      <c r="E88" s="13">
+        <v>200700001</v>
+      </c>
+      <c r="F88" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="E88" s="13">
-        <v>200800001</v>
-      </c>
-      <c r="F88" s="13" t="s">
-        <v>67</v>
-      </c>
       <c r="G88" s="18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H88" s="18">
         <v>12</v>
@@ -5810,7 +5807,7 @@
         <v>0</v>
       </c>
       <c r="L88" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M88" s="18">
         <v>0</v>
@@ -5825,25 +5822,25 @@
     <row r="89" spans="1:19">
       <c r="A89" s="1">
         <f t="shared" si="10"/>
-        <v>20090010</v>
+        <v>20080010</v>
       </c>
       <c r="B89" s="13">
-        <v>200900</v>
+        <v>200800</v>
       </c>
       <c r="C89" s="13">
         <v>2</v>
       </c>
       <c r="D89" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E89" s="13">
+        <v>200800001</v>
+      </c>
+      <c r="F89" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="E89" s="13">
-        <v>200900001</v>
-      </c>
-      <c r="F89" s="13" t="s">
-        <v>69</v>
-      </c>
       <c r="G89" s="18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H89" s="18">
         <v>10</v>
@@ -5858,7 +5855,7 @@
         <v>0</v>
       </c>
       <c r="L89" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M89" s="18">
         <v>0</v>
@@ -5873,25 +5870,25 @@
     <row r="90" spans="1:19">
       <c r="A90" s="1">
         <f t="shared" si="10"/>
-        <v>20090011</v>
+        <v>20080011</v>
       </c>
       <c r="B90" s="13">
-        <v>200900</v>
+        <v>200800</v>
       </c>
       <c r="C90" s="13">
         <v>2</v>
       </c>
       <c r="D90" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E90" s="13">
+        <v>200800001</v>
+      </c>
+      <c r="F90" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="E90" s="13">
-        <v>200900001</v>
-      </c>
-      <c r="F90" s="13" t="s">
-        <v>69</v>
-      </c>
       <c r="G90" s="18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H90" s="18">
         <v>11</v>
@@ -5906,7 +5903,7 @@
         <v>0</v>
       </c>
       <c r="L90" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M90" s="18">
         <v>0</v>
@@ -5921,25 +5918,25 @@
     <row r="91" spans="1:19">
       <c r="A91" s="1">
         <f t="shared" si="10"/>
-        <v>20090012</v>
+        <v>20080012</v>
       </c>
       <c r="B91" s="13">
-        <v>200900</v>
+        <v>200800</v>
       </c>
       <c r="C91" s="13">
         <v>2</v>
       </c>
       <c r="D91" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E91" s="13">
+        <v>200800001</v>
+      </c>
+      <c r="F91" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="E91" s="13">
-        <v>200900001</v>
-      </c>
-      <c r="F91" s="13" t="s">
-        <v>69</v>
-      </c>
       <c r="G91" s="18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H91" s="18">
         <v>12</v>
@@ -5954,7 +5951,7 @@
         <v>0</v>
       </c>
       <c r="L91" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M91" s="18">
         <v>0</v>
@@ -5966,28 +5963,28 @@
         <v>1980000</v>
       </c>
     </row>
-    <row r="92" s="1" customFormat="1" spans="1:19">
+    <row r="92" spans="1:19">
       <c r="A92" s="1">
         <f t="shared" si="10"/>
-        <v>30020010</v>
-      </c>
-      <c r="B92" s="12">
-        <v>300200</v>
-      </c>
-      <c r="C92" s="12">
-        <v>3</v>
-      </c>
-      <c r="D92" s="12" t="s">
-        <v>75</v>
+        <v>20090010</v>
+      </c>
+      <c r="B92" s="13">
+        <v>200900</v>
+      </c>
+      <c r="C92" s="13">
+        <v>2</v>
+      </c>
+      <c r="D92" s="13" t="s">
+        <v>69</v>
       </c>
       <c r="E92" s="13">
-        <v>300200006</v>
+        <v>200900001</v>
       </c>
       <c r="F92" s="13" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G92" s="18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H92" s="18">
         <v>10</v>
@@ -5995,14 +5992,14 @@
       <c r="I92" s="18">
         <v>0</v>
       </c>
-      <c r="J92" s="1">
+      <c r="J92" s="18">
         <v>-1</v>
       </c>
       <c r="K92" s="1">
         <v>0</v>
       </c>
-      <c r="L92" s="21" t="s">
-        <v>82</v>
+      <c r="L92" s="18" t="s">
+        <v>80</v>
       </c>
       <c r="M92" s="18">
         <v>0</v>
@@ -6013,30 +6010,29 @@
       <c r="O92" s="19">
         <v>1980000</v>
       </c>
-      <c r="S92" s="3"/>
-    </row>
-    <row r="93" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="93" spans="1:19">
       <c r="A93" s="1">
         <f t="shared" si="10"/>
-        <v>30020011</v>
-      </c>
-      <c r="B93" s="12">
-        <v>300200</v>
-      </c>
-      <c r="C93" s="12">
-        <v>3</v>
-      </c>
-      <c r="D93" s="12" t="s">
-        <v>75</v>
+        <v>20090011</v>
+      </c>
+      <c r="B93" s="13">
+        <v>200900</v>
+      </c>
+      <c r="C93" s="13">
+        <v>2</v>
+      </c>
+      <c r="D93" s="13" t="s">
+        <v>69</v>
       </c>
       <c r="E93" s="13">
-        <v>300200006</v>
+        <v>200900001</v>
       </c>
       <c r="F93" s="13" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G93" s="18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H93" s="18">
         <v>11</v>
@@ -6044,14 +6040,14 @@
       <c r="I93" s="18">
         <v>0</v>
       </c>
-      <c r="J93" s="1">
+      <c r="J93" s="18">
         <v>-1</v>
       </c>
       <c r="K93" s="1">
         <v>0</v>
       </c>
-      <c r="L93" s="21" t="s">
-        <v>82</v>
+      <c r="L93" s="18" t="s">
+        <v>80</v>
       </c>
       <c r="M93" s="18">
         <v>0</v>
@@ -6062,30 +6058,29 @@
       <c r="O93" s="19">
         <v>1980000</v>
       </c>
-      <c r="S93" s="3"/>
-    </row>
-    <row r="94" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="94" spans="1:19">
       <c r="A94" s="1">
         <f t="shared" si="10"/>
-        <v>30020012</v>
-      </c>
-      <c r="B94" s="12">
-        <v>300200</v>
-      </c>
-      <c r="C94" s="12">
-        <v>3</v>
-      </c>
-      <c r="D94" s="12" t="s">
-        <v>75</v>
+        <v>20090012</v>
+      </c>
+      <c r="B94" s="13">
+        <v>200900</v>
+      </c>
+      <c r="C94" s="13">
+        <v>2</v>
+      </c>
+      <c r="D94" s="13" t="s">
+        <v>69</v>
       </c>
       <c r="E94" s="13">
-        <v>300200006</v>
+        <v>200900001</v>
       </c>
       <c r="F94" s="13" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G94" s="18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H94" s="18">
         <v>12</v>
@@ -6093,14 +6088,14 @@
       <c r="I94" s="18">
         <v>0</v>
       </c>
-      <c r="J94" s="1">
+      <c r="J94" s="18">
         <v>-1</v>
       </c>
       <c r="K94" s="1">
         <v>0</v>
       </c>
-      <c r="L94" s="21" t="s">
-        <v>82</v>
+      <c r="L94" s="18" t="s">
+        <v>80</v>
       </c>
       <c r="M94" s="18">
         <v>0</v>
@@ -6111,7 +6106,153 @@
       <c r="O94" s="19">
         <v>1980000</v>
       </c>
-      <c r="S94" s="3"/>
+    </row>
+    <row r="95" s="1" customFormat="1" spans="1:19">
+      <c r="A95" s="1">
+        <f t="shared" si="10"/>
+        <v>30020010</v>
+      </c>
+      <c r="B95" s="12">
+        <v>300200</v>
+      </c>
+      <c r="C95" s="12">
+        <v>3</v>
+      </c>
+      <c r="D95" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E95" s="13">
+        <v>300200006</v>
+      </c>
+      <c r="F95" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="G95" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="H95" s="18">
+        <v>10</v>
+      </c>
+      <c r="I95" s="18">
+        <v>0</v>
+      </c>
+      <c r="J95" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K95" s="1">
+        <v>0</v>
+      </c>
+      <c r="L95" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="M95" s="18">
+        <v>0</v>
+      </c>
+      <c r="N95">
+        <v>200</v>
+      </c>
+      <c r="O95" s="19">
+        <v>1980000</v>
+      </c>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" s="1" customFormat="1" spans="1:19">
+      <c r="A96" s="1">
+        <f t="shared" si="10"/>
+        <v>30020011</v>
+      </c>
+      <c r="B96" s="12">
+        <v>300200</v>
+      </c>
+      <c r="C96" s="12">
+        <v>3</v>
+      </c>
+      <c r="D96" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E96" s="13">
+        <v>300200006</v>
+      </c>
+      <c r="F96" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="G96" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="H96" s="18">
+        <v>11</v>
+      </c>
+      <c r="I96" s="18">
+        <v>0</v>
+      </c>
+      <c r="J96" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K96" s="1">
+        <v>0</v>
+      </c>
+      <c r="L96" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="M96" s="18">
+        <v>0</v>
+      </c>
+      <c r="N96">
+        <v>5000</v>
+      </c>
+      <c r="O96" s="19">
+        <v>1980000</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" s="1" customFormat="1" spans="1:19">
+      <c r="A97" s="1">
+        <f t="shared" si="10"/>
+        <v>30020012</v>
+      </c>
+      <c r="B97" s="12">
+        <v>300200</v>
+      </c>
+      <c r="C97" s="12">
+        <v>3</v>
+      </c>
+      <c r="D97" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E97" s="13">
+        <v>300200006</v>
+      </c>
+      <c r="F97" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="G97" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="H97" s="18">
+        <v>12</v>
+      </c>
+      <c r="I97" s="18">
+        <v>0</v>
+      </c>
+      <c r="J97" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K97" s="1">
+        <v>0</v>
+      </c>
+      <c r="L97" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="M97" s="18">
+        <v>0</v>
+      </c>
+      <c r="N97">
+        <v>100000</v>
+      </c>
+      <c r="O97" s="19">
+        <v>1980000</v>
+      </c>
+      <c r="S97" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -302,7 +302,7 @@
     <t>雷神</t>
   </si>
   <si>
-    <t>leishen</t>
+    <t>Thor</t>
   </si>
   <si>
     <t>圣诞狂欢夜</t>
@@ -2587,7 +2587,7 @@
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="1">
-        <f t="shared" ref="A23:A28" si="4">B23*10+H23</f>
+        <f t="shared" ref="A23:A31" si="4">B23*10+H23</f>
         <v>1022001</v>
       </c>
       <c r="B23" s="12">
@@ -2875,7 +2875,7 @@
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="1">
-        <f>B29*10+H29</f>
+        <f t="shared" si="4"/>
         <v>1021001</v>
       </c>
       <c r="B29" s="12">
@@ -2921,7 +2921,7 @@
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="1">
-        <f>B30*10+H30</f>
+        <f t="shared" si="4"/>
         <v>1021002</v>
       </c>
       <c r="B30" s="12">
@@ -2967,7 +2967,7 @@
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="1">
-        <f>B31*10+H31</f>
+        <f t="shared" si="4"/>
         <v>1021003</v>
       </c>
       <c r="B31" s="12">

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="794"/>
+    <workbookView windowWidth="27945" windowHeight="11925" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Warehouse" sheetId="42" r:id="rId1"/>
@@ -156,7 +156,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="84">
   <si>
     <t>sid</t>
   </si>
@@ -631,7 +631,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -659,6 +659,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1000,7 +1012,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1024,16 +1036,16 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1042,85 +1054,85 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
@@ -1143,7 +1155,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1198,17 +1210,33 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1541,7 +1569,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S97"/>
+  <dimension ref="A1:S124"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="3" width="9.375" style="1"/>
@@ -1739,7 +1767,7 @@
       <c r="L5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M5" s="20" t="s">
+      <c r="M5" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N5">
@@ -1788,7 +1816,7 @@
       <c r="L6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M6" s="20" t="s">
+      <c r="M6" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N6">
@@ -1837,7 +1865,7 @@
       <c r="L7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M7" s="20" t="s">
+      <c r="M7" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N7">
@@ -1885,7 +1913,7 @@
       <c r="L8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M8" s="20" t="s">
+      <c r="M8" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N8">
@@ -1935,7 +1963,7 @@
       <c r="L9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M9" s="20" t="s">
+      <c r="M9" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N9">
@@ -1985,7 +2013,7 @@
       <c r="L10" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M10" s="20" t="s">
+      <c r="M10" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N10">
@@ -2033,7 +2061,7 @@
       <c r="L11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M11" s="20" t="s">
+      <c r="M11" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N11">
@@ -2083,7 +2111,7 @@
       <c r="L12" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M12" s="20" t="s">
+      <c r="M12" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N12">
@@ -2133,7 +2161,7 @@
       <c r="L13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M13" s="20" t="s">
+      <c r="M13" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N13">
@@ -2181,7 +2209,7 @@
       <c r="L14" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M14" s="20" t="s">
+      <c r="M14" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N14">
@@ -2231,7 +2259,7 @@
       <c r="L15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M15" s="20" t="s">
+      <c r="M15" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N15">
@@ -2281,7 +2309,7 @@
       <c r="L16" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M16" s="20" t="s">
+      <c r="M16" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N16">
@@ -2329,7 +2357,7 @@
       <c r="L17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M17" s="20" t="s">
+      <c r="M17" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N17">
@@ -2379,7 +2407,7 @@
       <c r="L18" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M18" s="20" t="s">
+      <c r="M18" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N18">
@@ -2429,7 +2457,7 @@
       <c r="L19" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M19" s="20" t="s">
+      <c r="M19" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N19">
@@ -2477,7 +2505,7 @@
       <c r="L20" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M20" s="20" t="s">
+      <c r="M20" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N20">
@@ -2526,7 +2554,7 @@
       <c r="L21" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M21" s="20" t="s">
+      <c r="M21" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N21">
@@ -2575,7 +2603,7 @@
       <c r="L22" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M22" s="20" t="s">
+      <c r="M22" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N22">
@@ -2623,7 +2651,7 @@
       <c r="L23" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M23" s="20" t="s">
+      <c r="M23" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N23">
@@ -2671,7 +2699,7 @@
       <c r="L24" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M24" s="20" t="s">
+      <c r="M24" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N24">
@@ -2719,7 +2747,7 @@
       <c r="L25" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M25" s="20" t="s">
+      <c r="M25" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N25">
@@ -2767,7 +2795,7 @@
       <c r="L26" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M26" s="20" t="s">
+      <c r="M26" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N26">
@@ -2815,7 +2843,7 @@
       <c r="L27" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M27" s="20" t="s">
+      <c r="M27" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N27">
@@ -2863,7 +2891,7 @@
       <c r="L28" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M28" s="20" t="s">
+      <c r="M28" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N28">
@@ -2909,7 +2937,7 @@
       <c r="L29" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M29" s="20" t="s">
+      <c r="M29" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N29">
@@ -2955,7 +2983,7 @@
       <c r="L30" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M30" s="20" t="s">
+      <c r="M30" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N30">
@@ -3001,7 +3029,7 @@
       <c r="L31" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M31" s="20" t="s">
+      <c r="M31" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N31">
@@ -3049,7 +3077,7 @@
       <c r="L32" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M32" s="20" t="s">
+      <c r="M32" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N32">
@@ -3098,7 +3126,7 @@
       <c r="L33" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M33" s="20" t="s">
+      <c r="M33" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N33">
@@ -3147,7 +3175,7 @@
       <c r="L34" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M34" s="20" t="s">
+      <c r="M34" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N34">
@@ -3196,7 +3224,7 @@
       <c r="L35" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M35" s="20" t="s">
+      <c r="M35" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N35">
@@ -3245,7 +3273,7 @@
       <c r="L36" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M36" s="20" t="s">
+      <c r="M36" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N36">
@@ -3295,7 +3323,7 @@
       <c r="L37" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M37" s="20" t="s">
+      <c r="M37" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N37">
@@ -3344,7 +3372,7 @@
       <c r="L38" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M38" s="20" t="s">
+      <c r="M38" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N38">
@@ -3393,7 +3421,7 @@
       <c r="L39" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M39" s="20" t="s">
+      <c r="M39" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N39">
@@ -3445,7 +3473,7 @@
       <c r="L40" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M40" s="20" t="s">
+      <c r="M40" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N40">
@@ -3496,7 +3524,7 @@
       <c r="L41" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M41" s="20" t="s">
+      <c r="M41" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N41">
@@ -3547,7 +3575,7 @@
       <c r="L42" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M42" s="20" t="s">
+      <c r="M42" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N42">
@@ -3598,7 +3626,7 @@
       <c r="L43" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M43" s="20" t="s">
+      <c r="M43" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N43">
@@ -3649,7 +3677,7 @@
       <c r="L44" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M44" s="20" t="s">
+      <c r="M44" s="25" t="s">
         <v>62</v>
       </c>
       <c r="N44">
@@ -3700,7 +3728,7 @@
       <c r="L45" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M45" s="20" t="s">
+      <c r="M45" s="25" t="s">
         <v>62</v>
       </c>
       <c r="N45">
@@ -3751,7 +3779,7 @@
       <c r="L46" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M46" s="20" t="s">
+      <c r="M46" s="25" t="s">
         <v>62</v>
       </c>
       <c r="N46">
@@ -3802,7 +3830,7 @@
       <c r="L47" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M47" s="20" t="s">
+      <c r="M47" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N47">
@@ -3853,7 +3881,7 @@
       <c r="L48" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M48" s="20" t="s">
+      <c r="M48" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N48">
@@ -3904,7 +3932,7 @@
       <c r="L49" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M49" s="20" t="s">
+      <c r="M49" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N49">
@@ -3955,7 +3983,7 @@
       <c r="L50" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M50" s="20" t="s">
+      <c r="M50" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N50">
@@ -4007,7 +4035,7 @@
       <c r="L51" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M51" s="20" t="s">
+      <c r="M51" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N51">
@@ -4059,7 +4087,7 @@
       <c r="L52" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M52" s="20" t="s">
+      <c r="M52" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N52">
@@ -4108,7 +4136,7 @@
       <c r="L53" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M53" s="20" t="s">
+      <c r="M53" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N53">
@@ -4157,7 +4185,7 @@
       <c r="L54" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M54" s="20" t="s">
+      <c r="M54" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N54">
@@ -4206,7 +4234,7 @@
       <c r="L55" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M55" s="20" t="s">
+      <c r="M55" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N55">
@@ -4255,7 +4283,7 @@
       <c r="L56" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M56" s="20" t="s">
+      <c r="M56" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N56">
@@ -4304,7 +4332,7 @@
       <c r="L57" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M57" s="20" t="s">
+      <c r="M57" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N57">
@@ -4353,7 +4381,7 @@
       <c r="L58" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M58" s="20" t="s">
+      <c r="M58" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N58">
@@ -4399,7 +4427,7 @@
       <c r="L59" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M59" s="20" t="s">
+      <c r="M59" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N59">
@@ -4445,7 +4473,7 @@
       <c r="L60" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M60" s="20" t="s">
+      <c r="M60" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N60">
@@ -4491,7 +4519,7 @@
       <c r="L61" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M61" s="20" t="s">
+      <c r="M61" s="25" t="s">
         <v>34</v>
       </c>
       <c r="N61">
@@ -4536,10 +4564,10 @@
       <c r="K62" s="1">
         <v>0</v>
       </c>
-      <c r="L62" s="21" t="s">
+      <c r="L62" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="M62" s="21" t="s">
+      <c r="M62" s="26" t="s">
         <v>75</v>
       </c>
       <c r="N62">
@@ -4584,10 +4612,10 @@
       <c r="K63" s="1">
         <v>0</v>
       </c>
-      <c r="L63" s="21" t="s">
+      <c r="L63" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="M63" s="21" t="s">
+      <c r="M63" s="26" t="s">
         <v>75</v>
       </c>
       <c r="N63">
@@ -4633,10 +4661,10 @@
       <c r="K64" s="1">
         <v>0</v>
       </c>
-      <c r="L64" s="21" t="s">
+      <c r="L64" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="M64" s="21" t="s">
+      <c r="M64" s="26" t="s">
         <v>75</v>
       </c>
       <c r="N64">
@@ -4682,10 +4710,10 @@
       <c r="K65" s="1">
         <v>0</v>
       </c>
-      <c r="L65" s="21" t="s">
+      <c r="L65" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="M65" s="21" t="s">
+      <c r="M65" s="26" t="s">
         <v>75</v>
       </c>
       <c r="N65">
@@ -4731,10 +4759,10 @@
       <c r="K66" s="1">
         <v>0</v>
       </c>
-      <c r="L66" s="21" t="s">
+      <c r="L66" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="M66" s="21" t="s">
+      <c r="M66" s="26" t="s">
         <v>75</v>
       </c>
       <c r="N66">
@@ -4780,10 +4808,10 @@
       <c r="K67" s="1">
         <v>0</v>
       </c>
-      <c r="L67" s="21" t="s">
+      <c r="L67" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="M67" s="21" t="s">
+      <c r="M67" s="26" t="s">
         <v>75</v>
       </c>
       <c r="N67">
@@ -4799,46 +4827,46 @@
         <f t="shared" ref="A68:A74" si="8">B68*100+H68</f>
         <v>20010010</v>
       </c>
-      <c r="B68" s="13">
+      <c r="B68" s="18">
         <v>200100</v>
       </c>
-      <c r="C68" s="13">
-        <v>2</v>
-      </c>
-      <c r="D68" s="13" t="s">
+      <c r="C68" s="18">
+        <v>2</v>
+      </c>
+      <c r="D68" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="E68" s="13">
+      <c r="E68" s="18">
         <v>200100038</v>
       </c>
-      <c r="F68" s="13" t="s">
+      <c r="F68" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="G68" s="18" t="s">
+      <c r="G68" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="H68" s="18">
+      <c r="H68" s="19">
         <v>10</v>
       </c>
-      <c r="I68" s="18">
-        <v>0</v>
-      </c>
-      <c r="J68" s="18">
-        <v>-1</v>
-      </c>
-      <c r="K68" s="1">
-        <v>0</v>
-      </c>
-      <c r="L68" s="18" t="s">
+      <c r="I68" s="19">
+        <v>0</v>
+      </c>
+      <c r="J68" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K68" s="20">
+        <v>0</v>
+      </c>
+      <c r="L68" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="M68" s="18">
-        <v>0</v>
-      </c>
-      <c r="N68">
+      <c r="M68" s="19">
+        <v>0</v>
+      </c>
+      <c r="N68" s="21">
         <v>200</v>
       </c>
-      <c r="O68" s="19">
+      <c r="O68" s="22">
         <v>1980000</v>
       </c>
       <c r="S68" s="3"/>
@@ -4848,46 +4876,46 @@
         <f t="shared" si="8"/>
         <v>20010011</v>
       </c>
-      <c r="B69" s="13">
+      <c r="B69" s="18">
         <v>200100</v>
       </c>
-      <c r="C69" s="13">
-        <v>2</v>
-      </c>
-      <c r="D69" s="13" t="s">
+      <c r="C69" s="18">
+        <v>2</v>
+      </c>
+      <c r="D69" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="E69" s="13">
+      <c r="E69" s="18">
         <v>200100038</v>
       </c>
-      <c r="F69" s="13" t="s">
+      <c r="F69" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="G69" s="18" t="s">
+      <c r="G69" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="H69" s="18">
+      <c r="H69" s="19">
         <v>11</v>
       </c>
-      <c r="I69" s="18">
-        <v>0</v>
-      </c>
-      <c r="J69" s="18">
-        <v>-1</v>
-      </c>
-      <c r="K69" s="1">
-        <v>0</v>
-      </c>
-      <c r="L69" s="18" t="s">
+      <c r="I69" s="19">
+        <v>0</v>
+      </c>
+      <c r="J69" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K69" s="20">
+        <v>0</v>
+      </c>
+      <c r="L69" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="M69" s="18">
-        <v>0</v>
-      </c>
-      <c r="N69">
+      <c r="M69" s="19">
+        <v>0</v>
+      </c>
+      <c r="N69" s="21">
         <v>5000</v>
       </c>
-      <c r="O69" s="19">
+      <c r="O69" s="22">
         <v>1980000</v>
       </c>
       <c r="S69" s="3"/>
@@ -4897,46 +4925,46 @@
         <f t="shared" si="8"/>
         <v>20010012</v>
       </c>
-      <c r="B70" s="13">
+      <c r="B70" s="18">
         <v>200100</v>
       </c>
-      <c r="C70" s="13">
-        <v>2</v>
-      </c>
-      <c r="D70" s="13" t="s">
+      <c r="C70" s="18">
+        <v>2</v>
+      </c>
+      <c r="D70" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="E70" s="13">
+      <c r="E70" s="18">
         <v>200100038</v>
       </c>
-      <c r="F70" s="13" t="s">
+      <c r="F70" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="G70" s="18" t="s">
+      <c r="G70" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="H70" s="18">
+      <c r="H70" s="19">
         <v>12</v>
       </c>
-      <c r="I70" s="18">
-        <v>0</v>
-      </c>
-      <c r="J70" s="18">
-        <v>-1</v>
-      </c>
-      <c r="K70" s="1">
-        <v>0</v>
-      </c>
-      <c r="L70" s="18" t="s">
+      <c r="I70" s="19">
+        <v>0</v>
+      </c>
+      <c r="J70" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K70" s="20">
+        <v>0</v>
+      </c>
+      <c r="L70" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="M70" s="18">
-        <v>0</v>
-      </c>
-      <c r="N70">
+      <c r="M70" s="19">
+        <v>0</v>
+      </c>
+      <c r="N70" s="21">
         <v>100000</v>
       </c>
-      <c r="O70" s="19">
+      <c r="O70" s="22">
         <v>1980000</v>
       </c>
       <c r="S70" s="3"/>
@@ -4946,46 +4974,46 @@
         <f t="shared" si="8"/>
         <v>20010110</v>
       </c>
-      <c r="B71" s="13">
+      <c r="B71" s="18">
         <v>200101</v>
       </c>
-      <c r="C71" s="13">
-        <v>2</v>
-      </c>
-      <c r="D71" s="13" t="s">
+      <c r="C71" s="18">
+        <v>2</v>
+      </c>
+      <c r="D71" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="E71" s="13">
+      <c r="E71" s="18">
         <v>200101001</v>
       </c>
-      <c r="F71" s="13" t="s">
+      <c r="F71" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="G71" s="18" t="s">
+      <c r="G71" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="H71" s="18">
+      <c r="H71" s="19">
         <v>10</v>
       </c>
-      <c r="I71" s="18">
-        <v>0</v>
-      </c>
-      <c r="J71" s="18">
-        <v>-1</v>
-      </c>
-      <c r="K71" s="1">
-        <v>0</v>
-      </c>
-      <c r="L71" s="18" t="s">
+      <c r="I71" s="19">
+        <v>0</v>
+      </c>
+      <c r="J71" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K71" s="20">
+        <v>0</v>
+      </c>
+      <c r="L71" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="M71" s="18">
-        <v>0</v>
-      </c>
-      <c r="N71">
+      <c r="M71" s="19">
+        <v>0</v>
+      </c>
+      <c r="N71" s="21">
         <v>200</v>
       </c>
-      <c r="O71" s="19">
+      <c r="O71" s="22">
         <v>1980000</v>
       </c>
       <c r="S71" s="3"/>
@@ -4995,46 +5023,46 @@
         <f t="shared" si="8"/>
         <v>20010111</v>
       </c>
-      <c r="B72" s="13">
+      <c r="B72" s="18">
         <v>200101</v>
       </c>
-      <c r="C72" s="13">
-        <v>2</v>
-      </c>
-      <c r="D72" s="13" t="s">
+      <c r="C72" s="18">
+        <v>2</v>
+      </c>
+      <c r="D72" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="E72" s="13">
+      <c r="E72" s="18">
         <v>200101001</v>
       </c>
-      <c r="F72" s="13" t="s">
+      <c r="F72" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="G72" s="18" t="s">
+      <c r="G72" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="H72" s="18">
+      <c r="H72" s="19">
         <v>11</v>
       </c>
-      <c r="I72" s="18">
-        <v>0</v>
-      </c>
-      <c r="J72" s="18">
-        <v>-1</v>
-      </c>
-      <c r="K72" s="1">
-        <v>0</v>
-      </c>
-      <c r="L72" s="18" t="s">
+      <c r="I72" s="19">
+        <v>0</v>
+      </c>
+      <c r="J72" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K72" s="20">
+        <v>0</v>
+      </c>
+      <c r="L72" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="M72" s="18">
-        <v>0</v>
-      </c>
-      <c r="N72">
+      <c r="M72" s="19">
+        <v>0</v>
+      </c>
+      <c r="N72" s="21">
         <v>5000</v>
       </c>
-      <c r="O72" s="19">
+      <c r="O72" s="22">
         <v>1980000</v>
       </c>
       <c r="S72" s="3"/>
@@ -5044,46 +5072,46 @@
         <f t="shared" si="8"/>
         <v>20010112</v>
       </c>
-      <c r="B73" s="13">
+      <c r="B73" s="18">
         <v>200101</v>
       </c>
-      <c r="C73" s="13">
-        <v>2</v>
-      </c>
-      <c r="D73" s="13" t="s">
+      <c r="C73" s="18">
+        <v>2</v>
+      </c>
+      <c r="D73" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="E73" s="13">
+      <c r="E73" s="18">
         <v>200101001</v>
       </c>
-      <c r="F73" s="13" t="s">
+      <c r="F73" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="G73" s="18" t="s">
+      <c r="G73" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="H73" s="18">
+      <c r="H73" s="19">
         <v>12</v>
       </c>
-      <c r="I73" s="18">
-        <v>0</v>
-      </c>
-      <c r="J73" s="18">
-        <v>-1</v>
-      </c>
-      <c r="K73" s="1">
-        <v>0</v>
-      </c>
-      <c r="L73" s="18" t="s">
+      <c r="I73" s="19">
+        <v>0</v>
+      </c>
+      <c r="J73" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K73" s="20">
+        <v>0</v>
+      </c>
+      <c r="L73" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="M73" s="18">
-        <v>0</v>
-      </c>
-      <c r="N73">
+      <c r="M73" s="19">
+        <v>0</v>
+      </c>
+      <c r="N73" s="21">
         <v>100000</v>
       </c>
-      <c r="O73" s="19">
+      <c r="O73" s="22">
         <v>1980000</v>
       </c>
       <c r="S73" s="3"/>
@@ -5093,46 +5121,46 @@
         <f t="shared" si="8"/>
         <v>20030010</v>
       </c>
-      <c r="B74" s="13">
+      <c r="B74" s="18">
         <v>200300</v>
       </c>
-      <c r="C74" s="13">
-        <v>2</v>
-      </c>
-      <c r="D74" s="13" t="s">
+      <c r="C74" s="18">
+        <v>2</v>
+      </c>
+      <c r="D74" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="E74" s="13">
+      <c r="E74" s="18">
         <v>200300001</v>
       </c>
-      <c r="F74" s="13" t="s">
+      <c r="F74" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="G74" s="18" t="s">
+      <c r="G74" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="H74" s="18">
+      <c r="H74" s="19">
         <v>10</v>
       </c>
-      <c r="I74" s="18">
-        <v>0</v>
-      </c>
-      <c r="J74" s="18">
-        <v>-1</v>
-      </c>
-      <c r="K74" s="1">
-        <v>0</v>
-      </c>
-      <c r="L74" s="18" t="s">
+      <c r="I74" s="19">
+        <v>0</v>
+      </c>
+      <c r="J74" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K74" s="20">
+        <v>0</v>
+      </c>
+      <c r="L74" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="M74" s="18">
-        <v>0</v>
-      </c>
-      <c r="N74">
+      <c r="M74" s="19">
+        <v>0</v>
+      </c>
+      <c r="N74" s="21">
         <v>200</v>
       </c>
-      <c r="O74" s="19">
+      <c r="O74" s="22">
         <v>1980000</v>
       </c>
       <c r="S74" s="3"/>
@@ -5142,46 +5170,46 @@
         <f t="shared" ref="A75:A83" si="9">B75*100+H75</f>
         <v>20030011</v>
       </c>
-      <c r="B75" s="13">
+      <c r="B75" s="18">
         <v>200300</v>
       </c>
-      <c r="C75" s="13">
-        <v>2</v>
-      </c>
-      <c r="D75" s="13" t="s">
+      <c r="C75" s="18">
+        <v>2</v>
+      </c>
+      <c r="D75" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="E75" s="13">
+      <c r="E75" s="18">
         <v>200300001</v>
       </c>
-      <c r="F75" s="13" t="s">
+      <c r="F75" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="G75" s="18" t="s">
+      <c r="G75" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="H75" s="18">
+      <c r="H75" s="19">
         <v>11</v>
       </c>
-      <c r="I75" s="18">
-        <v>0</v>
-      </c>
-      <c r="J75" s="18">
-        <v>-1</v>
-      </c>
-      <c r="K75" s="1">
-        <v>0</v>
-      </c>
-      <c r="L75" s="18" t="s">
+      <c r="I75" s="19">
+        <v>0</v>
+      </c>
+      <c r="J75" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K75" s="20">
+        <v>0</v>
+      </c>
+      <c r="L75" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="M75" s="18">
-        <v>0</v>
-      </c>
-      <c r="N75">
+      <c r="M75" s="19">
+        <v>0</v>
+      </c>
+      <c r="N75" s="21">
         <v>5000</v>
       </c>
-      <c r="O75" s="19">
+      <c r="O75" s="22">
         <v>1980000</v>
       </c>
       <c r="S75" s="3"/>
@@ -5191,46 +5219,46 @@
         <f t="shared" si="9"/>
         <v>20030012</v>
       </c>
-      <c r="B76" s="13">
+      <c r="B76" s="18">
         <v>200300</v>
       </c>
-      <c r="C76" s="13">
-        <v>2</v>
-      </c>
-      <c r="D76" s="13" t="s">
+      <c r="C76" s="18">
+        <v>2</v>
+      </c>
+      <c r="D76" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="E76" s="13">
+      <c r="E76" s="18">
         <v>200300001</v>
       </c>
-      <c r="F76" s="13" t="s">
+      <c r="F76" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="G76" s="18" t="s">
+      <c r="G76" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="H76" s="18">
+      <c r="H76" s="19">
         <v>12</v>
       </c>
-      <c r="I76" s="18">
-        <v>0</v>
-      </c>
-      <c r="J76" s="18">
-        <v>-1</v>
-      </c>
-      <c r="K76" s="1">
-        <v>0</v>
-      </c>
-      <c r="L76" s="18" t="s">
+      <c r="I76" s="19">
+        <v>0</v>
+      </c>
+      <c r="J76" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K76" s="20">
+        <v>0</v>
+      </c>
+      <c r="L76" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="M76" s="18">
-        <v>0</v>
-      </c>
-      <c r="N76">
+      <c r="M76" s="19">
+        <v>0</v>
+      </c>
+      <c r="N76" s="21">
         <v>100000</v>
       </c>
-      <c r="O76" s="19">
+      <c r="O76" s="22">
         <v>1980000</v>
       </c>
       <c r="S76" s="3"/>
@@ -5240,46 +5268,46 @@
         <f t="shared" si="9"/>
         <v>20040010</v>
       </c>
-      <c r="B77" s="13">
+      <c r="B77" s="18">
         <v>200400</v>
       </c>
-      <c r="C77" s="13">
-        <v>2</v>
-      </c>
-      <c r="D77" s="16" t="s">
+      <c r="C77" s="18">
+        <v>2</v>
+      </c>
+      <c r="D77" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="E77" s="13">
+      <c r="E77" s="18">
         <v>200400009</v>
       </c>
-      <c r="F77" s="13" t="s">
+      <c r="F77" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="G77" s="18" t="s">
+      <c r="G77" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="H77" s="18">
+      <c r="H77" s="19">
         <v>10</v>
       </c>
-      <c r="I77" s="18">
-        <v>0</v>
-      </c>
-      <c r="J77" s="18">
-        <v>-1</v>
-      </c>
-      <c r="K77" s="1">
-        <v>0</v>
-      </c>
-      <c r="L77" s="18" t="s">
+      <c r="I77" s="19">
+        <v>0</v>
+      </c>
+      <c r="J77" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K77" s="20">
+        <v>0</v>
+      </c>
+      <c r="L77" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="M77" s="18">
-        <v>0</v>
-      </c>
-      <c r="N77">
+      <c r="M77" s="19">
+        <v>0</v>
+      </c>
+      <c r="N77" s="21">
         <v>200</v>
       </c>
-      <c r="O77" s="19">
+      <c r="O77" s="22">
         <v>1980000</v>
       </c>
       <c r="S77" s="3"/>
@@ -5289,46 +5317,46 @@
         <f t="shared" si="9"/>
         <v>20040011</v>
       </c>
-      <c r="B78" s="13">
+      <c r="B78" s="18">
         <v>200400</v>
       </c>
-      <c r="C78" s="13">
-        <v>2</v>
-      </c>
-      <c r="D78" s="16" t="s">
+      <c r="C78" s="18">
+        <v>2</v>
+      </c>
+      <c r="D78" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="E78" s="13">
+      <c r="E78" s="18">
         <v>200400009</v>
       </c>
-      <c r="F78" s="13" t="s">
+      <c r="F78" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="G78" s="18" t="s">
+      <c r="G78" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="H78" s="18">
+      <c r="H78" s="19">
         <v>11</v>
       </c>
-      <c r="I78" s="18">
-        <v>0</v>
-      </c>
-      <c r="J78" s="18">
-        <v>-1</v>
-      </c>
-      <c r="K78" s="1">
-        <v>0</v>
-      </c>
-      <c r="L78" s="18" t="s">
+      <c r="I78" s="19">
+        <v>0</v>
+      </c>
+      <c r="J78" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K78" s="20">
+        <v>0</v>
+      </c>
+      <c r="L78" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="M78" s="18">
-        <v>0</v>
-      </c>
-      <c r="N78">
+      <c r="M78" s="19">
+        <v>0</v>
+      </c>
+      <c r="N78" s="21">
         <v>5000</v>
       </c>
-      <c r="O78" s="19">
+      <c r="O78" s="22">
         <v>1980000</v>
       </c>
       <c r="S78" s="3"/>
@@ -5338,46 +5366,46 @@
         <f t="shared" si="9"/>
         <v>20040012</v>
       </c>
-      <c r="B79" s="13">
+      <c r="B79" s="18">
         <v>200400</v>
       </c>
-      <c r="C79" s="13">
-        <v>2</v>
-      </c>
-      <c r="D79" s="16" t="s">
+      <c r="C79" s="18">
+        <v>2</v>
+      </c>
+      <c r="D79" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="E79" s="13">
+      <c r="E79" s="18">
         <v>200400009</v>
       </c>
-      <c r="F79" s="13" t="s">
+      <c r="F79" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="G79" s="18" t="s">
+      <c r="G79" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="H79" s="18">
+      <c r="H79" s="19">
         <v>12</v>
       </c>
-      <c r="I79" s="18">
-        <v>0</v>
-      </c>
-      <c r="J79" s="18">
-        <v>-1</v>
-      </c>
-      <c r="K79" s="1">
-        <v>0</v>
-      </c>
-      <c r="L79" s="18" t="s">
+      <c r="I79" s="19">
+        <v>0</v>
+      </c>
+      <c r="J79" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K79" s="20">
+        <v>0</v>
+      </c>
+      <c r="L79" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="M79" s="18">
-        <v>0</v>
-      </c>
-      <c r="N79">
+      <c r="M79" s="19">
+        <v>0</v>
+      </c>
+      <c r="N79" s="21">
         <v>100000</v>
       </c>
-      <c r="O79" s="19">
+      <c r="O79" s="22">
         <v>1980000</v>
       </c>
       <c r="S79" s="3"/>
@@ -5387,46 +5415,46 @@
         <f t="shared" si="9"/>
         <v>20050010</v>
       </c>
-      <c r="B80" s="13">
+      <c r="B80" s="18">
         <v>200500</v>
       </c>
-      <c r="C80" s="13">
-        <v>2</v>
-      </c>
-      <c r="D80" s="13" t="s">
+      <c r="C80" s="18">
+        <v>2</v>
+      </c>
+      <c r="D80" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="E80" s="13">
+      <c r="E80" s="18">
         <v>200500025</v>
       </c>
-      <c r="F80" s="13" t="s">
+      <c r="F80" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="G80" s="18" t="s">
+      <c r="G80" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="H80" s="18">
+      <c r="H80" s="19">
         <v>10</v>
       </c>
-      <c r="I80" s="18">
-        <v>0</v>
-      </c>
-      <c r="J80" s="18">
-        <v>-1</v>
-      </c>
-      <c r="K80" s="1">
-        <v>0</v>
-      </c>
-      <c r="L80" s="18" t="s">
+      <c r="I80" s="19">
+        <v>0</v>
+      </c>
+      <c r="J80" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K80" s="20">
+        <v>0</v>
+      </c>
+      <c r="L80" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="M80" s="18">
-        <v>0</v>
-      </c>
-      <c r="N80">
+      <c r="M80" s="19">
+        <v>0</v>
+      </c>
+      <c r="N80" s="21">
         <v>200</v>
       </c>
-      <c r="O80" s="19">
+      <c r="O80" s="22">
         <v>1980000</v>
       </c>
       <c r="S80" s="3"/>
@@ -5436,46 +5464,46 @@
         <f t="shared" si="9"/>
         <v>20050011</v>
       </c>
-      <c r="B81" s="13">
+      <c r="B81" s="18">
         <v>200500</v>
       </c>
-      <c r="C81" s="13">
-        <v>2</v>
-      </c>
-      <c r="D81" s="13" t="s">
+      <c r="C81" s="18">
+        <v>2</v>
+      </c>
+      <c r="D81" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="E81" s="13">
+      <c r="E81" s="18">
         <v>200500025</v>
       </c>
-      <c r="F81" s="13" t="s">
+      <c r="F81" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="G81" s="18" t="s">
+      <c r="G81" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="H81" s="18">
+      <c r="H81" s="19">
         <v>11</v>
       </c>
-      <c r="I81" s="18">
-        <v>0</v>
-      </c>
-      <c r="J81" s="18">
-        <v>-1</v>
-      </c>
-      <c r="K81" s="1">
-        <v>0</v>
-      </c>
-      <c r="L81" s="18" t="s">
+      <c r="I81" s="19">
+        <v>0</v>
+      </c>
+      <c r="J81" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K81" s="20">
+        <v>0</v>
+      </c>
+      <c r="L81" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="M81" s="18">
-        <v>0</v>
-      </c>
-      <c r="N81">
+      <c r="M81" s="19">
+        <v>0</v>
+      </c>
+      <c r="N81" s="21">
         <v>5000</v>
       </c>
-      <c r="O81" s="19">
+      <c r="O81" s="22">
         <v>1980000</v>
       </c>
       <c r="S81" s="3"/>
@@ -5485,46 +5513,46 @@
         <f t="shared" si="9"/>
         <v>20050012</v>
       </c>
-      <c r="B82" s="13">
+      <c r="B82" s="18">
         <v>200500</v>
       </c>
-      <c r="C82" s="13">
-        <v>2</v>
-      </c>
-      <c r="D82" s="13" t="s">
+      <c r="C82" s="18">
+        <v>2</v>
+      </c>
+      <c r="D82" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="E82" s="13">
+      <c r="E82" s="18">
         <v>200500025</v>
       </c>
-      <c r="F82" s="13" t="s">
+      <c r="F82" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="G82" s="18" t="s">
+      <c r="G82" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="H82" s="18">
+      <c r="H82" s="19">
         <v>12</v>
       </c>
-      <c r="I82" s="18">
-        <v>0</v>
-      </c>
-      <c r="J82" s="18">
-        <v>-1</v>
-      </c>
-      <c r="K82" s="1">
-        <v>0</v>
-      </c>
-      <c r="L82" s="18" t="s">
+      <c r="I82" s="19">
+        <v>0</v>
+      </c>
+      <c r="J82" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K82" s="20">
+        <v>0</v>
+      </c>
+      <c r="L82" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="M82" s="18">
-        <v>0</v>
-      </c>
-      <c r="N82">
+      <c r="M82" s="19">
+        <v>0</v>
+      </c>
+      <c r="N82" s="21">
         <v>100000</v>
       </c>
-      <c r="O82" s="19">
+      <c r="O82" s="22">
         <v>1980000</v>
       </c>
       <c r="S82" s="3"/>
@@ -5534,46 +5562,46 @@
         <f t="shared" si="9"/>
         <v>20060010</v>
       </c>
-      <c r="B83" s="13">
+      <c r="B83" s="18">
         <v>200600</v>
       </c>
-      <c r="C83" s="13">
-        <v>2</v>
-      </c>
-      <c r="D83" s="13" t="s">
+      <c r="C83" s="18">
+        <v>2</v>
+      </c>
+      <c r="D83" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="E83" s="13">
+      <c r="E83" s="18">
         <v>200600001</v>
       </c>
-      <c r="F83" s="13" t="s">
+      <c r="F83" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="G83" s="18" t="s">
+      <c r="G83" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="H83" s="18">
+      <c r="H83" s="19">
         <v>10</v>
       </c>
-      <c r="I83" s="18">
-        <v>0</v>
-      </c>
-      <c r="J83" s="18">
-        <v>-1</v>
-      </c>
-      <c r="K83" s="1">
-        <v>0</v>
-      </c>
-      <c r="L83" s="18" t="s">
+      <c r="I83" s="19">
+        <v>0</v>
+      </c>
+      <c r="J83" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K83" s="20">
+        <v>0</v>
+      </c>
+      <c r="L83" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="M83" s="18">
-        <v>0</v>
-      </c>
-      <c r="N83">
+      <c r="M83" s="19">
+        <v>0</v>
+      </c>
+      <c r="N83" s="21">
         <v>200</v>
       </c>
-      <c r="O83" s="19">
+      <c r="O83" s="22">
         <v>1980000</v>
       </c>
     </row>
@@ -5582,46 +5610,46 @@
         <f t="shared" ref="A84:A98" si="10">B84*100+H84</f>
         <v>20060011</v>
       </c>
-      <c r="B84" s="13">
+      <c r="B84" s="18">
         <v>200600</v>
       </c>
-      <c r="C84" s="13">
-        <v>2</v>
-      </c>
-      <c r="D84" s="13" t="s">
+      <c r="C84" s="18">
+        <v>2</v>
+      </c>
+      <c r="D84" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="E84" s="13">
+      <c r="E84" s="18">
         <v>200600001</v>
       </c>
-      <c r="F84" s="13" t="s">
+      <c r="F84" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="G84" s="18" t="s">
+      <c r="G84" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="H84" s="18">
+      <c r="H84" s="19">
         <v>11</v>
       </c>
-      <c r="I84" s="18">
-        <v>0</v>
-      </c>
-      <c r="J84" s="18">
-        <v>-1</v>
-      </c>
-      <c r="K84" s="1">
-        <v>0</v>
-      </c>
-      <c r="L84" s="18" t="s">
+      <c r="I84" s="19">
+        <v>0</v>
+      </c>
+      <c r="J84" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K84" s="20">
+        <v>0</v>
+      </c>
+      <c r="L84" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="M84" s="18">
-        <v>0</v>
-      </c>
-      <c r="N84">
+      <c r="M84" s="19">
+        <v>0</v>
+      </c>
+      <c r="N84" s="21">
         <v>5000</v>
       </c>
-      <c r="O84" s="19">
+      <c r="O84" s="22">
         <v>1980000</v>
       </c>
     </row>
@@ -5630,46 +5658,46 @@
         <f t="shared" si="10"/>
         <v>20060012</v>
       </c>
-      <c r="B85" s="13">
+      <c r="B85" s="18">
         <v>200600</v>
       </c>
-      <c r="C85" s="13">
-        <v>2</v>
-      </c>
-      <c r="D85" s="13" t="s">
+      <c r="C85" s="18">
+        <v>2</v>
+      </c>
+      <c r="D85" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="E85" s="13">
+      <c r="E85" s="18">
         <v>200600001</v>
       </c>
-      <c r="F85" s="13" t="s">
+      <c r="F85" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="G85" s="18" t="s">
+      <c r="G85" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="H85" s="18">
+      <c r="H85" s="19">
         <v>12</v>
       </c>
-      <c r="I85" s="18">
-        <v>0</v>
-      </c>
-      <c r="J85" s="18">
-        <v>-1</v>
-      </c>
-      <c r="K85" s="1">
-        <v>0</v>
-      </c>
-      <c r="L85" s="18" t="s">
+      <c r="I85" s="19">
+        <v>0</v>
+      </c>
+      <c r="J85" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K85" s="20">
+        <v>0</v>
+      </c>
+      <c r="L85" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="M85" s="18">
-        <v>0</v>
-      </c>
-      <c r="N85">
+      <c r="M85" s="19">
+        <v>0</v>
+      </c>
+      <c r="N85" s="21">
         <v>100000</v>
       </c>
-      <c r="O85" s="19">
+      <c r="O85" s="22">
         <v>1980000</v>
       </c>
     </row>
@@ -5678,46 +5706,46 @@
         <f t="shared" si="10"/>
         <v>20070010</v>
       </c>
-      <c r="B86" s="13">
+      <c r="B86" s="18">
         <v>200700</v>
       </c>
-      <c r="C86" s="13">
-        <v>2</v>
-      </c>
-      <c r="D86" s="12" t="s">
+      <c r="C86" s="18">
+        <v>2</v>
+      </c>
+      <c r="D86" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="E86" s="13">
+      <c r="E86" s="18">
         <v>200700001</v>
       </c>
-      <c r="F86" s="13" t="s">
+      <c r="F86" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="G86" s="18" t="s">
+      <c r="G86" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="H86" s="18">
+      <c r="H86" s="19">
         <v>10</v>
       </c>
-      <c r="I86" s="18">
-        <v>0</v>
-      </c>
-      <c r="J86" s="18">
-        <v>-1</v>
-      </c>
-      <c r="K86" s="1">
-        <v>0</v>
-      </c>
-      <c r="L86" s="18" t="s">
+      <c r="I86" s="19">
+        <v>0</v>
+      </c>
+      <c r="J86" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K86" s="20">
+        <v>0</v>
+      </c>
+      <c r="L86" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="M86" s="18">
-        <v>0</v>
-      </c>
-      <c r="N86">
+      <c r="M86" s="19">
+        <v>0</v>
+      </c>
+      <c r="N86" s="21">
         <v>200</v>
       </c>
-      <c r="O86" s="19">
+      <c r="O86" s="22">
         <v>1980000</v>
       </c>
     </row>
@@ -5726,47 +5754,47 @@
         <f t="shared" si="10"/>
         <v>20070011</v>
       </c>
-      <c r="B87" s="13">
+      <c r="B87" s="18">
         <v>200700</v>
       </c>
-      <c r="C87" s="13">
-        <v>2</v>
-      </c>
-      <c r="D87" s="12" t="str">
+      <c r="C87" s="18">
+        <v>2</v>
+      </c>
+      <c r="D87" s="24" t="str">
         <f>D86</f>
         <v>越南色碟</v>
       </c>
-      <c r="E87" s="13">
+      <c r="E87" s="18">
         <v>200700001</v>
       </c>
-      <c r="F87" s="13" t="s">
+      <c r="F87" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="G87" s="18" t="s">
+      <c r="G87" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="H87" s="18">
+      <c r="H87" s="19">
         <v>11</v>
       </c>
-      <c r="I87" s="18">
-        <v>0</v>
-      </c>
-      <c r="J87" s="18">
-        <v>-1</v>
-      </c>
-      <c r="K87" s="1">
-        <v>0</v>
-      </c>
-      <c r="L87" s="18" t="s">
+      <c r="I87" s="19">
+        <v>0</v>
+      </c>
+      <c r="J87" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K87" s="20">
+        <v>0</v>
+      </c>
+      <c r="L87" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="M87" s="18">
-        <v>0</v>
-      </c>
-      <c r="N87">
+      <c r="M87" s="19">
+        <v>0</v>
+      </c>
+      <c r="N87" s="21">
         <v>5000</v>
       </c>
-      <c r="O87" s="19">
+      <c r="O87" s="22">
         <v>1980000</v>
       </c>
     </row>
@@ -5775,47 +5803,47 @@
         <f t="shared" si="10"/>
         <v>20070012</v>
       </c>
-      <c r="B88" s="13">
+      <c r="B88" s="18">
         <v>200700</v>
       </c>
-      <c r="C88" s="13">
-        <v>2</v>
-      </c>
-      <c r="D88" s="12" t="str">
+      <c r="C88" s="18">
+        <v>2</v>
+      </c>
+      <c r="D88" s="24" t="str">
         <f>D87</f>
         <v>越南色碟</v>
       </c>
-      <c r="E88" s="13">
+      <c r="E88" s="18">
         <v>200700001</v>
       </c>
-      <c r="F88" s="13" t="s">
+      <c r="F88" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="G88" s="18" t="s">
+      <c r="G88" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="H88" s="18">
+      <c r="H88" s="19">
         <v>12</v>
       </c>
-      <c r="I88" s="18">
-        <v>0</v>
-      </c>
-      <c r="J88" s="18">
-        <v>-1</v>
-      </c>
-      <c r="K88" s="1">
-        <v>0</v>
-      </c>
-      <c r="L88" s="18" t="s">
+      <c r="I88" s="19">
+        <v>0</v>
+      </c>
+      <c r="J88" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K88" s="20">
+        <v>0</v>
+      </c>
+      <c r="L88" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="M88" s="18">
-        <v>0</v>
-      </c>
-      <c r="N88">
+      <c r="M88" s="19">
+        <v>0</v>
+      </c>
+      <c r="N88" s="21">
         <v>100000</v>
       </c>
-      <c r="O88" s="19">
+      <c r="O88" s="22">
         <v>1980000</v>
       </c>
     </row>
@@ -5824,46 +5852,46 @@
         <f t="shared" si="10"/>
         <v>20080010</v>
       </c>
-      <c r="B89" s="13">
+      <c r="B89" s="18">
         <v>200800</v>
       </c>
-      <c r="C89" s="13">
-        <v>2</v>
-      </c>
-      <c r="D89" s="13" t="s">
+      <c r="C89" s="18">
+        <v>2</v>
+      </c>
+      <c r="D89" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="E89" s="13">
+      <c r="E89" s="18">
         <v>200800001</v>
       </c>
-      <c r="F89" s="13" t="s">
+      <c r="F89" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="G89" s="18" t="s">
+      <c r="G89" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="H89" s="18">
+      <c r="H89" s="19">
         <v>10</v>
       </c>
-      <c r="I89" s="18">
-        <v>0</v>
-      </c>
-      <c r="J89" s="18">
-        <v>-1</v>
-      </c>
-      <c r="K89" s="1">
-        <v>0</v>
-      </c>
-      <c r="L89" s="18" t="s">
+      <c r="I89" s="19">
+        <v>0</v>
+      </c>
+      <c r="J89" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K89" s="20">
+        <v>0</v>
+      </c>
+      <c r="L89" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="M89" s="18">
-        <v>0</v>
-      </c>
-      <c r="N89">
+      <c r="M89" s="19">
+        <v>0</v>
+      </c>
+      <c r="N89" s="21">
         <v>200</v>
       </c>
-      <c r="O89" s="19">
+      <c r="O89" s="22">
         <v>1980000</v>
       </c>
     </row>
@@ -5872,46 +5900,46 @@
         <f t="shared" si="10"/>
         <v>20080011</v>
       </c>
-      <c r="B90" s="13">
+      <c r="B90" s="18">
         <v>200800</v>
       </c>
-      <c r="C90" s="13">
-        <v>2</v>
-      </c>
-      <c r="D90" s="13" t="s">
+      <c r="C90" s="18">
+        <v>2</v>
+      </c>
+      <c r="D90" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="E90" s="13">
+      <c r="E90" s="18">
         <v>200800001</v>
       </c>
-      <c r="F90" s="13" t="s">
+      <c r="F90" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="G90" s="18" t="s">
+      <c r="G90" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="H90" s="18">
+      <c r="H90" s="19">
         <v>11</v>
       </c>
-      <c r="I90" s="18">
-        <v>0</v>
-      </c>
-      <c r="J90" s="18">
-        <v>-1</v>
-      </c>
-      <c r="K90" s="1">
-        <v>0</v>
-      </c>
-      <c r="L90" s="18" t="s">
+      <c r="I90" s="19">
+        <v>0</v>
+      </c>
+      <c r="J90" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K90" s="20">
+        <v>0</v>
+      </c>
+      <c r="L90" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="M90" s="18">
-        <v>0</v>
-      </c>
-      <c r="N90">
+      <c r="M90" s="19">
+        <v>0</v>
+      </c>
+      <c r="N90" s="21">
         <v>5000</v>
       </c>
-      <c r="O90" s="19">
+      <c r="O90" s="22">
         <v>1980000</v>
       </c>
     </row>
@@ -5920,46 +5948,46 @@
         <f t="shared" si="10"/>
         <v>20080012</v>
       </c>
-      <c r="B91" s="13">
+      <c r="B91" s="18">
         <v>200800</v>
       </c>
-      <c r="C91" s="13">
-        <v>2</v>
-      </c>
-      <c r="D91" s="13" t="s">
+      <c r="C91" s="18">
+        <v>2</v>
+      </c>
+      <c r="D91" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="E91" s="13">
+      <c r="E91" s="18">
         <v>200800001</v>
       </c>
-      <c r="F91" s="13" t="s">
+      <c r="F91" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="G91" s="18" t="s">
+      <c r="G91" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="H91" s="18">
+      <c r="H91" s="19">
         <v>12</v>
       </c>
-      <c r="I91" s="18">
-        <v>0</v>
-      </c>
-      <c r="J91" s="18">
-        <v>-1</v>
-      </c>
-      <c r="K91" s="1">
-        <v>0</v>
-      </c>
-      <c r="L91" s="18" t="s">
+      <c r="I91" s="19">
+        <v>0</v>
+      </c>
+      <c r="J91" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K91" s="20">
+        <v>0</v>
+      </c>
+      <c r="L91" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="M91" s="18">
-        <v>0</v>
-      </c>
-      <c r="N91">
+      <c r="M91" s="19">
+        <v>0</v>
+      </c>
+      <c r="N91" s="21">
         <v>100000</v>
       </c>
-      <c r="O91" s="19">
+      <c r="O91" s="22">
         <v>1980000</v>
       </c>
     </row>
@@ -5968,46 +5996,46 @@
         <f t="shared" si="10"/>
         <v>20090010</v>
       </c>
-      <c r="B92" s="13">
+      <c r="B92" s="18">
         <v>200900</v>
       </c>
-      <c r="C92" s="13">
-        <v>2</v>
-      </c>
-      <c r="D92" s="13" t="s">
+      <c r="C92" s="18">
+        <v>2</v>
+      </c>
+      <c r="D92" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="E92" s="13">
+      <c r="E92" s="18">
         <v>200900001</v>
       </c>
-      <c r="F92" s="13" t="s">
+      <c r="F92" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="G92" s="18" t="s">
+      <c r="G92" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="H92" s="18">
+      <c r="H92" s="19">
         <v>10</v>
       </c>
-      <c r="I92" s="18">
-        <v>0</v>
-      </c>
-      <c r="J92" s="18">
-        <v>-1</v>
-      </c>
-      <c r="K92" s="1">
-        <v>0</v>
-      </c>
-      <c r="L92" s="18" t="s">
+      <c r="I92" s="19">
+        <v>0</v>
+      </c>
+      <c r="J92" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K92" s="20">
+        <v>0</v>
+      </c>
+      <c r="L92" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="M92" s="18">
-        <v>0</v>
-      </c>
-      <c r="N92">
+      <c r="M92" s="19">
+        <v>0</v>
+      </c>
+      <c r="N92" s="21">
         <v>200</v>
       </c>
-      <c r="O92" s="19">
+      <c r="O92" s="22">
         <v>1980000</v>
       </c>
     </row>
@@ -6016,46 +6044,46 @@
         <f t="shared" si="10"/>
         <v>20090011</v>
       </c>
-      <c r="B93" s="13">
+      <c r="B93" s="18">
         <v>200900</v>
       </c>
-      <c r="C93" s="13">
-        <v>2</v>
-      </c>
-      <c r="D93" s="13" t="s">
+      <c r="C93" s="18">
+        <v>2</v>
+      </c>
+      <c r="D93" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="E93" s="13">
+      <c r="E93" s="18">
         <v>200900001</v>
       </c>
-      <c r="F93" s="13" t="s">
+      <c r="F93" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="G93" s="18" t="s">
+      <c r="G93" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="H93" s="18">
+      <c r="H93" s="19">
         <v>11</v>
       </c>
-      <c r="I93" s="18">
-        <v>0</v>
-      </c>
-      <c r="J93" s="18">
-        <v>-1</v>
-      </c>
-      <c r="K93" s="1">
-        <v>0</v>
-      </c>
-      <c r="L93" s="18" t="s">
+      <c r="I93" s="19">
+        <v>0</v>
+      </c>
+      <c r="J93" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K93" s="20">
+        <v>0</v>
+      </c>
+      <c r="L93" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="M93" s="18">
-        <v>0</v>
-      </c>
-      <c r="N93">
+      <c r="M93" s="19">
+        <v>0</v>
+      </c>
+      <c r="N93" s="21">
         <v>5000</v>
       </c>
-      <c r="O93" s="19">
+      <c r="O93" s="22">
         <v>1980000</v>
       </c>
     </row>
@@ -6064,46 +6092,46 @@
         <f t="shared" si="10"/>
         <v>20090012</v>
       </c>
-      <c r="B94" s="13">
+      <c r="B94" s="18">
         <v>200900</v>
       </c>
-      <c r="C94" s="13">
-        <v>2</v>
-      </c>
-      <c r="D94" s="13" t="s">
+      <c r="C94" s="18">
+        <v>2</v>
+      </c>
+      <c r="D94" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="E94" s="13">
+      <c r="E94" s="18">
         <v>200900001</v>
       </c>
-      <c r="F94" s="13" t="s">
+      <c r="F94" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="G94" s="18" t="s">
+      <c r="G94" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="H94" s="18">
+      <c r="H94" s="19">
         <v>12</v>
       </c>
-      <c r="I94" s="18">
-        <v>0</v>
-      </c>
-      <c r="J94" s="18">
-        <v>-1</v>
-      </c>
-      <c r="K94" s="1">
-        <v>0</v>
-      </c>
-      <c r="L94" s="18" t="s">
+      <c r="I94" s="19">
+        <v>0</v>
+      </c>
+      <c r="J94" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K94" s="20">
+        <v>0</v>
+      </c>
+      <c r="L94" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="M94" s="18">
-        <v>0</v>
-      </c>
-      <c r="N94">
+      <c r="M94" s="19">
+        <v>0</v>
+      </c>
+      <c r="N94" s="21">
         <v>100000</v>
       </c>
-      <c r="O94" s="19">
+      <c r="O94" s="22">
         <v>1980000</v>
       </c>
     </row>
@@ -6112,46 +6140,46 @@
         <f t="shared" si="10"/>
         <v>30020010</v>
       </c>
-      <c r="B95" s="12">
+      <c r="B95" s="24">
         <v>300200</v>
       </c>
-      <c r="C95" s="12">
+      <c r="C95" s="24">
         <v>3</v>
       </c>
-      <c r="D95" s="12" t="s">
+      <c r="D95" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="E95" s="13">
+      <c r="E95" s="18">
         <v>300200006</v>
       </c>
-      <c r="F95" s="13" t="s">
+      <c r="F95" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="G95" s="18" t="s">
+      <c r="G95" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="H95" s="18">
+      <c r="H95" s="19">
         <v>10</v>
       </c>
-      <c r="I95" s="18">
-        <v>0</v>
-      </c>
-      <c r="J95" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K95" s="1">
-        <v>0</v>
-      </c>
-      <c r="L95" s="21" t="s">
+      <c r="I95" s="19">
+        <v>0</v>
+      </c>
+      <c r="J95" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K95" s="20">
+        <v>0</v>
+      </c>
+      <c r="L95" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="M95" s="18">
-        <v>0</v>
-      </c>
-      <c r="N95">
+      <c r="M95" s="19">
+        <v>0</v>
+      </c>
+      <c r="N95" s="21">
         <v>200</v>
       </c>
-      <c r="O95" s="19">
+      <c r="O95" s="22">
         <v>1980000</v>
       </c>
       <c r="S95" s="3"/>
@@ -6161,46 +6189,46 @@
         <f t="shared" si="10"/>
         <v>30020011</v>
       </c>
-      <c r="B96" s="12">
+      <c r="B96" s="24">
         <v>300200</v>
       </c>
-      <c r="C96" s="12">
+      <c r="C96" s="24">
         <v>3</v>
       </c>
-      <c r="D96" s="12" t="s">
+      <c r="D96" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="E96" s="13">
+      <c r="E96" s="18">
         <v>300200006</v>
       </c>
-      <c r="F96" s="13" t="s">
+      <c r="F96" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="G96" s="18" t="s">
+      <c r="G96" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="H96" s="18">
+      <c r="H96" s="19">
         <v>11</v>
       </c>
-      <c r="I96" s="18">
-        <v>0</v>
-      </c>
-      <c r="J96" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K96" s="1">
-        <v>0</v>
-      </c>
-      <c r="L96" s="21" t="s">
+      <c r="I96" s="19">
+        <v>0</v>
+      </c>
+      <c r="J96" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K96" s="20">
+        <v>0</v>
+      </c>
+      <c r="L96" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="M96" s="18">
-        <v>0</v>
-      </c>
-      <c r="N96">
+      <c r="M96" s="19">
+        <v>0</v>
+      </c>
+      <c r="N96" s="21">
         <v>5000</v>
       </c>
-      <c r="O96" s="19">
+      <c r="O96" s="22">
         <v>1980000</v>
       </c>
       <c r="S96" s="3"/>
@@ -6210,49 +6238,1359 @@
         <f t="shared" si="10"/>
         <v>30020012</v>
       </c>
-      <c r="B97" s="12">
+      <c r="B97" s="24">
         <v>300200</v>
       </c>
-      <c r="C97" s="12">
+      <c r="C97" s="24">
         <v>3</v>
       </c>
-      <c r="D97" s="12" t="s">
+      <c r="D97" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="E97" s="13">
+      <c r="E97" s="18">
         <v>300200006</v>
       </c>
-      <c r="F97" s="13" t="s">
+      <c r="F97" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="G97" s="18" t="s">
+      <c r="G97" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="H97" s="18">
+      <c r="H97" s="19">
         <v>12</v>
       </c>
-      <c r="I97" s="18">
-        <v>0</v>
-      </c>
-      <c r="J97" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K97" s="1">
-        <v>0</v>
-      </c>
-      <c r="L97" s="21" t="s">
+      <c r="I97" s="19">
+        <v>0</v>
+      </c>
+      <c r="J97" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K97" s="20">
+        <v>0</v>
+      </c>
+      <c r="L97" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="M97" s="18">
-        <v>0</v>
-      </c>
-      <c r="N97">
+      <c r="M97" s="19">
+        <v>0</v>
+      </c>
+      <c r="N97" s="21">
         <v>100000</v>
       </c>
-      <c r="O97" s="19">
+      <c r="O97" s="22">
         <v>1980000</v>
       </c>
       <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="1:19">
+      <c r="A98" s="1">
+        <f t="shared" ref="A98:A124" si="11">B98*10+H98</f>
+        <v>1001010</v>
+      </c>
+      <c r="B98" s="24">
+        <v>100100</v>
+      </c>
+      <c r="C98" s="24">
+        <v>1</v>
+      </c>
+      <c r="D98" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="E98" s="18">
+        <v>100100026</v>
+      </c>
+      <c r="F98" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="G98" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="H98" s="19">
+        <v>10</v>
+      </c>
+      <c r="I98" s="19">
+        <v>0</v>
+      </c>
+      <c r="J98" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K98" s="20">
+        <v>0</v>
+      </c>
+      <c r="L98" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="M98" s="19">
+        <v>0</v>
+      </c>
+      <c r="N98" s="21">
+        <v>50</v>
+      </c>
+      <c r="O98" s="22">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19">
+      <c r="A99" s="1">
+        <f t="shared" si="11"/>
+        <v>1001011</v>
+      </c>
+      <c r="B99" s="24">
+        <v>100100</v>
+      </c>
+      <c r="C99" s="24">
+        <v>1</v>
+      </c>
+      <c r="D99" s="24" t="str">
+        <f t="shared" ref="D99:D103" si="12">D98</f>
+        <v>金礦大亨</v>
+      </c>
+      <c r="E99" s="18">
+        <v>100100026</v>
+      </c>
+      <c r="F99" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="G99" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="H99" s="19">
+        <v>11</v>
+      </c>
+      <c r="I99" s="19">
+        <v>0</v>
+      </c>
+      <c r="J99" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K99" s="20">
+        <v>0</v>
+      </c>
+      <c r="L99" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="M99" s="19">
+        <v>0</v>
+      </c>
+      <c r="N99" s="21">
+        <v>500</v>
+      </c>
+      <c r="O99" s="22">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19">
+      <c r="A100" s="1">
+        <f t="shared" si="11"/>
+        <v>1001012</v>
+      </c>
+      <c r="B100" s="24">
+        <v>100100</v>
+      </c>
+      <c r="C100" s="24">
+        <v>1</v>
+      </c>
+      <c r="D100" s="24" t="str">
+        <f t="shared" si="12"/>
+        <v>金礦大亨</v>
+      </c>
+      <c r="E100" s="18">
+        <v>100100026</v>
+      </c>
+      <c r="F100" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="G100" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="H100" s="19">
+        <v>12</v>
+      </c>
+      <c r="I100" s="19">
+        <v>0</v>
+      </c>
+      <c r="J100" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K100" s="20">
+        <v>0</v>
+      </c>
+      <c r="L100" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="M100" s="19">
+        <v>0</v>
+      </c>
+      <c r="N100" s="21">
+        <v>5000</v>
+      </c>
+      <c r="O100" s="22">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19">
+      <c r="A101" s="1">
+        <f t="shared" si="11"/>
+        <v>1003010</v>
+      </c>
+      <c r="B101" s="24">
+        <v>100300</v>
+      </c>
+      <c r="C101" s="24">
+        <v>1</v>
+      </c>
+      <c r="D101" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="E101" s="18">
+        <v>100300001</v>
+      </c>
+      <c r="F101" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="G101" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="H101" s="19">
+        <v>10</v>
+      </c>
+      <c r="I101" s="19">
+        <v>0</v>
+      </c>
+      <c r="J101" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K101" s="20">
+        <v>0</v>
+      </c>
+      <c r="L101" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="M101" s="19">
+        <v>0</v>
+      </c>
+      <c r="N101" s="21">
+        <v>50</v>
+      </c>
+      <c r="O101" s="22">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="102" spans="1:19">
+      <c r="A102" s="1">
+        <f t="shared" si="11"/>
+        <v>1003011</v>
+      </c>
+      <c r="B102" s="24">
+        <v>100300</v>
+      </c>
+      <c r="C102" s="24">
+        <v>1</v>
+      </c>
+      <c r="D102" s="24" t="str">
+        <f t="shared" si="12"/>
+        <v>超级明星</v>
+      </c>
+      <c r="E102" s="18">
+        <v>100300001</v>
+      </c>
+      <c r="F102" s="18" t="str">
+        <f t="shared" ref="F102:F106" si="13">F101</f>
+        <v>SuperStar</v>
+      </c>
+      <c r="G102" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="H102" s="19">
+        <v>11</v>
+      </c>
+      <c r="I102" s="19">
+        <v>0</v>
+      </c>
+      <c r="J102" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K102" s="20">
+        <v>0</v>
+      </c>
+      <c r="L102" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="M102" s="19">
+        <v>0</v>
+      </c>
+      <c r="N102" s="21">
+        <v>500</v>
+      </c>
+      <c r="O102" s="22">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="103" spans="1:19">
+      <c r="A103" s="1">
+        <f t="shared" si="11"/>
+        <v>1003012</v>
+      </c>
+      <c r="B103" s="24">
+        <v>100300</v>
+      </c>
+      <c r="C103" s="24">
+        <v>1</v>
+      </c>
+      <c r="D103" s="24" t="str">
+        <f t="shared" si="12"/>
+        <v>超级明星</v>
+      </c>
+      <c r="E103" s="18">
+        <v>100300001</v>
+      </c>
+      <c r="F103" s="18" t="str">
+        <f t="shared" si="13"/>
+        <v>SuperStar</v>
+      </c>
+      <c r="G103" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="H103" s="19">
+        <v>12</v>
+      </c>
+      <c r="I103" s="19">
+        <v>0</v>
+      </c>
+      <c r="J103" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K103" s="20">
+        <v>0</v>
+      </c>
+      <c r="L103" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="M103" s="19">
+        <v>0</v>
+      </c>
+      <c r="N103" s="21">
+        <v>5000</v>
+      </c>
+      <c r="O103" s="22">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="104" spans="1:19">
+      <c r="A104" s="1">
+        <f t="shared" si="11"/>
+        <v>1007010</v>
+      </c>
+      <c r="B104" s="24">
+        <v>100700</v>
+      </c>
+      <c r="C104" s="24">
+        <v>1</v>
+      </c>
+      <c r="D104" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="E104" s="18">
+        <v>100700001</v>
+      </c>
+      <c r="F104" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="G104" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="H104" s="19">
+        <v>10</v>
+      </c>
+      <c r="I104" s="19">
+        <v>0</v>
+      </c>
+      <c r="J104" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K104" s="20">
+        <v>0</v>
+      </c>
+      <c r="L104" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="M104" s="19">
+        <v>0</v>
+      </c>
+      <c r="N104" s="21">
+        <v>50</v>
+      </c>
+      <c r="O104" s="22">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="105" spans="1:19">
+      <c r="A105" s="1">
+        <f t="shared" si="11"/>
+        <v>1007011</v>
+      </c>
+      <c r="B105" s="24">
+        <v>100700</v>
+      </c>
+      <c r="C105" s="24">
+        <v>1</v>
+      </c>
+      <c r="D105" s="24" t="str">
+        <f t="shared" ref="D105:D109" si="14">D104</f>
+        <v>麻将胡了</v>
+      </c>
+      <c r="E105" s="18">
+        <v>100700001</v>
+      </c>
+      <c r="F105" s="18" t="str">
+        <f t="shared" si="13"/>
+        <v>MahjongWays</v>
+      </c>
+      <c r="G105" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="H105" s="19">
+        <v>11</v>
+      </c>
+      <c r="I105" s="19">
+        <v>0</v>
+      </c>
+      <c r="J105" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K105" s="20">
+        <v>0</v>
+      </c>
+      <c r="L105" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="M105" s="19">
+        <v>0</v>
+      </c>
+      <c r="N105" s="21">
+        <v>500</v>
+      </c>
+      <c r="O105" s="22">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="106" spans="1:19">
+      <c r="A106" s="1">
+        <f t="shared" si="11"/>
+        <v>1007012</v>
+      </c>
+      <c r="B106" s="24">
+        <v>100700</v>
+      </c>
+      <c r="C106" s="24">
+        <v>1</v>
+      </c>
+      <c r="D106" s="24" t="str">
+        <f t="shared" si="14"/>
+        <v>麻将胡了</v>
+      </c>
+      <c r="E106" s="18">
+        <v>100700001</v>
+      </c>
+      <c r="F106" s="18" t="str">
+        <f t="shared" si="13"/>
+        <v>MahjongWays</v>
+      </c>
+      <c r="G106" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="H106" s="19">
+        <v>12</v>
+      </c>
+      <c r="I106" s="19">
+        <v>0</v>
+      </c>
+      <c r="J106" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K106" s="20">
+        <v>0</v>
+      </c>
+      <c r="L106" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="M106" s="19">
+        <v>0</v>
+      </c>
+      <c r="N106" s="21">
+        <v>5000</v>
+      </c>
+      <c r="O106" s="22">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="107" spans="1:19">
+      <c r="A107" s="1">
+        <f t="shared" si="11"/>
+        <v>1012010</v>
+      </c>
+      <c r="B107" s="24">
+        <v>101200</v>
+      </c>
+      <c r="C107" s="24">
+        <v>1</v>
+      </c>
+      <c r="D107" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="E107" s="18">
+        <v>101200001</v>
+      </c>
+      <c r="F107" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="G107" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="H107" s="19">
+        <v>10</v>
+      </c>
+      <c r="I107" s="19">
+        <v>0</v>
+      </c>
+      <c r="J107" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K107" s="20">
+        <v>0</v>
+      </c>
+      <c r="L107" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="M107" s="19">
+        <v>0</v>
+      </c>
+      <c r="N107" s="21">
+        <v>50</v>
+      </c>
+      <c r="O107" s="22">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="108" spans="1:19">
+      <c r="A108" s="1">
+        <f t="shared" si="11"/>
+        <v>1012011</v>
+      </c>
+      <c r="B108" s="24">
+        <v>101200</v>
+      </c>
+      <c r="C108" s="24">
+        <v>1</v>
+      </c>
+      <c r="D108" s="24" t="str">
+        <f t="shared" si="14"/>
+        <v>财神</v>
+      </c>
+      <c r="E108" s="18">
+        <v>101200001</v>
+      </c>
+      <c r="F108" s="18" t="str">
+        <f t="shared" ref="F108:F112" si="15">F107</f>
+        <v>Godofwealth</v>
+      </c>
+      <c r="G108" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="H108" s="19">
+        <v>11</v>
+      </c>
+      <c r="I108" s="19">
+        <v>0</v>
+      </c>
+      <c r="J108" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K108" s="20">
+        <v>0</v>
+      </c>
+      <c r="L108" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="M108" s="19">
+        <v>0</v>
+      </c>
+      <c r="N108" s="21">
+        <v>500</v>
+      </c>
+      <c r="O108" s="22">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="109" spans="1:19">
+      <c r="A109" s="1">
+        <f t="shared" si="11"/>
+        <v>1012012</v>
+      </c>
+      <c r="B109" s="24">
+        <v>101200</v>
+      </c>
+      <c r="C109" s="24">
+        <v>1</v>
+      </c>
+      <c r="D109" s="24" t="str">
+        <f t="shared" si="14"/>
+        <v>财神</v>
+      </c>
+      <c r="E109" s="18">
+        <v>101200001</v>
+      </c>
+      <c r="F109" s="18" t="str">
+        <f t="shared" si="15"/>
+        <v>Godofwealth</v>
+      </c>
+      <c r="G109" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="H109" s="19">
+        <v>12</v>
+      </c>
+      <c r="I109" s="19">
+        <v>0</v>
+      </c>
+      <c r="J109" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K109" s="20">
+        <v>0</v>
+      </c>
+      <c r="L109" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="M109" s="19">
+        <v>0</v>
+      </c>
+      <c r="N109" s="21">
+        <v>5000</v>
+      </c>
+      <c r="O109" s="22">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="110" spans="1:19">
+      <c r="A110" s="1">
+        <f t="shared" si="11"/>
+        <v>1014010</v>
+      </c>
+      <c r="B110" s="24">
+        <v>101400</v>
+      </c>
+      <c r="C110" s="24">
+        <v>1</v>
+      </c>
+      <c r="D110" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="E110" s="18">
+        <v>101400001</v>
+      </c>
+      <c r="F110" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="G110" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="H110" s="19">
+        <v>10</v>
+      </c>
+      <c r="I110" s="19">
+        <v>0</v>
+      </c>
+      <c r="J110" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K110" s="20">
+        <v>0</v>
+      </c>
+      <c r="L110" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="M110" s="19">
+        <v>0</v>
+      </c>
+      <c r="N110" s="21">
+        <v>50</v>
+      </c>
+      <c r="O110" s="22">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19">
+      <c r="A111" s="1">
+        <f t="shared" si="11"/>
+        <v>1014011</v>
+      </c>
+      <c r="B111" s="24">
+        <v>101400</v>
+      </c>
+      <c r="C111" s="24">
+        <v>1</v>
+      </c>
+      <c r="D111" s="24" t="str">
+        <f t="shared" ref="D111:D115" si="16">D110</f>
+        <v>埃及艳后</v>
+      </c>
+      <c r="E111" s="18">
+        <v>101400001</v>
+      </c>
+      <c r="F111" s="18" t="str">
+        <f t="shared" si="15"/>
+        <v>Cleopatra</v>
+      </c>
+      <c r="G111" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="H111" s="19">
+        <v>11</v>
+      </c>
+      <c r="I111" s="19">
+        <v>0</v>
+      </c>
+      <c r="J111" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K111" s="20">
+        <v>0</v>
+      </c>
+      <c r="L111" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="M111" s="19">
+        <v>0</v>
+      </c>
+      <c r="N111" s="21">
+        <v>500</v>
+      </c>
+      <c r="O111" s="22">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="112" spans="1:19">
+      <c r="A112" s="1">
+        <f t="shared" si="11"/>
+        <v>1014012</v>
+      </c>
+      <c r="B112" s="24">
+        <v>101400</v>
+      </c>
+      <c r="C112" s="24">
+        <v>1</v>
+      </c>
+      <c r="D112" s="24" t="str">
+        <f t="shared" si="16"/>
+        <v>埃及艳后</v>
+      </c>
+      <c r="E112" s="18">
+        <v>101400001</v>
+      </c>
+      <c r="F112" s="18" t="str">
+        <f t="shared" si="15"/>
+        <v>Cleopatra</v>
+      </c>
+      <c r="G112" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="H112" s="19">
+        <v>12</v>
+      </c>
+      <c r="I112" s="19">
+        <v>0</v>
+      </c>
+      <c r="J112" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K112" s="20">
+        <v>0</v>
+      </c>
+      <c r="L112" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="M112" s="19">
+        <v>0</v>
+      </c>
+      <c r="N112" s="21">
+        <v>5000</v>
+      </c>
+      <c r="O112" s="22">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15">
+      <c r="A113" s="1">
+        <f t="shared" si="11"/>
+        <v>1024010</v>
+      </c>
+      <c r="B113" s="24">
+        <v>102400</v>
+      </c>
+      <c r="C113" s="24">
+        <v>1</v>
+      </c>
+      <c r="D113" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="E113" s="18">
+        <v>102400026</v>
+      </c>
+      <c r="F113" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="G113" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="H113" s="19">
+        <v>10</v>
+      </c>
+      <c r="I113" s="19">
+        <v>0</v>
+      </c>
+      <c r="J113" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K113" s="20">
+        <v>0</v>
+      </c>
+      <c r="L113" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="M113" s="19">
+        <v>0</v>
+      </c>
+      <c r="N113" s="21">
+        <v>50</v>
+      </c>
+      <c r="O113" s="22">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15">
+      <c r="A114" s="1">
+        <f t="shared" si="11"/>
+        <v>1024011</v>
+      </c>
+      <c r="B114" s="24">
+        <v>102400</v>
+      </c>
+      <c r="C114" s="24">
+        <v>1</v>
+      </c>
+      <c r="D114" s="24" t="str">
+        <f t="shared" si="16"/>
+        <v>财富银行</v>
+      </c>
+      <c r="E114" s="18">
+        <v>102400026</v>
+      </c>
+      <c r="F114" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="G114" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="H114" s="19">
+        <v>11</v>
+      </c>
+      <c r="I114" s="19">
+        <v>0</v>
+      </c>
+      <c r="J114" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K114" s="20">
+        <v>0</v>
+      </c>
+      <c r="L114" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="M114" s="19">
+        <v>0</v>
+      </c>
+      <c r="N114" s="21">
+        <v>500</v>
+      </c>
+      <c r="O114" s="22">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15">
+      <c r="A115" s="1">
+        <f t="shared" si="11"/>
+        <v>1024012</v>
+      </c>
+      <c r="B115" s="24">
+        <v>102400</v>
+      </c>
+      <c r="C115" s="24">
+        <v>1</v>
+      </c>
+      <c r="D115" s="24" t="str">
+        <f t="shared" si="16"/>
+        <v>财富银行</v>
+      </c>
+      <c r="E115" s="18">
+        <v>102400026</v>
+      </c>
+      <c r="F115" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="G115" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="H115" s="19">
+        <v>12</v>
+      </c>
+      <c r="I115" s="19">
+        <v>0</v>
+      </c>
+      <c r="J115" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K115" s="20">
+        <v>0</v>
+      </c>
+      <c r="L115" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="M115" s="19">
+        <v>0</v>
+      </c>
+      <c r="N115" s="21">
+        <v>5000</v>
+      </c>
+      <c r="O115" s="22">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15">
+      <c r="A116" s="1">
+        <f t="shared" si="11"/>
+        <v>1022010</v>
+      </c>
+      <c r="B116" s="24">
+        <v>102200</v>
+      </c>
+      <c r="C116" s="24">
+        <v>1</v>
+      </c>
+      <c r="D116" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="E116" s="18">
+        <v>102200001</v>
+      </c>
+      <c r="F116" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="G116" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="H116" s="19">
+        <v>10</v>
+      </c>
+      <c r="I116" s="19">
+        <v>0</v>
+      </c>
+      <c r="J116" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K116" s="20">
+        <v>0</v>
+      </c>
+      <c r="L116" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="M116" s="19">
+        <v>0</v>
+      </c>
+      <c r="N116" s="21">
+        <v>50</v>
+      </c>
+      <c r="O116" s="22">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15">
+      <c r="A117" s="1">
+        <f t="shared" si="11"/>
+        <v>1022011</v>
+      </c>
+      <c r="B117" s="24">
+        <v>102200</v>
+      </c>
+      <c r="C117" s="24">
+        <v>1</v>
+      </c>
+      <c r="D117" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="E117" s="18">
+        <v>102200001</v>
+      </c>
+      <c r="F117" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="G117" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="H117" s="19">
+        <v>11</v>
+      </c>
+      <c r="I117" s="19">
+        <v>0</v>
+      </c>
+      <c r="J117" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K117" s="20">
+        <v>0</v>
+      </c>
+      <c r="L117" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="M117" s="19">
+        <v>0</v>
+      </c>
+      <c r="N117" s="21">
+        <v>500</v>
+      </c>
+      <c r="O117" s="22">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15">
+      <c r="A118" s="1">
+        <f t="shared" si="11"/>
+        <v>1022012</v>
+      </c>
+      <c r="B118" s="24">
+        <v>102200</v>
+      </c>
+      <c r="C118" s="24">
+        <v>1</v>
+      </c>
+      <c r="D118" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="E118" s="18">
+        <v>102200001</v>
+      </c>
+      <c r="F118" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="G118" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="H118" s="19">
+        <v>12</v>
+      </c>
+      <c r="I118" s="19">
+        <v>0</v>
+      </c>
+      <c r="J118" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K118" s="20">
+        <v>0</v>
+      </c>
+      <c r="L118" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="M118" s="19">
+        <v>0</v>
+      </c>
+      <c r="N118" s="21">
+        <v>5000</v>
+      </c>
+      <c r="O118" s="22">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15">
+      <c r="A119" s="1">
+        <f t="shared" si="11"/>
+        <v>1017010</v>
+      </c>
+      <c r="B119" s="24">
+        <v>101700</v>
+      </c>
+      <c r="C119" s="24">
+        <v>1</v>
+      </c>
+      <c r="D119" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="E119" s="18">
+        <v>101700001</v>
+      </c>
+      <c r="F119" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="G119" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="H119" s="19">
+        <v>10</v>
+      </c>
+      <c r="I119" s="19">
+        <v>0</v>
+      </c>
+      <c r="J119" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K119" s="20">
+        <v>0</v>
+      </c>
+      <c r="L119" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="M119" s="19">
+        <v>0</v>
+      </c>
+      <c r="N119" s="21">
+        <v>50</v>
+      </c>
+      <c r="O119" s="22">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15">
+      <c r="A120" s="1">
+        <f t="shared" si="11"/>
+        <v>1017011</v>
+      </c>
+      <c r="B120" s="24">
+        <v>101700</v>
+      </c>
+      <c r="C120" s="24">
+        <v>1</v>
+      </c>
+      <c r="D120" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="E120" s="18">
+        <v>101700001</v>
+      </c>
+      <c r="F120" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="G120" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="H120" s="19">
+        <v>11</v>
+      </c>
+      <c r="I120" s="19">
+        <v>0</v>
+      </c>
+      <c r="J120" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K120" s="20">
+        <v>0</v>
+      </c>
+      <c r="L120" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="M120" s="19">
+        <v>0</v>
+      </c>
+      <c r="N120" s="21">
+        <v>500</v>
+      </c>
+      <c r="O120" s="22">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15">
+      <c r="A121" s="1">
+        <f t="shared" si="11"/>
+        <v>1017012</v>
+      </c>
+      <c r="B121" s="24">
+        <v>101700</v>
+      </c>
+      <c r="C121" s="24">
+        <v>1</v>
+      </c>
+      <c r="D121" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="E121" s="18">
+        <v>101700001</v>
+      </c>
+      <c r="F121" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="G121" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="H121" s="19">
+        <v>12</v>
+      </c>
+      <c r="I121" s="19">
+        <v>0</v>
+      </c>
+      <c r="J121" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K121" s="20">
+        <v>0</v>
+      </c>
+      <c r="L121" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="M121" s="19">
+        <v>0</v>
+      </c>
+      <c r="N121" s="21">
+        <v>5000</v>
+      </c>
+      <c r="O121" s="22">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15">
+      <c r="A122" s="1">
+        <f t="shared" si="11"/>
+        <v>1021010</v>
+      </c>
+      <c r="B122" s="24">
+        <v>102100</v>
+      </c>
+      <c r="C122" s="24">
+        <v>1</v>
+      </c>
+      <c r="D122" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="E122" s="18">
+        <v>102100001</v>
+      </c>
+      <c r="F122" s="18"/>
+      <c r="G122" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="H122" s="19">
+        <v>10</v>
+      </c>
+      <c r="I122" s="19">
+        <v>0</v>
+      </c>
+      <c r="J122" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K122" s="20">
+        <v>0</v>
+      </c>
+      <c r="L122" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="M122" s="19">
+        <v>0</v>
+      </c>
+      <c r="N122" s="21">
+        <v>50</v>
+      </c>
+      <c r="O122" s="22">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15">
+      <c r="A123" s="1">
+        <f t="shared" si="11"/>
+        <v>1021011</v>
+      </c>
+      <c r="B123" s="24">
+        <v>102100</v>
+      </c>
+      <c r="C123" s="24">
+        <v>1</v>
+      </c>
+      <c r="D123" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="E123" s="18">
+        <v>102100001</v>
+      </c>
+      <c r="F123" s="18"/>
+      <c r="G123" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="H123" s="19">
+        <v>11</v>
+      </c>
+      <c r="I123" s="19">
+        <v>0</v>
+      </c>
+      <c r="J123" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K123" s="20">
+        <v>0</v>
+      </c>
+      <c r="L123" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="M123" s="19">
+        <v>0</v>
+      </c>
+      <c r="N123" s="21">
+        <v>500</v>
+      </c>
+      <c r="O123" s="22">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15">
+      <c r="A124" s="1">
+        <f t="shared" si="11"/>
+        <v>1021012</v>
+      </c>
+      <c r="B124" s="24">
+        <v>102100</v>
+      </c>
+      <c r="C124" s="24">
+        <v>1</v>
+      </c>
+      <c r="D124" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="E124" s="18">
+        <v>102100001</v>
+      </c>
+      <c r="F124" s="18"/>
+      <c r="G124" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="H124" s="19">
+        <v>12</v>
+      </c>
+      <c r="I124" s="19">
+        <v>0</v>
+      </c>
+      <c r="J124" s="20">
+        <v>-1</v>
+      </c>
+      <c r="K124" s="20">
+        <v>0</v>
+      </c>
+      <c r="L124" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="M124" s="19">
+        <v>0</v>
+      </c>
+      <c r="N124" s="21">
+        <v>5000</v>
+      </c>
+      <c r="O124" s="22">
+        <v>1980000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925" tabRatio="794"/>
+    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Warehouse" sheetId="42" r:id="rId1"/>
@@ -156,7 +156,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="85">
   <si>
     <t>sid</t>
   </si>
@@ -312,6 +312,9 @@
   </si>
   <si>
     <t>杰克船长</t>
+  </si>
+  <si>
+    <t>CaptainJack</t>
   </si>
   <si>
     <t>紅黑大戰</t>
@@ -631,7 +634,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -659,12 +662,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1012,7 +1009,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1036,16 +1033,16 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1054,85 +1051,85 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
@@ -1155,7 +1152,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1204,31 +1201,25 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1236,7 +1227,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1767,7 +1758,7 @@
       <c r="L5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M5" s="25" t="s">
+      <c r="M5" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N5">
@@ -1816,7 +1807,7 @@
       <c r="L6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M6" s="25" t="s">
+      <c r="M6" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N6">
@@ -1865,7 +1856,7 @@
       <c r="L7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M7" s="25" t="s">
+      <c r="M7" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N7">
@@ -1913,7 +1904,7 @@
       <c r="L8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M8" s="25" t="s">
+      <c r="M8" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N8">
@@ -1963,7 +1954,7 @@
       <c r="L9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M9" s="25" t="s">
+      <c r="M9" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N9">
@@ -2013,7 +2004,7 @@
       <c r="L10" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M10" s="25" t="s">
+      <c r="M10" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N10">
@@ -2061,7 +2052,7 @@
       <c r="L11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M11" s="25" t="s">
+      <c r="M11" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N11">
@@ -2111,7 +2102,7 @@
       <c r="L12" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M12" s="25" t="s">
+      <c r="M12" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N12">
@@ -2161,7 +2152,7 @@
       <c r="L13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M13" s="25" t="s">
+      <c r="M13" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N13">
@@ -2209,7 +2200,7 @@
       <c r="L14" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M14" s="25" t="s">
+      <c r="M14" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N14">
@@ -2259,7 +2250,7 @@
       <c r="L15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M15" s="25" t="s">
+      <c r="M15" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N15">
@@ -2309,7 +2300,7 @@
       <c r="L16" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M16" s="25" t="s">
+      <c r="M16" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N16">
@@ -2357,7 +2348,7 @@
       <c r="L17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M17" s="25" t="s">
+      <c r="M17" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N17">
@@ -2407,7 +2398,7 @@
       <c r="L18" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M18" s="25" t="s">
+      <c r="M18" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N18">
@@ -2457,7 +2448,7 @@
       <c r="L19" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M19" s="25" t="s">
+      <c r="M19" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N19">
@@ -2505,7 +2496,7 @@
       <c r="L20" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M20" s="25" t="s">
+      <c r="M20" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N20">
@@ -2554,7 +2545,7 @@
       <c r="L21" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M21" s="25" t="s">
+      <c r="M21" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N21">
@@ -2603,7 +2594,7 @@
       <c r="L22" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M22" s="25" t="s">
+      <c r="M22" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N22">
@@ -2651,7 +2642,7 @@
       <c r="L23" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M23" s="25" t="s">
+      <c r="M23" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N23">
@@ -2699,7 +2690,7 @@
       <c r="L24" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M24" s="25" t="s">
+      <c r="M24" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N24">
@@ -2747,7 +2738,7 @@
       <c r="L25" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M25" s="25" t="s">
+      <c r="M25" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N25">
@@ -2795,7 +2786,7 @@
       <c r="L26" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M26" s="25" t="s">
+      <c r="M26" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N26">
@@ -2843,7 +2834,7 @@
       <c r="L27" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M27" s="25" t="s">
+      <c r="M27" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N27">
@@ -2891,7 +2882,7 @@
       <c r="L28" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M28" s="25" t="s">
+      <c r="M28" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N28">
@@ -2918,7 +2909,9 @@
       <c r="E29" s="13">
         <v>102100001</v>
       </c>
-      <c r="F29" s="13"/>
+      <c r="F29" s="16" t="s">
+        <v>52</v>
+      </c>
       <c r="G29" s="1" t="s">
         <v>32</v>
       </c>
@@ -2937,7 +2930,7 @@
       <c r="L29" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M29" s="25" t="s">
+      <c r="M29" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N29">
@@ -2964,7 +2957,9 @@
       <c r="E30" s="13">
         <v>102100001</v>
       </c>
-      <c r="F30" s="13"/>
+      <c r="F30" s="16" t="s">
+        <v>52</v>
+      </c>
       <c r="G30" s="1" t="s">
         <v>35</v>
       </c>
@@ -2983,7 +2978,7 @@
       <c r="L30" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M30" s="25" t="s">
+      <c r="M30" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N30">
@@ -3010,7 +3005,9 @@
       <c r="E31" s="13">
         <v>102100001</v>
       </c>
-      <c r="F31" s="13"/>
+      <c r="F31" s="16" t="s">
+        <v>52</v>
+      </c>
       <c r="G31" s="1" t="s">
         <v>36</v>
       </c>
@@ -3029,7 +3026,7 @@
       <c r="L31" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M31" s="25" t="s">
+      <c r="M31" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N31">
@@ -3051,13 +3048,13 @@
         <v>2</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E32" s="13">
         <v>200100038</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>32</v>
@@ -3077,7 +3074,7 @@
       <c r="L32" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M32" s="25" t="s">
+      <c r="M32" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N32">
@@ -3106,7 +3103,7 @@
         <v>200100038</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>35</v>
@@ -3126,7 +3123,7 @@
       <c r="L33" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M33" s="25" t="s">
+      <c r="M33" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N33">
@@ -3155,7 +3152,7 @@
         <v>200100038</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>36</v>
@@ -3175,7 +3172,7 @@
       <c r="L34" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M34" s="25" t="s">
+      <c r="M34" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N34">
@@ -3198,13 +3195,13 @@
         <v>2</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E35" s="13">
         <v>200101001</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>32</v>
@@ -3224,7 +3221,7 @@
       <c r="L35" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M35" s="25" t="s">
+      <c r="M35" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N35">
@@ -3253,7 +3250,7 @@
         <v>200101001</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>35</v>
@@ -3273,7 +3270,7 @@
       <c r="L36" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M36" s="25" t="s">
+      <c r="M36" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N36">
@@ -3303,7 +3300,7 @@
         <v>200101001</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>36</v>
@@ -3323,7 +3320,7 @@
       <c r="L37" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M37" s="25" t="s">
+      <c r="M37" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N37">
@@ -3346,13 +3343,13 @@
         <v>2</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E38" s="13">
         <v>200300001</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>32</v>
@@ -3372,7 +3369,7 @@
       <c r="L38" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M38" s="25" t="s">
+      <c r="M38" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N38">
@@ -3401,7 +3398,7 @@
         <v>200300001</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>35</v>
@@ -3421,7 +3418,7 @@
       <c r="L39" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M39" s="25" t="s">
+      <c r="M39" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N39">
@@ -3453,7 +3450,7 @@
         <v>200300001</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>36</v>
@@ -3473,7 +3470,7 @@
       <c r="L40" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M40" s="25" t="s">
+      <c r="M40" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N40">
@@ -3483,8 +3480,8 @@
         <v>1990000</v>
       </c>
       <c r="Q40" s="3"/>
-      <c r="R40" s="16"/>
-      <c r="S40" s="16"/>
+      <c r="R40" s="17"/>
+      <c r="S40" s="17"/>
     </row>
     <row r="41" spans="1:19">
       <c r="A41" s="1">
@@ -3497,14 +3494,14 @@
       <c r="C41" s="12">
         <v>2</v>
       </c>
-      <c r="D41" s="16" t="s">
-        <v>58</v>
+      <c r="D41" s="17" t="s">
+        <v>59</v>
       </c>
       <c r="E41" s="13">
         <v>200400009</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>32</v>
@@ -3524,7 +3521,7 @@
       <c r="L41" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M41" s="25" t="s">
+      <c r="M41" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N41">
@@ -3534,8 +3531,8 @@
         <v>1990000</v>
       </c>
       <c r="Q41" s="3"/>
-      <c r="R41" s="16"/>
-      <c r="S41" s="16"/>
+      <c r="R41" s="17"/>
+      <c r="S41" s="17"/>
     </row>
     <row r="42" s="1" customFormat="1" spans="1:19">
       <c r="A42" s="1">
@@ -3548,14 +3545,14 @@
       <c r="C42" s="12">
         <v>2</v>
       </c>
-      <c r="D42" s="16" t="s">
-        <v>58</v>
+      <c r="D42" s="17" t="s">
+        <v>59</v>
       </c>
       <c r="E42" s="13">
         <v>200400009</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>35</v>
@@ -3575,7 +3572,7 @@
       <c r="L42" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M42" s="25" t="s">
+      <c r="M42" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N42">
@@ -3585,8 +3582,8 @@
         <v>1990000</v>
       </c>
       <c r="Q42" s="3"/>
-      <c r="R42" s="16"/>
-      <c r="S42" s="16"/>
+      <c r="R42" s="17"/>
+      <c r="S42" s="17"/>
     </row>
     <row r="43" s="1" customFormat="1" spans="1:19">
       <c r="A43" s="1">
@@ -3599,14 +3596,14 @@
       <c r="C43" s="12">
         <v>2</v>
       </c>
-      <c r="D43" s="16" t="s">
-        <v>58</v>
+      <c r="D43" s="17" t="s">
+        <v>59</v>
       </c>
       <c r="E43" s="13">
         <v>200400009</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>36</v>
@@ -3626,7 +3623,7 @@
       <c r="L43" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M43" s="25" t="s">
+      <c r="M43" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N43">
@@ -3636,8 +3633,8 @@
         <v>1990000</v>
       </c>
       <c r="Q43" s="3"/>
-      <c r="R43" s="16"/>
-      <c r="S43" s="16"/>
+      <c r="R43" s="17"/>
+      <c r="S43" s="17"/>
     </row>
     <row r="44" spans="1:19">
       <c r="A44" s="1">
@@ -3651,13 +3648,13 @@
         <v>2</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E44" s="13">
         <v>200500025</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>32</v>
@@ -3677,8 +3674,8 @@
       <c r="L44" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M44" s="25" t="s">
-        <v>62</v>
+      <c r="M44" s="23" t="s">
+        <v>63</v>
       </c>
       <c r="N44">
         <v>5000</v>
@@ -3687,8 +3684,8 @@
         <v>1990000</v>
       </c>
       <c r="Q44" s="3"/>
-      <c r="R44" s="16"/>
-      <c r="S44" s="16"/>
+      <c r="R44" s="17"/>
+      <c r="S44" s="17"/>
     </row>
     <row r="45" spans="1:19">
       <c r="A45" s="1">
@@ -3702,13 +3699,13 @@
         <v>2</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E45" s="13">
         <v>200500025</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>35</v>
@@ -3728,8 +3725,8 @@
       <c r="L45" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M45" s="25" t="s">
-        <v>62</v>
+      <c r="M45" s="23" t="s">
+        <v>63</v>
       </c>
       <c r="N45">
         <v>500000</v>
@@ -3738,8 +3735,8 @@
         <v>1990000</v>
       </c>
       <c r="Q45" s="3"/>
-      <c r="R45" s="16"/>
-      <c r="S45" s="16"/>
+      <c r="R45" s="17"/>
+      <c r="S45" s="17"/>
     </row>
     <row r="46" spans="1:19">
       <c r="A46" s="1">
@@ -3753,13 +3750,13 @@
         <v>2</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E46" s="13">
         <v>200500025</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>36</v>
@@ -3779,8 +3776,8 @@
       <c r="L46" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M46" s="25" t="s">
-        <v>62</v>
+      <c r="M46" s="23" t="s">
+        <v>63</v>
       </c>
       <c r="N46">
         <v>50000000</v>
@@ -3789,8 +3786,8 @@
         <v>1990000</v>
       </c>
       <c r="Q46" s="3"/>
-      <c r="R46" s="16"/>
-      <c r="S46" s="16"/>
+      <c r="R46" s="17"/>
+      <c r="S46" s="17"/>
     </row>
     <row r="47" spans="1:19">
       <c r="A47" s="1">
@@ -3804,13 +3801,13 @@
         <v>2</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E47" s="13">
         <v>200600001</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>32</v>
@@ -3830,7 +3827,7 @@
       <c r="L47" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M47" s="25" t="s">
+      <c r="M47" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N47">
@@ -3840,8 +3837,8 @@
         <v>1990000</v>
       </c>
       <c r="Q47" s="3"/>
-      <c r="R47" s="16"/>
-      <c r="S47" s="16"/>
+      <c r="R47" s="17"/>
+      <c r="S47" s="17"/>
     </row>
     <row r="48" s="1" customFormat="1" spans="1:19">
       <c r="A48" s="1">
@@ -3855,13 +3852,13 @@
         <v>2</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E48" s="13">
         <v>200600001</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>35</v>
@@ -3881,7 +3878,7 @@
       <c r="L48" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M48" s="25" t="s">
+      <c r="M48" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N48">
@@ -3891,8 +3888,8 @@
         <v>1990000</v>
       </c>
       <c r="Q48" s="3"/>
-      <c r="R48" s="16"/>
-      <c r="S48" s="16"/>
+      <c r="R48" s="17"/>
+      <c r="S48" s="17"/>
     </row>
     <row r="49" s="1" customFormat="1" spans="1:19">
       <c r="A49" s="1">
@@ -3906,13 +3903,13 @@
         <v>2</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E49" s="13">
         <v>200600001</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>36</v>
@@ -3932,7 +3929,7 @@
       <c r="L49" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M49" s="25" t="s">
+      <c r="M49" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N49">
@@ -3943,7 +3940,7 @@
       </c>
       <c r="Q49" s="3"/>
       <c r="R49"/>
-      <c r="S49" s="16"/>
+      <c r="S49" s="17"/>
     </row>
     <row r="50" spans="1:19">
       <c r="A50" s="1">
@@ -3957,13 +3954,13 @@
         <v>2</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E50" s="13">
         <v>200700001</v>
       </c>
       <c r="F50" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>32</v>
@@ -3983,7 +3980,7 @@
       <c r="L50" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M50" s="25" t="s">
+      <c r="M50" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N50">
@@ -3993,8 +3990,8 @@
         <v>1990000</v>
       </c>
       <c r="Q50" s="3"/>
-      <c r="R50" s="16"/>
-      <c r="S50" s="16"/>
+      <c r="R50" s="17"/>
+      <c r="S50" s="17"/>
     </row>
     <row r="51" s="1" customFormat="1" spans="1:19">
       <c r="A51" s="1">
@@ -4015,7 +4012,7 @@
         <v>200700001</v>
       </c>
       <c r="F51" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>35</v>
@@ -4035,7 +4032,7 @@
       <c r="L51" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M51" s="25" t="s">
+      <c r="M51" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N51">
@@ -4045,8 +4042,8 @@
         <v>1990000</v>
       </c>
       <c r="Q51" s="3"/>
-      <c r="R51" s="16"/>
-      <c r="S51" s="16"/>
+      <c r="R51" s="17"/>
+      <c r="S51" s="17"/>
     </row>
     <row r="52" s="1" customFormat="1" spans="1:19">
       <c r="A52" s="1">
@@ -4067,7 +4064,7 @@
         <v>200700001</v>
       </c>
       <c r="F52" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>36</v>
@@ -4087,7 +4084,7 @@
       <c r="L52" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M52" s="25" t="s">
+      <c r="M52" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N52">
@@ -4110,13 +4107,13 @@
         <v>2</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E53" s="13">
         <v>200800001</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>32</v>
@@ -4136,7 +4133,7 @@
       <c r="L53" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M53" s="25" t="s">
+      <c r="M53" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N53">
@@ -4159,13 +4156,13 @@
         <v>2</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E54" s="13">
         <v>200800001</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>35</v>
@@ -4185,7 +4182,7 @@
       <c r="L54" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M54" s="25" t="s">
+      <c r="M54" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N54">
@@ -4208,13 +4205,13 @@
         <v>2</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E55" s="13">
         <v>200800001</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>36</v>
@@ -4234,7 +4231,7 @@
       <c r="L55" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M55" s="25" t="s">
+      <c r="M55" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N55">
@@ -4250,20 +4247,20 @@
         <f t="shared" si="5"/>
         <v>2009001</v>
       </c>
-      <c r="B56" s="17">
+      <c r="B56" s="18">
         <v>200900</v>
       </c>
       <c r="C56" s="12">
         <v>2</v>
       </c>
-      <c r="D56" s="17" t="s">
-        <v>69</v>
+      <c r="D56" s="18" t="s">
+        <v>70</v>
       </c>
       <c r="E56" s="13">
         <v>200900001</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>32</v>
@@ -4283,7 +4280,7 @@
       <c r="L56" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M56" s="25" t="s">
+      <c r="M56" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N56">
@@ -4312,7 +4309,7 @@
         <v>200900001</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>35</v>
@@ -4332,7 +4329,7 @@
       <c r="L57" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M57" s="25" t="s">
+      <c r="M57" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N57">
@@ -4361,7 +4358,7 @@
         <v>200900001</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>36</v>
@@ -4381,7 +4378,7 @@
       <c r="L58" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M58" s="25" t="s">
+      <c r="M58" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N58">
@@ -4403,7 +4400,7 @@
         <v>2</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E59" s="13">
         <v>101000006</v>
@@ -4427,7 +4424,7 @@
       <c r="L59" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M59" s="25" t="s">
+      <c r="M59" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N59">
@@ -4449,7 +4446,7 @@
         <v>2</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E60" s="13">
         <v>101000006</v>
@@ -4473,7 +4470,7 @@
       <c r="L60" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M60" s="25" t="s">
+      <c r="M60" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N60">
@@ -4495,7 +4492,7 @@
         <v>2</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E61" s="13">
         <v>101000006</v>
@@ -4519,7 +4516,7 @@
       <c r="L61" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M61" s="25" t="s">
+      <c r="M61" s="23" t="s">
         <v>34</v>
       </c>
       <c r="N61">
@@ -4541,13 +4538,13 @@
         <v>3</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E62" s="13">
         <v>300100001</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>32</v>
@@ -4564,11 +4561,11 @@
       <c r="K62" s="1">
         <v>0</v>
       </c>
-      <c r="L62" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="M62" s="26" t="s">
+      <c r="L62" s="24" t="s">
         <v>75</v>
+      </c>
+      <c r="M62" s="24" t="s">
+        <v>76</v>
       </c>
       <c r="N62">
         <v>5000</v>
@@ -4589,13 +4586,13 @@
         <v>3</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E63" s="13">
         <v>300100001</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>35</v>
@@ -4612,11 +4609,11 @@
       <c r="K63" s="1">
         <v>0</v>
       </c>
-      <c r="L63" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="M63" s="26" t="s">
+      <c r="L63" s="24" t="s">
         <v>75</v>
+      </c>
+      <c r="M63" s="24" t="s">
+        <v>76</v>
       </c>
       <c r="N63">
         <v>500000</v>
@@ -4638,13 +4635,13 @@
         <v>3</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E64" s="13">
         <v>300100001</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>36</v>
@@ -4661,11 +4658,11 @@
       <c r="K64" s="1">
         <v>0</v>
       </c>
-      <c r="L64" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="M64" s="26" t="s">
+      <c r="L64" s="24" t="s">
         <v>75</v>
+      </c>
+      <c r="M64" s="24" t="s">
+        <v>76</v>
       </c>
       <c r="N64">
         <v>50000000</v>
@@ -4687,13 +4684,13 @@
         <v>3</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E65" s="13">
         <v>300200006</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>32</v>
@@ -4710,11 +4707,11 @@
       <c r="K65" s="1">
         <v>0</v>
       </c>
-      <c r="L65" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="M65" s="26" t="s">
-        <v>75</v>
+      <c r="L65" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="M65" s="24" t="s">
+        <v>76</v>
       </c>
       <c r="N65">
         <v>5000</v>
@@ -4736,13 +4733,13 @@
         <v>3</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E66" s="13">
         <v>300200006</v>
       </c>
       <c r="F66" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>35</v>
@@ -4759,11 +4756,11 @@
       <c r="K66" s="1">
         <v>0</v>
       </c>
-      <c r="L66" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="M66" s="26" t="s">
-        <v>75</v>
+      <c r="L66" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="M66" s="24" t="s">
+        <v>76</v>
       </c>
       <c r="N66">
         <v>500000</v>
@@ -4785,13 +4782,13 @@
         <v>3</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E67" s="13">
         <v>300200006</v>
       </c>
       <c r="F67" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>36</v>
@@ -4808,11 +4805,11 @@
       <c r="K67" s="1">
         <v>0</v>
       </c>
-      <c r="L67" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="M67" s="26" t="s">
-        <v>75</v>
+      <c r="L67" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="M67" s="24" t="s">
+        <v>76</v>
       </c>
       <c r="N67">
         <v>50000000</v>
@@ -4827,23 +4824,23 @@
         <f t="shared" ref="A68:A74" si="8">B68*100+H68</f>
         <v>20010010</v>
       </c>
-      <c r="B68" s="18">
+      <c r="B68" s="16">
         <v>200100</v>
       </c>
-      <c r="C68" s="18">
-        <v>2</v>
-      </c>
-      <c r="D68" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="E68" s="18">
+      <c r="C68" s="16">
+        <v>2</v>
+      </c>
+      <c r="D68" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="E68" s="16">
         <v>200100038</v>
       </c>
-      <c r="F68" s="18" t="s">
-        <v>53</v>
+      <c r="F68" s="16" t="s">
+        <v>54</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H68" s="19">
         <v>10</v>
@@ -4854,19 +4851,19 @@
       <c r="J68" s="19">
         <v>-1</v>
       </c>
-      <c r="K68" s="20">
+      <c r="K68" s="19">
         <v>0</v>
       </c>
       <c r="L68" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M68" s="19">
         <v>0</v>
       </c>
-      <c r="N68" s="21">
+      <c r="N68" s="20">
         <v>200</v>
       </c>
-      <c r="O68" s="22">
+      <c r="O68" s="21">
         <v>1980000</v>
       </c>
       <c r="S68" s="3"/>
@@ -4876,23 +4873,23 @@
         <f t="shared" si="8"/>
         <v>20010011</v>
       </c>
-      <c r="B69" s="18">
+      <c r="B69" s="16">
         <v>200100</v>
       </c>
-      <c r="C69" s="18">
-        <v>2</v>
-      </c>
-      <c r="D69" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="E69" s="18">
+      <c r="C69" s="16">
+        <v>2</v>
+      </c>
+      <c r="D69" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="E69" s="16">
         <v>200100038</v>
       </c>
-      <c r="F69" s="18" t="s">
-        <v>53</v>
+      <c r="F69" s="16" t="s">
+        <v>54</v>
       </c>
       <c r="G69" s="19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H69" s="19">
         <v>11</v>
@@ -4903,19 +4900,19 @@
       <c r="J69" s="19">
         <v>-1</v>
       </c>
-      <c r="K69" s="20">
+      <c r="K69" s="19">
         <v>0</v>
       </c>
       <c r="L69" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M69" s="19">
         <v>0</v>
       </c>
-      <c r="N69" s="21">
+      <c r="N69" s="20">
         <v>5000</v>
       </c>
-      <c r="O69" s="22">
+      <c r="O69" s="21">
         <v>1980000</v>
       </c>
       <c r="S69" s="3"/>
@@ -4925,23 +4922,23 @@
         <f t="shared" si="8"/>
         <v>20010012</v>
       </c>
-      <c r="B70" s="18">
+      <c r="B70" s="16">
         <v>200100</v>
       </c>
-      <c r="C70" s="18">
-        <v>2</v>
-      </c>
-      <c r="D70" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="E70" s="18">
+      <c r="C70" s="16">
+        <v>2</v>
+      </c>
+      <c r="D70" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="E70" s="16">
         <v>200100038</v>
       </c>
-      <c r="F70" s="18" t="s">
-        <v>53</v>
+      <c r="F70" s="16" t="s">
+        <v>54</v>
       </c>
       <c r="G70" s="19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H70" s="19">
         <v>12</v>
@@ -4952,19 +4949,19 @@
       <c r="J70" s="19">
         <v>-1</v>
       </c>
-      <c r="K70" s="20">
+      <c r="K70" s="19">
         <v>0</v>
       </c>
       <c r="L70" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M70" s="19">
         <v>0</v>
       </c>
-      <c r="N70" s="21">
+      <c r="N70" s="20">
         <v>100000</v>
       </c>
-      <c r="O70" s="22">
+      <c r="O70" s="21">
         <v>1980000</v>
       </c>
       <c r="S70" s="3"/>
@@ -4974,23 +4971,23 @@
         <f t="shared" si="8"/>
         <v>20010110</v>
       </c>
-      <c r="B71" s="18">
+      <c r="B71" s="16">
         <v>200101</v>
       </c>
-      <c r="C71" s="18">
-        <v>2</v>
-      </c>
-      <c r="D71" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="E71" s="18">
+      <c r="C71" s="16">
+        <v>2</v>
+      </c>
+      <c r="D71" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E71" s="16">
         <v>200101001</v>
       </c>
-      <c r="F71" s="18" t="s">
-        <v>55</v>
+      <c r="F71" s="16" t="s">
+        <v>56</v>
       </c>
       <c r="G71" s="19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H71" s="19">
         <v>10</v>
@@ -5001,19 +4998,19 @@
       <c r="J71" s="19">
         <v>-1</v>
       </c>
-      <c r="K71" s="20">
+      <c r="K71" s="19">
         <v>0</v>
       </c>
       <c r="L71" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M71" s="19">
         <v>0</v>
       </c>
-      <c r="N71" s="21">
+      <c r="N71" s="20">
         <v>200</v>
       </c>
-      <c r="O71" s="22">
+      <c r="O71" s="21">
         <v>1980000</v>
       </c>
       <c r="S71" s="3"/>
@@ -5023,23 +5020,23 @@
         <f t="shared" si="8"/>
         <v>20010111</v>
       </c>
-      <c r="B72" s="18">
+      <c r="B72" s="16">
         <v>200101</v>
       </c>
-      <c r="C72" s="18">
-        <v>2</v>
-      </c>
-      <c r="D72" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="E72" s="18">
+      <c r="C72" s="16">
+        <v>2</v>
+      </c>
+      <c r="D72" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E72" s="16">
         <v>200101001</v>
       </c>
-      <c r="F72" s="18" t="s">
-        <v>55</v>
+      <c r="F72" s="16" t="s">
+        <v>56</v>
       </c>
       <c r="G72" s="19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H72" s="19">
         <v>11</v>
@@ -5050,19 +5047,19 @@
       <c r="J72" s="19">
         <v>-1</v>
       </c>
-      <c r="K72" s="20">
+      <c r="K72" s="19">
         <v>0</v>
       </c>
       <c r="L72" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M72" s="19">
         <v>0</v>
       </c>
-      <c r="N72" s="21">
+      <c r="N72" s="20">
         <v>5000</v>
       </c>
-      <c r="O72" s="22">
+      <c r="O72" s="21">
         <v>1980000</v>
       </c>
       <c r="S72" s="3"/>
@@ -5072,23 +5069,23 @@
         <f t="shared" si="8"/>
         <v>20010112</v>
       </c>
-      <c r="B73" s="18">
+      <c r="B73" s="16">
         <v>200101</v>
       </c>
-      <c r="C73" s="18">
-        <v>2</v>
-      </c>
-      <c r="D73" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="E73" s="18">
+      <c r="C73" s="16">
+        <v>2</v>
+      </c>
+      <c r="D73" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E73" s="16">
         <v>200101001</v>
       </c>
-      <c r="F73" s="18" t="s">
-        <v>55</v>
+      <c r="F73" s="16" t="s">
+        <v>56</v>
       </c>
       <c r="G73" s="19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H73" s="19">
         <v>12</v>
@@ -5099,19 +5096,19 @@
       <c r="J73" s="19">
         <v>-1</v>
       </c>
-      <c r="K73" s="20">
+      <c r="K73" s="19">
         <v>0</v>
       </c>
       <c r="L73" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M73" s="19">
         <v>0</v>
       </c>
-      <c r="N73" s="21">
+      <c r="N73" s="20">
         <v>100000</v>
       </c>
-      <c r="O73" s="22">
+      <c r="O73" s="21">
         <v>1980000</v>
       </c>
       <c r="S73" s="3"/>
@@ -5121,23 +5118,23 @@
         <f t="shared" si="8"/>
         <v>20030010</v>
       </c>
-      <c r="B74" s="18">
+      <c r="B74" s="16">
         <v>200300</v>
       </c>
-      <c r="C74" s="18">
-        <v>2</v>
-      </c>
-      <c r="D74" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="E74" s="18">
+      <c r="C74" s="16">
+        <v>2</v>
+      </c>
+      <c r="D74" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="E74" s="16">
         <v>200300001</v>
       </c>
-      <c r="F74" s="18" t="s">
-        <v>57</v>
+      <c r="F74" s="16" t="s">
+        <v>58</v>
       </c>
       <c r="G74" s="19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H74" s="19">
         <v>10</v>
@@ -5148,19 +5145,19 @@
       <c r="J74" s="19">
         <v>-1</v>
       </c>
-      <c r="K74" s="20">
+      <c r="K74" s="19">
         <v>0</v>
       </c>
       <c r="L74" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M74" s="19">
         <v>0</v>
       </c>
-      <c r="N74" s="21">
+      <c r="N74" s="20">
         <v>200</v>
       </c>
-      <c r="O74" s="22">
+      <c r="O74" s="21">
         <v>1980000</v>
       </c>
       <c r="S74" s="3"/>
@@ -5170,23 +5167,23 @@
         <f t="shared" ref="A75:A83" si="9">B75*100+H75</f>
         <v>20030011</v>
       </c>
-      <c r="B75" s="18">
+      <c r="B75" s="16">
         <v>200300</v>
       </c>
-      <c r="C75" s="18">
-        <v>2</v>
-      </c>
-      <c r="D75" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="E75" s="18">
+      <c r="C75" s="16">
+        <v>2</v>
+      </c>
+      <c r="D75" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="E75" s="16">
         <v>200300001</v>
       </c>
-      <c r="F75" s="18" t="s">
-        <v>57</v>
+      <c r="F75" s="16" t="s">
+        <v>58</v>
       </c>
       <c r="G75" s="19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H75" s="19">
         <v>11</v>
@@ -5197,19 +5194,19 @@
       <c r="J75" s="19">
         <v>-1</v>
       </c>
-      <c r="K75" s="20">
+      <c r="K75" s="19">
         <v>0</v>
       </c>
       <c r="L75" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M75" s="19">
         <v>0</v>
       </c>
-      <c r="N75" s="21">
+      <c r="N75" s="20">
         <v>5000</v>
       </c>
-      <c r="O75" s="22">
+      <c r="O75" s="21">
         <v>1980000</v>
       </c>
       <c r="S75" s="3"/>
@@ -5219,23 +5216,23 @@
         <f t="shared" si="9"/>
         <v>20030012</v>
       </c>
-      <c r="B76" s="18">
+      <c r="B76" s="16">
         <v>200300</v>
       </c>
-      <c r="C76" s="18">
-        <v>2</v>
-      </c>
-      <c r="D76" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="E76" s="18">
+      <c r="C76" s="16">
+        <v>2</v>
+      </c>
+      <c r="D76" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="E76" s="16">
         <v>200300001</v>
       </c>
-      <c r="F76" s="18" t="s">
-        <v>57</v>
+      <c r="F76" s="16" t="s">
+        <v>58</v>
       </c>
       <c r="G76" s="19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H76" s="19">
         <v>12</v>
@@ -5246,19 +5243,19 @@
       <c r="J76" s="19">
         <v>-1</v>
       </c>
-      <c r="K76" s="20">
+      <c r="K76" s="19">
         <v>0</v>
       </c>
       <c r="L76" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M76" s="19">
         <v>0</v>
       </c>
-      <c r="N76" s="21">
+      <c r="N76" s="20">
         <v>100000</v>
       </c>
-      <c r="O76" s="22">
+      <c r="O76" s="21">
         <v>1980000</v>
       </c>
       <c r="S76" s="3"/>
@@ -5268,23 +5265,23 @@
         <f t="shared" si="9"/>
         <v>20040010</v>
       </c>
-      <c r="B77" s="18">
+      <c r="B77" s="16">
         <v>200400</v>
       </c>
-      <c r="C77" s="18">
-        <v>2</v>
-      </c>
-      <c r="D77" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="E77" s="18">
+      <c r="C77" s="16">
+        <v>2</v>
+      </c>
+      <c r="D77" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="E77" s="16">
         <v>200400009</v>
       </c>
-      <c r="F77" s="18" t="s">
-        <v>59</v>
+      <c r="F77" s="16" t="s">
+        <v>60</v>
       </c>
       <c r="G77" s="19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H77" s="19">
         <v>10</v>
@@ -5295,19 +5292,19 @@
       <c r="J77" s="19">
         <v>-1</v>
       </c>
-      <c r="K77" s="20">
+      <c r="K77" s="19">
         <v>0</v>
       </c>
       <c r="L77" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M77" s="19">
         <v>0</v>
       </c>
-      <c r="N77" s="21">
+      <c r="N77" s="20">
         <v>200</v>
       </c>
-      <c r="O77" s="22">
+      <c r="O77" s="21">
         <v>1980000</v>
       </c>
       <c r="S77" s="3"/>
@@ -5317,23 +5314,23 @@
         <f t="shared" si="9"/>
         <v>20040011</v>
       </c>
-      <c r="B78" s="18">
+      <c r="B78" s="16">
         <v>200400</v>
       </c>
-      <c r="C78" s="18">
-        <v>2</v>
-      </c>
-      <c r="D78" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="E78" s="18">
+      <c r="C78" s="16">
+        <v>2</v>
+      </c>
+      <c r="D78" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="E78" s="16">
         <v>200400009</v>
       </c>
-      <c r="F78" s="18" t="s">
-        <v>59</v>
+      <c r="F78" s="16" t="s">
+        <v>60</v>
       </c>
       <c r="G78" s="19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H78" s="19">
         <v>11</v>
@@ -5344,19 +5341,19 @@
       <c r="J78" s="19">
         <v>-1</v>
       </c>
-      <c r="K78" s="20">
+      <c r="K78" s="19">
         <v>0</v>
       </c>
       <c r="L78" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M78" s="19">
         <v>0</v>
       </c>
-      <c r="N78" s="21">
+      <c r="N78" s="20">
         <v>5000</v>
       </c>
-      <c r="O78" s="22">
+      <c r="O78" s="21">
         <v>1980000</v>
       </c>
       <c r="S78" s="3"/>
@@ -5366,23 +5363,23 @@
         <f t="shared" si="9"/>
         <v>20040012</v>
       </c>
-      <c r="B79" s="18">
+      <c r="B79" s="16">
         <v>200400</v>
       </c>
-      <c r="C79" s="18">
-        <v>2</v>
-      </c>
-      <c r="D79" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="E79" s="18">
+      <c r="C79" s="16">
+        <v>2</v>
+      </c>
+      <c r="D79" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="E79" s="16">
         <v>200400009</v>
       </c>
-      <c r="F79" s="18" t="s">
-        <v>59</v>
+      <c r="F79" s="16" t="s">
+        <v>60</v>
       </c>
       <c r="G79" s="19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H79" s="19">
         <v>12</v>
@@ -5393,19 +5390,19 @@
       <c r="J79" s="19">
         <v>-1</v>
       </c>
-      <c r="K79" s="20">
+      <c r="K79" s="19">
         <v>0</v>
       </c>
       <c r="L79" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M79" s="19">
         <v>0</v>
       </c>
-      <c r="N79" s="21">
+      <c r="N79" s="20">
         <v>100000</v>
       </c>
-      <c r="O79" s="22">
+      <c r="O79" s="21">
         <v>1980000</v>
       </c>
       <c r="S79" s="3"/>
@@ -5415,23 +5412,23 @@
         <f t="shared" si="9"/>
         <v>20050010</v>
       </c>
-      <c r="B80" s="18">
+      <c r="B80" s="16">
         <v>200500</v>
       </c>
-      <c r="C80" s="18">
-        <v>2</v>
-      </c>
-      <c r="D80" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="E80" s="18">
+      <c r="C80" s="16">
+        <v>2</v>
+      </c>
+      <c r="D80" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="E80" s="16">
         <v>200500025</v>
       </c>
-      <c r="F80" s="18" t="s">
-        <v>61</v>
+      <c r="F80" s="16" t="s">
+        <v>62</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H80" s="19">
         <v>10</v>
@@ -5442,19 +5439,19 @@
       <c r="J80" s="19">
         <v>-1</v>
       </c>
-      <c r="K80" s="20">
+      <c r="K80" s="19">
         <v>0</v>
       </c>
       <c r="L80" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M80" s="19">
         <v>0</v>
       </c>
-      <c r="N80" s="21">
+      <c r="N80" s="20">
         <v>200</v>
       </c>
-      <c r="O80" s="22">
+      <c r="O80" s="21">
         <v>1980000</v>
       </c>
       <c r="S80" s="3"/>
@@ -5464,23 +5461,23 @@
         <f t="shared" si="9"/>
         <v>20050011</v>
       </c>
-      <c r="B81" s="18">
+      <c r="B81" s="16">
         <v>200500</v>
       </c>
-      <c r="C81" s="18">
-        <v>2</v>
-      </c>
-      <c r="D81" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="E81" s="18">
+      <c r="C81" s="16">
+        <v>2</v>
+      </c>
+      <c r="D81" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="E81" s="16">
         <v>200500025</v>
       </c>
-      <c r="F81" s="18" t="s">
-        <v>61</v>
+      <c r="F81" s="16" t="s">
+        <v>62</v>
       </c>
       <c r="G81" s="19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H81" s="19">
         <v>11</v>
@@ -5491,19 +5488,19 @@
       <c r="J81" s="19">
         <v>-1</v>
       </c>
-      <c r="K81" s="20">
+      <c r="K81" s="19">
         <v>0</v>
       </c>
       <c r="L81" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M81" s="19">
         <v>0</v>
       </c>
-      <c r="N81" s="21">
+      <c r="N81" s="20">
         <v>5000</v>
       </c>
-      <c r="O81" s="22">
+      <c r="O81" s="21">
         <v>1980000</v>
       </c>
       <c r="S81" s="3"/>
@@ -5513,23 +5510,23 @@
         <f t="shared" si="9"/>
         <v>20050012</v>
       </c>
-      <c r="B82" s="18">
+      <c r="B82" s="16">
         <v>200500</v>
       </c>
-      <c r="C82" s="18">
-        <v>2</v>
-      </c>
-      <c r="D82" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="E82" s="18">
+      <c r="C82" s="16">
+        <v>2</v>
+      </c>
+      <c r="D82" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="E82" s="16">
         <v>200500025</v>
       </c>
-      <c r="F82" s="18" t="s">
-        <v>61</v>
+      <c r="F82" s="16" t="s">
+        <v>62</v>
       </c>
       <c r="G82" s="19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H82" s="19">
         <v>12</v>
@@ -5540,19 +5537,19 @@
       <c r="J82" s="19">
         <v>-1</v>
       </c>
-      <c r="K82" s="20">
+      <c r="K82" s="19">
         <v>0</v>
       </c>
       <c r="L82" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M82" s="19">
         <v>0</v>
       </c>
-      <c r="N82" s="21">
+      <c r="N82" s="20">
         <v>100000</v>
       </c>
-      <c r="O82" s="22">
+      <c r="O82" s="21">
         <v>1980000</v>
       </c>
       <c r="S82" s="3"/>
@@ -5562,23 +5559,23 @@
         <f t="shared" si="9"/>
         <v>20060010</v>
       </c>
-      <c r="B83" s="18">
+      <c r="B83" s="16">
         <v>200600</v>
       </c>
-      <c r="C83" s="18">
-        <v>2</v>
-      </c>
-      <c r="D83" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="E83" s="18">
+      <c r="C83" s="16">
+        <v>2</v>
+      </c>
+      <c r="D83" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="E83" s="16">
         <v>200600001</v>
       </c>
-      <c r="F83" s="18" t="s">
-        <v>64</v>
+      <c r="F83" s="16" t="s">
+        <v>65</v>
       </c>
       <c r="G83" s="19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H83" s="19">
         <v>10</v>
@@ -5589,19 +5586,19 @@
       <c r="J83" s="19">
         <v>-1</v>
       </c>
-      <c r="K83" s="20">
+      <c r="K83" s="19">
         <v>0</v>
       </c>
       <c r="L83" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M83" s="19">
         <v>0</v>
       </c>
-      <c r="N83" s="21">
+      <c r="N83" s="20">
         <v>200</v>
       </c>
-      <c r="O83" s="22">
+      <c r="O83" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -5610,23 +5607,23 @@
         <f t="shared" ref="A84:A98" si="10">B84*100+H84</f>
         <v>20060011</v>
       </c>
-      <c r="B84" s="18">
+      <c r="B84" s="16">
         <v>200600</v>
       </c>
-      <c r="C84" s="18">
-        <v>2</v>
-      </c>
-      <c r="D84" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="E84" s="18">
+      <c r="C84" s="16">
+        <v>2</v>
+      </c>
+      <c r="D84" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="E84" s="16">
         <v>200600001</v>
       </c>
-      <c r="F84" s="18" t="s">
-        <v>64</v>
+      <c r="F84" s="16" t="s">
+        <v>65</v>
       </c>
       <c r="G84" s="19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H84" s="19">
         <v>11</v>
@@ -5637,19 +5634,19 @@
       <c r="J84" s="19">
         <v>-1</v>
       </c>
-      <c r="K84" s="20">
+      <c r="K84" s="19">
         <v>0</v>
       </c>
       <c r="L84" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M84" s="19">
         <v>0</v>
       </c>
-      <c r="N84" s="21">
+      <c r="N84" s="20">
         <v>5000</v>
       </c>
-      <c r="O84" s="22">
+      <c r="O84" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -5658,23 +5655,23 @@
         <f t="shared" si="10"/>
         <v>20060012</v>
       </c>
-      <c r="B85" s="18">
+      <c r="B85" s="16">
         <v>200600</v>
       </c>
-      <c r="C85" s="18">
-        <v>2</v>
-      </c>
-      <c r="D85" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="E85" s="18">
+      <c r="C85" s="16">
+        <v>2</v>
+      </c>
+      <c r="D85" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="E85" s="16">
         <v>200600001</v>
       </c>
-      <c r="F85" s="18" t="s">
-        <v>64</v>
+      <c r="F85" s="16" t="s">
+        <v>65</v>
       </c>
       <c r="G85" s="19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H85" s="19">
         <v>12</v>
@@ -5685,19 +5682,19 @@
       <c r="J85" s="19">
         <v>-1</v>
       </c>
-      <c r="K85" s="20">
+      <c r="K85" s="19">
         <v>0</v>
       </c>
       <c r="L85" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M85" s="19">
         <v>0</v>
       </c>
-      <c r="N85" s="21">
+      <c r="N85" s="20">
         <v>100000</v>
       </c>
-      <c r="O85" s="22">
+      <c r="O85" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -5706,23 +5703,23 @@
         <f t="shared" si="10"/>
         <v>20070010</v>
       </c>
-      <c r="B86" s="18">
+      <c r="B86" s="16">
         <v>200700</v>
       </c>
-      <c r="C86" s="18">
-        <v>2</v>
-      </c>
-      <c r="D86" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="E86" s="18">
+      <c r="C86" s="16">
+        <v>2</v>
+      </c>
+      <c r="D86" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="E86" s="16">
         <v>200700001</v>
       </c>
-      <c r="F86" s="18" t="s">
-        <v>66</v>
+      <c r="F86" s="16" t="s">
+        <v>67</v>
       </c>
       <c r="G86" s="19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H86" s="19">
         <v>10</v>
@@ -5733,19 +5730,19 @@
       <c r="J86" s="19">
         <v>-1</v>
       </c>
-      <c r="K86" s="20">
+      <c r="K86" s="19">
         <v>0</v>
       </c>
       <c r="L86" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M86" s="19">
         <v>0</v>
       </c>
-      <c r="N86" s="21">
+      <c r="N86" s="20">
         <v>200</v>
       </c>
-      <c r="O86" s="22">
+      <c r="O86" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -5754,24 +5751,24 @@
         <f t="shared" si="10"/>
         <v>20070011</v>
       </c>
-      <c r="B87" s="18">
+      <c r="B87" s="16">
         <v>200700</v>
       </c>
-      <c r="C87" s="18">
-        <v>2</v>
-      </c>
-      <c r="D87" s="24" t="str">
+      <c r="C87" s="16">
+        <v>2</v>
+      </c>
+      <c r="D87" s="16" t="str">
         <f>D86</f>
         <v>越南色碟</v>
       </c>
-      <c r="E87" s="18">
+      <c r="E87" s="16">
         <v>200700001</v>
       </c>
-      <c r="F87" s="18" t="s">
-        <v>66</v>
+      <c r="F87" s="16" t="s">
+        <v>67</v>
       </c>
       <c r="G87" s="19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H87" s="19">
         <v>11</v>
@@ -5782,19 +5779,19 @@
       <c r="J87" s="19">
         <v>-1</v>
       </c>
-      <c r="K87" s="20">
+      <c r="K87" s="19">
         <v>0</v>
       </c>
       <c r="L87" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M87" s="19">
         <v>0</v>
       </c>
-      <c r="N87" s="21">
+      <c r="N87" s="20">
         <v>5000</v>
       </c>
-      <c r="O87" s="22">
+      <c r="O87" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -5803,24 +5800,24 @@
         <f t="shared" si="10"/>
         <v>20070012</v>
       </c>
-      <c r="B88" s="18">
+      <c r="B88" s="16">
         <v>200700</v>
       </c>
-      <c r="C88" s="18">
-        <v>2</v>
-      </c>
-      <c r="D88" s="24" t="str">
+      <c r="C88" s="16">
+        <v>2</v>
+      </c>
+      <c r="D88" s="16" t="str">
         <f>D87</f>
         <v>越南色碟</v>
       </c>
-      <c r="E88" s="18">
+      <c r="E88" s="16">
         <v>200700001</v>
       </c>
-      <c r="F88" s="18" t="s">
-        <v>66</v>
+      <c r="F88" s="16" t="s">
+        <v>67</v>
       </c>
       <c r="G88" s="19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H88" s="19">
         <v>12</v>
@@ -5831,19 +5828,19 @@
       <c r="J88" s="19">
         <v>-1</v>
       </c>
-      <c r="K88" s="20">
+      <c r="K88" s="19">
         <v>0</v>
       </c>
       <c r="L88" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M88" s="19">
         <v>0</v>
       </c>
-      <c r="N88" s="21">
+      <c r="N88" s="20">
         <v>100000</v>
       </c>
-      <c r="O88" s="22">
+      <c r="O88" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -5852,23 +5849,23 @@
         <f t="shared" si="10"/>
         <v>20080010</v>
       </c>
-      <c r="B89" s="18">
+      <c r="B89" s="16">
         <v>200800</v>
       </c>
-      <c r="C89" s="18">
-        <v>2</v>
-      </c>
-      <c r="D89" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="E89" s="18">
+      <c r="C89" s="16">
+        <v>2</v>
+      </c>
+      <c r="D89" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="E89" s="16">
         <v>200800001</v>
       </c>
-      <c r="F89" s="18" t="s">
-        <v>68</v>
+      <c r="F89" s="16" t="s">
+        <v>69</v>
       </c>
       <c r="G89" s="19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H89" s="19">
         <v>10</v>
@@ -5879,19 +5876,19 @@
       <c r="J89" s="19">
         <v>-1</v>
       </c>
-      <c r="K89" s="20">
+      <c r="K89" s="19">
         <v>0</v>
       </c>
       <c r="L89" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M89" s="19">
         <v>0</v>
       </c>
-      <c r="N89" s="21">
+      <c r="N89" s="20">
         <v>200</v>
       </c>
-      <c r="O89" s="22">
+      <c r="O89" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -5900,23 +5897,23 @@
         <f t="shared" si="10"/>
         <v>20080011</v>
       </c>
-      <c r="B90" s="18">
+      <c r="B90" s="16">
         <v>200800</v>
       </c>
-      <c r="C90" s="18">
-        <v>2</v>
-      </c>
-      <c r="D90" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="E90" s="18">
+      <c r="C90" s="16">
+        <v>2</v>
+      </c>
+      <c r="D90" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="E90" s="16">
         <v>200800001</v>
       </c>
-      <c r="F90" s="18" t="s">
-        <v>68</v>
+      <c r="F90" s="16" t="s">
+        <v>69</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H90" s="19">
         <v>11</v>
@@ -5927,19 +5924,19 @@
       <c r="J90" s="19">
         <v>-1</v>
       </c>
-      <c r="K90" s="20">
+      <c r="K90" s="19">
         <v>0</v>
       </c>
       <c r="L90" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M90" s="19">
         <v>0</v>
       </c>
-      <c r="N90" s="21">
+      <c r="N90" s="20">
         <v>5000</v>
       </c>
-      <c r="O90" s="22">
+      <c r="O90" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -5948,23 +5945,23 @@
         <f t="shared" si="10"/>
         <v>20080012</v>
       </c>
-      <c r="B91" s="18">
+      <c r="B91" s="16">
         <v>200800</v>
       </c>
-      <c r="C91" s="18">
-        <v>2</v>
-      </c>
-      <c r="D91" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="E91" s="18">
+      <c r="C91" s="16">
+        <v>2</v>
+      </c>
+      <c r="D91" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="E91" s="16">
         <v>200800001</v>
       </c>
-      <c r="F91" s="18" t="s">
-        <v>68</v>
+      <c r="F91" s="16" t="s">
+        <v>69</v>
       </c>
       <c r="G91" s="19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H91" s="19">
         <v>12</v>
@@ -5975,19 +5972,19 @@
       <c r="J91" s="19">
         <v>-1</v>
       </c>
-      <c r="K91" s="20">
+      <c r="K91" s="19">
         <v>0</v>
       </c>
       <c r="L91" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M91" s="19">
         <v>0</v>
       </c>
-      <c r="N91" s="21">
+      <c r="N91" s="20">
         <v>100000</v>
       </c>
-      <c r="O91" s="22">
+      <c r="O91" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -5996,23 +5993,23 @@
         <f t="shared" si="10"/>
         <v>20090010</v>
       </c>
-      <c r="B92" s="18">
+      <c r="B92" s="16">
         <v>200900</v>
       </c>
-      <c r="C92" s="18">
-        <v>2</v>
-      </c>
-      <c r="D92" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="E92" s="18">
+      <c r="C92" s="16">
+        <v>2</v>
+      </c>
+      <c r="D92" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="E92" s="16">
         <v>200900001</v>
       </c>
-      <c r="F92" s="18" t="s">
-        <v>70</v>
+      <c r="F92" s="16" t="s">
+        <v>71</v>
       </c>
       <c r="G92" s="19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H92" s="19">
         <v>10</v>
@@ -6023,19 +6020,19 @@
       <c r="J92" s="19">
         <v>-1</v>
       </c>
-      <c r="K92" s="20">
+      <c r="K92" s="19">
         <v>0</v>
       </c>
       <c r="L92" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M92" s="19">
         <v>0</v>
       </c>
-      <c r="N92" s="21">
+      <c r="N92" s="20">
         <v>200</v>
       </c>
-      <c r="O92" s="22">
+      <c r="O92" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -6044,23 +6041,23 @@
         <f t="shared" si="10"/>
         <v>20090011</v>
       </c>
-      <c r="B93" s="18">
+      <c r="B93" s="16">
         <v>200900</v>
       </c>
-      <c r="C93" s="18">
-        <v>2</v>
-      </c>
-      <c r="D93" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="E93" s="18">
+      <c r="C93" s="16">
+        <v>2</v>
+      </c>
+      <c r="D93" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="E93" s="16">
         <v>200900001</v>
       </c>
-      <c r="F93" s="18" t="s">
-        <v>70</v>
+      <c r="F93" s="16" t="s">
+        <v>71</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H93" s="19">
         <v>11</v>
@@ -6071,19 +6068,19 @@
       <c r="J93" s="19">
         <v>-1</v>
       </c>
-      <c r="K93" s="20">
+      <c r="K93" s="19">
         <v>0</v>
       </c>
       <c r="L93" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M93" s="19">
         <v>0</v>
       </c>
-      <c r="N93" s="21">
+      <c r="N93" s="20">
         <v>5000</v>
       </c>
-      <c r="O93" s="22">
+      <c r="O93" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -6092,23 +6089,23 @@
         <f t="shared" si="10"/>
         <v>20090012</v>
       </c>
-      <c r="B94" s="18">
+      <c r="B94" s="16">
         <v>200900</v>
       </c>
-      <c r="C94" s="18">
-        <v>2</v>
-      </c>
-      <c r="D94" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="E94" s="18">
+      <c r="C94" s="16">
+        <v>2</v>
+      </c>
+      <c r="D94" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="E94" s="16">
         <v>200900001</v>
       </c>
-      <c r="F94" s="18" t="s">
-        <v>70</v>
+      <c r="F94" s="16" t="s">
+        <v>71</v>
       </c>
       <c r="G94" s="19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H94" s="19">
         <v>12</v>
@@ -6119,19 +6116,19 @@
       <c r="J94" s="19">
         <v>-1</v>
       </c>
-      <c r="K94" s="20">
+      <c r="K94" s="19">
         <v>0</v>
       </c>
       <c r="L94" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M94" s="19">
         <v>0</v>
       </c>
-      <c r="N94" s="21">
+      <c r="N94" s="20">
         <v>100000</v>
       </c>
-      <c r="O94" s="22">
+      <c r="O94" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -6140,23 +6137,23 @@
         <f t="shared" si="10"/>
         <v>30020010</v>
       </c>
-      <c r="B95" s="24">
+      <c r="B95" s="16">
         <v>300200</v>
       </c>
-      <c r="C95" s="24">
+      <c r="C95" s="16">
         <v>3</v>
       </c>
-      <c r="D95" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="E95" s="18">
+      <c r="D95" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="E95" s="16">
         <v>300200006</v>
       </c>
-      <c r="F95" s="18" t="s">
-        <v>77</v>
+      <c r="F95" s="16" t="s">
+        <v>78</v>
       </c>
       <c r="G95" s="19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H95" s="19">
         <v>10</v>
@@ -6164,22 +6161,22 @@
       <c r="I95" s="19">
         <v>0</v>
       </c>
-      <c r="J95" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K95" s="20">
-        <v>0</v>
-      </c>
-      <c r="L95" s="27" t="s">
-        <v>83</v>
+      <c r="J95" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K95" s="19">
+        <v>0</v>
+      </c>
+      <c r="L95" s="25" t="s">
+        <v>84</v>
       </c>
       <c r="M95" s="19">
         <v>0</v>
       </c>
-      <c r="N95" s="21">
+      <c r="N95" s="20">
         <v>200</v>
       </c>
-      <c r="O95" s="22">
+      <c r="O95" s="21">
         <v>1980000</v>
       </c>
       <c r="S95" s="3"/>
@@ -6189,23 +6186,23 @@
         <f t="shared" si="10"/>
         <v>30020011</v>
       </c>
-      <c r="B96" s="24">
+      <c r="B96" s="16">
         <v>300200</v>
       </c>
-      <c r="C96" s="24">
+      <c r="C96" s="16">
         <v>3</v>
       </c>
-      <c r="D96" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="E96" s="18">
+      <c r="D96" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="E96" s="16">
         <v>300200006</v>
       </c>
-      <c r="F96" s="18" t="s">
-        <v>77</v>
+      <c r="F96" s="16" t="s">
+        <v>78</v>
       </c>
       <c r="G96" s="19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H96" s="19">
         <v>11</v>
@@ -6213,22 +6210,22 @@
       <c r="I96" s="19">
         <v>0</v>
       </c>
-      <c r="J96" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K96" s="20">
-        <v>0</v>
-      </c>
-      <c r="L96" s="27" t="s">
-        <v>83</v>
+      <c r="J96" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K96" s="19">
+        <v>0</v>
+      </c>
+      <c r="L96" s="25" t="s">
+        <v>84</v>
       </c>
       <c r="M96" s="19">
         <v>0</v>
       </c>
-      <c r="N96" s="21">
+      <c r="N96" s="20">
         <v>5000</v>
       </c>
-      <c r="O96" s="22">
+      <c r="O96" s="21">
         <v>1980000</v>
       </c>
       <c r="S96" s="3"/>
@@ -6238,23 +6235,23 @@
         <f t="shared" si="10"/>
         <v>30020012</v>
       </c>
-      <c r="B97" s="24">
+      <c r="B97" s="16">
         <v>300200</v>
       </c>
-      <c r="C97" s="24">
+      <c r="C97" s="16">
         <v>3</v>
       </c>
-      <c r="D97" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="E97" s="18">
+      <c r="D97" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="E97" s="16">
         <v>300200006</v>
       </c>
-      <c r="F97" s="18" t="s">
-        <v>77</v>
+      <c r="F97" s="16" t="s">
+        <v>78</v>
       </c>
       <c r="G97" s="19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H97" s="19">
         <v>12</v>
@@ -6262,22 +6259,22 @@
       <c r="I97" s="19">
         <v>0</v>
       </c>
-      <c r="J97" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K97" s="20">
-        <v>0</v>
-      </c>
-      <c r="L97" s="27" t="s">
-        <v>83</v>
+      <c r="J97" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K97" s="19">
+        <v>0</v>
+      </c>
+      <c r="L97" s="25" t="s">
+        <v>84</v>
       </c>
       <c r="M97" s="19">
         <v>0</v>
       </c>
-      <c r="N97" s="21">
+      <c r="N97" s="20">
         <v>100000</v>
       </c>
-      <c r="O97" s="22">
+      <c r="O97" s="21">
         <v>1980000</v>
       </c>
       <c r="S97" s="3"/>
@@ -6287,23 +6284,23 @@
         <f t="shared" ref="A98:A124" si="11">B98*10+H98</f>
         <v>1001010</v>
       </c>
-      <c r="B98" s="24">
+      <c r="B98" s="16">
         <v>100100</v>
       </c>
-      <c r="C98" s="24">
+      <c r="C98" s="16">
         <v>1</v>
       </c>
-      <c r="D98" s="24" t="s">
+      <c r="D98" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="E98" s="18">
+      <c r="E98" s="16">
         <v>100100026</v>
       </c>
-      <c r="F98" s="18" t="s">
+      <c r="F98" s="16" t="s">
         <v>31</v>
       </c>
       <c r="G98" s="19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H98" s="19">
         <v>10</v>
@@ -6311,22 +6308,22 @@
       <c r="I98" s="19">
         <v>0</v>
       </c>
-      <c r="J98" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K98" s="20">
-        <v>0</v>
-      </c>
-      <c r="L98" s="20" t="s">
-        <v>80</v>
+      <c r="J98" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K98" s="19">
+        <v>0</v>
+      </c>
+      <c r="L98" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="M98" s="19">
         <v>0</v>
       </c>
-      <c r="N98" s="21">
+      <c r="N98" s="20">
         <v>50</v>
       </c>
-      <c r="O98" s="22">
+      <c r="O98" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -6335,24 +6332,24 @@
         <f t="shared" si="11"/>
         <v>1001011</v>
       </c>
-      <c r="B99" s="24">
+      <c r="B99" s="16">
         <v>100100</v>
       </c>
-      <c r="C99" s="24">
+      <c r="C99" s="16">
         <v>1</v>
       </c>
-      <c r="D99" s="24" t="str">
+      <c r="D99" s="16" t="str">
         <f t="shared" ref="D99:D103" si="12">D98</f>
         <v>金礦大亨</v>
       </c>
-      <c r="E99" s="18">
+      <c r="E99" s="16">
         <v>100100026</v>
       </c>
-      <c r="F99" s="18" t="s">
+      <c r="F99" s="16" t="s">
         <v>31</v>
       </c>
       <c r="G99" s="19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H99" s="19">
         <v>11</v>
@@ -6360,22 +6357,22 @@
       <c r="I99" s="19">
         <v>0</v>
       </c>
-      <c r="J99" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K99" s="20">
-        <v>0</v>
-      </c>
-      <c r="L99" s="20" t="s">
-        <v>80</v>
+      <c r="J99" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K99" s="19">
+        <v>0</v>
+      </c>
+      <c r="L99" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="M99" s="19">
         <v>0</v>
       </c>
-      <c r="N99" s="21">
+      <c r="N99" s="20">
         <v>500</v>
       </c>
-      <c r="O99" s="22">
+      <c r="O99" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -6384,24 +6381,24 @@
         <f t="shared" si="11"/>
         <v>1001012</v>
       </c>
-      <c r="B100" s="24">
+      <c r="B100" s="16">
         <v>100100</v>
       </c>
-      <c r="C100" s="24">
+      <c r="C100" s="16">
         <v>1</v>
       </c>
-      <c r="D100" s="24" t="str">
+      <c r="D100" s="16" t="str">
         <f t="shared" si="12"/>
         <v>金礦大亨</v>
       </c>
-      <c r="E100" s="18">
+      <c r="E100" s="16">
         <v>100100026</v>
       </c>
-      <c r="F100" s="18" t="s">
+      <c r="F100" s="16" t="s">
         <v>31</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H100" s="19">
         <v>12</v>
@@ -6409,22 +6406,22 @@
       <c r="I100" s="19">
         <v>0</v>
       </c>
-      <c r="J100" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K100" s="20">
-        <v>0</v>
-      </c>
-      <c r="L100" s="20" t="s">
-        <v>80</v>
+      <c r="J100" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K100" s="19">
+        <v>0</v>
+      </c>
+      <c r="L100" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="M100" s="19">
         <v>0</v>
       </c>
-      <c r="N100" s="21">
+      <c r="N100" s="20">
         <v>5000</v>
       </c>
-      <c r="O100" s="22">
+      <c r="O100" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -6433,23 +6430,23 @@
         <f t="shared" si="11"/>
         <v>1003010</v>
       </c>
-      <c r="B101" s="24">
+      <c r="B101" s="16">
         <v>100300</v>
       </c>
-      <c r="C101" s="24">
+      <c r="C101" s="16">
         <v>1</v>
       </c>
-      <c r="D101" s="24" t="s">
+      <c r="D101" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="E101" s="18">
+      <c r="E101" s="16">
         <v>100300001</v>
       </c>
-      <c r="F101" s="18" t="s">
+      <c r="F101" s="16" t="s">
         <v>38</v>
       </c>
       <c r="G101" s="19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H101" s="19">
         <v>10</v>
@@ -6457,22 +6454,22 @@
       <c r="I101" s="19">
         <v>0</v>
       </c>
-      <c r="J101" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K101" s="20">
-        <v>0</v>
-      </c>
-      <c r="L101" s="20" t="s">
-        <v>80</v>
+      <c r="J101" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K101" s="19">
+        <v>0</v>
+      </c>
+      <c r="L101" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="M101" s="19">
         <v>0</v>
       </c>
-      <c r="N101" s="21">
+      <c r="N101" s="20">
         <v>50</v>
       </c>
-      <c r="O101" s="22">
+      <c r="O101" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -6481,25 +6478,25 @@
         <f t="shared" si="11"/>
         <v>1003011</v>
       </c>
-      <c r="B102" s="24">
+      <c r="B102" s="16">
         <v>100300</v>
       </c>
-      <c r="C102" s="24">
+      <c r="C102" s="16">
         <v>1</v>
       </c>
-      <c r="D102" s="24" t="str">
+      <c r="D102" s="16" t="str">
         <f t="shared" si="12"/>
         <v>超级明星</v>
       </c>
-      <c r="E102" s="18">
+      <c r="E102" s="16">
         <v>100300001</v>
       </c>
-      <c r="F102" s="18" t="str">
+      <c r="F102" s="16" t="str">
         <f t="shared" ref="F102:F106" si="13">F101</f>
         <v>SuperStar</v>
       </c>
       <c r="G102" s="19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H102" s="19">
         <v>11</v>
@@ -6507,22 +6504,22 @@
       <c r="I102" s="19">
         <v>0</v>
       </c>
-      <c r="J102" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K102" s="20">
-        <v>0</v>
-      </c>
-      <c r="L102" s="20" t="s">
-        <v>80</v>
+      <c r="J102" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K102" s="19">
+        <v>0</v>
+      </c>
+      <c r="L102" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="M102" s="19">
         <v>0</v>
       </c>
-      <c r="N102" s="21">
+      <c r="N102" s="20">
         <v>500</v>
       </c>
-      <c r="O102" s="22">
+      <c r="O102" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -6531,25 +6528,25 @@
         <f t="shared" si="11"/>
         <v>1003012</v>
       </c>
-      <c r="B103" s="24">
+      <c r="B103" s="16">
         <v>100300</v>
       </c>
-      <c r="C103" s="24">
+      <c r="C103" s="16">
         <v>1</v>
       </c>
-      <c r="D103" s="24" t="str">
+      <c r="D103" s="16" t="str">
         <f t="shared" si="12"/>
         <v>超级明星</v>
       </c>
-      <c r="E103" s="18">
+      <c r="E103" s="16">
         <v>100300001</v>
       </c>
-      <c r="F103" s="18" t="str">
+      <c r="F103" s="16" t="str">
         <f t="shared" si="13"/>
         <v>SuperStar</v>
       </c>
       <c r="G103" s="19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H103" s="19">
         <v>12</v>
@@ -6557,22 +6554,22 @@
       <c r="I103" s="19">
         <v>0</v>
       </c>
-      <c r="J103" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K103" s="20">
-        <v>0</v>
-      </c>
-      <c r="L103" s="20" t="s">
-        <v>80</v>
+      <c r="J103" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K103" s="19">
+        <v>0</v>
+      </c>
+      <c r="L103" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="M103" s="19">
         <v>0</v>
       </c>
-      <c r="N103" s="21">
+      <c r="N103" s="20">
         <v>5000</v>
       </c>
-      <c r="O103" s="22">
+      <c r="O103" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -6581,23 +6578,23 @@
         <f t="shared" si="11"/>
         <v>1007010</v>
       </c>
-      <c r="B104" s="24">
+      <c r="B104" s="16">
         <v>100700</v>
       </c>
-      <c r="C104" s="24">
+      <c r="C104" s="16">
         <v>1</v>
       </c>
-      <c r="D104" s="24" t="s">
+      <c r="D104" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E104" s="18">
+      <c r="E104" s="16">
         <v>100700001</v>
       </c>
-      <c r="F104" s="18" t="s">
+      <c r="F104" s="16" t="s">
         <v>40</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H104" s="19">
         <v>10</v>
@@ -6605,22 +6602,22 @@
       <c r="I104" s="19">
         <v>0</v>
       </c>
-      <c r="J104" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K104" s="20">
-        <v>0</v>
-      </c>
-      <c r="L104" s="20" t="s">
-        <v>80</v>
+      <c r="J104" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K104" s="19">
+        <v>0</v>
+      </c>
+      <c r="L104" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="M104" s="19">
         <v>0</v>
       </c>
-      <c r="N104" s="21">
+      <c r="N104" s="20">
         <v>50</v>
       </c>
-      <c r="O104" s="22">
+      <c r="O104" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -6629,25 +6626,25 @@
         <f t="shared" si="11"/>
         <v>1007011</v>
       </c>
-      <c r="B105" s="24">
+      <c r="B105" s="16">
         <v>100700</v>
       </c>
-      <c r="C105" s="24">
+      <c r="C105" s="16">
         <v>1</v>
       </c>
-      <c r="D105" s="24" t="str">
+      <c r="D105" s="16" t="str">
         <f t="shared" ref="D105:D109" si="14">D104</f>
         <v>麻将胡了</v>
       </c>
-      <c r="E105" s="18">
+      <c r="E105" s="16">
         <v>100700001</v>
       </c>
-      <c r="F105" s="18" t="str">
+      <c r="F105" s="16" t="str">
         <f t="shared" si="13"/>
         <v>MahjongWays</v>
       </c>
       <c r="G105" s="19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H105" s="19">
         <v>11</v>
@@ -6655,22 +6652,22 @@
       <c r="I105" s="19">
         <v>0</v>
       </c>
-      <c r="J105" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K105" s="20">
-        <v>0</v>
-      </c>
-      <c r="L105" s="20" t="s">
-        <v>80</v>
+      <c r="J105" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K105" s="19">
+        <v>0</v>
+      </c>
+      <c r="L105" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="M105" s="19">
         <v>0</v>
       </c>
-      <c r="N105" s="21">
+      <c r="N105" s="20">
         <v>500</v>
       </c>
-      <c r="O105" s="22">
+      <c r="O105" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -6679,25 +6676,25 @@
         <f t="shared" si="11"/>
         <v>1007012</v>
       </c>
-      <c r="B106" s="24">
+      <c r="B106" s="16">
         <v>100700</v>
       </c>
-      <c r="C106" s="24">
+      <c r="C106" s="16">
         <v>1</v>
       </c>
-      <c r="D106" s="24" t="str">
+      <c r="D106" s="16" t="str">
         <f t="shared" si="14"/>
         <v>麻将胡了</v>
       </c>
-      <c r="E106" s="18">
+      <c r="E106" s="16">
         <v>100700001</v>
       </c>
-      <c r="F106" s="18" t="str">
+      <c r="F106" s="16" t="str">
         <f t="shared" si="13"/>
         <v>MahjongWays</v>
       </c>
       <c r="G106" s="19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H106" s="19">
         <v>12</v>
@@ -6705,22 +6702,22 @@
       <c r="I106" s="19">
         <v>0</v>
       </c>
-      <c r="J106" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K106" s="20">
-        <v>0</v>
-      </c>
-      <c r="L106" s="20" t="s">
-        <v>80</v>
+      <c r="J106" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K106" s="19">
+        <v>0</v>
+      </c>
+      <c r="L106" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="M106" s="19">
         <v>0</v>
       </c>
-      <c r="N106" s="21">
+      <c r="N106" s="20">
         <v>5000</v>
       </c>
-      <c r="O106" s="22">
+      <c r="O106" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -6729,23 +6726,23 @@
         <f t="shared" si="11"/>
         <v>1012010</v>
       </c>
-      <c r="B107" s="24">
+      <c r="B107" s="16">
         <v>101200</v>
       </c>
-      <c r="C107" s="24">
+      <c r="C107" s="16">
         <v>1</v>
       </c>
-      <c r="D107" s="24" t="s">
+      <c r="D107" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="E107" s="18">
+      <c r="E107" s="16">
         <v>101200001</v>
       </c>
-      <c r="F107" s="18" t="s">
+      <c r="F107" s="16" t="s">
         <v>42</v>
       </c>
       <c r="G107" s="19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H107" s="19">
         <v>10</v>
@@ -6753,22 +6750,22 @@
       <c r="I107" s="19">
         <v>0</v>
       </c>
-      <c r="J107" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K107" s="20">
-        <v>0</v>
-      </c>
-      <c r="L107" s="20" t="s">
-        <v>80</v>
+      <c r="J107" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K107" s="19">
+        <v>0</v>
+      </c>
+      <c r="L107" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="M107" s="19">
         <v>0</v>
       </c>
-      <c r="N107" s="21">
+      <c r="N107" s="20">
         <v>50</v>
       </c>
-      <c r="O107" s="22">
+      <c r="O107" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -6777,25 +6774,25 @@
         <f t="shared" si="11"/>
         <v>1012011</v>
       </c>
-      <c r="B108" s="24">
+      <c r="B108" s="16">
         <v>101200</v>
       </c>
-      <c r="C108" s="24">
+      <c r="C108" s="16">
         <v>1</v>
       </c>
-      <c r="D108" s="24" t="str">
+      <c r="D108" s="16" t="str">
         <f t="shared" si="14"/>
         <v>财神</v>
       </c>
-      <c r="E108" s="18">
+      <c r="E108" s="16">
         <v>101200001</v>
       </c>
-      <c r="F108" s="18" t="str">
+      <c r="F108" s="16" t="str">
         <f t="shared" ref="F108:F112" si="15">F107</f>
         <v>Godofwealth</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H108" s="19">
         <v>11</v>
@@ -6803,22 +6800,22 @@
       <c r="I108" s="19">
         <v>0</v>
       </c>
-      <c r="J108" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K108" s="20">
-        <v>0</v>
-      </c>
-      <c r="L108" s="20" t="s">
-        <v>80</v>
+      <c r="J108" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K108" s="19">
+        <v>0</v>
+      </c>
+      <c r="L108" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="M108" s="19">
         <v>0</v>
       </c>
-      <c r="N108" s="21">
+      <c r="N108" s="20">
         <v>500</v>
       </c>
-      <c r="O108" s="22">
+      <c r="O108" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -6827,25 +6824,25 @@
         <f t="shared" si="11"/>
         <v>1012012</v>
       </c>
-      <c r="B109" s="24">
+      <c r="B109" s="16">
         <v>101200</v>
       </c>
-      <c r="C109" s="24">
+      <c r="C109" s="16">
         <v>1</v>
       </c>
-      <c r="D109" s="24" t="str">
+      <c r="D109" s="16" t="str">
         <f t="shared" si="14"/>
         <v>财神</v>
       </c>
-      <c r="E109" s="18">
+      <c r="E109" s="16">
         <v>101200001</v>
       </c>
-      <c r="F109" s="18" t="str">
+      <c r="F109" s="16" t="str">
         <f t="shared" si="15"/>
         <v>Godofwealth</v>
       </c>
       <c r="G109" s="19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H109" s="19">
         <v>12</v>
@@ -6853,22 +6850,22 @@
       <c r="I109" s="19">
         <v>0</v>
       </c>
-      <c r="J109" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K109" s="20">
-        <v>0</v>
-      </c>
-      <c r="L109" s="20" t="s">
-        <v>80</v>
+      <c r="J109" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K109" s="19">
+        <v>0</v>
+      </c>
+      <c r="L109" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="M109" s="19">
         <v>0</v>
       </c>
-      <c r="N109" s="21">
+      <c r="N109" s="20">
         <v>5000</v>
       </c>
-      <c r="O109" s="22">
+      <c r="O109" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -6877,23 +6874,23 @@
         <f t="shared" si="11"/>
         <v>1014010</v>
       </c>
-      <c r="B110" s="24">
+      <c r="B110" s="16">
         <v>101400</v>
       </c>
-      <c r="C110" s="24">
+      <c r="C110" s="16">
         <v>1</v>
       </c>
-      <c r="D110" s="24" t="s">
+      <c r="D110" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="E110" s="18">
+      <c r="E110" s="16">
         <v>101400001</v>
       </c>
-      <c r="F110" s="18" t="s">
+      <c r="F110" s="16" t="s">
         <v>44</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H110" s="19">
         <v>10</v>
@@ -6901,22 +6898,22 @@
       <c r="I110" s="19">
         <v>0</v>
       </c>
-      <c r="J110" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K110" s="20">
-        <v>0</v>
-      </c>
-      <c r="L110" s="20" t="s">
-        <v>80</v>
+      <c r="J110" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K110" s="19">
+        <v>0</v>
+      </c>
+      <c r="L110" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="M110" s="19">
         <v>0</v>
       </c>
-      <c r="N110" s="21">
+      <c r="N110" s="20">
         <v>50</v>
       </c>
-      <c r="O110" s="22">
+      <c r="O110" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -6925,25 +6922,25 @@
         <f t="shared" si="11"/>
         <v>1014011</v>
       </c>
-      <c r="B111" s="24">
+      <c r="B111" s="16">
         <v>101400</v>
       </c>
-      <c r="C111" s="24">
+      <c r="C111" s="16">
         <v>1</v>
       </c>
-      <c r="D111" s="24" t="str">
+      <c r="D111" s="16" t="str">
         <f t="shared" ref="D111:D115" si="16">D110</f>
         <v>埃及艳后</v>
       </c>
-      <c r="E111" s="18">
+      <c r="E111" s="16">
         <v>101400001</v>
       </c>
-      <c r="F111" s="18" t="str">
+      <c r="F111" s="16" t="str">
         <f t="shared" si="15"/>
         <v>Cleopatra</v>
       </c>
       <c r="G111" s="19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H111" s="19">
         <v>11</v>
@@ -6951,22 +6948,22 @@
       <c r="I111" s="19">
         <v>0</v>
       </c>
-      <c r="J111" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K111" s="20">
-        <v>0</v>
-      </c>
-      <c r="L111" s="20" t="s">
-        <v>80</v>
+      <c r="J111" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K111" s="19">
+        <v>0</v>
+      </c>
+      <c r="L111" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="M111" s="19">
         <v>0</v>
       </c>
-      <c r="N111" s="21">
+      <c r="N111" s="20">
         <v>500</v>
       </c>
-      <c r="O111" s="22">
+      <c r="O111" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -6975,25 +6972,25 @@
         <f t="shared" si="11"/>
         <v>1014012</v>
       </c>
-      <c r="B112" s="24">
+      <c r="B112" s="16">
         <v>101400</v>
       </c>
-      <c r="C112" s="24">
+      <c r="C112" s="16">
         <v>1</v>
       </c>
-      <c r="D112" s="24" t="str">
+      <c r="D112" s="16" t="str">
         <f t="shared" si="16"/>
         <v>埃及艳后</v>
       </c>
-      <c r="E112" s="18">
+      <c r="E112" s="16">
         <v>101400001</v>
       </c>
-      <c r="F112" s="18" t="str">
+      <c r="F112" s="16" t="str">
         <f t="shared" si="15"/>
         <v>Cleopatra</v>
       </c>
       <c r="G112" s="19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H112" s="19">
         <v>12</v>
@@ -7001,22 +6998,22 @@
       <c r="I112" s="19">
         <v>0</v>
       </c>
-      <c r="J112" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K112" s="20">
-        <v>0</v>
-      </c>
-      <c r="L112" s="20" t="s">
-        <v>80</v>
+      <c r="J112" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K112" s="19">
+        <v>0</v>
+      </c>
+      <c r="L112" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="M112" s="19">
         <v>0</v>
       </c>
-      <c r="N112" s="21">
+      <c r="N112" s="20">
         <v>5000</v>
       </c>
-      <c r="O112" s="22">
+      <c r="O112" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -7025,23 +7022,23 @@
         <f t="shared" si="11"/>
         <v>1024010</v>
       </c>
-      <c r="B113" s="24">
+      <c r="B113" s="16">
         <v>102400</v>
       </c>
-      <c r="C113" s="24">
+      <c r="C113" s="16">
         <v>1</v>
       </c>
-      <c r="D113" s="24" t="s">
+      <c r="D113" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="E113" s="18">
+      <c r="E113" s="16">
         <v>102400026</v>
       </c>
-      <c r="F113" s="18" t="s">
+      <c r="F113" s="16" t="s">
         <v>46</v>
       </c>
       <c r="G113" s="19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H113" s="19">
         <v>10</v>
@@ -7049,22 +7046,22 @@
       <c r="I113" s="19">
         <v>0</v>
       </c>
-      <c r="J113" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K113" s="20">
-        <v>0</v>
-      </c>
-      <c r="L113" s="20" t="s">
-        <v>80</v>
+      <c r="J113" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K113" s="19">
+        <v>0</v>
+      </c>
+      <c r="L113" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="M113" s="19">
         <v>0</v>
       </c>
-      <c r="N113" s="21">
+      <c r="N113" s="20">
         <v>50</v>
       </c>
-      <c r="O113" s="22">
+      <c r="O113" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -7073,24 +7070,24 @@
         <f t="shared" si="11"/>
         <v>1024011</v>
       </c>
-      <c r="B114" s="24">
+      <c r="B114" s="16">
         <v>102400</v>
       </c>
-      <c r="C114" s="24">
+      <c r="C114" s="16">
         <v>1</v>
       </c>
-      <c r="D114" s="24" t="str">
+      <c r="D114" s="16" t="str">
         <f t="shared" si="16"/>
         <v>财富银行</v>
       </c>
-      <c r="E114" s="18">
+      <c r="E114" s="16">
         <v>102400026</v>
       </c>
-      <c r="F114" s="18" t="s">
+      <c r="F114" s="16" t="s">
         <v>46</v>
       </c>
       <c r="G114" s="19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H114" s="19">
         <v>11</v>
@@ -7098,22 +7095,22 @@
       <c r="I114" s="19">
         <v>0</v>
       </c>
-      <c r="J114" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K114" s="20">
-        <v>0</v>
-      </c>
-      <c r="L114" s="20" t="s">
-        <v>80</v>
+      <c r="J114" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K114" s="19">
+        <v>0</v>
+      </c>
+      <c r="L114" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="M114" s="19">
         <v>0</v>
       </c>
-      <c r="N114" s="21">
+      <c r="N114" s="20">
         <v>500</v>
       </c>
-      <c r="O114" s="22">
+      <c r="O114" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -7122,24 +7119,24 @@
         <f t="shared" si="11"/>
         <v>1024012</v>
       </c>
-      <c r="B115" s="24">
+      <c r="B115" s="16">
         <v>102400</v>
       </c>
-      <c r="C115" s="24">
+      <c r="C115" s="16">
         <v>1</v>
       </c>
-      <c r="D115" s="24" t="str">
+      <c r="D115" s="16" t="str">
         <f t="shared" si="16"/>
         <v>财富银行</v>
       </c>
-      <c r="E115" s="18">
+      <c r="E115" s="16">
         <v>102400026</v>
       </c>
-      <c r="F115" s="18" t="s">
+      <c r="F115" s="16" t="s">
         <v>46</v>
       </c>
       <c r="G115" s="19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H115" s="19">
         <v>12</v>
@@ -7147,22 +7144,22 @@
       <c r="I115" s="19">
         <v>0</v>
       </c>
-      <c r="J115" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K115" s="20">
-        <v>0</v>
-      </c>
-      <c r="L115" s="20" t="s">
-        <v>80</v>
+      <c r="J115" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K115" s="19">
+        <v>0</v>
+      </c>
+      <c r="L115" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="M115" s="19">
         <v>0</v>
       </c>
-      <c r="N115" s="21">
+      <c r="N115" s="20">
         <v>5000</v>
       </c>
-      <c r="O115" s="22">
+      <c r="O115" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -7171,23 +7168,23 @@
         <f t="shared" si="11"/>
         <v>1022010</v>
       </c>
-      <c r="B116" s="24">
+      <c r="B116" s="16">
         <v>102200</v>
       </c>
-      <c r="C116" s="24">
+      <c r="C116" s="16">
         <v>1</v>
       </c>
-      <c r="D116" s="24" t="s">
+      <c r="D116" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="E116" s="18">
+      <c r="E116" s="16">
         <v>102200001</v>
       </c>
-      <c r="F116" s="18" t="s">
+      <c r="F116" s="16" t="s">
         <v>48</v>
       </c>
       <c r="G116" s="19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H116" s="19">
         <v>10</v>
@@ -7195,22 +7192,22 @@
       <c r="I116" s="19">
         <v>0</v>
       </c>
-      <c r="J116" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K116" s="20">
-        <v>0</v>
-      </c>
-      <c r="L116" s="20" t="s">
-        <v>80</v>
+      <c r="J116" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K116" s="19">
+        <v>0</v>
+      </c>
+      <c r="L116" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="M116" s="19">
         <v>0</v>
       </c>
-      <c r="N116" s="21">
+      <c r="N116" s="20">
         <v>50</v>
       </c>
-      <c r="O116" s="22">
+      <c r="O116" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -7219,23 +7216,23 @@
         <f t="shared" si="11"/>
         <v>1022011</v>
       </c>
-      <c r="B117" s="24">
+      <c r="B117" s="16">
         <v>102200</v>
       </c>
-      <c r="C117" s="24">
+      <c r="C117" s="16">
         <v>1</v>
       </c>
-      <c r="D117" s="24" t="s">
+      <c r="D117" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="E117" s="18">
+      <c r="E117" s="16">
         <v>102200001</v>
       </c>
-      <c r="F117" s="18" t="s">
+      <c r="F117" s="16" t="s">
         <v>48</v>
       </c>
       <c r="G117" s="19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H117" s="19">
         <v>11</v>
@@ -7243,22 +7240,22 @@
       <c r="I117" s="19">
         <v>0</v>
       </c>
-      <c r="J117" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K117" s="20">
-        <v>0</v>
-      </c>
-      <c r="L117" s="20" t="s">
-        <v>80</v>
+      <c r="J117" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K117" s="19">
+        <v>0</v>
+      </c>
+      <c r="L117" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="M117" s="19">
         <v>0</v>
       </c>
-      <c r="N117" s="21">
+      <c r="N117" s="20">
         <v>500</v>
       </c>
-      <c r="O117" s="22">
+      <c r="O117" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -7267,23 +7264,23 @@
         <f t="shared" si="11"/>
         <v>1022012</v>
       </c>
-      <c r="B118" s="24">
+      <c r="B118" s="16">
         <v>102200</v>
       </c>
-      <c r="C118" s="24">
+      <c r="C118" s="16">
         <v>1</v>
       </c>
-      <c r="D118" s="24" t="s">
+      <c r="D118" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="E118" s="18">
+      <c r="E118" s="16">
         <v>102200001</v>
       </c>
-      <c r="F118" s="18" t="s">
+      <c r="F118" s="16" t="s">
         <v>48</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H118" s="19">
         <v>12</v>
@@ -7291,22 +7288,22 @@
       <c r="I118" s="19">
         <v>0</v>
       </c>
-      <c r="J118" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K118" s="20">
-        <v>0</v>
-      </c>
-      <c r="L118" s="20" t="s">
-        <v>80</v>
+      <c r="J118" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K118" s="19">
+        <v>0</v>
+      </c>
+      <c r="L118" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="M118" s="19">
         <v>0</v>
       </c>
-      <c r="N118" s="21">
+      <c r="N118" s="20">
         <v>5000</v>
       </c>
-      <c r="O118" s="22">
+      <c r="O118" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -7315,23 +7312,23 @@
         <f t="shared" si="11"/>
         <v>1017010</v>
       </c>
-      <c r="B119" s="24">
+      <c r="B119" s="16">
         <v>101700</v>
       </c>
-      <c r="C119" s="24">
+      <c r="C119" s="16">
         <v>1</v>
       </c>
-      <c r="D119" s="24" t="s">
+      <c r="D119" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="E119" s="18">
+      <c r="E119" s="16">
         <v>101700001</v>
       </c>
-      <c r="F119" s="18" t="s">
+      <c r="F119" s="16" t="s">
         <v>50</v>
       </c>
       <c r="G119" s="19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H119" s="19">
         <v>10</v>
@@ -7339,22 +7336,22 @@
       <c r="I119" s="19">
         <v>0</v>
       </c>
-      <c r="J119" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K119" s="20">
-        <v>0</v>
-      </c>
-      <c r="L119" s="20" t="s">
-        <v>80</v>
+      <c r="J119" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K119" s="19">
+        <v>0</v>
+      </c>
+      <c r="L119" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="M119" s="19">
         <v>0</v>
       </c>
-      <c r="N119" s="21">
+      <c r="N119" s="20">
         <v>50</v>
       </c>
-      <c r="O119" s="22">
+      <c r="O119" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -7363,23 +7360,23 @@
         <f t="shared" si="11"/>
         <v>1017011</v>
       </c>
-      <c r="B120" s="24">
+      <c r="B120" s="16">
         <v>101700</v>
       </c>
-      <c r="C120" s="24">
+      <c r="C120" s="16">
         <v>1</v>
       </c>
-      <c r="D120" s="24" t="s">
+      <c r="D120" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="E120" s="18">
+      <c r="E120" s="16">
         <v>101700001</v>
       </c>
-      <c r="F120" s="18" t="s">
+      <c r="F120" s="16" t="s">
         <v>50</v>
       </c>
       <c r="G120" s="19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H120" s="19">
         <v>11</v>
@@ -7387,22 +7384,22 @@
       <c r="I120" s="19">
         <v>0</v>
       </c>
-      <c r="J120" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K120" s="20">
-        <v>0</v>
-      </c>
-      <c r="L120" s="20" t="s">
-        <v>80</v>
+      <c r="J120" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K120" s="19">
+        <v>0</v>
+      </c>
+      <c r="L120" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="M120" s="19">
         <v>0</v>
       </c>
-      <c r="N120" s="21">
+      <c r="N120" s="20">
         <v>500</v>
       </c>
-      <c r="O120" s="22">
+      <c r="O120" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -7411,23 +7408,23 @@
         <f t="shared" si="11"/>
         <v>1017012</v>
       </c>
-      <c r="B121" s="24">
+      <c r="B121" s="16">
         <v>101700</v>
       </c>
-      <c r="C121" s="24">
+      <c r="C121" s="16">
         <v>1</v>
       </c>
-      <c r="D121" s="24" t="s">
+      <c r="D121" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="E121" s="18">
+      <c r="E121" s="16">
         <v>101700001</v>
       </c>
-      <c r="F121" s="18" t="s">
+      <c r="F121" s="16" t="s">
         <v>50</v>
       </c>
       <c r="G121" s="19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H121" s="19">
         <v>12</v>
@@ -7435,22 +7432,22 @@
       <c r="I121" s="19">
         <v>0</v>
       </c>
-      <c r="J121" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K121" s="20">
-        <v>0</v>
-      </c>
-      <c r="L121" s="20" t="s">
-        <v>80</v>
+      <c r="J121" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K121" s="19">
+        <v>0</v>
+      </c>
+      <c r="L121" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="M121" s="19">
         <v>0</v>
       </c>
-      <c r="N121" s="21">
+      <c r="N121" s="20">
         <v>5000</v>
       </c>
-      <c r="O121" s="22">
+      <c r="O121" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -7459,21 +7456,23 @@
         <f t="shared" si="11"/>
         <v>1021010</v>
       </c>
-      <c r="B122" s="24">
+      <c r="B122" s="16">
         <v>102100</v>
       </c>
-      <c r="C122" s="24">
+      <c r="C122" s="16">
         <v>1</v>
       </c>
-      <c r="D122" s="24" t="s">
+      <c r="D122" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="E122" s="18">
+      <c r="E122" s="16">
         <v>102100001</v>
       </c>
-      <c r="F122" s="18"/>
+      <c r="F122" s="16" t="s">
+        <v>52</v>
+      </c>
       <c r="G122" s="19" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H122" s="19">
         <v>10</v>
@@ -7481,22 +7480,22 @@
       <c r="I122" s="19">
         <v>0</v>
       </c>
-      <c r="J122" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K122" s="20">
-        <v>0</v>
-      </c>
-      <c r="L122" s="20" t="s">
-        <v>80</v>
+      <c r="J122" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K122" s="19">
+        <v>0</v>
+      </c>
+      <c r="L122" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="M122" s="19">
         <v>0</v>
       </c>
-      <c r="N122" s="21">
+      <c r="N122" s="20">
         <v>50</v>
       </c>
-      <c r="O122" s="22">
+      <c r="O122" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -7505,21 +7504,23 @@
         <f t="shared" si="11"/>
         <v>1021011</v>
       </c>
-      <c r="B123" s="24">
+      <c r="B123" s="16">
         <v>102100</v>
       </c>
-      <c r="C123" s="24">
+      <c r="C123" s="16">
         <v>1</v>
       </c>
-      <c r="D123" s="24" t="s">
+      <c r="D123" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="E123" s="18">
+      <c r="E123" s="16">
         <v>102100001</v>
       </c>
-      <c r="F123" s="18"/>
+      <c r="F123" s="16" t="s">
+        <v>52</v>
+      </c>
       <c r="G123" s="19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H123" s="19">
         <v>11</v>
@@ -7527,22 +7528,22 @@
       <c r="I123" s="19">
         <v>0</v>
       </c>
-      <c r="J123" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K123" s="20">
-        <v>0</v>
-      </c>
-      <c r="L123" s="20" t="s">
-        <v>80</v>
+      <c r="J123" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K123" s="19">
+        <v>0</v>
+      </c>
+      <c r="L123" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="M123" s="19">
         <v>0</v>
       </c>
-      <c r="N123" s="21">
+      <c r="N123" s="20">
         <v>500</v>
       </c>
-      <c r="O123" s="22">
+      <c r="O123" s="21">
         <v>1980000</v>
       </c>
     </row>
@@ -7551,21 +7552,23 @@
         <f t="shared" si="11"/>
         <v>1021012</v>
       </c>
-      <c r="B124" s="24">
+      <c r="B124" s="16">
         <v>102100</v>
       </c>
-      <c r="C124" s="24">
+      <c r="C124" s="16">
         <v>1</v>
       </c>
-      <c r="D124" s="24" t="s">
+      <c r="D124" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="E124" s="18">
+      <c r="E124" s="16">
         <v>102100001</v>
       </c>
-      <c r="F124" s="18"/>
+      <c r="F124" s="16" t="s">
+        <v>52</v>
+      </c>
       <c r="G124" s="19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H124" s="19">
         <v>12</v>
@@ -7573,22 +7576,22 @@
       <c r="I124" s="19">
         <v>0</v>
       </c>
-      <c r="J124" s="20">
-        <v>-1</v>
-      </c>
-      <c r="K124" s="20">
-        <v>0</v>
-      </c>
-      <c r="L124" s="20" t="s">
-        <v>80</v>
+      <c r="J124" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K124" s="19">
+        <v>0</v>
+      </c>
+      <c r="L124" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="M124" s="19">
         <v>0</v>
       </c>
-      <c r="N124" s="21">
+      <c r="N124" s="20">
         <v>5000</v>
       </c>
-      <c r="O124" s="22">
+      <c r="O124" s="21">
         <v>1980000</v>
       </c>
     </row>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="794"/>
+    <workbookView windowWidth="27945" windowHeight="11925" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Warehouse" sheetId="42" r:id="rId1"/>
@@ -156,7 +156,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="112">
   <si>
     <t>sid</t>
   </si>
@@ -411,6 +411,87 @@
   </si>
   <si>
     <t>9:999</t>
+  </si>
+  <si>
+    <t>10010010</t>
+  </si>
+  <si>
+    <t>10010011</t>
+  </si>
+  <si>
+    <t>10010012</t>
+  </si>
+  <si>
+    <t>10030010</t>
+  </si>
+  <si>
+    <t>10030011</t>
+  </si>
+  <si>
+    <t>10030012</t>
+  </si>
+  <si>
+    <t>10070010</t>
+  </si>
+  <si>
+    <t>10070011</t>
+  </si>
+  <si>
+    <t>10070012</t>
+  </si>
+  <si>
+    <t>10120010</t>
+  </si>
+  <si>
+    <t>10120011</t>
+  </si>
+  <si>
+    <t>10120012</t>
+  </si>
+  <si>
+    <t>10140010</t>
+  </si>
+  <si>
+    <t>10140011</t>
+  </si>
+  <si>
+    <t>10140012</t>
+  </si>
+  <si>
+    <t>10240010</t>
+  </si>
+  <si>
+    <t>10240011</t>
+  </si>
+  <si>
+    <t>10240012</t>
+  </si>
+  <si>
+    <t>10220010</t>
+  </si>
+  <si>
+    <t>10220011</t>
+  </si>
+  <si>
+    <t>10220012</t>
+  </si>
+  <si>
+    <t>10170010</t>
+  </si>
+  <si>
+    <t>10170011</t>
+  </si>
+  <si>
+    <t>10170012</t>
+  </si>
+  <si>
+    <t>10210010</t>
+  </si>
+  <si>
+    <t>10210011</t>
+  </si>
+  <si>
+    <t>10210012</t>
   </si>
 </sst>
 </file>
@@ -4821,7 +4902,6 @@
     </row>
     <row r="68" s="1" customFormat="1" spans="1:19">
       <c r="A68" s="1">
-        <f t="shared" ref="A68:A74" si="8">B68*100+H68</f>
         <v>20010010</v>
       </c>
       <c r="B68" s="16">
@@ -4870,7 +4950,6 @@
     </row>
     <row r="69" s="1" customFormat="1" spans="1:19">
       <c r="A69" s="1">
-        <f t="shared" si="8"/>
         <v>20010011</v>
       </c>
       <c r="B69" s="16">
@@ -4919,7 +4998,6 @@
     </row>
     <row r="70" s="1" customFormat="1" spans="1:19">
       <c r="A70" s="1">
-        <f t="shared" si="8"/>
         <v>20010012</v>
       </c>
       <c r="B70" s="16">
@@ -4968,7 +5046,6 @@
     </row>
     <row r="71" s="1" customFormat="1" spans="1:19">
       <c r="A71" s="1">
-        <f t="shared" si="8"/>
         <v>20010110</v>
       </c>
       <c r="B71" s="16">
@@ -5017,7 +5094,6 @@
     </row>
     <row r="72" s="1" customFormat="1" spans="1:19">
       <c r="A72" s="1">
-        <f t="shared" si="8"/>
         <v>20010111</v>
       </c>
       <c r="B72" s="16">
@@ -5066,7 +5142,6 @@
     </row>
     <row r="73" s="1" customFormat="1" spans="1:19">
       <c r="A73" s="1">
-        <f t="shared" si="8"/>
         <v>20010112</v>
       </c>
       <c r="B73" s="16">
@@ -5115,7 +5190,6 @@
     </row>
     <row r="74" s="1" customFormat="1" spans="1:19">
       <c r="A74" s="1">
-        <f t="shared" si="8"/>
         <v>20030010</v>
       </c>
       <c r="B74" s="16">
@@ -5164,7 +5238,6 @@
     </row>
     <row r="75" s="1" customFormat="1" spans="1:19">
       <c r="A75" s="1">
-        <f t="shared" ref="A75:A83" si="9">B75*100+H75</f>
         <v>20030011</v>
       </c>
       <c r="B75" s="16">
@@ -5213,7 +5286,6 @@
     </row>
     <row r="76" s="1" customFormat="1" spans="1:19">
       <c r="A76" s="1">
-        <f t="shared" si="9"/>
         <v>20030012</v>
       </c>
       <c r="B76" s="16">
@@ -5262,7 +5334,6 @@
     </row>
     <row r="77" s="1" customFormat="1" spans="1:19">
       <c r="A77" s="1">
-        <f t="shared" si="9"/>
         <v>20040010</v>
       </c>
       <c r="B77" s="16">
@@ -5311,7 +5382,6 @@
     </row>
     <row r="78" s="1" customFormat="1" spans="1:19">
       <c r="A78" s="1">
-        <f t="shared" si="9"/>
         <v>20040011</v>
       </c>
       <c r="B78" s="16">
@@ -5360,7 +5430,6 @@
     </row>
     <row r="79" s="1" customFormat="1" spans="1:19">
       <c r="A79" s="1">
-        <f t="shared" si="9"/>
         <v>20040012</v>
       </c>
       <c r="B79" s="16">
@@ -5409,7 +5478,6 @@
     </row>
     <row r="80" s="1" customFormat="1" spans="1:19">
       <c r="A80" s="1">
-        <f t="shared" si="9"/>
         <v>20050010</v>
       </c>
       <c r="B80" s="16">
@@ -5458,7 +5526,6 @@
     </row>
     <row r="81" s="1" customFormat="1" spans="1:19">
       <c r="A81" s="1">
-        <f t="shared" si="9"/>
         <v>20050011</v>
       </c>
       <c r="B81" s="16">
@@ -5507,7 +5574,6 @@
     </row>
     <row r="82" s="1" customFormat="1" spans="1:19">
       <c r="A82" s="1">
-        <f t="shared" si="9"/>
         <v>20050012</v>
       </c>
       <c r="B82" s="16">
@@ -5556,7 +5622,6 @@
     </row>
     <row r="83" spans="1:19">
       <c r="A83" s="1">
-        <f t="shared" si="9"/>
         <v>20060010</v>
       </c>
       <c r="B83" s="16">
@@ -5604,7 +5669,6 @@
     </row>
     <row r="84" spans="1:19">
       <c r="A84" s="1">
-        <f t="shared" ref="A84:A98" si="10">B84*100+H84</f>
         <v>20060011</v>
       </c>
       <c r="B84" s="16">
@@ -5652,7 +5716,6 @@
     </row>
     <row r="85" spans="1:19">
       <c r="A85" s="1">
-        <f t="shared" si="10"/>
         <v>20060012</v>
       </c>
       <c r="B85" s="16">
@@ -5700,7 +5763,6 @@
     </row>
     <row r="86" spans="1:19">
       <c r="A86" s="1">
-        <f t="shared" si="10"/>
         <v>20070010</v>
       </c>
       <c r="B86" s="16">
@@ -5748,7 +5810,6 @@
     </row>
     <row r="87" spans="1:19">
       <c r="A87" s="1">
-        <f t="shared" si="10"/>
         <v>20070011</v>
       </c>
       <c r="B87" s="16">
@@ -5797,7 +5858,6 @@
     </row>
     <row r="88" spans="1:19">
       <c r="A88" s="1">
-        <f t="shared" si="10"/>
         <v>20070012</v>
       </c>
       <c r="B88" s="16">
@@ -5846,7 +5906,6 @@
     </row>
     <row r="89" spans="1:19">
       <c r="A89" s="1">
-        <f t="shared" si="10"/>
         <v>20080010</v>
       </c>
       <c r="B89" s="16">
@@ -5894,7 +5953,6 @@
     </row>
     <row r="90" spans="1:19">
       <c r="A90" s="1">
-        <f t="shared" si="10"/>
         <v>20080011</v>
       </c>
       <c r="B90" s="16">
@@ -5942,7 +6000,6 @@
     </row>
     <row r="91" spans="1:19">
       <c r="A91" s="1">
-        <f t="shared" si="10"/>
         <v>20080012</v>
       </c>
       <c r="B91" s="16">
@@ -5990,7 +6047,6 @@
     </row>
     <row r="92" spans="1:19">
       <c r="A92" s="1">
-        <f t="shared" si="10"/>
         <v>20090010</v>
       </c>
       <c r="B92" s="16">
@@ -6038,7 +6094,6 @@
     </row>
     <row r="93" spans="1:19">
       <c r="A93" s="1">
-        <f t="shared" si="10"/>
         <v>20090011</v>
       </c>
       <c r="B93" s="16">
@@ -6086,7 +6141,6 @@
     </row>
     <row r="94" spans="1:19">
       <c r="A94" s="1">
-        <f t="shared" si="10"/>
         <v>20090012</v>
       </c>
       <c r="B94" s="16">
@@ -6134,7 +6188,6 @@
     </row>
     <row r="95" s="1" customFormat="1" spans="1:19">
       <c r="A95" s="1">
-        <f t="shared" si="10"/>
         <v>30020010</v>
       </c>
       <c r="B95" s="16">
@@ -6183,7 +6236,6 @@
     </row>
     <row r="96" s="1" customFormat="1" spans="1:19">
       <c r="A96" s="1">
-        <f t="shared" si="10"/>
         <v>30020011</v>
       </c>
       <c r="B96" s="16">
@@ -6232,7 +6284,6 @@
     </row>
     <row r="97" s="1" customFormat="1" spans="1:19">
       <c r="A97" s="1">
-        <f t="shared" si="10"/>
         <v>30020012</v>
       </c>
       <c r="B97" s="16">
@@ -6280,9 +6331,8 @@
       <c r="S97" s="3"/>
     </row>
     <row r="98" spans="1:19">
-      <c r="A98" s="1">
-        <f t="shared" ref="A98:A124" si="11">B98*10+H98</f>
-        <v>1001010</v>
+      <c r="A98" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="B98" s="16">
         <v>100100</v>
@@ -6328,9 +6378,8 @@
       </c>
     </row>
     <row r="99" spans="1:19">
-      <c r="A99" s="1">
-        <f t="shared" si="11"/>
-        <v>1001011</v>
+      <c r="A99" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="B99" s="16">
         <v>100100</v>
@@ -6339,7 +6388,7 @@
         <v>1</v>
       </c>
       <c r="D99" s="16" t="str">
-        <f t="shared" ref="D99:D103" si="12">D98</f>
+        <f t="shared" ref="D99:D103" si="8">D98</f>
         <v>金礦大亨</v>
       </c>
       <c r="E99" s="16">
@@ -6377,9 +6426,8 @@
       </c>
     </row>
     <row r="100" spans="1:19">
-      <c r="A100" s="1">
-        <f t="shared" si="11"/>
-        <v>1001012</v>
+      <c r="A100" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="B100" s="16">
         <v>100100</v>
@@ -6388,7 +6436,7 @@
         <v>1</v>
       </c>
       <c r="D100" s="16" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>金礦大亨</v>
       </c>
       <c r="E100" s="16">
@@ -6426,9 +6474,8 @@
       </c>
     </row>
     <row r="101" spans="1:19">
-      <c r="A101" s="1">
-        <f t="shared" si="11"/>
-        <v>1003010</v>
+      <c r="A101" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="B101" s="16">
         <v>100300</v>
@@ -6474,9 +6521,8 @@
       </c>
     </row>
     <row r="102" spans="1:19">
-      <c r="A102" s="1">
-        <f t="shared" si="11"/>
-        <v>1003011</v>
+      <c r="A102" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="B102" s="16">
         <v>100300</v>
@@ -6485,14 +6531,14 @@
         <v>1</v>
       </c>
       <c r="D102" s="16" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>超级明星</v>
       </c>
       <c r="E102" s="16">
         <v>100300001</v>
       </c>
       <c r="F102" s="16" t="str">
-        <f t="shared" ref="F102:F106" si="13">F101</f>
+        <f t="shared" ref="F102:F106" si="9">F101</f>
         <v>SuperStar</v>
       </c>
       <c r="G102" s="19" t="s">
@@ -6524,9 +6570,8 @@
       </c>
     </row>
     <row r="103" spans="1:19">
-      <c r="A103" s="1">
-        <f t="shared" si="11"/>
-        <v>1003012</v>
+      <c r="A103" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="B103" s="16">
         <v>100300</v>
@@ -6535,14 +6580,14 @@
         <v>1</v>
       </c>
       <c r="D103" s="16" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>超级明星</v>
       </c>
       <c r="E103" s="16">
         <v>100300001</v>
       </c>
       <c r="F103" s="16" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>SuperStar</v>
       </c>
       <c r="G103" s="19" t="s">
@@ -6574,9 +6619,8 @@
       </c>
     </row>
     <row r="104" spans="1:19">
-      <c r="A104" s="1">
-        <f t="shared" si="11"/>
-        <v>1007010</v>
+      <c r="A104" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="B104" s="16">
         <v>100700</v>
@@ -6622,9 +6666,8 @@
       </c>
     </row>
     <row r="105" spans="1:19">
-      <c r="A105" s="1">
-        <f t="shared" si="11"/>
-        <v>1007011</v>
+      <c r="A105" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="B105" s="16">
         <v>100700</v>
@@ -6633,14 +6676,14 @@
         <v>1</v>
       </c>
       <c r="D105" s="16" t="str">
-        <f t="shared" ref="D105:D109" si="14">D104</f>
+        <f t="shared" ref="D105:D109" si="10">D104</f>
         <v>麻将胡了</v>
       </c>
       <c r="E105" s="16">
         <v>100700001</v>
       </c>
       <c r="F105" s="16" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>MahjongWays</v>
       </c>
       <c r="G105" s="19" t="s">
@@ -6672,9 +6715,8 @@
       </c>
     </row>
     <row r="106" spans="1:19">
-      <c r="A106" s="1">
-        <f t="shared" si="11"/>
-        <v>1007012</v>
+      <c r="A106" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="B106" s="16">
         <v>100700</v>
@@ -6683,14 +6725,14 @@
         <v>1</v>
       </c>
       <c r="D106" s="16" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>麻将胡了</v>
       </c>
       <c r="E106" s="16">
         <v>100700001</v>
       </c>
       <c r="F106" s="16" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="9"/>
         <v>MahjongWays</v>
       </c>
       <c r="G106" s="19" t="s">
@@ -6722,9 +6764,8 @@
       </c>
     </row>
     <row r="107" spans="1:19">
-      <c r="A107" s="1">
-        <f t="shared" si="11"/>
-        <v>1012010</v>
+      <c r="A107" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="B107" s="16">
         <v>101200</v>
@@ -6770,9 +6811,8 @@
       </c>
     </row>
     <row r="108" spans="1:19">
-      <c r="A108" s="1">
-        <f t="shared" si="11"/>
-        <v>1012011</v>
+      <c r="A108" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="B108" s="16">
         <v>101200</v>
@@ -6781,14 +6821,14 @@
         <v>1</v>
       </c>
       <c r="D108" s="16" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>财神</v>
       </c>
       <c r="E108" s="16">
         <v>101200001</v>
       </c>
       <c r="F108" s="16" t="str">
-        <f t="shared" ref="F108:F112" si="15">F107</f>
+        <f t="shared" ref="F108:F112" si="11">F107</f>
         <v>Godofwealth</v>
       </c>
       <c r="G108" s="19" t="s">
@@ -6820,9 +6860,8 @@
       </c>
     </row>
     <row r="109" spans="1:19">
-      <c r="A109" s="1">
-        <f t="shared" si="11"/>
-        <v>1012012</v>
+      <c r="A109" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="B109" s="16">
         <v>101200</v>
@@ -6831,14 +6870,14 @@
         <v>1</v>
       </c>
       <c r="D109" s="16" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="10"/>
         <v>财神</v>
       </c>
       <c r="E109" s="16">
         <v>101200001</v>
       </c>
       <c r="F109" s="16" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>Godofwealth</v>
       </c>
       <c r="G109" s="19" t="s">
@@ -6870,9 +6909,8 @@
       </c>
     </row>
     <row r="110" spans="1:19">
-      <c r="A110" s="1">
-        <f t="shared" si="11"/>
-        <v>1014010</v>
+      <c r="A110" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="B110" s="16">
         <v>101400</v>
@@ -6918,9 +6956,8 @@
       </c>
     </row>
     <row r="111" spans="1:19">
-      <c r="A111" s="1">
-        <f t="shared" si="11"/>
-        <v>1014011</v>
+      <c r="A111" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="B111" s="16">
         <v>101400</v>
@@ -6929,14 +6966,14 @@
         <v>1</v>
       </c>
       <c r="D111" s="16" t="str">
-        <f t="shared" ref="D111:D115" si="16">D110</f>
+        <f t="shared" ref="D111:D115" si="12">D110</f>
         <v>埃及艳后</v>
       </c>
       <c r="E111" s="16">
         <v>101400001</v>
       </c>
       <c r="F111" s="16" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>Cleopatra</v>
       </c>
       <c r="G111" s="19" t="s">
@@ -6968,9 +7005,8 @@
       </c>
     </row>
     <row r="112" spans="1:19">
-      <c r="A112" s="1">
-        <f t="shared" si="11"/>
-        <v>1014012</v>
+      <c r="A112" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="B112" s="16">
         <v>101400</v>
@@ -6979,14 +7015,14 @@
         <v>1</v>
       </c>
       <c r="D112" s="16" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>埃及艳后</v>
       </c>
       <c r="E112" s="16">
         <v>101400001</v>
       </c>
       <c r="F112" s="16" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>Cleopatra</v>
       </c>
       <c r="G112" s="19" t="s">
@@ -7018,9 +7054,8 @@
       </c>
     </row>
     <row r="113" spans="1:15">
-      <c r="A113" s="1">
-        <f t="shared" si="11"/>
-        <v>1024010</v>
+      <c r="A113" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="B113" s="16">
         <v>102400</v>
@@ -7066,9 +7101,8 @@
       </c>
     </row>
     <row r="114" spans="1:15">
-      <c r="A114" s="1">
-        <f t="shared" si="11"/>
-        <v>1024011</v>
+      <c r="A114" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="B114" s="16">
         <v>102400</v>
@@ -7077,7 +7111,7 @@
         <v>1</v>
       </c>
       <c r="D114" s="16" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>财富银行</v>
       </c>
       <c r="E114" s="16">
@@ -7115,9 +7149,8 @@
       </c>
     </row>
     <row r="115" spans="1:15">
-      <c r="A115" s="1">
-        <f t="shared" si="11"/>
-        <v>1024012</v>
+      <c r="A115" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="B115" s="16">
         <v>102400</v>
@@ -7126,7 +7159,7 @@
         <v>1</v>
       </c>
       <c r="D115" s="16" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="12"/>
         <v>财富银行</v>
       </c>
       <c r="E115" s="16">
@@ -7164,9 +7197,8 @@
       </c>
     </row>
     <row r="116" spans="1:15">
-      <c r="A116" s="1">
-        <f t="shared" si="11"/>
-        <v>1022010</v>
+      <c r="A116" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="B116" s="16">
         <v>102200</v>
@@ -7212,9 +7244,8 @@
       </c>
     </row>
     <row r="117" spans="1:15">
-      <c r="A117" s="1">
-        <f t="shared" si="11"/>
-        <v>1022011</v>
+      <c r="A117" s="1" t="s">
+        <v>104</v>
       </c>
       <c r="B117" s="16">
         <v>102200</v>
@@ -7260,9 +7291,8 @@
       </c>
     </row>
     <row r="118" spans="1:15">
-      <c r="A118" s="1">
-        <f t="shared" si="11"/>
-        <v>1022012</v>
+      <c r="A118" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="B118" s="16">
         <v>102200</v>
@@ -7308,9 +7338,8 @@
       </c>
     </row>
     <row r="119" spans="1:15">
-      <c r="A119" s="1">
-        <f t="shared" si="11"/>
-        <v>1017010</v>
+      <c r="A119" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="B119" s="16">
         <v>101700</v>
@@ -7356,9 +7385,8 @@
       </c>
     </row>
     <row r="120" spans="1:15">
-      <c r="A120" s="1">
-        <f t="shared" si="11"/>
-        <v>1017011</v>
+      <c r="A120" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="B120" s="16">
         <v>101700</v>
@@ -7404,9 +7432,8 @@
       </c>
     </row>
     <row r="121" spans="1:15">
-      <c r="A121" s="1">
-        <f t="shared" si="11"/>
-        <v>1017012</v>
+      <c r="A121" s="1" t="s">
+        <v>108</v>
       </c>
       <c r="B121" s="16">
         <v>101700</v>
@@ -7452,9 +7479,8 @@
       </c>
     </row>
     <row r="122" spans="1:15">
-      <c r="A122" s="1">
-        <f t="shared" si="11"/>
-        <v>1021010</v>
+      <c r="A122" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="B122" s="16">
         <v>102100</v>
@@ -7500,9 +7526,8 @@
       </c>
     </row>
     <row r="123" spans="1:15">
-      <c r="A123" s="1">
-        <f t="shared" si="11"/>
-        <v>1021011</v>
+      <c r="A123" s="1" t="s">
+        <v>110</v>
       </c>
       <c r="B123" s="16">
         <v>102100</v>
@@ -7548,9 +7573,8 @@
       </c>
     </row>
     <row r="124" spans="1:15">
-      <c r="A124" s="1">
-        <f t="shared" si="11"/>
-        <v>1021012</v>
+      <c r="A124" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="B124" s="16">
         <v>102100</v>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925" tabRatio="794"/>
+    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Warehouse" sheetId="42" r:id="rId1"/>
@@ -156,7 +156,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="115">
   <si>
     <t>sid</t>
   </si>
@@ -492,6 +492,15 @@
   </si>
   <si>
     <t>10210012</t>
+  </si>
+  <si>
+    <t>篮球巨星</t>
+  </si>
+  <si>
+    <t>BasketballSuperstar</t>
+  </si>
+  <si>
+    <t>FrozenThrone</t>
   </si>
 </sst>
 </file>
@@ -1641,7 +1650,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S124"/>
+  <dimension ref="A1:S130"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="3" width="9.375" style="1"/>
@@ -7619,6 +7628,288 @@
         <v>1980000</v>
       </c>
     </row>
+    <row r="125" spans="1:15">
+      <c r="A125" s="1">
+        <v>10180010</v>
+      </c>
+      <c r="B125" s="16">
+        <v>101800</v>
+      </c>
+      <c r="C125" s="16">
+        <v>1</v>
+      </c>
+      <c r="D125" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="E125" s="16">
+        <v>101800001</v>
+      </c>
+      <c r="F125" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="G125" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="H125" s="19">
+        <v>10</v>
+      </c>
+      <c r="I125" s="19">
+        <v>0</v>
+      </c>
+      <c r="J125" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K125" s="19">
+        <v>0</v>
+      </c>
+      <c r="L125" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="M125" s="19">
+        <v>0</v>
+      </c>
+      <c r="N125" s="20">
+        <v>50</v>
+      </c>
+      <c r="O125" s="21">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15">
+      <c r="A126" s="1">
+        <v>10180011</v>
+      </c>
+      <c r="B126" s="16">
+        <v>101800</v>
+      </c>
+      <c r="C126" s="16">
+        <v>1</v>
+      </c>
+      <c r="D126" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="E126" s="16">
+        <v>101800001</v>
+      </c>
+      <c r="F126" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="G126" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="H126" s="19">
+        <v>11</v>
+      </c>
+      <c r="I126" s="19">
+        <v>0</v>
+      </c>
+      <c r="J126" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K126" s="19">
+        <v>0</v>
+      </c>
+      <c r="L126" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="M126" s="19">
+        <v>0</v>
+      </c>
+      <c r="N126" s="20">
+        <v>500</v>
+      </c>
+      <c r="O126" s="21">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15">
+      <c r="A127" s="1">
+        <v>10180012</v>
+      </c>
+      <c r="B127" s="16">
+        <v>101800</v>
+      </c>
+      <c r="C127" s="16">
+        <v>1</v>
+      </c>
+      <c r="D127" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="E127" s="16">
+        <v>101800001</v>
+      </c>
+      <c r="F127" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="G127" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="H127" s="19">
+        <v>12</v>
+      </c>
+      <c r="I127" s="19">
+        <v>0</v>
+      </c>
+      <c r="J127" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K127" s="19">
+        <v>0</v>
+      </c>
+      <c r="L127" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="M127" s="19">
+        <v>0</v>
+      </c>
+      <c r="N127" s="20">
+        <v>5000</v>
+      </c>
+      <c r="O127" s="21">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15">
+      <c r="A128" s="1">
+        <v>10250010</v>
+      </c>
+      <c r="B128" s="16">
+        <v>102500</v>
+      </c>
+      <c r="C128" s="16">
+        <v>1</v>
+      </c>
+      <c r="D128" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="E128" s="16">
+        <v>101800001</v>
+      </c>
+      <c r="F128" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="G128" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="H128" s="19">
+        <v>10</v>
+      </c>
+      <c r="I128" s="19">
+        <v>0</v>
+      </c>
+      <c r="J128" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K128" s="19">
+        <v>0</v>
+      </c>
+      <c r="L128" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="M128" s="19">
+        <v>0</v>
+      </c>
+      <c r="N128" s="20">
+        <v>50</v>
+      </c>
+      <c r="O128" s="21">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15">
+      <c r="A129" s="1">
+        <v>10250011</v>
+      </c>
+      <c r="B129" s="16">
+        <v>102500</v>
+      </c>
+      <c r="C129" s="16">
+        <v>1</v>
+      </c>
+      <c r="D129" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="E129" s="16">
+        <v>101800001</v>
+      </c>
+      <c r="F129" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="G129" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="H129" s="19">
+        <v>11</v>
+      </c>
+      <c r="I129" s="19">
+        <v>0</v>
+      </c>
+      <c r="J129" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K129" s="19">
+        <v>0</v>
+      </c>
+      <c r="L129" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="M129" s="19">
+        <v>0</v>
+      </c>
+      <c r="N129" s="20">
+        <v>500</v>
+      </c>
+      <c r="O129" s="21">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15">
+      <c r="A130" s="1">
+        <v>10250012</v>
+      </c>
+      <c r="B130" s="16">
+        <v>102500</v>
+      </c>
+      <c r="C130" s="16">
+        <v>1</v>
+      </c>
+      <c r="D130" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="E130" s="16">
+        <v>101800001</v>
+      </c>
+      <c r="F130" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="G130" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="H130" s="19">
+        <v>12</v>
+      </c>
+      <c r="I130" s="19">
+        <v>0</v>
+      </c>
+      <c r="J130" s="19">
+        <v>-1</v>
+      </c>
+      <c r="K130" s="19">
+        <v>0</v>
+      </c>
+      <c r="L130" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="M130" s="19">
+        <v>0</v>
+      </c>
+      <c r="N130" s="20">
+        <v>5000</v>
+      </c>
+      <c r="O130" s="21">
+        <v>1980000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -156,7 +156,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="116">
   <si>
     <t>sid</t>
   </si>
@@ -498,6 +498,9 @@
   </si>
   <si>
     <t>BasketballSuperstar</t>
+  </si>
+  <si>
+    <t>寒冰王座</t>
   </si>
   <si>
     <t>FrozenThrone</t>
@@ -7780,13 +7783,13 @@
         <v>1</v>
       </c>
       <c r="D128" s="16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E128" s="16">
-        <v>101800001</v>
+        <v>102500001</v>
       </c>
       <c r="F128" s="16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G128" s="19" t="s">
         <v>80</v>
@@ -7827,13 +7830,13 @@
         <v>1</v>
       </c>
       <c r="D129" s="16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E129" s="16">
-        <v>101800001</v>
+        <v>102500001</v>
       </c>
       <c r="F129" s="16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G129" s="19" t="s">
         <v>82</v>
@@ -7874,13 +7877,13 @@
         <v>1</v>
       </c>
       <c r="D130" s="16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E130" s="16">
-        <v>101800001</v>
+        <v>102500001</v>
       </c>
       <c r="F130" s="16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G130" s="19" t="s">
         <v>83</v>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -156,7 +156,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="116">
   <si>
     <t>sid</t>
   </si>
@@ -317,6 +317,18 @@
     <t>CaptainJack</t>
   </si>
   <si>
+    <t>篮球巨星</t>
+  </si>
+  <si>
+    <t>BasketballSuperstar</t>
+  </si>
+  <si>
+    <t>寒冰王座</t>
+  </si>
+  <si>
+    <t>FrozenThrone</t>
+  </si>
+  <si>
     <t>紅黑大戰</t>
   </si>
   <si>
@@ -492,18 +504,6 @@
   </si>
   <si>
     <t>10210012</t>
-  </si>
-  <si>
-    <t>篮球巨星</t>
-  </si>
-  <si>
-    <t>BasketballSuperstar</t>
-  </si>
-  <si>
-    <t>寒冰王座</t>
-  </si>
-  <si>
-    <t>FrozenThrone</t>
   </si>
 </sst>
 </file>
@@ -1297,14 +1297,14 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1653,7 +1653,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S130"/>
+  <dimension ref="A1:S136"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="3" width="9.375" style="1"/>
@@ -3131,37 +3131,36 @@
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="1">
-        <f t="shared" ref="A32:A78" si="5">B32*10+H32</f>
-        <v>2001001</v>
-      </c>
-      <c r="B32" s="12">
-        <v>200100</v>
-      </c>
-      <c r="C32" s="12">
-        <v>2</v>
-      </c>
-      <c r="D32" s="12" t="s">
+        <v>10180001</v>
+      </c>
+      <c r="B32" s="16">
+        <v>101800</v>
+      </c>
+      <c r="C32" s="16">
+        <v>1</v>
+      </c>
+      <c r="D32" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="E32" s="13">
-        <v>200100038</v>
-      </c>
-      <c r="F32" s="13" t="s">
+      <c r="E32" s="16">
+        <v>101800001</v>
+      </c>
+      <c r="F32" s="16" t="s">
         <v>54</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H32" s="1">
+      <c r="H32" s="17">
         <v>1</v>
       </c>
       <c r="I32" s="1">
         <v>0</v>
       </c>
-      <c r="J32" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K32" s="1">
+      <c r="J32" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K32" s="17">
         <v>0</v>
       </c>
       <c r="L32" s="1" t="s">
@@ -3179,368 +3178,353 @@
     </row>
     <row r="33" spans="1:19">
       <c r="A33" s="1">
+        <v>10180002</v>
+      </c>
+      <c r="B33" s="16">
+        <v>101800</v>
+      </c>
+      <c r="C33" s="16">
+        <v>1</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="E33" s="16">
+        <v>101800001</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H33" s="17">
+        <v>2</v>
+      </c>
+      <c r="I33" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J33" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K33" s="17">
+        <v>0</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M33" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="N33">
+        <v>500000</v>
+      </c>
+      <c r="O33" s="15">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19">
+      <c r="A34" s="1">
+        <v>10180003</v>
+      </c>
+      <c r="B34" s="16">
+        <v>101800</v>
+      </c>
+      <c r="C34" s="16">
+        <v>1</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="E34" s="16">
+        <v>101800001</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H34" s="17">
+        <v>3</v>
+      </c>
+      <c r="I34" s="1">
+        <v>50000000</v>
+      </c>
+      <c r="J34" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K34" s="17">
+        <v>0</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M34" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="N34">
+        <v>50000000</v>
+      </c>
+      <c r="O34" s="15">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19">
+      <c r="A35" s="1">
+        <v>10250001</v>
+      </c>
+      <c r="B35" s="16">
+        <v>102500</v>
+      </c>
+      <c r="C35" s="16">
+        <v>1</v>
+      </c>
+      <c r="D35" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E35" s="16">
+        <v>102500001</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H35" s="17">
+        <v>1</v>
+      </c>
+      <c r="I35" s="1">
+        <v>0</v>
+      </c>
+      <c r="J35" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K35" s="17">
+        <v>0</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M35" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="N35">
+        <v>5000</v>
+      </c>
+      <c r="O35" s="15">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19">
+      <c r="A36" s="1">
+        <v>10250002</v>
+      </c>
+      <c r="B36" s="16">
+        <v>102500</v>
+      </c>
+      <c r="C36" s="16">
+        <v>1</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E36" s="16">
+        <v>102500001</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H36" s="17">
+        <v>2</v>
+      </c>
+      <c r="I36" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J36" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K36" s="17">
+        <v>0</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M36" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="N36">
+        <v>500000</v>
+      </c>
+      <c r="O36" s="15">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19">
+      <c r="A37" s="1">
+        <v>10250003</v>
+      </c>
+      <c r="B37" s="16">
+        <v>102500</v>
+      </c>
+      <c r="C37" s="16">
+        <v>1</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E37" s="16">
+        <v>102500001</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H37" s="17">
+        <v>3</v>
+      </c>
+      <c r="I37" s="1">
+        <v>50000000</v>
+      </c>
+      <c r="J37" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K37" s="17">
+        <v>0</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M37" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="N37">
+        <v>50000000</v>
+      </c>
+      <c r="O37" s="15">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19">
+      <c r="A38" s="1">
+        <f t="shared" ref="A38:A84" si="5">B38*10+H38</f>
+        <v>2001001</v>
+      </c>
+      <c r="B38" s="12">
+        <v>200100</v>
+      </c>
+      <c r="C38" s="12">
+        <v>2</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E38" s="13">
+        <v>200100038</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H38" s="1">
+        <v>1</v>
+      </c>
+      <c r="I38" s="1">
+        <v>0</v>
+      </c>
+      <c r="J38" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K38" s="1">
+        <v>0</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M38" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="N38">
+        <v>5000</v>
+      </c>
+      <c r="O38" s="15">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19">
+      <c r="A39" s="1">
         <f t="shared" si="5"/>
         <v>2001002</v>
       </c>
-      <c r="B33" s="12">
+      <c r="B39" s="12">
         <v>200100</v>
       </c>
-      <c r="C33" s="12">
+      <c r="C39" s="12">
         <v>2</v>
       </c>
-      <c r="D33" s="12" t="str">
-        <f>D32</f>
+      <c r="D39" s="12" t="str">
+        <f>D38</f>
         <v>紅黑大戰</v>
       </c>
-      <c r="E33" s="13">
+      <c r="E39" s="13">
         <v>200100038</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G33" s="1" t="s">
+      <c r="F39" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H33" s="1">
+      <c r="H39" s="1">
         <v>2</v>
       </c>
-      <c r="I33" s="1">
+      <c r="I39" s="1">
         <v>500000</v>
       </c>
-      <c r="J33" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K33" s="1">
-        <v>0</v>
-      </c>
-      <c r="L33" s="1" t="s">
+      <c r="J39" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K39" s="1">
+        <v>0</v>
+      </c>
+      <c r="L39" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M33" s="23" t="s">
+      <c r="M39" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="N33">
+      <c r="N39">
         <v>500000</v>
       </c>
-      <c r="O33" s="15">
+      <c r="O39" s="15">
         <v>1990000</v>
       </c>
     </row>
-    <row r="34" spans="1:19">
-      <c r="A34" s="1">
+    <row r="40" spans="1:19">
+      <c r="A40" s="1">
         <f t="shared" si="5"/>
         <v>2001003</v>
       </c>
-      <c r="B34" s="12">
+      <c r="B40" s="12">
         <v>200100</v>
-      </c>
-      <c r="C34" s="12">
-        <v>2</v>
-      </c>
-      <c r="D34" s="12" t="str">
-        <f>D33</f>
-        <v>紅黑大戰</v>
-      </c>
-      <c r="E34" s="13">
-        <v>200100038</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H34" s="1">
-        <v>3</v>
-      </c>
-      <c r="I34" s="1">
-        <v>50000000</v>
-      </c>
-      <c r="J34" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K34" s="1">
-        <v>0</v>
-      </c>
-      <c r="L34" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M34" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="N34">
-        <v>50000000</v>
-      </c>
-      <c r="O34" s="15">
-        <v>1990000</v>
-      </c>
-      <c r="Q34"/>
-    </row>
-    <row r="35" spans="1:19">
-      <c r="A35" s="1">
-        <f t="shared" si="5"/>
-        <v>2001011</v>
-      </c>
-      <c r="B35" s="12">
-        <v>200101</v>
-      </c>
-      <c r="C35" s="12">
-        <v>2</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E35" s="13">
-        <v>200101001</v>
-      </c>
-      <c r="F35" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H35" s="1">
-        <v>1</v>
-      </c>
-      <c r="I35" s="1">
-        <v>0</v>
-      </c>
-      <c r="J35" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K35" s="1">
-        <v>0</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M35" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="N35">
-        <v>5000</v>
-      </c>
-      <c r="O35" s="15">
-        <v>1990000</v>
-      </c>
-    </row>
-    <row r="36" s="1" customFormat="1" spans="1:19">
-      <c r="A36" s="1">
-        <f t="shared" si="5"/>
-        <v>2001012</v>
-      </c>
-      <c r="B36" s="12">
-        <v>200101</v>
-      </c>
-      <c r="C36" s="12">
-        <v>2</v>
-      </c>
-      <c r="D36" s="12" t="str">
-        <f t="shared" ref="D36:D40" si="6">D35</f>
-        <v>龍虎鬥</v>
-      </c>
-      <c r="E36" s="13">
-        <v>200101001</v>
-      </c>
-      <c r="F36" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H36" s="1">
-        <v>2</v>
-      </c>
-      <c r="I36" s="1">
-        <v>500000</v>
-      </c>
-      <c r="J36" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K36" s="1">
-        <v>0</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M36" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="N36">
-        <v>500000</v>
-      </c>
-      <c r="O36" s="15">
-        <v>1990000</v>
-      </c>
-      <c r="S36" s="3"/>
-    </row>
-    <row r="37" s="1" customFormat="1" spans="1:19">
-      <c r="A37" s="1">
-        <f t="shared" si="5"/>
-        <v>2001013</v>
-      </c>
-      <c r="B37" s="12">
-        <v>200101</v>
-      </c>
-      <c r="C37" s="12">
-        <v>2</v>
-      </c>
-      <c r="D37" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v>龍虎鬥</v>
-      </c>
-      <c r="E37" s="13">
-        <v>200101001</v>
-      </c>
-      <c r="F37" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H37" s="1">
-        <v>3</v>
-      </c>
-      <c r="I37" s="1">
-        <v>50000000</v>
-      </c>
-      <c r="J37" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K37" s="1">
-        <v>0</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M37" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="N37">
-        <v>50000000</v>
-      </c>
-      <c r="O37" s="15">
-        <v>1990000</v>
-      </c>
-      <c r="S37" s="3"/>
-    </row>
-    <row r="38" spans="1:19">
-      <c r="A38" s="1">
-        <f t="shared" si="5"/>
-        <v>2003001</v>
-      </c>
-      <c r="B38" s="12">
-        <v>200300</v>
-      </c>
-      <c r="C38" s="12">
-        <v>2</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="E38" s="13">
-        <v>200300001</v>
-      </c>
-      <c r="F38" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H38" s="1">
-        <v>1</v>
-      </c>
-      <c r="I38" s="1">
-        <v>0</v>
-      </c>
-      <c r="J38" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K38" s="1">
-        <v>0</v>
-      </c>
-      <c r="L38" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M38" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="N38">
-        <v>5000</v>
-      </c>
-      <c r="O38" s="15">
-        <v>1990000</v>
-      </c>
-    </row>
-    <row r="39" s="1" customFormat="1" spans="1:19">
-      <c r="A39" s="1">
-        <f t="shared" si="5"/>
-        <v>2003002</v>
-      </c>
-      <c r="B39" s="12">
-        <v>200300</v>
-      </c>
-      <c r="C39" s="12">
-        <v>2</v>
-      </c>
-      <c r="D39" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v>飛禽走獸</v>
-      </c>
-      <c r="E39" s="13">
-        <v>200300001</v>
-      </c>
-      <c r="F39" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H39" s="1">
-        <v>2</v>
-      </c>
-      <c r="I39" s="1">
-        <v>500000</v>
-      </c>
-      <c r="J39" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K39" s="1">
-        <v>0</v>
-      </c>
-      <c r="L39" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M39" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="N39">
-        <v>500000</v>
-      </c>
-      <c r="O39" s="15">
-        <v>1990000</v>
-      </c>
-      <c r="Q39" s="3"/>
-      <c r="R39" s="12"/>
-      <c r="S39" s="3"/>
-    </row>
-    <row r="40" s="1" customFormat="1" spans="1:19">
-      <c r="A40" s="1">
-        <f t="shared" si="5"/>
-        <v>2003003</v>
-      </c>
-      <c r="B40" s="12">
-        <v>200300</v>
       </c>
       <c r="C40" s="12">
         <v>2</v>
       </c>
       <c r="D40" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v>飛禽走獸</v>
+        <f>D39</f>
+        <v>紅黑大戰</v>
       </c>
       <c r="E40" s="13">
-        <v>200300001</v>
+        <v>200100038</v>
       </c>
       <c r="F40" s="13" t="s">
         <v>58</v>
@@ -3572,26 +3556,24 @@
       <c r="O40" s="15">
         <v>1990000</v>
       </c>
-      <c r="Q40" s="3"/>
-      <c r="R40" s="17"/>
-      <c r="S40" s="17"/>
+      <c r="Q40"/>
     </row>
     <row r="41" spans="1:19">
       <c r="A41" s="1">
         <f t="shared" si="5"/>
-        <v>2004001</v>
+        <v>2001011</v>
       </c>
       <c r="B41" s="12">
-        <v>200400</v>
+        <v>200101</v>
       </c>
       <c r="C41" s="12">
         <v>2</v>
       </c>
-      <c r="D41" s="17" t="s">
+      <c r="D41" s="12" t="s">
         <v>59</v>
       </c>
       <c r="E41" s="13">
-        <v>200400009</v>
+        <v>200101001</v>
       </c>
       <c r="F41" s="13" t="s">
         <v>60</v>
@@ -3623,26 +3605,24 @@
       <c r="O41" s="15">
         <v>1990000</v>
       </c>
-      <c r="Q41" s="3"/>
-      <c r="R41" s="17"/>
-      <c r="S41" s="17"/>
     </row>
     <row r="42" s="1" customFormat="1" spans="1:19">
       <c r="A42" s="1">
         <f t="shared" si="5"/>
-        <v>2004002</v>
+        <v>2001012</v>
       </c>
       <c r="B42" s="12">
-        <v>200400</v>
+        <v>200101</v>
       </c>
       <c r="C42" s="12">
         <v>2</v>
       </c>
-      <c r="D42" s="17" t="s">
-        <v>59</v>
+      <c r="D42" s="12" t="str">
+        <f t="shared" ref="D42:D46" si="6">D41</f>
+        <v>龍虎鬥</v>
       </c>
       <c r="E42" s="13">
-        <v>200400009</v>
+        <v>200101001</v>
       </c>
       <c r="F42" s="13" t="s">
         <v>60</v>
@@ -3674,26 +3654,25 @@
       <c r="O42" s="15">
         <v>1990000</v>
       </c>
-      <c r="Q42" s="3"/>
-      <c r="R42" s="17"/>
-      <c r="S42" s="17"/>
+      <c r="S42" s="3"/>
     </row>
     <row r="43" s="1" customFormat="1" spans="1:19">
       <c r="A43" s="1">
         <f t="shared" si="5"/>
-        <v>2004003</v>
+        <v>2001013</v>
       </c>
       <c r="B43" s="12">
-        <v>200400</v>
+        <v>200101</v>
       </c>
       <c r="C43" s="12">
         <v>2</v>
       </c>
-      <c r="D43" s="17" t="s">
-        <v>59</v>
+      <c r="D43" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>龍虎鬥</v>
       </c>
       <c r="E43" s="13">
-        <v>200400009</v>
+        <v>200101001</v>
       </c>
       <c r="F43" s="13" t="s">
         <v>60</v>
@@ -3725,17 +3704,15 @@
       <c r="O43" s="15">
         <v>1990000</v>
       </c>
-      <c r="Q43" s="3"/>
-      <c r="R43" s="17"/>
-      <c r="S43" s="17"/>
+      <c r="S43" s="3"/>
     </row>
     <row r="44" spans="1:19">
       <c r="A44" s="1">
         <f t="shared" si="5"/>
-        <v>2005001</v>
+        <v>2003001</v>
       </c>
       <c r="B44" s="12">
-        <v>200500</v>
+        <v>200300</v>
       </c>
       <c r="C44" s="12">
         <v>2</v>
@@ -3744,7 +3721,7 @@
         <v>61</v>
       </c>
       <c r="E44" s="13">
-        <v>200500025</v>
+        <v>200300001</v>
       </c>
       <c r="F44" s="13" t="s">
         <v>62</v>
@@ -3768,7 +3745,7 @@
         <v>33</v>
       </c>
       <c r="M44" s="23" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="N44">
         <v>5000</v>
@@ -3776,26 +3753,24 @@
       <c r="O44" s="15">
         <v>1990000</v>
       </c>
-      <c r="Q44" s="3"/>
-      <c r="R44" s="17"/>
-      <c r="S44" s="17"/>
-    </row>
-    <row r="45" spans="1:19">
+    </row>
+    <row r="45" s="1" customFormat="1" spans="1:19">
       <c r="A45" s="1">
         <f t="shared" si="5"/>
-        <v>2005002</v>
+        <v>2003002</v>
       </c>
       <c r="B45" s="12">
-        <v>200500</v>
+        <v>200300</v>
       </c>
       <c r="C45" s="12">
         <v>2</v>
       </c>
-      <c r="D45" s="12" t="s">
-        <v>61</v>
+      <c r="D45" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>飛禽走獸</v>
       </c>
       <c r="E45" s="13">
-        <v>200500025</v>
+        <v>200300001</v>
       </c>
       <c r="F45" s="13" t="s">
         <v>62</v>
@@ -3819,7 +3794,7 @@
         <v>33</v>
       </c>
       <c r="M45" s="23" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="N45">
         <v>500000</v>
@@ -3828,25 +3803,26 @@
         <v>1990000</v>
       </c>
       <c r="Q45" s="3"/>
-      <c r="R45" s="17"/>
-      <c r="S45" s="17"/>
-    </row>
-    <row r="46" spans="1:19">
+      <c r="R45" s="12"/>
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" s="1" customFormat="1" spans="1:19">
       <c r="A46" s="1">
         <f t="shared" si="5"/>
-        <v>2005003</v>
+        <v>2003003</v>
       </c>
       <c r="B46" s="12">
-        <v>200500</v>
+        <v>200300</v>
       </c>
       <c r="C46" s="12">
         <v>2</v>
       </c>
-      <c r="D46" s="12" t="s">
-        <v>61</v>
+      <c r="D46" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>飛禽走獸</v>
       </c>
       <c r="E46" s="13">
-        <v>200500025</v>
+        <v>200300001</v>
       </c>
       <c r="F46" s="13" t="s">
         <v>62</v>
@@ -3870,7 +3846,7 @@
         <v>33</v>
       </c>
       <c r="M46" s="23" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="N46">
         <v>50000000</v>
@@ -3879,28 +3855,28 @@
         <v>1990000</v>
       </c>
       <c r="Q46" s="3"/>
-      <c r="R46" s="17"/>
-      <c r="S46" s="17"/>
+      <c r="R46" s="18"/>
+      <c r="S46" s="18"/>
     </row>
     <row r="47" spans="1:19">
       <c r="A47" s="1">
         <f t="shared" si="5"/>
-        <v>2006001</v>
+        <v>2004001</v>
       </c>
       <c r="B47" s="12">
-        <v>200600</v>
+        <v>200400</v>
       </c>
       <c r="C47" s="12">
         <v>2</v>
       </c>
-      <c r="D47" s="13" t="s">
+      <c r="D47" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="E47" s="13">
+        <v>200400009</v>
+      </c>
+      <c r="F47" s="13" t="s">
         <v>64</v>
-      </c>
-      <c r="E47" s="13">
-        <v>200600001</v>
-      </c>
-      <c r="F47" s="13" t="s">
-        <v>65</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>32</v>
@@ -3930,28 +3906,28 @@
         <v>1990000</v>
       </c>
       <c r="Q47" s="3"/>
-      <c r="R47" s="17"/>
-      <c r="S47" s="17"/>
+      <c r="R47" s="18"/>
+      <c r="S47" s="18"/>
     </row>
     <row r="48" s="1" customFormat="1" spans="1:19">
       <c r="A48" s="1">
         <f t="shared" si="5"/>
-        <v>2006002</v>
+        <v>2004002</v>
       </c>
       <c r="B48" s="12">
-        <v>200600</v>
+        <v>200400</v>
       </c>
       <c r="C48" s="12">
         <v>2</v>
       </c>
-      <c r="D48" s="13" t="s">
+      <c r="D48" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="E48" s="13">
+        <v>200400009</v>
+      </c>
+      <c r="F48" s="13" t="s">
         <v>64</v>
-      </c>
-      <c r="E48" s="13">
-        <v>200600001</v>
-      </c>
-      <c r="F48" s="13" t="s">
-        <v>65</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>35</v>
@@ -3981,28 +3957,28 @@
         <v>1990000</v>
       </c>
       <c r="Q48" s="3"/>
-      <c r="R48" s="17"/>
-      <c r="S48" s="17"/>
+      <c r="R48" s="18"/>
+      <c r="S48" s="18"/>
     </row>
     <row r="49" s="1" customFormat="1" spans="1:19">
       <c r="A49" s="1">
         <f t="shared" si="5"/>
-        <v>2006003</v>
+        <v>2004003</v>
       </c>
       <c r="B49" s="12">
-        <v>200600</v>
+        <v>200400</v>
       </c>
       <c r="C49" s="12">
         <v>2</v>
       </c>
-      <c r="D49" s="13" t="s">
+      <c r="D49" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="E49" s="13">
+        <v>200400009</v>
+      </c>
+      <c r="F49" s="13" t="s">
         <v>64</v>
-      </c>
-      <c r="E49" s="13">
-        <v>200600001</v>
-      </c>
-      <c r="F49" s="13" t="s">
-        <v>65</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>36</v>
@@ -4032,28 +4008,28 @@
         <v>1990000</v>
       </c>
       <c r="Q49" s="3"/>
-      <c r="R49"/>
-      <c r="S49" s="17"/>
+      <c r="R49" s="18"/>
+      <c r="S49" s="18"/>
     </row>
     <row r="50" spans="1:19">
       <c r="A50" s="1">
         <f t="shared" si="5"/>
-        <v>2007001</v>
+        <v>2005001</v>
       </c>
       <c r="B50" s="12">
-        <v>200700</v>
+        <v>200500</v>
       </c>
       <c r="C50" s="12">
         <v>2</v>
       </c>
       <c r="D50" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E50" s="13">
+        <v>200500025</v>
+      </c>
+      <c r="F50" s="13" t="s">
         <v>66</v>
-      </c>
-      <c r="E50" s="13">
-        <v>200700001</v>
-      </c>
-      <c r="F50" s="13" t="s">
-        <v>67</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>32</v>
@@ -4074,7 +4050,7 @@
         <v>33</v>
       </c>
       <c r="M50" s="23" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="N50">
         <v>5000</v>
@@ -4083,29 +4059,28 @@
         <v>1990000</v>
       </c>
       <c r="Q50" s="3"/>
-      <c r="R50" s="17"/>
-      <c r="S50" s="17"/>
-    </row>
-    <row r="51" s="1" customFormat="1" spans="1:19">
+      <c r="R50" s="18"/>
+      <c r="S50" s="18"/>
+    </row>
+    <row r="51" spans="1:19">
       <c r="A51" s="1">
         <f t="shared" si="5"/>
-        <v>2007002</v>
+        <v>2005002</v>
       </c>
       <c r="B51" s="12">
-        <v>200700</v>
+        <v>200500</v>
       </c>
       <c r="C51" s="12">
         <v>2</v>
       </c>
-      <c r="D51" s="12" t="str">
-        <f t="shared" ref="D48:D52" si="7">D50</f>
-        <v>越南色碟</v>
+      <c r="D51" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="E51" s="13">
-        <v>200700001</v>
+        <v>200500025</v>
       </c>
       <c r="F51" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>35</v>
@@ -4126,7 +4101,7 @@
         <v>33</v>
       </c>
       <c r="M51" s="23" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="N51">
         <v>500000</v>
@@ -4135,29 +4110,28 @@
         <v>1990000</v>
       </c>
       <c r="Q51" s="3"/>
-      <c r="R51" s="17"/>
-      <c r="S51" s="17"/>
-    </row>
-    <row r="52" s="1" customFormat="1" spans="1:19">
+      <c r="R51" s="18"/>
+      <c r="S51" s="18"/>
+    </row>
+    <row r="52" spans="1:19">
       <c r="A52" s="1">
         <f t="shared" si="5"/>
-        <v>2007003</v>
+        <v>2005003</v>
       </c>
       <c r="B52" s="12">
-        <v>200700</v>
+        <v>200500</v>
       </c>
       <c r="C52" s="12">
         <v>2</v>
       </c>
-      <c r="D52" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v>越南色碟</v>
+      <c r="D52" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="E52" s="13">
-        <v>200700001</v>
+        <v>200500025</v>
       </c>
       <c r="F52" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>36</v>
@@ -4178,7 +4152,7 @@
         <v>33</v>
       </c>
       <c r="M52" s="23" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="N52">
         <v>50000000</v>
@@ -4186,15 +4160,17 @@
       <c r="O52" s="15">
         <v>1990000</v>
       </c>
-      <c r="S52" s="3"/>
-    </row>
-    <row r="53" s="1" customFormat="1" spans="1:19">
+      <c r="Q52" s="3"/>
+      <c r="R52" s="18"/>
+      <c r="S52" s="18"/>
+    </row>
+    <row r="53" spans="1:19">
       <c r="A53" s="1">
         <f t="shared" si="5"/>
-        <v>2008001</v>
+        <v>2006001</v>
       </c>
       <c r="B53" s="12">
-        <v>200800</v>
+        <v>200600</v>
       </c>
       <c r="C53" s="12">
         <v>2</v>
@@ -4203,7 +4179,7 @@
         <v>68</v>
       </c>
       <c r="E53" s="13">
-        <v>200800001</v>
+        <v>200600001</v>
       </c>
       <c r="F53" s="13" t="s">
         <v>69</v>
@@ -4235,15 +4211,17 @@
       <c r="O53" s="15">
         <v>1990000</v>
       </c>
-      <c r="S53" s="3"/>
+      <c r="Q53" s="3"/>
+      <c r="R53" s="18"/>
+      <c r="S53" s="18"/>
     </row>
     <row r="54" s="1" customFormat="1" spans="1:19">
       <c r="A54" s="1">
         <f t="shared" si="5"/>
-        <v>2008002</v>
+        <v>2006002</v>
       </c>
       <c r="B54" s="12">
-        <v>200800</v>
+        <v>200600</v>
       </c>
       <c r="C54" s="12">
         <v>2</v>
@@ -4252,7 +4230,7 @@
         <v>68</v>
       </c>
       <c r="E54" s="13">
-        <v>200800001</v>
+        <v>200600001</v>
       </c>
       <c r="F54" s="13" t="s">
         <v>69</v>
@@ -4284,15 +4262,17 @@
       <c r="O54" s="15">
         <v>1990000</v>
       </c>
-      <c r="S54" s="3"/>
+      <c r="Q54" s="3"/>
+      <c r="R54" s="18"/>
+      <c r="S54" s="18"/>
     </row>
     <row r="55" s="1" customFormat="1" spans="1:19">
       <c r="A55" s="1">
         <f t="shared" si="5"/>
-        <v>2008003</v>
+        <v>2006003</v>
       </c>
       <c r="B55" s="12">
-        <v>200800</v>
+        <v>200600</v>
       </c>
       <c r="C55" s="12">
         <v>2</v>
@@ -4301,7 +4281,7 @@
         <v>68</v>
       </c>
       <c r="E55" s="13">
-        <v>200800001</v>
+        <v>200600001</v>
       </c>
       <c r="F55" s="13" t="s">
         <v>69</v>
@@ -4333,24 +4313,26 @@
       <c r="O55" s="15">
         <v>1990000</v>
       </c>
-      <c r="S55" s="3"/>
+      <c r="Q55" s="3"/>
+      <c r="R55"/>
+      <c r="S55" s="18"/>
     </row>
     <row r="56" spans="1:19">
       <c r="A56" s="1">
         <f t="shared" si="5"/>
-        <v>2009001</v>
-      </c>
-      <c r="B56" s="18">
-        <v>200900</v>
+        <v>2007001</v>
+      </c>
+      <c r="B56" s="12">
+        <v>200700</v>
       </c>
       <c r="C56" s="12">
         <v>2</v>
       </c>
-      <c r="D56" s="18" t="s">
+      <c r="D56" s="12" t="s">
         <v>70</v>
       </c>
       <c r="E56" s="13">
-        <v>200900001</v>
+        <v>200700001</v>
       </c>
       <c r="F56" s="13" t="s">
         <v>71</v>
@@ -4382,24 +4364,27 @@
       <c r="O56" s="15">
         <v>1990000</v>
       </c>
-    </row>
-    <row r="57" spans="1:19">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="18"/>
+      <c r="S56" s="18"/>
+    </row>
+    <row r="57" s="1" customFormat="1" spans="1:19">
       <c r="A57" s="1">
         <f t="shared" si="5"/>
-        <v>2009002</v>
+        <v>2007002</v>
       </c>
       <c r="B57" s="12">
-        <v>200900</v>
+        <v>200700</v>
       </c>
       <c r="C57" s="12">
         <v>2</v>
       </c>
       <c r="D57" s="12" t="str">
-        <f>D56</f>
-        <v>魚蝦蟹</v>
+        <f t="shared" ref="D54:D58" si="7">D56</f>
+        <v>越南色碟</v>
       </c>
       <c r="E57" s="13">
-        <v>200900001</v>
+        <v>200700001</v>
       </c>
       <c r="F57" s="13" t="s">
         <v>71</v>
@@ -4431,24 +4416,27 @@
       <c r="O57" s="15">
         <v>1990000</v>
       </c>
-    </row>
-    <row r="58" spans="1:19">
+      <c r="Q57" s="3"/>
+      <c r="R57" s="18"/>
+      <c r="S57" s="18"/>
+    </row>
+    <row r="58" s="1" customFormat="1" spans="1:19">
       <c r="A58" s="1">
         <f t="shared" si="5"/>
-        <v>2009003</v>
+        <v>2007003</v>
       </c>
       <c r="B58" s="12">
-        <v>200900</v>
+        <v>200700</v>
       </c>
       <c r="C58" s="12">
         <v>2</v>
       </c>
       <c r="D58" s="12" t="str">
-        <f>D57</f>
-        <v>魚蝦蟹</v>
+        <f t="shared" si="7"/>
+        <v>越南色碟</v>
       </c>
       <c r="E58" s="13">
-        <v>200900001</v>
+        <v>200700001</v>
       </c>
       <c r="F58" s="13" t="s">
         <v>71</v>
@@ -4480,25 +4468,28 @@
       <c r="O58" s="15">
         <v>1990000</v>
       </c>
-    </row>
-    <row r="59" spans="1:19">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" s="1" customFormat="1" spans="1:19">
       <c r="A59" s="1">
         <f t="shared" si="5"/>
-        <v>2010001</v>
+        <v>2008001</v>
       </c>
       <c r="B59" s="12">
-        <v>201000</v>
+        <v>200800</v>
       </c>
       <c r="C59" s="12">
         <v>2</v>
       </c>
-      <c r="D59" s="12" t="s">
+      <c r="D59" s="13" t="s">
         <v>72</v>
       </c>
       <c r="E59" s="13">
-        <v>101000006</v>
-      </c>
-      <c r="F59" s="13"/>
+        <v>200800001</v>
+      </c>
+      <c r="F59" s="13" t="s">
+        <v>73</v>
+      </c>
       <c r="G59" s="1" t="s">
         <v>32</v>
       </c>
@@ -4526,25 +4517,28 @@
       <c r="O59" s="15">
         <v>1990000</v>
       </c>
-    </row>
-    <row r="60" spans="1:19">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" s="1" customFormat="1" spans="1:19">
       <c r="A60" s="1">
         <f t="shared" si="5"/>
-        <v>2010002</v>
+        <v>2008002</v>
       </c>
       <c r="B60" s="12">
-        <v>201000</v>
+        <v>200800</v>
       </c>
       <c r="C60" s="12">
         <v>2</v>
       </c>
-      <c r="D60" s="12" t="s">
+      <c r="D60" s="13" t="s">
         <v>72</v>
       </c>
       <c r="E60" s="13">
-        <v>101000006</v>
-      </c>
-      <c r="F60" s="13"/>
+        <v>200800001</v>
+      </c>
+      <c r="F60" s="13" t="s">
+        <v>73</v>
+      </c>
       <c r="G60" s="1" t="s">
         <v>35</v>
       </c>
@@ -4572,25 +4566,28 @@
       <c r="O60" s="15">
         <v>1990000</v>
       </c>
-    </row>
-    <row r="61" spans="1:19">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" s="1" customFormat="1" spans="1:19">
       <c r="A61" s="1">
         <f t="shared" si="5"/>
-        <v>2010003</v>
+        <v>2008003</v>
       </c>
       <c r="B61" s="12">
-        <v>201000</v>
+        <v>200800</v>
       </c>
       <c r="C61" s="12">
         <v>2</v>
       </c>
-      <c r="D61" s="12" t="s">
+      <c r="D61" s="13" t="s">
         <v>72</v>
       </c>
       <c r="E61" s="13">
-        <v>101000006</v>
-      </c>
-      <c r="F61" s="13"/>
+        <v>200800001</v>
+      </c>
+      <c r="F61" s="13" t="s">
+        <v>73</v>
+      </c>
       <c r="G61" s="1" t="s">
         <v>36</v>
       </c>
@@ -4618,26 +4615,27 @@
       <c r="O61" s="15">
         <v>1990000</v>
       </c>
+      <c r="S61" s="3"/>
     </row>
     <row r="62" spans="1:19">
       <c r="A62" s="1">
         <f t="shared" si="5"/>
-        <v>3001001</v>
-      </c>
-      <c r="B62" s="12">
-        <v>300100</v>
+        <v>2009001</v>
+      </c>
+      <c r="B62" s="19">
+        <v>200900</v>
       </c>
       <c r="C62" s="12">
-        <v>3</v>
-      </c>
-      <c r="D62" s="12" t="s">
-        <v>73</v>
+        <v>2</v>
+      </c>
+      <c r="D62" s="19" t="s">
+        <v>74</v>
       </c>
       <c r="E62" s="13">
-        <v>300100001</v>
+        <v>200900001</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>32</v>
@@ -4654,11 +4652,11 @@
       <c r="K62" s="1">
         <v>0</v>
       </c>
-      <c r="L62" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="M62" s="24" t="s">
-        <v>76</v>
+      <c r="L62" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M62" s="23" t="s">
+        <v>34</v>
       </c>
       <c r="N62">
         <v>5000</v>
@@ -4667,25 +4665,26 @@
         <v>1990000</v>
       </c>
     </row>
-    <row r="63" s="1" customFormat="1" spans="1:19">
+    <row r="63" spans="1:19">
       <c r="A63" s="1">
         <f t="shared" si="5"/>
-        <v>3001002</v>
+        <v>2009002</v>
       </c>
       <c r="B63" s="12">
-        <v>300100</v>
+        <v>200900</v>
       </c>
       <c r="C63" s="12">
-        <v>3</v>
-      </c>
-      <c r="D63" s="12" t="s">
-        <v>73</v>
+        <v>2</v>
+      </c>
+      <c r="D63" s="12" t="str">
+        <f>D62</f>
+        <v>魚蝦蟹</v>
       </c>
       <c r="E63" s="13">
-        <v>300100001</v>
+        <v>200900001</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>35</v>
@@ -4702,11 +4701,11 @@
       <c r="K63" s="1">
         <v>0</v>
       </c>
-      <c r="L63" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="M63" s="24" t="s">
-        <v>76</v>
+      <c r="L63" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M63" s="23" t="s">
+        <v>34</v>
       </c>
       <c r="N63">
         <v>500000</v>
@@ -4714,27 +4713,27 @@
       <c r="O63" s="15">
         <v>1990000</v>
       </c>
-      <c r="S63" s="3"/>
-    </row>
-    <row r="64" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="64" spans="1:19">
       <c r="A64" s="1">
         <f t="shared" si="5"/>
-        <v>3001003</v>
+        <v>2009003</v>
       </c>
       <c r="B64" s="12">
-        <v>300100</v>
+        <v>200900</v>
       </c>
       <c r="C64" s="12">
-        <v>3</v>
-      </c>
-      <c r="D64" s="12" t="s">
-        <v>73</v>
+        <v>2</v>
+      </c>
+      <c r="D64" s="12" t="str">
+        <f>D63</f>
+        <v>魚蝦蟹</v>
       </c>
       <c r="E64" s="13">
-        <v>300100001</v>
+        <v>200900001</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>36</v>
@@ -4751,11 +4750,11 @@
       <c r="K64" s="1">
         <v>0</v>
       </c>
-      <c r="L64" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="M64" s="24" t="s">
-        <v>76</v>
+      <c r="L64" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M64" s="23" t="s">
+        <v>34</v>
       </c>
       <c r="N64">
         <v>50000000</v>
@@ -4763,28 +4762,25 @@
       <c r="O64" s="15">
         <v>1990000</v>
       </c>
-      <c r="S64" s="3"/>
-    </row>
-    <row r="65" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="65" spans="1:19">
       <c r="A65" s="1">
         <f t="shared" si="5"/>
-        <v>3002001</v>
+        <v>2010001</v>
       </c>
       <c r="B65" s="12">
-        <v>300200</v>
+        <v>201000</v>
       </c>
       <c r="C65" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E65" s="13">
-        <v>300200006</v>
-      </c>
-      <c r="F65" s="13" t="s">
-        <v>78</v>
-      </c>
+        <v>101000006</v>
+      </c>
+      <c r="F65" s="13"/>
       <c r="G65" s="1" t="s">
         <v>32</v>
       </c>
@@ -4792,7 +4788,7 @@
         <v>1</v>
       </c>
       <c r="I65" s="1">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="J65" s="1">
         <v>-1</v>
@@ -4800,11 +4796,11 @@
       <c r="K65" s="1">
         <v>0</v>
       </c>
-      <c r="L65" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="M65" s="24" t="s">
-        <v>76</v>
+      <c r="L65" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M65" s="23" t="s">
+        <v>34</v>
       </c>
       <c r="N65">
         <v>5000</v>
@@ -4812,28 +4808,25 @@
       <c r="O65" s="15">
         <v>1990000</v>
       </c>
-      <c r="S65" s="3"/>
-    </row>
-    <row r="66" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="66" spans="1:19">
       <c r="A66" s="1">
         <f t="shared" si="5"/>
-        <v>3002002</v>
+        <v>2010002</v>
       </c>
       <c r="B66" s="12">
-        <v>300200</v>
+        <v>201000</v>
       </c>
       <c r="C66" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E66" s="13">
-        <v>300200006</v>
-      </c>
-      <c r="F66" s="13" t="s">
-        <v>78</v>
-      </c>
+        <v>101000006</v>
+      </c>
+      <c r="F66" s="13"/>
       <c r="G66" s="1" t="s">
         <v>35</v>
       </c>
@@ -4849,11 +4842,11 @@
       <c r="K66" s="1">
         <v>0</v>
       </c>
-      <c r="L66" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="M66" s="24" t="s">
-        <v>76</v>
+      <c r="L66" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M66" s="23" t="s">
+        <v>34</v>
       </c>
       <c r="N66">
         <v>500000</v>
@@ -4861,28 +4854,25 @@
       <c r="O66" s="15">
         <v>1990000</v>
       </c>
-      <c r="S66" s="3"/>
-    </row>
-    <row r="67" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="67" spans="1:19">
       <c r="A67" s="1">
         <f t="shared" si="5"/>
-        <v>3002003</v>
+        <v>2010003</v>
       </c>
       <c r="B67" s="12">
-        <v>300200</v>
+        <v>201000</v>
       </c>
       <c r="C67" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E67" s="13">
-        <v>300200006</v>
-      </c>
-      <c r="F67" s="13" t="s">
-        <v>78</v>
-      </c>
+        <v>101000006</v>
+      </c>
+      <c r="F67" s="13"/>
       <c r="G67" s="1" t="s">
         <v>36</v>
       </c>
@@ -4898,11 +4888,11 @@
       <c r="K67" s="1">
         <v>0</v>
       </c>
-      <c r="L67" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="M67" s="24" t="s">
-        <v>76</v>
+      <c r="L67" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M67" s="23" t="s">
+        <v>34</v>
       </c>
       <c r="N67">
         <v>50000000</v>
@@ -4910,302 +4900,306 @@
       <c r="O67" s="15">
         <v>1990000</v>
       </c>
-      <c r="S67" s="3"/>
-    </row>
-    <row r="68" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="68" spans="1:19">
       <c r="A68" s="1">
-        <v>20010010</v>
-      </c>
-      <c r="B68" s="16">
-        <v>200100</v>
-      </c>
-      <c r="C68" s="16">
-        <v>2</v>
-      </c>
-      <c r="D68" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="E68" s="16">
-        <v>200100038</v>
-      </c>
-      <c r="F68" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="G68" s="19" t="s">
+        <f t="shared" si="5"/>
+        <v>3001001</v>
+      </c>
+      <c r="B68" s="12">
+        <v>300100</v>
+      </c>
+      <c r="C68" s="12">
+        <v>3</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="E68" s="13">
+        <v>300100001</v>
+      </c>
+      <c r="F68" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H68" s="1">
+        <v>1</v>
+      </c>
+      <c r="I68" s="1">
+        <v>0</v>
+      </c>
+      <c r="J68" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K68" s="1">
+        <v>0</v>
+      </c>
+      <c r="L68" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="M68" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="H68" s="19">
-        <v>10</v>
-      </c>
-      <c r="I68" s="19">
-        <v>0</v>
-      </c>
-      <c r="J68" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K68" s="19">
-        <v>0</v>
-      </c>
-      <c r="L68" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M68" s="19">
-        <v>0</v>
-      </c>
-      <c r="N68" s="20">
-        <v>200</v>
-      </c>
-      <c r="O68" s="21">
-        <v>1980000</v>
-      </c>
-      <c r="S68" s="3"/>
+      <c r="N68">
+        <v>5000</v>
+      </c>
+      <c r="O68" s="15">
+        <v>1990000</v>
+      </c>
     </row>
     <row r="69" s="1" customFormat="1" spans="1:19">
       <c r="A69" s="1">
-        <v>20010011</v>
-      </c>
-      <c r="B69" s="16">
-        <v>200100</v>
-      </c>
-      <c r="C69" s="16">
+        <f t="shared" si="5"/>
+        <v>3001002</v>
+      </c>
+      <c r="B69" s="12">
+        <v>300100</v>
+      </c>
+      <c r="C69" s="12">
+        <v>3</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="E69" s="13">
+        <v>300100001</v>
+      </c>
+      <c r="F69" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H69" s="1">
         <v>2</v>
       </c>
-      <c r="D69" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="E69" s="16">
-        <v>200100038</v>
-      </c>
-      <c r="F69" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="G69" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="H69" s="19">
-        <v>11</v>
-      </c>
-      <c r="I69" s="19">
-        <v>0</v>
-      </c>
-      <c r="J69" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K69" s="19">
-        <v>0</v>
-      </c>
-      <c r="L69" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M69" s="19">
-        <v>0</v>
-      </c>
-      <c r="N69" s="20">
-        <v>5000</v>
-      </c>
-      <c r="O69" s="21">
-        <v>1980000</v>
+      <c r="I69" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J69" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K69" s="1">
+        <v>0</v>
+      </c>
+      <c r="L69" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="M69" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="N69">
+        <v>500000</v>
+      </c>
+      <c r="O69" s="15">
+        <v>1990000</v>
       </c>
       <c r="S69" s="3"/>
     </row>
     <row r="70" s="1" customFormat="1" spans="1:19">
       <c r="A70" s="1">
-        <v>20010012</v>
-      </c>
-      <c r="B70" s="16">
-        <v>200100</v>
-      </c>
-      <c r="C70" s="16">
-        <v>2</v>
-      </c>
-      <c r="D70" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="E70" s="16">
-        <v>200100038</v>
-      </c>
-      <c r="F70" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="G70" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H70" s="19">
-        <v>12</v>
-      </c>
-      <c r="I70" s="19">
-        <v>0</v>
-      </c>
-      <c r="J70" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K70" s="19">
-        <v>0</v>
-      </c>
-      <c r="L70" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M70" s="19">
-        <v>0</v>
-      </c>
-      <c r="N70" s="20">
-        <v>100000</v>
-      </c>
-      <c r="O70" s="21">
-        <v>1980000</v>
+        <f t="shared" si="5"/>
+        <v>3001003</v>
+      </c>
+      <c r="B70" s="12">
+        <v>300100</v>
+      </c>
+      <c r="C70" s="12">
+        <v>3</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="E70" s="13">
+        <v>300100001</v>
+      </c>
+      <c r="F70" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H70" s="1">
+        <v>3</v>
+      </c>
+      <c r="I70" s="1">
+        <v>50000000</v>
+      </c>
+      <c r="J70" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K70" s="1">
+        <v>0</v>
+      </c>
+      <c r="L70" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="M70" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="N70">
+        <v>50000000</v>
+      </c>
+      <c r="O70" s="15">
+        <v>1990000</v>
       </c>
       <c r="S70" s="3"/>
     </row>
     <row r="71" s="1" customFormat="1" spans="1:19">
       <c r="A71" s="1">
-        <v>20010110</v>
-      </c>
-      <c r="B71" s="16">
-        <v>200101</v>
-      </c>
-      <c r="C71" s="16">
-        <v>2</v>
-      </c>
-      <c r="D71" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="E71" s="16">
-        <v>200101001</v>
-      </c>
-      <c r="F71" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="G71" s="19" t="s">
+        <f t="shared" si="5"/>
+        <v>3002001</v>
+      </c>
+      <c r="B71" s="12">
+        <v>300200</v>
+      </c>
+      <c r="C71" s="12">
+        <v>3</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="E71" s="13">
+        <v>300200006</v>
+      </c>
+      <c r="F71" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H71" s="1">
+        <v>1</v>
+      </c>
+      <c r="I71" s="1">
+        <v>2000</v>
+      </c>
+      <c r="J71" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K71" s="1">
+        <v>0</v>
+      </c>
+      <c r="L71" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="M71" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="H71" s="19">
-        <v>10</v>
-      </c>
-      <c r="I71" s="19">
-        <v>0</v>
-      </c>
-      <c r="J71" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K71" s="19">
-        <v>0</v>
-      </c>
-      <c r="L71" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M71" s="19">
-        <v>0</v>
-      </c>
-      <c r="N71" s="20">
-        <v>200</v>
-      </c>
-      <c r="O71" s="21">
-        <v>1980000</v>
+      <c r="N71">
+        <v>5000</v>
+      </c>
+      <c r="O71" s="15">
+        <v>1990000</v>
       </c>
       <c r="S71" s="3"/>
     </row>
     <row r="72" s="1" customFormat="1" spans="1:19">
       <c r="A72" s="1">
-        <v>20010111</v>
-      </c>
-      <c r="B72" s="16">
-        <v>200101</v>
-      </c>
-      <c r="C72" s="16">
+        <f t="shared" si="5"/>
+        <v>3002002</v>
+      </c>
+      <c r="B72" s="12">
+        <v>300200</v>
+      </c>
+      <c r="C72" s="12">
+        <v>3</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="E72" s="13">
+        <v>300200006</v>
+      </c>
+      <c r="F72" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H72" s="1">
         <v>2</v>
       </c>
-      <c r="D72" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="E72" s="16">
-        <v>200101001</v>
-      </c>
-      <c r="F72" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="G72" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="H72" s="19">
-        <v>11</v>
-      </c>
-      <c r="I72" s="19">
-        <v>0</v>
-      </c>
-      <c r="J72" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K72" s="19">
-        <v>0</v>
-      </c>
-      <c r="L72" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M72" s="19">
-        <v>0</v>
-      </c>
-      <c r="N72" s="20">
-        <v>5000</v>
-      </c>
-      <c r="O72" s="21">
-        <v>1980000</v>
+      <c r="I72" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J72" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K72" s="1">
+        <v>0</v>
+      </c>
+      <c r="L72" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="M72" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="N72">
+        <v>500000</v>
+      </c>
+      <c r="O72" s="15">
+        <v>1990000</v>
       </c>
       <c r="S72" s="3"/>
     </row>
     <row r="73" s="1" customFormat="1" spans="1:19">
       <c r="A73" s="1">
-        <v>20010112</v>
-      </c>
-      <c r="B73" s="16">
-        <v>200101</v>
-      </c>
-      <c r="C73" s="16">
-        <v>2</v>
-      </c>
-      <c r="D73" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="E73" s="16">
-        <v>200101001</v>
-      </c>
-      <c r="F73" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="G73" s="19" t="s">
+        <f t="shared" si="5"/>
+        <v>3002003</v>
+      </c>
+      <c r="B73" s="12">
+        <v>300200</v>
+      </c>
+      <c r="C73" s="12">
+        <v>3</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="E73" s="13">
+        <v>300200006</v>
+      </c>
+      <c r="F73" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H73" s="1">
+        <v>3</v>
+      </c>
+      <c r="I73" s="1">
+        <v>50000000</v>
+      </c>
+      <c r="J73" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K73" s="1">
+        <v>0</v>
+      </c>
+      <c r="L73" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="H73" s="19">
-        <v>12</v>
-      </c>
-      <c r="I73" s="19">
-        <v>0</v>
-      </c>
-      <c r="J73" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K73" s="19">
-        <v>0</v>
-      </c>
-      <c r="L73" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M73" s="19">
-        <v>0</v>
-      </c>
-      <c r="N73" s="20">
-        <v>100000</v>
-      </c>
-      <c r="O73" s="21">
-        <v>1980000</v>
+      <c r="M73" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="N73">
+        <v>50000000</v>
+      </c>
+      <c r="O73" s="15">
+        <v>1990000</v>
       </c>
       <c r="S73" s="3"/>
     </row>
     <row r="74" s="1" customFormat="1" spans="1:19">
       <c r="A74" s="1">
-        <v>20030010</v>
+        <v>20010010</v>
       </c>
       <c r="B74" s="16">
-        <v>200300</v>
+        <v>200100</v>
       </c>
       <c r="C74" s="16">
         <v>2</v>
@@ -5214,30 +5208,30 @@
         <v>57</v>
       </c>
       <c r="E74" s="16">
-        <v>200300001</v>
+        <v>200100038</v>
       </c>
       <c r="F74" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="G74" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H74" s="19">
+      <c r="G74" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="H74" s="17">
         <v>10</v>
       </c>
-      <c r="I74" s="19">
-        <v>0</v>
-      </c>
-      <c r="J74" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K74" s="19">
-        <v>0</v>
-      </c>
-      <c r="L74" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M74" s="19">
+      <c r="I74" s="17">
+        <v>0</v>
+      </c>
+      <c r="J74" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K74" s="17">
+        <v>0</v>
+      </c>
+      <c r="L74" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M74" s="17">
         <v>0</v>
       </c>
       <c r="N74" s="20">
@@ -5250,10 +5244,10 @@
     </row>
     <row r="75" s="1" customFormat="1" spans="1:19">
       <c r="A75" s="1">
-        <v>20030011</v>
+        <v>20010011</v>
       </c>
       <c r="B75" s="16">
-        <v>200300</v>
+        <v>200100</v>
       </c>
       <c r="C75" s="16">
         <v>2</v>
@@ -5262,30 +5256,30 @@
         <v>57</v>
       </c>
       <c r="E75" s="16">
-        <v>200300001</v>
+        <v>200100038</v>
       </c>
       <c r="F75" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="G75" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="H75" s="19">
+      <c r="G75" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H75" s="17">
         <v>11</v>
       </c>
-      <c r="I75" s="19">
-        <v>0</v>
-      </c>
-      <c r="J75" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K75" s="19">
-        <v>0</v>
-      </c>
-      <c r="L75" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M75" s="19">
+      <c r="I75" s="17">
+        <v>0</v>
+      </c>
+      <c r="J75" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K75" s="17">
+        <v>0</v>
+      </c>
+      <c r="L75" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M75" s="17">
         <v>0</v>
       </c>
       <c r="N75" s="20">
@@ -5298,10 +5292,10 @@
     </row>
     <row r="76" s="1" customFormat="1" spans="1:19">
       <c r="A76" s="1">
-        <v>20030012</v>
+        <v>20010012</v>
       </c>
       <c r="B76" s="16">
-        <v>200300</v>
+        <v>200100</v>
       </c>
       <c r="C76" s="16">
         <v>2</v>
@@ -5310,30 +5304,30 @@
         <v>57</v>
       </c>
       <c r="E76" s="16">
-        <v>200300001</v>
+        <v>200100038</v>
       </c>
       <c r="F76" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="G76" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H76" s="19">
+      <c r="G76" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="H76" s="17">
         <v>12</v>
       </c>
-      <c r="I76" s="19">
-        <v>0</v>
-      </c>
-      <c r="J76" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K76" s="19">
-        <v>0</v>
-      </c>
-      <c r="L76" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M76" s="19">
+      <c r="I76" s="17">
+        <v>0</v>
+      </c>
+      <c r="J76" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K76" s="17">
+        <v>0</v>
+      </c>
+      <c r="L76" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M76" s="17">
         <v>0</v>
       </c>
       <c r="N76" s="20">
@@ -5346,42 +5340,42 @@
     </row>
     <row r="77" s="1" customFormat="1" spans="1:19">
       <c r="A77" s="1">
-        <v>20040010</v>
+        <v>20010110</v>
       </c>
       <c r="B77" s="16">
-        <v>200400</v>
+        <v>200101</v>
       </c>
       <c r="C77" s="16">
         <v>2</v>
       </c>
-      <c r="D77" s="22" t="s">
+      <c r="D77" s="16" t="s">
         <v>59</v>
       </c>
       <c r="E77" s="16">
-        <v>200400009</v>
+        <v>200101001</v>
       </c>
       <c r="F77" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="G77" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H77" s="19">
+      <c r="G77" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="H77" s="17">
         <v>10</v>
       </c>
-      <c r="I77" s="19">
-        <v>0</v>
-      </c>
-      <c r="J77" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K77" s="19">
-        <v>0</v>
-      </c>
-      <c r="L77" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M77" s="19">
+      <c r="I77" s="17">
+        <v>0</v>
+      </c>
+      <c r="J77" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K77" s="17">
+        <v>0</v>
+      </c>
+      <c r="L77" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M77" s="17">
         <v>0</v>
       </c>
       <c r="N77" s="20">
@@ -5394,42 +5388,42 @@
     </row>
     <row r="78" s="1" customFormat="1" spans="1:19">
       <c r="A78" s="1">
-        <v>20040011</v>
+        <v>20010111</v>
       </c>
       <c r="B78" s="16">
-        <v>200400</v>
+        <v>200101</v>
       </c>
       <c r="C78" s="16">
         <v>2</v>
       </c>
-      <c r="D78" s="22" t="s">
+      <c r="D78" s="16" t="s">
         <v>59</v>
       </c>
       <c r="E78" s="16">
-        <v>200400009</v>
+        <v>200101001</v>
       </c>
       <c r="F78" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="G78" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="H78" s="19">
+      <c r="G78" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H78" s="17">
         <v>11</v>
       </c>
-      <c r="I78" s="19">
-        <v>0</v>
-      </c>
-      <c r="J78" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K78" s="19">
-        <v>0</v>
-      </c>
-      <c r="L78" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M78" s="19">
+      <c r="I78" s="17">
+        <v>0</v>
+      </c>
+      <c r="J78" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K78" s="17">
+        <v>0</v>
+      </c>
+      <c r="L78" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M78" s="17">
         <v>0</v>
       </c>
       <c r="N78" s="20">
@@ -5442,42 +5436,42 @@
     </row>
     <row r="79" s="1" customFormat="1" spans="1:19">
       <c r="A79" s="1">
-        <v>20040012</v>
+        <v>20010112</v>
       </c>
       <c r="B79" s="16">
-        <v>200400</v>
+        <v>200101</v>
       </c>
       <c r="C79" s="16">
         <v>2</v>
       </c>
-      <c r="D79" s="22" t="s">
+      <c r="D79" s="16" t="s">
         <v>59</v>
       </c>
       <c r="E79" s="16">
-        <v>200400009</v>
+        <v>200101001</v>
       </c>
       <c r="F79" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="G79" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H79" s="19">
+      <c r="G79" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="H79" s="17">
         <v>12</v>
       </c>
-      <c r="I79" s="19">
-        <v>0</v>
-      </c>
-      <c r="J79" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K79" s="19">
-        <v>0</v>
-      </c>
-      <c r="L79" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M79" s="19">
+      <c r="I79" s="17">
+        <v>0</v>
+      </c>
+      <c r="J79" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K79" s="17">
+        <v>0</v>
+      </c>
+      <c r="L79" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M79" s="17">
         <v>0</v>
       </c>
       <c r="N79" s="20">
@@ -5490,10 +5484,10 @@
     </row>
     <row r="80" s="1" customFormat="1" spans="1:19">
       <c r="A80" s="1">
-        <v>20050010</v>
+        <v>20030010</v>
       </c>
       <c r="B80" s="16">
-        <v>200500</v>
+        <v>200300</v>
       </c>
       <c r="C80" s="16">
         <v>2</v>
@@ -5502,30 +5496,30 @@
         <v>61</v>
       </c>
       <c r="E80" s="16">
-        <v>200500025</v>
+        <v>200300001</v>
       </c>
       <c r="F80" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="G80" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H80" s="19">
+      <c r="G80" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="H80" s="17">
         <v>10</v>
       </c>
-      <c r="I80" s="19">
-        <v>0</v>
-      </c>
-      <c r="J80" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K80" s="19">
-        <v>0</v>
-      </c>
-      <c r="L80" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M80" s="19">
+      <c r="I80" s="17">
+        <v>0</v>
+      </c>
+      <c r="J80" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K80" s="17">
+        <v>0</v>
+      </c>
+      <c r="L80" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M80" s="17">
         <v>0</v>
       </c>
       <c r="N80" s="20">
@@ -5538,10 +5532,10 @@
     </row>
     <row r="81" s="1" customFormat="1" spans="1:19">
       <c r="A81" s="1">
-        <v>20050011</v>
+        <v>20030011</v>
       </c>
       <c r="B81" s="16">
-        <v>200500</v>
+        <v>200300</v>
       </c>
       <c r="C81" s="16">
         <v>2</v>
@@ -5550,30 +5544,30 @@
         <v>61</v>
       </c>
       <c r="E81" s="16">
-        <v>200500025</v>
+        <v>200300001</v>
       </c>
       <c r="F81" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="G81" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="H81" s="19">
+      <c r="G81" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H81" s="17">
         <v>11</v>
       </c>
-      <c r="I81" s="19">
-        <v>0</v>
-      </c>
-      <c r="J81" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K81" s="19">
-        <v>0</v>
-      </c>
-      <c r="L81" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M81" s="19">
+      <c r="I81" s="17">
+        <v>0</v>
+      </c>
+      <c r="J81" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K81" s="17">
+        <v>0</v>
+      </c>
+      <c r="L81" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M81" s="17">
         <v>0</v>
       </c>
       <c r="N81" s="20">
@@ -5586,10 +5580,10 @@
     </row>
     <row r="82" s="1" customFormat="1" spans="1:19">
       <c r="A82" s="1">
-        <v>20050012</v>
+        <v>20030012</v>
       </c>
       <c r="B82" s="16">
-        <v>200500</v>
+        <v>200300</v>
       </c>
       <c r="C82" s="16">
         <v>2</v>
@@ -5598,30 +5592,30 @@
         <v>61</v>
       </c>
       <c r="E82" s="16">
-        <v>200500025</v>
+        <v>200300001</v>
       </c>
       <c r="F82" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="G82" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H82" s="19">
+      <c r="G82" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="H82" s="17">
         <v>12</v>
       </c>
-      <c r="I82" s="19">
-        <v>0</v>
-      </c>
-      <c r="J82" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K82" s="19">
-        <v>0</v>
-      </c>
-      <c r="L82" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M82" s="19">
+      <c r="I82" s="17">
+        <v>0</v>
+      </c>
+      <c r="J82" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K82" s="17">
+        <v>0</v>
+      </c>
+      <c r="L82" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M82" s="17">
         <v>0</v>
       </c>
       <c r="N82" s="20">
@@ -5632,44 +5626,44 @@
       </c>
       <c r="S82" s="3"/>
     </row>
-    <row r="83" spans="1:19">
+    <row r="83" s="1" customFormat="1" spans="1:19">
       <c r="A83" s="1">
-        <v>20060010</v>
+        <v>20040010</v>
       </c>
       <c r="B83" s="16">
-        <v>200600</v>
+        <v>200400</v>
       </c>
       <c r="C83" s="16">
         <v>2</v>
       </c>
-      <c r="D83" s="16" t="s">
+      <c r="D83" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="E83" s="16">
+        <v>200400009</v>
+      </c>
+      <c r="F83" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="E83" s="16">
-        <v>200600001</v>
-      </c>
-      <c r="F83" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="G83" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H83" s="19">
+      <c r="G83" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="H83" s="17">
         <v>10</v>
       </c>
-      <c r="I83" s="19">
-        <v>0</v>
-      </c>
-      <c r="J83" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K83" s="19">
-        <v>0</v>
-      </c>
-      <c r="L83" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M83" s="19">
+      <c r="I83" s="17">
+        <v>0</v>
+      </c>
+      <c r="J83" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K83" s="17">
+        <v>0</v>
+      </c>
+      <c r="L83" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M83" s="17">
         <v>0</v>
       </c>
       <c r="N83" s="20">
@@ -5678,45 +5672,46 @@
       <c r="O83" s="21">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="84" spans="1:19">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" s="1" customFormat="1" spans="1:19">
       <c r="A84" s="1">
-        <v>20060011</v>
+        <v>20040011</v>
       </c>
       <c r="B84" s="16">
-        <v>200600</v>
+        <v>200400</v>
       </c>
       <c r="C84" s="16">
         <v>2</v>
       </c>
-      <c r="D84" s="16" t="s">
+      <c r="D84" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="E84" s="16">
+        <v>200400009</v>
+      </c>
+      <c r="F84" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="E84" s="16">
-        <v>200600001</v>
-      </c>
-      <c r="F84" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="G84" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="H84" s="19">
+      <c r="G84" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H84" s="17">
         <v>11</v>
       </c>
-      <c r="I84" s="19">
-        <v>0</v>
-      </c>
-      <c r="J84" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K84" s="19">
-        <v>0</v>
-      </c>
-      <c r="L84" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M84" s="19">
+      <c r="I84" s="17">
+        <v>0</v>
+      </c>
+      <c r="J84" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K84" s="17">
+        <v>0</v>
+      </c>
+      <c r="L84" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M84" s="17">
         <v>0</v>
       </c>
       <c r="N84" s="20">
@@ -5725,45 +5720,46 @@
       <c r="O84" s="21">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="85" spans="1:19">
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" s="1" customFormat="1" spans="1:19">
       <c r="A85" s="1">
-        <v>20060012</v>
+        <v>20040012</v>
       </c>
       <c r="B85" s="16">
-        <v>200600</v>
+        <v>200400</v>
       </c>
       <c r="C85" s="16">
         <v>2</v>
       </c>
-      <c r="D85" s="16" t="s">
+      <c r="D85" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="E85" s="16">
+        <v>200400009</v>
+      </c>
+      <c r="F85" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="E85" s="16">
-        <v>200600001</v>
-      </c>
-      <c r="F85" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="G85" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H85" s="19">
+      <c r="G85" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="H85" s="17">
         <v>12</v>
       </c>
-      <c r="I85" s="19">
-        <v>0</v>
-      </c>
-      <c r="J85" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K85" s="19">
-        <v>0</v>
-      </c>
-      <c r="L85" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M85" s="19">
+      <c r="I85" s="17">
+        <v>0</v>
+      </c>
+      <c r="J85" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K85" s="17">
+        <v>0</v>
+      </c>
+      <c r="L85" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M85" s="17">
         <v>0</v>
       </c>
       <c r="N85" s="20">
@@ -5772,45 +5768,46 @@
       <c r="O85" s="21">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="86" spans="1:19">
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" s="1" customFormat="1" spans="1:19">
       <c r="A86" s="1">
-        <v>20070010</v>
+        <v>20050010</v>
       </c>
       <c r="B86" s="16">
-        <v>200700</v>
+        <v>200500</v>
       </c>
       <c r="C86" s="16">
         <v>2</v>
       </c>
       <c r="D86" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E86" s="16">
+        <v>200500025</v>
+      </c>
+      <c r="F86" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="E86" s="16">
-        <v>200700001</v>
-      </c>
-      <c r="F86" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="G86" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H86" s="19">
+      <c r="G86" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="H86" s="17">
         <v>10</v>
       </c>
-      <c r="I86" s="19">
-        <v>0</v>
-      </c>
-      <c r="J86" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K86" s="19">
-        <v>0</v>
-      </c>
-      <c r="L86" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M86" s="19">
+      <c r="I86" s="17">
+        <v>0</v>
+      </c>
+      <c r="J86" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K86" s="17">
+        <v>0</v>
+      </c>
+      <c r="L86" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M86" s="17">
         <v>0</v>
       </c>
       <c r="N86" s="20">
@@ -5819,46 +5816,46 @@
       <c r="O86" s="21">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="87" spans="1:19">
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" s="1" customFormat="1" spans="1:19">
       <c r="A87" s="1">
-        <v>20070011</v>
+        <v>20050011</v>
       </c>
       <c r="B87" s="16">
-        <v>200700</v>
+        <v>200500</v>
       </c>
       <c r="C87" s="16">
         <v>2</v>
       </c>
-      <c r="D87" s="16" t="str">
-        <f>D86</f>
-        <v>越南色碟</v>
+      <c r="D87" s="16" t="s">
+        <v>65</v>
       </c>
       <c r="E87" s="16">
-        <v>200700001</v>
+        <v>200500025</v>
       </c>
       <c r="F87" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="G87" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="H87" s="19">
+        <v>66</v>
+      </c>
+      <c r="G87" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H87" s="17">
         <v>11</v>
       </c>
-      <c r="I87" s="19">
-        <v>0</v>
-      </c>
-      <c r="J87" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K87" s="19">
-        <v>0</v>
-      </c>
-      <c r="L87" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M87" s="19">
+      <c r="I87" s="17">
+        <v>0</v>
+      </c>
+      <c r="J87" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K87" s="17">
+        <v>0</v>
+      </c>
+      <c r="L87" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M87" s="17">
         <v>0</v>
       </c>
       <c r="N87" s="20">
@@ -5867,46 +5864,46 @@
       <c r="O87" s="21">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="88" spans="1:19">
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" s="1" customFormat="1" spans="1:19">
       <c r="A88" s="1">
-        <v>20070012</v>
+        <v>20050012</v>
       </c>
       <c r="B88" s="16">
-        <v>200700</v>
+        <v>200500</v>
       </c>
       <c r="C88" s="16">
         <v>2</v>
       </c>
-      <c r="D88" s="16" t="str">
-        <f>D87</f>
-        <v>越南色碟</v>
+      <c r="D88" s="16" t="s">
+        <v>65</v>
       </c>
       <c r="E88" s="16">
-        <v>200700001</v>
+        <v>200500025</v>
       </c>
       <c r="F88" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="G88" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H88" s="19">
+        <v>66</v>
+      </c>
+      <c r="G88" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="H88" s="17">
         <v>12</v>
       </c>
-      <c r="I88" s="19">
-        <v>0</v>
-      </c>
-      <c r="J88" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K88" s="19">
-        <v>0</v>
-      </c>
-      <c r="L88" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M88" s="19">
+      <c r="I88" s="17">
+        <v>0</v>
+      </c>
+      <c r="J88" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K88" s="17">
+        <v>0</v>
+      </c>
+      <c r="L88" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M88" s="17">
         <v>0</v>
       </c>
       <c r="N88" s="20">
@@ -5915,13 +5912,14 @@
       <c r="O88" s="21">
         <v>1980000</v>
       </c>
+      <c r="S88" s="3"/>
     </row>
     <row r="89" spans="1:19">
       <c r="A89" s="1">
-        <v>20080010</v>
+        <v>20060010</v>
       </c>
       <c r="B89" s="16">
-        <v>200800</v>
+        <v>200600</v>
       </c>
       <c r="C89" s="16">
         <v>2</v>
@@ -5930,30 +5928,30 @@
         <v>68</v>
       </c>
       <c r="E89" s="16">
-        <v>200800001</v>
+        <v>200600001</v>
       </c>
       <c r="F89" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="G89" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H89" s="19">
+      <c r="G89" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="H89" s="17">
         <v>10</v>
       </c>
-      <c r="I89" s="19">
-        <v>0</v>
-      </c>
-      <c r="J89" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K89" s="19">
-        <v>0</v>
-      </c>
-      <c r="L89" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M89" s="19">
+      <c r="I89" s="17">
+        <v>0</v>
+      </c>
+      <c r="J89" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K89" s="17">
+        <v>0</v>
+      </c>
+      <c r="L89" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M89" s="17">
         <v>0</v>
       </c>
       <c r="N89" s="20">
@@ -5965,10 +5963,10 @@
     </row>
     <row r="90" spans="1:19">
       <c r="A90" s="1">
-        <v>20080011</v>
+        <v>20060011</v>
       </c>
       <c r="B90" s="16">
-        <v>200800</v>
+        <v>200600</v>
       </c>
       <c r="C90" s="16">
         <v>2</v>
@@ -5977,30 +5975,30 @@
         <v>68</v>
       </c>
       <c r="E90" s="16">
-        <v>200800001</v>
+        <v>200600001</v>
       </c>
       <c r="F90" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="G90" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="H90" s="19">
+      <c r="G90" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H90" s="17">
         <v>11</v>
       </c>
-      <c r="I90" s="19">
-        <v>0</v>
-      </c>
-      <c r="J90" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K90" s="19">
-        <v>0</v>
-      </c>
-      <c r="L90" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M90" s="19">
+      <c r="I90" s="17">
+        <v>0</v>
+      </c>
+      <c r="J90" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K90" s="17">
+        <v>0</v>
+      </c>
+      <c r="L90" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M90" s="17">
         <v>0</v>
       </c>
       <c r="N90" s="20">
@@ -6012,10 +6010,10 @@
     </row>
     <row r="91" spans="1:19">
       <c r="A91" s="1">
-        <v>20080012</v>
+        <v>20060012</v>
       </c>
       <c r="B91" s="16">
-        <v>200800</v>
+        <v>200600</v>
       </c>
       <c r="C91" s="16">
         <v>2</v>
@@ -6024,30 +6022,30 @@
         <v>68</v>
       </c>
       <c r="E91" s="16">
-        <v>200800001</v>
+        <v>200600001</v>
       </c>
       <c r="F91" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="G91" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H91" s="19">
+      <c r="G91" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="H91" s="17">
         <v>12</v>
       </c>
-      <c r="I91" s="19">
-        <v>0</v>
-      </c>
-      <c r="J91" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K91" s="19">
-        <v>0</v>
-      </c>
-      <c r="L91" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M91" s="19">
+      <c r="I91" s="17">
+        <v>0</v>
+      </c>
+      <c r="J91" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K91" s="17">
+        <v>0</v>
+      </c>
+      <c r="L91" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M91" s="17">
         <v>0</v>
       </c>
       <c r="N91" s="20">
@@ -6059,10 +6057,10 @@
     </row>
     <row r="92" spans="1:19">
       <c r="A92" s="1">
-        <v>20090010</v>
+        <v>20070010</v>
       </c>
       <c r="B92" s="16">
-        <v>200900</v>
+        <v>200700</v>
       </c>
       <c r="C92" s="16">
         <v>2</v>
@@ -6071,30 +6069,30 @@
         <v>70</v>
       </c>
       <c r="E92" s="16">
-        <v>200900001</v>
+        <v>200700001</v>
       </c>
       <c r="F92" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="G92" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H92" s="19">
+      <c r="G92" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="H92" s="17">
         <v>10</v>
       </c>
-      <c r="I92" s="19">
-        <v>0</v>
-      </c>
-      <c r="J92" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K92" s="19">
-        <v>0</v>
-      </c>
-      <c r="L92" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M92" s="19">
+      <c r="I92" s="17">
+        <v>0</v>
+      </c>
+      <c r="J92" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K92" s="17">
+        <v>0</v>
+      </c>
+      <c r="L92" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M92" s="17">
         <v>0</v>
       </c>
       <c r="N92" s="20">
@@ -6106,42 +6104,43 @@
     </row>
     <row r="93" spans="1:19">
       <c r="A93" s="1">
-        <v>20090011</v>
+        <v>20070011</v>
       </c>
       <c r="B93" s="16">
-        <v>200900</v>
+        <v>200700</v>
       </c>
       <c r="C93" s="16">
         <v>2</v>
       </c>
-      <c r="D93" s="16" t="s">
-        <v>70</v>
+      <c r="D93" s="16" t="str">
+        <f>D92</f>
+        <v>越南色碟</v>
       </c>
       <c r="E93" s="16">
-        <v>200900001</v>
+        <v>200700001</v>
       </c>
       <c r="F93" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="G93" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="H93" s="19">
+      <c r="G93" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H93" s="17">
         <v>11</v>
       </c>
-      <c r="I93" s="19">
-        <v>0</v>
-      </c>
-      <c r="J93" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K93" s="19">
-        <v>0</v>
-      </c>
-      <c r="L93" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M93" s="19">
+      <c r="I93" s="17">
+        <v>0</v>
+      </c>
+      <c r="J93" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K93" s="17">
+        <v>0</v>
+      </c>
+      <c r="L93" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M93" s="17">
         <v>0</v>
       </c>
       <c r="N93" s="20">
@@ -6153,42 +6152,43 @@
     </row>
     <row r="94" spans="1:19">
       <c r="A94" s="1">
-        <v>20090012</v>
+        <v>20070012</v>
       </c>
       <c r="B94" s="16">
-        <v>200900</v>
+        <v>200700</v>
       </c>
       <c r="C94" s="16">
         <v>2</v>
       </c>
-      <c r="D94" s="16" t="s">
-        <v>70</v>
+      <c r="D94" s="16" t="str">
+        <f>D93</f>
+        <v>越南色碟</v>
       </c>
       <c r="E94" s="16">
-        <v>200900001</v>
+        <v>200700001</v>
       </c>
       <c r="F94" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="G94" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H94" s="19">
+      <c r="G94" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="H94" s="17">
         <v>12</v>
       </c>
-      <c r="I94" s="19">
-        <v>0</v>
-      </c>
-      <c r="J94" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K94" s="19">
-        <v>0</v>
-      </c>
-      <c r="L94" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M94" s="19">
+      <c r="I94" s="17">
+        <v>0</v>
+      </c>
+      <c r="J94" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K94" s="17">
+        <v>0</v>
+      </c>
+      <c r="L94" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M94" s="17">
         <v>0</v>
       </c>
       <c r="N94" s="20">
@@ -6198,44 +6198,44 @@
         <v>1980000</v>
       </c>
     </row>
-    <row r="95" s="1" customFormat="1" spans="1:19">
+    <row r="95" spans="1:19">
       <c r="A95" s="1">
-        <v>30020010</v>
+        <v>20080010</v>
       </c>
       <c r="B95" s="16">
-        <v>300200</v>
+        <v>200800</v>
       </c>
       <c r="C95" s="16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D95" s="16" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E95" s="16">
-        <v>300200006</v>
+        <v>200800001</v>
       </c>
       <c r="F95" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="G95" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H95" s="19">
+        <v>73</v>
+      </c>
+      <c r="G95" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="H95" s="17">
         <v>10</v>
       </c>
-      <c r="I95" s="19">
-        <v>0</v>
-      </c>
-      <c r="J95" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K95" s="19">
-        <v>0</v>
-      </c>
-      <c r="L95" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="M95" s="19">
+      <c r="I95" s="17">
+        <v>0</v>
+      </c>
+      <c r="J95" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K95" s="17">
+        <v>0</v>
+      </c>
+      <c r="L95" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M95" s="17">
         <v>0</v>
       </c>
       <c r="N95" s="20">
@@ -6244,46 +6244,45 @@
       <c r="O95" s="21">
         <v>1980000</v>
       </c>
-      <c r="S95" s="3"/>
-    </row>
-    <row r="96" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="96" spans="1:19">
       <c r="A96" s="1">
-        <v>30020011</v>
+        <v>20080011</v>
       </c>
       <c r="B96" s="16">
-        <v>300200</v>
+        <v>200800</v>
       </c>
       <c r="C96" s="16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D96" s="16" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E96" s="16">
-        <v>300200006</v>
+        <v>200800001</v>
       </c>
       <c r="F96" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="G96" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="H96" s="19">
+        <v>73</v>
+      </c>
+      <c r="G96" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H96" s="17">
         <v>11</v>
       </c>
-      <c r="I96" s="19">
-        <v>0</v>
-      </c>
-      <c r="J96" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K96" s="19">
-        <v>0</v>
-      </c>
-      <c r="L96" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="M96" s="19">
+      <c r="I96" s="17">
+        <v>0</v>
+      </c>
+      <c r="J96" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K96" s="17">
+        <v>0</v>
+      </c>
+      <c r="L96" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M96" s="17">
         <v>0</v>
       </c>
       <c r="N96" s="20">
@@ -6292,46 +6291,45 @@
       <c r="O96" s="21">
         <v>1980000</v>
       </c>
-      <c r="S96" s="3"/>
-    </row>
-    <row r="97" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="97" spans="1:19">
       <c r="A97" s="1">
-        <v>30020012</v>
+        <v>20080012</v>
       </c>
       <c r="B97" s="16">
-        <v>300200</v>
+        <v>200800</v>
       </c>
       <c r="C97" s="16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D97" s="16" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E97" s="16">
-        <v>300200006</v>
+        <v>200800001</v>
       </c>
       <c r="F97" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="G97" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H97" s="19">
+        <v>73</v>
+      </c>
+      <c r="G97" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="H97" s="17">
         <v>12</v>
       </c>
-      <c r="I97" s="19">
-        <v>0</v>
-      </c>
-      <c r="J97" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K97" s="19">
-        <v>0</v>
-      </c>
-      <c r="L97" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="M97" s="19">
+      <c r="I97" s="17">
+        <v>0</v>
+      </c>
+      <c r="J97" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K97" s="17">
+        <v>0</v>
+      </c>
+      <c r="L97" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M97" s="17">
         <v>0</v>
       </c>
       <c r="N97" s="20">
@@ -6340,1147 +6338,1149 @@
       <c r="O97" s="21">
         <v>1980000</v>
       </c>
-      <c r="S97" s="3"/>
     </row>
     <row r="98" spans="1:19">
-      <c r="A98" s="1" t="s">
+      <c r="A98" s="1">
+        <v>20090010</v>
+      </c>
+      <c r="B98" s="16">
+        <v>200900</v>
+      </c>
+      <c r="C98" s="16">
+        <v>2</v>
+      </c>
+      <c r="D98" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="E98" s="16">
+        <v>200900001</v>
+      </c>
+      <c r="F98" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="G98" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="H98" s="17">
+        <v>10</v>
+      </c>
+      <c r="I98" s="17">
+        <v>0</v>
+      </c>
+      <c r="J98" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K98" s="17">
+        <v>0</v>
+      </c>
+      <c r="L98" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="B98" s="16">
-        <v>100100</v>
-      </c>
-      <c r="C98" s="16">
-        <v>1</v>
-      </c>
-      <c r="D98" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="E98" s="16">
-        <v>100100026</v>
-      </c>
-      <c r="F98" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="G98" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H98" s="19">
-        <v>10</v>
-      </c>
-      <c r="I98" s="19">
-        <v>0</v>
-      </c>
-      <c r="J98" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K98" s="19">
-        <v>0</v>
-      </c>
-      <c r="L98" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M98" s="19">
+      <c r="M98" s="17">
         <v>0</v>
       </c>
       <c r="N98" s="20">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="O98" s="21">
         <v>1980000</v>
       </c>
     </row>
     <row r="99" spans="1:19">
-      <c r="A99" s="1" t="s">
+      <c r="A99" s="1">
+        <v>20090011</v>
+      </c>
+      <c r="B99" s="16">
+        <v>200900</v>
+      </c>
+      <c r="C99" s="16">
+        <v>2</v>
+      </c>
+      <c r="D99" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="E99" s="16">
+        <v>200900001</v>
+      </c>
+      <c r="F99" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="G99" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="B99" s="16">
-        <v>100100</v>
-      </c>
-      <c r="C99" s="16">
-        <v>1</v>
-      </c>
-      <c r="D99" s="16" t="str">
-        <f t="shared" ref="D99:D103" si="8">D98</f>
-        <v>金礦大亨</v>
-      </c>
-      <c r="E99" s="16">
-        <v>100100026</v>
-      </c>
-      <c r="F99" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="G99" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="H99" s="19">
+      <c r="H99" s="17">
         <v>11</v>
       </c>
-      <c r="I99" s="19">
-        <v>0</v>
-      </c>
-      <c r="J99" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K99" s="19">
-        <v>0</v>
-      </c>
-      <c r="L99" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M99" s="19">
+      <c r="I99" s="17">
+        <v>0</v>
+      </c>
+      <c r="J99" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K99" s="17">
+        <v>0</v>
+      </c>
+      <c r="L99" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M99" s="17">
         <v>0</v>
       </c>
       <c r="N99" s="20">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="O99" s="21">
         <v>1980000</v>
       </c>
     </row>
     <row r="100" spans="1:19">
-      <c r="A100" s="1" t="s">
+      <c r="A100" s="1">
+        <v>20090012</v>
+      </c>
+      <c r="B100" s="16">
+        <v>200900</v>
+      </c>
+      <c r="C100" s="16">
+        <v>2</v>
+      </c>
+      <c r="D100" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="E100" s="16">
+        <v>200900001</v>
+      </c>
+      <c r="F100" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="G100" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="B100" s="16">
+      <c r="H100" s="17">
+        <v>12</v>
+      </c>
+      <c r="I100" s="17">
+        <v>0</v>
+      </c>
+      <c r="J100" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K100" s="17">
+        <v>0</v>
+      </c>
+      <c r="L100" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M100" s="17">
+        <v>0</v>
+      </c>
+      <c r="N100" s="20">
+        <v>100000</v>
+      </c>
+      <c r="O100" s="21">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="101" s="1" customFormat="1" spans="1:19">
+      <c r="A101" s="1">
+        <v>30020010</v>
+      </c>
+      <c r="B101" s="16">
+        <v>300200</v>
+      </c>
+      <c r="C101" s="16">
+        <v>3</v>
+      </c>
+      <c r="D101" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="E101" s="16">
+        <v>300200006</v>
+      </c>
+      <c r="F101" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G101" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="H101" s="17">
+        <v>10</v>
+      </c>
+      <c r="I101" s="17">
+        <v>0</v>
+      </c>
+      <c r="J101" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K101" s="17">
+        <v>0</v>
+      </c>
+      <c r="L101" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="M101" s="17">
+        <v>0</v>
+      </c>
+      <c r="N101" s="20">
+        <v>200</v>
+      </c>
+      <c r="O101" s="21">
+        <v>1980000</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" s="1" customFormat="1" spans="1:19">
+      <c r="A102" s="1">
+        <v>30020011</v>
+      </c>
+      <c r="B102" s="16">
+        <v>300200</v>
+      </c>
+      <c r="C102" s="16">
+        <v>3</v>
+      </c>
+      <c r="D102" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="E102" s="16">
+        <v>300200006</v>
+      </c>
+      <c r="F102" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G102" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H102" s="17">
+        <v>11</v>
+      </c>
+      <c r="I102" s="17">
+        <v>0</v>
+      </c>
+      <c r="J102" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K102" s="17">
+        <v>0</v>
+      </c>
+      <c r="L102" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="M102" s="17">
+        <v>0</v>
+      </c>
+      <c r="N102" s="20">
+        <v>5000</v>
+      </c>
+      <c r="O102" s="21">
+        <v>1980000</v>
+      </c>
+      <c r="S102" s="3"/>
+    </row>
+    <row r="103" s="1" customFormat="1" spans="1:19">
+      <c r="A103" s="1">
+        <v>30020012</v>
+      </c>
+      <c r="B103" s="16">
+        <v>300200</v>
+      </c>
+      <c r="C103" s="16">
+        <v>3</v>
+      </c>
+      <c r="D103" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="E103" s="16">
+        <v>300200006</v>
+      </c>
+      <c r="F103" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G103" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="H103" s="17">
+        <v>12</v>
+      </c>
+      <c r="I103" s="17">
+        <v>0</v>
+      </c>
+      <c r="J103" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K103" s="17">
+        <v>0</v>
+      </c>
+      <c r="L103" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="M103" s="17">
+        <v>0</v>
+      </c>
+      <c r="N103" s="20">
+        <v>100000</v>
+      </c>
+      <c r="O103" s="21">
+        <v>1980000</v>
+      </c>
+      <c r="S103" s="3"/>
+    </row>
+    <row r="104" spans="1:19">
+      <c r="A104" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B104" s="16">
         <v>100100</v>
       </c>
-      <c r="C100" s="16">
-        <v>1</v>
-      </c>
-      <c r="D100" s="16" t="str">
+      <c r="C104" s="16">
+        <v>1</v>
+      </c>
+      <c r="D104" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="E104" s="16">
+        <v>100100026</v>
+      </c>
+      <c r="F104" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="G104" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="H104" s="17">
+        <v>10</v>
+      </c>
+      <c r="I104" s="17">
+        <v>0</v>
+      </c>
+      <c r="J104" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K104" s="17">
+        <v>0</v>
+      </c>
+      <c r="L104" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M104" s="17">
+        <v>0</v>
+      </c>
+      <c r="N104" s="20">
+        <v>50</v>
+      </c>
+      <c r="O104" s="21">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="105" spans="1:19">
+      <c r="A105" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B105" s="16">
+        <v>100100</v>
+      </c>
+      <c r="C105" s="16">
+        <v>1</v>
+      </c>
+      <c r="D105" s="16" t="str">
+        <f t="shared" ref="D105:D109" si="8">D104</f>
+        <v>金礦大亨</v>
+      </c>
+      <c r="E105" s="16">
+        <v>100100026</v>
+      </c>
+      <c r="F105" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="G105" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H105" s="17">
+        <v>11</v>
+      </c>
+      <c r="I105" s="17">
+        <v>0</v>
+      </c>
+      <c r="J105" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K105" s="17">
+        <v>0</v>
+      </c>
+      <c r="L105" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M105" s="17">
+        <v>0</v>
+      </c>
+      <c r="N105" s="20">
+        <v>500</v>
+      </c>
+      <c r="O105" s="21">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="106" spans="1:19">
+      <c r="A106" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B106" s="16">
+        <v>100100</v>
+      </c>
+      <c r="C106" s="16">
+        <v>1</v>
+      </c>
+      <c r="D106" s="16" t="str">
         <f t="shared" si="8"/>
         <v>金礦大亨</v>
       </c>
-      <c r="E100" s="16">
+      <c r="E106" s="16">
         <v>100100026</v>
       </c>
-      <c r="F100" s="16" t="s">
+      <c r="F106" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="G100" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H100" s="19">
+      <c r="G106" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="H106" s="17">
         <v>12</v>
       </c>
-      <c r="I100" s="19">
-        <v>0</v>
-      </c>
-      <c r="J100" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K100" s="19">
-        <v>0</v>
-      </c>
-      <c r="L100" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M100" s="19">
-        <v>0</v>
-      </c>
-      <c r="N100" s="20">
+      <c r="I106" s="17">
+        <v>0</v>
+      </c>
+      <c r="J106" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K106" s="17">
+        <v>0</v>
+      </c>
+      <c r="L106" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M106" s="17">
+        <v>0</v>
+      </c>
+      <c r="N106" s="20">
         <v>5000</v>
       </c>
-      <c r="O100" s="21">
+      <c r="O106" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="101" spans="1:19">
-      <c r="A101" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B101" s="16">
+    <row r="107" spans="1:19">
+      <c r="A107" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B107" s="16">
         <v>100300</v>
       </c>
-      <c r="C101" s="16">
-        <v>1</v>
-      </c>
-      <c r="D101" s="16" t="s">
+      <c r="C107" s="16">
+        <v>1</v>
+      </c>
+      <c r="D107" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="E101" s="16">
+      <c r="E107" s="16">
         <v>100300001</v>
       </c>
-      <c r="F101" s="16" t="s">
+      <c r="F107" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="G101" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H101" s="19">
+      <c r="G107" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="H107" s="17">
         <v>10</v>
       </c>
-      <c r="I101" s="19">
-        <v>0</v>
-      </c>
-      <c r="J101" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K101" s="19">
-        <v>0</v>
-      </c>
-      <c r="L101" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M101" s="19">
-        <v>0</v>
-      </c>
-      <c r="N101" s="20">
+      <c r="I107" s="17">
+        <v>0</v>
+      </c>
+      <c r="J107" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K107" s="17">
+        <v>0</v>
+      </c>
+      <c r="L107" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M107" s="17">
+        <v>0</v>
+      </c>
+      <c r="N107" s="20">
         <v>50</v>
       </c>
-      <c r="O101" s="21">
+      <c r="O107" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="102" spans="1:19">
-      <c r="A102" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B102" s="16">
+    <row r="108" spans="1:19">
+      <c r="A108" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B108" s="16">
         <v>100300</v>
       </c>
-      <c r="C102" s="16">
-        <v>1</v>
-      </c>
-      <c r="D102" s="16" t="str">
+      <c r="C108" s="16">
+        <v>1</v>
+      </c>
+      <c r="D108" s="16" t="str">
         <f t="shared" si="8"/>
         <v>超级明星</v>
       </c>
-      <c r="E102" s="16">
+      <c r="E108" s="16">
         <v>100300001</v>
       </c>
-      <c r="F102" s="16" t="str">
-        <f t="shared" ref="F102:F106" si="9">F101</f>
+      <c r="F108" s="16" t="str">
+        <f t="shared" ref="F108:F112" si="9">F107</f>
         <v>SuperStar</v>
       </c>
-      <c r="G102" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="H102" s="19">
+      <c r="G108" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H108" s="17">
         <v>11</v>
       </c>
-      <c r="I102" s="19">
-        <v>0</v>
-      </c>
-      <c r="J102" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K102" s="19">
-        <v>0</v>
-      </c>
-      <c r="L102" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M102" s="19">
-        <v>0</v>
-      </c>
-      <c r="N102" s="20">
+      <c r="I108" s="17">
+        <v>0</v>
+      </c>
+      <c r="J108" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K108" s="17">
+        <v>0</v>
+      </c>
+      <c r="L108" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M108" s="17">
+        <v>0</v>
+      </c>
+      <c r="N108" s="20">
         <v>500</v>
       </c>
-      <c r="O102" s="21">
+      <c r="O108" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="103" spans="1:19">
-      <c r="A103" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B103" s="16">
+    <row r="109" spans="1:19">
+      <c r="A109" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B109" s="16">
         <v>100300</v>
       </c>
-      <c r="C103" s="16">
-        <v>1</v>
-      </c>
-      <c r="D103" s="16" t="str">
+      <c r="C109" s="16">
+        <v>1</v>
+      </c>
+      <c r="D109" s="16" t="str">
         <f t="shared" si="8"/>
         <v>超级明星</v>
       </c>
-      <c r="E103" s="16">
+      <c r="E109" s="16">
         <v>100300001</v>
       </c>
-      <c r="F103" s="16" t="str">
+      <c r="F109" s="16" t="str">
         <f t="shared" si="9"/>
         <v>SuperStar</v>
       </c>
-      <c r="G103" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H103" s="19">
+      <c r="G109" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="H109" s="17">
         <v>12</v>
       </c>
-      <c r="I103" s="19">
-        <v>0</v>
-      </c>
-      <c r="J103" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K103" s="19">
-        <v>0</v>
-      </c>
-      <c r="L103" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M103" s="19">
-        <v>0</v>
-      </c>
-      <c r="N103" s="20">
+      <c r="I109" s="17">
+        <v>0</v>
+      </c>
+      <c r="J109" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K109" s="17">
+        <v>0</v>
+      </c>
+      <c r="L109" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M109" s="17">
+        <v>0</v>
+      </c>
+      <c r="N109" s="20">
         <v>5000</v>
       </c>
-      <c r="O103" s="21">
+      <c r="O109" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="104" spans="1:19">
-      <c r="A104" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B104" s="16">
+    <row r="110" spans="1:19">
+      <c r="A110" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B110" s="16">
         <v>100700</v>
       </c>
-      <c r="C104" s="16">
-        <v>1</v>
-      </c>
-      <c r="D104" s="16" t="s">
+      <c r="C110" s="16">
+        <v>1</v>
+      </c>
+      <c r="D110" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E104" s="16">
+      <c r="E110" s="16">
         <v>100700001</v>
       </c>
-      <c r="F104" s="16" t="s">
+      <c r="F110" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="G104" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H104" s="19">
+      <c r="G110" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="H110" s="17">
         <v>10</v>
       </c>
-      <c r="I104" s="19">
-        <v>0</v>
-      </c>
-      <c r="J104" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K104" s="19">
-        <v>0</v>
-      </c>
-      <c r="L104" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M104" s="19">
-        <v>0</v>
-      </c>
-      <c r="N104" s="20">
+      <c r="I110" s="17">
+        <v>0</v>
+      </c>
+      <c r="J110" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K110" s="17">
+        <v>0</v>
+      </c>
+      <c r="L110" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M110" s="17">
+        <v>0</v>
+      </c>
+      <c r="N110" s="20">
         <v>50</v>
       </c>
-      <c r="O104" s="21">
+      <c r="O110" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="105" spans="1:19">
-      <c r="A105" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B105" s="16">
+    <row r="111" spans="1:19">
+      <c r="A111" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B111" s="16">
         <v>100700</v>
       </c>
-      <c r="C105" s="16">
-        <v>1</v>
-      </c>
-      <c r="D105" s="16" t="str">
-        <f t="shared" ref="D105:D109" si="10">D104</f>
+      <c r="C111" s="16">
+        <v>1</v>
+      </c>
+      <c r="D111" s="16" t="str">
+        <f t="shared" ref="D111:D115" si="10">D110</f>
         <v>麻将胡了</v>
       </c>
-      <c r="E105" s="16">
+      <c r="E111" s="16">
         <v>100700001</v>
       </c>
-      <c r="F105" s="16" t="str">
+      <c r="F111" s="16" t="str">
         <f t="shared" si="9"/>
         <v>MahjongWays</v>
       </c>
-      <c r="G105" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="H105" s="19">
+      <c r="G111" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H111" s="17">
         <v>11</v>
       </c>
-      <c r="I105" s="19">
-        <v>0</v>
-      </c>
-      <c r="J105" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K105" s="19">
-        <v>0</v>
-      </c>
-      <c r="L105" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M105" s="19">
-        <v>0</v>
-      </c>
-      <c r="N105" s="20">
+      <c r="I111" s="17">
+        <v>0</v>
+      </c>
+      <c r="J111" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K111" s="17">
+        <v>0</v>
+      </c>
+      <c r="L111" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M111" s="17">
+        <v>0</v>
+      </c>
+      <c r="N111" s="20">
         <v>500</v>
       </c>
-      <c r="O105" s="21">
+      <c r="O111" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="106" spans="1:19">
-      <c r="A106" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B106" s="16">
+    <row r="112" spans="1:19">
+      <c r="A112" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B112" s="16">
         <v>100700</v>
       </c>
-      <c r="C106" s="16">
-        <v>1</v>
-      </c>
-      <c r="D106" s="16" t="str">
+      <c r="C112" s="16">
+        <v>1</v>
+      </c>
+      <c r="D112" s="16" t="str">
         <f t="shared" si="10"/>
         <v>麻将胡了</v>
       </c>
-      <c r="E106" s="16">
+      <c r="E112" s="16">
         <v>100700001</v>
       </c>
-      <c r="F106" s="16" t="str">
+      <c r="F112" s="16" t="str">
         <f t="shared" si="9"/>
         <v>MahjongWays</v>
       </c>
-      <c r="G106" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H106" s="19">
+      <c r="G112" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="H112" s="17">
         <v>12</v>
       </c>
-      <c r="I106" s="19">
-        <v>0</v>
-      </c>
-      <c r="J106" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K106" s="19">
-        <v>0</v>
-      </c>
-      <c r="L106" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M106" s="19">
-        <v>0</v>
-      </c>
-      <c r="N106" s="20">
+      <c r="I112" s="17">
+        <v>0</v>
+      </c>
+      <c r="J112" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K112" s="17">
+        <v>0</v>
+      </c>
+      <c r="L112" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M112" s="17">
+        <v>0</v>
+      </c>
+      <c r="N112" s="20">
         <v>5000</v>
       </c>
-      <c r="O106" s="21">
+      <c r="O112" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="107" spans="1:19">
-      <c r="A107" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B107" s="16">
+    <row r="113" spans="1:15">
+      <c r="A113" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B113" s="16">
         <v>101200</v>
       </c>
-      <c r="C107" s="16">
-        <v>1</v>
-      </c>
-      <c r="D107" s="16" t="s">
+      <c r="C113" s="16">
+        <v>1</v>
+      </c>
+      <c r="D113" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="E107" s="16">
+      <c r="E113" s="16">
         <v>101200001</v>
       </c>
-      <c r="F107" s="16" t="s">
+      <c r="F113" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="G107" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H107" s="19">
+      <c r="G113" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="H113" s="17">
         <v>10</v>
       </c>
-      <c r="I107" s="19">
-        <v>0</v>
-      </c>
-      <c r="J107" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K107" s="19">
-        <v>0</v>
-      </c>
-      <c r="L107" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M107" s="19">
-        <v>0</v>
-      </c>
-      <c r="N107" s="20">
+      <c r="I113" s="17">
+        <v>0</v>
+      </c>
+      <c r="J113" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K113" s="17">
+        <v>0</v>
+      </c>
+      <c r="L113" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M113" s="17">
+        <v>0</v>
+      </c>
+      <c r="N113" s="20">
         <v>50</v>
       </c>
-      <c r="O107" s="21">
+      <c r="O113" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="108" spans="1:19">
-      <c r="A108" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B108" s="16">
+    <row r="114" spans="1:15">
+      <c r="A114" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B114" s="16">
         <v>101200</v>
       </c>
-      <c r="C108" s="16">
-        <v>1</v>
-      </c>
-      <c r="D108" s="16" t="str">
+      <c r="C114" s="16">
+        <v>1</v>
+      </c>
+      <c r="D114" s="16" t="str">
         <f t="shared" si="10"/>
         <v>财神</v>
       </c>
-      <c r="E108" s="16">
+      <c r="E114" s="16">
         <v>101200001</v>
       </c>
-      <c r="F108" s="16" t="str">
-        <f t="shared" ref="F108:F112" si="11">F107</f>
+      <c r="F114" s="16" t="str">
+        <f t="shared" ref="F114:F118" si="11">F113</f>
         <v>Godofwealth</v>
       </c>
-      <c r="G108" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="H108" s="19">
+      <c r="G114" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H114" s="17">
         <v>11</v>
       </c>
-      <c r="I108" s="19">
-        <v>0</v>
-      </c>
-      <c r="J108" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K108" s="19">
-        <v>0</v>
-      </c>
-      <c r="L108" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M108" s="19">
-        <v>0</v>
-      </c>
-      <c r="N108" s="20">
+      <c r="I114" s="17">
+        <v>0</v>
+      </c>
+      <c r="J114" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K114" s="17">
+        <v>0</v>
+      </c>
+      <c r="L114" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M114" s="17">
+        <v>0</v>
+      </c>
+      <c r="N114" s="20">
         <v>500</v>
       </c>
-      <c r="O108" s="21">
+      <c r="O114" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="109" spans="1:19">
-      <c r="A109" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B109" s="16">
+    <row r="115" spans="1:15">
+      <c r="A115" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B115" s="16">
         <v>101200</v>
       </c>
-      <c r="C109" s="16">
-        <v>1</v>
-      </c>
-      <c r="D109" s="16" t="str">
+      <c r="C115" s="16">
+        <v>1</v>
+      </c>
+      <c r="D115" s="16" t="str">
         <f t="shared" si="10"/>
         <v>财神</v>
       </c>
-      <c r="E109" s="16">
+      <c r="E115" s="16">
         <v>101200001</v>
       </c>
-      <c r="F109" s="16" t="str">
+      <c r="F115" s="16" t="str">
         <f t="shared" si="11"/>
         <v>Godofwealth</v>
       </c>
-      <c r="G109" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H109" s="19">
+      <c r="G115" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="H115" s="17">
         <v>12</v>
       </c>
-      <c r="I109" s="19">
-        <v>0</v>
-      </c>
-      <c r="J109" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K109" s="19">
-        <v>0</v>
-      </c>
-      <c r="L109" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M109" s="19">
-        <v>0</v>
-      </c>
-      <c r="N109" s="20">
+      <c r="I115" s="17">
+        <v>0</v>
+      </c>
+      <c r="J115" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K115" s="17">
+        <v>0</v>
+      </c>
+      <c r="L115" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M115" s="17">
+        <v>0</v>
+      </c>
+      <c r="N115" s="20">
         <v>5000</v>
       </c>
-      <c r="O109" s="21">
+      <c r="O115" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="110" spans="1:19">
-      <c r="A110" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B110" s="16">
+    <row r="116" spans="1:15">
+      <c r="A116" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B116" s="16">
         <v>101400</v>
       </c>
-      <c r="C110" s="16">
-        <v>1</v>
-      </c>
-      <c r="D110" s="16" t="s">
+      <c r="C116" s="16">
+        <v>1</v>
+      </c>
+      <c r="D116" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="E110" s="16">
+      <c r="E116" s="16">
         <v>101400001</v>
       </c>
-      <c r="F110" s="16" t="s">
+      <c r="F116" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="G110" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H110" s="19">
+      <c r="G116" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="H116" s="17">
         <v>10</v>
       </c>
-      <c r="I110" s="19">
-        <v>0</v>
-      </c>
-      <c r="J110" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K110" s="19">
-        <v>0</v>
-      </c>
-      <c r="L110" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M110" s="19">
-        <v>0</v>
-      </c>
-      <c r="N110" s="20">
+      <c r="I116" s="17">
+        <v>0</v>
+      </c>
+      <c r="J116" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K116" s="17">
+        <v>0</v>
+      </c>
+      <c r="L116" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M116" s="17">
+        <v>0</v>
+      </c>
+      <c r="N116" s="20">
         <v>50</v>
       </c>
-      <c r="O110" s="21">
+      <c r="O116" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="111" spans="1:19">
-      <c r="A111" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B111" s="16">
+    <row r="117" spans="1:15">
+      <c r="A117" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B117" s="16">
         <v>101400</v>
       </c>
-      <c r="C111" s="16">
-        <v>1</v>
-      </c>
-      <c r="D111" s="16" t="str">
-        <f t="shared" ref="D111:D115" si="12">D110</f>
+      <c r="C117" s="16">
+        <v>1</v>
+      </c>
+      <c r="D117" s="16" t="str">
+        <f t="shared" ref="D117:D121" si="12">D116</f>
         <v>埃及艳后</v>
       </c>
-      <c r="E111" s="16">
+      <c r="E117" s="16">
         <v>101400001</v>
       </c>
-      <c r="F111" s="16" t="str">
+      <c r="F117" s="16" t="str">
         <f t="shared" si="11"/>
         <v>Cleopatra</v>
       </c>
-      <c r="G111" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="H111" s="19">
+      <c r="G117" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H117" s="17">
         <v>11</v>
       </c>
-      <c r="I111" s="19">
-        <v>0</v>
-      </c>
-      <c r="J111" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K111" s="19">
-        <v>0</v>
-      </c>
-      <c r="L111" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M111" s="19">
-        <v>0</v>
-      </c>
-      <c r="N111" s="20">
+      <c r="I117" s="17">
+        <v>0</v>
+      </c>
+      <c r="J117" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K117" s="17">
+        <v>0</v>
+      </c>
+      <c r="L117" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M117" s="17">
+        <v>0</v>
+      </c>
+      <c r="N117" s="20">
         <v>500</v>
       </c>
-      <c r="O111" s="21">
+      <c r="O117" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="112" spans="1:19">
-      <c r="A112" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B112" s="16">
+    <row r="118" spans="1:15">
+      <c r="A118" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B118" s="16">
         <v>101400</v>
       </c>
-      <c r="C112" s="16">
-        <v>1</v>
-      </c>
-      <c r="D112" s="16" t="str">
+      <c r="C118" s="16">
+        <v>1</v>
+      </c>
+      <c r="D118" s="16" t="str">
         <f t="shared" si="12"/>
         <v>埃及艳后</v>
       </c>
-      <c r="E112" s="16">
+      <c r="E118" s="16">
         <v>101400001</v>
       </c>
-      <c r="F112" s="16" t="str">
+      <c r="F118" s="16" t="str">
         <f t="shared" si="11"/>
         <v>Cleopatra</v>
       </c>
-      <c r="G112" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H112" s="19">
+      <c r="G118" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="H118" s="17">
         <v>12</v>
       </c>
-      <c r="I112" s="19">
-        <v>0</v>
-      </c>
-      <c r="J112" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K112" s="19">
-        <v>0</v>
-      </c>
-      <c r="L112" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M112" s="19">
-        <v>0</v>
-      </c>
-      <c r="N112" s="20">
+      <c r="I118" s="17">
+        <v>0</v>
+      </c>
+      <c r="J118" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K118" s="17">
+        <v>0</v>
+      </c>
+      <c r="L118" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M118" s="17">
+        <v>0</v>
+      </c>
+      <c r="N118" s="20">
         <v>5000</v>
       </c>
-      <c r="O112" s="21">
+      <c r="O118" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="113" spans="1:15">
-      <c r="A113" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B113" s="16">
+    <row r="119" spans="1:15">
+      <c r="A119" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B119" s="16">
         <v>102400</v>
       </c>
-      <c r="C113" s="16">
-        <v>1</v>
-      </c>
-      <c r="D113" s="16" t="s">
+      <c r="C119" s="16">
+        <v>1</v>
+      </c>
+      <c r="D119" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="E113" s="16">
+      <c r="E119" s="16">
         <v>102400026</v>
       </c>
-      <c r="F113" s="16" t="s">
+      <c r="F119" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="G113" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H113" s="19">
+      <c r="G119" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="H119" s="17">
         <v>10</v>
       </c>
-      <c r="I113" s="19">
-        <v>0</v>
-      </c>
-      <c r="J113" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K113" s="19">
-        <v>0</v>
-      </c>
-      <c r="L113" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M113" s="19">
-        <v>0</v>
-      </c>
-      <c r="N113" s="20">
+      <c r="I119" s="17">
+        <v>0</v>
+      </c>
+      <c r="J119" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K119" s="17">
+        <v>0</v>
+      </c>
+      <c r="L119" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M119" s="17">
+        <v>0</v>
+      </c>
+      <c r="N119" s="20">
         <v>50</v>
       </c>
-      <c r="O113" s="21">
+      <c r="O119" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="114" spans="1:15">
-      <c r="A114" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B114" s="16">
+    <row r="120" spans="1:15">
+      <c r="A120" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B120" s="16">
         <v>102400</v>
       </c>
-      <c r="C114" s="16">
-        <v>1</v>
-      </c>
-      <c r="D114" s="16" t="str">
+      <c r="C120" s="16">
+        <v>1</v>
+      </c>
+      <c r="D120" s="16" t="str">
         <f t="shared" si="12"/>
         <v>财富银行</v>
       </c>
-      <c r="E114" s="16">
+      <c r="E120" s="16">
         <v>102400026</v>
       </c>
-      <c r="F114" s="16" t="s">
+      <c r="F120" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="G114" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="H114" s="19">
+      <c r="G120" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H120" s="17">
         <v>11</v>
       </c>
-      <c r="I114" s="19">
-        <v>0</v>
-      </c>
-      <c r="J114" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K114" s="19">
-        <v>0</v>
-      </c>
-      <c r="L114" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M114" s="19">
-        <v>0</v>
-      </c>
-      <c r="N114" s="20">
+      <c r="I120" s="17">
+        <v>0</v>
+      </c>
+      <c r="J120" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K120" s="17">
+        <v>0</v>
+      </c>
+      <c r="L120" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M120" s="17">
+        <v>0</v>
+      </c>
+      <c r="N120" s="20">
         <v>500</v>
       </c>
-      <c r="O114" s="21">
+      <c r="O120" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="115" spans="1:15">
-      <c r="A115" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B115" s="16">
+    <row r="121" spans="1:15">
+      <c r="A121" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B121" s="16">
         <v>102400</v>
       </c>
-      <c r="C115" s="16">
-        <v>1</v>
-      </c>
-      <c r="D115" s="16" t="str">
+      <c r="C121" s="16">
+        <v>1</v>
+      </c>
+      <c r="D121" s="16" t="str">
         <f t="shared" si="12"/>
         <v>财富银行</v>
       </c>
-      <c r="E115" s="16">
+      <c r="E121" s="16">
         <v>102400026</v>
       </c>
-      <c r="F115" s="16" t="s">
+      <c r="F121" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="G115" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H115" s="19">
+      <c r="G121" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="H121" s="17">
         <v>12</v>
       </c>
-      <c r="I115" s="19">
-        <v>0</v>
-      </c>
-      <c r="J115" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K115" s="19">
-        <v>0</v>
-      </c>
-      <c r="L115" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M115" s="19">
-        <v>0</v>
-      </c>
-      <c r="N115" s="20">
-        <v>5000</v>
-      </c>
-      <c r="O115" s="21">
-        <v>1980000</v>
-      </c>
-    </row>
-    <row r="116" spans="1:15">
-      <c r="A116" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B116" s="16">
-        <v>102200</v>
-      </c>
-      <c r="C116" s="16">
-        <v>1</v>
-      </c>
-      <c r="D116" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="E116" s="16">
-        <v>102200001</v>
-      </c>
-      <c r="F116" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="G116" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H116" s="19">
-        <v>10</v>
-      </c>
-      <c r="I116" s="19">
-        <v>0</v>
-      </c>
-      <c r="J116" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K116" s="19">
-        <v>0</v>
-      </c>
-      <c r="L116" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M116" s="19">
-        <v>0</v>
-      </c>
-      <c r="N116" s="20">
-        <v>50</v>
-      </c>
-      <c r="O116" s="21">
-        <v>1980000</v>
-      </c>
-    </row>
-    <row r="117" spans="1:15">
-      <c r="A117" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B117" s="16">
-        <v>102200</v>
-      </c>
-      <c r="C117" s="16">
-        <v>1</v>
-      </c>
-      <c r="D117" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="E117" s="16">
-        <v>102200001</v>
-      </c>
-      <c r="F117" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="G117" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="H117" s="19">
-        <v>11</v>
-      </c>
-      <c r="I117" s="19">
-        <v>0</v>
-      </c>
-      <c r="J117" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K117" s="19">
-        <v>0</v>
-      </c>
-      <c r="L117" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M117" s="19">
-        <v>0</v>
-      </c>
-      <c r="N117" s="20">
-        <v>500</v>
-      </c>
-      <c r="O117" s="21">
-        <v>1980000</v>
-      </c>
-    </row>
-    <row r="118" spans="1:15">
-      <c r="A118" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B118" s="16">
-        <v>102200</v>
-      </c>
-      <c r="C118" s="16">
-        <v>1</v>
-      </c>
-      <c r="D118" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="E118" s="16">
-        <v>102200001</v>
-      </c>
-      <c r="F118" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="G118" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H118" s="19">
-        <v>12</v>
-      </c>
-      <c r="I118" s="19">
-        <v>0</v>
-      </c>
-      <c r="J118" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K118" s="19">
-        <v>0</v>
-      </c>
-      <c r="L118" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M118" s="19">
-        <v>0</v>
-      </c>
-      <c r="N118" s="20">
-        <v>5000</v>
-      </c>
-      <c r="O118" s="21">
-        <v>1980000</v>
-      </c>
-    </row>
-    <row r="119" spans="1:15">
-      <c r="A119" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B119" s="16">
-        <v>101700</v>
-      </c>
-      <c r="C119" s="16">
-        <v>1</v>
-      </c>
-      <c r="D119" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="E119" s="16">
-        <v>101700001</v>
-      </c>
-      <c r="F119" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="G119" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H119" s="19">
-        <v>10</v>
-      </c>
-      <c r="I119" s="19">
-        <v>0</v>
-      </c>
-      <c r="J119" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K119" s="19">
-        <v>0</v>
-      </c>
-      <c r="L119" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M119" s="19">
-        <v>0</v>
-      </c>
-      <c r="N119" s="20">
-        <v>50</v>
-      </c>
-      <c r="O119" s="21">
-        <v>1980000</v>
-      </c>
-    </row>
-    <row r="120" spans="1:15">
-      <c r="A120" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B120" s="16">
-        <v>101700</v>
-      </c>
-      <c r="C120" s="16">
-        <v>1</v>
-      </c>
-      <c r="D120" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="E120" s="16">
-        <v>101700001</v>
-      </c>
-      <c r="F120" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="G120" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="H120" s="19">
-        <v>11</v>
-      </c>
-      <c r="I120" s="19">
-        <v>0</v>
-      </c>
-      <c r="J120" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K120" s="19">
-        <v>0</v>
-      </c>
-      <c r="L120" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M120" s="19">
-        <v>0</v>
-      </c>
-      <c r="N120" s="20">
-        <v>500</v>
-      </c>
-      <c r="O120" s="21">
-        <v>1980000</v>
-      </c>
-    </row>
-    <row r="121" spans="1:15">
-      <c r="A121" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B121" s="16">
-        <v>101700</v>
-      </c>
-      <c r="C121" s="16">
-        <v>1</v>
-      </c>
-      <c r="D121" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="E121" s="16">
-        <v>101700001</v>
-      </c>
-      <c r="F121" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="G121" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H121" s="19">
-        <v>12</v>
-      </c>
-      <c r="I121" s="19">
-        <v>0</v>
-      </c>
-      <c r="J121" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K121" s="19">
-        <v>0</v>
-      </c>
-      <c r="L121" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M121" s="19">
+      <c r="I121" s="17">
+        <v>0</v>
+      </c>
+      <c r="J121" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K121" s="17">
+        <v>0</v>
+      </c>
+      <c r="L121" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M121" s="17">
         <v>0</v>
       </c>
       <c r="N121" s="20">
@@ -7492,42 +7492,42 @@
     </row>
     <row r="122" spans="1:15">
       <c r="A122" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B122" s="16">
-        <v>102100</v>
+        <v>102200</v>
       </c>
       <c r="C122" s="16">
         <v>1</v>
       </c>
       <c r="D122" s="16" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E122" s="16">
-        <v>102100001</v>
+        <v>102200001</v>
       </c>
       <c r="F122" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="G122" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H122" s="19">
+        <v>48</v>
+      </c>
+      <c r="G122" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="H122" s="17">
         <v>10</v>
       </c>
-      <c r="I122" s="19">
-        <v>0</v>
-      </c>
-      <c r="J122" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K122" s="19">
-        <v>0</v>
-      </c>
-      <c r="L122" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M122" s="19">
+      <c r="I122" s="17">
+        <v>0</v>
+      </c>
+      <c r="J122" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K122" s="17">
+        <v>0</v>
+      </c>
+      <c r="L122" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M122" s="17">
         <v>0</v>
       </c>
       <c r="N122" s="20">
@@ -7539,42 +7539,42 @@
     </row>
     <row r="123" spans="1:15">
       <c r="A123" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B123" s="16">
-        <v>102100</v>
+        <v>102200</v>
       </c>
       <c r="C123" s="16">
         <v>1</v>
       </c>
       <c r="D123" s="16" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E123" s="16">
-        <v>102100001</v>
+        <v>102200001</v>
       </c>
       <c r="F123" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="G123" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="H123" s="19">
+        <v>48</v>
+      </c>
+      <c r="G123" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H123" s="17">
         <v>11</v>
       </c>
-      <c r="I123" s="19">
-        <v>0</v>
-      </c>
-      <c r="J123" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K123" s="19">
-        <v>0</v>
-      </c>
-      <c r="L123" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M123" s="19">
+      <c r="I123" s="17">
+        <v>0</v>
+      </c>
+      <c r="J123" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K123" s="17">
+        <v>0</v>
+      </c>
+      <c r="L123" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M123" s="17">
         <v>0</v>
       </c>
       <c r="N123" s="20">
@@ -7586,42 +7586,42 @@
     </row>
     <row r="124" spans="1:15">
       <c r="A124" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B124" s="16">
-        <v>102100</v>
+        <v>102200</v>
       </c>
       <c r="C124" s="16">
         <v>1</v>
       </c>
       <c r="D124" s="16" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E124" s="16">
-        <v>102100001</v>
+        <v>102200001</v>
       </c>
       <c r="F124" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="G124" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H124" s="19">
+        <v>48</v>
+      </c>
+      <c r="G124" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="H124" s="17">
         <v>12</v>
       </c>
-      <c r="I124" s="19">
-        <v>0</v>
-      </c>
-      <c r="J124" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K124" s="19">
-        <v>0</v>
-      </c>
-      <c r="L124" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M124" s="19">
+      <c r="I124" s="17">
+        <v>0</v>
+      </c>
+      <c r="J124" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K124" s="17">
+        <v>0</v>
+      </c>
+      <c r="L124" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M124" s="17">
         <v>0</v>
       </c>
       <c r="N124" s="20">
@@ -7632,43 +7632,43 @@
       </c>
     </row>
     <row r="125" spans="1:15">
-      <c r="A125" s="1">
-        <v>10180010</v>
+      <c r="A125" s="1" t="s">
+        <v>110</v>
       </c>
       <c r="B125" s="16">
-        <v>101800</v>
+        <v>101700</v>
       </c>
       <c r="C125" s="16">
         <v>1</v>
       </c>
       <c r="D125" s="16" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="E125" s="16">
-        <v>101800001</v>
+        <v>101700001</v>
       </c>
       <c r="F125" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="G125" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H125" s="19">
+        <v>50</v>
+      </c>
+      <c r="G125" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="H125" s="17">
         <v>10</v>
       </c>
-      <c r="I125" s="19">
-        <v>0</v>
-      </c>
-      <c r="J125" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K125" s="19">
-        <v>0</v>
-      </c>
-      <c r="L125" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M125" s="19">
+      <c r="I125" s="17">
+        <v>0</v>
+      </c>
+      <c r="J125" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K125" s="17">
+        <v>0</v>
+      </c>
+      <c r="L125" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M125" s="17">
         <v>0</v>
       </c>
       <c r="N125" s="20">
@@ -7679,43 +7679,43 @@
       </c>
     </row>
     <row r="126" spans="1:15">
-      <c r="A126" s="1">
-        <v>10180011</v>
+      <c r="A126" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="B126" s="16">
-        <v>101800</v>
+        <v>101700</v>
       </c>
       <c r="C126" s="16">
         <v>1</v>
       </c>
       <c r="D126" s="16" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="E126" s="16">
-        <v>101800001</v>
+        <v>101700001</v>
       </c>
       <c r="F126" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="G126" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="H126" s="19">
+        <v>50</v>
+      </c>
+      <c r="G126" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H126" s="17">
         <v>11</v>
       </c>
-      <c r="I126" s="19">
-        <v>0</v>
-      </c>
-      <c r="J126" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K126" s="19">
-        <v>0</v>
-      </c>
-      <c r="L126" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M126" s="19">
+      <c r="I126" s="17">
+        <v>0</v>
+      </c>
+      <c r="J126" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K126" s="17">
+        <v>0</v>
+      </c>
+      <c r="L126" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M126" s="17">
         <v>0</v>
       </c>
       <c r="N126" s="20">
@@ -7726,43 +7726,43 @@
       </c>
     </row>
     <row r="127" spans="1:15">
-      <c r="A127" s="1">
-        <v>10180012</v>
+      <c r="A127" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="B127" s="16">
-        <v>101800</v>
+        <v>101700</v>
       </c>
       <c r="C127" s="16">
         <v>1</v>
       </c>
       <c r="D127" s="16" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="E127" s="16">
-        <v>101800001</v>
+        <v>101700001</v>
       </c>
       <c r="F127" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="G127" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H127" s="19">
+        <v>50</v>
+      </c>
+      <c r="G127" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="H127" s="17">
         <v>12</v>
       </c>
-      <c r="I127" s="19">
-        <v>0</v>
-      </c>
-      <c r="J127" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K127" s="19">
-        <v>0</v>
-      </c>
-      <c r="L127" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M127" s="19">
+      <c r="I127" s="17">
+        <v>0</v>
+      </c>
+      <c r="J127" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K127" s="17">
+        <v>0</v>
+      </c>
+      <c r="L127" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M127" s="17">
         <v>0</v>
       </c>
       <c r="N127" s="20">
@@ -7773,43 +7773,43 @@
       </c>
     </row>
     <row r="128" spans="1:15">
-      <c r="A128" s="1">
-        <v>10250010</v>
+      <c r="A128" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="B128" s="16">
-        <v>102500</v>
+        <v>102100</v>
       </c>
       <c r="C128" s="16">
         <v>1</v>
       </c>
       <c r="D128" s="16" t="s">
-        <v>114</v>
+        <v>51</v>
       </c>
       <c r="E128" s="16">
-        <v>102500001</v>
+        <v>102100001</v>
       </c>
       <c r="F128" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="G128" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H128" s="19">
+        <v>52</v>
+      </c>
+      <c r="G128" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="H128" s="17">
         <v>10</v>
       </c>
-      <c r="I128" s="19">
-        <v>0</v>
-      </c>
-      <c r="J128" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K128" s="19">
-        <v>0</v>
-      </c>
-      <c r="L128" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M128" s="19">
+      <c r="I128" s="17">
+        <v>0</v>
+      </c>
+      <c r="J128" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K128" s="17">
+        <v>0</v>
+      </c>
+      <c r="L128" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M128" s="17">
         <v>0</v>
       </c>
       <c r="N128" s="20">
@@ -7820,43 +7820,43 @@
       </c>
     </row>
     <row r="129" spans="1:15">
-      <c r="A129" s="1">
-        <v>10250011</v>
+      <c r="A129" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="B129" s="16">
-        <v>102500</v>
+        <v>102100</v>
       </c>
       <c r="C129" s="16">
         <v>1</v>
       </c>
       <c r="D129" s="16" t="s">
-        <v>114</v>
+        <v>51</v>
       </c>
       <c r="E129" s="16">
-        <v>102500001</v>
+        <v>102100001</v>
       </c>
       <c r="F129" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="G129" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="H129" s="19">
+        <v>52</v>
+      </c>
+      <c r="G129" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H129" s="17">
         <v>11</v>
       </c>
-      <c r="I129" s="19">
-        <v>0</v>
-      </c>
-      <c r="J129" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K129" s="19">
-        <v>0</v>
-      </c>
-      <c r="L129" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M129" s="19">
+      <c r="I129" s="17">
+        <v>0</v>
+      </c>
+      <c r="J129" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K129" s="17">
+        <v>0</v>
+      </c>
+      <c r="L129" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M129" s="17">
         <v>0</v>
       </c>
       <c r="N129" s="20">
@@ -7867,49 +7867,331 @@
       </c>
     </row>
     <row r="130" spans="1:15">
-      <c r="A130" s="1">
-        <v>10250012</v>
+      <c r="A130" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="B130" s="16">
-        <v>102500</v>
+        <v>102100</v>
       </c>
       <c r="C130" s="16">
         <v>1</v>
       </c>
       <c r="D130" s="16" t="s">
-        <v>114</v>
+        <v>51</v>
       </c>
       <c r="E130" s="16">
-        <v>102500001</v>
+        <v>102100001</v>
       </c>
       <c r="F130" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="G130" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H130" s="19">
+        <v>52</v>
+      </c>
+      <c r="G130" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="H130" s="17">
         <v>12</v>
       </c>
-      <c r="I130" s="19">
-        <v>0</v>
-      </c>
-      <c r="J130" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K130" s="19">
-        <v>0</v>
-      </c>
-      <c r="L130" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M130" s="19">
+      <c r="I130" s="17">
+        <v>0</v>
+      </c>
+      <c r="J130" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K130" s="17">
+        <v>0</v>
+      </c>
+      <c r="L130" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M130" s="17">
         <v>0</v>
       </c>
       <c r="N130" s="20">
         <v>5000</v>
       </c>
       <c r="O130" s="21">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15">
+      <c r="A131" s="1">
+        <v>10180010</v>
+      </c>
+      <c r="B131" s="16">
+        <v>101800</v>
+      </c>
+      <c r="C131" s="16">
+        <v>1</v>
+      </c>
+      <c r="D131" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="E131" s="16">
+        <v>101800001</v>
+      </c>
+      <c r="F131" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="G131" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="H131" s="17">
+        <v>10</v>
+      </c>
+      <c r="I131" s="17">
+        <v>0</v>
+      </c>
+      <c r="J131" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K131" s="17">
+        <v>0</v>
+      </c>
+      <c r="L131" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M131" s="17">
+        <v>0</v>
+      </c>
+      <c r="N131" s="20">
+        <v>50</v>
+      </c>
+      <c r="O131" s="21">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15">
+      <c r="A132" s="1">
+        <v>10180011</v>
+      </c>
+      <c r="B132" s="16">
+        <v>101800</v>
+      </c>
+      <c r="C132" s="16">
+        <v>1</v>
+      </c>
+      <c r="D132" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="E132" s="16">
+        <v>101800001</v>
+      </c>
+      <c r="F132" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="G132" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H132" s="17">
+        <v>11</v>
+      </c>
+      <c r="I132" s="17">
+        <v>0</v>
+      </c>
+      <c r="J132" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K132" s="17">
+        <v>0</v>
+      </c>
+      <c r="L132" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M132" s="17">
+        <v>0</v>
+      </c>
+      <c r="N132" s="20">
+        <v>500</v>
+      </c>
+      <c r="O132" s="21">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15">
+      <c r="A133" s="1">
+        <v>10180012</v>
+      </c>
+      <c r="B133" s="16">
+        <v>101800</v>
+      </c>
+      <c r="C133" s="16">
+        <v>1</v>
+      </c>
+      <c r="D133" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="E133" s="16">
+        <v>101800001</v>
+      </c>
+      <c r="F133" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="G133" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="H133" s="17">
+        <v>12</v>
+      </c>
+      <c r="I133" s="17">
+        <v>0</v>
+      </c>
+      <c r="J133" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K133" s="17">
+        <v>0</v>
+      </c>
+      <c r="L133" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M133" s="17">
+        <v>0</v>
+      </c>
+      <c r="N133" s="20">
+        <v>5000</v>
+      </c>
+      <c r="O133" s="21">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15">
+      <c r="A134" s="1">
+        <v>10250010</v>
+      </c>
+      <c r="B134" s="16">
+        <v>102500</v>
+      </c>
+      <c r="C134" s="16">
+        <v>1</v>
+      </c>
+      <c r="D134" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E134" s="16">
+        <v>102500001</v>
+      </c>
+      <c r="F134" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="G134" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="H134" s="17">
+        <v>10</v>
+      </c>
+      <c r="I134" s="17">
+        <v>0</v>
+      </c>
+      <c r="J134" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K134" s="17">
+        <v>0</v>
+      </c>
+      <c r="L134" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M134" s="17">
+        <v>0</v>
+      </c>
+      <c r="N134" s="20">
+        <v>50</v>
+      </c>
+      <c r="O134" s="21">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15">
+      <c r="A135" s="1">
+        <v>10250011</v>
+      </c>
+      <c r="B135" s="16">
+        <v>102500</v>
+      </c>
+      <c r="C135" s="16">
+        <v>1</v>
+      </c>
+      <c r="D135" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E135" s="16">
+        <v>102500001</v>
+      </c>
+      <c r="F135" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="G135" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H135" s="17">
+        <v>11</v>
+      </c>
+      <c r="I135" s="17">
+        <v>0</v>
+      </c>
+      <c r="J135" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K135" s="17">
+        <v>0</v>
+      </c>
+      <c r="L135" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M135" s="17">
+        <v>0</v>
+      </c>
+      <c r="N135" s="20">
+        <v>500</v>
+      </c>
+      <c r="O135" s="21">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15">
+      <c r="A136" s="1">
+        <v>10250012</v>
+      </c>
+      <c r="B136" s="16">
+        <v>102500</v>
+      </c>
+      <c r="C136" s="16">
+        <v>1</v>
+      </c>
+      <c r="D136" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E136" s="16">
+        <v>102500001</v>
+      </c>
+      <c r="F136" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="G136" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="H136" s="17">
+        <v>12</v>
+      </c>
+      <c r="I136" s="17">
+        <v>0</v>
+      </c>
+      <c r="J136" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K136" s="17">
+        <v>0</v>
+      </c>
+      <c r="L136" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="M136" s="17">
+        <v>0</v>
+      </c>
+      <c r="N136" s="20">
+        <v>5000</v>
+      </c>
+      <c r="O136" s="21">
         <v>1980000</v>
       </c>
     </row>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -3131,7 +3131,7 @@
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="1">
-        <v>10180001</v>
+        <v>1018001</v>
       </c>
       <c r="B32" s="16">
         <v>101800</v>
@@ -3178,7 +3178,7 @@
     </row>
     <row r="33" spans="1:19">
       <c r="A33" s="1">
-        <v>10180002</v>
+        <v>1018002</v>
       </c>
       <c r="B33" s="16">
         <v>101800</v>
@@ -3225,7 +3225,7 @@
     </row>
     <row r="34" spans="1:19">
       <c r="A34" s="1">
-        <v>10180003</v>
+        <v>1018003</v>
       </c>
       <c r="B34" s="16">
         <v>101800</v>
@@ -3272,7 +3272,7 @@
     </row>
     <row r="35" spans="1:19">
       <c r="A35" s="1">
-        <v>10250001</v>
+        <v>1025001</v>
       </c>
       <c r="B35" s="16">
         <v>102500</v>
@@ -3319,7 +3319,7 @@
     </row>
     <row r="36" spans="1:19">
       <c r="A36" s="1">
-        <v>10250002</v>
+        <v>1025002</v>
       </c>
       <c r="B36" s="16">
         <v>102500</v>
@@ -3366,7 +3366,7 @@
     </row>
     <row r="37" spans="1:19">
       <c r="A37" s="1">
-        <v>10250003</v>
+        <v>1025003</v>
       </c>
       <c r="B37" s="16">
         <v>102500</v>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -156,7 +156,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="118">
   <si>
     <t>sid</t>
   </si>
@@ -327,6 +327,12 @@
   </si>
   <si>
     <t>FrozenThrone</t>
+  </si>
+  <si>
+    <t>蒸汽时代</t>
+  </si>
+  <si>
+    <t>AgeSteam</t>
   </si>
   <si>
     <t>紅黑大戰</t>
@@ -1653,7 +1659,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S136"/>
+  <dimension ref="A1:S142"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="3" width="9.375" style="1"/>
@@ -3413,20 +3419,19 @@
     </row>
     <row r="38" spans="1:19">
       <c r="A38" s="1">
-        <f t="shared" ref="A38:A84" si="5">B38*10+H38</f>
-        <v>2001001</v>
+        <v>1023001</v>
       </c>
       <c r="B38" s="12">
-        <v>200100</v>
+        <v>102300</v>
       </c>
       <c r="C38" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38" s="12" t="s">
         <v>57</v>
       </c>
       <c r="E38" s="13">
-        <v>200100038</v>
+        <v>102300001</v>
       </c>
       <c r="F38" s="13" t="s">
         <v>58</v>
@@ -3440,10 +3445,10 @@
       <c r="I38" s="1">
         <v>0</v>
       </c>
-      <c r="J38" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K38" s="1">
+      <c r="J38" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K38" s="17">
         <v>0</v>
       </c>
       <c r="L38" s="1" t="s">
@@ -3461,218 +3466,212 @@
     </row>
     <row r="39" spans="1:19">
       <c r="A39" s="1">
+        <v>1023002</v>
+      </c>
+      <c r="B39" s="12">
+        <v>102300</v>
+      </c>
+      <c r="C39" s="12">
+        <v>1</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E39" s="13">
+        <v>102300001</v>
+      </c>
+      <c r="F39" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H39" s="1">
+        <v>2</v>
+      </c>
+      <c r="I39" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J39" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K39" s="17">
+        <v>0</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M39" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="N39">
+        <v>500000</v>
+      </c>
+      <c r="O39" s="15">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19">
+      <c r="A40" s="1">
+        <v>1023003</v>
+      </c>
+      <c r="B40" s="12">
+        <v>102300</v>
+      </c>
+      <c r="C40" s="12">
+        <v>1</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E40" s="13">
+        <v>102300001</v>
+      </c>
+      <c r="F40" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H40" s="1">
+        <v>3</v>
+      </c>
+      <c r="I40" s="1">
+        <v>50000000</v>
+      </c>
+      <c r="J40" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K40" s="17">
+        <v>0</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M40" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="N40">
+        <v>50000000</v>
+      </c>
+      <c r="O40" s="15">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19">
+      <c r="A41" s="1">
+        <f t="shared" ref="A41:A87" si="5">B41*10+H41</f>
+        <v>2001001</v>
+      </c>
+      <c r="B41" s="12">
+        <v>200100</v>
+      </c>
+      <c r="C41" s="12">
+        <v>2</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E41" s="13">
+        <v>200100038</v>
+      </c>
+      <c r="F41" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H41" s="1">
+        <v>1</v>
+      </c>
+      <c r="I41" s="1">
+        <v>0</v>
+      </c>
+      <c r="J41" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K41" s="1">
+        <v>0</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M41" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="N41">
+        <v>5000</v>
+      </c>
+      <c r="O41" s="15">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19">
+      <c r="A42" s="1">
         <f t="shared" si="5"/>
         <v>2001002</v>
       </c>
-      <c r="B39" s="12">
+      <c r="B42" s="12">
         <v>200100</v>
       </c>
-      <c r="C39" s="12">
+      <c r="C42" s="12">
         <v>2</v>
       </c>
-      <c r="D39" s="12" t="str">
-        <f>D38</f>
+      <c r="D42" s="12" t="str">
+        <f>D41</f>
         <v>紅黑大戰</v>
       </c>
-      <c r="E39" s="13">
+      <c r="E42" s="13">
         <v>200100038</v>
       </c>
-      <c r="F39" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="G39" s="1" t="s">
+      <c r="F42" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="G42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H39" s="1">
+      <c r="H42" s="1">
         <v>2</v>
       </c>
-      <c r="I39" s="1">
+      <c r="I42" s="1">
         <v>500000</v>
       </c>
-      <c r="J39" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K39" s="1">
-        <v>0</v>
-      </c>
-      <c r="L39" s="1" t="s">
+      <c r="J42" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K42" s="1">
+        <v>0</v>
+      </c>
+      <c r="L42" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M39" s="23" t="s">
+      <c r="M42" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="N39">
+      <c r="N42">
         <v>500000</v>
       </c>
-      <c r="O39" s="15">
+      <c r="O42" s="15">
         <v>1990000</v>
       </c>
     </row>
-    <row r="40" spans="1:19">
-      <c r="A40" s="1">
+    <row r="43" spans="1:19">
+      <c r="A43" s="1">
         <f t="shared" si="5"/>
         <v>2001003</v>
       </c>
-      <c r="B40" s="12">
+      <c r="B43" s="12">
         <v>200100</v>
-      </c>
-      <c r="C40" s="12">
-        <v>2</v>
-      </c>
-      <c r="D40" s="12" t="str">
-        <f>D39</f>
-        <v>紅黑大戰</v>
-      </c>
-      <c r="E40" s="13">
-        <v>200100038</v>
-      </c>
-      <c r="F40" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H40" s="1">
-        <v>3</v>
-      </c>
-      <c r="I40" s="1">
-        <v>50000000</v>
-      </c>
-      <c r="J40" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K40" s="1">
-        <v>0</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M40" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="N40">
-        <v>50000000</v>
-      </c>
-      <c r="O40" s="15">
-        <v>1990000</v>
-      </c>
-      <c r="Q40"/>
-    </row>
-    <row r="41" spans="1:19">
-      <c r="A41" s="1">
-        <f t="shared" si="5"/>
-        <v>2001011</v>
-      </c>
-      <c r="B41" s="12">
-        <v>200101</v>
-      </c>
-      <c r="C41" s="12">
-        <v>2</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="E41" s="13">
-        <v>200101001</v>
-      </c>
-      <c r="F41" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H41" s="1">
-        <v>1</v>
-      </c>
-      <c r="I41" s="1">
-        <v>0</v>
-      </c>
-      <c r="J41" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K41" s="1">
-        <v>0</v>
-      </c>
-      <c r="L41" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M41" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="N41">
-        <v>5000</v>
-      </c>
-      <c r="O41" s="15">
-        <v>1990000</v>
-      </c>
-    </row>
-    <row r="42" s="1" customFormat="1" spans="1:19">
-      <c r="A42" s="1">
-        <f t="shared" si="5"/>
-        <v>2001012</v>
-      </c>
-      <c r="B42" s="12">
-        <v>200101</v>
-      </c>
-      <c r="C42" s="12">
-        <v>2</v>
-      </c>
-      <c r="D42" s="12" t="str">
-        <f t="shared" ref="D42:D46" si="6">D41</f>
-        <v>龍虎鬥</v>
-      </c>
-      <c r="E42" s="13">
-        <v>200101001</v>
-      </c>
-      <c r="F42" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H42" s="1">
-        <v>2</v>
-      </c>
-      <c r="I42" s="1">
-        <v>500000</v>
-      </c>
-      <c r="J42" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K42" s="1">
-        <v>0</v>
-      </c>
-      <c r="L42" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M42" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="N42">
-        <v>500000</v>
-      </c>
-      <c r="O42" s="15">
-        <v>1990000</v>
-      </c>
-      <c r="S42" s="3"/>
-    </row>
-    <row r="43" s="1" customFormat="1" spans="1:19">
-      <c r="A43" s="1">
-        <f t="shared" si="5"/>
-        <v>2001013</v>
-      </c>
-      <c r="B43" s="12">
-        <v>200101</v>
       </c>
       <c r="C43" s="12">
         <v>2</v>
       </c>
       <c r="D43" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v>龍虎鬥</v>
+        <f>D42</f>
+        <v>紅黑大戰</v>
       </c>
       <c r="E43" s="13">
-        <v>200101001</v>
+        <v>200100038</v>
       </c>
       <c r="F43" s="13" t="s">
         <v>60</v>
@@ -3704,15 +3703,15 @@
       <c r="O43" s="15">
         <v>1990000</v>
       </c>
-      <c r="S43" s="3"/>
+      <c r="Q43"/>
     </row>
     <row r="44" spans="1:19">
       <c r="A44" s="1">
         <f t="shared" si="5"/>
-        <v>2003001</v>
+        <v>2001011</v>
       </c>
       <c r="B44" s="12">
-        <v>200300</v>
+        <v>200101</v>
       </c>
       <c r="C44" s="12">
         <v>2</v>
@@ -3721,7 +3720,7 @@
         <v>61</v>
       </c>
       <c r="E44" s="13">
-        <v>200300001</v>
+        <v>200101001</v>
       </c>
       <c r="F44" s="13" t="s">
         <v>62</v>
@@ -3757,20 +3756,20 @@
     <row r="45" s="1" customFormat="1" spans="1:19">
       <c r="A45" s="1">
         <f t="shared" si="5"/>
-        <v>2003002</v>
+        <v>2001012</v>
       </c>
       <c r="B45" s="12">
-        <v>200300</v>
+        <v>200101</v>
       </c>
       <c r="C45" s="12">
         <v>2</v>
       </c>
       <c r="D45" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v>飛禽走獸</v>
+        <f t="shared" ref="D45:D49" si="6">D44</f>
+        <v>龍虎鬥</v>
       </c>
       <c r="E45" s="13">
-        <v>200300001</v>
+        <v>200101001</v>
       </c>
       <c r="F45" s="13" t="s">
         <v>62</v>
@@ -3802,27 +3801,25 @@
       <c r="O45" s="15">
         <v>1990000</v>
       </c>
-      <c r="Q45" s="3"/>
-      <c r="R45" s="12"/>
       <c r="S45" s="3"/>
     </row>
     <row r="46" s="1" customFormat="1" spans="1:19">
       <c r="A46" s="1">
         <f t="shared" si="5"/>
-        <v>2003003</v>
+        <v>2001013</v>
       </c>
       <c r="B46" s="12">
-        <v>200300</v>
+        <v>200101</v>
       </c>
       <c r="C46" s="12">
         <v>2</v>
       </c>
       <c r="D46" s="12" t="str">
         <f t="shared" si="6"/>
-        <v>飛禽走獸</v>
+        <v>龍虎鬥</v>
       </c>
       <c r="E46" s="13">
-        <v>200300001</v>
+        <v>200101001</v>
       </c>
       <c r="F46" s="13" t="s">
         <v>62</v>
@@ -3854,26 +3851,24 @@
       <c r="O46" s="15">
         <v>1990000</v>
       </c>
-      <c r="Q46" s="3"/>
-      <c r="R46" s="18"/>
-      <c r="S46" s="18"/>
+      <c r="S46" s="3"/>
     </row>
     <row r="47" spans="1:19">
       <c r="A47" s="1">
         <f t="shared" si="5"/>
-        <v>2004001</v>
+        <v>2003001</v>
       </c>
       <c r="B47" s="12">
-        <v>200400</v>
+        <v>200300</v>
       </c>
       <c r="C47" s="12">
         <v>2</v>
       </c>
-      <c r="D47" s="18" t="s">
+      <c r="D47" s="12" t="s">
         <v>63</v>
       </c>
       <c r="E47" s="13">
-        <v>200400009</v>
+        <v>200300001</v>
       </c>
       <c r="F47" s="13" t="s">
         <v>64</v>
@@ -3905,26 +3900,24 @@
       <c r="O47" s="15">
         <v>1990000</v>
       </c>
-      <c r="Q47" s="3"/>
-      <c r="R47" s="18"/>
-      <c r="S47" s="18"/>
     </row>
     <row r="48" s="1" customFormat="1" spans="1:19">
       <c r="A48" s="1">
         <f t="shared" si="5"/>
-        <v>2004002</v>
+        <v>2003002</v>
       </c>
       <c r="B48" s="12">
-        <v>200400</v>
+        <v>200300</v>
       </c>
       <c r="C48" s="12">
         <v>2</v>
       </c>
-      <c r="D48" s="18" t="s">
-        <v>63</v>
+      <c r="D48" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>飛禽走獸</v>
       </c>
       <c r="E48" s="13">
-        <v>200400009</v>
+        <v>200300001</v>
       </c>
       <c r="F48" s="13" t="s">
         <v>64</v>
@@ -3957,25 +3950,26 @@
         <v>1990000</v>
       </c>
       <c r="Q48" s="3"/>
-      <c r="R48" s="18"/>
-      <c r="S48" s="18"/>
+      <c r="R48" s="12"/>
+      <c r="S48" s="3"/>
     </row>
     <row r="49" s="1" customFormat="1" spans="1:19">
       <c r="A49" s="1">
         <f t="shared" si="5"/>
-        <v>2004003</v>
+        <v>2003003</v>
       </c>
       <c r="B49" s="12">
-        <v>200400</v>
+        <v>200300</v>
       </c>
       <c r="C49" s="12">
         <v>2</v>
       </c>
-      <c r="D49" s="18" t="s">
-        <v>63</v>
+      <c r="D49" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>飛禽走獸</v>
       </c>
       <c r="E49" s="13">
-        <v>200400009</v>
+        <v>200300001</v>
       </c>
       <c r="F49" s="13" t="s">
         <v>64</v>
@@ -4014,19 +4008,19 @@
     <row r="50" spans="1:19">
       <c r="A50" s="1">
         <f t="shared" si="5"/>
-        <v>2005001</v>
+        <v>2004001</v>
       </c>
       <c r="B50" s="12">
-        <v>200500</v>
+        <v>200400</v>
       </c>
       <c r="C50" s="12">
         <v>2</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D50" s="18" t="s">
         <v>65</v>
       </c>
       <c r="E50" s="13">
-        <v>200500025</v>
+        <v>200400009</v>
       </c>
       <c r="F50" s="13" t="s">
         <v>66</v>
@@ -4050,7 +4044,7 @@
         <v>33</v>
       </c>
       <c r="M50" s="23" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="N50">
         <v>5000</v>
@@ -4062,22 +4056,22 @@
       <c r="R50" s="18"/>
       <c r="S50" s="18"/>
     </row>
-    <row r="51" spans="1:19">
+    <row r="51" s="1" customFormat="1" spans="1:19">
       <c r="A51" s="1">
         <f t="shared" si="5"/>
-        <v>2005002</v>
+        <v>2004002</v>
       </c>
       <c r="B51" s="12">
-        <v>200500</v>
+        <v>200400</v>
       </c>
       <c r="C51" s="12">
         <v>2</v>
       </c>
-      <c r="D51" s="12" t="s">
+      <c r="D51" s="18" t="s">
         <v>65</v>
       </c>
       <c r="E51" s="13">
-        <v>200500025</v>
+        <v>200400009</v>
       </c>
       <c r="F51" s="13" t="s">
         <v>66</v>
@@ -4101,7 +4095,7 @@
         <v>33</v>
       </c>
       <c r="M51" s="23" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="N51">
         <v>500000</v>
@@ -4113,22 +4107,22 @@
       <c r="R51" s="18"/>
       <c r="S51" s="18"/>
     </row>
-    <row r="52" spans="1:19">
+    <row r="52" s="1" customFormat="1" spans="1:19">
       <c r="A52" s="1">
         <f t="shared" si="5"/>
-        <v>2005003</v>
+        <v>2004003</v>
       </c>
       <c r="B52" s="12">
-        <v>200500</v>
+        <v>200400</v>
       </c>
       <c r="C52" s="12">
         <v>2</v>
       </c>
-      <c r="D52" s="12" t="s">
+      <c r="D52" s="18" t="s">
         <v>65</v>
       </c>
       <c r="E52" s="13">
-        <v>200500025</v>
+        <v>200400009</v>
       </c>
       <c r="F52" s="13" t="s">
         <v>66</v>
@@ -4152,7 +4146,7 @@
         <v>33</v>
       </c>
       <c r="M52" s="23" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="N52">
         <v>50000000</v>
@@ -4167,22 +4161,22 @@
     <row r="53" spans="1:19">
       <c r="A53" s="1">
         <f t="shared" si="5"/>
-        <v>2006001</v>
+        <v>2005001</v>
       </c>
       <c r="B53" s="12">
-        <v>200600</v>
+        <v>200500</v>
       </c>
       <c r="C53" s="12">
         <v>2</v>
       </c>
-      <c r="D53" s="13" t="s">
+      <c r="D53" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="E53" s="13">
+        <v>200500025</v>
+      </c>
+      <c r="F53" s="13" t="s">
         <v>68</v>
-      </c>
-      <c r="E53" s="13">
-        <v>200600001</v>
-      </c>
-      <c r="F53" s="13" t="s">
-        <v>69</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>32</v>
@@ -4203,7 +4197,7 @@
         <v>33</v>
       </c>
       <c r="M53" s="23" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="N53">
         <v>5000</v>
@@ -4215,25 +4209,25 @@
       <c r="R53" s="18"/>
       <c r="S53" s="18"/>
     </row>
-    <row r="54" s="1" customFormat="1" spans="1:19">
+    <row r="54" spans="1:19">
       <c r="A54" s="1">
         <f t="shared" si="5"/>
-        <v>2006002</v>
+        <v>2005002</v>
       </c>
       <c r="B54" s="12">
-        <v>200600</v>
+        <v>200500</v>
       </c>
       <c r="C54" s="12">
         <v>2</v>
       </c>
-      <c r="D54" s="13" t="s">
+      <c r="D54" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="E54" s="13">
+        <v>200500025</v>
+      </c>
+      <c r="F54" s="13" t="s">
         <v>68</v>
-      </c>
-      <c r="E54" s="13">
-        <v>200600001</v>
-      </c>
-      <c r="F54" s="13" t="s">
-        <v>69</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>35</v>
@@ -4254,7 +4248,7 @@
         <v>33</v>
       </c>
       <c r="M54" s="23" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="N54">
         <v>500000</v>
@@ -4266,25 +4260,25 @@
       <c r="R54" s="18"/>
       <c r="S54" s="18"/>
     </row>
-    <row r="55" s="1" customFormat="1" spans="1:19">
+    <row r="55" spans="1:19">
       <c r="A55" s="1">
         <f t="shared" si="5"/>
-        <v>2006003</v>
+        <v>2005003</v>
       </c>
       <c r="B55" s="12">
-        <v>200600</v>
+        <v>200500</v>
       </c>
       <c r="C55" s="12">
         <v>2</v>
       </c>
-      <c r="D55" s="13" t="s">
+      <c r="D55" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="E55" s="13">
+        <v>200500025</v>
+      </c>
+      <c r="F55" s="13" t="s">
         <v>68</v>
-      </c>
-      <c r="E55" s="13">
-        <v>200600001</v>
-      </c>
-      <c r="F55" s="13" t="s">
-        <v>69</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>36</v>
@@ -4305,7 +4299,7 @@
         <v>33</v>
       </c>
       <c r="M55" s="23" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="N55">
         <v>50000000</v>
@@ -4314,25 +4308,25 @@
         <v>1990000</v>
       </c>
       <c r="Q55" s="3"/>
-      <c r="R55"/>
+      <c r="R55" s="18"/>
       <c r="S55" s="18"/>
     </row>
     <row r="56" spans="1:19">
       <c r="A56" s="1">
         <f t="shared" si="5"/>
-        <v>2007001</v>
+        <v>2006001</v>
       </c>
       <c r="B56" s="12">
-        <v>200700</v>
+        <v>200600</v>
       </c>
       <c r="C56" s="12">
         <v>2</v>
       </c>
-      <c r="D56" s="12" t="s">
+      <c r="D56" s="13" t="s">
         <v>70</v>
       </c>
       <c r="E56" s="13">
-        <v>200700001</v>
+        <v>200600001</v>
       </c>
       <c r="F56" s="13" t="s">
         <v>71</v>
@@ -4371,20 +4365,19 @@
     <row r="57" s="1" customFormat="1" spans="1:19">
       <c r="A57" s="1">
         <f t="shared" si="5"/>
-        <v>2007002</v>
+        <v>2006002</v>
       </c>
       <c r="B57" s="12">
-        <v>200700</v>
+        <v>200600</v>
       </c>
       <c r="C57" s="12">
         <v>2</v>
       </c>
-      <c r="D57" s="12" t="str">
-        <f t="shared" ref="D54:D58" si="7">D56</f>
-        <v>越南色碟</v>
+      <c r="D57" s="13" t="s">
+        <v>70</v>
       </c>
       <c r="E57" s="13">
-        <v>200700001</v>
+        <v>200600001</v>
       </c>
       <c r="F57" s="13" t="s">
         <v>71</v>
@@ -4423,20 +4416,19 @@
     <row r="58" s="1" customFormat="1" spans="1:19">
       <c r="A58" s="1">
         <f t="shared" si="5"/>
-        <v>2007003</v>
+        <v>2006003</v>
       </c>
       <c r="B58" s="12">
-        <v>200700</v>
+        <v>200600</v>
       </c>
       <c r="C58" s="12">
         <v>2</v>
       </c>
-      <c r="D58" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v>越南色碟</v>
+      <c r="D58" s="13" t="s">
+        <v>70</v>
       </c>
       <c r="E58" s="13">
-        <v>200700001</v>
+        <v>200600001</v>
       </c>
       <c r="F58" s="13" t="s">
         <v>71</v>
@@ -4468,24 +4460,26 @@
       <c r="O58" s="15">
         <v>1990000</v>
       </c>
-      <c r="S58" s="3"/>
-    </row>
-    <row r="59" s="1" customFormat="1" spans="1:19">
+      <c r="Q58" s="3"/>
+      <c r="R58"/>
+      <c r="S58" s="18"/>
+    </row>
+    <row r="59" spans="1:19">
       <c r="A59" s="1">
         <f t="shared" si="5"/>
-        <v>2008001</v>
+        <v>2007001</v>
       </c>
       <c r="B59" s="12">
-        <v>200800</v>
+        <v>200700</v>
       </c>
       <c r="C59" s="12">
         <v>2</v>
       </c>
-      <c r="D59" s="13" t="s">
+      <c r="D59" s="12" t="s">
         <v>72</v>
       </c>
       <c r="E59" s="13">
-        <v>200800001</v>
+        <v>200700001</v>
       </c>
       <c r="F59" s="13" t="s">
         <v>73</v>
@@ -4517,24 +4511,27 @@
       <c r="O59" s="15">
         <v>1990000</v>
       </c>
-      <c r="S59" s="3"/>
+      <c r="Q59" s="3"/>
+      <c r="R59" s="18"/>
+      <c r="S59" s="18"/>
     </row>
     <row r="60" s="1" customFormat="1" spans="1:19">
       <c r="A60" s="1">
         <f t="shared" si="5"/>
-        <v>2008002</v>
+        <v>2007002</v>
       </c>
       <c r="B60" s="12">
-        <v>200800</v>
+        <v>200700</v>
       </c>
       <c r="C60" s="12">
         <v>2</v>
       </c>
-      <c r="D60" s="13" t="s">
-        <v>72</v>
+      <c r="D60" s="12" t="str">
+        <f t="shared" ref="D57:D61" si="7">D59</f>
+        <v>越南色碟</v>
       </c>
       <c r="E60" s="13">
-        <v>200800001</v>
+        <v>200700001</v>
       </c>
       <c r="F60" s="13" t="s">
         <v>73</v>
@@ -4566,24 +4563,27 @@
       <c r="O60" s="15">
         <v>1990000</v>
       </c>
-      <c r="S60" s="3"/>
+      <c r="Q60" s="3"/>
+      <c r="R60" s="18"/>
+      <c r="S60" s="18"/>
     </row>
     <row r="61" s="1" customFormat="1" spans="1:19">
       <c r="A61" s="1">
         <f t="shared" si="5"/>
-        <v>2008003</v>
+        <v>2007003</v>
       </c>
       <c r="B61" s="12">
-        <v>200800</v>
+        <v>200700</v>
       </c>
       <c r="C61" s="12">
         <v>2</v>
       </c>
-      <c r="D61" s="13" t="s">
-        <v>72</v>
+      <c r="D61" s="12" t="str">
+        <f t="shared" si="7"/>
+        <v>越南色碟</v>
       </c>
       <c r="E61" s="13">
-        <v>200800001</v>
+        <v>200700001</v>
       </c>
       <c r="F61" s="13" t="s">
         <v>73</v>
@@ -4617,22 +4617,22 @@
       </c>
       <c r="S61" s="3"/>
     </row>
-    <row r="62" spans="1:19">
+    <row r="62" s="1" customFormat="1" spans="1:19">
       <c r="A62" s="1">
         <f t="shared" si="5"/>
-        <v>2009001</v>
-      </c>
-      <c r="B62" s="19">
-        <v>200900</v>
+        <v>2008001</v>
+      </c>
+      <c r="B62" s="12">
+        <v>200800</v>
       </c>
       <c r="C62" s="12">
         <v>2</v>
       </c>
-      <c r="D62" s="19" t="s">
+      <c r="D62" s="13" t="s">
         <v>74</v>
       </c>
       <c r="E62" s="13">
-        <v>200900001</v>
+        <v>200800001</v>
       </c>
       <c r="F62" s="13" t="s">
         <v>75</v>
@@ -4664,24 +4664,24 @@
       <c r="O62" s="15">
         <v>1990000</v>
       </c>
-    </row>
-    <row r="63" spans="1:19">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" s="1" customFormat="1" spans="1:19">
       <c r="A63" s="1">
         <f t="shared" si="5"/>
-        <v>2009002</v>
+        <v>2008002</v>
       </c>
       <c r="B63" s="12">
-        <v>200900</v>
+        <v>200800</v>
       </c>
       <c r="C63" s="12">
         <v>2</v>
       </c>
-      <c r="D63" s="12" t="str">
-        <f>D62</f>
-        <v>魚蝦蟹</v>
+      <c r="D63" s="13" t="s">
+        <v>74</v>
       </c>
       <c r="E63" s="13">
-        <v>200900001</v>
+        <v>200800001</v>
       </c>
       <c r="F63" s="13" t="s">
         <v>75</v>
@@ -4713,24 +4713,24 @@
       <c r="O63" s="15">
         <v>1990000</v>
       </c>
-    </row>
-    <row r="64" spans="1:19">
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" s="1" customFormat="1" spans="1:19">
       <c r="A64" s="1">
         <f t="shared" si="5"/>
-        <v>2009003</v>
+        <v>2008003</v>
       </c>
       <c r="B64" s="12">
-        <v>200900</v>
+        <v>200800</v>
       </c>
       <c r="C64" s="12">
         <v>2</v>
       </c>
-      <c r="D64" s="12" t="str">
-        <f>D63</f>
-        <v>魚蝦蟹</v>
+      <c r="D64" s="13" t="s">
+        <v>74</v>
       </c>
       <c r="E64" s="13">
-        <v>200900001</v>
+        <v>200800001</v>
       </c>
       <c r="F64" s="13" t="s">
         <v>75</v>
@@ -4762,25 +4762,28 @@
       <c r="O64" s="15">
         <v>1990000</v>
       </c>
+      <c r="S64" s="3"/>
     </row>
     <row r="65" spans="1:19">
       <c r="A65" s="1">
         <f t="shared" si="5"/>
-        <v>2010001</v>
-      </c>
-      <c r="B65" s="12">
-        <v>201000</v>
+        <v>2009001</v>
+      </c>
+      <c r="B65" s="19">
+        <v>200900</v>
       </c>
       <c r="C65" s="12">
         <v>2</v>
       </c>
-      <c r="D65" s="12" t="s">
+      <c r="D65" s="19" t="s">
         <v>76</v>
       </c>
       <c r="E65" s="13">
-        <v>101000006</v>
-      </c>
-      <c r="F65" s="13"/>
+        <v>200900001</v>
+      </c>
+      <c r="F65" s="13" t="s">
+        <v>77</v>
+      </c>
       <c r="G65" s="1" t="s">
         <v>32</v>
       </c>
@@ -4812,21 +4815,24 @@
     <row r="66" spans="1:19">
       <c r="A66" s="1">
         <f t="shared" si="5"/>
-        <v>2010002</v>
+        <v>2009002</v>
       </c>
       <c r="B66" s="12">
-        <v>201000</v>
+        <v>200900</v>
       </c>
       <c r="C66" s="12">
         <v>2</v>
       </c>
-      <c r="D66" s="12" t="s">
-        <v>76</v>
+      <c r="D66" s="12" t="str">
+        <f>D65</f>
+        <v>魚蝦蟹</v>
       </c>
       <c r="E66" s="13">
-        <v>101000006</v>
-      </c>
-      <c r="F66" s="13"/>
+        <v>200900001</v>
+      </c>
+      <c r="F66" s="13" t="s">
+        <v>77</v>
+      </c>
       <c r="G66" s="1" t="s">
         <v>35</v>
       </c>
@@ -4858,21 +4864,24 @@
     <row r="67" spans="1:19">
       <c r="A67" s="1">
         <f t="shared" si="5"/>
-        <v>2010003</v>
+        <v>2009003</v>
       </c>
       <c r="B67" s="12">
-        <v>201000</v>
+        <v>200900</v>
       </c>
       <c r="C67" s="12">
         <v>2</v>
       </c>
-      <c r="D67" s="12" t="s">
-        <v>76</v>
+      <c r="D67" s="12" t="str">
+        <f>D66</f>
+        <v>魚蝦蟹</v>
       </c>
       <c r="E67" s="13">
-        <v>101000006</v>
-      </c>
-      <c r="F67" s="13"/>
+        <v>200900001</v>
+      </c>
+      <c r="F67" s="13" t="s">
+        <v>77</v>
+      </c>
       <c r="G67" s="1" t="s">
         <v>36</v>
       </c>
@@ -4904,23 +4913,21 @@
     <row r="68" spans="1:19">
       <c r="A68" s="1">
         <f t="shared" si="5"/>
-        <v>3001001</v>
+        <v>2010001</v>
       </c>
       <c r="B68" s="12">
-        <v>300100</v>
+        <v>201000</v>
       </c>
       <c r="C68" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E68" s="13">
-        <v>300100001</v>
-      </c>
-      <c r="F68" s="13" t="s">
-        <v>78</v>
-      </c>
+        <v>101000006</v>
+      </c>
+      <c r="F68" s="13"/>
       <c r="G68" s="1" t="s">
         <v>32</v>
       </c>
@@ -4936,11 +4943,11 @@
       <c r="K68" s="1">
         <v>0</v>
       </c>
-      <c r="L68" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="M68" s="24" t="s">
-        <v>80</v>
+      <c r="L68" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M68" s="23" t="s">
+        <v>34</v>
       </c>
       <c r="N68">
         <v>5000</v>
@@ -4949,26 +4956,24 @@
         <v>1990000</v>
       </c>
     </row>
-    <row r="69" s="1" customFormat="1" spans="1:19">
+    <row r="69" spans="1:19">
       <c r="A69" s="1">
         <f t="shared" si="5"/>
-        <v>3001002</v>
+        <v>2010002</v>
       </c>
       <c r="B69" s="12">
-        <v>300100</v>
+        <v>201000</v>
       </c>
       <c r="C69" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E69" s="13">
-        <v>300100001</v>
-      </c>
-      <c r="F69" s="13" t="s">
-        <v>78</v>
-      </c>
+        <v>101000006</v>
+      </c>
+      <c r="F69" s="13"/>
       <c r="G69" s="1" t="s">
         <v>35</v>
       </c>
@@ -4984,11 +4989,11 @@
       <c r="K69" s="1">
         <v>0</v>
       </c>
-      <c r="L69" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="M69" s="24" t="s">
-        <v>80</v>
+      <c r="L69" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M69" s="23" t="s">
+        <v>34</v>
       </c>
       <c r="N69">
         <v>500000</v>
@@ -4996,28 +5001,25 @@
       <c r="O69" s="15">
         <v>1990000</v>
       </c>
-      <c r="S69" s="3"/>
-    </row>
-    <row r="70" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="70" spans="1:19">
       <c r="A70" s="1">
         <f t="shared" si="5"/>
-        <v>3001003</v>
+        <v>2010003</v>
       </c>
       <c r="B70" s="12">
-        <v>300100</v>
+        <v>201000</v>
       </c>
       <c r="C70" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E70" s="13">
-        <v>300100001</v>
-      </c>
-      <c r="F70" s="13" t="s">
-        <v>78</v>
-      </c>
+        <v>101000006</v>
+      </c>
+      <c r="F70" s="13"/>
       <c r="G70" s="1" t="s">
         <v>36</v>
       </c>
@@ -5033,11 +5035,11 @@
       <c r="K70" s="1">
         <v>0</v>
       </c>
-      <c r="L70" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="M70" s="24" t="s">
-        <v>80</v>
+      <c r="L70" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M70" s="23" t="s">
+        <v>34</v>
       </c>
       <c r="N70">
         <v>50000000</v>
@@ -5045,27 +5047,26 @@
       <c r="O70" s="15">
         <v>1990000</v>
       </c>
-      <c r="S70" s="3"/>
-    </row>
-    <row r="71" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="71" spans="1:19">
       <c r="A71" s="1">
         <f t="shared" si="5"/>
-        <v>3002001</v>
+        <v>3001001</v>
       </c>
       <c r="B71" s="12">
-        <v>300200</v>
+        <v>300100</v>
       </c>
       <c r="C71" s="12">
         <v>3</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E71" s="13">
-        <v>300200006</v>
+        <v>300100001</v>
       </c>
       <c r="F71" s="13" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>32</v>
@@ -5074,7 +5075,7 @@
         <v>1</v>
       </c>
       <c r="I71" s="1">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="J71" s="1">
         <v>-1</v>
@@ -5083,10 +5084,10 @@
         <v>0</v>
       </c>
       <c r="L71" s="24" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="M71" s="24" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="N71">
         <v>5000</v>
@@ -5094,27 +5095,26 @@
       <c r="O71" s="15">
         <v>1990000</v>
       </c>
-      <c r="S71" s="3"/>
     </row>
     <row r="72" s="1" customFormat="1" spans="1:19">
       <c r="A72" s="1">
         <f t="shared" si="5"/>
-        <v>3002002</v>
+        <v>3001002</v>
       </c>
       <c r="B72" s="12">
-        <v>300200</v>
+        <v>300100</v>
       </c>
       <c r="C72" s="12">
         <v>3</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E72" s="13">
-        <v>300200006</v>
+        <v>300100001</v>
       </c>
       <c r="F72" s="13" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>35</v>
@@ -5132,10 +5132,10 @@
         <v>0</v>
       </c>
       <c r="L72" s="24" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="M72" s="24" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="N72">
         <v>500000</v>
@@ -5148,22 +5148,22 @@
     <row r="73" s="1" customFormat="1" spans="1:19">
       <c r="A73" s="1">
         <f t="shared" si="5"/>
-        <v>3002003</v>
+        <v>3001003</v>
       </c>
       <c r="B73" s="12">
-        <v>300200</v>
+        <v>300100</v>
       </c>
       <c r="C73" s="12">
         <v>3</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E73" s="13">
-        <v>300200006</v>
+        <v>300100001</v>
       </c>
       <c r="F73" s="13" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>36</v>
@@ -5181,10 +5181,10 @@
         <v>0</v>
       </c>
       <c r="L73" s="24" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="M73" s="24" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="N73">
         <v>50000000</v>
@@ -5196,154 +5196,157 @@
     </row>
     <row r="74" s="1" customFormat="1" spans="1:19">
       <c r="A74" s="1">
-        <v>20010010</v>
-      </c>
-      <c r="B74" s="16">
-        <v>200100</v>
-      </c>
-      <c r="C74" s="16">
-        <v>2</v>
-      </c>
-      <c r="D74" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="E74" s="16">
-        <v>200100038</v>
-      </c>
-      <c r="F74" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="G74" s="17" t="s">
+        <f t="shared" si="5"/>
+        <v>3002001</v>
+      </c>
+      <c r="B74" s="12">
+        <v>300200</v>
+      </c>
+      <c r="C74" s="12">
+        <v>3</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="E74" s="13">
+        <v>300200006</v>
+      </c>
+      <c r="F74" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="H74" s="17">
-        <v>10</v>
-      </c>
-      <c r="I74" s="17">
-        <v>0</v>
-      </c>
-      <c r="J74" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K74" s="17">
-        <v>0</v>
-      </c>
-      <c r="L74" s="17" t="s">
+      <c r="G74" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H74" s="1">
+        <v>1</v>
+      </c>
+      <c r="I74" s="1">
+        <v>2000</v>
+      </c>
+      <c r="J74" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K74" s="1">
+        <v>0</v>
+      </c>
+      <c r="L74" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="M74" s="17">
-        <v>0</v>
-      </c>
-      <c r="N74" s="20">
-        <v>200</v>
-      </c>
-      <c r="O74" s="21">
-        <v>1980000</v>
+      <c r="M74" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="N74">
+        <v>5000</v>
+      </c>
+      <c r="O74" s="15">
+        <v>1990000</v>
       </c>
       <c r="S74" s="3"/>
     </row>
     <row r="75" s="1" customFormat="1" spans="1:19">
       <c r="A75" s="1">
-        <v>20010011</v>
-      </c>
-      <c r="B75" s="16">
-        <v>200100</v>
-      </c>
-      <c r="C75" s="16">
+        <f t="shared" si="5"/>
+        <v>3002002</v>
+      </c>
+      <c r="B75" s="12">
+        <v>300200</v>
+      </c>
+      <c r="C75" s="12">
+        <v>3</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="E75" s="13">
+        <v>300200006</v>
+      </c>
+      <c r="F75" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H75" s="1">
         <v>2</v>
       </c>
-      <c r="D75" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="E75" s="16">
-        <v>200100038</v>
-      </c>
-      <c r="F75" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="G75" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="H75" s="17">
-        <v>11</v>
-      </c>
-      <c r="I75" s="17">
-        <v>0</v>
-      </c>
-      <c r="J75" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K75" s="17">
-        <v>0</v>
-      </c>
-      <c r="L75" s="17" t="s">
+      <c r="I75" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J75" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K75" s="1">
+        <v>0</v>
+      </c>
+      <c r="L75" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="M75" s="17">
-        <v>0</v>
-      </c>
-      <c r="N75" s="20">
-        <v>5000</v>
-      </c>
-      <c r="O75" s="21">
-        <v>1980000</v>
+      <c r="M75" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="N75">
+        <v>500000</v>
+      </c>
+      <c r="O75" s="15">
+        <v>1990000</v>
       </c>
       <c r="S75" s="3"/>
     </row>
     <row r="76" s="1" customFormat="1" spans="1:19">
       <c r="A76" s="1">
-        <v>20010012</v>
-      </c>
-      <c r="B76" s="16">
-        <v>200100</v>
-      </c>
-      <c r="C76" s="16">
-        <v>2</v>
-      </c>
-      <c r="D76" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="E76" s="16">
-        <v>200100038</v>
-      </c>
-      <c r="F76" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="G76" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="H76" s="17">
-        <v>12</v>
-      </c>
-      <c r="I76" s="17">
-        <v>0</v>
-      </c>
-      <c r="J76" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K76" s="17">
-        <v>0</v>
-      </c>
-      <c r="L76" s="17" t="s">
+        <f t="shared" si="5"/>
+        <v>3002003</v>
+      </c>
+      <c r="B76" s="12">
+        <v>300200</v>
+      </c>
+      <c r="C76" s="12">
+        <v>3</v>
+      </c>
+      <c r="D76" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="E76" s="13">
+        <v>300200006</v>
+      </c>
+      <c r="F76" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H76" s="1">
+        <v>3</v>
+      </c>
+      <c r="I76" s="1">
+        <v>50000000</v>
+      </c>
+      <c r="J76" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K76" s="1">
+        <v>0</v>
+      </c>
+      <c r="L76" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="M76" s="17">
-        <v>0</v>
-      </c>
-      <c r="N76" s="20">
-        <v>100000</v>
-      </c>
-      <c r="O76" s="21">
-        <v>1980000</v>
+      <c r="M76" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="N76">
+        <v>50000000</v>
+      </c>
+      <c r="O76" s="15">
+        <v>1990000</v>
       </c>
       <c r="S76" s="3"/>
     </row>
     <row r="77" s="1" customFormat="1" spans="1:19">
       <c r="A77" s="1">
-        <v>20010110</v>
+        <v>20010010</v>
       </c>
       <c r="B77" s="16">
-        <v>200101</v>
+        <v>200100</v>
       </c>
       <c r="C77" s="16">
         <v>2</v>
@@ -5352,13 +5355,13 @@
         <v>59</v>
       </c>
       <c r="E77" s="16">
-        <v>200101001</v>
+        <v>200100038</v>
       </c>
       <c r="F77" s="16" t="s">
         <v>60</v>
       </c>
       <c r="G77" s="17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H77" s="17">
         <v>10</v>
@@ -5373,7 +5376,7 @@
         <v>0</v>
       </c>
       <c r="L77" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M77" s="17">
         <v>0</v>
@@ -5388,10 +5391,10 @@
     </row>
     <row r="78" s="1" customFormat="1" spans="1:19">
       <c r="A78" s="1">
-        <v>20010111</v>
+        <v>20010011</v>
       </c>
       <c r="B78" s="16">
-        <v>200101</v>
+        <v>200100</v>
       </c>
       <c r="C78" s="16">
         <v>2</v>
@@ -5400,13 +5403,13 @@
         <v>59</v>
       </c>
       <c r="E78" s="16">
-        <v>200101001</v>
+        <v>200100038</v>
       </c>
       <c r="F78" s="16" t="s">
         <v>60</v>
       </c>
       <c r="G78" s="17" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H78" s="17">
         <v>11</v>
@@ -5421,7 +5424,7 @@
         <v>0</v>
       </c>
       <c r="L78" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M78" s="17">
         <v>0</v>
@@ -5436,10 +5439,10 @@
     </row>
     <row r="79" s="1" customFormat="1" spans="1:19">
       <c r="A79" s="1">
-        <v>20010112</v>
+        <v>20010012</v>
       </c>
       <c r="B79" s="16">
-        <v>200101</v>
+        <v>200100</v>
       </c>
       <c r="C79" s="16">
         <v>2</v>
@@ -5448,13 +5451,13 @@
         <v>59</v>
       </c>
       <c r="E79" s="16">
-        <v>200101001</v>
+        <v>200100038</v>
       </c>
       <c r="F79" s="16" t="s">
         <v>60</v>
       </c>
       <c r="G79" s="17" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H79" s="17">
         <v>12</v>
@@ -5469,7 +5472,7 @@
         <v>0</v>
       </c>
       <c r="L79" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M79" s="17">
         <v>0</v>
@@ -5484,10 +5487,10 @@
     </row>
     <row r="80" s="1" customFormat="1" spans="1:19">
       <c r="A80" s="1">
-        <v>20030010</v>
+        <v>20010110</v>
       </c>
       <c r="B80" s="16">
-        <v>200300</v>
+        <v>200101</v>
       </c>
       <c r="C80" s="16">
         <v>2</v>
@@ -5496,13 +5499,13 @@
         <v>61</v>
       </c>
       <c r="E80" s="16">
-        <v>200300001</v>
+        <v>200101001</v>
       </c>
       <c r="F80" s="16" t="s">
         <v>62</v>
       </c>
       <c r="G80" s="17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H80" s="17">
         <v>10</v>
@@ -5517,7 +5520,7 @@
         <v>0</v>
       </c>
       <c r="L80" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M80" s="17">
         <v>0</v>
@@ -5532,10 +5535,10 @@
     </row>
     <row r="81" s="1" customFormat="1" spans="1:19">
       <c r="A81" s="1">
-        <v>20030011</v>
+        <v>20010111</v>
       </c>
       <c r="B81" s="16">
-        <v>200300</v>
+        <v>200101</v>
       </c>
       <c r="C81" s="16">
         <v>2</v>
@@ -5544,13 +5547,13 @@
         <v>61</v>
       </c>
       <c r="E81" s="16">
-        <v>200300001</v>
+        <v>200101001</v>
       </c>
       <c r="F81" s="16" t="s">
         <v>62</v>
       </c>
       <c r="G81" s="17" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H81" s="17">
         <v>11</v>
@@ -5565,7 +5568,7 @@
         <v>0</v>
       </c>
       <c r="L81" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M81" s="17">
         <v>0</v>
@@ -5580,10 +5583,10 @@
     </row>
     <row r="82" s="1" customFormat="1" spans="1:19">
       <c r="A82" s="1">
-        <v>20030012</v>
+        <v>20010112</v>
       </c>
       <c r="B82" s="16">
-        <v>200300</v>
+        <v>200101</v>
       </c>
       <c r="C82" s="16">
         <v>2</v>
@@ -5592,13 +5595,13 @@
         <v>61</v>
       </c>
       <c r="E82" s="16">
-        <v>200300001</v>
+        <v>200101001</v>
       </c>
       <c r="F82" s="16" t="s">
         <v>62</v>
       </c>
       <c r="G82" s="17" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H82" s="17">
         <v>12</v>
@@ -5613,7 +5616,7 @@
         <v>0</v>
       </c>
       <c r="L82" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M82" s="17">
         <v>0</v>
@@ -5628,25 +5631,25 @@
     </row>
     <row r="83" s="1" customFormat="1" spans="1:19">
       <c r="A83" s="1">
-        <v>20040010</v>
+        <v>20030010</v>
       </c>
       <c r="B83" s="16">
-        <v>200400</v>
+        <v>200300</v>
       </c>
       <c r="C83" s="16">
         <v>2</v>
       </c>
-      <c r="D83" s="22" t="s">
+      <c r="D83" s="16" t="s">
         <v>63</v>
       </c>
       <c r="E83" s="16">
-        <v>200400009</v>
+        <v>200300001</v>
       </c>
       <c r="F83" s="16" t="s">
         <v>64</v>
       </c>
       <c r="G83" s="17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H83" s="17">
         <v>10</v>
@@ -5661,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="L83" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M83" s="17">
         <v>0</v>
@@ -5676,25 +5679,25 @@
     </row>
     <row r="84" s="1" customFormat="1" spans="1:19">
       <c r="A84" s="1">
-        <v>20040011</v>
+        <v>20030011</v>
       </c>
       <c r="B84" s="16">
-        <v>200400</v>
+        <v>200300</v>
       </c>
       <c r="C84" s="16">
         <v>2</v>
       </c>
-      <c r="D84" s="22" t="s">
+      <c r="D84" s="16" t="s">
         <v>63</v>
       </c>
       <c r="E84" s="16">
-        <v>200400009</v>
+        <v>200300001</v>
       </c>
       <c r="F84" s="16" t="s">
         <v>64</v>
       </c>
       <c r="G84" s="17" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H84" s="17">
         <v>11</v>
@@ -5709,7 +5712,7 @@
         <v>0</v>
       </c>
       <c r="L84" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M84" s="17">
         <v>0</v>
@@ -5724,25 +5727,25 @@
     </row>
     <row r="85" s="1" customFormat="1" spans="1:19">
       <c r="A85" s="1">
-        <v>20040012</v>
+        <v>20030012</v>
       </c>
       <c r="B85" s="16">
-        <v>200400</v>
+        <v>200300</v>
       </c>
       <c r="C85" s="16">
         <v>2</v>
       </c>
-      <c r="D85" s="22" t="s">
+      <c r="D85" s="16" t="s">
         <v>63</v>
       </c>
       <c r="E85" s="16">
-        <v>200400009</v>
+        <v>200300001</v>
       </c>
       <c r="F85" s="16" t="s">
         <v>64</v>
       </c>
       <c r="G85" s="17" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H85" s="17">
         <v>12</v>
@@ -5757,7 +5760,7 @@
         <v>0</v>
       </c>
       <c r="L85" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M85" s="17">
         <v>0</v>
@@ -5772,25 +5775,25 @@
     </row>
     <row r="86" s="1" customFormat="1" spans="1:19">
       <c r="A86" s="1">
-        <v>20050010</v>
+        <v>20040010</v>
       </c>
       <c r="B86" s="16">
-        <v>200500</v>
+        <v>200400</v>
       </c>
       <c r="C86" s="16">
         <v>2</v>
       </c>
-      <c r="D86" s="16" t="s">
+      <c r="D86" s="22" t="s">
         <v>65</v>
       </c>
       <c r="E86" s="16">
-        <v>200500025</v>
+        <v>200400009</v>
       </c>
       <c r="F86" s="16" t="s">
         <v>66</v>
       </c>
       <c r="G86" s="17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H86" s="17">
         <v>10</v>
@@ -5805,7 +5808,7 @@
         <v>0</v>
       </c>
       <c r="L86" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M86" s="17">
         <v>0</v>
@@ -5820,25 +5823,25 @@
     </row>
     <row r="87" s="1" customFormat="1" spans="1:19">
       <c r="A87" s="1">
-        <v>20050011</v>
+        <v>20040011</v>
       </c>
       <c r="B87" s="16">
-        <v>200500</v>
+        <v>200400</v>
       </c>
       <c r="C87" s="16">
         <v>2</v>
       </c>
-      <c r="D87" s="16" t="s">
+      <c r="D87" s="22" t="s">
         <v>65</v>
       </c>
       <c r="E87" s="16">
-        <v>200500025</v>
+        <v>200400009</v>
       </c>
       <c r="F87" s="16" t="s">
         <v>66</v>
       </c>
       <c r="G87" s="17" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H87" s="17">
         <v>11</v>
@@ -5853,7 +5856,7 @@
         <v>0</v>
       </c>
       <c r="L87" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M87" s="17">
         <v>0</v>
@@ -5868,25 +5871,25 @@
     </row>
     <row r="88" s="1" customFormat="1" spans="1:19">
       <c r="A88" s="1">
-        <v>20050012</v>
+        <v>20040012</v>
       </c>
       <c r="B88" s="16">
-        <v>200500</v>
+        <v>200400</v>
       </c>
       <c r="C88" s="16">
         <v>2</v>
       </c>
-      <c r="D88" s="16" t="s">
+      <c r="D88" s="22" t="s">
         <v>65</v>
       </c>
       <c r="E88" s="16">
-        <v>200500025</v>
+        <v>200400009</v>
       </c>
       <c r="F88" s="16" t="s">
         <v>66</v>
       </c>
       <c r="G88" s="17" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H88" s="17">
         <v>12</v>
@@ -5901,7 +5904,7 @@
         <v>0</v>
       </c>
       <c r="L88" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M88" s="17">
         <v>0</v>
@@ -5914,27 +5917,27 @@
       </c>
       <c r="S88" s="3"/>
     </row>
-    <row r="89" spans="1:19">
+    <row r="89" s="1" customFormat="1" spans="1:19">
       <c r="A89" s="1">
-        <v>20060010</v>
+        <v>20050010</v>
       </c>
       <c r="B89" s="16">
-        <v>200600</v>
+        <v>200500</v>
       </c>
       <c r="C89" s="16">
         <v>2</v>
       </c>
       <c r="D89" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E89" s="16">
+        <v>200500025</v>
+      </c>
+      <c r="F89" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="E89" s="16">
-        <v>200600001</v>
-      </c>
-      <c r="F89" s="16" t="s">
-        <v>69</v>
-      </c>
       <c r="G89" s="17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H89" s="17">
         <v>10</v>
@@ -5949,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="L89" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M89" s="17">
         <v>0</v>
@@ -5960,28 +5963,29 @@
       <c r="O89" s="21">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="90" spans="1:19">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" s="1" customFormat="1" spans="1:19">
       <c r="A90" s="1">
-        <v>20060011</v>
+        <v>20050011</v>
       </c>
       <c r="B90" s="16">
-        <v>200600</v>
+        <v>200500</v>
       </c>
       <c r="C90" s="16">
         <v>2</v>
       </c>
       <c r="D90" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E90" s="16">
+        <v>200500025</v>
+      </c>
+      <c r="F90" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="E90" s="16">
-        <v>200600001</v>
-      </c>
-      <c r="F90" s="16" t="s">
-        <v>69</v>
-      </c>
       <c r="G90" s="17" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H90" s="17">
         <v>11</v>
@@ -5996,7 +6000,7 @@
         <v>0</v>
       </c>
       <c r="L90" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M90" s="17">
         <v>0</v>
@@ -6007,28 +6011,29 @@
       <c r="O90" s="21">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="91" spans="1:19">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" s="1" customFormat="1" spans="1:19">
       <c r="A91" s="1">
-        <v>20060012</v>
+        <v>20050012</v>
       </c>
       <c r="B91" s="16">
-        <v>200600</v>
+        <v>200500</v>
       </c>
       <c r="C91" s="16">
         <v>2</v>
       </c>
       <c r="D91" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E91" s="16">
+        <v>200500025</v>
+      </c>
+      <c r="F91" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="E91" s="16">
-        <v>200600001</v>
-      </c>
-      <c r="F91" s="16" t="s">
-        <v>69</v>
-      </c>
       <c r="G91" s="17" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H91" s="17">
         <v>12</v>
@@ -6043,7 +6048,7 @@
         <v>0</v>
       </c>
       <c r="L91" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M91" s="17">
         <v>0</v>
@@ -6054,13 +6059,14 @@
       <c r="O91" s="21">
         <v>1980000</v>
       </c>
+      <c r="S91" s="3"/>
     </row>
     <row r="92" spans="1:19">
       <c r="A92" s="1">
-        <v>20070010</v>
+        <v>20060010</v>
       </c>
       <c r="B92" s="16">
-        <v>200700</v>
+        <v>200600</v>
       </c>
       <c r="C92" s="16">
         <v>2</v>
@@ -6069,13 +6075,13 @@
         <v>70</v>
       </c>
       <c r="E92" s="16">
-        <v>200700001</v>
+        <v>200600001</v>
       </c>
       <c r="F92" s="16" t="s">
         <v>71</v>
       </c>
       <c r="G92" s="17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H92" s="17">
         <v>10</v>
@@ -6090,7 +6096,7 @@
         <v>0</v>
       </c>
       <c r="L92" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M92" s="17">
         <v>0</v>
@@ -6104,26 +6110,25 @@
     </row>
     <row r="93" spans="1:19">
       <c r="A93" s="1">
-        <v>20070011</v>
+        <v>20060011</v>
       </c>
       <c r="B93" s="16">
-        <v>200700</v>
+        <v>200600</v>
       </c>
       <c r="C93" s="16">
         <v>2</v>
       </c>
-      <c r="D93" s="16" t="str">
-        <f>D92</f>
-        <v>越南色碟</v>
+      <c r="D93" s="16" t="s">
+        <v>70</v>
       </c>
       <c r="E93" s="16">
-        <v>200700001</v>
+        <v>200600001</v>
       </c>
       <c r="F93" s="16" t="s">
         <v>71</v>
       </c>
       <c r="G93" s="17" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H93" s="17">
         <v>11</v>
@@ -6138,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="L93" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M93" s="17">
         <v>0</v>
@@ -6152,26 +6157,25 @@
     </row>
     <row r="94" spans="1:19">
       <c r="A94" s="1">
-        <v>20070012</v>
+        <v>20060012</v>
       </c>
       <c r="B94" s="16">
-        <v>200700</v>
+        <v>200600</v>
       </c>
       <c r="C94" s="16">
         <v>2</v>
       </c>
-      <c r="D94" s="16" t="str">
-        <f>D93</f>
-        <v>越南色碟</v>
+      <c r="D94" s="16" t="s">
+        <v>70</v>
       </c>
       <c r="E94" s="16">
-        <v>200700001</v>
+        <v>200600001</v>
       </c>
       <c r="F94" s="16" t="s">
         <v>71</v>
       </c>
       <c r="G94" s="17" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H94" s="17">
         <v>12</v>
@@ -6186,7 +6190,7 @@
         <v>0</v>
       </c>
       <c r="L94" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M94" s="17">
         <v>0</v>
@@ -6200,10 +6204,10 @@
     </row>
     <row r="95" spans="1:19">
       <c r="A95" s="1">
-        <v>20080010</v>
+        <v>20070010</v>
       </c>
       <c r="B95" s="16">
-        <v>200800</v>
+        <v>200700</v>
       </c>
       <c r="C95" s="16">
         <v>2</v>
@@ -6212,13 +6216,13 @@
         <v>72</v>
       </c>
       <c r="E95" s="16">
-        <v>200800001</v>
+        <v>200700001</v>
       </c>
       <c r="F95" s="16" t="s">
         <v>73</v>
       </c>
       <c r="G95" s="17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H95" s="17">
         <v>10</v>
@@ -6233,7 +6237,7 @@
         <v>0</v>
       </c>
       <c r="L95" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M95" s="17">
         <v>0</v>
@@ -6247,25 +6251,26 @@
     </row>
     <row r="96" spans="1:19">
       <c r="A96" s="1">
-        <v>20080011</v>
+        <v>20070011</v>
       </c>
       <c r="B96" s="16">
-        <v>200800</v>
+        <v>200700</v>
       </c>
       <c r="C96" s="16">
         <v>2</v>
       </c>
-      <c r="D96" s="16" t="s">
-        <v>72</v>
+      <c r="D96" s="16" t="str">
+        <f>D95</f>
+        <v>越南色碟</v>
       </c>
       <c r="E96" s="16">
-        <v>200800001</v>
+        <v>200700001</v>
       </c>
       <c r="F96" s="16" t="s">
         <v>73</v>
       </c>
       <c r="G96" s="17" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H96" s="17">
         <v>11</v>
@@ -6280,7 +6285,7 @@
         <v>0</v>
       </c>
       <c r="L96" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M96" s="17">
         <v>0</v>
@@ -6294,25 +6299,26 @@
     </row>
     <row r="97" spans="1:19">
       <c r="A97" s="1">
-        <v>20080012</v>
+        <v>20070012</v>
       </c>
       <c r="B97" s="16">
-        <v>200800</v>
+        <v>200700</v>
       </c>
       <c r="C97" s="16">
         <v>2</v>
       </c>
-      <c r="D97" s="16" t="s">
-        <v>72</v>
+      <c r="D97" s="16" t="str">
+        <f>D96</f>
+        <v>越南色碟</v>
       </c>
       <c r="E97" s="16">
-        <v>200800001</v>
+        <v>200700001</v>
       </c>
       <c r="F97" s="16" t="s">
         <v>73</v>
       </c>
       <c r="G97" s="17" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H97" s="17">
         <v>12</v>
@@ -6327,7 +6333,7 @@
         <v>0</v>
       </c>
       <c r="L97" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M97" s="17">
         <v>0</v>
@@ -6341,10 +6347,10 @@
     </row>
     <row r="98" spans="1:19">
       <c r="A98" s="1">
-        <v>20090010</v>
+        <v>20080010</v>
       </c>
       <c r="B98" s="16">
-        <v>200900</v>
+        <v>200800</v>
       </c>
       <c r="C98" s="16">
         <v>2</v>
@@ -6353,13 +6359,13 @@
         <v>74</v>
       </c>
       <c r="E98" s="16">
-        <v>200900001</v>
+        <v>200800001</v>
       </c>
       <c r="F98" s="16" t="s">
         <v>75</v>
       </c>
       <c r="G98" s="17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H98" s="17">
         <v>10</v>
@@ -6374,7 +6380,7 @@
         <v>0</v>
       </c>
       <c r="L98" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M98" s="17">
         <v>0</v>
@@ -6388,10 +6394,10 @@
     </row>
     <row r="99" spans="1:19">
       <c r="A99" s="1">
-        <v>20090011</v>
+        <v>20080011</v>
       </c>
       <c r="B99" s="16">
-        <v>200900</v>
+        <v>200800</v>
       </c>
       <c r="C99" s="16">
         <v>2</v>
@@ -6400,13 +6406,13 @@
         <v>74</v>
       </c>
       <c r="E99" s="16">
-        <v>200900001</v>
+        <v>200800001</v>
       </c>
       <c r="F99" s="16" t="s">
         <v>75</v>
       </c>
       <c r="G99" s="17" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H99" s="17">
         <v>11</v>
@@ -6421,7 +6427,7 @@
         <v>0</v>
       </c>
       <c r="L99" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M99" s="17">
         <v>0</v>
@@ -6435,10 +6441,10 @@
     </row>
     <row r="100" spans="1:19">
       <c r="A100" s="1">
-        <v>20090012</v>
+        <v>20080012</v>
       </c>
       <c r="B100" s="16">
-        <v>200900</v>
+        <v>200800</v>
       </c>
       <c r="C100" s="16">
         <v>2</v>
@@ -6447,13 +6453,13 @@
         <v>74</v>
       </c>
       <c r="E100" s="16">
-        <v>200900001</v>
+        <v>200800001</v>
       </c>
       <c r="F100" s="16" t="s">
         <v>75</v>
       </c>
       <c r="G100" s="17" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H100" s="17">
         <v>12</v>
@@ -6468,7 +6474,7 @@
         <v>0</v>
       </c>
       <c r="L100" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M100" s="17">
         <v>0</v>
@@ -6480,27 +6486,27 @@
         <v>1980000</v>
       </c>
     </row>
-    <row r="101" s="1" customFormat="1" spans="1:19">
+    <row r="101" spans="1:19">
       <c r="A101" s="1">
-        <v>30020010</v>
+        <v>20090010</v>
       </c>
       <c r="B101" s="16">
-        <v>300200</v>
+        <v>200900</v>
       </c>
       <c r="C101" s="16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D101" s="16" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E101" s="16">
-        <v>300200006</v>
+        <v>200900001</v>
       </c>
       <c r="F101" s="16" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G101" s="17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H101" s="17">
         <v>10</v>
@@ -6514,8 +6520,8 @@
       <c r="K101" s="17">
         <v>0</v>
       </c>
-      <c r="L101" s="25" t="s">
-        <v>88</v>
+      <c r="L101" s="17" t="s">
+        <v>87</v>
       </c>
       <c r="M101" s="17">
         <v>0</v>
@@ -6526,29 +6532,28 @@
       <c r="O101" s="21">
         <v>1980000</v>
       </c>
-      <c r="S101" s="3"/>
-    </row>
-    <row r="102" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="102" spans="1:19">
       <c r="A102" s="1">
-        <v>30020011</v>
+        <v>20090011</v>
       </c>
       <c r="B102" s="16">
-        <v>300200</v>
+        <v>200900</v>
       </c>
       <c r="C102" s="16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D102" s="16" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E102" s="16">
-        <v>300200006</v>
+        <v>200900001</v>
       </c>
       <c r="F102" s="16" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G102" s="17" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H102" s="17">
         <v>11</v>
@@ -6562,8 +6567,8 @@
       <c r="K102" s="17">
         <v>0</v>
       </c>
-      <c r="L102" s="25" t="s">
-        <v>88</v>
+      <c r="L102" s="17" t="s">
+        <v>87</v>
       </c>
       <c r="M102" s="17">
         <v>0</v>
@@ -6574,29 +6579,28 @@
       <c r="O102" s="21">
         <v>1980000</v>
       </c>
-      <c r="S102" s="3"/>
-    </row>
-    <row r="103" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="103" spans="1:19">
       <c r="A103" s="1">
-        <v>30020012</v>
+        <v>20090012</v>
       </c>
       <c r="B103" s="16">
-        <v>300200</v>
+        <v>200900</v>
       </c>
       <c r="C103" s="16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D103" s="16" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E103" s="16">
-        <v>300200006</v>
+        <v>200900001</v>
       </c>
       <c r="F103" s="16" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G103" s="17" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H103" s="17">
         <v>12</v>
@@ -6610,8 +6614,8 @@
       <c r="K103" s="17">
         <v>0</v>
       </c>
-      <c r="L103" s="25" t="s">
-        <v>88</v>
+      <c r="L103" s="17" t="s">
+        <v>87</v>
       </c>
       <c r="M103" s="17">
         <v>0</v>
@@ -6622,29 +6626,28 @@
       <c r="O103" s="21">
         <v>1980000</v>
       </c>
-      <c r="S103" s="3"/>
-    </row>
-    <row r="104" spans="1:19">
-      <c r="A104" s="1" t="s">
-        <v>89</v>
+    </row>
+    <row r="104" s="1" customFormat="1" spans="1:19">
+      <c r="A104" s="1">
+        <v>30020010</v>
       </c>
       <c r="B104" s="16">
-        <v>100100</v>
+        <v>300200</v>
       </c>
       <c r="C104" s="16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D104" s="16" t="s">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="E104" s="16">
-        <v>100100026</v>
+        <v>300200006</v>
       </c>
       <c r="F104" s="16" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="G104" s="17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H104" s="17">
         <v>10</v>
@@ -6658,41 +6661,41 @@
       <c r="K104" s="17">
         <v>0</v>
       </c>
-      <c r="L104" s="17" t="s">
-        <v>85</v>
+      <c r="L104" s="25" t="s">
+        <v>90</v>
       </c>
       <c r="M104" s="17">
         <v>0</v>
       </c>
       <c r="N104" s="20">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="O104" s="21">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="105" spans="1:19">
-      <c r="A105" s="1" t="s">
-        <v>90</v>
+      <c r="S104" s="3"/>
+    </row>
+    <row r="105" s="1" customFormat="1" spans="1:19">
+      <c r="A105" s="1">
+        <v>30020011</v>
       </c>
       <c r="B105" s="16">
-        <v>100100</v>
+        <v>300200</v>
       </c>
       <c r="C105" s="16">
-        <v>1</v>
-      </c>
-      <c r="D105" s="16" t="str">
-        <f t="shared" ref="D105:D109" si="8">D104</f>
-        <v>金礦大亨</v>
+        <v>3</v>
+      </c>
+      <c r="D105" s="16" t="s">
+        <v>83</v>
       </c>
       <c r="E105" s="16">
-        <v>100100026</v>
+        <v>300200006</v>
       </c>
       <c r="F105" s="16" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="G105" s="17" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H105" s="17">
         <v>11</v>
@@ -6706,905 +6709,908 @@
       <c r="K105" s="17">
         <v>0</v>
       </c>
-      <c r="L105" s="17" t="s">
-        <v>85</v>
+      <c r="L105" s="25" t="s">
+        <v>90</v>
       </c>
       <c r="M105" s="17">
         <v>0</v>
       </c>
       <c r="N105" s="20">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="O105" s="21">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="106" spans="1:19">
-      <c r="A106" s="1" t="s">
+      <c r="S105" s="3"/>
+    </row>
+    <row r="106" s="1" customFormat="1" spans="1:19">
+      <c r="A106" s="1">
+        <v>30020012</v>
+      </c>
+      <c r="B106" s="16">
+        <v>300200</v>
+      </c>
+      <c r="C106" s="16">
+        <v>3</v>
+      </c>
+      <c r="D106" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E106" s="16">
+        <v>300200006</v>
+      </c>
+      <c r="F106" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="G106" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H106" s="17">
+        <v>12</v>
+      </c>
+      <c r="I106" s="17">
+        <v>0</v>
+      </c>
+      <c r="J106" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K106" s="17">
+        <v>0</v>
+      </c>
+      <c r="L106" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="M106" s="17">
+        <v>0</v>
+      </c>
+      <c r="N106" s="20">
+        <v>100000</v>
+      </c>
+      <c r="O106" s="21">
+        <v>1980000</v>
+      </c>
+      <c r="S106" s="3"/>
+    </row>
+    <row r="107" spans="1:19">
+      <c r="A107" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B106" s="16">
+      <c r="B107" s="16">
         <v>100100</v>
       </c>
-      <c r="C106" s="16">
-        <v>1</v>
-      </c>
-      <c r="D106" s="16" t="str">
+      <c r="C107" s="16">
+        <v>1</v>
+      </c>
+      <c r="D107" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="E107" s="16">
+        <v>100100026</v>
+      </c>
+      <c r="F107" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="G107" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H107" s="17">
+        <v>10</v>
+      </c>
+      <c r="I107" s="17">
+        <v>0</v>
+      </c>
+      <c r="J107" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K107" s="17">
+        <v>0</v>
+      </c>
+      <c r="L107" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M107" s="17">
+        <v>0</v>
+      </c>
+      <c r="N107" s="20">
+        <v>50</v>
+      </c>
+      <c r="O107" s="21">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="108" spans="1:19">
+      <c r="A108" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B108" s="16">
+        <v>100100</v>
+      </c>
+      <c r="C108" s="16">
+        <v>1</v>
+      </c>
+      <c r="D108" s="16" t="str">
+        <f t="shared" ref="D108:D112" si="8">D107</f>
+        <v>金礦大亨</v>
+      </c>
+      <c r="E108" s="16">
+        <v>100100026</v>
+      </c>
+      <c r="F108" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="G108" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H108" s="17">
+        <v>11</v>
+      </c>
+      <c r="I108" s="17">
+        <v>0</v>
+      </c>
+      <c r="J108" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K108" s="17">
+        <v>0</v>
+      </c>
+      <c r="L108" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M108" s="17">
+        <v>0</v>
+      </c>
+      <c r="N108" s="20">
+        <v>500</v>
+      </c>
+      <c r="O108" s="21">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="109" spans="1:19">
+      <c r="A109" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B109" s="16">
+        <v>100100</v>
+      </c>
+      <c r="C109" s="16">
+        <v>1</v>
+      </c>
+      <c r="D109" s="16" t="str">
         <f t="shared" si="8"/>
         <v>金礦大亨</v>
       </c>
-      <c r="E106" s="16">
+      <c r="E109" s="16">
         <v>100100026</v>
       </c>
-      <c r="F106" s="16" t="s">
+      <c r="F109" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="G106" s="17" t="s">
+      <c r="G109" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H109" s="17">
+        <v>12</v>
+      </c>
+      <c r="I109" s="17">
+        <v>0</v>
+      </c>
+      <c r="J109" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K109" s="17">
+        <v>0</v>
+      </c>
+      <c r="L109" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="H106" s="17">
-        <v>12</v>
-      </c>
-      <c r="I106" s="17">
-        <v>0</v>
-      </c>
-      <c r="J106" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K106" s="17">
-        <v>0</v>
-      </c>
-      <c r="L106" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="M106" s="17">
-        <v>0</v>
-      </c>
-      <c r="N106" s="20">
+      <c r="M109" s="17">
+        <v>0</v>
+      </c>
+      <c r="N109" s="20">
         <v>5000</v>
       </c>
-      <c r="O106" s="21">
+      <c r="O109" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="107" spans="1:19">
-      <c r="A107" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B107" s="16">
+    <row r="110" spans="1:19">
+      <c r="A110" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B110" s="16">
         <v>100300</v>
       </c>
-      <c r="C107" s="16">
-        <v>1</v>
-      </c>
-      <c r="D107" s="16" t="s">
+      <c r="C110" s="16">
+        <v>1</v>
+      </c>
+      <c r="D110" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="E107" s="16">
+      <c r="E110" s="16">
         <v>100300001</v>
       </c>
-      <c r="F107" s="16" t="s">
+      <c r="F110" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="G107" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="H107" s="17">
+      <c r="G110" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H110" s="17">
         <v>10</v>
       </c>
-      <c r="I107" s="17">
-        <v>0</v>
-      </c>
-      <c r="J107" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K107" s="17">
-        <v>0</v>
-      </c>
-      <c r="L107" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="M107" s="17">
-        <v>0</v>
-      </c>
-      <c r="N107" s="20">
+      <c r="I110" s="17">
+        <v>0</v>
+      </c>
+      <c r="J110" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K110" s="17">
+        <v>0</v>
+      </c>
+      <c r="L110" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M110" s="17">
+        <v>0</v>
+      </c>
+      <c r="N110" s="20">
         <v>50</v>
       </c>
-      <c r="O107" s="21">
+      <c r="O110" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="108" spans="1:19">
-      <c r="A108" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B108" s="16">
+    <row r="111" spans="1:19">
+      <c r="A111" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B111" s="16">
         <v>100300</v>
       </c>
-      <c r="C108" s="16">
-        <v>1</v>
-      </c>
-      <c r="D108" s="16" t="str">
+      <c r="C111" s="16">
+        <v>1</v>
+      </c>
+      <c r="D111" s="16" t="str">
         <f t="shared" si="8"/>
         <v>超级明星</v>
       </c>
-      <c r="E108" s="16">
+      <c r="E111" s="16">
         <v>100300001</v>
       </c>
-      <c r="F108" s="16" t="str">
-        <f t="shared" ref="F108:F112" si="9">F107</f>
+      <c r="F111" s="16" t="str">
+        <f t="shared" ref="F111:F115" si="9">F110</f>
         <v>SuperStar</v>
       </c>
-      <c r="G108" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="H108" s="17">
+      <c r="G111" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H111" s="17">
         <v>11</v>
       </c>
-      <c r="I108" s="17">
-        <v>0</v>
-      </c>
-      <c r="J108" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K108" s="17">
-        <v>0</v>
-      </c>
-      <c r="L108" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="M108" s="17">
-        <v>0</v>
-      </c>
-      <c r="N108" s="20">
+      <c r="I111" s="17">
+        <v>0</v>
+      </c>
+      <c r="J111" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K111" s="17">
+        <v>0</v>
+      </c>
+      <c r="L111" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M111" s="17">
+        <v>0</v>
+      </c>
+      <c r="N111" s="20">
         <v>500</v>
       </c>
-      <c r="O108" s="21">
+      <c r="O111" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="109" spans="1:19">
-      <c r="A109" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B109" s="16">
+    <row r="112" spans="1:19">
+      <c r="A112" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B112" s="16">
         <v>100300</v>
       </c>
-      <c r="C109" s="16">
-        <v>1</v>
-      </c>
-      <c r="D109" s="16" t="str">
+      <c r="C112" s="16">
+        <v>1</v>
+      </c>
+      <c r="D112" s="16" t="str">
         <f t="shared" si="8"/>
         <v>超级明星</v>
       </c>
-      <c r="E109" s="16">
+      <c r="E112" s="16">
         <v>100300001</v>
       </c>
-      <c r="F109" s="16" t="str">
+      <c r="F112" s="16" t="str">
         <f t="shared" si="9"/>
         <v>SuperStar</v>
       </c>
-      <c r="G109" s="17" t="s">
+      <c r="G112" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H112" s="17">
+        <v>12</v>
+      </c>
+      <c r="I112" s="17">
+        <v>0</v>
+      </c>
+      <c r="J112" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K112" s="17">
+        <v>0</v>
+      </c>
+      <c r="L112" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="H109" s="17">
-        <v>12</v>
-      </c>
-      <c r="I109" s="17">
-        <v>0</v>
-      </c>
-      <c r="J109" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K109" s="17">
-        <v>0</v>
-      </c>
-      <c r="L109" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="M109" s="17">
-        <v>0</v>
-      </c>
-      <c r="N109" s="20">
+      <c r="M112" s="17">
+        <v>0</v>
+      </c>
+      <c r="N112" s="20">
         <v>5000</v>
       </c>
-      <c r="O109" s="21">
+      <c r="O112" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="110" spans="1:19">
-      <c r="A110" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B110" s="16">
+    <row r="113" spans="1:15">
+      <c r="A113" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B113" s="16">
         <v>100700</v>
       </c>
-      <c r="C110" s="16">
-        <v>1</v>
-      </c>
-      <c r="D110" s="16" t="s">
+      <c r="C113" s="16">
+        <v>1</v>
+      </c>
+      <c r="D113" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E110" s="16">
+      <c r="E113" s="16">
         <v>100700001</v>
       </c>
-      <c r="F110" s="16" t="s">
+      <c r="F113" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="G110" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="H110" s="17">
+      <c r="G113" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H113" s="17">
         <v>10</v>
       </c>
-      <c r="I110" s="17">
-        <v>0</v>
-      </c>
-      <c r="J110" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K110" s="17">
-        <v>0</v>
-      </c>
-      <c r="L110" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="M110" s="17">
-        <v>0</v>
-      </c>
-      <c r="N110" s="20">
+      <c r="I113" s="17">
+        <v>0</v>
+      </c>
+      <c r="J113" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K113" s="17">
+        <v>0</v>
+      </c>
+      <c r="L113" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M113" s="17">
+        <v>0</v>
+      </c>
+      <c r="N113" s="20">
         <v>50</v>
       </c>
-      <c r="O110" s="21">
+      <c r="O113" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="111" spans="1:19">
-      <c r="A111" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B111" s="16">
+    <row r="114" spans="1:15">
+      <c r="A114" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B114" s="16">
         <v>100700</v>
       </c>
-      <c r="C111" s="16">
-        <v>1</v>
-      </c>
-      <c r="D111" s="16" t="str">
-        <f t="shared" ref="D111:D115" si="10">D110</f>
+      <c r="C114" s="16">
+        <v>1</v>
+      </c>
+      <c r="D114" s="16" t="str">
+        <f t="shared" ref="D114:D118" si="10">D113</f>
         <v>麻将胡了</v>
       </c>
-      <c r="E111" s="16">
+      <c r="E114" s="16">
         <v>100700001</v>
       </c>
-      <c r="F111" s="16" t="str">
+      <c r="F114" s="16" t="str">
         <f t="shared" si="9"/>
         <v>MahjongWays</v>
       </c>
-      <c r="G111" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="H111" s="17">
+      <c r="G114" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H114" s="17">
         <v>11</v>
       </c>
-      <c r="I111" s="17">
-        <v>0</v>
-      </c>
-      <c r="J111" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K111" s="17">
-        <v>0</v>
-      </c>
-      <c r="L111" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="M111" s="17">
-        <v>0</v>
-      </c>
-      <c r="N111" s="20">
+      <c r="I114" s="17">
+        <v>0</v>
+      </c>
+      <c r="J114" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K114" s="17">
+        <v>0</v>
+      </c>
+      <c r="L114" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M114" s="17">
+        <v>0</v>
+      </c>
+      <c r="N114" s="20">
         <v>500</v>
       </c>
-      <c r="O111" s="21">
+      <c r="O114" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="112" spans="1:19">
-      <c r="A112" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B112" s="16">
+    <row r="115" spans="1:15">
+      <c r="A115" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B115" s="16">
         <v>100700</v>
       </c>
-      <c r="C112" s="16">
-        <v>1</v>
-      </c>
-      <c r="D112" s="16" t="str">
+      <c r="C115" s="16">
+        <v>1</v>
+      </c>
+      <c r="D115" s="16" t="str">
         <f t="shared" si="10"/>
         <v>麻将胡了</v>
       </c>
-      <c r="E112" s="16">
+      <c r="E115" s="16">
         <v>100700001</v>
       </c>
-      <c r="F112" s="16" t="str">
+      <c r="F115" s="16" t="str">
         <f t="shared" si="9"/>
         <v>MahjongWays</v>
       </c>
-      <c r="G112" s="17" t="s">
+      <c r="G115" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H115" s="17">
+        <v>12</v>
+      </c>
+      <c r="I115" s="17">
+        <v>0</v>
+      </c>
+      <c r="J115" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K115" s="17">
+        <v>0</v>
+      </c>
+      <c r="L115" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="H112" s="17">
-        <v>12</v>
-      </c>
-      <c r="I112" s="17">
-        <v>0</v>
-      </c>
-      <c r="J112" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K112" s="17">
-        <v>0</v>
-      </c>
-      <c r="L112" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="M112" s="17">
-        <v>0</v>
-      </c>
-      <c r="N112" s="20">
+      <c r="M115" s="17">
+        <v>0</v>
+      </c>
+      <c r="N115" s="20">
         <v>5000</v>
       </c>
-      <c r="O112" s="21">
+      <c r="O115" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="113" spans="1:15">
-      <c r="A113" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B113" s="16">
+    <row r="116" spans="1:15">
+      <c r="A116" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B116" s="16">
         <v>101200</v>
       </c>
-      <c r="C113" s="16">
-        <v>1</v>
-      </c>
-      <c r="D113" s="16" t="s">
+      <c r="C116" s="16">
+        <v>1</v>
+      </c>
+      <c r="D116" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="E113" s="16">
+      <c r="E116" s="16">
         <v>101200001</v>
       </c>
-      <c r="F113" s="16" t="s">
+      <c r="F116" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="G113" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="H113" s="17">
+      <c r="G116" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H116" s="17">
         <v>10</v>
       </c>
-      <c r="I113" s="17">
-        <v>0</v>
-      </c>
-      <c r="J113" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K113" s="17">
-        <v>0</v>
-      </c>
-      <c r="L113" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="M113" s="17">
-        <v>0</v>
-      </c>
-      <c r="N113" s="20">
+      <c r="I116" s="17">
+        <v>0</v>
+      </c>
+      <c r="J116" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K116" s="17">
+        <v>0</v>
+      </c>
+      <c r="L116" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M116" s="17">
+        <v>0</v>
+      </c>
+      <c r="N116" s="20">
         <v>50</v>
       </c>
-      <c r="O113" s="21">
+      <c r="O116" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="114" spans="1:15">
-      <c r="A114" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B114" s="16">
+    <row r="117" spans="1:15">
+      <c r="A117" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B117" s="16">
         <v>101200</v>
       </c>
-      <c r="C114" s="16">
-        <v>1</v>
-      </c>
-      <c r="D114" s="16" t="str">
+      <c r="C117" s="16">
+        <v>1</v>
+      </c>
+      <c r="D117" s="16" t="str">
         <f t="shared" si="10"/>
         <v>财神</v>
       </c>
-      <c r="E114" s="16">
+      <c r="E117" s="16">
         <v>101200001</v>
       </c>
-      <c r="F114" s="16" t="str">
-        <f t="shared" ref="F114:F118" si="11">F113</f>
+      <c r="F117" s="16" t="str">
+        <f t="shared" ref="F117:F121" si="11">F116</f>
         <v>Godofwealth</v>
       </c>
-      <c r="G114" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="H114" s="17">
+      <c r="G117" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H117" s="17">
         <v>11</v>
       </c>
-      <c r="I114" s="17">
-        <v>0</v>
-      </c>
-      <c r="J114" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K114" s="17">
-        <v>0</v>
-      </c>
-      <c r="L114" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="M114" s="17">
-        <v>0</v>
-      </c>
-      <c r="N114" s="20">
+      <c r="I117" s="17">
+        <v>0</v>
+      </c>
+      <c r="J117" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K117" s="17">
+        <v>0</v>
+      </c>
+      <c r="L117" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M117" s="17">
+        <v>0</v>
+      </c>
+      <c r="N117" s="20">
         <v>500</v>
       </c>
-      <c r="O114" s="21">
+      <c r="O117" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="115" spans="1:15">
-      <c r="A115" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B115" s="16">
+    <row r="118" spans="1:15">
+      <c r="A118" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B118" s="16">
         <v>101200</v>
       </c>
-      <c r="C115" s="16">
-        <v>1</v>
-      </c>
-      <c r="D115" s="16" t="str">
+      <c r="C118" s="16">
+        <v>1</v>
+      </c>
+      <c r="D118" s="16" t="str">
         <f t="shared" si="10"/>
         <v>财神</v>
       </c>
-      <c r="E115" s="16">
+      <c r="E118" s="16">
         <v>101200001</v>
       </c>
-      <c r="F115" s="16" t="str">
+      <c r="F118" s="16" t="str">
         <f t="shared" si="11"/>
         <v>Godofwealth</v>
       </c>
-      <c r="G115" s="17" t="s">
+      <c r="G118" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H118" s="17">
+        <v>12</v>
+      </c>
+      <c r="I118" s="17">
+        <v>0</v>
+      </c>
+      <c r="J118" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K118" s="17">
+        <v>0</v>
+      </c>
+      <c r="L118" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="H115" s="17">
-        <v>12</v>
-      </c>
-      <c r="I115" s="17">
-        <v>0</v>
-      </c>
-      <c r="J115" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K115" s="17">
-        <v>0</v>
-      </c>
-      <c r="L115" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="M115" s="17">
-        <v>0</v>
-      </c>
-      <c r="N115" s="20">
+      <c r="M118" s="17">
+        <v>0</v>
+      </c>
+      <c r="N118" s="20">
         <v>5000</v>
       </c>
-      <c r="O115" s="21">
+      <c r="O118" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="116" spans="1:15">
-      <c r="A116" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B116" s="16">
+    <row r="119" spans="1:15">
+      <c r="A119" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B119" s="16">
         <v>101400</v>
       </c>
-      <c r="C116" s="16">
-        <v>1</v>
-      </c>
-      <c r="D116" s="16" t="s">
+      <c r="C119" s="16">
+        <v>1</v>
+      </c>
+      <c r="D119" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="E116" s="16">
+      <c r="E119" s="16">
         <v>101400001</v>
       </c>
-      <c r="F116" s="16" t="s">
+      <c r="F119" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="G116" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="H116" s="17">
+      <c r="G119" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H119" s="17">
         <v>10</v>
       </c>
-      <c r="I116" s="17">
-        <v>0</v>
-      </c>
-      <c r="J116" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K116" s="17">
-        <v>0</v>
-      </c>
-      <c r="L116" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="M116" s="17">
-        <v>0</v>
-      </c>
-      <c r="N116" s="20">
+      <c r="I119" s="17">
+        <v>0</v>
+      </c>
+      <c r="J119" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K119" s="17">
+        <v>0</v>
+      </c>
+      <c r="L119" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M119" s="17">
+        <v>0</v>
+      </c>
+      <c r="N119" s="20">
         <v>50</v>
       </c>
-      <c r="O116" s="21">
+      <c r="O119" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="117" spans="1:15">
-      <c r="A117" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B117" s="16">
+    <row r="120" spans="1:15">
+      <c r="A120" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B120" s="16">
         <v>101400</v>
       </c>
-      <c r="C117" s="16">
-        <v>1</v>
-      </c>
-      <c r="D117" s="16" t="str">
-        <f t="shared" ref="D117:D121" si="12">D116</f>
+      <c r="C120" s="16">
+        <v>1</v>
+      </c>
+      <c r="D120" s="16" t="str">
+        <f t="shared" ref="D120:D124" si="12">D119</f>
         <v>埃及艳后</v>
       </c>
-      <c r="E117" s="16">
+      <c r="E120" s="16">
         <v>101400001</v>
       </c>
-      <c r="F117" s="16" t="str">
+      <c r="F120" s="16" t="str">
         <f t="shared" si="11"/>
         <v>Cleopatra</v>
       </c>
-      <c r="G117" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="H117" s="17">
+      <c r="G120" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H120" s="17">
         <v>11</v>
       </c>
-      <c r="I117" s="17">
-        <v>0</v>
-      </c>
-      <c r="J117" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K117" s="17">
-        <v>0</v>
-      </c>
-      <c r="L117" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="M117" s="17">
-        <v>0</v>
-      </c>
-      <c r="N117" s="20">
+      <c r="I120" s="17">
+        <v>0</v>
+      </c>
+      <c r="J120" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K120" s="17">
+        <v>0</v>
+      </c>
+      <c r="L120" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M120" s="17">
+        <v>0</v>
+      </c>
+      <c r="N120" s="20">
         <v>500</v>
       </c>
-      <c r="O117" s="21">
+      <c r="O120" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="118" spans="1:15">
-      <c r="A118" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B118" s="16">
+    <row r="121" spans="1:15">
+      <c r="A121" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B121" s="16">
         <v>101400</v>
       </c>
-      <c r="C118" s="16">
-        <v>1</v>
-      </c>
-      <c r="D118" s="16" t="str">
+      <c r="C121" s="16">
+        <v>1</v>
+      </c>
+      <c r="D121" s="16" t="str">
         <f t="shared" si="12"/>
         <v>埃及艳后</v>
       </c>
-      <c r="E118" s="16">
+      <c r="E121" s="16">
         <v>101400001</v>
       </c>
-      <c r="F118" s="16" t="str">
+      <c r="F121" s="16" t="str">
         <f t="shared" si="11"/>
         <v>Cleopatra</v>
       </c>
-      <c r="G118" s="17" t="s">
+      <c r="G121" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H121" s="17">
+        <v>12</v>
+      </c>
+      <c r="I121" s="17">
+        <v>0</v>
+      </c>
+      <c r="J121" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K121" s="17">
+        <v>0</v>
+      </c>
+      <c r="L121" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="H118" s="17">
-        <v>12</v>
-      </c>
-      <c r="I118" s="17">
-        <v>0</v>
-      </c>
-      <c r="J118" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K118" s="17">
-        <v>0</v>
-      </c>
-      <c r="L118" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="M118" s="17">
-        <v>0</v>
-      </c>
-      <c r="N118" s="20">
+      <c r="M121" s="17">
+        <v>0</v>
+      </c>
+      <c r="N121" s="20">
         <v>5000</v>
       </c>
-      <c r="O118" s="21">
+      <c r="O121" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="119" spans="1:15">
-      <c r="A119" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B119" s="16">
+    <row r="122" spans="1:15">
+      <c r="A122" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B122" s="16">
         <v>102400</v>
       </c>
-      <c r="C119" s="16">
-        <v>1</v>
-      </c>
-      <c r="D119" s="16" t="s">
+      <c r="C122" s="16">
+        <v>1</v>
+      </c>
+      <c r="D122" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="E119" s="16">
+      <c r="E122" s="16">
         <v>102400026</v>
       </c>
-      <c r="F119" s="16" t="s">
+      <c r="F122" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="G119" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="H119" s="17">
+      <c r="G122" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H122" s="17">
         <v>10</v>
       </c>
-      <c r="I119" s="17">
-        <v>0</v>
-      </c>
-      <c r="J119" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K119" s="17">
-        <v>0</v>
-      </c>
-      <c r="L119" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="M119" s="17">
-        <v>0</v>
-      </c>
-      <c r="N119" s="20">
+      <c r="I122" s="17">
+        <v>0</v>
+      </c>
+      <c r="J122" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K122" s="17">
+        <v>0</v>
+      </c>
+      <c r="L122" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M122" s="17">
+        <v>0</v>
+      </c>
+      <c r="N122" s="20">
         <v>50</v>
       </c>
-      <c r="O119" s="21">
+      <c r="O122" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="120" spans="1:15">
-      <c r="A120" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B120" s="16">
+    <row r="123" spans="1:15">
+      <c r="A123" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B123" s="16">
         <v>102400</v>
       </c>
-      <c r="C120" s="16">
-        <v>1</v>
-      </c>
-      <c r="D120" s="16" t="str">
+      <c r="C123" s="16">
+        <v>1</v>
+      </c>
+      <c r="D123" s="16" t="str">
         <f t="shared" si="12"/>
         <v>财富银行</v>
       </c>
-      <c r="E120" s="16">
+      <c r="E123" s="16">
         <v>102400026</v>
       </c>
-      <c r="F120" s="16" t="s">
+      <c r="F123" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="G120" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="H120" s="17">
+      <c r="G123" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H123" s="17">
         <v>11</v>
       </c>
-      <c r="I120" s="17">
-        <v>0</v>
-      </c>
-      <c r="J120" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K120" s="17">
-        <v>0</v>
-      </c>
-      <c r="L120" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="M120" s="17">
-        <v>0</v>
-      </c>
-      <c r="N120" s="20">
+      <c r="I123" s="17">
+        <v>0</v>
+      </c>
+      <c r="J123" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K123" s="17">
+        <v>0</v>
+      </c>
+      <c r="L123" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M123" s="17">
+        <v>0</v>
+      </c>
+      <c r="N123" s="20">
         <v>500</v>
       </c>
-      <c r="O120" s="21">
+      <c r="O123" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="121" spans="1:15">
-      <c r="A121" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B121" s="16">
+    <row r="124" spans="1:15">
+      <c r="A124" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B124" s="16">
         <v>102400</v>
       </c>
-      <c r="C121" s="16">
-        <v>1</v>
-      </c>
-      <c r="D121" s="16" t="str">
+      <c r="C124" s="16">
+        <v>1</v>
+      </c>
+      <c r="D124" s="16" t="str">
         <f t="shared" si="12"/>
         <v>财富银行</v>
       </c>
-      <c r="E121" s="16">
+      <c r="E124" s="16">
         <v>102400026</v>
       </c>
-      <c r="F121" s="16" t="s">
+      <c r="F124" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="G121" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="H121" s="17">
-        <v>12</v>
-      </c>
-      <c r="I121" s="17">
-        <v>0</v>
-      </c>
-      <c r="J121" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K121" s="17">
-        <v>0</v>
-      </c>
-      <c r="L121" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="M121" s="17">
-        <v>0</v>
-      </c>
-      <c r="N121" s="20">
-        <v>5000</v>
-      </c>
-      <c r="O121" s="21">
-        <v>1980000</v>
-      </c>
-    </row>
-    <row r="122" spans="1:15">
-      <c r="A122" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B122" s="16">
-        <v>102200</v>
-      </c>
-      <c r="C122" s="16">
-        <v>1</v>
-      </c>
-      <c r="D122" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="E122" s="16">
-        <v>102200001</v>
-      </c>
-      <c r="F122" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="G122" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="H122" s="17">
-        <v>10</v>
-      </c>
-      <c r="I122" s="17">
-        <v>0</v>
-      </c>
-      <c r="J122" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K122" s="17">
-        <v>0</v>
-      </c>
-      <c r="L122" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="M122" s="17">
-        <v>0</v>
-      </c>
-      <c r="N122" s="20">
-        <v>50</v>
-      </c>
-      <c r="O122" s="21">
-        <v>1980000</v>
-      </c>
-    </row>
-    <row r="123" spans="1:15">
-      <c r="A123" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B123" s="16">
-        <v>102200</v>
-      </c>
-      <c r="C123" s="16">
-        <v>1</v>
-      </c>
-      <c r="D123" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="E123" s="16">
-        <v>102200001</v>
-      </c>
-      <c r="F123" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="G123" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="H123" s="17">
-        <v>11</v>
-      </c>
-      <c r="I123" s="17">
-        <v>0</v>
-      </c>
-      <c r="J123" s="17">
-        <v>-1</v>
-      </c>
-      <c r="K123" s="17">
-        <v>0</v>
-      </c>
-      <c r="L123" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="M123" s="17">
-        <v>0</v>
-      </c>
-      <c r="N123" s="20">
-        <v>500</v>
-      </c>
-      <c r="O123" s="21">
-        <v>1980000</v>
-      </c>
-    </row>
-    <row r="124" spans="1:15">
-      <c r="A124" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B124" s="16">
-        <v>102200</v>
-      </c>
-      <c r="C124" s="16">
-        <v>1</v>
-      </c>
-      <c r="D124" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="E124" s="16">
-        <v>102200001</v>
-      </c>
-      <c r="F124" s="16" t="s">
-        <v>48</v>
-      </c>
       <c r="G124" s="17" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H124" s="17">
         <v>12</v>
@@ -7619,7 +7625,7 @@
         <v>0</v>
       </c>
       <c r="L124" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M124" s="17">
         <v>0</v>
@@ -7633,25 +7639,25 @@
     </row>
     <row r="125" spans="1:15">
       <c r="A125" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B125" s="16">
-        <v>101700</v>
+        <v>102200</v>
       </c>
       <c r="C125" s="16">
         <v>1</v>
       </c>
       <c r="D125" s="16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E125" s="16">
-        <v>101700001</v>
+        <v>102200001</v>
       </c>
       <c r="F125" s="16" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G125" s="17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H125" s="17">
         <v>10</v>
@@ -7666,7 +7672,7 @@
         <v>0</v>
       </c>
       <c r="L125" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M125" s="17">
         <v>0</v>
@@ -7680,25 +7686,25 @@
     </row>
     <row r="126" spans="1:15">
       <c r="A126" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B126" s="16">
-        <v>101700</v>
+        <v>102200</v>
       </c>
       <c r="C126" s="16">
         <v>1</v>
       </c>
       <c r="D126" s="16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E126" s="16">
-        <v>101700001</v>
+        <v>102200001</v>
       </c>
       <c r="F126" s="16" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G126" s="17" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H126" s="17">
         <v>11</v>
@@ -7713,7 +7719,7 @@
         <v>0</v>
       </c>
       <c r="L126" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M126" s="17">
         <v>0</v>
@@ -7727,25 +7733,25 @@
     </row>
     <row r="127" spans="1:15">
       <c r="A127" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B127" s="16">
-        <v>101700</v>
+        <v>102200</v>
       </c>
       <c r="C127" s="16">
         <v>1</v>
       </c>
       <c r="D127" s="16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E127" s="16">
-        <v>101700001</v>
+        <v>102200001</v>
       </c>
       <c r="F127" s="16" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G127" s="17" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H127" s="17">
         <v>12</v>
@@ -7760,7 +7766,7 @@
         <v>0</v>
       </c>
       <c r="L127" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M127" s="17">
         <v>0</v>
@@ -7774,25 +7780,25 @@
     </row>
     <row r="128" spans="1:15">
       <c r="A128" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B128" s="16">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C128" s="16">
         <v>1</v>
       </c>
       <c r="D128" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E128" s="16">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="F128" s="16" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G128" s="17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H128" s="17">
         <v>10</v>
@@ -7807,7 +7813,7 @@
         <v>0</v>
       </c>
       <c r="L128" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M128" s="17">
         <v>0</v>
@@ -7821,25 +7827,25 @@
     </row>
     <row r="129" spans="1:15">
       <c r="A129" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B129" s="16">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C129" s="16">
         <v>1</v>
       </c>
       <c r="D129" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E129" s="16">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="F129" s="16" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G129" s="17" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H129" s="17">
         <v>11</v>
@@ -7854,7 +7860,7 @@
         <v>0</v>
       </c>
       <c r="L129" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M129" s="17">
         <v>0</v>
@@ -7868,25 +7874,25 @@
     </row>
     <row r="130" spans="1:15">
       <c r="A130" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B130" s="16">
-        <v>102100</v>
+        <v>101700</v>
       </c>
       <c r="C130" s="16">
         <v>1</v>
       </c>
       <c r="D130" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E130" s="16">
-        <v>102100001</v>
+        <v>101700001</v>
       </c>
       <c r="F130" s="16" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G130" s="17" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H130" s="17">
         <v>12</v>
@@ -7901,7 +7907,7 @@
         <v>0</v>
       </c>
       <c r="L130" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M130" s="17">
         <v>0</v>
@@ -7914,26 +7920,26 @@
       </c>
     </row>
     <row r="131" spans="1:15">
-      <c r="A131" s="1">
-        <v>10180010</v>
+      <c r="A131" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="B131" s="16">
-        <v>101800</v>
+        <v>102100</v>
       </c>
       <c r="C131" s="16">
         <v>1</v>
       </c>
       <c r="D131" s="16" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E131" s="16">
-        <v>101800001</v>
+        <v>102100001</v>
       </c>
       <c r="F131" s="16" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G131" s="17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H131" s="17">
         <v>10</v>
@@ -7948,7 +7954,7 @@
         <v>0</v>
       </c>
       <c r="L131" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M131" s="17">
         <v>0</v>
@@ -7961,26 +7967,26 @@
       </c>
     </row>
     <row r="132" spans="1:15">
-      <c r="A132" s="1">
-        <v>10180011</v>
+      <c r="A132" s="1" t="s">
+        <v>116</v>
       </c>
       <c r="B132" s="16">
-        <v>101800</v>
+        <v>102100</v>
       </c>
       <c r="C132" s="16">
         <v>1</v>
       </c>
       <c r="D132" s="16" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E132" s="16">
-        <v>101800001</v>
+        <v>102100001</v>
       </c>
       <c r="F132" s="16" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G132" s="17" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H132" s="17">
         <v>11</v>
@@ -7995,7 +8001,7 @@
         <v>0</v>
       </c>
       <c r="L132" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M132" s="17">
         <v>0</v>
@@ -8008,26 +8014,26 @@
       </c>
     </row>
     <row r="133" spans="1:15">
-      <c r="A133" s="1">
-        <v>10180012</v>
+      <c r="A133" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="B133" s="16">
-        <v>101800</v>
+        <v>102100</v>
       </c>
       <c r="C133" s="16">
         <v>1</v>
       </c>
       <c r="D133" s="16" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E133" s="16">
-        <v>101800001</v>
+        <v>102100001</v>
       </c>
       <c r="F133" s="16" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G133" s="17" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H133" s="17">
         <v>12</v>
@@ -8042,7 +8048,7 @@
         <v>0</v>
       </c>
       <c r="L133" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M133" s="17">
         <v>0</v>
@@ -8056,25 +8062,25 @@
     </row>
     <row r="134" spans="1:15">
       <c r="A134" s="1">
-        <v>10250010</v>
+        <v>10180010</v>
       </c>
       <c r="B134" s="16">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C134" s="16">
         <v>1</v>
       </c>
       <c r="D134" s="16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E134" s="16">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="F134" s="16" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G134" s="17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H134" s="17">
         <v>10</v>
@@ -8089,7 +8095,7 @@
         <v>0</v>
       </c>
       <c r="L134" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M134" s="17">
         <v>0</v>
@@ -8103,25 +8109,25 @@
     </row>
     <row r="135" spans="1:15">
       <c r="A135" s="1">
-        <v>10250011</v>
+        <v>10180011</v>
       </c>
       <c r="B135" s="16">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C135" s="16">
         <v>1</v>
       </c>
       <c r="D135" s="16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E135" s="16">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="F135" s="16" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G135" s="17" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H135" s="17">
         <v>11</v>
@@ -8136,7 +8142,7 @@
         <v>0</v>
       </c>
       <c r="L135" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M135" s="17">
         <v>0</v>
@@ -8150,25 +8156,25 @@
     </row>
     <row r="136" spans="1:15">
       <c r="A136" s="1">
-        <v>10250012</v>
+        <v>10180012</v>
       </c>
       <c r="B136" s="16">
-        <v>102500</v>
+        <v>101800</v>
       </c>
       <c r="C136" s="16">
         <v>1</v>
       </c>
       <c r="D136" s="16" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E136" s="16">
-        <v>102500001</v>
+        <v>101800001</v>
       </c>
       <c r="F136" s="16" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G136" s="17" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H136" s="17">
         <v>12</v>
@@ -8183,7 +8189,7 @@
         <v>0</v>
       </c>
       <c r="L136" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M136" s="17">
         <v>0</v>
@@ -8192,6 +8198,288 @@
         <v>5000</v>
       </c>
       <c r="O136" s="21">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15">
+      <c r="A137" s="1">
+        <v>10250010</v>
+      </c>
+      <c r="B137" s="16">
+        <v>102500</v>
+      </c>
+      <c r="C137" s="16">
+        <v>1</v>
+      </c>
+      <c r="D137" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E137" s="16">
+        <v>102500001</v>
+      </c>
+      <c r="F137" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="G137" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H137" s="17">
+        <v>10</v>
+      </c>
+      <c r="I137" s="17">
+        <v>0</v>
+      </c>
+      <c r="J137" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K137" s="17">
+        <v>0</v>
+      </c>
+      <c r="L137" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M137" s="17">
+        <v>0</v>
+      </c>
+      <c r="N137" s="20">
+        <v>50</v>
+      </c>
+      <c r="O137" s="21">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15">
+      <c r="A138" s="1">
+        <v>10250011</v>
+      </c>
+      <c r="B138" s="16">
+        <v>102500</v>
+      </c>
+      <c r="C138" s="16">
+        <v>1</v>
+      </c>
+      <c r="D138" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E138" s="16">
+        <v>102500001</v>
+      </c>
+      <c r="F138" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="G138" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H138" s="17">
+        <v>11</v>
+      </c>
+      <c r="I138" s="17">
+        <v>0</v>
+      </c>
+      <c r="J138" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K138" s="17">
+        <v>0</v>
+      </c>
+      <c r="L138" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M138" s="17">
+        <v>0</v>
+      </c>
+      <c r="N138" s="20">
+        <v>500</v>
+      </c>
+      <c r="O138" s="21">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15">
+      <c r="A139" s="1">
+        <v>10250012</v>
+      </c>
+      <c r="B139" s="16">
+        <v>102500</v>
+      </c>
+      <c r="C139" s="16">
+        <v>1</v>
+      </c>
+      <c r="D139" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E139" s="16">
+        <v>102500001</v>
+      </c>
+      <c r="F139" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="G139" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H139" s="17">
+        <v>12</v>
+      </c>
+      <c r="I139" s="17">
+        <v>0</v>
+      </c>
+      <c r="J139" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K139" s="17">
+        <v>0</v>
+      </c>
+      <c r="L139" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M139" s="17">
+        <v>0</v>
+      </c>
+      <c r="N139" s="20">
+        <v>5000</v>
+      </c>
+      <c r="O139" s="21">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15">
+      <c r="A140" s="1">
+        <v>10230010</v>
+      </c>
+      <c r="B140" s="16">
+        <v>102300</v>
+      </c>
+      <c r="C140" s="16">
+        <v>1</v>
+      </c>
+      <c r="D140" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="E140" s="16">
+        <v>102300001</v>
+      </c>
+      <c r="F140" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="G140" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H140" s="17">
+        <v>10</v>
+      </c>
+      <c r="I140" s="17">
+        <v>0</v>
+      </c>
+      <c r="J140" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K140" s="17">
+        <v>0</v>
+      </c>
+      <c r="L140" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M140" s="17">
+        <v>0</v>
+      </c>
+      <c r="N140" s="20">
+        <v>50</v>
+      </c>
+      <c r="O140" s="21">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15">
+      <c r="A141" s="1">
+        <v>10230011</v>
+      </c>
+      <c r="B141" s="16">
+        <v>102300</v>
+      </c>
+      <c r="C141" s="16">
+        <v>1</v>
+      </c>
+      <c r="D141" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="E141" s="16">
+        <v>102300001</v>
+      </c>
+      <c r="F141" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="G141" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H141" s="17">
+        <v>11</v>
+      </c>
+      <c r="I141" s="17">
+        <v>0</v>
+      </c>
+      <c r="J141" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K141" s="17">
+        <v>0</v>
+      </c>
+      <c r="L141" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M141" s="17">
+        <v>0</v>
+      </c>
+      <c r="N141" s="20">
+        <v>500</v>
+      </c>
+      <c r="O141" s="21">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15">
+      <c r="A142" s="1">
+        <v>10230012</v>
+      </c>
+      <c r="B142" s="16">
+        <v>102300</v>
+      </c>
+      <c r="C142" s="16">
+        <v>1</v>
+      </c>
+      <c r="D142" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="E142" s="16">
+        <v>102300001</v>
+      </c>
+      <c r="F142" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="G142" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H142" s="17">
+        <v>12</v>
+      </c>
+      <c r="I142" s="17">
+        <v>0</v>
+      </c>
+      <c r="J142" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K142" s="17">
+        <v>0</v>
+      </c>
+      <c r="L142" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M142" s="17">
+        <v>0</v>
+      </c>
+      <c r="N142" s="20">
+        <v>5000</v>
+      </c>
+      <c r="O142" s="21">
         <v>1980000</v>
       </c>
     </row>

--- a/hall/resources/sample/warehouse.xlsx
+++ b/hall/resources/sample/warehouse.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925" tabRatio="794"/>
+    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Warehouse" sheetId="42" r:id="rId1"/>
@@ -156,7 +156,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="118">
   <si>
     <t>sid</t>
   </si>
@@ -315,6 +315,24 @@
   </si>
   <si>
     <t>CaptainJack</t>
+  </si>
+  <si>
+    <t>篮球巨星</t>
+  </si>
+  <si>
+    <t>BasketballSuperstar</t>
+  </si>
+  <si>
+    <t>寒冰王座</t>
+  </si>
+  <si>
+    <t>FrozenThrone</t>
+  </si>
+  <si>
+    <t>蒸汽时代</t>
+  </si>
+  <si>
+    <t>AgeSteam</t>
   </si>
   <si>
     <t>紅黑大戰</t>
@@ -1285,14 +1303,14 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1641,7 +1659,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S124"/>
+  <dimension ref="A1:S142"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="3" width="9.375" style="1"/>
@@ -3119,37 +3137,36 @@
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="1">
-        <f t="shared" ref="A32:A78" si="5">B32*10+H32</f>
-        <v>2001001</v>
-      </c>
-      <c r="B32" s="12">
-        <v>200100</v>
-      </c>
-      <c r="C32" s="12">
-        <v>2</v>
-      </c>
-      <c r="D32" s="12" t="s">
+        <v>1018001</v>
+      </c>
+      <c r="B32" s="16">
+        <v>101800</v>
+      </c>
+      <c r="C32" s="16">
+        <v>1</v>
+      </c>
+      <c r="D32" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="E32" s="13">
-        <v>200100038</v>
-      </c>
-      <c r="F32" s="13" t="s">
+      <c r="E32" s="16">
+        <v>101800001</v>
+      </c>
+      <c r="F32" s="16" t="s">
         <v>54</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H32" s="1">
+      <c r="H32" s="17">
         <v>1</v>
       </c>
       <c r="I32" s="1">
         <v>0</v>
       </c>
-      <c r="J32" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K32" s="1">
+      <c r="J32" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K32" s="17">
         <v>0</v>
       </c>
       <c r="L32" s="1" t="s">
@@ -3167,521 +3184,494 @@
     </row>
     <row r="33" spans="1:19">
       <c r="A33" s="1">
+        <v>1018002</v>
+      </c>
+      <c r="B33" s="16">
+        <v>101800</v>
+      </c>
+      <c r="C33" s="16">
+        <v>1</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="E33" s="16">
+        <v>101800001</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H33" s="17">
+        <v>2</v>
+      </c>
+      <c r="I33" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J33" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K33" s="17">
+        <v>0</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M33" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="N33">
+        <v>500000</v>
+      </c>
+      <c r="O33" s="15">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19">
+      <c r="A34" s="1">
+        <v>1018003</v>
+      </c>
+      <c r="B34" s="16">
+        <v>101800</v>
+      </c>
+      <c r="C34" s="16">
+        <v>1</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="E34" s="16">
+        <v>101800001</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H34" s="17">
+        <v>3</v>
+      </c>
+      <c r="I34" s="1">
+        <v>50000000</v>
+      </c>
+      <c r="J34" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K34" s="17">
+        <v>0</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M34" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="N34">
+        <v>50000000</v>
+      </c>
+      <c r="O34" s="15">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19">
+      <c r="A35" s="1">
+        <v>1025001</v>
+      </c>
+      <c r="B35" s="16">
+        <v>102500</v>
+      </c>
+      <c r="C35" s="16">
+        <v>1</v>
+      </c>
+      <c r="D35" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E35" s="16">
+        <v>102500001</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H35" s="17">
+        <v>1</v>
+      </c>
+      <c r="I35" s="1">
+        <v>0</v>
+      </c>
+      <c r="J35" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K35" s="17">
+        <v>0</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M35" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="N35">
+        <v>5000</v>
+      </c>
+      <c r="O35" s="15">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19">
+      <c r="A36" s="1">
+        <v>1025002</v>
+      </c>
+      <c r="B36" s="16">
+        <v>102500</v>
+      </c>
+      <c r="C36" s="16">
+        <v>1</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E36" s="16">
+        <v>102500001</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H36" s="17">
+        <v>2</v>
+      </c>
+      <c r="I36" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J36" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K36" s="17">
+        <v>0</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M36" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="N36">
+        <v>500000</v>
+      </c>
+      <c r="O36" s="15">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19">
+      <c r="A37" s="1">
+        <v>1025003</v>
+      </c>
+      <c r="B37" s="16">
+        <v>102500</v>
+      </c>
+      <c r="C37" s="16">
+        <v>1</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E37" s="16">
+        <v>102500001</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H37" s="17">
+        <v>3</v>
+      </c>
+      <c r="I37" s="1">
+        <v>50000000</v>
+      </c>
+      <c r="J37" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K37" s="17">
+        <v>0</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M37" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="N37">
+        <v>50000000</v>
+      </c>
+      <c r="O37" s="15">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19">
+      <c r="A38" s="1">
+        <v>1023001</v>
+      </c>
+      <c r="B38" s="12">
+        <v>102300</v>
+      </c>
+      <c r="C38" s="12">
+        <v>1</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E38" s="13">
+        <v>102300001</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H38" s="1">
+        <v>1</v>
+      </c>
+      <c r="I38" s="1">
+        <v>0</v>
+      </c>
+      <c r="J38" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K38" s="17">
+        <v>0</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M38" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="N38">
+        <v>5000</v>
+      </c>
+      <c r="O38" s="15">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19">
+      <c r="A39" s="1">
+        <v>1023002</v>
+      </c>
+      <c r="B39" s="12">
+        <v>102300</v>
+      </c>
+      <c r="C39" s="12">
+        <v>1</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E39" s="13">
+        <v>102300001</v>
+      </c>
+      <c r="F39" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H39" s="1">
+        <v>2</v>
+      </c>
+      <c r="I39" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J39" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K39" s="17">
+        <v>0</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M39" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="N39">
+        <v>500000</v>
+      </c>
+      <c r="O39" s="15">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19">
+      <c r="A40" s="1">
+        <v>1023003</v>
+      </c>
+      <c r="B40" s="12">
+        <v>102300</v>
+      </c>
+      <c r="C40" s="12">
+        <v>1</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E40" s="13">
+        <v>102300001</v>
+      </c>
+      <c r="F40" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H40" s="1">
+        <v>3</v>
+      </c>
+      <c r="I40" s="1">
+        <v>50000000</v>
+      </c>
+      <c r="J40" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K40" s="17">
+        <v>0</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M40" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="N40">
+        <v>50000000</v>
+      </c>
+      <c r="O40" s="15">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19">
+      <c r="A41" s="1">
+        <f t="shared" ref="A41:A87" si="5">B41*10+H41</f>
+        <v>2001001</v>
+      </c>
+      <c r="B41" s="12">
+        <v>200100</v>
+      </c>
+      <c r="C41" s="12">
+        <v>2</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E41" s="13">
+        <v>200100038</v>
+      </c>
+      <c r="F41" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H41" s="1">
+        <v>1</v>
+      </c>
+      <c r="I41" s="1">
+        <v>0</v>
+      </c>
+      <c r="J41" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K41" s="1">
+        <v>0</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M41" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="N41">
+        <v>5000</v>
+      </c>
+      <c r="O41" s="15">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19">
+      <c r="A42" s="1">
         <f t="shared" si="5"/>
         <v>2001002</v>
       </c>
-      <c r="B33" s="12">
+      <c r="B42" s="12">
         <v>200100</v>
       </c>
-      <c r="C33" s="12">
+      <c r="C42" s="12">
         <v>2</v>
       </c>
-      <c r="D33" s="12" t="str">
-        <f>D32</f>
+      <c r="D42" s="12" t="str">
+        <f>D41</f>
         <v>紅黑大戰</v>
       </c>
-      <c r="E33" s="13">
+      <c r="E42" s="13">
         <v>200100038</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G33" s="1" t="s">
+      <c r="F42" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="G42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H33" s="1">
+      <c r="H42" s="1">
         <v>2</v>
       </c>
-      <c r="I33" s="1">
+      <c r="I42" s="1">
         <v>500000</v>
       </c>
-      <c r="J33" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K33" s="1">
-        <v>0</v>
-      </c>
-      <c r="L33" s="1" t="s">
+      <c r="J42" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K42" s="1">
+        <v>0</v>
+      </c>
+      <c r="L42" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M33" s="23" t="s">
+      <c r="M42" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="N33">
+      <c r="N42">
         <v>500000</v>
       </c>
-      <c r="O33" s="15">
+      <c r="O42" s="15">
         <v>1990000</v>
       </c>
     </row>
-    <row r="34" spans="1:19">
-      <c r="A34" s="1">
+    <row r="43" spans="1:19">
+      <c r="A43" s="1">
         <f t="shared" si="5"/>
         <v>2001003</v>
       </c>
-      <c r="B34" s="12">
+      <c r="B43" s="12">
         <v>200100</v>
-      </c>
-      <c r="C34" s="12">
-        <v>2</v>
-      </c>
-      <c r="D34" s="12" t="str">
-        <f>D33</f>
-        <v>紅黑大戰</v>
-      </c>
-      <c r="E34" s="13">
-        <v>200100038</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H34" s="1">
-        <v>3</v>
-      </c>
-      <c r="I34" s="1">
-        <v>50000000</v>
-      </c>
-      <c r="J34" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K34" s="1">
-        <v>0</v>
-      </c>
-      <c r="L34" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M34" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="N34">
-        <v>50000000</v>
-      </c>
-      <c r="O34" s="15">
-        <v>1990000</v>
-      </c>
-      <c r="Q34"/>
-    </row>
-    <row r="35" spans="1:19">
-      <c r="A35" s="1">
-        <f t="shared" si="5"/>
-        <v>2001011</v>
-      </c>
-      <c r="B35" s="12">
-        <v>200101</v>
-      </c>
-      <c r="C35" s="12">
-        <v>2</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E35" s="13">
-        <v>200101001</v>
-      </c>
-      <c r="F35" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H35" s="1">
-        <v>1</v>
-      </c>
-      <c r="I35" s="1">
-        <v>0</v>
-      </c>
-      <c r="J35" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K35" s="1">
-        <v>0</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M35" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="N35">
-        <v>5000</v>
-      </c>
-      <c r="O35" s="15">
-        <v>1990000</v>
-      </c>
-    </row>
-    <row r="36" s="1" customFormat="1" spans="1:19">
-      <c r="A36" s="1">
-        <f t="shared" si="5"/>
-        <v>2001012</v>
-      </c>
-      <c r="B36" s="12">
-        <v>200101</v>
-      </c>
-      <c r="C36" s="12">
-        <v>2</v>
-      </c>
-      <c r="D36" s="12" t="str">
-        <f t="shared" ref="D36:D40" si="6">D35</f>
-        <v>龍虎鬥</v>
-      </c>
-      <c r="E36" s="13">
-        <v>200101001</v>
-      </c>
-      <c r="F36" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H36" s="1">
-        <v>2</v>
-      </c>
-      <c r="I36" s="1">
-        <v>500000</v>
-      </c>
-      <c r="J36" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K36" s="1">
-        <v>0</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M36" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="N36">
-        <v>500000</v>
-      </c>
-      <c r="O36" s="15">
-        <v>1990000</v>
-      </c>
-      <c r="S36" s="3"/>
-    </row>
-    <row r="37" s="1" customFormat="1" spans="1:19">
-      <c r="A37" s="1">
-        <f t="shared" si="5"/>
-        <v>2001013</v>
-      </c>
-      <c r="B37" s="12">
-        <v>200101</v>
-      </c>
-      <c r="C37" s="12">
-        <v>2</v>
-      </c>
-      <c r="D37" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v>龍虎鬥</v>
-      </c>
-      <c r="E37" s="13">
-        <v>200101001</v>
-      </c>
-      <c r="F37" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H37" s="1">
-        <v>3</v>
-      </c>
-      <c r="I37" s="1">
-        <v>50000000</v>
-      </c>
-      <c r="J37" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K37" s="1">
-        <v>0</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M37" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="N37">
-        <v>50000000</v>
-      </c>
-      <c r="O37" s="15">
-        <v>1990000</v>
-      </c>
-      <c r="S37" s="3"/>
-    </row>
-    <row r="38" spans="1:19">
-      <c r="A38" s="1">
-        <f t="shared" si="5"/>
-        <v>2003001</v>
-      </c>
-      <c r="B38" s="12">
-        <v>200300</v>
-      </c>
-      <c r="C38" s="12">
-        <v>2</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="E38" s="13">
-        <v>200300001</v>
-      </c>
-      <c r="F38" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H38" s="1">
-        <v>1</v>
-      </c>
-      <c r="I38" s="1">
-        <v>0</v>
-      </c>
-      <c r="J38" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K38" s="1">
-        <v>0</v>
-      </c>
-      <c r="L38" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M38" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="N38">
-        <v>5000</v>
-      </c>
-      <c r="O38" s="15">
-        <v>1990000</v>
-      </c>
-    </row>
-    <row r="39" s="1" customFormat="1" spans="1:19">
-      <c r="A39" s="1">
-        <f t="shared" si="5"/>
-        <v>2003002</v>
-      </c>
-      <c r="B39" s="12">
-        <v>200300</v>
-      </c>
-      <c r="C39" s="12">
-        <v>2</v>
-      </c>
-      <c r="D39" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v>飛禽走獸</v>
-      </c>
-      <c r="E39" s="13">
-        <v>200300001</v>
-      </c>
-      <c r="F39" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H39" s="1">
-        <v>2</v>
-      </c>
-      <c r="I39" s="1">
-        <v>500000</v>
-      </c>
-      <c r="J39" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K39" s="1">
-        <v>0</v>
-      </c>
-      <c r="L39" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M39" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="N39">
-        <v>500000</v>
-      </c>
-      <c r="O39" s="15">
-        <v>1990000</v>
-      </c>
-      <c r="Q39" s="3"/>
-      <c r="R39" s="12"/>
-      <c r="S39" s="3"/>
-    </row>
-    <row r="40" s="1" customFormat="1" spans="1:19">
-      <c r="A40" s="1">
-        <f t="shared" si="5"/>
-        <v>2003003</v>
-      </c>
-      <c r="B40" s="12">
-        <v>200300</v>
-      </c>
-      <c r="C40" s="12">
-        <v>2</v>
-      </c>
-      <c r="D40" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v>飛禽走獸</v>
-      </c>
-      <c r="E40" s="13">
-        <v>200300001</v>
-      </c>
-      <c r="F40" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H40" s="1">
-        <v>3</v>
-      </c>
-      <c r="I40" s="1">
-        <v>50000000</v>
-      </c>
-      <c r="J40" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K40" s="1">
-        <v>0</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M40" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="N40">
-        <v>50000000</v>
-      </c>
-      <c r="O40" s="15">
-        <v>1990000</v>
-      </c>
-      <c r="Q40" s="3"/>
-      <c r="R40" s="17"/>
-      <c r="S40" s="17"/>
-    </row>
-    <row r="41" spans="1:19">
-      <c r="A41" s="1">
-        <f t="shared" si="5"/>
-        <v>2004001</v>
-      </c>
-      <c r="B41" s="12">
-        <v>200400</v>
-      </c>
-      <c r="C41" s="12">
-        <v>2</v>
-      </c>
-      <c r="D41" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="E41" s="13">
-        <v>200400009</v>
-      </c>
-      <c r="F41" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H41" s="1">
-        <v>1</v>
-      </c>
-      <c r="I41" s="1">
-        <v>0</v>
-      </c>
-      <c r="J41" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K41" s="1">
-        <v>0</v>
-      </c>
-      <c r="L41" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M41" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="N41">
-        <v>5000</v>
-      </c>
-      <c r="O41" s="15">
-        <v>1990000</v>
-      </c>
-      <c r="Q41" s="3"/>
-      <c r="R41" s="17"/>
-      <c r="S41" s="17"/>
-    </row>
-    <row r="42" s="1" customFormat="1" spans="1:19">
-      <c r="A42" s="1">
-        <f t="shared" si="5"/>
-        <v>2004002</v>
-      </c>
-      <c r="B42" s="12">
-        <v>200400</v>
-      </c>
-      <c r="C42" s="12">
-        <v>2</v>
-      </c>
-      <c r="D42" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="E42" s="13">
-        <v>200400009</v>
-      </c>
-      <c r="F42" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H42" s="1">
-        <v>2</v>
-      </c>
-      <c r="I42" s="1">
-        <v>500000</v>
-      </c>
-      <c r="J42" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K42" s="1">
-        <v>0</v>
-      </c>
-      <c r="L42" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M42" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="N42">
-        <v>500000</v>
-      </c>
-      <c r="O42" s="15">
-        <v>1990000</v>
-      </c>
-      <c r="Q42" s="3"/>
-      <c r="R42" s="17"/>
-      <c r="S42" s="17"/>
-    </row>
-    <row r="43" s="1" customFormat="1" spans="1:19">
-      <c r="A43" s="1">
-        <f t="shared" si="5"/>
-        <v>2004003</v>
-      </c>
-      <c r="B43" s="12">
-        <v>200400</v>
       </c>
       <c r="C43" s="12">
         <v>2</v>
       </c>
-      <c r="D43" s="17" t="s">
-        <v>59</v>
+      <c r="D43" s="12" t="str">
+        <f>D42</f>
+        <v>紅黑大戰</v>
       </c>
       <c r="E43" s="13">
-        <v>200400009</v>
+        <v>200100038</v>
       </c>
       <c r="F43" s="13" t="s">
         <v>60</v>
@@ -3713,17 +3703,15 @@
       <c r="O43" s="15">
         <v>1990000</v>
       </c>
-      <c r="Q43" s="3"/>
-      <c r="R43" s="17"/>
-      <c r="S43" s="17"/>
+      <c r="Q43"/>
     </row>
     <row r="44" spans="1:19">
       <c r="A44" s="1">
         <f t="shared" si="5"/>
-        <v>2005001</v>
+        <v>2001011</v>
       </c>
       <c r="B44" s="12">
-        <v>200500</v>
+        <v>200101</v>
       </c>
       <c r="C44" s="12">
         <v>2</v>
@@ -3732,7 +3720,7 @@
         <v>61</v>
       </c>
       <c r="E44" s="13">
-        <v>200500025</v>
+        <v>200101001</v>
       </c>
       <c r="F44" s="13" t="s">
         <v>62</v>
@@ -3756,7 +3744,7 @@
         <v>33</v>
       </c>
       <c r="M44" s="23" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="N44">
         <v>5000</v>
@@ -3764,26 +3752,24 @@
       <c r="O44" s="15">
         <v>1990000</v>
       </c>
-      <c r="Q44" s="3"/>
-      <c r="R44" s="17"/>
-      <c r="S44" s="17"/>
-    </row>
-    <row r="45" spans="1:19">
+    </row>
+    <row r="45" s="1" customFormat="1" spans="1:19">
       <c r="A45" s="1">
         <f t="shared" si="5"/>
-        <v>2005002</v>
+        <v>2001012</v>
       </c>
       <c r="B45" s="12">
-        <v>200500</v>
+        <v>200101</v>
       </c>
       <c r="C45" s="12">
         <v>2</v>
       </c>
-      <c r="D45" s="12" t="s">
-        <v>61</v>
+      <c r="D45" s="12" t="str">
+        <f t="shared" ref="D45:D49" si="6">D44</f>
+        <v>龍虎鬥</v>
       </c>
       <c r="E45" s="13">
-        <v>200500025</v>
+        <v>200101001</v>
       </c>
       <c r="F45" s="13" t="s">
         <v>62</v>
@@ -3807,7 +3793,7 @@
         <v>33</v>
       </c>
       <c r="M45" s="23" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="N45">
         <v>500000</v>
@@ -3815,26 +3801,25 @@
       <c r="O45" s="15">
         <v>1990000</v>
       </c>
-      <c r="Q45" s="3"/>
-      <c r="R45" s="17"/>
-      <c r="S45" s="17"/>
-    </row>
-    <row r="46" spans="1:19">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" s="1" customFormat="1" spans="1:19">
       <c r="A46" s="1">
         <f t="shared" si="5"/>
-        <v>2005003</v>
+        <v>2001013</v>
       </c>
       <c r="B46" s="12">
-        <v>200500</v>
+        <v>200101</v>
       </c>
       <c r="C46" s="12">
         <v>2</v>
       </c>
-      <c r="D46" s="12" t="s">
-        <v>61</v>
+      <c r="D46" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>龍虎鬥</v>
       </c>
       <c r="E46" s="13">
-        <v>200500025</v>
+        <v>200101001</v>
       </c>
       <c r="F46" s="13" t="s">
         <v>62</v>
@@ -3858,7 +3843,7 @@
         <v>33</v>
       </c>
       <c r="M46" s="23" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="N46">
         <v>50000000</v>
@@ -3866,29 +3851,27 @@
       <c r="O46" s="15">
         <v>1990000</v>
       </c>
-      <c r="Q46" s="3"/>
-      <c r="R46" s="17"/>
-      <c r="S46" s="17"/>
+      <c r="S46" s="3"/>
     </row>
     <row r="47" spans="1:19">
       <c r="A47" s="1">
         <f t="shared" si="5"/>
-        <v>2006001</v>
+        <v>2003001</v>
       </c>
       <c r="B47" s="12">
-        <v>200600</v>
+        <v>200300</v>
       </c>
       <c r="C47" s="12">
         <v>2</v>
       </c>
-      <c r="D47" s="13" t="s">
+      <c r="D47" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E47" s="13">
+        <v>200300001</v>
+      </c>
+      <c r="F47" s="13" t="s">
         <v>64</v>
-      </c>
-      <c r="E47" s="13">
-        <v>200600001</v>
-      </c>
-      <c r="F47" s="13" t="s">
-        <v>65</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>32</v>
@@ -3917,29 +3900,27 @@
       <c r="O47" s="15">
         <v>1990000</v>
       </c>
-      <c r="Q47" s="3"/>
-      <c r="R47" s="17"/>
-      <c r="S47" s="17"/>
     </row>
     <row r="48" s="1" customFormat="1" spans="1:19">
       <c r="A48" s="1">
         <f t="shared" si="5"/>
-        <v>2006002</v>
+        <v>2003002</v>
       </c>
       <c r="B48" s="12">
-        <v>200600</v>
+        <v>200300</v>
       </c>
       <c r="C48" s="12">
         <v>2</v>
       </c>
-      <c r="D48" s="13" t="s">
+      <c r="D48" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>飛禽走獸</v>
+      </c>
+      <c r="E48" s="13">
+        <v>200300001</v>
+      </c>
+      <c r="F48" s="13" t="s">
         <v>64</v>
-      </c>
-      <c r="E48" s="13">
-        <v>200600001</v>
-      </c>
-      <c r="F48" s="13" t="s">
-        <v>65</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>35</v>
@@ -3969,28 +3950,29 @@
         <v>1990000</v>
       </c>
       <c r="Q48" s="3"/>
-      <c r="R48" s="17"/>
-      <c r="S48" s="17"/>
+      <c r="R48" s="12"/>
+      <c r="S48" s="3"/>
     </row>
     <row r="49" s="1" customFormat="1" spans="1:19">
       <c r="A49" s="1">
         <f t="shared" si="5"/>
-        <v>2006003</v>
+        <v>2003003</v>
       </c>
       <c r="B49" s="12">
-        <v>200600</v>
+        <v>200300</v>
       </c>
       <c r="C49" s="12">
         <v>2</v>
       </c>
-      <c r="D49" s="13" t="s">
+      <c r="D49" s="12" t="str">
+        <f t="shared" si="6"/>
+        <v>飛禽走獸</v>
+      </c>
+      <c r="E49" s="13">
+        <v>200300001</v>
+      </c>
+      <c r="F49" s="13" t="s">
         <v>64</v>
-      </c>
-      <c r="E49" s="13">
-        <v>200600001</v>
-      </c>
-      <c r="F49" s="13" t="s">
-        <v>65</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>36</v>
@@ -4020,28 +4002,28 @@
         <v>1990000</v>
       </c>
       <c r="Q49" s="3"/>
-      <c r="R49"/>
-      <c r="S49" s="17"/>
+      <c r="R49" s="18"/>
+      <c r="S49" s="18"/>
     </row>
     <row r="50" spans="1:19">
       <c r="A50" s="1">
         <f t="shared" si="5"/>
-        <v>2007001</v>
+        <v>2004001</v>
       </c>
       <c r="B50" s="12">
-        <v>200700</v>
+        <v>200400</v>
       </c>
       <c r="C50" s="12">
         <v>2</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D50" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="E50" s="13">
+        <v>200400009</v>
+      </c>
+      <c r="F50" s="13" t="s">
         <v>66</v>
-      </c>
-      <c r="E50" s="13">
-        <v>200700001</v>
-      </c>
-      <c r="F50" s="13" t="s">
-        <v>67</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>32</v>
@@ -4071,29 +4053,28 @@
         <v>1990000</v>
       </c>
       <c r="Q50" s="3"/>
-      <c r="R50" s="17"/>
-      <c r="S50" s="17"/>
+      <c r="R50" s="18"/>
+      <c r="S50" s="18"/>
     </row>
     <row r="51" s="1" customFormat="1" spans="1:19">
       <c r="A51" s="1">
         <f t="shared" si="5"/>
-        <v>2007002</v>
+        <v>2004002</v>
       </c>
       <c r="B51" s="12">
-        <v>200700</v>
+        <v>200400</v>
       </c>
       <c r="C51" s="12">
         <v>2</v>
       </c>
-      <c r="D51" s="12" t="str">
-        <f t="shared" ref="D48:D52" si="7">D50</f>
-        <v>越南色碟</v>
+      <c r="D51" s="18" t="s">
+        <v>65</v>
       </c>
       <c r="E51" s="13">
-        <v>200700001</v>
+        <v>200400009</v>
       </c>
       <c r="F51" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>35</v>
@@ -4123,29 +4104,28 @@
         <v>1990000</v>
       </c>
       <c r="Q51" s="3"/>
-      <c r="R51" s="17"/>
-      <c r="S51" s="17"/>
+      <c r="R51" s="18"/>
+      <c r="S51" s="18"/>
     </row>
     <row r="52" s="1" customFormat="1" spans="1:19">
       <c r="A52" s="1">
         <f t="shared" si="5"/>
-        <v>2007003</v>
+        <v>2004003</v>
       </c>
       <c r="B52" s="12">
-        <v>200700</v>
+        <v>200400</v>
       </c>
       <c r="C52" s="12">
         <v>2</v>
       </c>
-      <c r="D52" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v>越南色碟</v>
+      <c r="D52" s="18" t="s">
+        <v>65</v>
       </c>
       <c r="E52" s="13">
-        <v>200700001</v>
+        <v>200400009</v>
       </c>
       <c r="F52" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>36</v>
@@ -4174,27 +4154,29 @@
       <c r="O52" s="15">
         <v>1990000</v>
       </c>
-      <c r="S52" s="3"/>
-    </row>
-    <row r="53" s="1" customFormat="1" spans="1:19">
+      <c r="Q52" s="3"/>
+      <c r="R52" s="18"/>
+      <c r="S52" s="18"/>
+    </row>
+    <row r="53" spans="1:19">
       <c r="A53" s="1">
         <f t="shared" si="5"/>
-        <v>2008001</v>
+        <v>2005001</v>
       </c>
       <c r="B53" s="12">
-        <v>200800</v>
+        <v>200500</v>
       </c>
       <c r="C53" s="12">
         <v>2</v>
       </c>
-      <c r="D53" s="13" t="s">
+      <c r="D53" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="E53" s="13">
+        <v>200500025</v>
+      </c>
+      <c r="F53" s="13" t="s">
         <v>68</v>
-      </c>
-      <c r="E53" s="13">
-        <v>200800001</v>
-      </c>
-      <c r="F53" s="13" t="s">
-        <v>69</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>32</v>
@@ -4215,7 +4197,7 @@
         <v>33</v>
       </c>
       <c r="M53" s="23" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="N53">
         <v>5000</v>
@@ -4223,27 +4205,29 @@
       <c r="O53" s="15">
         <v>1990000</v>
       </c>
-      <c r="S53" s="3"/>
-    </row>
-    <row r="54" s="1" customFormat="1" spans="1:19">
+      <c r="Q53" s="3"/>
+      <c r="R53" s="18"/>
+      <c r="S53" s="18"/>
+    </row>
+    <row r="54" spans="1:19">
       <c r="A54" s="1">
         <f t="shared" si="5"/>
-        <v>2008002</v>
+        <v>2005002</v>
       </c>
       <c r="B54" s="12">
-        <v>200800</v>
+        <v>200500</v>
       </c>
       <c r="C54" s="12">
         <v>2</v>
       </c>
-      <c r="D54" s="13" t="s">
+      <c r="D54" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="E54" s="13">
+        <v>200500025</v>
+      </c>
+      <c r="F54" s="13" t="s">
         <v>68</v>
-      </c>
-      <c r="E54" s="13">
-        <v>200800001</v>
-      </c>
-      <c r="F54" s="13" t="s">
-        <v>69</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>35</v>
@@ -4264,7 +4248,7 @@
         <v>33</v>
       </c>
       <c r="M54" s="23" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="N54">
         <v>500000</v>
@@ -4272,27 +4256,29 @@
       <c r="O54" s="15">
         <v>1990000</v>
       </c>
-      <c r="S54" s="3"/>
-    </row>
-    <row r="55" s="1" customFormat="1" spans="1:19">
+      <c r="Q54" s="3"/>
+      <c r="R54" s="18"/>
+      <c r="S54" s="18"/>
+    </row>
+    <row r="55" spans="1:19">
       <c r="A55" s="1">
         <f t="shared" si="5"/>
-        <v>2008003</v>
+        <v>2005003</v>
       </c>
       <c r="B55" s="12">
-        <v>200800</v>
+        <v>200500</v>
       </c>
       <c r="C55" s="12">
         <v>2</v>
       </c>
-      <c r="D55" s="13" t="s">
+      <c r="D55" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="E55" s="13">
+        <v>200500025</v>
+      </c>
+      <c r="F55" s="13" t="s">
         <v>68</v>
-      </c>
-      <c r="E55" s="13">
-        <v>200800001</v>
-      </c>
-      <c r="F55" s="13" t="s">
-        <v>69</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>36</v>
@@ -4313,7 +4299,7 @@
         <v>33</v>
       </c>
       <c r="M55" s="23" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="N55">
         <v>50000000</v>
@@ -4321,24 +4307,26 @@
       <c r="O55" s="15">
         <v>1990000</v>
       </c>
-      <c r="S55" s="3"/>
+      <c r="Q55" s="3"/>
+      <c r="R55" s="18"/>
+      <c r="S55" s="18"/>
     </row>
     <row r="56" spans="1:19">
       <c r="A56" s="1">
         <f t="shared" si="5"/>
-        <v>2009001</v>
-      </c>
-      <c r="B56" s="18">
-        <v>200900</v>
+        <v>2006001</v>
+      </c>
+      <c r="B56" s="12">
+        <v>200600</v>
       </c>
       <c r="C56" s="12">
         <v>2</v>
       </c>
-      <c r="D56" s="18" t="s">
+      <c r="D56" s="13" t="s">
         <v>70</v>
       </c>
       <c r="E56" s="13">
-        <v>200900001</v>
+        <v>200600001</v>
       </c>
       <c r="F56" s="13" t="s">
         <v>71</v>
@@ -4370,24 +4358,26 @@
       <c r="O56" s="15">
         <v>1990000</v>
       </c>
-    </row>
-    <row r="57" spans="1:19">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="18"/>
+      <c r="S56" s="18"/>
+    </row>
+    <row r="57" s="1" customFormat="1" spans="1:19">
       <c r="A57" s="1">
         <f t="shared" si="5"/>
-        <v>2009002</v>
+        <v>2006002</v>
       </c>
       <c r="B57" s="12">
-        <v>200900</v>
+        <v>200600</v>
       </c>
       <c r="C57" s="12">
         <v>2</v>
       </c>
-      <c r="D57" s="12" t="str">
-        <f>D56</f>
-        <v>魚蝦蟹</v>
+      <c r="D57" s="13" t="s">
+        <v>70</v>
       </c>
       <c r="E57" s="13">
-        <v>200900001</v>
+        <v>200600001</v>
       </c>
       <c r="F57" s="13" t="s">
         <v>71</v>
@@ -4419,24 +4409,26 @@
       <c r="O57" s="15">
         <v>1990000</v>
       </c>
-    </row>
-    <row r="58" spans="1:19">
+      <c r="Q57" s="3"/>
+      <c r="R57" s="18"/>
+      <c r="S57" s="18"/>
+    </row>
+    <row r="58" s="1" customFormat="1" spans="1:19">
       <c r="A58" s="1">
         <f t="shared" si="5"/>
-        <v>2009003</v>
+        <v>2006003</v>
       </c>
       <c r="B58" s="12">
-        <v>200900</v>
+        <v>200600</v>
       </c>
       <c r="C58" s="12">
         <v>2</v>
       </c>
-      <c r="D58" s="12" t="str">
-        <f>D57</f>
-        <v>魚蝦蟹</v>
+      <c r="D58" s="13" t="s">
+        <v>70</v>
       </c>
       <c r="E58" s="13">
-        <v>200900001</v>
+        <v>200600001</v>
       </c>
       <c r="F58" s="13" t="s">
         <v>71</v>
@@ -4468,14 +4460,17 @@
       <c r="O58" s="15">
         <v>1990000</v>
       </c>
+      <c r="Q58" s="3"/>
+      <c r="R58"/>
+      <c r="S58" s="18"/>
     </row>
     <row r="59" spans="1:19">
       <c r="A59" s="1">
         <f t="shared" si="5"/>
-        <v>2010001</v>
+        <v>2007001</v>
       </c>
       <c r="B59" s="12">
-        <v>201000</v>
+        <v>200700</v>
       </c>
       <c r="C59" s="12">
         <v>2</v>
@@ -4484,9 +4479,11 @@
         <v>72</v>
       </c>
       <c r="E59" s="13">
-        <v>101000006</v>
-      </c>
-      <c r="F59" s="13"/>
+        <v>200700001</v>
+      </c>
+      <c r="F59" s="13" t="s">
+        <v>73</v>
+      </c>
       <c r="G59" s="1" t="s">
         <v>32</v>
       </c>
@@ -4514,25 +4511,31 @@
       <c r="O59" s="15">
         <v>1990000</v>
       </c>
-    </row>
-    <row r="60" spans="1:19">
+      <c r="Q59" s="3"/>
+      <c r="R59" s="18"/>
+      <c r="S59" s="18"/>
+    </row>
+    <row r="60" s="1" customFormat="1" spans="1:19">
       <c r="A60" s="1">
         <f t="shared" si="5"/>
-        <v>2010002</v>
+        <v>2007002</v>
       </c>
       <c r="B60" s="12">
-        <v>201000</v>
+        <v>200700</v>
       </c>
       <c r="C60" s="12">
         <v>2</v>
       </c>
-      <c r="D60" s="12" t="s">
-        <v>72</v>
+      <c r="D60" s="12" t="str">
+        <f t="shared" ref="D57:D61" si="7">D59</f>
+        <v>越南色碟</v>
       </c>
       <c r="E60" s="13">
-        <v>101000006</v>
-      </c>
-      <c r="F60" s="13"/>
+        <v>200700001</v>
+      </c>
+      <c r="F60" s="13" t="s">
+        <v>73</v>
+      </c>
       <c r="G60" s="1" t="s">
         <v>35</v>
       </c>
@@ -4560,25 +4563,31 @@
       <c r="O60" s="15">
         <v>1990000</v>
       </c>
-    </row>
-    <row r="61" spans="1:19">
+      <c r="Q60" s="3"/>
+      <c r="R60" s="18"/>
+      <c r="S60" s="18"/>
+    </row>
+    <row r="61" s="1" customFormat="1" spans="1:19">
       <c r="A61" s="1">
         <f t="shared" si="5"/>
-        <v>2010003</v>
+        <v>2007003</v>
       </c>
       <c r="B61" s="12">
-        <v>201000</v>
+        <v>200700</v>
       </c>
       <c r="C61" s="12">
         <v>2</v>
       </c>
-      <c r="D61" s="12" t="s">
-        <v>72</v>
+      <c r="D61" s="12" t="str">
+        <f t="shared" si="7"/>
+        <v>越南色碟</v>
       </c>
       <c r="E61" s="13">
-        <v>101000006</v>
-      </c>
-      <c r="F61" s="13"/>
+        <v>200700001</v>
+      </c>
+      <c r="F61" s="13" t="s">
+        <v>73</v>
+      </c>
       <c r="G61" s="1" t="s">
         <v>36</v>
       </c>
@@ -4606,26 +4615,27 @@
       <c r="O61" s="15">
         <v>1990000</v>
       </c>
-    </row>
-    <row r="62" spans="1:19">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" s="1" customFormat="1" spans="1:19">
       <c r="A62" s="1">
         <f t="shared" si="5"/>
-        <v>3001001</v>
+        <v>2008001</v>
       </c>
       <c r="B62" s="12">
-        <v>300100</v>
+        <v>200800</v>
       </c>
       <c r="C62" s="12">
-        <v>3</v>
-      </c>
-      <c r="D62" s="12" t="s">
-        <v>73</v>
+        <v>2</v>
+      </c>
+      <c r="D62" s="13" t="s">
+        <v>74</v>
       </c>
       <c r="E62" s="13">
-        <v>300100001</v>
+        <v>200800001</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>32</v>
@@ -4642,11 +4652,11 @@
       <c r="K62" s="1">
         <v>0</v>
       </c>
-      <c r="L62" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="M62" s="24" t="s">
-        <v>76</v>
+      <c r="L62" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M62" s="23" t="s">
+        <v>34</v>
       </c>
       <c r="N62">
         <v>5000</v>
@@ -4654,26 +4664,27 @@
       <c r="O62" s="15">
         <v>1990000</v>
       </c>
+      <c r="S62" s="3"/>
     </row>
     <row r="63" s="1" customFormat="1" spans="1:19">
       <c r="A63" s="1">
         <f t="shared" si="5"/>
-        <v>3001002</v>
+        <v>2008002</v>
       </c>
       <c r="B63" s="12">
-        <v>300100</v>
+        <v>200800</v>
       </c>
       <c r="C63" s="12">
-        <v>3</v>
-      </c>
-      <c r="D63" s="12" t="s">
-        <v>73</v>
+        <v>2</v>
+      </c>
+      <c r="D63" s="13" t="s">
+        <v>74</v>
       </c>
       <c r="E63" s="13">
-        <v>300100001</v>
+        <v>200800001</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>35</v>
@@ -4690,11 +4701,11 @@
       <c r="K63" s="1">
         <v>0</v>
       </c>
-      <c r="L63" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="M63" s="24" t="s">
-        <v>76</v>
+      <c r="L63" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M63" s="23" t="s">
+        <v>34</v>
       </c>
       <c r="N63">
         <v>500000</v>
@@ -4707,22 +4718,22 @@
     <row r="64" s="1" customFormat="1" spans="1:19">
       <c r="A64" s="1">
         <f t="shared" si="5"/>
-        <v>3001003</v>
+        <v>2008003</v>
       </c>
       <c r="B64" s="12">
-        <v>300100</v>
+        <v>200800</v>
       </c>
       <c r="C64" s="12">
-        <v>3</v>
-      </c>
-      <c r="D64" s="12" t="s">
-        <v>73</v>
+        <v>2</v>
+      </c>
+      <c r="D64" s="13" t="s">
+        <v>74</v>
       </c>
       <c r="E64" s="13">
-        <v>300100001</v>
+        <v>200800001</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>36</v>
@@ -4739,11 +4750,11 @@
       <c r="K64" s="1">
         <v>0</v>
       </c>
-      <c r="L64" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="M64" s="24" t="s">
-        <v>76</v>
+      <c r="L64" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M64" s="23" t="s">
+        <v>34</v>
       </c>
       <c r="N64">
         <v>50000000</v>
@@ -4753,25 +4764,25 @@
       </c>
       <c r="S64" s="3"/>
     </row>
-    <row r="65" s="1" customFormat="1" spans="1:19">
+    <row r="65" spans="1:19">
       <c r="A65" s="1">
         <f t="shared" si="5"/>
-        <v>3002001</v>
-      </c>
-      <c r="B65" s="12">
-        <v>300200</v>
+        <v>2009001</v>
+      </c>
+      <c r="B65" s="19">
+        <v>200900</v>
       </c>
       <c r="C65" s="12">
-        <v>3</v>
-      </c>
-      <c r="D65" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D65" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="E65" s="13">
+        <v>200900001</v>
+      </c>
+      <c r="F65" s="13" t="s">
         <v>77</v>
-      </c>
-      <c r="E65" s="13">
-        <v>300200006</v>
-      </c>
-      <c r="F65" s="13" t="s">
-        <v>78</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>32</v>
@@ -4780,7 +4791,7 @@
         <v>1</v>
       </c>
       <c r="I65" s="1">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="J65" s="1">
         <v>-1</v>
@@ -4788,11 +4799,11 @@
       <c r="K65" s="1">
         <v>0</v>
       </c>
-      <c r="L65" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="M65" s="24" t="s">
-        <v>76</v>
+      <c r="L65" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M65" s="23" t="s">
+        <v>34</v>
       </c>
       <c r="N65">
         <v>5000</v>
@@ -4800,27 +4811,27 @@
       <c r="O65" s="15">
         <v>1990000</v>
       </c>
-      <c r="S65" s="3"/>
-    </row>
-    <row r="66" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="66" spans="1:19">
       <c r="A66" s="1">
         <f t="shared" si="5"/>
-        <v>3002002</v>
+        <v>2009002</v>
       </c>
       <c r="B66" s="12">
-        <v>300200</v>
+        <v>200900</v>
       </c>
       <c r="C66" s="12">
-        <v>3</v>
-      </c>
-      <c r="D66" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D66" s="12" t="str">
+        <f>D65</f>
+        <v>魚蝦蟹</v>
+      </c>
+      <c r="E66" s="13">
+        <v>200900001</v>
+      </c>
+      <c r="F66" s="13" t="s">
         <v>77</v>
-      </c>
-      <c r="E66" s="13">
-        <v>300200006</v>
-      </c>
-      <c r="F66" s="13" t="s">
-        <v>78</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>35</v>
@@ -4837,11 +4848,11 @@
       <c r="K66" s="1">
         <v>0</v>
       </c>
-      <c r="L66" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="M66" s="24" t="s">
-        <v>76</v>
+      <c r="L66" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M66" s="23" t="s">
+        <v>34</v>
       </c>
       <c r="N66">
         <v>500000</v>
@@ -4849,27 +4860,27 @@
       <c r="O66" s="15">
         <v>1990000</v>
       </c>
-      <c r="S66" s="3"/>
-    </row>
-    <row r="67" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="67" spans="1:19">
       <c r="A67" s="1">
         <f t="shared" si="5"/>
-        <v>3002003</v>
+        <v>2009003</v>
       </c>
       <c r="B67" s="12">
-        <v>300200</v>
+        <v>200900</v>
       </c>
       <c r="C67" s="12">
-        <v>3</v>
-      </c>
-      <c r="D67" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D67" s="12" t="str">
+        <f>D66</f>
+        <v>魚蝦蟹</v>
+      </c>
+      <c r="E67" s="13">
+        <v>200900001</v>
+      </c>
+      <c r="F67" s="13" t="s">
         <v>77</v>
-      </c>
-      <c r="E67" s="13">
-        <v>300200006</v>
-      </c>
-      <c r="F67" s="13" t="s">
-        <v>78</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>36</v>
@@ -4886,11 +4897,11 @@
       <c r="K67" s="1">
         <v>0</v>
       </c>
-      <c r="L67" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="M67" s="24" t="s">
-        <v>76</v>
+      <c r="L67" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M67" s="23" t="s">
+        <v>34</v>
       </c>
       <c r="N67">
         <v>50000000</v>
@@ -4898,478 +4909,476 @@
       <c r="O67" s="15">
         <v>1990000</v>
       </c>
-      <c r="S67" s="3"/>
-    </row>
-    <row r="68" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="68" spans="1:19">
       <c r="A68" s="1">
-        <v>20010010</v>
-      </c>
-      <c r="B68" s="16">
-        <v>200100</v>
-      </c>
-      <c r="C68" s="16">
+        <f t="shared" si="5"/>
+        <v>2010001</v>
+      </c>
+      <c r="B68" s="12">
+        <v>201000</v>
+      </c>
+      <c r="C68" s="12">
         <v>2</v>
       </c>
-      <c r="D68" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="E68" s="16">
-        <v>200100038</v>
-      </c>
-      <c r="F68" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="G68" s="19" t="s">
+      <c r="D68" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="E68" s="13">
+        <v>101000006</v>
+      </c>
+      <c r="F68" s="13"/>
+      <c r="G68" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H68" s="1">
+        <v>1</v>
+      </c>
+      <c r="I68" s="1">
+        <v>0</v>
+      </c>
+      <c r="J68" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K68" s="1">
+        <v>0</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M68" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="N68">
+        <v>5000</v>
+      </c>
+      <c r="O68" s="15">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19">
+      <c r="A69" s="1">
+        <f t="shared" si="5"/>
+        <v>2010002</v>
+      </c>
+      <c r="B69" s="12">
+        <v>201000</v>
+      </c>
+      <c r="C69" s="12">
+        <v>2</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="E69" s="13">
+        <v>101000006</v>
+      </c>
+      <c r="F69" s="13"/>
+      <c r="G69" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H69" s="1">
+        <v>2</v>
+      </c>
+      <c r="I69" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J69" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K69" s="1">
+        <v>0</v>
+      </c>
+      <c r="L69" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M69" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="N69">
+        <v>500000</v>
+      </c>
+      <c r="O69" s="15">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19">
+      <c r="A70" s="1">
+        <f t="shared" si="5"/>
+        <v>2010003</v>
+      </c>
+      <c r="B70" s="12">
+        <v>201000</v>
+      </c>
+      <c r="C70" s="12">
+        <v>2</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="E70" s="13">
+        <v>101000006</v>
+      </c>
+      <c r="F70" s="13"/>
+      <c r="G70" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H70" s="1">
+        <v>3</v>
+      </c>
+      <c r="I70" s="1">
+        <v>50000000</v>
+      </c>
+      <c r="J70" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K70" s="1">
+        <v>0</v>
+      </c>
+      <c r="L70" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M70" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="N70">
+        <v>50000000</v>
+      </c>
+      <c r="O70" s="15">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19">
+      <c r="A71" s="1">
+        <f t="shared" si="5"/>
+        <v>3001001</v>
+      </c>
+      <c r="B71" s="12">
+        <v>300100</v>
+      </c>
+      <c r="C71" s="12">
+        <v>3</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E71" s="13">
+        <v>300100001</v>
+      </c>
+      <c r="F71" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="H68" s="19">
-        <v>10</v>
-      </c>
-      <c r="I68" s="19">
-        <v>0</v>
-      </c>
-      <c r="J68" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K68" s="19">
-        <v>0</v>
-      </c>
-      <c r="L68" s="19" t="s">
+      <c r="G71" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H71" s="1">
+        <v>1</v>
+      </c>
+      <c r="I71" s="1">
+        <v>0</v>
+      </c>
+      <c r="J71" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K71" s="1">
+        <v>0</v>
+      </c>
+      <c r="L71" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="M68" s="19">
-        <v>0</v>
-      </c>
-      <c r="N68" s="20">
-        <v>200</v>
-      </c>
-      <c r="O68" s="21">
-        <v>1980000</v>
-      </c>
-      <c r="S68" s="3"/>
-    </row>
-    <row r="69" s="1" customFormat="1" spans="1:19">
-      <c r="A69" s="1">
-        <v>20010011</v>
-      </c>
-      <c r="B69" s="16">
-        <v>200100</v>
-      </c>
-      <c r="C69" s="16">
-        <v>2</v>
-      </c>
-      <c r="D69" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="E69" s="16">
-        <v>200100038</v>
-      </c>
-      <c r="F69" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="G69" s="19" t="s">
+      <c r="M71" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="H69" s="19">
-        <v>11</v>
-      </c>
-      <c r="I69" s="19">
-        <v>0</v>
-      </c>
-      <c r="J69" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K69" s="19">
-        <v>0</v>
-      </c>
-      <c r="L69" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M69" s="19">
-        <v>0</v>
-      </c>
-      <c r="N69" s="20">
+      <c r="N71">
         <v>5000</v>
       </c>
-      <c r="O69" s="21">
-        <v>1980000</v>
-      </c>
-      <c r="S69" s="3"/>
-    </row>
-    <row r="70" s="1" customFormat="1" spans="1:19">
-      <c r="A70" s="1">
-        <v>20010012</v>
-      </c>
-      <c r="B70" s="16">
-        <v>200100</v>
-      </c>
-      <c r="C70" s="16">
-        <v>2</v>
-      </c>
-      <c r="D70" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="E70" s="16">
-        <v>200100038</v>
-      </c>
-      <c r="F70" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="G70" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H70" s="19">
-        <v>12</v>
-      </c>
-      <c r="I70" s="19">
-        <v>0</v>
-      </c>
-      <c r="J70" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K70" s="19">
-        <v>0</v>
-      </c>
-      <c r="L70" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M70" s="19">
-        <v>0</v>
-      </c>
-      <c r="N70" s="20">
-        <v>100000</v>
-      </c>
-      <c r="O70" s="21">
-        <v>1980000</v>
-      </c>
-      <c r="S70" s="3"/>
-    </row>
-    <row r="71" s="1" customFormat="1" spans="1:19">
-      <c r="A71" s="1">
-        <v>20010110</v>
-      </c>
-      <c r="B71" s="16">
-        <v>200101</v>
-      </c>
-      <c r="C71" s="16">
-        <v>2</v>
-      </c>
-      <c r="D71" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="E71" s="16">
-        <v>200101001</v>
-      </c>
-      <c r="F71" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="G71" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H71" s="19">
-        <v>10</v>
-      </c>
-      <c r="I71" s="19">
-        <v>0</v>
-      </c>
-      <c r="J71" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K71" s="19">
-        <v>0</v>
-      </c>
-      <c r="L71" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M71" s="19">
-        <v>0</v>
-      </c>
-      <c r="N71" s="20">
-        <v>200</v>
-      </c>
-      <c r="O71" s="21">
-        <v>1980000</v>
-      </c>
-      <c r="S71" s="3"/>
+      <c r="O71" s="15">
+        <v>1990000</v>
+      </c>
     </row>
     <row r="72" s="1" customFormat="1" spans="1:19">
       <c r="A72" s="1">
-        <v>20010111</v>
-      </c>
-      <c r="B72" s="16">
-        <v>200101</v>
-      </c>
-      <c r="C72" s="16">
+        <f t="shared" si="5"/>
+        <v>3001002</v>
+      </c>
+      <c r="B72" s="12">
+        <v>300100</v>
+      </c>
+      <c r="C72" s="12">
+        <v>3</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E72" s="13">
+        <v>300100001</v>
+      </c>
+      <c r="F72" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H72" s="1">
         <v>2</v>
       </c>
-      <c r="D72" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="E72" s="16">
-        <v>200101001</v>
-      </c>
-      <c r="F72" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="G72" s="19" t="s">
+      <c r="I72" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J72" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K72" s="1">
+        <v>0</v>
+      </c>
+      <c r="L72" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="M72" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="H72" s="19">
-        <v>11</v>
-      </c>
-      <c r="I72" s="19">
-        <v>0</v>
-      </c>
-      <c r="J72" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K72" s="19">
-        <v>0</v>
-      </c>
-      <c r="L72" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M72" s="19">
-        <v>0</v>
-      </c>
-      <c r="N72" s="20">
-        <v>5000</v>
-      </c>
-      <c r="O72" s="21">
-        <v>1980000</v>
+      <c r="N72">
+        <v>500000</v>
+      </c>
+      <c r="O72" s="15">
+        <v>1990000</v>
       </c>
       <c r="S72" s="3"/>
     </row>
     <row r="73" s="1" customFormat="1" spans="1:19">
       <c r="A73" s="1">
-        <v>20010112</v>
-      </c>
-      <c r="B73" s="16">
-        <v>200101</v>
-      </c>
-      <c r="C73" s="16">
-        <v>2</v>
-      </c>
-      <c r="D73" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="E73" s="16">
-        <v>200101001</v>
-      </c>
-      <c r="F73" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="G73" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H73" s="19">
-        <v>12</v>
-      </c>
-      <c r="I73" s="19">
-        <v>0</v>
-      </c>
-      <c r="J73" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K73" s="19">
-        <v>0</v>
-      </c>
-      <c r="L73" s="19" t="s">
+        <f t="shared" si="5"/>
+        <v>3001003</v>
+      </c>
+      <c r="B73" s="12">
+        <v>300100</v>
+      </c>
+      <c r="C73" s="12">
+        <v>3</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E73" s="13">
+        <v>300100001</v>
+      </c>
+      <c r="F73" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H73" s="1">
+        <v>3</v>
+      </c>
+      <c r="I73" s="1">
+        <v>50000000</v>
+      </c>
+      <c r="J73" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K73" s="1">
+        <v>0</v>
+      </c>
+      <c r="L73" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="M73" s="19">
-        <v>0</v>
-      </c>
-      <c r="N73" s="20">
-        <v>100000</v>
-      </c>
-      <c r="O73" s="21">
-        <v>1980000</v>
+      <c r="M73" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="N73">
+        <v>50000000</v>
+      </c>
+      <c r="O73" s="15">
+        <v>1990000</v>
       </c>
       <c r="S73" s="3"/>
     </row>
     <row r="74" s="1" customFormat="1" spans="1:19">
       <c r="A74" s="1">
-        <v>20030010</v>
-      </c>
-      <c r="B74" s="16">
-        <v>200300</v>
-      </c>
-      <c r="C74" s="16">
-        <v>2</v>
-      </c>
-      <c r="D74" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="E74" s="16">
-        <v>200300001</v>
-      </c>
-      <c r="F74" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="G74" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H74" s="19">
-        <v>10</v>
-      </c>
-      <c r="I74" s="19">
-        <v>0</v>
-      </c>
-      <c r="J74" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K74" s="19">
-        <v>0</v>
-      </c>
-      <c r="L74" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M74" s="19">
-        <v>0</v>
-      </c>
-      <c r="N74" s="20">
-        <v>200</v>
-      </c>
-      <c r="O74" s="21">
-        <v>1980000</v>
+        <f t="shared" si="5"/>
+        <v>3002001</v>
+      </c>
+      <c r="B74" s="12">
+        <v>300200</v>
+      </c>
+      <c r="C74" s="12">
+        <v>3</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="E74" s="13">
+        <v>300200006</v>
+      </c>
+      <c r="F74" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H74" s="1">
+        <v>1</v>
+      </c>
+      <c r="I74" s="1">
+        <v>2000</v>
+      </c>
+      <c r="J74" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K74" s="1">
+        <v>0</v>
+      </c>
+      <c r="L74" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="M74" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="N74">
+        <v>5000</v>
+      </c>
+      <c r="O74" s="15">
+        <v>1990000</v>
       </c>
       <c r="S74" s="3"/>
     </row>
     <row r="75" s="1" customFormat="1" spans="1:19">
       <c r="A75" s="1">
-        <v>20030011</v>
-      </c>
-      <c r="B75" s="16">
-        <v>200300</v>
-      </c>
-      <c r="C75" s="16">
+        <f t="shared" si="5"/>
+        <v>3002002</v>
+      </c>
+      <c r="B75" s="12">
+        <v>300200</v>
+      </c>
+      <c r="C75" s="12">
+        <v>3</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="E75" s="13">
+        <v>300200006</v>
+      </c>
+      <c r="F75" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H75" s="1">
         <v>2</v>
       </c>
-      <c r="D75" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="E75" s="16">
-        <v>200300001</v>
-      </c>
-      <c r="F75" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="G75" s="19" t="s">
+      <c r="I75" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J75" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K75" s="1">
+        <v>0</v>
+      </c>
+      <c r="L75" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="M75" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="H75" s="19">
-        <v>11</v>
-      </c>
-      <c r="I75" s="19">
-        <v>0</v>
-      </c>
-      <c r="J75" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K75" s="19">
-        <v>0</v>
-      </c>
-      <c r="L75" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M75" s="19">
-        <v>0</v>
-      </c>
-      <c r="N75" s="20">
-        <v>5000</v>
-      </c>
-      <c r="O75" s="21">
-        <v>1980000</v>
+      <c r="N75">
+        <v>500000</v>
+      </c>
+      <c r="O75" s="15">
+        <v>1990000</v>
       </c>
       <c r="S75" s="3"/>
     </row>
     <row r="76" s="1" customFormat="1" spans="1:19">
       <c r="A76" s="1">
-        <v>20030012</v>
-      </c>
-      <c r="B76" s="16">
-        <v>200300</v>
-      </c>
-      <c r="C76" s="16">
-        <v>2</v>
-      </c>
-      <c r="D76" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="E76" s="16">
-        <v>200300001</v>
-      </c>
-      <c r="F76" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="G76" s="19" t="s">
+        <f t="shared" si="5"/>
+        <v>3002003</v>
+      </c>
+      <c r="B76" s="12">
+        <v>300200</v>
+      </c>
+      <c r="C76" s="12">
+        <v>3</v>
+      </c>
+      <c r="D76" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="H76" s="19">
-        <v>12</v>
-      </c>
-      <c r="I76" s="19">
-        <v>0</v>
-      </c>
-      <c r="J76" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K76" s="19">
-        <v>0</v>
-      </c>
-      <c r="L76" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M76" s="19">
-        <v>0</v>
-      </c>
-      <c r="N76" s="20">
-        <v>100000</v>
-      </c>
-      <c r="O76" s="21">
-        <v>1980000</v>
+      <c r="E76" s="13">
+        <v>300200006</v>
+      </c>
+      <c r="F76" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H76" s="1">
+        <v>3</v>
+      </c>
+      <c r="I76" s="1">
+        <v>50000000</v>
+      </c>
+      <c r="J76" s="1">
+        <v>-1</v>
+      </c>
+      <c r="K76" s="1">
+        <v>0</v>
+      </c>
+      <c r="L76" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="M76" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="N76">
+        <v>50000000</v>
+      </c>
+      <c r="O76" s="15">
+        <v>1990000</v>
       </c>
       <c r="S76" s="3"/>
     </row>
     <row r="77" s="1" customFormat="1" spans="1:19">
       <c r="A77" s="1">
-        <v>20040010</v>
+        <v>20010010</v>
       </c>
       <c r="B77" s="16">
-        <v>200400</v>
+        <v>200100</v>
       </c>
       <c r="C77" s="16">
         <v>2</v>
       </c>
-      <c r="D77" s="22" t="s">
+      <c r="D77" s="16" t="s">
         <v>59</v>
       </c>
       <c r="E77" s="16">
-        <v>200400009</v>
+        <v>200100038</v>
       </c>
       <c r="F77" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="G77" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H77" s="19">
+      <c r="G77" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H77" s="17">
         <v>10</v>
       </c>
-      <c r="I77" s="19">
-        <v>0</v>
-      </c>
-      <c r="J77" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K77" s="19">
-        <v>0</v>
-      </c>
-      <c r="L77" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M77" s="19">
+      <c r="I77" s="17">
+        <v>0</v>
+      </c>
+      <c r="J77" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K77" s="17">
+        <v>0</v>
+      </c>
+      <c r="L77" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M77" s="17">
         <v>0</v>
       </c>
       <c r="N77" s="20">
@@ -5382,42 +5391,42 @@
     </row>
     <row r="78" s="1" customFormat="1" spans="1:19">
       <c r="A78" s="1">
-        <v>20040011</v>
+        <v>20010011</v>
       </c>
       <c r="B78" s="16">
-        <v>200400</v>
+        <v>200100</v>
       </c>
       <c r="C78" s="16">
         <v>2</v>
       </c>
-      <c r="D78" s="22" t="s">
+      <c r="D78" s="16" t="s">
         <v>59</v>
       </c>
       <c r="E78" s="16">
-        <v>200400009</v>
+        <v>200100038</v>
       </c>
       <c r="F78" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="G78" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="H78" s="19">
+      <c r="G78" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H78" s="17">
         <v>11</v>
       </c>
-      <c r="I78" s="19">
-        <v>0</v>
-      </c>
-      <c r="J78" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K78" s="19">
-        <v>0</v>
-      </c>
-      <c r="L78" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M78" s="19">
+      <c r="I78" s="17">
+        <v>0</v>
+      </c>
+      <c r="J78" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K78" s="17">
+        <v>0</v>
+      </c>
+      <c r="L78" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M78" s="17">
         <v>0</v>
       </c>
       <c r="N78" s="20">
@@ -5430,42 +5439,42 @@
     </row>
     <row r="79" s="1" customFormat="1" spans="1:19">
       <c r="A79" s="1">
-        <v>20040012</v>
+        <v>20010012</v>
       </c>
       <c r="B79" s="16">
-        <v>200400</v>
+        <v>200100</v>
       </c>
       <c r="C79" s="16">
         <v>2</v>
       </c>
-      <c r="D79" s="22" t="s">
+      <c r="D79" s="16" t="s">
         <v>59</v>
       </c>
       <c r="E79" s="16">
-        <v>200400009</v>
+        <v>200100038</v>
       </c>
       <c r="F79" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="G79" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H79" s="19">
+      <c r="G79" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H79" s="17">
         <v>12</v>
       </c>
-      <c r="I79" s="19">
-        <v>0</v>
-      </c>
-      <c r="J79" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K79" s="19">
-        <v>0</v>
-      </c>
-      <c r="L79" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M79" s="19">
+      <c r="I79" s="17">
+        <v>0</v>
+      </c>
+      <c r="J79" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K79" s="17">
+        <v>0</v>
+      </c>
+      <c r="L79" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M79" s="17">
         <v>0</v>
       </c>
       <c r="N79" s="20">
@@ -5478,10 +5487,10 @@
     </row>
     <row r="80" s="1" customFormat="1" spans="1:19">
       <c r="A80" s="1">
-        <v>20050010</v>
+        <v>20010110</v>
       </c>
       <c r="B80" s="16">
-        <v>200500</v>
+        <v>200101</v>
       </c>
       <c r="C80" s="16">
         <v>2</v>
@@ -5490,30 +5499,30 @@
         <v>61</v>
       </c>
       <c r="E80" s="16">
-        <v>200500025</v>
+        <v>200101001</v>
       </c>
       <c r="F80" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="G80" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H80" s="19">
+      <c r="G80" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H80" s="17">
         <v>10</v>
       </c>
-      <c r="I80" s="19">
-        <v>0</v>
-      </c>
-      <c r="J80" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K80" s="19">
-        <v>0</v>
-      </c>
-      <c r="L80" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M80" s="19">
+      <c r="I80" s="17">
+        <v>0</v>
+      </c>
+      <c r="J80" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K80" s="17">
+        <v>0</v>
+      </c>
+      <c r="L80" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M80" s="17">
         <v>0</v>
       </c>
       <c r="N80" s="20">
@@ -5526,10 +5535,10 @@
     </row>
     <row r="81" s="1" customFormat="1" spans="1:19">
       <c r="A81" s="1">
-        <v>20050011</v>
+        <v>20010111</v>
       </c>
       <c r="B81" s="16">
-        <v>200500</v>
+        <v>200101</v>
       </c>
       <c r="C81" s="16">
         <v>2</v>
@@ -5538,30 +5547,30 @@
         <v>61</v>
       </c>
       <c r="E81" s="16">
-        <v>200500025</v>
+        <v>200101001</v>
       </c>
       <c r="F81" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="G81" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="H81" s="19">
+      <c r="G81" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H81" s="17">
         <v>11</v>
       </c>
-      <c r="I81" s="19">
-        <v>0</v>
-      </c>
-      <c r="J81" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K81" s="19">
-        <v>0</v>
-      </c>
-      <c r="L81" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M81" s="19">
+      <c r="I81" s="17">
+        <v>0</v>
+      </c>
+      <c r="J81" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K81" s="17">
+        <v>0</v>
+      </c>
+      <c r="L81" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M81" s="17">
         <v>0</v>
       </c>
       <c r="N81" s="20">
@@ -5574,10 +5583,10 @@
     </row>
     <row r="82" s="1" customFormat="1" spans="1:19">
       <c r="A82" s="1">
-        <v>20050012</v>
+        <v>20010112</v>
       </c>
       <c r="B82" s="16">
-        <v>200500</v>
+        <v>200101</v>
       </c>
       <c r="C82" s="16">
         <v>2</v>
@@ -5586,30 +5595,30 @@
         <v>61</v>
       </c>
       <c r="E82" s="16">
-        <v>200500025</v>
+        <v>200101001</v>
       </c>
       <c r="F82" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="G82" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H82" s="19">
+      <c r="G82" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H82" s="17">
         <v>12</v>
       </c>
-      <c r="I82" s="19">
-        <v>0</v>
-      </c>
-      <c r="J82" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K82" s="19">
-        <v>0</v>
-      </c>
-      <c r="L82" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M82" s="19">
+      <c r="I82" s="17">
+        <v>0</v>
+      </c>
+      <c r="J82" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K82" s="17">
+        <v>0</v>
+      </c>
+      <c r="L82" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M82" s="17">
         <v>0</v>
       </c>
       <c r="N82" s="20">
@@ -5620,44 +5629,44 @@
       </c>
       <c r="S82" s="3"/>
     </row>
-    <row r="83" spans="1:19">
+    <row r="83" s="1" customFormat="1" spans="1:19">
       <c r="A83" s="1">
-        <v>20060010</v>
+        <v>20030010</v>
       </c>
       <c r="B83" s="16">
-        <v>200600</v>
+        <v>200300</v>
       </c>
       <c r="C83" s="16">
         <v>2</v>
       </c>
       <c r="D83" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E83" s="16">
+        <v>200300001</v>
+      </c>
+      <c r="F83" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="E83" s="16">
-        <v>200600001</v>
-      </c>
-      <c r="F83" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="G83" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H83" s="19">
+      <c r="G83" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H83" s="17">
         <v>10</v>
       </c>
-      <c r="I83" s="19">
-        <v>0</v>
-      </c>
-      <c r="J83" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K83" s="19">
-        <v>0</v>
-      </c>
-      <c r="L83" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M83" s="19">
+      <c r="I83" s="17">
+        <v>0</v>
+      </c>
+      <c r="J83" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K83" s="17">
+        <v>0</v>
+      </c>
+      <c r="L83" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M83" s="17">
         <v>0</v>
       </c>
       <c r="N83" s="20">
@@ -5666,45 +5675,46 @@
       <c r="O83" s="21">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="84" spans="1:19">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" s="1" customFormat="1" spans="1:19">
       <c r="A84" s="1">
-        <v>20060011</v>
+        <v>20030011</v>
       </c>
       <c r="B84" s="16">
-        <v>200600</v>
+        <v>200300</v>
       </c>
       <c r="C84" s="16">
         <v>2</v>
       </c>
       <c r="D84" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E84" s="16">
+        <v>200300001</v>
+      </c>
+      <c r="F84" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="E84" s="16">
-        <v>200600001</v>
-      </c>
-      <c r="F84" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="G84" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="H84" s="19">
+      <c r="G84" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H84" s="17">
         <v>11</v>
       </c>
-      <c r="I84" s="19">
-        <v>0</v>
-      </c>
-      <c r="J84" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K84" s="19">
-        <v>0</v>
-      </c>
-      <c r="L84" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M84" s="19">
+      <c r="I84" s="17">
+        <v>0</v>
+      </c>
+      <c r="J84" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K84" s="17">
+        <v>0</v>
+      </c>
+      <c r="L84" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M84" s="17">
         <v>0</v>
       </c>
       <c r="N84" s="20">
@@ -5713,45 +5723,46 @@
       <c r="O84" s="21">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="85" spans="1:19">
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" s="1" customFormat="1" spans="1:19">
       <c r="A85" s="1">
-        <v>20060012</v>
+        <v>20030012</v>
       </c>
       <c r="B85" s="16">
-        <v>200600</v>
+        <v>200300</v>
       </c>
       <c r="C85" s="16">
         <v>2</v>
       </c>
       <c r="D85" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E85" s="16">
+        <v>200300001</v>
+      </c>
+      <c r="F85" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="E85" s="16">
-        <v>200600001</v>
-      </c>
-      <c r="F85" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="G85" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H85" s="19">
+      <c r="G85" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H85" s="17">
         <v>12</v>
       </c>
-      <c r="I85" s="19">
-        <v>0</v>
-      </c>
-      <c r="J85" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K85" s="19">
-        <v>0</v>
-      </c>
-      <c r="L85" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M85" s="19">
+      <c r="I85" s="17">
+        <v>0</v>
+      </c>
+      <c r="J85" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K85" s="17">
+        <v>0</v>
+      </c>
+      <c r="L85" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M85" s="17">
         <v>0</v>
       </c>
       <c r="N85" s="20">
@@ -5760,45 +5771,46 @@
       <c r="O85" s="21">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="86" spans="1:19">
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" s="1" customFormat="1" spans="1:19">
       <c r="A86" s="1">
-        <v>20070010</v>
+        <v>20040010</v>
       </c>
       <c r="B86" s="16">
-        <v>200700</v>
+        <v>200400</v>
       </c>
       <c r="C86" s="16">
         <v>2</v>
       </c>
-      <c r="D86" s="16" t="s">
+      <c r="D86" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="E86" s="16">
+        <v>200400009</v>
+      </c>
+      <c r="F86" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="E86" s="16">
-        <v>200700001</v>
-      </c>
-      <c r="F86" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="G86" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H86" s="19">
+      <c r="G86" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H86" s="17">
         <v>10</v>
       </c>
-      <c r="I86" s="19">
-        <v>0</v>
-      </c>
-      <c r="J86" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K86" s="19">
-        <v>0</v>
-      </c>
-      <c r="L86" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M86" s="19">
+      <c r="I86" s="17">
+        <v>0</v>
+      </c>
+      <c r="J86" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K86" s="17">
+        <v>0</v>
+      </c>
+      <c r="L86" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M86" s="17">
         <v>0</v>
       </c>
       <c r="N86" s="20">
@@ -5807,46 +5819,46 @@
       <c r="O86" s="21">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="87" spans="1:19">
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" s="1" customFormat="1" spans="1:19">
       <c r="A87" s="1">
-        <v>20070011</v>
+        <v>20040011</v>
       </c>
       <c r="B87" s="16">
-        <v>200700</v>
+        <v>200400</v>
       </c>
       <c r="C87" s="16">
         <v>2</v>
       </c>
-      <c r="D87" s="16" t="str">
-        <f>D86</f>
-        <v>越南色碟</v>
+      <c r="D87" s="22" t="s">
+        <v>65</v>
       </c>
       <c r="E87" s="16">
-        <v>200700001</v>
+        <v>200400009</v>
       </c>
       <c r="F87" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="G87" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="H87" s="19">
+        <v>66</v>
+      </c>
+      <c r="G87" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H87" s="17">
         <v>11</v>
       </c>
-      <c r="I87" s="19">
-        <v>0</v>
-      </c>
-      <c r="J87" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K87" s="19">
-        <v>0</v>
-      </c>
-      <c r="L87" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M87" s="19">
+      <c r="I87" s="17">
+        <v>0</v>
+      </c>
+      <c r="J87" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K87" s="17">
+        <v>0</v>
+      </c>
+      <c r="L87" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M87" s="17">
         <v>0</v>
       </c>
       <c r="N87" s="20">
@@ -5855,46 +5867,46 @@
       <c r="O87" s="21">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="88" spans="1:19">
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" s="1" customFormat="1" spans="1:19">
       <c r="A88" s="1">
-        <v>20070012</v>
+        <v>20040012</v>
       </c>
       <c r="B88" s="16">
-        <v>200700</v>
+        <v>200400</v>
       </c>
       <c r="C88" s="16">
         <v>2</v>
       </c>
-      <c r="D88" s="16" t="str">
-        <f>D87</f>
-        <v>越南色碟</v>
+      <c r="D88" s="22" t="s">
+        <v>65</v>
       </c>
       <c r="E88" s="16">
-        <v>200700001</v>
+        <v>200400009</v>
       </c>
       <c r="F88" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="G88" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H88" s="19">
+        <v>66</v>
+      </c>
+      <c r="G88" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H88" s="17">
         <v>12</v>
       </c>
-      <c r="I88" s="19">
-        <v>0</v>
-      </c>
-      <c r="J88" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K88" s="19">
-        <v>0</v>
-      </c>
-      <c r="L88" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M88" s="19">
+      <c r="I88" s="17">
+        <v>0</v>
+      </c>
+      <c r="J88" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K88" s="17">
+        <v>0</v>
+      </c>
+      <c r="L88" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M88" s="17">
         <v>0</v>
       </c>
       <c r="N88" s="20">
@@ -5903,45 +5915,46 @@
       <c r="O88" s="21">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="89" spans="1:19">
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" s="1" customFormat="1" spans="1:19">
       <c r="A89" s="1">
-        <v>20080010</v>
+        <v>20050010</v>
       </c>
       <c r="B89" s="16">
-        <v>200800</v>
+        <v>200500</v>
       </c>
       <c r="C89" s="16">
         <v>2</v>
       </c>
       <c r="D89" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E89" s="16">
+        <v>200500025</v>
+      </c>
+      <c r="F89" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="E89" s="16">
-        <v>200800001</v>
-      </c>
-      <c r="F89" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="G89" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H89" s="19">
+      <c r="G89" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H89" s="17">
         <v>10</v>
       </c>
-      <c r="I89" s="19">
-        <v>0</v>
-      </c>
-      <c r="J89" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K89" s="19">
-        <v>0</v>
-      </c>
-      <c r="L89" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M89" s="19">
+      <c r="I89" s="17">
+        <v>0</v>
+      </c>
+      <c r="J89" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K89" s="17">
+        <v>0</v>
+      </c>
+      <c r="L89" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M89" s="17">
         <v>0</v>
       </c>
       <c r="N89" s="20">
@@ -5950,45 +5963,46 @@
       <c r="O89" s="21">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="90" spans="1:19">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" s="1" customFormat="1" spans="1:19">
       <c r="A90" s="1">
-        <v>20080011</v>
+        <v>20050011</v>
       </c>
       <c r="B90" s="16">
-        <v>200800</v>
+        <v>200500</v>
       </c>
       <c r="C90" s="16">
         <v>2</v>
       </c>
       <c r="D90" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E90" s="16">
+        <v>200500025</v>
+      </c>
+      <c r="F90" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="E90" s="16">
-        <v>200800001</v>
-      </c>
-      <c r="F90" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="G90" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="H90" s="19">
+      <c r="G90" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H90" s="17">
         <v>11</v>
       </c>
-      <c r="I90" s="19">
-        <v>0</v>
-      </c>
-      <c r="J90" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K90" s="19">
-        <v>0</v>
-      </c>
-      <c r="L90" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M90" s="19">
+      <c r="I90" s="17">
+        <v>0</v>
+      </c>
+      <c r="J90" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K90" s="17">
+        <v>0</v>
+      </c>
+      <c r="L90" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M90" s="17">
         <v>0</v>
       </c>
       <c r="N90" s="20">
@@ -5997,45 +6011,46 @@
       <c r="O90" s="21">
         <v>1980000</v>
       </c>
-    </row>
-    <row r="91" spans="1:19">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" s="1" customFormat="1" spans="1:19">
       <c r="A91" s="1">
-        <v>20080012</v>
+        <v>20050012</v>
       </c>
       <c r="B91" s="16">
-        <v>200800</v>
+        <v>200500</v>
       </c>
       <c r="C91" s="16">
         <v>2</v>
       </c>
       <c r="D91" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E91" s="16">
+        <v>200500025</v>
+      </c>
+      <c r="F91" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="E91" s="16">
-        <v>200800001</v>
-      </c>
-      <c r="F91" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="G91" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H91" s="19">
+      <c r="G91" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H91" s="17">
         <v>12</v>
       </c>
-      <c r="I91" s="19">
-        <v>0</v>
-      </c>
-      <c r="J91" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K91" s="19">
-        <v>0</v>
-      </c>
-      <c r="L91" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M91" s="19">
+      <c r="I91" s="17">
+        <v>0</v>
+      </c>
+      <c r="J91" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K91" s="17">
+        <v>0</v>
+      </c>
+      <c r="L91" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M91" s="17">
         <v>0</v>
       </c>
       <c r="N91" s="20">
@@ -6044,13 +6059,14 @@
       <c r="O91" s="21">
         <v>1980000</v>
       </c>
+      <c r="S91" s="3"/>
     </row>
     <row r="92" spans="1:19">
       <c r="A92" s="1">
-        <v>20090010</v>
+        <v>20060010</v>
       </c>
       <c r="B92" s="16">
-        <v>200900</v>
+        <v>200600</v>
       </c>
       <c r="C92" s="16">
         <v>2</v>
@@ -6059,30 +6075,30 @@
         <v>70</v>
       </c>
       <c r="E92" s="16">
-        <v>200900001</v>
+        <v>200600001</v>
       </c>
       <c r="F92" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="G92" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H92" s="19">
+      <c r="G92" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H92" s="17">
         <v>10</v>
       </c>
-      <c r="I92" s="19">
-        <v>0</v>
-      </c>
-      <c r="J92" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K92" s="19">
-        <v>0</v>
-      </c>
-      <c r="L92" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M92" s="19">
+      <c r="I92" s="17">
+        <v>0</v>
+      </c>
+      <c r="J92" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K92" s="17">
+        <v>0</v>
+      </c>
+      <c r="L92" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M92" s="17">
         <v>0</v>
       </c>
       <c r="N92" s="20">
@@ -6094,10 +6110,10 @@
     </row>
     <row r="93" spans="1:19">
       <c r="A93" s="1">
-        <v>20090011</v>
+        <v>20060011</v>
       </c>
       <c r="B93" s="16">
-        <v>200900</v>
+        <v>200600</v>
       </c>
       <c r="C93" s="16">
         <v>2</v>
@@ -6106,30 +6122,30 @@
         <v>70</v>
       </c>
       <c r="E93" s="16">
-        <v>200900001</v>
+        <v>200600001</v>
       </c>
       <c r="F93" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="G93" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="H93" s="19">
+      <c r="G93" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H93" s="17">
         <v>11</v>
       </c>
-      <c r="I93" s="19">
-        <v>0</v>
-      </c>
-      <c r="J93" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K93" s="19">
-        <v>0</v>
-      </c>
-      <c r="L93" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M93" s="19">
+      <c r="I93" s="17">
+        <v>0</v>
+      </c>
+      <c r="J93" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K93" s="17">
+        <v>0</v>
+      </c>
+      <c r="L93" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M93" s="17">
         <v>0</v>
       </c>
       <c r="N93" s="20">
@@ -6141,10 +6157,10 @@
     </row>
     <row r="94" spans="1:19">
       <c r="A94" s="1">
-        <v>20090012</v>
+        <v>20060012</v>
       </c>
       <c r="B94" s="16">
-        <v>200900</v>
+        <v>200600</v>
       </c>
       <c r="C94" s="16">
         <v>2</v>
@@ -6153,30 +6169,30 @@
         <v>70</v>
       </c>
       <c r="E94" s="16">
-        <v>200900001</v>
+        <v>200600001</v>
       </c>
       <c r="F94" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="G94" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H94" s="19">
+      <c r="G94" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H94" s="17">
         <v>12</v>
       </c>
-      <c r="I94" s="19">
-        <v>0</v>
-      </c>
-      <c r="J94" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K94" s="19">
-        <v>0</v>
-      </c>
-      <c r="L94" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M94" s="19">
+      <c r="I94" s="17">
+        <v>0</v>
+      </c>
+      <c r="J94" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K94" s="17">
+        <v>0</v>
+      </c>
+      <c r="L94" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M94" s="17">
         <v>0</v>
       </c>
       <c r="N94" s="20">
@@ -6186,44 +6202,44 @@
         <v>1980000</v>
       </c>
     </row>
-    <row r="95" s="1" customFormat="1" spans="1:19">
+    <row r="95" spans="1:19">
       <c r="A95" s="1">
-        <v>30020010</v>
+        <v>20070010</v>
       </c>
       <c r="B95" s="16">
-        <v>300200</v>
+        <v>200700</v>
       </c>
       <c r="C95" s="16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D95" s="16" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E95" s="16">
-        <v>300200006</v>
+        <v>200700001</v>
       </c>
       <c r="F95" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="G95" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H95" s="19">
+        <v>73</v>
+      </c>
+      <c r="G95" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H95" s="17">
         <v>10</v>
       </c>
-      <c r="I95" s="19">
-        <v>0</v>
-      </c>
-      <c r="J95" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K95" s="19">
-        <v>0</v>
-      </c>
-      <c r="L95" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="M95" s="19">
+      <c r="I95" s="17">
+        <v>0</v>
+      </c>
+      <c r="J95" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K95" s="17">
+        <v>0</v>
+      </c>
+      <c r="L95" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M95" s="17">
         <v>0</v>
       </c>
       <c r="N95" s="20">
@@ -6232,46 +6248,46 @@
       <c r="O95" s="21">
         <v>1980000</v>
       </c>
-      <c r="S95" s="3"/>
-    </row>
-    <row r="96" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="96" spans="1:19">
       <c r="A96" s="1">
-        <v>30020011</v>
+        <v>20070011</v>
       </c>
       <c r="B96" s="16">
-        <v>300200</v>
+        <v>200700</v>
       </c>
       <c r="C96" s="16">
-        <v>3</v>
-      </c>
-      <c r="D96" s="16" t="s">
-        <v>77</v>
+        <v>2</v>
+      </c>
+      <c r="D96" s="16" t="str">
+        <f>D95</f>
+        <v>越南色碟</v>
       </c>
       <c r="E96" s="16">
-        <v>300200006</v>
+        <v>200700001</v>
       </c>
       <c r="F96" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="G96" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="H96" s="19">
+        <v>73</v>
+      </c>
+      <c r="G96" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H96" s="17">
         <v>11</v>
       </c>
-      <c r="I96" s="19">
-        <v>0</v>
-      </c>
-      <c r="J96" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K96" s="19">
-        <v>0</v>
-      </c>
-      <c r="L96" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="M96" s="19">
+      <c r="I96" s="17">
+        <v>0</v>
+      </c>
+      <c r="J96" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K96" s="17">
+        <v>0</v>
+      </c>
+      <c r="L96" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M96" s="17">
         <v>0</v>
       </c>
       <c r="N96" s="20">
@@ -6280,46 +6296,46 @@
       <c r="O96" s="21">
         <v>1980000</v>
       </c>
-      <c r="S96" s="3"/>
-    </row>
-    <row r="97" s="1" customFormat="1" spans="1:19">
+    </row>
+    <row r="97" spans="1:19">
       <c r="A97" s="1">
-        <v>30020012</v>
+        <v>20070012</v>
       </c>
       <c r="B97" s="16">
-        <v>300200</v>
+        <v>200700</v>
       </c>
       <c r="C97" s="16">
-        <v>3</v>
-      </c>
-      <c r="D97" s="16" t="s">
-        <v>77</v>
+        <v>2</v>
+      </c>
+      <c r="D97" s="16" t="str">
+        <f>D96</f>
+        <v>越南色碟</v>
       </c>
       <c r="E97" s="16">
-        <v>300200006</v>
+        <v>200700001</v>
       </c>
       <c r="F97" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="G97" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H97" s="19">
+        <v>73</v>
+      </c>
+      <c r="G97" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H97" s="17">
         <v>12</v>
       </c>
-      <c r="I97" s="19">
-        <v>0</v>
-      </c>
-      <c r="J97" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K97" s="19">
-        <v>0</v>
-      </c>
-      <c r="L97" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="M97" s="19">
+      <c r="I97" s="17">
+        <v>0</v>
+      </c>
+      <c r="J97" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K97" s="17">
+        <v>0</v>
+      </c>
+      <c r="L97" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M97" s="17">
         <v>0</v>
       </c>
       <c r="N97" s="20">
@@ -6328,1294 +6344,2142 @@
       <c r="O97" s="21">
         <v>1980000</v>
       </c>
-      <c r="S97" s="3"/>
     </row>
     <row r="98" spans="1:19">
-      <c r="A98" s="1" t="s">
-        <v>85</v>
+      <c r="A98" s="1">
+        <v>20080010</v>
       </c>
       <c r="B98" s="16">
-        <v>100100</v>
+        <v>200800</v>
       </c>
       <c r="C98" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D98" s="16" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="E98" s="16">
-        <v>100100026</v>
+        <v>200800001</v>
       </c>
       <c r="F98" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="G98" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H98" s="19">
+        <v>75</v>
+      </c>
+      <c r="G98" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H98" s="17">
         <v>10</v>
       </c>
-      <c r="I98" s="19">
-        <v>0</v>
-      </c>
-      <c r="J98" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K98" s="19">
-        <v>0</v>
-      </c>
-      <c r="L98" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M98" s="19">
+      <c r="I98" s="17">
+        <v>0</v>
+      </c>
+      <c r="J98" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K98" s="17">
+        <v>0</v>
+      </c>
+      <c r="L98" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M98" s="17">
         <v>0</v>
       </c>
       <c r="N98" s="20">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="O98" s="21">
         <v>1980000</v>
       </c>
     </row>
     <row r="99" spans="1:19">
-      <c r="A99" s="1" t="s">
-        <v>86</v>
+      <c r="A99" s="1">
+        <v>20080011</v>
       </c>
       <c r="B99" s="16">
-        <v>100100</v>
+        <v>200800</v>
       </c>
       <c r="C99" s="16">
-        <v>1</v>
-      </c>
-      <c r="D99" s="16" t="str">
-        <f t="shared" ref="D99:D103" si="8">D98</f>
-        <v>金礦大亨</v>
+        <v>2</v>
+      </c>
+      <c r="D99" s="16" t="s">
+        <v>74</v>
       </c>
       <c r="E99" s="16">
-        <v>100100026</v>
+        <v>200800001</v>
       </c>
       <c r="F99" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="G99" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="H99" s="19">
+        <v>75</v>
+      </c>
+      <c r="G99" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H99" s="17">
         <v>11</v>
       </c>
-      <c r="I99" s="19">
-        <v>0</v>
-      </c>
-      <c r="J99" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K99" s="19">
-        <v>0</v>
-      </c>
-      <c r="L99" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M99" s="19">
+      <c r="I99" s="17">
+        <v>0</v>
+      </c>
+      <c r="J99" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K99" s="17">
+        <v>0</v>
+      </c>
+      <c r="L99" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M99" s="17">
         <v>0</v>
       </c>
       <c r="N99" s="20">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="O99" s="21">
         <v>1980000</v>
       </c>
     </row>
     <row r="100" spans="1:19">
-      <c r="A100" s="1" t="s">
+      <c r="A100" s="1">
+        <v>20080012</v>
+      </c>
+      <c r="B100" s="16">
+        <v>200800</v>
+      </c>
+      <c r="C100" s="16">
+        <v>2</v>
+      </c>
+      <c r="D100" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="E100" s="16">
+        <v>200800001</v>
+      </c>
+      <c r="F100" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="G100" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H100" s="17">
+        <v>12</v>
+      </c>
+      <c r="I100" s="17">
+        <v>0</v>
+      </c>
+      <c r="J100" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K100" s="17">
+        <v>0</v>
+      </c>
+      <c r="L100" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="B100" s="16">
+      <c r="M100" s="17">
+        <v>0</v>
+      </c>
+      <c r="N100" s="20">
+        <v>100000</v>
+      </c>
+      <c r="O100" s="21">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19">
+      <c r="A101" s="1">
+        <v>20090010</v>
+      </c>
+      <c r="B101" s="16">
+        <v>200900</v>
+      </c>
+      <c r="C101" s="16">
+        <v>2</v>
+      </c>
+      <c r="D101" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="E101" s="16">
+        <v>200900001</v>
+      </c>
+      <c r="F101" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G101" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H101" s="17">
+        <v>10</v>
+      </c>
+      <c r="I101" s="17">
+        <v>0</v>
+      </c>
+      <c r="J101" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K101" s="17">
+        <v>0</v>
+      </c>
+      <c r="L101" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M101" s="17">
+        <v>0</v>
+      </c>
+      <c r="N101" s="20">
+        <v>200</v>
+      </c>
+      <c r="O101" s="21">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="102" spans="1:19">
+      <c r="A102" s="1">
+        <v>20090011</v>
+      </c>
+      <c r="B102" s="16">
+        <v>200900</v>
+      </c>
+      <c r="C102" s="16">
+        <v>2</v>
+      </c>
+      <c r="D102" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="E102" s="16">
+        <v>200900001</v>
+      </c>
+      <c r="F102" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G102" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H102" s="17">
+        <v>11</v>
+      </c>
+      <c r="I102" s="17">
+        <v>0</v>
+      </c>
+      <c r="J102" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K102" s="17">
+        <v>0</v>
+      </c>
+      <c r="L102" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M102" s="17">
+        <v>0</v>
+      </c>
+      <c r="N102" s="20">
+        <v>5000</v>
+      </c>
+      <c r="O102" s="21">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="103" spans="1:19">
+      <c r="A103" s="1">
+        <v>20090012</v>
+      </c>
+      <c r="B103" s="16">
+        <v>200900</v>
+      </c>
+      <c r="C103" s="16">
+        <v>2</v>
+      </c>
+      <c r="D103" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="E103" s="16">
+        <v>200900001</v>
+      </c>
+      <c r="F103" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G103" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H103" s="17">
+        <v>12</v>
+      </c>
+      <c r="I103" s="17">
+        <v>0</v>
+      </c>
+      <c r="J103" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K103" s="17">
+        <v>0</v>
+      </c>
+      <c r="L103" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M103" s="17">
+        <v>0</v>
+      </c>
+      <c r="N103" s="20">
+        <v>100000</v>
+      </c>
+      <c r="O103" s="21">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="104" s="1" customFormat="1" spans="1:19">
+      <c r="A104" s="1">
+        <v>30020010</v>
+      </c>
+      <c r="B104" s="16">
+        <v>300200</v>
+      </c>
+      <c r="C104" s="16">
+        <v>3</v>
+      </c>
+      <c r="D104" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E104" s="16">
+        <v>300200006</v>
+      </c>
+      <c r="F104" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="G104" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H104" s="17">
+        <v>10</v>
+      </c>
+      <c r="I104" s="17">
+        <v>0</v>
+      </c>
+      <c r="J104" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K104" s="17">
+        <v>0</v>
+      </c>
+      <c r="L104" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="M104" s="17">
+        <v>0</v>
+      </c>
+      <c r="N104" s="20">
+        <v>200</v>
+      </c>
+      <c r="O104" s="21">
+        <v>1980000</v>
+      </c>
+      <c r="S104" s="3"/>
+    </row>
+    <row r="105" s="1" customFormat="1" spans="1:19">
+      <c r="A105" s="1">
+        <v>30020011</v>
+      </c>
+      <c r="B105" s="16">
+        <v>300200</v>
+      </c>
+      <c r="C105" s="16">
+        <v>3</v>
+      </c>
+      <c r="D105" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E105" s="16">
+        <v>300200006</v>
+      </c>
+      <c r="F105" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="G105" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H105" s="17">
+        <v>11</v>
+      </c>
+      <c r="I105" s="17">
+        <v>0</v>
+      </c>
+      <c r="J105" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K105" s="17">
+        <v>0</v>
+      </c>
+      <c r="L105" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="M105" s="17">
+        <v>0</v>
+      </c>
+      <c r="N105" s="20">
+        <v>5000</v>
+      </c>
+      <c r="O105" s="21">
+        <v>1980000</v>
+      </c>
+      <c r="S105" s="3"/>
+    </row>
+    <row r="106" s="1" customFormat="1" spans="1:19">
+      <c r="A106" s="1">
+        <v>30020012</v>
+      </c>
+      <c r="B106" s="16">
+        <v>300200</v>
+      </c>
+      <c r="C106" s="16">
+        <v>3</v>
+      </c>
+      <c r="D106" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E106" s="16">
+        <v>300200006</v>
+      </c>
+      <c r="F106" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="G106" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H106" s="17">
+        <v>12</v>
+      </c>
+      <c r="I106" s="17">
+        <v>0</v>
+      </c>
+      <c r="J106" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K106" s="17">
+        <v>0</v>
+      </c>
+      <c r="L106" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="M106" s="17">
+        <v>0</v>
+      </c>
+      <c r="N106" s="20">
+        <v>100000</v>
+      </c>
+      <c r="O106" s="21">
+        <v>1980000</v>
+      </c>
+      <c r="S106" s="3"/>
+    </row>
+    <row r="107" spans="1:19">
+      <c r="A107" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B107" s="16">
         <v>100100</v>
       </c>
-      <c r="C100" s="16">
-        <v>1</v>
-      </c>
-      <c r="D100" s="16" t="str">
+      <c r="C107" s="16">
+        <v>1</v>
+      </c>
+      <c r="D107" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="E107" s="16">
+        <v>100100026</v>
+      </c>
+      <c r="F107" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="G107" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H107" s="17">
+        <v>10</v>
+      </c>
+      <c r="I107" s="17">
+        <v>0</v>
+      </c>
+      <c r="J107" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K107" s="17">
+        <v>0</v>
+      </c>
+      <c r="L107" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M107" s="17">
+        <v>0</v>
+      </c>
+      <c r="N107" s="20">
+        <v>50</v>
+      </c>
+      <c r="O107" s="21">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="108" spans="1:19">
+      <c r="A108" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B108" s="16">
+        <v>100100</v>
+      </c>
+      <c r="C108" s="16">
+        <v>1</v>
+      </c>
+      <c r="D108" s="16" t="str">
+        <f t="shared" ref="D108:D112" si="8">D107</f>
+        <v>金礦大亨</v>
+      </c>
+      <c r="E108" s="16">
+        <v>100100026</v>
+      </c>
+      <c r="F108" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="G108" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H108" s="17">
+        <v>11</v>
+      </c>
+      <c r="I108" s="17">
+        <v>0</v>
+      </c>
+      <c r="J108" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K108" s="17">
+        <v>0</v>
+      </c>
+      <c r="L108" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M108" s="17">
+        <v>0</v>
+      </c>
+      <c r="N108" s="20">
+        <v>500</v>
+      </c>
+      <c r="O108" s="21">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="109" spans="1:19">
+      <c r="A109" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B109" s="16">
+        <v>100100</v>
+      </c>
+      <c r="C109" s="16">
+        <v>1</v>
+      </c>
+      <c r="D109" s="16" t="str">
         <f t="shared" si="8"/>
         <v>金礦大亨</v>
       </c>
-      <c r="E100" s="16">
+      <c r="E109" s="16">
         <v>100100026</v>
       </c>
-      <c r="F100" s="16" t="s">
+      <c r="F109" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="G100" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H100" s="19">
+      <c r="G109" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H109" s="17">
         <v>12</v>
       </c>
-      <c r="I100" s="19">
-        <v>0</v>
-      </c>
-      <c r="J100" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K100" s="19">
-        <v>0</v>
-      </c>
-      <c r="L100" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M100" s="19">
-        <v>0</v>
-      </c>
-      <c r="N100" s="20">
+      <c r="I109" s="17">
+        <v>0</v>
+      </c>
+      <c r="J109" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K109" s="17">
+        <v>0</v>
+      </c>
+      <c r="L109" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M109" s="17">
+        <v>0</v>
+      </c>
+      <c r="N109" s="20">
         <v>5000</v>
       </c>
-      <c r="O100" s="21">
+      <c r="O109" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="101" spans="1:19">
-      <c r="A101" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B101" s="16">
+    <row r="110" spans="1:19">
+      <c r="A110" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B110" s="16">
         <v>100300</v>
       </c>
-      <c r="C101" s="16">
-        <v>1</v>
-      </c>
-      <c r="D101" s="16" t="s">
+      <c r="C110" s="16">
+        <v>1</v>
+      </c>
+      <c r="D110" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="E101" s="16">
+      <c r="E110" s="16">
         <v>100300001</v>
       </c>
-      <c r="F101" s="16" t="s">
+      <c r="F110" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="G101" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H101" s="19">
+      <c r="G110" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H110" s="17">
         <v>10</v>
       </c>
-      <c r="I101" s="19">
-        <v>0</v>
-      </c>
-      <c r="J101" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K101" s="19">
-        <v>0</v>
-      </c>
-      <c r="L101" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M101" s="19">
-        <v>0</v>
-      </c>
-      <c r="N101" s="20">
+      <c r="I110" s="17">
+        <v>0</v>
+      </c>
+      <c r="J110" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K110" s="17">
+        <v>0</v>
+      </c>
+      <c r="L110" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M110" s="17">
+        <v>0</v>
+      </c>
+      <c r="N110" s="20">
         <v>50</v>
       </c>
-      <c r="O101" s="21">
+      <c r="O110" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="102" spans="1:19">
-      <c r="A102" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B102" s="16">
+    <row r="111" spans="1:19">
+      <c r="A111" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B111" s="16">
         <v>100300</v>
       </c>
-      <c r="C102" s="16">
-        <v>1</v>
-      </c>
-      <c r="D102" s="16" t="str">
+      <c r="C111" s="16">
+        <v>1</v>
+      </c>
+      <c r="D111" s="16" t="str">
         <f t="shared" si="8"/>
         <v>超级明星</v>
       </c>
-      <c r="E102" s="16">
+      <c r="E111" s="16">
         <v>100300001</v>
       </c>
-      <c r="F102" s="16" t="str">
-        <f t="shared" ref="F102:F106" si="9">F101</f>
+      <c r="F111" s="16" t="str">
+        <f t="shared" ref="F111:F115" si="9">F110</f>
         <v>SuperStar</v>
       </c>
-      <c r="G102" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="H102" s="19">
+      <c r="G111" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H111" s="17">
         <v>11</v>
       </c>
-      <c r="I102" s="19">
-        <v>0</v>
-      </c>
-      <c r="J102" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K102" s="19">
-        <v>0</v>
-      </c>
-      <c r="L102" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M102" s="19">
-        <v>0</v>
-      </c>
-      <c r="N102" s="20">
+      <c r="I111" s="17">
+        <v>0</v>
+      </c>
+      <c r="J111" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K111" s="17">
+        <v>0</v>
+      </c>
+      <c r="L111" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M111" s="17">
+        <v>0</v>
+      </c>
+      <c r="N111" s="20">
         <v>500</v>
       </c>
-      <c r="O102" s="21">
+      <c r="O111" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="103" spans="1:19">
-      <c r="A103" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B103" s="16">
+    <row r="112" spans="1:19">
+      <c r="A112" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B112" s="16">
         <v>100300</v>
       </c>
-      <c r="C103" s="16">
-        <v>1</v>
-      </c>
-      <c r="D103" s="16" t="str">
+      <c r="C112" s="16">
+        <v>1</v>
+      </c>
+      <c r="D112" s="16" t="str">
         <f t="shared" si="8"/>
         <v>超级明星</v>
       </c>
-      <c r="E103" s="16">
+      <c r="E112" s="16">
         <v>100300001</v>
       </c>
-      <c r="F103" s="16" t="str">
+      <c r="F112" s="16" t="str">
         <f t="shared" si="9"/>
         <v>SuperStar</v>
       </c>
-      <c r="G103" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H103" s="19">
+      <c r="G112" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H112" s="17">
         <v>12</v>
       </c>
-      <c r="I103" s="19">
-        <v>0</v>
-      </c>
-      <c r="J103" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K103" s="19">
-        <v>0</v>
-      </c>
-      <c r="L103" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M103" s="19">
-        <v>0</v>
-      </c>
-      <c r="N103" s="20">
+      <c r="I112" s="17">
+        <v>0</v>
+      </c>
+      <c r="J112" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K112" s="17">
+        <v>0</v>
+      </c>
+      <c r="L112" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M112" s="17">
+        <v>0</v>
+      </c>
+      <c r="N112" s="20">
         <v>5000</v>
       </c>
-      <c r="O103" s="21">
+      <c r="O112" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="104" spans="1:19">
-      <c r="A104" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B104" s="16">
+    <row r="113" spans="1:15">
+      <c r="A113" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B113" s="16">
         <v>100700</v>
       </c>
-      <c r="C104" s="16">
-        <v>1</v>
-      </c>
-      <c r="D104" s="16" t="s">
+      <c r="C113" s="16">
+        <v>1</v>
+      </c>
+      <c r="D113" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E104" s="16">
+      <c r="E113" s="16">
         <v>100700001</v>
       </c>
-      <c r="F104" s="16" t="s">
+      <c r="F113" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="G104" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H104" s="19">
+      <c r="G113" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H113" s="17">
         <v>10</v>
       </c>
-      <c r="I104" s="19">
-        <v>0</v>
-      </c>
-      <c r="J104" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K104" s="19">
-        <v>0</v>
-      </c>
-      <c r="L104" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M104" s="19">
-        <v>0</v>
-      </c>
-      <c r="N104" s="20">
+      <c r="I113" s="17">
+        <v>0</v>
+      </c>
+      <c r="J113" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K113" s="17">
+        <v>0</v>
+      </c>
+      <c r="L113" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M113" s="17">
+        <v>0</v>
+      </c>
+      <c r="N113" s="20">
         <v>50</v>
       </c>
-      <c r="O104" s="21">
+      <c r="O113" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="105" spans="1:19">
-      <c r="A105" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B105" s="16">
+    <row r="114" spans="1:15">
+      <c r="A114" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B114" s="16">
         <v>100700</v>
       </c>
-      <c r="C105" s="16">
-        <v>1</v>
-      </c>
-      <c r="D105" s="16" t="str">
-        <f t="shared" ref="D105:D109" si="10">D104</f>
+      <c r="C114" s="16">
+        <v>1</v>
+      </c>
+      <c r="D114" s="16" t="str">
+        <f t="shared" ref="D114:D118" si="10">D113</f>
         <v>麻将胡了</v>
       </c>
-      <c r="E105" s="16">
+      <c r="E114" s="16">
         <v>100700001</v>
       </c>
-      <c r="F105" s="16" t="str">
+      <c r="F114" s="16" t="str">
         <f t="shared" si="9"/>
         <v>MahjongWays</v>
       </c>
-      <c r="G105" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="H105" s="19">
+      <c r="G114" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H114" s="17">
         <v>11</v>
       </c>
-      <c r="I105" s="19">
-        <v>0</v>
-      </c>
-      <c r="J105" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K105" s="19">
-        <v>0</v>
-      </c>
-      <c r="L105" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M105" s="19">
-        <v>0</v>
-      </c>
-      <c r="N105" s="20">
+      <c r="I114" s="17">
+        <v>0</v>
+      </c>
+      <c r="J114" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K114" s="17">
+        <v>0</v>
+      </c>
+      <c r="L114" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M114" s="17">
+        <v>0</v>
+      </c>
+      <c r="N114" s="20">
         <v>500</v>
       </c>
-      <c r="O105" s="21">
+      <c r="O114" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="106" spans="1:19">
-      <c r="A106" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B106" s="16">
+    <row r="115" spans="1:15">
+      <c r="A115" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B115" s="16">
         <v>100700</v>
       </c>
-      <c r="C106" s="16">
-        <v>1</v>
-      </c>
-      <c r="D106" s="16" t="str">
+      <c r="C115" s="16">
+        <v>1</v>
+      </c>
+      <c r="D115" s="16" t="str">
         <f t="shared" si="10"/>
         <v>麻将胡了</v>
       </c>
-      <c r="E106" s="16">
+      <c r="E115" s="16">
         <v>100700001</v>
       </c>
-      <c r="F106" s="16" t="str">
+      <c r="F115" s="16" t="str">
         <f t="shared" si="9"/>
         <v>MahjongWays</v>
       </c>
-      <c r="G106" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H106" s="19">
+      <c r="G115" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H115" s="17">
         <v>12</v>
       </c>
-      <c r="I106" s="19">
-        <v>0</v>
-      </c>
-      <c r="J106" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K106" s="19">
-        <v>0</v>
-      </c>
-      <c r="L106" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M106" s="19">
-        <v>0</v>
-      </c>
-      <c r="N106" s="20">
+      <c r="I115" s="17">
+        <v>0</v>
+      </c>
+      <c r="J115" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K115" s="17">
+        <v>0</v>
+      </c>
+      <c r="L115" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M115" s="17">
+        <v>0</v>
+      </c>
+      <c r="N115" s="20">
         <v>5000</v>
       </c>
-      <c r="O106" s="21">
+      <c r="O115" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="107" spans="1:19">
-      <c r="A107" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B107" s="16">
+    <row r="116" spans="1:15">
+      <c r="A116" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B116" s="16">
         <v>101200</v>
       </c>
-      <c r="C107" s="16">
-        <v>1</v>
-      </c>
-      <c r="D107" s="16" t="s">
+      <c r="C116" s="16">
+        <v>1</v>
+      </c>
+      <c r="D116" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="E107" s="16">
+      <c r="E116" s="16">
         <v>101200001</v>
       </c>
-      <c r="F107" s="16" t="s">
+      <c r="F116" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="G107" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H107" s="19">
+      <c r="G116" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H116" s="17">
         <v>10</v>
       </c>
-      <c r="I107" s="19">
-        <v>0</v>
-      </c>
-      <c r="J107" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K107" s="19">
-        <v>0</v>
-      </c>
-      <c r="L107" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M107" s="19">
-        <v>0</v>
-      </c>
-      <c r="N107" s="20">
+      <c r="I116" s="17">
+        <v>0</v>
+      </c>
+      <c r="J116" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K116" s="17">
+        <v>0</v>
+      </c>
+      <c r="L116" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M116" s="17">
+        <v>0</v>
+      </c>
+      <c r="N116" s="20">
         <v>50</v>
       </c>
-      <c r="O107" s="21">
+      <c r="O116" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="108" spans="1:19">
-      <c r="A108" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B108" s="16">
+    <row r="117" spans="1:15">
+      <c r="A117" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B117" s="16">
         <v>101200</v>
       </c>
-      <c r="C108" s="16">
-        <v>1</v>
-      </c>
-      <c r="D108" s="16" t="str">
+      <c r="C117" s="16">
+        <v>1</v>
+      </c>
+      <c r="D117" s="16" t="str">
         <f t="shared" si="10"/>
         <v>财神</v>
       </c>
-      <c r="E108" s="16">
+      <c r="E117" s="16">
         <v>101200001</v>
       </c>
-      <c r="F108" s="16" t="str">
-        <f t="shared" ref="F108:F112" si="11">F107</f>
+      <c r="F117" s="16" t="str">
+        <f t="shared" ref="F117:F121" si="11">F116</f>
         <v>Godofwealth</v>
       </c>
-      <c r="G108" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="H108" s="19">
+      <c r="G117" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H117" s="17">
         <v>11</v>
       </c>
-      <c r="I108" s="19">
-        <v>0</v>
-      </c>
-      <c r="J108" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K108" s="19">
-        <v>0</v>
-      </c>
-      <c r="L108" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M108" s="19">
-        <v>0</v>
-      </c>
-      <c r="N108" s="20">
+      <c r="I117" s="17">
+        <v>0</v>
+      </c>
+      <c r="J117" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K117" s="17">
+        <v>0</v>
+      </c>
+      <c r="L117" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M117" s="17">
+        <v>0</v>
+      </c>
+      <c r="N117" s="20">
         <v>500</v>
       </c>
-      <c r="O108" s="21">
+      <c r="O117" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="109" spans="1:19">
-      <c r="A109" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B109" s="16">
+    <row r="118" spans="1:15">
+      <c r="A118" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B118" s="16">
         <v>101200</v>
       </c>
-      <c r="C109" s="16">
-        <v>1</v>
-      </c>
-      <c r="D109" s="16" t="str">
+      <c r="C118" s="16">
+        <v>1</v>
+      </c>
+      <c r="D118" s="16" t="str">
         <f t="shared" si="10"/>
         <v>财神</v>
       </c>
-      <c r="E109" s="16">
+      <c r="E118" s="16">
         <v>101200001</v>
       </c>
-      <c r="F109" s="16" t="str">
+      <c r="F118" s="16" t="str">
         <f t="shared" si="11"/>
         <v>Godofwealth</v>
       </c>
-      <c r="G109" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H109" s="19">
+      <c r="G118" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H118" s="17">
         <v>12</v>
       </c>
-      <c r="I109" s="19">
-        <v>0</v>
-      </c>
-      <c r="J109" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K109" s="19">
-        <v>0</v>
-      </c>
-      <c r="L109" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M109" s="19">
-        <v>0</v>
-      </c>
-      <c r="N109" s="20">
+      <c r="I118" s="17">
+        <v>0</v>
+      </c>
+      <c r="J118" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K118" s="17">
+        <v>0</v>
+      </c>
+      <c r="L118" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M118" s="17">
+        <v>0</v>
+      </c>
+      <c r="N118" s="20">
         <v>5000</v>
       </c>
-      <c r="O109" s="21">
+      <c r="O118" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="110" spans="1:19">
-      <c r="A110" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B110" s="16">
+    <row r="119" spans="1:15">
+      <c r="A119" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B119" s="16">
         <v>101400</v>
       </c>
-      <c r="C110" s="16">
-        <v>1</v>
-      </c>
-      <c r="D110" s="16" t="s">
+      <c r="C119" s="16">
+        <v>1</v>
+      </c>
+      <c r="D119" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="E110" s="16">
+      <c r="E119" s="16">
         <v>101400001</v>
       </c>
-      <c r="F110" s="16" t="s">
+      <c r="F119" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="G110" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H110" s="19">
+      <c r="G119" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H119" s="17">
         <v>10</v>
       </c>
-      <c r="I110" s="19">
-        <v>0</v>
-      </c>
-      <c r="J110" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K110" s="19">
-        <v>0</v>
-      </c>
-      <c r="L110" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M110" s="19">
-        <v>0</v>
-      </c>
-      <c r="N110" s="20">
+      <c r="I119" s="17">
+        <v>0</v>
+      </c>
+      <c r="J119" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K119" s="17">
+        <v>0</v>
+      </c>
+      <c r="L119" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M119" s="17">
+        <v>0</v>
+      </c>
+      <c r="N119" s="20">
         <v>50</v>
       </c>
-      <c r="O110" s="21">
+      <c r="O119" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="111" spans="1:19">
-      <c r="A111" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B111" s="16">
+    <row r="120" spans="1:15">
+      <c r="A120" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B120" s="16">
         <v>101400</v>
       </c>
-      <c r="C111" s="16">
-        <v>1</v>
-      </c>
-      <c r="D111" s="16" t="str">
-        <f t="shared" ref="D111:D115" si="12">D110</f>
+      <c r="C120" s="16">
+        <v>1</v>
+      </c>
+      <c r="D120" s="16" t="str">
+        <f t="shared" ref="D120:D124" si="12">D119</f>
         <v>埃及艳后</v>
       </c>
-      <c r="E111" s="16">
+      <c r="E120" s="16">
         <v>101400001</v>
       </c>
-      <c r="F111" s="16" t="str">
+      <c r="F120" s="16" t="str">
         <f t="shared" si="11"/>
         <v>Cleopatra</v>
       </c>
-      <c r="G111" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="H111" s="19">
+      <c r="G120" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H120" s="17">
         <v>11</v>
       </c>
-      <c r="I111" s="19">
-        <v>0</v>
-      </c>
-      <c r="J111" s="19">
-        <v>-1</v>
-      </c>
-      <c r="K111" s="19">
-        <v>0</v>
-      </c>
-      <c r="L111" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="M111" s="19">
-        <v>0</v>
-      </c>
-      <c r="N111" s="20">
+      <c r="I120" s="17">
+        <v>0</v>
+      </c>
+      <c r="J120" s="17">
+        <v>-1</v>
+      </c>
+      <c r="K120" s="17">
+        <v>0</v>
+      </c>
+      <c r="L120" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="M120" s="17">
+        <v>0</v>
+      </c>
+      <c r="N120" s="20">
         <v>500</v>
       </c>
-      <c r="O111" s="21">
+      <c r="O120" s="21">
         <v>1980000</v>
       </c>
     </row>
-    <row r="112" spans="1:19">
-      <c r="A112" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B112" s="16">
+    <row r="121" spans="1:15">
+      <c r="A121" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B121" s="16">
         <v>101400</v>
       </c>
-      <c r="C112" s="16">
-        <v>1</v>
-      </c>
-      <c r="D112" s="16" t="str">
+      <c r="C121" s="16">
+        <v>1</v>
+      </c>
+      <c r="D121" s="16" t="str">
         <f t="shared" si="12"/>
         <v>埃及艳后</v>
       </c>
-      <c r="E112" s="16">
+      <c r="E121" s="16">
         <v>101400001</v>
       </c>